--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="136">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -368,6 +368,12 @@
   </si>
   <si>
     <t>['44', '55']</t>
+  </si>
+  <si>
+    <t>['18']</t>
+  </si>
+  <si>
+    <t>['5', '23']</t>
   </si>
   <si>
     <t>['18', '26', '48']</t>
@@ -777,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP31"/>
+  <dimension ref="A1:BP34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1033,7 +1039,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1114,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1445,7 +1451,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1651,7 +1657,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1732,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="AQ5">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1857,7 +1863,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1935,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
         <v>3</v>
@@ -2063,7 +2069,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2141,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
         <v>3</v>
@@ -2269,7 +2275,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2475,7 +2481,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2681,7 +2687,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2759,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ10">
         <v>1.5</v>
@@ -3093,7 +3099,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3505,7 +3511,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -4535,7 +4541,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -5153,7 +5159,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -5359,7 +5365,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -5565,7 +5571,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -5977,7 +5983,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -6389,7 +6395,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -7163,6 +7169,624 @@
         <v>0</v>
       </c>
       <c r="BP31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7820345</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45689.70833333334</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s">
+        <v>85</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32" t="s">
+        <v>118</v>
+      </c>
+      <c r="P32" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>3</v>
+      </c>
+      <c r="AP32">
+        <v>1.5</v>
+      </c>
+      <c r="AQ32">
+        <v>1.5</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>-1</v>
+      </c>
+      <c r="AV32">
+        <v>-1</v>
+      </c>
+      <c r="AW32">
+        <v>-1</v>
+      </c>
+      <c r="AX32">
+        <v>-1</v>
+      </c>
+      <c r="AY32">
+        <v>-1</v>
+      </c>
+      <c r="AZ32">
+        <v>-1</v>
+      </c>
+      <c r="BA32">
+        <v>-1</v>
+      </c>
+      <c r="BB32">
+        <v>-1</v>
+      </c>
+      <c r="BC32">
+        <v>-1</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>0</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7820346</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45689.79166666666</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" t="s">
+        <v>87</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>100</v>
+      </c>
+      <c r="P33" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>0</v>
+      </c>
+      <c r="AO33">
+        <v>3</v>
+      </c>
+      <c r="AP33">
+        <v>0.5</v>
+      </c>
+      <c r="AQ33">
+        <v>2</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33">
+        <v>-1</v>
+      </c>
+      <c r="AV33">
+        <v>-1</v>
+      </c>
+      <c r="AW33">
+        <v>-1</v>
+      </c>
+      <c r="AX33">
+        <v>-1</v>
+      </c>
+      <c r="AY33">
+        <v>-1</v>
+      </c>
+      <c r="AZ33">
+        <v>-1</v>
+      </c>
+      <c r="BA33">
+        <v>-1</v>
+      </c>
+      <c r="BB33">
+        <v>-1</v>
+      </c>
+      <c r="BC33">
+        <v>-1</v>
+      </c>
+      <c r="BD33">
+        <v>0</v>
+      </c>
+      <c r="BE33">
+        <v>0</v>
+      </c>
+      <c r="BF33">
+        <v>0</v>
+      </c>
+      <c r="BG33">
+        <v>0</v>
+      </c>
+      <c r="BH33">
+        <v>0</v>
+      </c>
+      <c r="BI33">
+        <v>0</v>
+      </c>
+      <c r="BJ33">
+        <v>0</v>
+      </c>
+      <c r="BK33">
+        <v>0</v>
+      </c>
+      <c r="BL33">
+        <v>0</v>
+      </c>
+      <c r="BM33">
+        <v>0</v>
+      </c>
+      <c r="BN33">
+        <v>0</v>
+      </c>
+      <c r="BO33">
+        <v>0</v>
+      </c>
+      <c r="BP33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7820347</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45689.875</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H34" t="s">
+        <v>88</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>2</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>2</v>
+      </c>
+      <c r="O34" t="s">
+        <v>119</v>
+      </c>
+      <c r="P34" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>1.5</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>-1</v>
+      </c>
+      <c r="AV34">
+        <v>-1</v>
+      </c>
+      <c r="AW34">
+        <v>-1</v>
+      </c>
+      <c r="AX34">
+        <v>-1</v>
+      </c>
+      <c r="AY34">
+        <v>-1</v>
+      </c>
+      <c r="AZ34">
+        <v>-1</v>
+      </c>
+      <c r="BA34">
+        <v>-1</v>
+      </c>
+      <c r="BB34">
+        <v>-1</v>
+      </c>
+      <c r="BC34">
+        <v>-1</v>
+      </c>
+      <c r="BD34">
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="BF34">
+        <v>0</v>
+      </c>
+      <c r="BG34">
+        <v>0</v>
+      </c>
+      <c r="BH34">
+        <v>0</v>
+      </c>
+      <c r="BI34">
+        <v>0</v>
+      </c>
+      <c r="BJ34">
+        <v>0</v>
+      </c>
+      <c r="BK34">
+        <v>0</v>
+      </c>
+      <c r="BL34">
+        <v>0</v>
+      </c>
+      <c r="BM34">
+        <v>0</v>
+      </c>
+      <c r="BN34">
+        <v>0</v>
+      </c>
+      <c r="BO34">
+        <v>0</v>
+      </c>
+      <c r="BP34">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="146">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -376,6 +376,27 @@
     <t>['5', '23']</t>
   </si>
   <si>
+    <t>['19', '68']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['43', '51']</t>
+  </si>
+  <si>
+    <t>['10', '81']</t>
+  </si>
+  <si>
+    <t>['65', '79']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['34', '58']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -422,6 +443,15 @@
   </si>
   <si>
     <t>['4', '25', '49', '68', '84']</t>
+  </si>
+  <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['7', '17', '45+2']</t>
   </si>
 </sst>
 </file>
@@ -783,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP34"/>
+  <dimension ref="A1:BP44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1039,7 +1069,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1451,7 +1481,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1529,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4">
         <v>3</v>
@@ -1657,7 +1687,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1735,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
         <v>1.5</v>
@@ -1863,7 +1893,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2069,7 +2099,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2150,7 +2180,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2275,7 +2305,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2481,7 +2511,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2559,10 +2589,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2687,7 +2717,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2971,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -3099,7 +3129,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3511,7 +3541,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3795,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4541,7 +4571,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -5159,7 +5189,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -5240,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="AQ22">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5365,7 +5395,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -5571,7 +5601,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -5983,7 +6013,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -6395,7 +6425,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -7787,6 +7817,2066 @@
         <v>0</v>
       </c>
       <c r="BP34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7820348</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45690.70833333334</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>79</v>
+      </c>
+      <c r="H35" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>100</v>
+      </c>
+      <c r="P35" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35">
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
+        <v>3</v>
+      </c>
+      <c r="AO35">
+        <v>1</v>
+      </c>
+      <c r="AP35">
+        <v>2</v>
+      </c>
+      <c r="AQ35">
+        <v>1</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
+        <v>-1</v>
+      </c>
+      <c r="AV35">
+        <v>-1</v>
+      </c>
+      <c r="AW35">
+        <v>-1</v>
+      </c>
+      <c r="AX35">
+        <v>-1</v>
+      </c>
+      <c r="AY35">
+        <v>-1</v>
+      </c>
+      <c r="AZ35">
+        <v>-1</v>
+      </c>
+      <c r="BA35">
+        <v>-1</v>
+      </c>
+      <c r="BB35">
+        <v>-1</v>
+      </c>
+      <c r="BC35">
+        <v>-1</v>
+      </c>
+      <c r="BD35">
+        <v>0</v>
+      </c>
+      <c r="BE35">
+        <v>0</v>
+      </c>
+      <c r="BF35">
+        <v>0</v>
+      </c>
+      <c r="BG35">
+        <v>0</v>
+      </c>
+      <c r="BH35">
+        <v>0</v>
+      </c>
+      <c r="BI35">
+        <v>0</v>
+      </c>
+      <c r="BJ35">
+        <v>0</v>
+      </c>
+      <c r="BK35">
+        <v>0</v>
+      </c>
+      <c r="BL35">
+        <v>0</v>
+      </c>
+      <c r="BM35">
+        <v>0</v>
+      </c>
+      <c r="BN35">
+        <v>0</v>
+      </c>
+      <c r="BO35">
+        <v>0</v>
+      </c>
+      <c r="BP35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7820349</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45690.80208333334</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+      <c r="G36" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" t="s">
+        <v>93</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36">
+        <v>2</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36" t="s">
+        <v>120</v>
+      </c>
+      <c r="P36" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>1</v>
+      </c>
+      <c r="AO36">
+        <v>1</v>
+      </c>
+      <c r="AP36">
+        <v>2</v>
+      </c>
+      <c r="AQ36">
+        <v>0.5</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>-1</v>
+      </c>
+      <c r="AV36">
+        <v>-1</v>
+      </c>
+      <c r="AW36">
+        <v>-1</v>
+      </c>
+      <c r="AX36">
+        <v>-1</v>
+      </c>
+      <c r="AY36">
+        <v>-1</v>
+      </c>
+      <c r="AZ36">
+        <v>-1</v>
+      </c>
+      <c r="BA36">
+        <v>-1</v>
+      </c>
+      <c r="BB36">
+        <v>-1</v>
+      </c>
+      <c r="BC36">
+        <v>-1</v>
+      </c>
+      <c r="BD36">
+        <v>0</v>
+      </c>
+      <c r="BE36">
+        <v>0</v>
+      </c>
+      <c r="BF36">
+        <v>0</v>
+      </c>
+      <c r="BG36">
+        <v>0</v>
+      </c>
+      <c r="BH36">
+        <v>0</v>
+      </c>
+      <c r="BI36">
+        <v>0</v>
+      </c>
+      <c r="BJ36">
+        <v>0</v>
+      </c>
+      <c r="BK36">
+        <v>0</v>
+      </c>
+      <c r="BL36">
+        <v>0</v>
+      </c>
+      <c r="BM36">
+        <v>0</v>
+      </c>
+      <c r="BN36">
+        <v>0</v>
+      </c>
+      <c r="BO36">
+        <v>0</v>
+      </c>
+      <c r="BP36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7820350</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45690.80208333334</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" t="s">
+        <v>72</v>
+      </c>
+      <c r="H37" t="s">
+        <v>96</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37" t="s">
+        <v>121</v>
+      </c>
+      <c r="P37" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <v>0</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>1.5</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37">
+        <v>-1</v>
+      </c>
+      <c r="AV37">
+        <v>-1</v>
+      </c>
+      <c r="AW37">
+        <v>-1</v>
+      </c>
+      <c r="AX37">
+        <v>-1</v>
+      </c>
+      <c r="AY37">
+        <v>-1</v>
+      </c>
+      <c r="AZ37">
+        <v>-1</v>
+      </c>
+      <c r="BA37">
+        <v>-1</v>
+      </c>
+      <c r="BB37">
+        <v>-1</v>
+      </c>
+      <c r="BC37">
+        <v>-1</v>
+      </c>
+      <c r="BD37">
+        <v>0</v>
+      </c>
+      <c r="BE37">
+        <v>0</v>
+      </c>
+      <c r="BF37">
+        <v>0</v>
+      </c>
+      <c r="BG37">
+        <v>0</v>
+      </c>
+      <c r="BH37">
+        <v>0</v>
+      </c>
+      <c r="BI37">
+        <v>0</v>
+      </c>
+      <c r="BJ37">
+        <v>0</v>
+      </c>
+      <c r="BK37">
+        <v>0</v>
+      </c>
+      <c r="BL37">
+        <v>0</v>
+      </c>
+      <c r="BM37">
+        <v>0</v>
+      </c>
+      <c r="BN37">
+        <v>0</v>
+      </c>
+      <c r="BO37">
+        <v>0</v>
+      </c>
+      <c r="BP37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7820351</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45690.89583333334</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38" t="s">
+        <v>81</v>
+      </c>
+      <c r="H38" t="s">
+        <v>90</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>2</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>2</v>
+      </c>
+      <c r="O38" t="s">
+        <v>122</v>
+      </c>
+      <c r="P38" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>3</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>3</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>-1</v>
+      </c>
+      <c r="AV38">
+        <v>-1</v>
+      </c>
+      <c r="AW38">
+        <v>-1</v>
+      </c>
+      <c r="AX38">
+        <v>-1</v>
+      </c>
+      <c r="AY38">
+        <v>-1</v>
+      </c>
+      <c r="AZ38">
+        <v>-1</v>
+      </c>
+      <c r="BA38">
+        <v>-1</v>
+      </c>
+      <c r="BB38">
+        <v>-1</v>
+      </c>
+      <c r="BC38">
+        <v>-1</v>
+      </c>
+      <c r="BD38">
+        <v>0</v>
+      </c>
+      <c r="BE38">
+        <v>0</v>
+      </c>
+      <c r="BF38">
+        <v>0</v>
+      </c>
+      <c r="BG38">
+        <v>0</v>
+      </c>
+      <c r="BH38">
+        <v>0</v>
+      </c>
+      <c r="BI38">
+        <v>0</v>
+      </c>
+      <c r="BJ38">
+        <v>0</v>
+      </c>
+      <c r="BK38">
+        <v>0</v>
+      </c>
+      <c r="BL38">
+        <v>0</v>
+      </c>
+      <c r="BM38">
+        <v>0</v>
+      </c>
+      <c r="BN38">
+        <v>0</v>
+      </c>
+      <c r="BO38">
+        <v>0</v>
+      </c>
+      <c r="BP38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7820352</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45690.89583333334</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39" t="s">
+        <v>76</v>
+      </c>
+      <c r="H39" t="s">
+        <v>92</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>2</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>2</v>
+      </c>
+      <c r="O39" t="s">
+        <v>123</v>
+      </c>
+      <c r="P39" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+      <c r="AN39">
+        <v>3</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>3</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39">
+        <v>-1</v>
+      </c>
+      <c r="AV39">
+        <v>-1</v>
+      </c>
+      <c r="AW39">
+        <v>-1</v>
+      </c>
+      <c r="AX39">
+        <v>-1</v>
+      </c>
+      <c r="AY39">
+        <v>-1</v>
+      </c>
+      <c r="AZ39">
+        <v>-1</v>
+      </c>
+      <c r="BA39">
+        <v>-1</v>
+      </c>
+      <c r="BB39">
+        <v>-1</v>
+      </c>
+      <c r="BC39">
+        <v>-1</v>
+      </c>
+      <c r="BD39">
+        <v>0</v>
+      </c>
+      <c r="BE39">
+        <v>0</v>
+      </c>
+      <c r="BF39">
+        <v>0</v>
+      </c>
+      <c r="BG39">
+        <v>0</v>
+      </c>
+      <c r="BH39">
+        <v>0</v>
+      </c>
+      <c r="BI39">
+        <v>0</v>
+      </c>
+      <c r="BJ39">
+        <v>0</v>
+      </c>
+      <c r="BK39">
+        <v>0</v>
+      </c>
+      <c r="BL39">
+        <v>0</v>
+      </c>
+      <c r="BM39">
+        <v>0</v>
+      </c>
+      <c r="BN39">
+        <v>0</v>
+      </c>
+      <c r="BO39">
+        <v>0</v>
+      </c>
+      <c r="BP39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7820354</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45691.70833333334</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40" t="s">
+        <v>73</v>
+      </c>
+      <c r="H40" t="s">
+        <v>84</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>2</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>3</v>
+      </c>
+      <c r="O40" t="s">
+        <v>124</v>
+      </c>
+      <c r="P40" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <v>0</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40">
+        <v>0</v>
+      </c>
+      <c r="AO40">
+        <v>0</v>
+      </c>
+      <c r="AP40">
+        <v>1.5</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40">
+        <v>-1</v>
+      </c>
+      <c r="AV40">
+        <v>-1</v>
+      </c>
+      <c r="AW40">
+        <v>-1</v>
+      </c>
+      <c r="AX40">
+        <v>-1</v>
+      </c>
+      <c r="AY40">
+        <v>-1</v>
+      </c>
+      <c r="AZ40">
+        <v>-1</v>
+      </c>
+      <c r="BA40">
+        <v>-1</v>
+      </c>
+      <c r="BB40">
+        <v>-1</v>
+      </c>
+      <c r="BC40">
+        <v>-1</v>
+      </c>
+      <c r="BD40">
+        <v>0</v>
+      </c>
+      <c r="BE40">
+        <v>0</v>
+      </c>
+      <c r="BF40">
+        <v>0</v>
+      </c>
+      <c r="BG40">
+        <v>0</v>
+      </c>
+      <c r="BH40">
+        <v>0</v>
+      </c>
+      <c r="BI40">
+        <v>0</v>
+      </c>
+      <c r="BJ40">
+        <v>0</v>
+      </c>
+      <c r="BK40">
+        <v>0</v>
+      </c>
+      <c r="BL40">
+        <v>0</v>
+      </c>
+      <c r="BM40">
+        <v>0</v>
+      </c>
+      <c r="BN40">
+        <v>0</v>
+      </c>
+      <c r="BO40">
+        <v>0</v>
+      </c>
+      <c r="BP40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:68">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>7820353</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45691.80208333334</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="G41" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41" t="s">
+        <v>94</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41" t="s">
+        <v>125</v>
+      </c>
+      <c r="P41" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41">
+        <v>0</v>
+      </c>
+      <c r="AI41">
+        <v>0</v>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
+      <c r="AN41">
+        <v>3</v>
+      </c>
+      <c r="AO41">
+        <v>0</v>
+      </c>
+      <c r="AP41">
+        <v>3</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41">
+        <v>-1</v>
+      </c>
+      <c r="AV41">
+        <v>-1</v>
+      </c>
+      <c r="AW41">
+        <v>-1</v>
+      </c>
+      <c r="AX41">
+        <v>-1</v>
+      </c>
+      <c r="AY41">
+        <v>-1</v>
+      </c>
+      <c r="AZ41">
+        <v>-1</v>
+      </c>
+      <c r="BA41">
+        <v>-1</v>
+      </c>
+      <c r="BB41">
+        <v>-1</v>
+      </c>
+      <c r="BC41">
+        <v>-1</v>
+      </c>
+      <c r="BD41">
+        <v>0</v>
+      </c>
+      <c r="BE41">
+        <v>0</v>
+      </c>
+      <c r="BF41">
+        <v>0</v>
+      </c>
+      <c r="BG41">
+        <v>0</v>
+      </c>
+      <c r="BH41">
+        <v>0</v>
+      </c>
+      <c r="BI41">
+        <v>0</v>
+      </c>
+      <c r="BJ41">
+        <v>0</v>
+      </c>
+      <c r="BK41">
+        <v>0</v>
+      </c>
+      <c r="BL41">
+        <v>0</v>
+      </c>
+      <c r="BM41">
+        <v>0</v>
+      </c>
+      <c r="BN41">
+        <v>0</v>
+      </c>
+      <c r="BO41">
+        <v>0</v>
+      </c>
+      <c r="BP41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:68">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>7820355</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45691.80208333334</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42" t="s">
+        <v>80</v>
+      </c>
+      <c r="H42" t="s">
+        <v>97</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>2</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>2</v>
+      </c>
+      <c r="O42" t="s">
+        <v>126</v>
+      </c>
+      <c r="P42" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42">
+        <v>0</v>
+      </c>
+      <c r="AI42">
+        <v>0</v>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>0</v>
+      </c>
+      <c r="AN42">
+        <v>3</v>
+      </c>
+      <c r="AO42">
+        <v>3</v>
+      </c>
+      <c r="AP42">
+        <v>3</v>
+      </c>
+      <c r="AQ42">
+        <v>1.5</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42">
+        <v>-1</v>
+      </c>
+      <c r="AV42">
+        <v>-1</v>
+      </c>
+      <c r="AW42">
+        <v>-1</v>
+      </c>
+      <c r="AX42">
+        <v>-1</v>
+      </c>
+      <c r="AY42">
+        <v>-1</v>
+      </c>
+      <c r="AZ42">
+        <v>-1</v>
+      </c>
+      <c r="BA42">
+        <v>-1</v>
+      </c>
+      <c r="BB42">
+        <v>-1</v>
+      </c>
+      <c r="BC42">
+        <v>-1</v>
+      </c>
+      <c r="BD42">
+        <v>0</v>
+      </c>
+      <c r="BE42">
+        <v>0</v>
+      </c>
+      <c r="BF42">
+        <v>0</v>
+      </c>
+      <c r="BG42">
+        <v>0</v>
+      </c>
+      <c r="BH42">
+        <v>0</v>
+      </c>
+      <c r="BI42">
+        <v>0</v>
+      </c>
+      <c r="BJ42">
+        <v>0</v>
+      </c>
+      <c r="BK42">
+        <v>0</v>
+      </c>
+      <c r="BL42">
+        <v>0</v>
+      </c>
+      <c r="BM42">
+        <v>0</v>
+      </c>
+      <c r="BN42">
+        <v>0</v>
+      </c>
+      <c r="BO42">
+        <v>0</v>
+      </c>
+      <c r="BP42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:68">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7820357</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45691.89583333334</v>
+      </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43" t="s">
+        <v>98</v>
+      </c>
+      <c r="H43" t="s">
+        <v>82</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43" t="s">
+        <v>113</v>
+      </c>
+      <c r="P43" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43">
+        <v>0</v>
+      </c>
+      <c r="AI43">
+        <v>0</v>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>0</v>
+      </c>
+      <c r="AN43">
+        <v>3</v>
+      </c>
+      <c r="AO43">
+        <v>3</v>
+      </c>
+      <c r="AP43">
+        <v>3</v>
+      </c>
+      <c r="AQ43">
+        <v>1.5</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43">
+        <v>-1</v>
+      </c>
+      <c r="AV43">
+        <v>-1</v>
+      </c>
+      <c r="AW43">
+        <v>-1</v>
+      </c>
+      <c r="AX43">
+        <v>-1</v>
+      </c>
+      <c r="AY43">
+        <v>-1</v>
+      </c>
+      <c r="AZ43">
+        <v>-1</v>
+      </c>
+      <c r="BA43">
+        <v>-1</v>
+      </c>
+      <c r="BB43">
+        <v>-1</v>
+      </c>
+      <c r="BC43">
+        <v>-1</v>
+      </c>
+      <c r="BD43">
+        <v>0</v>
+      </c>
+      <c r="BE43">
+        <v>0</v>
+      </c>
+      <c r="BF43">
+        <v>0</v>
+      </c>
+      <c r="BG43">
+        <v>0</v>
+      </c>
+      <c r="BH43">
+        <v>0</v>
+      </c>
+      <c r="BI43">
+        <v>0</v>
+      </c>
+      <c r="BJ43">
+        <v>0</v>
+      </c>
+      <c r="BK43">
+        <v>0</v>
+      </c>
+      <c r="BL43">
+        <v>0</v>
+      </c>
+      <c r="BM43">
+        <v>0</v>
+      </c>
+      <c r="BN43">
+        <v>0</v>
+      </c>
+      <c r="BO43">
+        <v>0</v>
+      </c>
+      <c r="BP43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:68">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>7820356</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="2">
+        <v>45691.89583333334</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44" t="s">
+        <v>89</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3</v>
+      </c>
+      <c r="K44">
+        <v>3</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>3</v>
+      </c>
+      <c r="N44">
+        <v>3</v>
+      </c>
+      <c r="O44" t="s">
+        <v>100</v>
+      </c>
+      <c r="P44" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44">
+        <v>0</v>
+      </c>
+      <c r="AI44">
+        <v>0</v>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>0</v>
+      </c>
+      <c r="AN44">
+        <v>1</v>
+      </c>
+      <c r="AO44">
+        <v>3</v>
+      </c>
+      <c r="AP44">
+        <v>0.5</v>
+      </c>
+      <c r="AQ44">
+        <v>3</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44">
+        <v>-1</v>
+      </c>
+      <c r="AV44">
+        <v>-1</v>
+      </c>
+      <c r="AW44">
+        <v>-1</v>
+      </c>
+      <c r="AX44">
+        <v>-1</v>
+      </c>
+      <c r="AY44">
+        <v>-1</v>
+      </c>
+      <c r="AZ44">
+        <v>-1</v>
+      </c>
+      <c r="BA44">
+        <v>-1</v>
+      </c>
+      <c r="BB44">
+        <v>-1</v>
+      </c>
+      <c r="BC44">
+        <v>-1</v>
+      </c>
+      <c r="BD44">
+        <v>0</v>
+      </c>
+      <c r="BE44">
+        <v>0</v>
+      </c>
+      <c r="BF44">
+        <v>0</v>
+      </c>
+      <c r="BG44">
+        <v>0</v>
+      </c>
+      <c r="BH44">
+        <v>0</v>
+      </c>
+      <c r="BI44">
+        <v>0</v>
+      </c>
+      <c r="BJ44">
+        <v>0</v>
+      </c>
+      <c r="BK44">
+        <v>0</v>
+      </c>
+      <c r="BL44">
+        <v>0</v>
+      </c>
+      <c r="BM44">
+        <v>0</v>
+      </c>
+      <c r="BN44">
+        <v>0</v>
+      </c>
+      <c r="BO44">
+        <v>0</v>
+      </c>
+      <c r="BP44">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="147">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -452,6 +452,9 @@
   </si>
   <si>
     <t>['7', '17', '45+2']</t>
+  </si>
+  <si>
+    <t>['38', '69', '78']</t>
   </si>
 </sst>
 </file>
@@ -813,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP44"/>
+  <dimension ref="A1:BP45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -9880,6 +9883,212 @@
         <v>0</v>
       </c>
     </row>
+    <row r="45" spans="1:68">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>7820359</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="2">
+        <v>45692.875</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45" t="s">
+        <v>99</v>
+      </c>
+      <c r="H45" t="s">
+        <v>86</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>3</v>
+      </c>
+      <c r="N45">
+        <v>3</v>
+      </c>
+      <c r="O45" t="s">
+        <v>100</v>
+      </c>
+      <c r="P45" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45">
+        <v>0</v>
+      </c>
+      <c r="AI45">
+        <v>0</v>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>0</v>
+      </c>
+      <c r="AN45">
+        <v>0</v>
+      </c>
+      <c r="AO45">
+        <v>3</v>
+      </c>
+      <c r="AP45">
+        <v>0</v>
+      </c>
+      <c r="AQ45">
+        <v>3</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45">
+        <v>-1</v>
+      </c>
+      <c r="AV45">
+        <v>-1</v>
+      </c>
+      <c r="AW45">
+        <v>-1</v>
+      </c>
+      <c r="AX45">
+        <v>-1</v>
+      </c>
+      <c r="AY45">
+        <v>-1</v>
+      </c>
+      <c r="AZ45">
+        <v>-1</v>
+      </c>
+      <c r="BA45">
+        <v>-1</v>
+      </c>
+      <c r="BB45">
+        <v>-1</v>
+      </c>
+      <c r="BC45">
+        <v>-1</v>
+      </c>
+      <c r="BD45">
+        <v>0</v>
+      </c>
+      <c r="BE45">
+        <v>0</v>
+      </c>
+      <c r="BF45">
+        <v>0</v>
+      </c>
+      <c r="BG45">
+        <v>0</v>
+      </c>
+      <c r="BH45">
+        <v>0</v>
+      </c>
+      <c r="BI45">
+        <v>0</v>
+      </c>
+      <c r="BJ45">
+        <v>0</v>
+      </c>
+      <c r="BK45">
+        <v>0</v>
+      </c>
+      <c r="BL45">
+        <v>0</v>
+      </c>
+      <c r="BM45">
+        <v>0</v>
+      </c>
+      <c r="BN45">
+        <v>0</v>
+      </c>
+      <c r="BO45">
+        <v>0</v>
+      </c>
+      <c r="BP45">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="151">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -397,6 +397,12 @@
     <t>['34', '58']</t>
   </si>
   <si>
+    <t>['90+7']</t>
+  </si>
+  <si>
+    <t>['55']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -455,6 +461,12 @@
   </si>
   <si>
     <t>['38', '69', '78']</t>
+  </si>
+  <si>
+    <t>['28', '35', '89']</t>
+  </si>
+  <si>
+    <t>['15']</t>
   </si>
 </sst>
 </file>
@@ -816,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP45"/>
+  <dimension ref="A1:BP47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1072,7 +1084,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1484,7 +1496,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1690,7 +1702,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1896,7 +1908,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2102,7 +2114,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2308,7 +2320,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2514,7 +2526,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2720,7 +2732,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -3132,7 +3144,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3544,7 +3556,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -4574,7 +4586,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -5067,7 +5079,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5192,7 +5204,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -5398,7 +5410,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -5604,7 +5616,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -6016,7 +6028,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -6428,7 +6440,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -8076,7 +8088,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -8900,7 +8912,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -9724,7 +9736,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -9930,7 +9942,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -10086,6 +10098,418 @@
         <v>0</v>
       </c>
       <c r="BP45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:68">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>7820360</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="2">
+        <v>45694.70833333334</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46" t="s">
+        <v>96</v>
+      </c>
+      <c r="H46" t="s">
+        <v>75</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2</v>
+      </c>
+      <c r="K46">
+        <v>2</v>
+      </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46">
+        <v>3</v>
+      </c>
+      <c r="N46">
+        <v>4</v>
+      </c>
+      <c r="O46" t="s">
+        <v>127</v>
+      </c>
+      <c r="P46" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46">
+        <v>0</v>
+      </c>
+      <c r="AI46">
+        <v>0</v>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>0</v>
+      </c>
+      <c r="AN46">
+        <v>0</v>
+      </c>
+      <c r="AO46">
+        <v>1</v>
+      </c>
+      <c r="AP46">
+        <v>0</v>
+      </c>
+      <c r="AQ46">
+        <v>2</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46">
+        <v>-1</v>
+      </c>
+      <c r="AV46">
+        <v>-1</v>
+      </c>
+      <c r="AW46">
+        <v>-1</v>
+      </c>
+      <c r="AX46">
+        <v>-1</v>
+      </c>
+      <c r="AY46">
+        <v>-1</v>
+      </c>
+      <c r="AZ46">
+        <v>-1</v>
+      </c>
+      <c r="BA46">
+        <v>-1</v>
+      </c>
+      <c r="BB46">
+        <v>-1</v>
+      </c>
+      <c r="BC46">
+        <v>-1</v>
+      </c>
+      <c r="BD46">
+        <v>0</v>
+      </c>
+      <c r="BE46">
+        <v>0</v>
+      </c>
+      <c r="BF46">
+        <v>0</v>
+      </c>
+      <c r="BG46">
+        <v>0</v>
+      </c>
+      <c r="BH46">
+        <v>0</v>
+      </c>
+      <c r="BI46">
+        <v>0</v>
+      </c>
+      <c r="BJ46">
+        <v>0</v>
+      </c>
+      <c r="BK46">
+        <v>0</v>
+      </c>
+      <c r="BL46">
+        <v>0</v>
+      </c>
+      <c r="BM46">
+        <v>0</v>
+      </c>
+      <c r="BN46">
+        <v>0</v>
+      </c>
+      <c r="BO46">
+        <v>0</v>
+      </c>
+      <c r="BP46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:68">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>7820361</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="2">
+        <v>45694.83333333334</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47" t="s">
+        <v>88</v>
+      </c>
+      <c r="H47" t="s">
+        <v>78</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>2</v>
+      </c>
+      <c r="O47" t="s">
+        <v>128</v>
+      </c>
+      <c r="P47" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47">
+        <v>0</v>
+      </c>
+      <c r="AI47">
+        <v>0</v>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>0</v>
+      </c>
+      <c r="AN47">
+        <v>1</v>
+      </c>
+      <c r="AO47">
+        <v>1</v>
+      </c>
+      <c r="AP47">
+        <v>1</v>
+      </c>
+      <c r="AQ47">
+        <v>1</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47">
+        <v>-1</v>
+      </c>
+      <c r="AV47">
+        <v>-1</v>
+      </c>
+      <c r="AW47">
+        <v>-1</v>
+      </c>
+      <c r="AX47">
+        <v>-1</v>
+      </c>
+      <c r="AY47">
+        <v>-1</v>
+      </c>
+      <c r="AZ47">
+        <v>-1</v>
+      </c>
+      <c r="BA47">
+        <v>-1</v>
+      </c>
+      <c r="BB47">
+        <v>-1</v>
+      </c>
+      <c r="BC47">
+        <v>-1</v>
+      </c>
+      <c r="BD47">
+        <v>0</v>
+      </c>
+      <c r="BE47">
+        <v>0</v>
+      </c>
+      <c r="BF47">
+        <v>0</v>
+      </c>
+      <c r="BG47">
+        <v>0</v>
+      </c>
+      <c r="BH47">
+        <v>0</v>
+      </c>
+      <c r="BI47">
+        <v>0</v>
+      </c>
+      <c r="BJ47">
+        <v>0</v>
+      </c>
+      <c r="BK47">
+        <v>0</v>
+      </c>
+      <c r="BL47">
+        <v>0</v>
+      </c>
+      <c r="BM47">
+        <v>0</v>
+      </c>
+      <c r="BN47">
+        <v>0</v>
+      </c>
+      <c r="BO47">
+        <v>0</v>
+      </c>
+      <c r="BP47">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="161">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -412,6 +412,15 @@
     <t>['80', '83']</t>
   </si>
   <si>
+    <t>['36', '53', '61']</t>
+  </si>
+  <si>
+    <t>['51', '90+2']</t>
+  </si>
+  <si>
+    <t>['16', '87']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -485,6 +494,9 @@
   </si>
   <si>
     <t>['6']</t>
+  </si>
+  <si>
+    <t>['49']</t>
   </si>
 </sst>
 </file>
@@ -846,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP52"/>
+  <dimension ref="A1:BP56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1102,7 +1114,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1514,7 +1526,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1720,7 +1732,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -1926,7 +1938,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2132,7 +2144,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2338,7 +2350,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2544,7 +2556,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2750,7 +2762,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -2831,7 +2843,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ10">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3162,7 +3174,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3574,7 +3586,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q14">
         <v>6.5</v>
@@ -4604,7 +4616,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5222,7 +5234,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5300,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ22">
         <v>1.5</v>
@@ -5428,7 +5440,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5509,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AQ23">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5634,7 +5646,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -5715,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="AQ24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6046,7 +6058,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6127,7 +6139,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6458,7 +6470,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7157,7 +7169,7 @@
         <v>3</v>
       </c>
       <c r="AQ31">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR31">
         <v>1.4</v>
@@ -8106,7 +8118,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8930,7 +8942,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9754,7 +9766,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -9960,7 +9972,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10166,7 +10178,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10372,7 +10384,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10578,7 +10590,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11196,7 +11208,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11402,7 +11414,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11559,6 +11571,830 @@
       </c>
       <c r="BP52">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:68">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>7820368</v>
+      </c>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="2">
+        <v>45696.75</v>
+      </c>
+      <c r="F53">
+        <v>4</v>
+      </c>
+      <c r="G53" t="s">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s">
+        <v>79</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53" t="s">
+        <v>100</v>
+      </c>
+      <c r="P53" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q53">
+        <v>3.2</v>
+      </c>
+      <c r="R53">
+        <v>1.8</v>
+      </c>
+      <c r="S53">
+        <v>4.75</v>
+      </c>
+      <c r="T53">
+        <v>1.67</v>
+      </c>
+      <c r="U53">
+        <v>2.1</v>
+      </c>
+      <c r="V53">
+        <v>4.33</v>
+      </c>
+      <c r="W53">
+        <v>1.2</v>
+      </c>
+      <c r="X53">
+        <v>15</v>
+      </c>
+      <c r="Y53">
+        <v>1.03</v>
+      </c>
+      <c r="Z53">
+        <v>2.3</v>
+      </c>
+      <c r="AA53">
+        <v>2.78</v>
+      </c>
+      <c r="AB53">
+        <v>3.88</v>
+      </c>
+      <c r="AC53">
+        <v>1.15</v>
+      </c>
+      <c r="AD53">
+        <v>5.4</v>
+      </c>
+      <c r="AE53">
+        <v>1.61</v>
+      </c>
+      <c r="AF53">
+        <v>2.15</v>
+      </c>
+      <c r="AG53">
+        <v>3.1</v>
+      </c>
+      <c r="AH53">
+        <v>1.36</v>
+      </c>
+      <c r="AI53">
+        <v>2.38</v>
+      </c>
+      <c r="AJ53">
+        <v>1.53</v>
+      </c>
+      <c r="AK53">
+        <v>1.27</v>
+      </c>
+      <c r="AL53">
+        <v>1.39</v>
+      </c>
+      <c r="AM53">
+        <v>1.62</v>
+      </c>
+      <c r="AN53">
+        <v>0</v>
+      </c>
+      <c r="AO53">
+        <v>3</v>
+      </c>
+      <c r="AP53">
+        <v>0.5</v>
+      </c>
+      <c r="AQ53">
+        <v>2</v>
+      </c>
+      <c r="AR53">
+        <v>1.58</v>
+      </c>
+      <c r="AS53">
+        <v>1.18</v>
+      </c>
+      <c r="AT53">
+        <v>2.76</v>
+      </c>
+      <c r="AU53">
+        <v>4</v>
+      </c>
+      <c r="AV53">
+        <v>0</v>
+      </c>
+      <c r="AW53">
+        <v>6</v>
+      </c>
+      <c r="AX53">
+        <v>3</v>
+      </c>
+      <c r="AY53">
+        <v>11</v>
+      </c>
+      <c r="AZ53">
+        <v>4</v>
+      </c>
+      <c r="BA53">
+        <v>6</v>
+      </c>
+      <c r="BB53">
+        <v>5</v>
+      </c>
+      <c r="BC53">
+        <v>11</v>
+      </c>
+      <c r="BD53">
+        <v>1.58</v>
+      </c>
+      <c r="BE53">
+        <v>6.5</v>
+      </c>
+      <c r="BF53">
+        <v>2.63</v>
+      </c>
+      <c r="BG53">
+        <v>1.49</v>
+      </c>
+      <c r="BH53">
+        <v>2.4</v>
+      </c>
+      <c r="BI53">
+        <v>1.82</v>
+      </c>
+      <c r="BJ53">
+        <v>1.86</v>
+      </c>
+      <c r="BK53">
+        <v>2.3</v>
+      </c>
+      <c r="BL53">
+        <v>1.53</v>
+      </c>
+      <c r="BM53">
+        <v>3</v>
+      </c>
+      <c r="BN53">
+        <v>1.32</v>
+      </c>
+      <c r="BO53">
+        <v>4.1</v>
+      </c>
+      <c r="BP53">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:68">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>7820367</v>
+      </c>
+      <c r="C54" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="2">
+        <v>45696.8125</v>
+      </c>
+      <c r="F54">
+        <v>4</v>
+      </c>
+      <c r="G54" t="s">
+        <v>87</v>
+      </c>
+      <c r="H54" t="s">
+        <v>99</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54">
+        <v>3</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>4</v>
+      </c>
+      <c r="O54" t="s">
+        <v>132</v>
+      </c>
+      <c r="P54" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q54">
+        <v>2.63</v>
+      </c>
+      <c r="R54">
+        <v>1.91</v>
+      </c>
+      <c r="S54">
+        <v>5.5</v>
+      </c>
+      <c r="T54">
+        <v>1.57</v>
+      </c>
+      <c r="U54">
+        <v>2.25</v>
+      </c>
+      <c r="V54">
+        <v>3.75</v>
+      </c>
+      <c r="W54">
+        <v>1.25</v>
+      </c>
+      <c r="X54">
+        <v>13</v>
+      </c>
+      <c r="Y54">
+        <v>1.04</v>
+      </c>
+      <c r="Z54">
+        <v>1.85</v>
+      </c>
+      <c r="AA54">
+        <v>3.25</v>
+      </c>
+      <c r="AB54">
+        <v>4.75</v>
+      </c>
+      <c r="AC54">
+        <v>1.12</v>
+      </c>
+      <c r="AD54">
+        <v>6.4</v>
+      </c>
+      <c r="AE54">
+        <v>1.55</v>
+      </c>
+      <c r="AF54">
+        <v>2.37</v>
+      </c>
+      <c r="AG54">
+        <v>2.7</v>
+      </c>
+      <c r="AH54">
+        <v>1.44</v>
+      </c>
+      <c r="AI54">
+        <v>2.25</v>
+      </c>
+      <c r="AJ54">
+        <v>1.57</v>
+      </c>
+      <c r="AK54">
+        <v>1.19</v>
+      </c>
+      <c r="AL54">
+        <v>1.34</v>
+      </c>
+      <c r="AM54">
+        <v>1.87</v>
+      </c>
+      <c r="AN54">
+        <v>3</v>
+      </c>
+      <c r="AO54">
+        <v>1.5</v>
+      </c>
+      <c r="AP54">
+        <v>3</v>
+      </c>
+      <c r="AQ54">
+        <v>1</v>
+      </c>
+      <c r="AR54">
+        <v>1.05</v>
+      </c>
+      <c r="AS54">
+        <v>1.41</v>
+      </c>
+      <c r="AT54">
+        <v>2.46</v>
+      </c>
+      <c r="AU54">
+        <v>7</v>
+      </c>
+      <c r="AV54">
+        <v>8</v>
+      </c>
+      <c r="AW54">
+        <v>4</v>
+      </c>
+      <c r="AX54">
+        <v>6</v>
+      </c>
+      <c r="AY54">
+        <v>12</v>
+      </c>
+      <c r="AZ54">
+        <v>15</v>
+      </c>
+      <c r="BA54">
+        <v>4</v>
+      </c>
+      <c r="BB54">
+        <v>4</v>
+      </c>
+      <c r="BC54">
+        <v>8</v>
+      </c>
+      <c r="BD54">
+        <v>1.5</v>
+      </c>
+      <c r="BE54">
+        <v>6.75</v>
+      </c>
+      <c r="BF54">
+        <v>2.8</v>
+      </c>
+      <c r="BG54">
+        <v>1.36</v>
+      </c>
+      <c r="BH54">
+        <v>2.85</v>
+      </c>
+      <c r="BI54">
+        <v>1.6</v>
+      </c>
+      <c r="BJ54">
+        <v>2.17</v>
+      </c>
+      <c r="BK54">
+        <v>1.98</v>
+      </c>
+      <c r="BL54">
+        <v>1.72</v>
+      </c>
+      <c r="BM54">
+        <v>2.5</v>
+      </c>
+      <c r="BN54">
+        <v>1.46</v>
+      </c>
+      <c r="BO54">
+        <v>3.3</v>
+      </c>
+      <c r="BP54">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:68">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>7820369</v>
+      </c>
+      <c r="C55" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="2">
+        <v>45696.84375</v>
+      </c>
+      <c r="F55">
+        <v>4</v>
+      </c>
+      <c r="G55" t="s">
+        <v>95</v>
+      </c>
+      <c r="H55" t="s">
+        <v>76</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>2</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>2</v>
+      </c>
+      <c r="O55" t="s">
+        <v>133</v>
+      </c>
+      <c r="P55" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q55">
+        <v>2.4</v>
+      </c>
+      <c r="R55">
+        <v>2</v>
+      </c>
+      <c r="S55">
+        <v>6</v>
+      </c>
+      <c r="T55">
+        <v>1.53</v>
+      </c>
+      <c r="U55">
+        <v>2.38</v>
+      </c>
+      <c r="V55">
+        <v>3.5</v>
+      </c>
+      <c r="W55">
+        <v>1.29</v>
+      </c>
+      <c r="X55">
+        <v>11</v>
+      </c>
+      <c r="Y55">
+        <v>1.05</v>
+      </c>
+      <c r="Z55">
+        <v>1.7</v>
+      </c>
+      <c r="AA55">
+        <v>3.7</v>
+      </c>
+      <c r="AB55">
+        <v>4.75</v>
+      </c>
+      <c r="AC55">
+        <v>1.09</v>
+      </c>
+      <c r="AD55">
+        <v>7.4</v>
+      </c>
+      <c r="AE55">
+        <v>1.46</v>
+      </c>
+      <c r="AF55">
+        <v>2.6</v>
+      </c>
+      <c r="AG55">
+        <v>2.35</v>
+      </c>
+      <c r="AH55">
+        <v>1.57</v>
+      </c>
+      <c r="AI55">
+        <v>2.25</v>
+      </c>
+      <c r="AJ55">
+        <v>1.57</v>
+      </c>
+      <c r="AK55">
+        <v>1.15</v>
+      </c>
+      <c r="AL55">
+        <v>1.29</v>
+      </c>
+      <c r="AM55">
+        <v>2.1</v>
+      </c>
+      <c r="AN55">
+        <v>3</v>
+      </c>
+      <c r="AO55">
+        <v>3</v>
+      </c>
+      <c r="AP55">
+        <v>3</v>
+      </c>
+      <c r="AQ55">
+        <v>1.5</v>
+      </c>
+      <c r="AR55">
+        <v>1.6</v>
+      </c>
+      <c r="AS55">
+        <v>0.77</v>
+      </c>
+      <c r="AT55">
+        <v>2.37</v>
+      </c>
+      <c r="AU55">
+        <v>6</v>
+      </c>
+      <c r="AV55">
+        <v>4</v>
+      </c>
+      <c r="AW55">
+        <v>8</v>
+      </c>
+      <c r="AX55">
+        <v>5</v>
+      </c>
+      <c r="AY55">
+        <v>16</v>
+      </c>
+      <c r="AZ55">
+        <v>9</v>
+      </c>
+      <c r="BA55">
+        <v>2</v>
+      </c>
+      <c r="BB55">
+        <v>6</v>
+      </c>
+      <c r="BC55">
+        <v>8</v>
+      </c>
+      <c r="BD55">
+        <v>1.4</v>
+      </c>
+      <c r="BE55">
+        <v>7</v>
+      </c>
+      <c r="BF55">
+        <v>3.3</v>
+      </c>
+      <c r="BG55">
+        <v>1.4</v>
+      </c>
+      <c r="BH55">
+        <v>2.7</v>
+      </c>
+      <c r="BI55">
+        <v>1.66</v>
+      </c>
+      <c r="BJ55">
+        <v>2.06</v>
+      </c>
+      <c r="BK55">
+        <v>2.06</v>
+      </c>
+      <c r="BL55">
+        <v>1.66</v>
+      </c>
+      <c r="BM55">
+        <v>2.6</v>
+      </c>
+      <c r="BN55">
+        <v>1.43</v>
+      </c>
+      <c r="BO55">
+        <v>3.4</v>
+      </c>
+      <c r="BP55">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:68">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>7820370</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="2">
+        <v>45696.92708333334</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56" t="s">
+        <v>97</v>
+      </c>
+      <c r="H56" t="s">
+        <v>83</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>2</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>2</v>
+      </c>
+      <c r="O56" t="s">
+        <v>134</v>
+      </c>
+      <c r="P56" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q56">
+        <v>2.75</v>
+      </c>
+      <c r="R56">
+        <v>2.05</v>
+      </c>
+      <c r="S56">
+        <v>4.5</v>
+      </c>
+      <c r="T56">
+        <v>1.5</v>
+      </c>
+      <c r="U56">
+        <v>2.5</v>
+      </c>
+      <c r="V56">
+        <v>3.4</v>
+      </c>
+      <c r="W56">
+        <v>1.3</v>
+      </c>
+      <c r="X56">
+        <v>10</v>
+      </c>
+      <c r="Y56">
+        <v>1.06</v>
+      </c>
+      <c r="Z56">
+        <v>2</v>
+      </c>
+      <c r="AA56">
+        <v>3.5</v>
+      </c>
+      <c r="AB56">
+        <v>3.6</v>
+      </c>
+      <c r="AC56">
+        <v>1.08</v>
+      </c>
+      <c r="AD56">
+        <v>8.6</v>
+      </c>
+      <c r="AE56">
+        <v>1.38</v>
+      </c>
+      <c r="AF56">
+        <v>2.95</v>
+      </c>
+      <c r="AG56">
+        <v>2.15</v>
+      </c>
+      <c r="AH56">
+        <v>1.67</v>
+      </c>
+      <c r="AI56">
+        <v>1.95</v>
+      </c>
+      <c r="AJ56">
+        <v>1.8</v>
+      </c>
+      <c r="AK56">
+        <v>1.25</v>
+      </c>
+      <c r="AL56">
+        <v>1.32</v>
+      </c>
+      <c r="AM56">
+        <v>1.75</v>
+      </c>
+      <c r="AN56">
+        <v>3</v>
+      </c>
+      <c r="AO56">
+        <v>1</v>
+      </c>
+      <c r="AP56">
+        <v>3</v>
+      </c>
+      <c r="AQ56">
+        <v>0.5</v>
+      </c>
+      <c r="AR56">
+        <v>1.44</v>
+      </c>
+      <c r="AS56">
+        <v>1.32</v>
+      </c>
+      <c r="AT56">
+        <v>2.76</v>
+      </c>
+      <c r="AU56">
+        <v>4</v>
+      </c>
+      <c r="AV56">
+        <v>3</v>
+      </c>
+      <c r="AW56">
+        <v>8</v>
+      </c>
+      <c r="AX56">
+        <v>10</v>
+      </c>
+      <c r="AY56">
+        <v>13</v>
+      </c>
+      <c r="AZ56">
+        <v>15</v>
+      </c>
+      <c r="BA56">
+        <v>8</v>
+      </c>
+      <c r="BB56">
+        <v>3</v>
+      </c>
+      <c r="BC56">
+        <v>11</v>
+      </c>
+      <c r="BD56">
+        <v>1.63</v>
+      </c>
+      <c r="BE56">
+        <v>6.75</v>
+      </c>
+      <c r="BF56">
+        <v>2.55</v>
+      </c>
+      <c r="BG56">
+        <v>1.36</v>
+      </c>
+      <c r="BH56">
+        <v>2.85</v>
+      </c>
+      <c r="BI56">
+        <v>1.61</v>
+      </c>
+      <c r="BJ56">
+        <v>2.15</v>
+      </c>
+      <c r="BK56">
+        <v>1.98</v>
+      </c>
+      <c r="BL56">
+        <v>1.72</v>
+      </c>
+      <c r="BM56">
+        <v>2.5</v>
+      </c>
+      <c r="BN56">
+        <v>1.46</v>
+      </c>
+      <c r="BO56">
+        <v>3.25</v>
+      </c>
+      <c r="BP56">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="163">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -419,6 +419,12 @@
   </si>
   <si>
     <t>['16', '87']</t>
+  </si>
+  <si>
+    <t>['56']</t>
+  </si>
+  <si>
+    <t>['22', '63', '75']</t>
   </si>
   <si>
     <t>['18', '26', '48']</t>
@@ -858,7 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP56"/>
+  <dimension ref="A1:BP60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1114,7 +1120,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1526,7 +1532,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1732,7 +1738,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -1938,7 +1944,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2144,7 +2150,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2350,7 +2356,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2556,7 +2562,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2762,7 +2768,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3174,7 +3180,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3586,7 +3592,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q14">
         <v>6.5</v>
@@ -3664,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4616,7 +4622,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -4697,7 +4703,7 @@
         <v>3</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -4903,7 +4909,7 @@
         <v>1</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5234,7 +5240,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5440,7 +5446,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5646,7 +5652,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -5724,7 +5730,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
         <v>2</v>
@@ -6058,7 +6064,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6470,7 +6476,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6551,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="AQ28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -8118,7 +8124,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8942,7 +8948,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9766,7 +9772,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -9972,7 +9978,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10178,7 +10184,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10384,7 +10390,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10590,7 +10596,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11208,7 +11214,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11414,7 +11420,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11826,7 +11832,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12395,6 +12401,830 @@
       </c>
       <c r="BP56">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:68">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>7820372</v>
+      </c>
+      <c r="C57" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="2">
+        <v>45697.70833333334</v>
+      </c>
+      <c r="F57">
+        <v>4</v>
+      </c>
+      <c r="G57" t="s">
+        <v>86</v>
+      </c>
+      <c r="H57" t="s">
+        <v>73</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57">
+        <v>1</v>
+      </c>
+      <c r="N57">
+        <v>2</v>
+      </c>
+      <c r="O57" t="s">
+        <v>114</v>
+      </c>
+      <c r="P57" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q57">
+        <v>3.5</v>
+      </c>
+      <c r="R57">
+        <v>1.91</v>
+      </c>
+      <c r="S57">
+        <v>3.6</v>
+      </c>
+      <c r="T57">
+        <v>1.57</v>
+      </c>
+      <c r="U57">
+        <v>2.25</v>
+      </c>
+      <c r="V57">
+        <v>3.75</v>
+      </c>
+      <c r="W57">
+        <v>1.25</v>
+      </c>
+      <c r="X57">
+        <v>13</v>
+      </c>
+      <c r="Y57">
+        <v>1.04</v>
+      </c>
+      <c r="Z57">
+        <v>2.63</v>
+      </c>
+      <c r="AA57">
+        <v>3.1</v>
+      </c>
+      <c r="AB57">
+        <v>2.75</v>
+      </c>
+      <c r="AC57">
+        <v>1.11</v>
+      </c>
+      <c r="AD57">
+        <v>6.6</v>
+      </c>
+      <c r="AE57">
+        <v>1.5</v>
+      </c>
+      <c r="AF57">
+        <v>2.45</v>
+      </c>
+      <c r="AG57">
+        <v>2.5</v>
+      </c>
+      <c r="AH57">
+        <v>1.5</v>
+      </c>
+      <c r="AI57">
+        <v>2.1</v>
+      </c>
+      <c r="AJ57">
+        <v>1.67</v>
+      </c>
+      <c r="AK57">
+        <v>1.43</v>
+      </c>
+      <c r="AL57">
+        <v>1.36</v>
+      </c>
+      <c r="AM57">
+        <v>1.44</v>
+      </c>
+      <c r="AN57">
+        <v>1</v>
+      </c>
+      <c r="AO57">
+        <v>3</v>
+      </c>
+      <c r="AP57">
+        <v>1</v>
+      </c>
+      <c r="AQ57">
+        <v>2</v>
+      </c>
+      <c r="AR57">
+        <v>0.9</v>
+      </c>
+      <c r="AS57">
+        <v>1.63</v>
+      </c>
+      <c r="AT57">
+        <v>2.53</v>
+      </c>
+      <c r="AU57">
+        <v>4</v>
+      </c>
+      <c r="AV57">
+        <v>4</v>
+      </c>
+      <c r="AW57">
+        <v>6</v>
+      </c>
+      <c r="AX57">
+        <v>5</v>
+      </c>
+      <c r="AY57">
+        <v>13</v>
+      </c>
+      <c r="AZ57">
+        <v>12</v>
+      </c>
+      <c r="BA57">
+        <v>8</v>
+      </c>
+      <c r="BB57">
+        <v>6</v>
+      </c>
+      <c r="BC57">
+        <v>14</v>
+      </c>
+      <c r="BD57">
+        <v>2.06</v>
+      </c>
+      <c r="BE57">
+        <v>6.35</v>
+      </c>
+      <c r="BF57">
+        <v>2.22</v>
+      </c>
+      <c r="BG57">
+        <v>1.31</v>
+      </c>
+      <c r="BH57">
+        <v>3.1</v>
+      </c>
+      <c r="BI57">
+        <v>1.57</v>
+      </c>
+      <c r="BJ57">
+        <v>2.15</v>
+      </c>
+      <c r="BK57">
+        <v>2</v>
+      </c>
+      <c r="BL57">
+        <v>1.68</v>
+      </c>
+      <c r="BM57">
+        <v>2.7</v>
+      </c>
+      <c r="BN57">
+        <v>1.38</v>
+      </c>
+      <c r="BO57">
+        <v>3.8</v>
+      </c>
+      <c r="BP57">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:68">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>7820371</v>
+      </c>
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="2">
+        <v>45697.70833333334</v>
+      </c>
+      <c r="F58">
+        <v>4</v>
+      </c>
+      <c r="G58" t="s">
+        <v>82</v>
+      </c>
+      <c r="H58" t="s">
+        <v>81</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+      <c r="O58" t="s">
+        <v>135</v>
+      </c>
+      <c r="P58" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q58">
+        <v>3.6</v>
+      </c>
+      <c r="R58">
+        <v>1.8</v>
+      </c>
+      <c r="S58">
+        <v>4</v>
+      </c>
+      <c r="T58">
+        <v>1.73</v>
+      </c>
+      <c r="U58">
+        <v>2</v>
+      </c>
+      <c r="V58">
+        <v>4.5</v>
+      </c>
+      <c r="W58">
+        <v>1.18</v>
+      </c>
+      <c r="X58">
+        <v>17</v>
+      </c>
+      <c r="Y58">
+        <v>1.03</v>
+      </c>
+      <c r="Z58">
+        <v>2.6</v>
+      </c>
+      <c r="AA58">
+        <v>3</v>
+      </c>
+      <c r="AB58">
+        <v>2.9</v>
+      </c>
+      <c r="AC58">
+        <v>1.15</v>
+      </c>
+      <c r="AD58">
+        <v>5.2</v>
+      </c>
+      <c r="AE58">
+        <v>1.67</v>
+      </c>
+      <c r="AF58">
+        <v>2.05</v>
+      </c>
+      <c r="AG58">
+        <v>3.4</v>
+      </c>
+      <c r="AH58">
+        <v>1.33</v>
+      </c>
+      <c r="AI58">
+        <v>2.5</v>
+      </c>
+      <c r="AJ58">
+        <v>1.5</v>
+      </c>
+      <c r="AK58">
+        <v>1.37</v>
+      </c>
+      <c r="AL58">
+        <v>1.41</v>
+      </c>
+      <c r="AM58">
+        <v>1.46</v>
+      </c>
+      <c r="AN58">
+        <v>1</v>
+      </c>
+      <c r="AO58">
+        <v>0</v>
+      </c>
+      <c r="AP58">
+        <v>2</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0.73</v>
+      </c>
+      <c r="AS58">
+        <v>1.21</v>
+      </c>
+      <c r="AT58">
+        <v>1.94</v>
+      </c>
+      <c r="AU58">
+        <v>5</v>
+      </c>
+      <c r="AV58">
+        <v>3</v>
+      </c>
+      <c r="AW58">
+        <v>9</v>
+      </c>
+      <c r="AX58">
+        <v>1</v>
+      </c>
+      <c r="AY58">
+        <v>17</v>
+      </c>
+      <c r="AZ58">
+        <v>4</v>
+      </c>
+      <c r="BA58">
+        <v>3</v>
+      </c>
+      <c r="BB58">
+        <v>2</v>
+      </c>
+      <c r="BC58">
+        <v>5</v>
+      </c>
+      <c r="BD58">
+        <v>1.92</v>
+      </c>
+      <c r="BE58">
+        <v>6.15</v>
+      </c>
+      <c r="BF58">
+        <v>2.49</v>
+      </c>
+      <c r="BG58">
+        <v>1.43</v>
+      </c>
+      <c r="BH58">
+        <v>2.5</v>
+      </c>
+      <c r="BI58">
+        <v>1.8</v>
+      </c>
+      <c r="BJ58">
+        <v>1.85</v>
+      </c>
+      <c r="BK58">
+        <v>2.4</v>
+      </c>
+      <c r="BL58">
+        <v>1.47</v>
+      </c>
+      <c r="BM58">
+        <v>3.4</v>
+      </c>
+      <c r="BN58">
+        <v>1.26</v>
+      </c>
+      <c r="BO58">
+        <v>4.7</v>
+      </c>
+      <c r="BP58">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:68">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>7820373</v>
+      </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="2">
+        <v>45697.80208333334</v>
+      </c>
+      <c r="F59">
+        <v>4</v>
+      </c>
+      <c r="G59" t="s">
+        <v>92</v>
+      </c>
+      <c r="H59" t="s">
+        <v>70</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="L59">
+        <v>3</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>3</v>
+      </c>
+      <c r="O59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P59" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q59">
+        <v>2.75</v>
+      </c>
+      <c r="R59">
+        <v>1.91</v>
+      </c>
+      <c r="S59">
+        <v>5</v>
+      </c>
+      <c r="T59">
+        <v>1.57</v>
+      </c>
+      <c r="U59">
+        <v>2.25</v>
+      </c>
+      <c r="V59">
+        <v>3.75</v>
+      </c>
+      <c r="W59">
+        <v>1.25</v>
+      </c>
+      <c r="X59">
+        <v>13</v>
+      </c>
+      <c r="Y59">
+        <v>1.04</v>
+      </c>
+      <c r="Z59">
+        <v>1.95</v>
+      </c>
+      <c r="AA59">
+        <v>3.2</v>
+      </c>
+      <c r="AB59">
+        <v>4.1</v>
+      </c>
+      <c r="AC59">
+        <v>1.12</v>
+      </c>
+      <c r="AD59">
+        <v>6.4</v>
+      </c>
+      <c r="AE59">
+        <v>1.5</v>
+      </c>
+      <c r="AF59">
+        <v>2.37</v>
+      </c>
+      <c r="AG59">
+        <v>2.6</v>
+      </c>
+      <c r="AH59">
+        <v>1.48</v>
+      </c>
+      <c r="AI59">
+        <v>2.25</v>
+      </c>
+      <c r="AJ59">
+        <v>1.57</v>
+      </c>
+      <c r="AK59">
+        <v>1.24</v>
+      </c>
+      <c r="AL59">
+        <v>1.34</v>
+      </c>
+      <c r="AM59">
+        <v>1.77</v>
+      </c>
+      <c r="AN59">
+        <v>0</v>
+      </c>
+      <c r="AO59">
+        <v>1</v>
+      </c>
+      <c r="AP59">
+        <v>1.5</v>
+      </c>
+      <c r="AQ59">
+        <v>0.5</v>
+      </c>
+      <c r="AR59">
+        <v>1.06</v>
+      </c>
+      <c r="AS59">
+        <v>1.27</v>
+      </c>
+      <c r="AT59">
+        <v>2.33</v>
+      </c>
+      <c r="AU59">
+        <v>7</v>
+      </c>
+      <c r="AV59">
+        <v>2</v>
+      </c>
+      <c r="AW59">
+        <v>3</v>
+      </c>
+      <c r="AX59">
+        <v>4</v>
+      </c>
+      <c r="AY59">
+        <v>10</v>
+      </c>
+      <c r="AZ59">
+        <v>8</v>
+      </c>
+      <c r="BA59">
+        <v>4</v>
+      </c>
+      <c r="BB59">
+        <v>5</v>
+      </c>
+      <c r="BC59">
+        <v>9</v>
+      </c>
+      <c r="BD59">
+        <v>1.73</v>
+      </c>
+      <c r="BE59">
+        <v>8.5</v>
+      </c>
+      <c r="BF59">
+        <v>2.57</v>
+      </c>
+      <c r="BG59">
+        <v>1.24</v>
+      </c>
+      <c r="BH59">
+        <v>3.5</v>
+      </c>
+      <c r="BI59">
+        <v>1.46</v>
+      </c>
+      <c r="BJ59">
+        <v>2.45</v>
+      </c>
+      <c r="BK59">
+        <v>1.8</v>
+      </c>
+      <c r="BL59">
+        <v>1.83</v>
+      </c>
+      <c r="BM59">
+        <v>2.37</v>
+      </c>
+      <c r="BN59">
+        <v>1.47</v>
+      </c>
+      <c r="BO59">
+        <v>3.3</v>
+      </c>
+      <c r="BP59">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:68">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>7820374</v>
+      </c>
+      <c r="C60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="2">
+        <v>45697.89583333334</v>
+      </c>
+      <c r="F60">
+        <v>4</v>
+      </c>
+      <c r="G60" t="s">
+        <v>91</v>
+      </c>
+      <c r="H60" t="s">
+        <v>74</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+      <c r="O60" t="s">
+        <v>100</v>
+      </c>
+      <c r="P60" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q60">
+        <v>2.6</v>
+      </c>
+      <c r="R60">
+        <v>1.95</v>
+      </c>
+      <c r="S60">
+        <v>5.5</v>
+      </c>
+      <c r="T60">
+        <v>1.53</v>
+      </c>
+      <c r="U60">
+        <v>2.38</v>
+      </c>
+      <c r="V60">
+        <v>3.75</v>
+      </c>
+      <c r="W60">
+        <v>1.25</v>
+      </c>
+      <c r="X60">
+        <v>11</v>
+      </c>
+      <c r="Y60">
+        <v>1.05</v>
+      </c>
+      <c r="Z60">
+        <v>1.8</v>
+      </c>
+      <c r="AA60">
+        <v>3.4</v>
+      </c>
+      <c r="AB60">
+        <v>4.5</v>
+      </c>
+      <c r="AC60">
+        <v>1.1</v>
+      </c>
+      <c r="AD60">
+        <v>7</v>
+      </c>
+      <c r="AE60">
+        <v>1.51</v>
+      </c>
+      <c r="AF60">
+        <v>2.48</v>
+      </c>
+      <c r="AG60">
+        <v>2.4</v>
+      </c>
+      <c r="AH60">
+        <v>1.53</v>
+      </c>
+      <c r="AI60">
+        <v>2.25</v>
+      </c>
+      <c r="AJ60">
+        <v>1.57</v>
+      </c>
+      <c r="AK60">
+        <v>1.2</v>
+      </c>
+      <c r="AL60">
+        <v>1.31</v>
+      </c>
+      <c r="AM60">
+        <v>1.93</v>
+      </c>
+      <c r="AN60">
+        <v>0</v>
+      </c>
+      <c r="AO60">
+        <v>0</v>
+      </c>
+      <c r="AP60">
+        <v>0</v>
+      </c>
+      <c r="AQ60">
+        <v>1.5</v>
+      </c>
+      <c r="AR60">
+        <v>2.21</v>
+      </c>
+      <c r="AS60">
+        <v>1.22</v>
+      </c>
+      <c r="AT60">
+        <v>3.43</v>
+      </c>
+      <c r="AU60">
+        <v>7</v>
+      </c>
+      <c r="AV60">
+        <v>4</v>
+      </c>
+      <c r="AW60">
+        <v>13</v>
+      </c>
+      <c r="AX60">
+        <v>2</v>
+      </c>
+      <c r="AY60">
+        <v>22</v>
+      </c>
+      <c r="AZ60">
+        <v>7</v>
+      </c>
+      <c r="BA60">
+        <v>10</v>
+      </c>
+      <c r="BB60">
+        <v>3</v>
+      </c>
+      <c r="BC60">
+        <v>13</v>
+      </c>
+      <c r="BD60">
+        <v>1.48</v>
+      </c>
+      <c r="BE60">
+        <v>7.1</v>
+      </c>
+      <c r="BF60">
+        <v>3.72</v>
+      </c>
+      <c r="BG60">
+        <v>1.34</v>
+      </c>
+      <c r="BH60">
+        <v>2.85</v>
+      </c>
+      <c r="BI60">
+        <v>1.65</v>
+      </c>
+      <c r="BJ60">
+        <v>2.05</v>
+      </c>
+      <c r="BK60">
+        <v>2.1</v>
+      </c>
+      <c r="BL60">
+        <v>1.6</v>
+      </c>
+      <c r="BM60">
+        <v>2.9</v>
+      </c>
+      <c r="BN60">
+        <v>1.33</v>
+      </c>
+      <c r="BO60">
+        <v>3.85</v>
+      </c>
+      <c r="BP60">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="169">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -427,6 +427,21 @@
     <t>['22', '63', '75']</t>
   </si>
   <si>
+    <t>['55', '73', '90+6']</t>
+  </si>
+  <si>
+    <t>['51', '83']</t>
+  </si>
+  <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['4']</t>
+  </si>
+  <si>
+    <t>['5', '54']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -503,6 +518,9 @@
   </si>
   <si>
     <t>['49']</t>
+  </si>
+  <si>
+    <t>['62', '75', '80']</t>
   </si>
 </sst>
 </file>
@@ -864,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP60"/>
+  <dimension ref="A1:BP65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1120,7 +1138,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1532,7 +1550,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1613,7 +1631,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1738,7 +1756,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -1819,7 +1837,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1944,7 +1962,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2150,7 +2168,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2228,10 +2246,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2356,7 +2374,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2562,7 +2580,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2640,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9">
         <v>0.5</v>
@@ -2768,7 +2786,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3180,7 +3198,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3592,7 +3610,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="Q14">
         <v>6.5</v>
@@ -3876,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ15">
         <v>2</v>
@@ -4622,7 +4640,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5240,7 +5258,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5446,7 +5464,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5652,7 +5670,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6064,7 +6082,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6476,7 +6494,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7378,10 +7396,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.19</v>
@@ -8124,7 +8142,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8202,7 +8220,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ36">
         <v>0.5</v>
@@ -8948,7 +8966,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9029,7 +9047,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR40">
         <v>1.12</v>
@@ -9441,7 +9459,7 @@
         <v>3</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>2.46</v>
@@ -9772,7 +9790,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -9850,10 +9868,10 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR44">
         <v>1.93</v>
@@ -9978,7 +9996,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10184,7 +10202,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10390,7 +10408,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10596,7 +10614,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11214,7 +11232,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11420,7 +11438,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11832,7 +11850,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12450,7 +12468,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13225,6 +13243,1036 @@
       </c>
       <c r="BP60">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:68">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>7820376</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="2">
+        <v>45699.73958333334</v>
+      </c>
+      <c r="F61">
+        <v>5</v>
+      </c>
+      <c r="G61" t="s">
+        <v>75</v>
+      </c>
+      <c r="H61" t="s">
+        <v>84</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>3</v>
+      </c>
+      <c r="M61">
+        <v>3</v>
+      </c>
+      <c r="N61">
+        <v>6</v>
+      </c>
+      <c r="O61" t="s">
+        <v>137</v>
+      </c>
+      <c r="P61" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q61">
+        <v>3.9</v>
+      </c>
+      <c r="R61">
+        <v>1.8</v>
+      </c>
+      <c r="S61">
+        <v>3.2</v>
+      </c>
+      <c r="T61">
+        <v>1.6</v>
+      </c>
+      <c r="U61">
+        <v>2.15</v>
+      </c>
+      <c r="V61">
+        <v>3.75</v>
+      </c>
+      <c r="W61">
+        <v>1.23</v>
+      </c>
+      <c r="X61">
+        <v>11</v>
+      </c>
+      <c r="Y61">
+        <v>1.03</v>
+      </c>
+      <c r="Z61">
+        <v>3.47</v>
+      </c>
+      <c r="AA61">
+        <v>2.53</v>
+      </c>
+      <c r="AB61">
+        <v>2.58</v>
+      </c>
+      <c r="AC61">
+        <v>1.14</v>
+      </c>
+      <c r="AD61">
+        <v>5.6</v>
+      </c>
+      <c r="AE61">
+        <v>1.57</v>
+      </c>
+      <c r="AF61">
+        <v>2.25</v>
+      </c>
+      <c r="AG61">
+        <v>2.85</v>
+      </c>
+      <c r="AH61">
+        <v>1.43</v>
+      </c>
+      <c r="AI61">
+        <v>2.2</v>
+      </c>
+      <c r="AJ61">
+        <v>1.58</v>
+      </c>
+      <c r="AK61">
+        <v>1.52</v>
+      </c>
+      <c r="AL61">
+        <v>1.41</v>
+      </c>
+      <c r="AM61">
+        <v>1.32</v>
+      </c>
+      <c r="AN61">
+        <v>1.5</v>
+      </c>
+      <c r="AO61">
+        <v>0</v>
+      </c>
+      <c r="AP61">
+        <v>1.33</v>
+      </c>
+      <c r="AQ61">
+        <v>0.5</v>
+      </c>
+      <c r="AR61">
+        <v>0.96</v>
+      </c>
+      <c r="AS61">
+        <v>1.38</v>
+      </c>
+      <c r="AT61">
+        <v>2.34</v>
+      </c>
+      <c r="AU61">
+        <v>6</v>
+      </c>
+      <c r="AV61">
+        <v>5</v>
+      </c>
+      <c r="AW61">
+        <v>1</v>
+      </c>
+      <c r="AX61">
+        <v>9</v>
+      </c>
+      <c r="AY61">
+        <v>7</v>
+      </c>
+      <c r="AZ61">
+        <v>16</v>
+      </c>
+      <c r="BA61">
+        <v>2</v>
+      </c>
+      <c r="BB61">
+        <v>4</v>
+      </c>
+      <c r="BC61">
+        <v>6</v>
+      </c>
+      <c r="BD61">
+        <v>2.78</v>
+      </c>
+      <c r="BE61">
+        <v>6.4</v>
+      </c>
+      <c r="BF61">
+        <v>1.73</v>
+      </c>
+      <c r="BG61">
+        <v>1.41</v>
+      </c>
+      <c r="BH61">
+        <v>2.6</v>
+      </c>
+      <c r="BI61">
+        <v>1.76</v>
+      </c>
+      <c r="BJ61">
+        <v>1.95</v>
+      </c>
+      <c r="BK61">
+        <v>2.25</v>
+      </c>
+      <c r="BL61">
+        <v>1.54</v>
+      </c>
+      <c r="BM61">
+        <v>3.04</v>
+      </c>
+      <c r="BN61">
+        <v>1.29</v>
+      </c>
+      <c r="BO61">
+        <v>4.33</v>
+      </c>
+      <c r="BP61">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:68">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>7820377</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" s="2">
+        <v>45699.83333333334</v>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62" t="s">
+        <v>83</v>
+      </c>
+      <c r="H62" t="s">
+        <v>89</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>2</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>2</v>
+      </c>
+      <c r="O62" t="s">
+        <v>138</v>
+      </c>
+      <c r="P62" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q62">
+        <v>2.37</v>
+      </c>
+      <c r="R62">
+        <v>2.05</v>
+      </c>
+      <c r="S62">
+        <v>6.69</v>
+      </c>
+      <c r="T62">
+        <v>1.55</v>
+      </c>
+      <c r="U62">
+        <v>2.41</v>
+      </c>
+      <c r="V62">
+        <v>3.5</v>
+      </c>
+      <c r="W62">
+        <v>1.27</v>
+      </c>
+      <c r="X62">
+        <v>10</v>
+      </c>
+      <c r="Y62">
+        <v>1.04</v>
+      </c>
+      <c r="Z62">
+        <v>1.5</v>
+      </c>
+      <c r="AA62">
+        <v>3</v>
+      </c>
+      <c r="AB62">
+        <v>1.5</v>
+      </c>
+      <c r="AC62">
+        <v>1.11</v>
+      </c>
+      <c r="AD62">
+        <v>6.6</v>
+      </c>
+      <c r="AE62">
+        <v>1.5</v>
+      </c>
+      <c r="AF62">
+        <v>2.4</v>
+      </c>
+      <c r="AG62">
+        <v>2.65</v>
+      </c>
+      <c r="AH62">
+        <v>1.49</v>
+      </c>
+      <c r="AI62">
+        <v>2.37</v>
+      </c>
+      <c r="AJ62">
+        <v>1.51</v>
+      </c>
+      <c r="AK62">
+        <v>1.15</v>
+      </c>
+      <c r="AL62">
+        <v>1.3</v>
+      </c>
+      <c r="AM62">
+        <v>2.05</v>
+      </c>
+      <c r="AN62">
+        <v>2</v>
+      </c>
+      <c r="AO62">
+        <v>3</v>
+      </c>
+      <c r="AP62">
+        <v>2.33</v>
+      </c>
+      <c r="AQ62">
+        <v>2</v>
+      </c>
+      <c r="AR62">
+        <v>1.19</v>
+      </c>
+      <c r="AS62">
+        <v>1.48</v>
+      </c>
+      <c r="AT62">
+        <v>2.67</v>
+      </c>
+      <c r="AU62">
+        <v>6</v>
+      </c>
+      <c r="AV62">
+        <v>5</v>
+      </c>
+      <c r="AW62">
+        <v>4</v>
+      </c>
+      <c r="AX62">
+        <v>3</v>
+      </c>
+      <c r="AY62">
+        <v>13</v>
+      </c>
+      <c r="AZ62">
+        <v>8</v>
+      </c>
+      <c r="BA62">
+        <v>5</v>
+      </c>
+      <c r="BB62">
+        <v>4</v>
+      </c>
+      <c r="BC62">
+        <v>9</v>
+      </c>
+      <c r="BD62">
+        <v>1.3</v>
+      </c>
+      <c r="BE62">
+        <v>7</v>
+      </c>
+      <c r="BF62">
+        <v>3.9</v>
+      </c>
+      <c r="BG62">
+        <v>1.5</v>
+      </c>
+      <c r="BH62">
+        <v>2.35</v>
+      </c>
+      <c r="BI62">
+        <v>1.84</v>
+      </c>
+      <c r="BJ62">
+        <v>1.84</v>
+      </c>
+      <c r="BK62">
+        <v>2.33</v>
+      </c>
+      <c r="BL62">
+        <v>1.52</v>
+      </c>
+      <c r="BM62">
+        <v>3.05</v>
+      </c>
+      <c r="BN62">
+        <v>1.32</v>
+      </c>
+      <c r="BO62">
+        <v>4.1</v>
+      </c>
+      <c r="BP62">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:68">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>7820378</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="2">
+        <v>45699.83333333334</v>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63" t="s">
+        <v>80</v>
+      </c>
+      <c r="H63" t="s">
+        <v>85</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63" t="s">
+        <v>139</v>
+      </c>
+      <c r="P63" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q63">
+        <v>2.15</v>
+      </c>
+      <c r="R63">
+        <v>2.1</v>
+      </c>
+      <c r="S63">
+        <v>5.75</v>
+      </c>
+      <c r="T63">
+        <v>1.44</v>
+      </c>
+      <c r="U63">
+        <v>2.55</v>
+      </c>
+      <c r="V63">
+        <v>3.1</v>
+      </c>
+      <c r="W63">
+        <v>1.32</v>
+      </c>
+      <c r="X63">
+        <v>8.25</v>
+      </c>
+      <c r="Y63">
+        <v>1.06</v>
+      </c>
+      <c r="Z63">
+        <v>1.55</v>
+      </c>
+      <c r="AA63">
+        <v>3.73</v>
+      </c>
+      <c r="AB63">
+        <v>6.12</v>
+      </c>
+      <c r="AC63">
+        <v>1.08</v>
+      </c>
+      <c r="AD63">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE63">
+        <v>1.42</v>
+      </c>
+      <c r="AF63">
+        <v>2.75</v>
+      </c>
+      <c r="AG63">
+        <v>2.15</v>
+      </c>
+      <c r="AH63">
+        <v>1.6</v>
+      </c>
+      <c r="AI63">
+        <v>2.25</v>
+      </c>
+      <c r="AJ63">
+        <v>1.55</v>
+      </c>
+      <c r="AK63">
+        <v>1.12</v>
+      </c>
+      <c r="AL63">
+        <v>1.26</v>
+      </c>
+      <c r="AM63">
+        <v>2.3</v>
+      </c>
+      <c r="AN63">
+        <v>3</v>
+      </c>
+      <c r="AO63">
+        <v>1.5</v>
+      </c>
+      <c r="AP63">
+        <v>3</v>
+      </c>
+      <c r="AQ63">
+        <v>1</v>
+      </c>
+      <c r="AR63">
+        <v>1.97</v>
+      </c>
+      <c r="AS63">
+        <v>1.28</v>
+      </c>
+      <c r="AT63">
+        <v>3.25</v>
+      </c>
+      <c r="AU63">
+        <v>5</v>
+      </c>
+      <c r="AV63">
+        <v>0</v>
+      </c>
+      <c r="AW63">
+        <v>9</v>
+      </c>
+      <c r="AX63">
+        <v>9</v>
+      </c>
+      <c r="AY63">
+        <v>18</v>
+      </c>
+      <c r="AZ63">
+        <v>11</v>
+      </c>
+      <c r="BA63">
+        <v>4</v>
+      </c>
+      <c r="BB63">
+        <v>1</v>
+      </c>
+      <c r="BC63">
+        <v>5</v>
+      </c>
+      <c r="BD63">
+        <v>1.46</v>
+      </c>
+      <c r="BE63">
+        <v>8.9</v>
+      </c>
+      <c r="BF63">
+        <v>3.38</v>
+      </c>
+      <c r="BG63">
+        <v>1.31</v>
+      </c>
+      <c r="BH63">
+        <v>2.92</v>
+      </c>
+      <c r="BI63">
+        <v>1.6</v>
+      </c>
+      <c r="BJ63">
+        <v>2.14</v>
+      </c>
+      <c r="BK63">
+        <v>2.04</v>
+      </c>
+      <c r="BL63">
+        <v>1.69</v>
+      </c>
+      <c r="BM63">
+        <v>2.67</v>
+      </c>
+      <c r="BN63">
+        <v>1.39</v>
+      </c>
+      <c r="BO63">
+        <v>3.7</v>
+      </c>
+      <c r="BP63">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:68">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>7820375</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45699.92708333334</v>
+      </c>
+      <c r="F64">
+        <v>5</v>
+      </c>
+      <c r="G64" t="s">
+        <v>71</v>
+      </c>
+      <c r="H64" t="s">
+        <v>97</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
+        <v>140</v>
+      </c>
+      <c r="P64" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q64">
+        <v>4.01</v>
+      </c>
+      <c r="R64">
+        <v>2.19</v>
+      </c>
+      <c r="S64">
+        <v>2.85</v>
+      </c>
+      <c r="T64">
+        <v>1.4</v>
+      </c>
+      <c r="U64">
+        <v>2.87</v>
+      </c>
+      <c r="V64">
+        <v>3.02</v>
+      </c>
+      <c r="W64">
+        <v>1.36</v>
+      </c>
+      <c r="X64">
+        <v>7.25</v>
+      </c>
+      <c r="Y64">
+        <v>1.08</v>
+      </c>
+      <c r="Z64">
+        <v>1.5</v>
+      </c>
+      <c r="AA64">
+        <v>3</v>
+      </c>
+      <c r="AB64">
+        <v>1.5</v>
+      </c>
+      <c r="AC64">
+        <v>1.07</v>
+      </c>
+      <c r="AD64">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE64">
+        <v>1.32</v>
+      </c>
+      <c r="AF64">
+        <v>3.28</v>
+      </c>
+      <c r="AG64">
+        <v>2.04</v>
+      </c>
+      <c r="AH64">
+        <v>1.76</v>
+      </c>
+      <c r="AI64">
+        <v>1.78</v>
+      </c>
+      <c r="AJ64">
+        <v>1.9</v>
+      </c>
+      <c r="AK64">
+        <v>1.65</v>
+      </c>
+      <c r="AL64">
+        <v>1.32</v>
+      </c>
+      <c r="AM64">
+        <v>1.32</v>
+      </c>
+      <c r="AN64">
+        <v>3</v>
+      </c>
+      <c r="AO64">
+        <v>1.5</v>
+      </c>
+      <c r="AP64">
+        <v>3</v>
+      </c>
+      <c r="AQ64">
+        <v>1</v>
+      </c>
+      <c r="AR64">
+        <v>1.42</v>
+      </c>
+      <c r="AS64">
+        <v>1.49</v>
+      </c>
+      <c r="AT64">
+        <v>2.91</v>
+      </c>
+      <c r="AU64">
+        <v>5</v>
+      </c>
+      <c r="AV64">
+        <v>4</v>
+      </c>
+      <c r="AW64">
+        <v>5</v>
+      </c>
+      <c r="AX64">
+        <v>3</v>
+      </c>
+      <c r="AY64">
+        <v>12</v>
+      </c>
+      <c r="AZ64">
+        <v>7</v>
+      </c>
+      <c r="BA64">
+        <v>3</v>
+      </c>
+      <c r="BB64">
+        <v>4</v>
+      </c>
+      <c r="BC64">
+        <v>7</v>
+      </c>
+      <c r="BD64">
+        <v>2.23</v>
+      </c>
+      <c r="BE64">
+        <v>6.25</v>
+      </c>
+      <c r="BF64">
+        <v>1.79</v>
+      </c>
+      <c r="BG64">
+        <v>1.46</v>
+      </c>
+      <c r="BH64">
+        <v>2.5</v>
+      </c>
+      <c r="BI64">
+        <v>1.76</v>
+      </c>
+      <c r="BJ64">
+        <v>1.94</v>
+      </c>
+      <c r="BK64">
+        <v>2.2</v>
+      </c>
+      <c r="BL64">
+        <v>1.58</v>
+      </c>
+      <c r="BM64">
+        <v>2.9</v>
+      </c>
+      <c r="BN64">
+        <v>1.35</v>
+      </c>
+      <c r="BO64">
+        <v>3.8</v>
+      </c>
+      <c r="BP64">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:68">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>7820379</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="2">
+        <v>45699.92708333334</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65" t="s">
+        <v>77</v>
+      </c>
+      <c r="H65" t="s">
+        <v>96</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65">
+        <v>2</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>2</v>
+      </c>
+      <c r="O65" t="s">
+        <v>141</v>
+      </c>
+      <c r="P65" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q65">
+        <v>2.4</v>
+      </c>
+      <c r="R65">
+        <v>2.05</v>
+      </c>
+      <c r="S65">
+        <v>5.5</v>
+      </c>
+      <c r="T65">
+        <v>1.5</v>
+      </c>
+      <c r="U65">
+        <v>2.5</v>
+      </c>
+      <c r="V65">
+        <v>3.4</v>
+      </c>
+      <c r="W65">
+        <v>1.3</v>
+      </c>
+      <c r="X65">
+        <v>10</v>
+      </c>
+      <c r="Y65">
+        <v>1.06</v>
+      </c>
+      <c r="Z65">
+        <v>1.5</v>
+      </c>
+      <c r="AA65">
+        <v>3</v>
+      </c>
+      <c r="AB65">
+        <v>1.5</v>
+      </c>
+      <c r="AC65">
+        <v>1.09</v>
+      </c>
+      <c r="AD65">
+        <v>7</v>
+      </c>
+      <c r="AE65">
+        <v>1.48</v>
+      </c>
+      <c r="AF65">
+        <v>2.65</v>
+      </c>
+      <c r="AG65">
+        <v>2.25</v>
+      </c>
+      <c r="AH65">
+        <v>1.62</v>
+      </c>
+      <c r="AI65">
+        <v>2.1</v>
+      </c>
+      <c r="AJ65">
+        <v>1.67</v>
+      </c>
+      <c r="AK65">
+        <v>1.17</v>
+      </c>
+      <c r="AL65">
+        <v>1.25</v>
+      </c>
+      <c r="AM65">
+        <v>2</v>
+      </c>
+      <c r="AN65">
+        <v>0.5</v>
+      </c>
+      <c r="AO65">
+        <v>0</v>
+      </c>
+      <c r="AP65">
+        <v>1.33</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>1.99</v>
+      </c>
+      <c r="AS65">
+        <v>1.46</v>
+      </c>
+      <c r="AT65">
+        <v>3.45</v>
+      </c>
+      <c r="AU65">
+        <v>6</v>
+      </c>
+      <c r="AV65">
+        <v>3</v>
+      </c>
+      <c r="AW65">
+        <v>1</v>
+      </c>
+      <c r="AX65">
+        <v>5</v>
+      </c>
+      <c r="AY65">
+        <v>7</v>
+      </c>
+      <c r="AZ65">
+        <v>9</v>
+      </c>
+      <c r="BA65">
+        <v>5</v>
+      </c>
+      <c r="BB65">
+        <v>6</v>
+      </c>
+      <c r="BC65">
+        <v>11</v>
+      </c>
+      <c r="BD65">
+        <v>1.4</v>
+      </c>
+      <c r="BE65">
+        <v>7</v>
+      </c>
+      <c r="BF65">
+        <v>3.3</v>
+      </c>
+      <c r="BG65">
+        <v>1.3</v>
+      </c>
+      <c r="BH65">
+        <v>3.15</v>
+      </c>
+      <c r="BI65">
+        <v>1.52</v>
+      </c>
+      <c r="BJ65">
+        <v>2.33</v>
+      </c>
+      <c r="BK65">
+        <v>1.84</v>
+      </c>
+      <c r="BL65">
+        <v>1.84</v>
+      </c>
+      <c r="BM65">
+        <v>2.3</v>
+      </c>
+      <c r="BN65">
+        <v>1.54</v>
+      </c>
+      <c r="BO65">
+        <v>2.9</v>
+      </c>
+      <c r="BP65">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="169">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -882,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP65"/>
+  <dimension ref="A1:BP67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>2</v>
@@ -6575,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -7605,7 +7605,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ33">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR33">
         <v>1.45</v>
@@ -8426,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>1</v>
       </c>
       <c r="AQ57">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR57">
         <v>0.9</v>
@@ -14273,6 +14273,418 @@
       </c>
       <c r="BP65">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:68">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>7820381</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45700.70833333334</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66" t="s">
+        <v>86</v>
+      </c>
+      <c r="H66" t="s">
+        <v>87</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66" t="s">
+        <v>100</v>
+      </c>
+      <c r="P66" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q66">
+        <v>3.75</v>
+      </c>
+      <c r="R66">
+        <v>1.91</v>
+      </c>
+      <c r="S66">
+        <v>3.5</v>
+      </c>
+      <c r="T66">
+        <v>1.62</v>
+      </c>
+      <c r="U66">
+        <v>2.2</v>
+      </c>
+      <c r="V66">
+        <v>4</v>
+      </c>
+      <c r="W66">
+        <v>1.22</v>
+      </c>
+      <c r="X66">
+        <v>13</v>
+      </c>
+      <c r="Y66">
+        <v>1.04</v>
+      </c>
+      <c r="Z66">
+        <v>2.8</v>
+      </c>
+      <c r="AA66">
+        <v>3.1</v>
+      </c>
+      <c r="AB66">
+        <v>2.6</v>
+      </c>
+      <c r="AC66">
+        <v>1.1</v>
+      </c>
+      <c r="AD66">
+        <v>6.5</v>
+      </c>
+      <c r="AE66">
+        <v>1.57</v>
+      </c>
+      <c r="AF66">
+        <v>2.35</v>
+      </c>
+      <c r="AG66">
+        <v>2.7</v>
+      </c>
+      <c r="AH66">
+        <v>1.44</v>
+      </c>
+      <c r="AI66">
+        <v>2.2</v>
+      </c>
+      <c r="AJ66">
+        <v>1.62</v>
+      </c>
+      <c r="AK66">
+        <v>1.48</v>
+      </c>
+      <c r="AL66">
+        <v>1.3</v>
+      </c>
+      <c r="AM66">
+        <v>1.4</v>
+      </c>
+      <c r="AN66">
+        <v>1</v>
+      </c>
+      <c r="AO66">
+        <v>2</v>
+      </c>
+      <c r="AP66">
+        <v>1</v>
+      </c>
+      <c r="AQ66">
+        <v>1.67</v>
+      </c>
+      <c r="AR66">
+        <v>1.2</v>
+      </c>
+      <c r="AS66">
+        <v>1.56</v>
+      </c>
+      <c r="AT66">
+        <v>2.76</v>
+      </c>
+      <c r="AU66">
+        <v>3</v>
+      </c>
+      <c r="AV66">
+        <v>3</v>
+      </c>
+      <c r="AW66">
+        <v>3</v>
+      </c>
+      <c r="AX66">
+        <v>3</v>
+      </c>
+      <c r="AY66">
+        <v>6</v>
+      </c>
+      <c r="AZ66">
+        <v>6</v>
+      </c>
+      <c r="BA66">
+        <v>7</v>
+      </c>
+      <c r="BB66">
+        <v>7</v>
+      </c>
+      <c r="BC66">
+        <v>14</v>
+      </c>
+      <c r="BD66">
+        <v>2.45</v>
+      </c>
+      <c r="BE66">
+        <v>6.1</v>
+      </c>
+      <c r="BF66">
+        <v>1.92</v>
+      </c>
+      <c r="BG66">
+        <v>1.55</v>
+      </c>
+      <c r="BH66">
+        <v>2.23</v>
+      </c>
+      <c r="BI66">
+        <v>1.99</v>
+      </c>
+      <c r="BJ66">
+        <v>1.73</v>
+      </c>
+      <c r="BK66">
+        <v>2.64</v>
+      </c>
+      <c r="BL66">
+        <v>1.4</v>
+      </c>
+      <c r="BM66">
+        <v>3.7</v>
+      </c>
+      <c r="BN66">
+        <v>1.2</v>
+      </c>
+      <c r="BO66">
+        <v>5.35</v>
+      </c>
+      <c r="BP66">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="67" spans="1:68">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>7820380</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45700.73958333334</v>
+      </c>
+      <c r="F67">
+        <v>5</v>
+      </c>
+      <c r="G67" t="s">
+        <v>72</v>
+      </c>
+      <c r="H67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>100</v>
+      </c>
+      <c r="P67" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q67">
+        <v>3.2</v>
+      </c>
+      <c r="R67">
+        <v>1.91</v>
+      </c>
+      <c r="S67">
+        <v>4.33</v>
+      </c>
+      <c r="T67">
+        <v>1.62</v>
+      </c>
+      <c r="U67">
+        <v>2.2</v>
+      </c>
+      <c r="V67">
+        <v>4</v>
+      </c>
+      <c r="W67">
+        <v>1.22</v>
+      </c>
+      <c r="X67">
+        <v>13</v>
+      </c>
+      <c r="Y67">
+        <v>1.04</v>
+      </c>
+      <c r="Z67">
+        <v>2.3</v>
+      </c>
+      <c r="AA67">
+        <v>3</v>
+      </c>
+      <c r="AB67">
+        <v>3.4</v>
+      </c>
+      <c r="AC67">
+        <v>1.11</v>
+      </c>
+      <c r="AD67">
+        <v>6.25</v>
+      </c>
+      <c r="AE67">
+        <v>1.55</v>
+      </c>
+      <c r="AF67">
+        <v>2.4</v>
+      </c>
+      <c r="AG67">
+        <v>2.7</v>
+      </c>
+      <c r="AH67">
+        <v>1.44</v>
+      </c>
+      <c r="AI67">
+        <v>2.2</v>
+      </c>
+      <c r="AJ67">
+        <v>1.62</v>
+      </c>
+      <c r="AK67">
+        <v>1.3</v>
+      </c>
+      <c r="AL67">
+        <v>1.33</v>
+      </c>
+      <c r="AM67">
+        <v>1.6</v>
+      </c>
+      <c r="AN67">
+        <v>1.5</v>
+      </c>
+      <c r="AO67">
+        <v>2</v>
+      </c>
+      <c r="AP67">
+        <v>1</v>
+      </c>
+      <c r="AQ67">
+        <v>2.33</v>
+      </c>
+      <c r="AR67">
+        <v>1.78</v>
+      </c>
+      <c r="AS67">
+        <v>1.49</v>
+      </c>
+      <c r="AT67">
+        <v>3.27</v>
+      </c>
+      <c r="AU67">
+        <v>5</v>
+      </c>
+      <c r="AV67">
+        <v>5</v>
+      </c>
+      <c r="AW67">
+        <v>7</v>
+      </c>
+      <c r="AX67">
+        <v>8</v>
+      </c>
+      <c r="AY67">
+        <v>16</v>
+      </c>
+      <c r="AZ67">
+        <v>14</v>
+      </c>
+      <c r="BA67">
+        <v>5</v>
+      </c>
+      <c r="BB67">
+        <v>4</v>
+      </c>
+      <c r="BC67">
+        <v>9</v>
+      </c>
+      <c r="BD67">
+        <v>1.67</v>
+      </c>
+      <c r="BE67">
+        <v>6.65</v>
+      </c>
+      <c r="BF67">
+        <v>2.92</v>
+      </c>
+      <c r="BG67">
+        <v>1.31</v>
+      </c>
+      <c r="BH67">
+        <v>2.92</v>
+      </c>
+      <c r="BI67">
+        <v>1.59</v>
+      </c>
+      <c r="BJ67">
+        <v>2.16</v>
+      </c>
+      <c r="BK67">
+        <v>2.03</v>
+      </c>
+      <c r="BL67">
+        <v>1.7</v>
+      </c>
+      <c r="BM67">
+        <v>2.67</v>
+      </c>
+      <c r="BN67">
+        <v>1.39</v>
+      </c>
+      <c r="BO67">
+        <v>3.58</v>
+      </c>
+      <c r="BP67">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="172">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -442,6 +442,12 @@
     <t>['5', '54']</t>
   </si>
   <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['31', '43', '78']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -521,6 +527,9 @@
   </si>
   <si>
     <t>['62', '75', '80']</t>
+  </si>
+  <si>
+    <t>['57']</t>
   </si>
 </sst>
 </file>
@@ -882,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP67"/>
+  <dimension ref="A1:BP70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1138,7 +1147,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1216,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ2">
         <v>1.67</v>
@@ -1550,7 +1559,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1756,7 +1765,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -1962,7 +1971,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2168,7 +2177,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2374,7 +2383,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2580,7 +2589,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2661,7 +2670,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2786,7 +2795,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3198,7 +3207,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3610,7 +3619,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q14">
         <v>6.5</v>
@@ -4640,7 +4649,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5258,7 +5267,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5464,7 +5473,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5670,7 +5679,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6082,7 +6091,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6494,7 +6503,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6984,7 +6993,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ30">
         <v>0</v>
@@ -8142,7 +8151,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8223,7 +8232,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ36">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR36">
         <v>1</v>
@@ -8966,7 +8975,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9662,7 +9671,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ43">
         <v>1.5</v>
@@ -9790,7 +9799,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -9996,7 +10005,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10202,7 +10211,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10408,7 +10417,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10614,7 +10623,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11232,7 +11241,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11438,7 +11447,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11850,7 +11859,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12468,7 +12477,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13292,7 +13301,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14528,7 +14537,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14685,6 +14694,624 @@
       </c>
       <c r="BP67">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:68">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>7820382</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="2">
+        <v>45700.83333333334</v>
+      </c>
+      <c r="F68">
+        <v>5</v>
+      </c>
+      <c r="G68" t="s">
+        <v>98</v>
+      </c>
+      <c r="H68" t="s">
+        <v>93</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>2</v>
+      </c>
+      <c r="O68" t="s">
+        <v>142</v>
+      </c>
+      <c r="P68" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q68">
+        <v>2.75</v>
+      </c>
+      <c r="R68">
+        <v>1.82</v>
+      </c>
+      <c r="S68">
+        <v>4.8</v>
+      </c>
+      <c r="T68">
+        <v>1.61</v>
+      </c>
+      <c r="U68">
+        <v>2.15</v>
+      </c>
+      <c r="V68">
+        <v>3.8</v>
+      </c>
+      <c r="W68">
+        <v>1.22</v>
+      </c>
+      <c r="X68">
+        <v>11.5</v>
+      </c>
+      <c r="Y68">
+        <v>1.03</v>
+      </c>
+      <c r="Z68">
+        <v>1.5</v>
+      </c>
+      <c r="AA68">
+        <v>3</v>
+      </c>
+      <c r="AB68">
+        <v>1.5</v>
+      </c>
+      <c r="AC68">
+        <v>1.15</v>
+      </c>
+      <c r="AD68">
+        <v>5.2</v>
+      </c>
+      <c r="AE68">
+        <v>1.61</v>
+      </c>
+      <c r="AF68">
+        <v>2.15</v>
+      </c>
+      <c r="AG68">
+        <v>3.1</v>
+      </c>
+      <c r="AH68">
+        <v>1.37</v>
+      </c>
+      <c r="AI68">
+        <v>2.4</v>
+      </c>
+      <c r="AJ68">
+        <v>1.49</v>
+      </c>
+      <c r="AK68">
+        <v>1.21</v>
+      </c>
+      <c r="AL68">
+        <v>1.38</v>
+      </c>
+      <c r="AM68">
+        <v>1.75</v>
+      </c>
+      <c r="AN68">
+        <v>3</v>
+      </c>
+      <c r="AO68">
+        <v>0.5</v>
+      </c>
+      <c r="AP68">
+        <v>2.33</v>
+      </c>
+      <c r="AQ68">
+        <v>0.67</v>
+      </c>
+      <c r="AR68">
+        <v>1.54</v>
+      </c>
+      <c r="AS68">
+        <v>1.33</v>
+      </c>
+      <c r="AT68">
+        <v>2.87</v>
+      </c>
+      <c r="AU68">
+        <v>4</v>
+      </c>
+      <c r="AV68">
+        <v>2</v>
+      </c>
+      <c r="AW68">
+        <v>9</v>
+      </c>
+      <c r="AX68">
+        <v>3</v>
+      </c>
+      <c r="AY68">
+        <v>13</v>
+      </c>
+      <c r="AZ68">
+        <v>5</v>
+      </c>
+      <c r="BA68">
+        <v>4</v>
+      </c>
+      <c r="BB68">
+        <v>4</v>
+      </c>
+      <c r="BC68">
+        <v>8</v>
+      </c>
+      <c r="BD68">
+        <v>1.35</v>
+      </c>
+      <c r="BE68">
+        <v>7</v>
+      </c>
+      <c r="BF68">
+        <v>3.55</v>
+      </c>
+      <c r="BG68">
+        <v>1.47</v>
+      </c>
+      <c r="BH68">
+        <v>2.43</v>
+      </c>
+      <c r="BI68">
+        <v>1.81</v>
+      </c>
+      <c r="BJ68">
+        <v>1.88</v>
+      </c>
+      <c r="BK68">
+        <v>2.3</v>
+      </c>
+      <c r="BL68">
+        <v>1.54</v>
+      </c>
+      <c r="BM68">
+        <v>2.95</v>
+      </c>
+      <c r="BN68">
+        <v>1.33</v>
+      </c>
+      <c r="BO68">
+        <v>4.1</v>
+      </c>
+      <c r="BP68">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:68">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>7820383</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="2">
+        <v>45700.83333333334</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69" t="s">
+        <v>76</v>
+      </c>
+      <c r="H69" t="s">
+        <v>90</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>2</v>
+      </c>
+      <c r="L69">
+        <v>3</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>3</v>
+      </c>
+      <c r="O69" t="s">
+        <v>143</v>
+      </c>
+      <c r="P69" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q69">
+        <v>2.88</v>
+      </c>
+      <c r="R69">
+        <v>1.91</v>
+      </c>
+      <c r="S69">
+        <v>4.5</v>
+      </c>
+      <c r="T69">
+        <v>1.57</v>
+      </c>
+      <c r="U69">
+        <v>2.25</v>
+      </c>
+      <c r="V69">
+        <v>3.75</v>
+      </c>
+      <c r="W69">
+        <v>1.25</v>
+      </c>
+      <c r="X69">
+        <v>13</v>
+      </c>
+      <c r="Y69">
+        <v>1.04</v>
+      </c>
+      <c r="Z69">
+        <v>1.5</v>
+      </c>
+      <c r="AA69">
+        <v>3</v>
+      </c>
+      <c r="AB69">
+        <v>1.5</v>
+      </c>
+      <c r="AC69">
+        <v>1.11</v>
+      </c>
+      <c r="AD69">
+        <v>6.4</v>
+      </c>
+      <c r="AE69">
+        <v>1.5</v>
+      </c>
+      <c r="AF69">
+        <v>2.4</v>
+      </c>
+      <c r="AG69">
+        <v>2.5</v>
+      </c>
+      <c r="AH69">
+        <v>1.5</v>
+      </c>
+      <c r="AI69">
+        <v>2.1</v>
+      </c>
+      <c r="AJ69">
+        <v>1.67</v>
+      </c>
+      <c r="AK69">
+        <v>1.26</v>
+      </c>
+      <c r="AL69">
+        <v>1.34</v>
+      </c>
+      <c r="AM69">
+        <v>1.71</v>
+      </c>
+      <c r="AN69">
+        <v>3</v>
+      </c>
+      <c r="AO69">
+        <v>0</v>
+      </c>
+      <c r="AP69">
+        <v>3</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>2.02</v>
+      </c>
+      <c r="AS69">
+        <v>0.9</v>
+      </c>
+      <c r="AT69">
+        <v>2.92</v>
+      </c>
+      <c r="AU69">
+        <v>6</v>
+      </c>
+      <c r="AV69">
+        <v>3</v>
+      </c>
+      <c r="AW69">
+        <v>9</v>
+      </c>
+      <c r="AX69">
+        <v>7</v>
+      </c>
+      <c r="AY69">
+        <v>20</v>
+      </c>
+      <c r="AZ69">
+        <v>14</v>
+      </c>
+      <c r="BA69">
+        <v>1</v>
+      </c>
+      <c r="BB69">
+        <v>8</v>
+      </c>
+      <c r="BC69">
+        <v>9</v>
+      </c>
+      <c r="BD69">
+        <v>1.6</v>
+      </c>
+      <c r="BE69">
+        <v>6.4</v>
+      </c>
+      <c r="BF69">
+        <v>2.65</v>
+      </c>
+      <c r="BG69">
+        <v>1.52</v>
+      </c>
+      <c r="BH69">
+        <v>2.33</v>
+      </c>
+      <c r="BI69">
+        <v>1.87</v>
+      </c>
+      <c r="BJ69">
+        <v>1.82</v>
+      </c>
+      <c r="BK69">
+        <v>2.38</v>
+      </c>
+      <c r="BL69">
+        <v>1.5</v>
+      </c>
+      <c r="BM69">
+        <v>3.15</v>
+      </c>
+      <c r="BN69">
+        <v>1.3</v>
+      </c>
+      <c r="BO69">
+        <v>4.1</v>
+      </c>
+      <c r="BP69">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:68">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>7820384</v>
+      </c>
+      <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="2">
+        <v>45700.92708333334</v>
+      </c>
+      <c r="F70">
+        <v>5</v>
+      </c>
+      <c r="G70" t="s">
+        <v>70</v>
+      </c>
+      <c r="H70" t="s">
+        <v>95</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
+        <v>100</v>
+      </c>
+      <c r="P70" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q70">
+        <v>5.5</v>
+      </c>
+      <c r="R70">
+        <v>2.05</v>
+      </c>
+      <c r="S70">
+        <v>2.4</v>
+      </c>
+      <c r="T70">
+        <v>1.5</v>
+      </c>
+      <c r="U70">
+        <v>2.5</v>
+      </c>
+      <c r="V70">
+        <v>3.4</v>
+      </c>
+      <c r="W70">
+        <v>1.3</v>
+      </c>
+      <c r="X70">
+        <v>10</v>
+      </c>
+      <c r="Y70">
+        <v>1.06</v>
+      </c>
+      <c r="Z70">
+        <v>1.5</v>
+      </c>
+      <c r="AA70">
+        <v>3</v>
+      </c>
+      <c r="AB70">
+        <v>1.5</v>
+      </c>
+      <c r="AC70">
+        <v>1.08</v>
+      </c>
+      <c r="AD70">
+        <v>8</v>
+      </c>
+      <c r="AE70">
+        <v>1.4</v>
+      </c>
+      <c r="AF70">
+        <v>2.85</v>
+      </c>
+      <c r="AG70">
+        <v>2.2</v>
+      </c>
+      <c r="AH70">
+        <v>1.65</v>
+      </c>
+      <c r="AI70">
+        <v>2.05</v>
+      </c>
+      <c r="AJ70">
+        <v>1.7</v>
+      </c>
+      <c r="AK70">
+        <v>2</v>
+      </c>
+      <c r="AL70">
+        <v>1.3</v>
+      </c>
+      <c r="AM70">
+        <v>1.17</v>
+      </c>
+      <c r="AN70">
+        <v>0</v>
+      </c>
+      <c r="AO70">
+        <v>1</v>
+      </c>
+      <c r="AP70">
+        <v>0.5</v>
+      </c>
+      <c r="AQ70">
+        <v>1</v>
+      </c>
+      <c r="AR70">
+        <v>1.21</v>
+      </c>
+      <c r="AS70">
+        <v>1.67</v>
+      </c>
+      <c r="AT70">
+        <v>2.88</v>
+      </c>
+      <c r="AU70">
+        <v>5</v>
+      </c>
+      <c r="AV70">
+        <v>4</v>
+      </c>
+      <c r="AW70">
+        <v>5</v>
+      </c>
+      <c r="AX70">
+        <v>10</v>
+      </c>
+      <c r="AY70">
+        <v>12</v>
+      </c>
+      <c r="AZ70">
+        <v>17</v>
+      </c>
+      <c r="BA70">
+        <v>7</v>
+      </c>
+      <c r="BB70">
+        <v>8</v>
+      </c>
+      <c r="BC70">
+        <v>15</v>
+      </c>
+      <c r="BD70">
+        <v>3.02</v>
+      </c>
+      <c r="BE70">
+        <v>8.5</v>
+      </c>
+      <c r="BF70">
+        <v>1.55</v>
+      </c>
+      <c r="BG70">
+        <v>1.36</v>
+      </c>
+      <c r="BH70">
+        <v>2.79</v>
+      </c>
+      <c r="BI70">
+        <v>1.7</v>
+      </c>
+      <c r="BJ70">
+        <v>2.05</v>
+      </c>
+      <c r="BK70">
+        <v>2.11</v>
+      </c>
+      <c r="BL70">
+        <v>1.62</v>
+      </c>
+      <c r="BM70">
+        <v>2.78</v>
+      </c>
+      <c r="BN70">
+        <v>1.34</v>
+      </c>
+      <c r="BO70">
+        <v>3.92</v>
+      </c>
+      <c r="BP70">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="172">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -891,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP70"/>
+  <dimension ref="A1:BP71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
         <v>3</v>
@@ -3494,7 +3494,7 @@
         <v>3</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -7817,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34">
         <v>0</v>
@@ -8850,7 +8850,7 @@
         <v>3</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR39">
         <v>1.95</v>
@@ -15312,6 +15312,212 @@
       </c>
       <c r="BP70">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:68">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>7820385</v>
+      </c>
+      <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>45701.73958333334</v>
+      </c>
+      <c r="F71">
+        <v>5</v>
+      </c>
+      <c r="G71" t="s">
+        <v>74</v>
+      </c>
+      <c r="H71" t="s">
+        <v>92</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
+        <v>100</v>
+      </c>
+      <c r="P71" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q71">
+        <v>2.63</v>
+      </c>
+      <c r="R71">
+        <v>2</v>
+      </c>
+      <c r="S71">
+        <v>5</v>
+      </c>
+      <c r="T71">
+        <v>1.53</v>
+      </c>
+      <c r="U71">
+        <v>2.38</v>
+      </c>
+      <c r="V71">
+        <v>3.5</v>
+      </c>
+      <c r="W71">
+        <v>1.29</v>
+      </c>
+      <c r="X71">
+        <v>11</v>
+      </c>
+      <c r="Y71">
+        <v>1.05</v>
+      </c>
+      <c r="Z71">
+        <v>1.91</v>
+      </c>
+      <c r="AA71">
+        <v>3.2</v>
+      </c>
+      <c r="AB71">
+        <v>4.33</v>
+      </c>
+      <c r="AC71">
+        <v>1.1</v>
+      </c>
+      <c r="AD71">
+        <v>7.2</v>
+      </c>
+      <c r="AE71">
+        <v>1.45</v>
+      </c>
+      <c r="AF71">
+        <v>2.65</v>
+      </c>
+      <c r="AG71">
+        <v>2.35</v>
+      </c>
+      <c r="AH71">
+        <v>1.57</v>
+      </c>
+      <c r="AI71">
+        <v>2.1</v>
+      </c>
+      <c r="AJ71">
+        <v>1.67</v>
+      </c>
+      <c r="AK71">
+        <v>1.21</v>
+      </c>
+      <c r="AL71">
+        <v>1.33</v>
+      </c>
+      <c r="AM71">
+        <v>1.83</v>
+      </c>
+      <c r="AN71">
+        <v>1.5</v>
+      </c>
+      <c r="AO71">
+        <v>0</v>
+      </c>
+      <c r="AP71">
+        <v>1.33</v>
+      </c>
+      <c r="AQ71">
+        <v>0.33</v>
+      </c>
+      <c r="AR71">
+        <v>1.67</v>
+      </c>
+      <c r="AS71">
+        <v>1.1</v>
+      </c>
+      <c r="AT71">
+        <v>2.77</v>
+      </c>
+      <c r="AU71">
+        <v>9</v>
+      </c>
+      <c r="AV71">
+        <v>3</v>
+      </c>
+      <c r="AW71">
+        <v>10</v>
+      </c>
+      <c r="AX71">
+        <v>6</v>
+      </c>
+      <c r="AY71">
+        <v>24</v>
+      </c>
+      <c r="AZ71">
+        <v>11</v>
+      </c>
+      <c r="BA71">
+        <v>13</v>
+      </c>
+      <c r="BB71">
+        <v>6</v>
+      </c>
+      <c r="BC71">
+        <v>19</v>
+      </c>
+      <c r="BD71">
+        <v>1.65</v>
+      </c>
+      <c r="BE71">
+        <v>6.75</v>
+      </c>
+      <c r="BF71">
+        <v>2.95</v>
+      </c>
+      <c r="BG71">
+        <v>1.28</v>
+      </c>
+      <c r="BH71">
+        <v>3.08</v>
+      </c>
+      <c r="BI71">
+        <v>1.54</v>
+      </c>
+      <c r="BJ71">
+        <v>2.25</v>
+      </c>
+      <c r="BK71">
+        <v>1.95</v>
+      </c>
+      <c r="BL71">
+        <v>1.76</v>
+      </c>
+      <c r="BM71">
+        <v>2.54</v>
+      </c>
+      <c r="BN71">
+        <v>1.43</v>
+      </c>
+      <c r="BO71">
+        <v>3.42</v>
+      </c>
+      <c r="BP71">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="176">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -448,6 +448,12 @@
     <t>['31', '43', '78']</t>
   </si>
   <si>
+    <t>['44', '90+1']</t>
+  </si>
+  <si>
+    <t>['2', '30', '42', '45', '67']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -530,6 +536,12 @@
   </si>
   <si>
     <t>['57']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['31']</t>
   </si>
 </sst>
 </file>
@@ -891,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP71"/>
+  <dimension ref="A1:BP75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1147,7 +1159,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1559,7 +1571,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1765,7 +1777,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -1971,7 +1983,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2177,7 +2189,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2383,7 +2395,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2589,7 +2601,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2795,7 +2807,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -2873,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3079,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3207,7 +3219,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3619,7 +3631,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q14">
         <v>6.5</v>
@@ -4649,7 +4661,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5267,7 +5279,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5348,7 +5360,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ22">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5473,7 +5485,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5679,7 +5691,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6091,7 +6103,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6169,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ26">
         <v>0.5</v>
@@ -6378,7 +6390,7 @@
         <v>3</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -6503,7 +6515,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7611,7 +7623,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ33">
         <v>1.67</v>
@@ -8023,7 +8035,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8151,7 +8163,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8975,7 +8987,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9674,7 +9686,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ43">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -9799,7 +9811,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10005,7 +10017,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10083,7 +10095,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ45">
         <v>3</v>
@@ -10211,7 +10223,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10417,7 +10429,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10623,7 +10635,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11241,7 +11253,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11447,7 +11459,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11525,7 +11537,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ52">
         <v>2</v>
@@ -11859,7 +11871,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12477,7 +12489,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12764,7 +12776,7 @@
         <v>2</v>
       </c>
       <c r="AQ58">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR58">
         <v>0.73</v>
@@ -13301,7 +13313,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14537,7 +14549,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14743,7 +14755,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15518,6 +15530,830 @@
       </c>
       <c r="BP71">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:68">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>7820387</v>
+      </c>
+      <c r="C72" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45701.83333333334</v>
+      </c>
+      <c r="F72">
+        <v>5</v>
+      </c>
+      <c r="G72" t="s">
+        <v>78</v>
+      </c>
+      <c r="H72" t="s">
+        <v>91</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>1</v>
+      </c>
+      <c r="O72" t="s">
+        <v>100</v>
+      </c>
+      <c r="P72" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q72">
+        <v>4.5</v>
+      </c>
+      <c r="R72">
+        <v>1.91</v>
+      </c>
+      <c r="S72">
+        <v>3</v>
+      </c>
+      <c r="T72">
+        <v>1.62</v>
+      </c>
+      <c r="U72">
+        <v>2.2</v>
+      </c>
+      <c r="V72">
+        <v>4</v>
+      </c>
+      <c r="W72">
+        <v>1.22</v>
+      </c>
+      <c r="X72">
+        <v>13</v>
+      </c>
+      <c r="Y72">
+        <v>1.04</v>
+      </c>
+      <c r="Z72">
+        <v>3.75</v>
+      </c>
+      <c r="AA72">
+        <v>3.1</v>
+      </c>
+      <c r="AB72">
+        <v>2.1</v>
+      </c>
+      <c r="AC72">
+        <v>1.12</v>
+      </c>
+      <c r="AD72">
+        <v>5.75</v>
+      </c>
+      <c r="AE72">
+        <v>1.55</v>
+      </c>
+      <c r="AF72">
+        <v>2.25</v>
+      </c>
+      <c r="AG72">
+        <v>2.7</v>
+      </c>
+      <c r="AH72">
+        <v>1.44</v>
+      </c>
+      <c r="AI72">
+        <v>2.2</v>
+      </c>
+      <c r="AJ72">
+        <v>1.62</v>
+      </c>
+      <c r="AK72">
+        <v>1.66</v>
+      </c>
+      <c r="AL72">
+        <v>1.37</v>
+      </c>
+      <c r="AM72">
+        <v>1.26</v>
+      </c>
+      <c r="AN72">
+        <v>0.5</v>
+      </c>
+      <c r="AO72">
+        <v>0</v>
+      </c>
+      <c r="AP72">
+        <v>0.33</v>
+      </c>
+      <c r="AQ72">
+        <v>1.5</v>
+      </c>
+      <c r="AR72">
+        <v>1.31</v>
+      </c>
+      <c r="AS72">
+        <v>2.1</v>
+      </c>
+      <c r="AT72">
+        <v>3.41</v>
+      </c>
+      <c r="AU72">
+        <v>7</v>
+      </c>
+      <c r="AV72">
+        <v>9</v>
+      </c>
+      <c r="AW72">
+        <v>8</v>
+      </c>
+      <c r="AX72">
+        <v>8</v>
+      </c>
+      <c r="AY72">
+        <v>18</v>
+      </c>
+      <c r="AZ72">
+        <v>19</v>
+      </c>
+      <c r="BA72">
+        <v>4</v>
+      </c>
+      <c r="BB72">
+        <v>2</v>
+      </c>
+      <c r="BC72">
+        <v>6</v>
+      </c>
+      <c r="BD72">
+        <v>2.09</v>
+      </c>
+      <c r="BE72">
+        <v>6.15</v>
+      </c>
+      <c r="BF72">
+        <v>2.21</v>
+      </c>
+      <c r="BG72">
+        <v>1.45</v>
+      </c>
+      <c r="BH72">
+        <v>2.48</v>
+      </c>
+      <c r="BI72">
+        <v>1.83</v>
+      </c>
+      <c r="BJ72">
+        <v>1.87</v>
+      </c>
+      <c r="BK72">
+        <v>2.38</v>
+      </c>
+      <c r="BL72">
+        <v>1.49</v>
+      </c>
+      <c r="BM72">
+        <v>3.2</v>
+      </c>
+      <c r="BN72">
+        <v>1.26</v>
+      </c>
+      <c r="BO72">
+        <v>4.65</v>
+      </c>
+      <c r="BP72">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:68">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7820386</v>
+      </c>
+      <c r="C73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45701.83333333334</v>
+      </c>
+      <c r="F73">
+        <v>5</v>
+      </c>
+      <c r="G73" t="s">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s">
+        <v>82</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>2</v>
+      </c>
+      <c r="L73">
+        <v>2</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="N73">
+        <v>3</v>
+      </c>
+      <c r="O73" t="s">
+        <v>144</v>
+      </c>
+      <c r="P73" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q73">
+        <v>3.25</v>
+      </c>
+      <c r="R73">
+        <v>1.8</v>
+      </c>
+      <c r="S73">
+        <v>4.75</v>
+      </c>
+      <c r="T73">
+        <v>1.73</v>
+      </c>
+      <c r="U73">
+        <v>2</v>
+      </c>
+      <c r="V73">
+        <v>5</v>
+      </c>
+      <c r="W73">
+        <v>1.17</v>
+      </c>
+      <c r="X73">
+        <v>17</v>
+      </c>
+      <c r="Y73">
+        <v>1.03</v>
+      </c>
+      <c r="Z73">
+        <v>2.25</v>
+      </c>
+      <c r="AA73">
+        <v>2.63</v>
+      </c>
+      <c r="AB73">
+        <v>4</v>
+      </c>
+      <c r="AC73">
+        <v>1.17</v>
+      </c>
+      <c r="AD73">
+        <v>4.6</v>
+      </c>
+      <c r="AE73">
+        <v>1.7</v>
+      </c>
+      <c r="AF73">
+        <v>2</v>
+      </c>
+      <c r="AG73">
+        <v>3.5</v>
+      </c>
+      <c r="AH73">
+        <v>1.3</v>
+      </c>
+      <c r="AI73">
+        <v>2.63</v>
+      </c>
+      <c r="AJ73">
+        <v>1.44</v>
+      </c>
+      <c r="AK73">
+        <v>1.26</v>
+      </c>
+      <c r="AL73">
+        <v>1.44</v>
+      </c>
+      <c r="AM73">
+        <v>1.57</v>
+      </c>
+      <c r="AN73">
+        <v>2</v>
+      </c>
+      <c r="AO73">
+        <v>1.5</v>
+      </c>
+      <c r="AP73">
+        <v>2.33</v>
+      </c>
+      <c r="AQ73">
+        <v>1</v>
+      </c>
+      <c r="AR73">
+        <v>1.21</v>
+      </c>
+      <c r="AS73">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AT73">
+        <v>2.02</v>
+      </c>
+      <c r="AU73">
+        <v>8</v>
+      </c>
+      <c r="AV73">
+        <v>4</v>
+      </c>
+      <c r="AW73">
+        <v>7</v>
+      </c>
+      <c r="AX73">
+        <v>5</v>
+      </c>
+      <c r="AY73">
+        <v>16</v>
+      </c>
+      <c r="AZ73">
+        <v>10</v>
+      </c>
+      <c r="BA73">
+        <v>3</v>
+      </c>
+      <c r="BB73">
+        <v>4</v>
+      </c>
+      <c r="BC73">
+        <v>7</v>
+      </c>
+      <c r="BD73">
+        <v>1.61</v>
+      </c>
+      <c r="BE73">
+        <v>6.45</v>
+      </c>
+      <c r="BF73">
+        <v>3.15</v>
+      </c>
+      <c r="BG73">
+        <v>1.51</v>
+      </c>
+      <c r="BH73">
+        <v>2.32</v>
+      </c>
+      <c r="BI73">
+        <v>1.95</v>
+      </c>
+      <c r="BJ73">
+        <v>1.77</v>
+      </c>
+      <c r="BK73">
+        <v>2.54</v>
+      </c>
+      <c r="BL73">
+        <v>1.43</v>
+      </c>
+      <c r="BM73">
+        <v>3.5</v>
+      </c>
+      <c r="BN73">
+        <v>1.22</v>
+      </c>
+      <c r="BO73">
+        <v>5.1</v>
+      </c>
+      <c r="BP73">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:68">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7820388</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45701.92708333334</v>
+      </c>
+      <c r="F74">
+        <v>5</v>
+      </c>
+      <c r="G74" t="s">
+        <v>99</v>
+      </c>
+      <c r="H74" t="s">
+        <v>88</v>
+      </c>
+      <c r="I74">
+        <v>4</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>4</v>
+      </c>
+      <c r="L74">
+        <v>5</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>5</v>
+      </c>
+      <c r="O74" t="s">
+        <v>145</v>
+      </c>
+      <c r="P74" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q74">
+        <v>2.6</v>
+      </c>
+      <c r="R74">
+        <v>1.91</v>
+      </c>
+      <c r="S74">
+        <v>6</v>
+      </c>
+      <c r="T74">
+        <v>1.62</v>
+      </c>
+      <c r="U74">
+        <v>2.2</v>
+      </c>
+      <c r="V74">
+        <v>4</v>
+      </c>
+      <c r="W74">
+        <v>1.22</v>
+      </c>
+      <c r="X74">
+        <v>13</v>
+      </c>
+      <c r="Y74">
+        <v>1.04</v>
+      </c>
+      <c r="Z74">
+        <v>1.85</v>
+      </c>
+      <c r="AA74">
+        <v>3.2</v>
+      </c>
+      <c r="AB74">
+        <v>4.75</v>
+      </c>
+      <c r="AC74">
+        <v>1.12</v>
+      </c>
+      <c r="AD74">
+        <v>6.24</v>
+      </c>
+      <c r="AE74">
+        <v>1.53</v>
+      </c>
+      <c r="AF74">
+        <v>2.3</v>
+      </c>
+      <c r="AG74">
+        <v>2.7</v>
+      </c>
+      <c r="AH74">
+        <v>1.44</v>
+      </c>
+      <c r="AI74">
+        <v>2.38</v>
+      </c>
+      <c r="AJ74">
+        <v>1.53</v>
+      </c>
+      <c r="AK74">
+        <v>1.18</v>
+      </c>
+      <c r="AL74">
+        <v>1.33</v>
+      </c>
+      <c r="AM74">
+        <v>1.93</v>
+      </c>
+      <c r="AN74">
+        <v>0</v>
+      </c>
+      <c r="AO74">
+        <v>0</v>
+      </c>
+      <c r="AP74">
+        <v>1.5</v>
+      </c>
+      <c r="AQ74">
+        <v>0</v>
+      </c>
+      <c r="AR74">
+        <v>1.59</v>
+      </c>
+      <c r="AS74">
+        <v>1.34</v>
+      </c>
+      <c r="AT74">
+        <v>2.93</v>
+      </c>
+      <c r="AU74">
+        <v>11</v>
+      </c>
+      <c r="AV74">
+        <v>3</v>
+      </c>
+      <c r="AW74">
+        <v>4</v>
+      </c>
+      <c r="AX74">
+        <v>4</v>
+      </c>
+      <c r="AY74">
+        <v>17</v>
+      </c>
+      <c r="AZ74">
+        <v>9</v>
+      </c>
+      <c r="BA74">
+        <v>3</v>
+      </c>
+      <c r="BB74">
+        <v>4</v>
+      </c>
+      <c r="BC74">
+        <v>7</v>
+      </c>
+      <c r="BD74">
+        <v>1.49</v>
+      </c>
+      <c r="BE74">
+        <v>9.4</v>
+      </c>
+      <c r="BF74">
+        <v>3.16</v>
+      </c>
+      <c r="BG74">
+        <v>1.12</v>
+      </c>
+      <c r="BH74">
+        <v>4.65</v>
+      </c>
+      <c r="BI74">
+        <v>1.27</v>
+      </c>
+      <c r="BJ74">
+        <v>3.14</v>
+      </c>
+      <c r="BK74">
+        <v>1.51</v>
+      </c>
+      <c r="BL74">
+        <v>2.32</v>
+      </c>
+      <c r="BM74">
+        <v>1.91</v>
+      </c>
+      <c r="BN74">
+        <v>1.8</v>
+      </c>
+      <c r="BO74">
+        <v>2.38</v>
+      </c>
+      <c r="BP74">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:68">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7820389</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45701.92708333334</v>
+      </c>
+      <c r="F75">
+        <v>5</v>
+      </c>
+      <c r="G75" t="s">
+        <v>94</v>
+      </c>
+      <c r="H75" t="s">
+        <v>81</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75" t="s">
+        <v>100</v>
+      </c>
+      <c r="P75" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q75">
+        <v>3.6</v>
+      </c>
+      <c r="R75">
+        <v>1.8</v>
+      </c>
+      <c r="S75">
+        <v>4</v>
+      </c>
+      <c r="T75">
+        <v>1.67</v>
+      </c>
+      <c r="U75">
+        <v>2.1</v>
+      </c>
+      <c r="V75">
+        <v>4.33</v>
+      </c>
+      <c r="W75">
+        <v>1.2</v>
+      </c>
+      <c r="X75">
+        <v>15</v>
+      </c>
+      <c r="Y75">
+        <v>1.03</v>
+      </c>
+      <c r="Z75">
+        <v>2.63</v>
+      </c>
+      <c r="AA75">
+        <v>2.8</v>
+      </c>
+      <c r="AB75">
+        <v>3.1</v>
+      </c>
+      <c r="AC75">
+        <v>1.15</v>
+      </c>
+      <c r="AD75">
+        <v>5.4</v>
+      </c>
+      <c r="AE75">
+        <v>1.62</v>
+      </c>
+      <c r="AF75">
+        <v>2.15</v>
+      </c>
+      <c r="AG75">
+        <v>3.1</v>
+      </c>
+      <c r="AH75">
+        <v>1.36</v>
+      </c>
+      <c r="AI75">
+        <v>2.25</v>
+      </c>
+      <c r="AJ75">
+        <v>1.57</v>
+      </c>
+      <c r="AK75">
+        <v>1.35</v>
+      </c>
+      <c r="AL75">
+        <v>1.4</v>
+      </c>
+      <c r="AM75">
+        <v>1.49</v>
+      </c>
+      <c r="AN75">
+        <v>0.5</v>
+      </c>
+      <c r="AO75">
+        <v>0</v>
+      </c>
+      <c r="AP75">
+        <v>0.67</v>
+      </c>
+      <c r="AQ75">
+        <v>0.33</v>
+      </c>
+      <c r="AR75">
+        <v>1.66</v>
+      </c>
+      <c r="AS75">
+        <v>1.02</v>
+      </c>
+      <c r="AT75">
+        <v>2.68</v>
+      </c>
+      <c r="AU75">
+        <v>2</v>
+      </c>
+      <c r="AV75">
+        <v>5</v>
+      </c>
+      <c r="AW75">
+        <v>4</v>
+      </c>
+      <c r="AX75">
+        <v>7</v>
+      </c>
+      <c r="AY75">
+        <v>6</v>
+      </c>
+      <c r="AZ75">
+        <v>13</v>
+      </c>
+      <c r="BA75">
+        <v>8</v>
+      </c>
+      <c r="BB75">
+        <v>5</v>
+      </c>
+      <c r="BC75">
+        <v>13</v>
+      </c>
+      <c r="BD75">
+        <v>1.52</v>
+      </c>
+      <c r="BE75">
+        <v>6.6</v>
+      </c>
+      <c r="BF75">
+        <v>3.52</v>
+      </c>
+      <c r="BG75">
+        <v>1.57</v>
+      </c>
+      <c r="BH75">
+        <v>2.19</v>
+      </c>
+      <c r="BI75">
+        <v>2.05</v>
+      </c>
+      <c r="BJ75">
+        <v>1.7</v>
+      </c>
+      <c r="BK75">
+        <v>2.71</v>
+      </c>
+      <c r="BL75">
+        <v>1.38</v>
+      </c>
+      <c r="BM75">
+        <v>3.82</v>
+      </c>
+      <c r="BN75">
+        <v>1.19</v>
+      </c>
+      <c r="BO75">
+        <v>5.55</v>
+      </c>
+      <c r="BP75">
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="180">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -454,6 +454,12 @@
     <t>['2', '30', '42', '45', '67']</t>
   </si>
   <si>
+    <t>['37']</t>
+  </si>
+  <si>
+    <t>['57', '77']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -542,6 +548,12 @@
   </si>
   <si>
     <t>['31']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['12', '81']</t>
   </si>
 </sst>
 </file>
@@ -903,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP75"/>
+  <dimension ref="A1:BP78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1159,7 +1171,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1571,7 +1583,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1777,7 +1789,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -1855,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -1983,7 +1995,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2189,7 +2201,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2395,7 +2407,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2601,7 +2613,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2807,7 +2819,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3219,7 +3231,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3631,7 +3643,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q14">
         <v>6.5</v>
@@ -4327,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17">
         <v>0</v>
@@ -4661,7 +4673,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5154,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5279,7 +5291,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5485,7 +5497,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5691,7 +5703,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6103,7 +6115,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6184,7 +6196,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ26">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6515,7 +6527,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6593,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ28">
         <v>2.33</v>
@@ -8163,7 +8175,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8987,7 +8999,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9065,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ40">
         <v>0.5</v>
@@ -9811,7 +9823,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10017,7 +10029,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10223,7 +10235,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10301,10 +10313,10 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ46">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR46">
         <v>2.39</v>
@@ -10429,7 +10441,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10635,7 +10647,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -10713,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ48">
         <v>0.5</v>
@@ -11253,7 +11265,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11459,7 +11471,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11871,7 +11883,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12364,7 +12376,7 @@
         <v>3</v>
       </c>
       <c r="AQ56">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR56">
         <v>1.44</v>
@@ -12489,7 +12501,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13313,7 +13325,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14549,7 +14561,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14755,7 +14767,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15579,7 +15591,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15785,7 +15797,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16354,6 +16366,624 @@
       </c>
       <c r="BP75">
         <v>1.08</v>
+      </c>
+    </row>
+    <row r="76" spans="1:68">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>7820390</v>
+      </c>
+      <c r="C76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45702.83333333334</v>
+      </c>
+      <c r="F76">
+        <v>6</v>
+      </c>
+      <c r="G76" t="s">
+        <v>85</v>
+      </c>
+      <c r="H76" t="s">
+        <v>83</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76" t="s">
+        <v>100</v>
+      </c>
+      <c r="P76" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q76">
+        <v>4</v>
+      </c>
+      <c r="R76">
+        <v>2</v>
+      </c>
+      <c r="S76">
+        <v>3</v>
+      </c>
+      <c r="T76">
+        <v>1.5</v>
+      </c>
+      <c r="U76">
+        <v>2.5</v>
+      </c>
+      <c r="V76">
+        <v>3.5</v>
+      </c>
+      <c r="W76">
+        <v>1.29</v>
+      </c>
+      <c r="X76">
+        <v>11</v>
+      </c>
+      <c r="Y76">
+        <v>1.05</v>
+      </c>
+      <c r="Z76">
+        <v>3.22</v>
+      </c>
+      <c r="AA76">
+        <v>3.08</v>
+      </c>
+      <c r="AB76">
+        <v>2.11</v>
+      </c>
+      <c r="AC76">
+        <v>1.08</v>
+      </c>
+      <c r="AD76">
+        <v>7.5</v>
+      </c>
+      <c r="AE76">
+        <v>1.42</v>
+      </c>
+      <c r="AF76">
+        <v>2.8</v>
+      </c>
+      <c r="AG76">
+        <v>2.3</v>
+      </c>
+      <c r="AH76">
+        <v>1.6</v>
+      </c>
+      <c r="AI76">
+        <v>2</v>
+      </c>
+      <c r="AJ76">
+        <v>1.75</v>
+      </c>
+      <c r="AK76">
+        <v>1.62</v>
+      </c>
+      <c r="AL76">
+        <v>1.33</v>
+      </c>
+      <c r="AM76">
+        <v>1.32</v>
+      </c>
+      <c r="AN76">
+        <v>2</v>
+      </c>
+      <c r="AO76">
+        <v>0.5</v>
+      </c>
+      <c r="AP76">
+        <v>1.33</v>
+      </c>
+      <c r="AQ76">
+        <v>1.33</v>
+      </c>
+      <c r="AR76">
+        <v>1.36</v>
+      </c>
+      <c r="AS76">
+        <v>1.37</v>
+      </c>
+      <c r="AT76">
+        <v>2.73</v>
+      </c>
+      <c r="AU76">
+        <v>5</v>
+      </c>
+      <c r="AV76">
+        <v>3</v>
+      </c>
+      <c r="AW76">
+        <v>9</v>
+      </c>
+      <c r="AX76">
+        <v>9</v>
+      </c>
+      <c r="AY76">
+        <v>16</v>
+      </c>
+      <c r="AZ76">
+        <v>16</v>
+      </c>
+      <c r="BA76">
+        <v>5</v>
+      </c>
+      <c r="BB76">
+        <v>4</v>
+      </c>
+      <c r="BC76">
+        <v>9</v>
+      </c>
+      <c r="BD76">
+        <v>2.23</v>
+      </c>
+      <c r="BE76">
+        <v>6.25</v>
+      </c>
+      <c r="BF76">
+        <v>1.8</v>
+      </c>
+      <c r="BG76">
+        <v>1.49</v>
+      </c>
+      <c r="BH76">
+        <v>2.4</v>
+      </c>
+      <c r="BI76">
+        <v>1.81</v>
+      </c>
+      <c r="BJ76">
+        <v>1.88</v>
+      </c>
+      <c r="BK76">
+        <v>2.32</v>
+      </c>
+      <c r="BL76">
+        <v>1.53</v>
+      </c>
+      <c r="BM76">
+        <v>3</v>
+      </c>
+      <c r="BN76">
+        <v>1.32</v>
+      </c>
+      <c r="BO76">
+        <v>4.1</v>
+      </c>
+      <c r="BP76">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:68">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7820391</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45703.70833333334</v>
+      </c>
+      <c r="F77">
+        <v>6</v>
+      </c>
+      <c r="G77" t="s">
+        <v>73</v>
+      </c>
+      <c r="H77" t="s">
+        <v>75</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="L77">
+        <v>1</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <v>2</v>
+      </c>
+      <c r="O77" t="s">
+        <v>146</v>
+      </c>
+      <c r="P77" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q77">
+        <v>2.5</v>
+      </c>
+      <c r="R77">
+        <v>1.95</v>
+      </c>
+      <c r="S77">
+        <v>6</v>
+      </c>
+      <c r="T77">
+        <v>1.57</v>
+      </c>
+      <c r="U77">
+        <v>2.25</v>
+      </c>
+      <c r="V77">
+        <v>3.75</v>
+      </c>
+      <c r="W77">
+        <v>1.25</v>
+      </c>
+      <c r="X77">
+        <v>13</v>
+      </c>
+      <c r="Y77">
+        <v>1.04</v>
+      </c>
+      <c r="Z77">
+        <v>1.68</v>
+      </c>
+      <c r="AA77">
+        <v>3.07</v>
+      </c>
+      <c r="AB77">
+        <v>5.26</v>
+      </c>
+      <c r="AC77">
+        <v>1.1</v>
+      </c>
+      <c r="AD77">
+        <v>6.25</v>
+      </c>
+      <c r="AE77">
+        <v>1.49</v>
+      </c>
+      <c r="AF77">
+        <v>2.4</v>
+      </c>
+      <c r="AG77">
+        <v>2.6</v>
+      </c>
+      <c r="AH77">
+        <v>1.48</v>
+      </c>
+      <c r="AI77">
+        <v>2.38</v>
+      </c>
+      <c r="AJ77">
+        <v>1.53</v>
+      </c>
+      <c r="AK77">
+        <v>1.28</v>
+      </c>
+      <c r="AL77">
+        <v>1.35</v>
+      </c>
+      <c r="AM77">
+        <v>1.65</v>
+      </c>
+      <c r="AN77">
+        <v>1.5</v>
+      </c>
+      <c r="AO77">
+        <v>2</v>
+      </c>
+      <c r="AP77">
+        <v>1.33</v>
+      </c>
+      <c r="AQ77">
+        <v>1.67</v>
+      </c>
+      <c r="AR77">
+        <v>1.47</v>
+      </c>
+      <c r="AS77">
+        <v>1.02</v>
+      </c>
+      <c r="AT77">
+        <v>2.49</v>
+      </c>
+      <c r="AU77">
+        <v>8</v>
+      </c>
+      <c r="AV77">
+        <v>5</v>
+      </c>
+      <c r="AW77">
+        <v>7</v>
+      </c>
+      <c r="AX77">
+        <v>7</v>
+      </c>
+      <c r="AY77">
+        <v>17</v>
+      </c>
+      <c r="AZ77">
+        <v>12</v>
+      </c>
+      <c r="BA77">
+        <v>6</v>
+      </c>
+      <c r="BB77">
+        <v>2</v>
+      </c>
+      <c r="BC77">
+        <v>8</v>
+      </c>
+      <c r="BD77">
+        <v>1.45</v>
+      </c>
+      <c r="BE77">
+        <v>7</v>
+      </c>
+      <c r="BF77">
+        <v>3.05</v>
+      </c>
+      <c r="BG77">
+        <v>1.36</v>
+      </c>
+      <c r="BH77">
+        <v>2.8</v>
+      </c>
+      <c r="BI77">
+        <v>1.63</v>
+      </c>
+      <c r="BJ77">
+        <v>2.12</v>
+      </c>
+      <c r="BK77">
+        <v>1.98</v>
+      </c>
+      <c r="BL77">
+        <v>1.72</v>
+      </c>
+      <c r="BM77">
+        <v>2.5</v>
+      </c>
+      <c r="BN77">
+        <v>1.46</v>
+      </c>
+      <c r="BO77">
+        <v>3.3</v>
+      </c>
+      <c r="BP77">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:68">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7820392</v>
+      </c>
+      <c r="C78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45703.70833333334</v>
+      </c>
+      <c r="F78">
+        <v>6</v>
+      </c>
+      <c r="G78" t="s">
+        <v>96</v>
+      </c>
+      <c r="H78" t="s">
+        <v>80</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>2</v>
+      </c>
+      <c r="M78">
+        <v>2</v>
+      </c>
+      <c r="N78">
+        <v>4</v>
+      </c>
+      <c r="O78" t="s">
+        <v>147</v>
+      </c>
+      <c r="P78" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q78">
+        <v>5</v>
+      </c>
+      <c r="R78">
+        <v>2</v>
+      </c>
+      <c r="S78">
+        <v>2.63</v>
+      </c>
+      <c r="T78">
+        <v>1.53</v>
+      </c>
+      <c r="U78">
+        <v>2.38</v>
+      </c>
+      <c r="V78">
+        <v>3.5</v>
+      </c>
+      <c r="W78">
+        <v>1.29</v>
+      </c>
+      <c r="X78">
+        <v>11</v>
+      </c>
+      <c r="Y78">
+        <v>1.05</v>
+      </c>
+      <c r="Z78">
+        <v>4.39</v>
+      </c>
+      <c r="AA78">
+        <v>3.3</v>
+      </c>
+      <c r="AB78">
+        <v>1.84</v>
+      </c>
+      <c r="AC78">
+        <v>1.1</v>
+      </c>
+      <c r="AD78">
+        <v>6.5</v>
+      </c>
+      <c r="AE78">
+        <v>1.46</v>
+      </c>
+      <c r="AF78">
+        <v>2.5</v>
+      </c>
+      <c r="AG78">
+        <v>2.35</v>
+      </c>
+      <c r="AH78">
+        <v>1.57</v>
+      </c>
+      <c r="AI78">
+        <v>2.1</v>
+      </c>
+      <c r="AJ78">
+        <v>1.67</v>
+      </c>
+      <c r="AK78">
+        <v>1.85</v>
+      </c>
+      <c r="AL78">
+        <v>1.33</v>
+      </c>
+      <c r="AM78">
+        <v>1.2</v>
+      </c>
+      <c r="AN78">
+        <v>0</v>
+      </c>
+      <c r="AO78">
+        <v>1</v>
+      </c>
+      <c r="AP78">
+        <v>0.33</v>
+      </c>
+      <c r="AQ78">
+        <v>1</v>
+      </c>
+      <c r="AR78">
+        <v>2.48</v>
+      </c>
+      <c r="AS78">
+        <v>1.02</v>
+      </c>
+      <c r="AT78">
+        <v>3.5</v>
+      </c>
+      <c r="AU78">
+        <v>5</v>
+      </c>
+      <c r="AV78">
+        <v>4</v>
+      </c>
+      <c r="AW78">
+        <v>6</v>
+      </c>
+      <c r="AX78">
+        <v>3</v>
+      </c>
+      <c r="AY78">
+        <v>12</v>
+      </c>
+      <c r="AZ78">
+        <v>7</v>
+      </c>
+      <c r="BA78">
+        <v>6</v>
+      </c>
+      <c r="BB78">
+        <v>3</v>
+      </c>
+      <c r="BC78">
+        <v>9</v>
+      </c>
+      <c r="BD78">
+        <v>2.3</v>
+      </c>
+      <c r="BE78">
+        <v>6.4</v>
+      </c>
+      <c r="BF78">
+        <v>1.75</v>
+      </c>
+      <c r="BG78">
+        <v>1.41</v>
+      </c>
+      <c r="BH78">
+        <v>2.65</v>
+      </c>
+      <c r="BI78">
+        <v>1.71</v>
+      </c>
+      <c r="BJ78">
+        <v>2</v>
+      </c>
+      <c r="BK78">
+        <v>2.12</v>
+      </c>
+      <c r="BL78">
+        <v>1.63</v>
+      </c>
+      <c r="BM78">
+        <v>2.7</v>
+      </c>
+      <c r="BN78">
+        <v>1.38</v>
+      </c>
+      <c r="BO78">
+        <v>3.65</v>
+      </c>
+      <c r="BP78">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="185">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -460,6 +460,15 @@
     <t>['57', '77']</t>
   </si>
   <si>
+    <t>['18', '42', '61', '87']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['83', '88']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -554,6 +563,12 @@
   </si>
   <si>
     <t>['12', '81']</t>
+  </si>
+  <si>
+    <t>['5', '25', '55', '90+1']</t>
+  </si>
+  <si>
+    <t>['22', '28', '47']</t>
   </si>
 </sst>
 </file>
@@ -915,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP78"/>
+  <dimension ref="A1:BP81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1171,7 +1186,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1583,7 +1598,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1789,7 +1804,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -1995,7 +2010,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2201,7 +2216,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2407,7 +2422,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2613,7 +2628,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2819,7 +2834,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3231,7 +3246,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3643,7 +3658,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q14">
         <v>6.5</v>
@@ -3930,7 +3945,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ15">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4673,7 +4688,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5163,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ21">
         <v>1.67</v>
@@ -5291,7 +5306,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5497,7 +5512,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5703,7 +5718,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6115,7 +6130,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6527,7 +6542,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6811,10 +6826,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7020,7 +7035,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -8175,7 +8190,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8999,7 +9014,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9823,7 +9838,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10029,7 +10044,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10235,7 +10250,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10441,7 +10456,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10647,7 +10662,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -10728,7 +10743,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ48">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR48">
         <v>1.53</v>
@@ -11140,7 +11155,7 @@
         <v>2</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>2.5</v>
@@ -11265,7 +11280,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11343,7 +11358,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -11471,7 +11486,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11552,7 +11567,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ52">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR52">
         <v>1.64</v>
@@ -11883,7 +11898,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12373,7 +12388,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
         <v>1.33</v>
@@ -12501,7 +12516,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13325,7 +13340,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14561,7 +14576,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14767,7 +14782,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15591,7 +15606,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15797,7 +15812,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16415,7 +16430,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16621,7 +16636,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16827,7 +16842,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -16984,6 +16999,624 @@
       </c>
       <c r="BP78">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7820393</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45703.80208333334</v>
+      </c>
+      <c r="F79">
+        <v>6</v>
+      </c>
+      <c r="G79" t="s">
+        <v>84</v>
+      </c>
+      <c r="H79" t="s">
+        <v>77</v>
+      </c>
+      <c r="I79">
+        <v>2</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>2</v>
+      </c>
+      <c r="L79">
+        <v>4</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>4</v>
+      </c>
+      <c r="O79" t="s">
+        <v>148</v>
+      </c>
+      <c r="P79" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q79">
+        <v>3</v>
+      </c>
+      <c r="R79">
+        <v>2</v>
+      </c>
+      <c r="S79">
+        <v>4</v>
+      </c>
+      <c r="T79">
+        <v>1.5</v>
+      </c>
+      <c r="U79">
+        <v>2.5</v>
+      </c>
+      <c r="V79">
+        <v>3.5</v>
+      </c>
+      <c r="W79">
+        <v>1.29</v>
+      </c>
+      <c r="X79">
+        <v>11</v>
+      </c>
+      <c r="Y79">
+        <v>1.05</v>
+      </c>
+      <c r="Z79">
+        <v>2.2</v>
+      </c>
+      <c r="AA79">
+        <v>3.3</v>
+      </c>
+      <c r="AB79">
+        <v>3.4</v>
+      </c>
+      <c r="AC79">
+        <v>1.1</v>
+      </c>
+      <c r="AD79">
+        <v>6.25</v>
+      </c>
+      <c r="AE79">
+        <v>1.49</v>
+      </c>
+      <c r="AF79">
+        <v>2.45</v>
+      </c>
+      <c r="AG79">
+        <v>2.3</v>
+      </c>
+      <c r="AH79">
+        <v>1.6</v>
+      </c>
+      <c r="AI79">
+        <v>2</v>
+      </c>
+      <c r="AJ79">
+        <v>1.75</v>
+      </c>
+      <c r="AK79">
+        <v>1.3</v>
+      </c>
+      <c r="AL79">
+        <v>1.37</v>
+      </c>
+      <c r="AM79">
+        <v>1.6</v>
+      </c>
+      <c r="AN79">
+        <v>3</v>
+      </c>
+      <c r="AO79">
+        <v>0.5</v>
+      </c>
+      <c r="AP79">
+        <v>3</v>
+      </c>
+      <c r="AQ79">
+        <v>0.33</v>
+      </c>
+      <c r="AR79">
+        <v>1.81</v>
+      </c>
+      <c r="AS79">
+        <v>1.48</v>
+      </c>
+      <c r="AT79">
+        <v>3.29</v>
+      </c>
+      <c r="AU79">
+        <v>13</v>
+      </c>
+      <c r="AV79">
+        <v>3</v>
+      </c>
+      <c r="AW79">
+        <v>9</v>
+      </c>
+      <c r="AX79">
+        <v>8</v>
+      </c>
+      <c r="AY79">
+        <v>27</v>
+      </c>
+      <c r="AZ79">
+        <v>13</v>
+      </c>
+      <c r="BA79">
+        <v>9</v>
+      </c>
+      <c r="BB79">
+        <v>0</v>
+      </c>
+      <c r="BC79">
+        <v>9</v>
+      </c>
+      <c r="BD79">
+        <v>1.67</v>
+      </c>
+      <c r="BE79">
+        <v>6.4</v>
+      </c>
+      <c r="BF79">
+        <v>2.48</v>
+      </c>
+      <c r="BG79">
+        <v>1.48</v>
+      </c>
+      <c r="BH79">
+        <v>2.45</v>
+      </c>
+      <c r="BI79">
+        <v>1.78</v>
+      </c>
+      <c r="BJ79">
+        <v>1.91</v>
+      </c>
+      <c r="BK79">
+        <v>2.25</v>
+      </c>
+      <c r="BL79">
+        <v>1.55</v>
+      </c>
+      <c r="BM79">
+        <v>2.95</v>
+      </c>
+      <c r="BN79">
+        <v>1.33</v>
+      </c>
+      <c r="BO79">
+        <v>3.9</v>
+      </c>
+      <c r="BP79">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7820394</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45703.80208333334</v>
+      </c>
+      <c r="F80">
+        <v>6</v>
+      </c>
+      <c r="G80" t="s">
+        <v>89</v>
+      </c>
+      <c r="H80" t="s">
+        <v>71</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="M80">
+        <v>4</v>
+      </c>
+      <c r="N80">
+        <v>5</v>
+      </c>
+      <c r="O80" t="s">
+        <v>149</v>
+      </c>
+      <c r="P80" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q80">
+        <v>3.2</v>
+      </c>
+      <c r="R80">
+        <v>1.91</v>
+      </c>
+      <c r="S80">
+        <v>4</v>
+      </c>
+      <c r="T80">
+        <v>1.57</v>
+      </c>
+      <c r="U80">
+        <v>2.25</v>
+      </c>
+      <c r="V80">
+        <v>3.75</v>
+      </c>
+      <c r="W80">
+        <v>1.25</v>
+      </c>
+      <c r="X80">
+        <v>13</v>
+      </c>
+      <c r="Y80">
+        <v>1.04</v>
+      </c>
+      <c r="Z80">
+        <v>2.3</v>
+      </c>
+      <c r="AA80">
+        <v>2.9</v>
+      </c>
+      <c r="AB80">
+        <v>3.5</v>
+      </c>
+      <c r="AC80">
+        <v>1.07</v>
+      </c>
+      <c r="AD80">
+        <v>6.25</v>
+      </c>
+      <c r="AE80">
+        <v>1.53</v>
+      </c>
+      <c r="AF80">
+        <v>2.5</v>
+      </c>
+      <c r="AG80">
+        <v>2.6</v>
+      </c>
+      <c r="AH80">
+        <v>1.48</v>
+      </c>
+      <c r="AI80">
+        <v>2.1</v>
+      </c>
+      <c r="AJ80">
+        <v>1.67</v>
+      </c>
+      <c r="AK80">
+        <v>1.33</v>
+      </c>
+      <c r="AL80">
+        <v>1.38</v>
+      </c>
+      <c r="AM80">
+        <v>1.53</v>
+      </c>
+      <c r="AN80">
+        <v>1</v>
+      </c>
+      <c r="AO80">
+        <v>0</v>
+      </c>
+      <c r="AP80">
+        <v>0.67</v>
+      </c>
+      <c r="AQ80">
+        <v>1</v>
+      </c>
+      <c r="AR80">
+        <v>1.76</v>
+      </c>
+      <c r="AS80">
+        <v>1.25</v>
+      </c>
+      <c r="AT80">
+        <v>3.01</v>
+      </c>
+      <c r="AU80">
+        <v>10</v>
+      </c>
+      <c r="AV80">
+        <v>8</v>
+      </c>
+      <c r="AW80">
+        <v>7</v>
+      </c>
+      <c r="AX80">
+        <v>12</v>
+      </c>
+      <c r="AY80">
+        <v>18</v>
+      </c>
+      <c r="AZ80">
+        <v>24</v>
+      </c>
+      <c r="BA80">
+        <v>4</v>
+      </c>
+      <c r="BB80">
+        <v>7</v>
+      </c>
+      <c r="BC80">
+        <v>11</v>
+      </c>
+      <c r="BD80">
+        <v>1.88</v>
+      </c>
+      <c r="BE80">
+        <v>6.25</v>
+      </c>
+      <c r="BF80">
+        <v>2.15</v>
+      </c>
+      <c r="BG80">
+        <v>1.49</v>
+      </c>
+      <c r="BH80">
+        <v>2.4</v>
+      </c>
+      <c r="BI80">
+        <v>1.82</v>
+      </c>
+      <c r="BJ80">
+        <v>1.86</v>
+      </c>
+      <c r="BK80">
+        <v>2.32</v>
+      </c>
+      <c r="BL80">
+        <v>1.53</v>
+      </c>
+      <c r="BM80">
+        <v>3.05</v>
+      </c>
+      <c r="BN80">
+        <v>1.32</v>
+      </c>
+      <c r="BO80">
+        <v>4.1</v>
+      </c>
+      <c r="BP80">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7820395</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45703.89583333334</v>
+      </c>
+      <c r="F81">
+        <v>6</v>
+      </c>
+      <c r="G81" t="s">
+        <v>97</v>
+      </c>
+      <c r="H81" t="s">
+        <v>98</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2</v>
+      </c>
+      <c r="K81">
+        <v>2</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="M81">
+        <v>3</v>
+      </c>
+      <c r="N81">
+        <v>5</v>
+      </c>
+      <c r="O81" t="s">
+        <v>150</v>
+      </c>
+      <c r="P81" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q81">
+        <v>2.75</v>
+      </c>
+      <c r="R81">
+        <v>2</v>
+      </c>
+      <c r="S81">
+        <v>4.75</v>
+      </c>
+      <c r="T81">
+        <v>1.53</v>
+      </c>
+      <c r="U81">
+        <v>2.38</v>
+      </c>
+      <c r="V81">
+        <v>3.5</v>
+      </c>
+      <c r="W81">
+        <v>1.29</v>
+      </c>
+      <c r="X81">
+        <v>11</v>
+      </c>
+      <c r="Y81">
+        <v>1.05</v>
+      </c>
+      <c r="Z81">
+        <v>1.91</v>
+      </c>
+      <c r="AA81">
+        <v>3.5</v>
+      </c>
+      <c r="AB81">
+        <v>4</v>
+      </c>
+      <c r="AC81">
+        <v>1.09</v>
+      </c>
+      <c r="AD81">
+        <v>7.8</v>
+      </c>
+      <c r="AE81">
+        <v>1.46</v>
+      </c>
+      <c r="AF81">
+        <v>2.65</v>
+      </c>
+      <c r="AG81">
+        <v>2.35</v>
+      </c>
+      <c r="AH81">
+        <v>1.57</v>
+      </c>
+      <c r="AI81">
+        <v>2.1</v>
+      </c>
+      <c r="AJ81">
+        <v>1.67</v>
+      </c>
+      <c r="AK81">
+        <v>1.25</v>
+      </c>
+      <c r="AL81">
+        <v>1.3</v>
+      </c>
+      <c r="AM81">
+        <v>1.8</v>
+      </c>
+      <c r="AN81">
+        <v>3</v>
+      </c>
+      <c r="AO81">
+        <v>2</v>
+      </c>
+      <c r="AP81">
+        <v>2</v>
+      </c>
+      <c r="AQ81">
+        <v>2.33</v>
+      </c>
+      <c r="AR81">
+        <v>1.47</v>
+      </c>
+      <c r="AS81">
+        <v>1.52</v>
+      </c>
+      <c r="AT81">
+        <v>2.99</v>
+      </c>
+      <c r="AU81">
+        <v>4</v>
+      </c>
+      <c r="AV81">
+        <v>7</v>
+      </c>
+      <c r="AW81">
+        <v>8</v>
+      </c>
+      <c r="AX81">
+        <v>6</v>
+      </c>
+      <c r="AY81">
+        <v>14</v>
+      </c>
+      <c r="AZ81">
+        <v>15</v>
+      </c>
+      <c r="BA81">
+        <v>7</v>
+      </c>
+      <c r="BB81">
+        <v>5</v>
+      </c>
+      <c r="BC81">
+        <v>12</v>
+      </c>
+      <c r="BD81">
+        <v>1.75</v>
+      </c>
+      <c r="BE81">
+        <v>6.4</v>
+      </c>
+      <c r="BF81">
+        <v>2.32</v>
+      </c>
+      <c r="BG81">
+        <v>1.47</v>
+      </c>
+      <c r="BH81">
+        <v>2.48</v>
+      </c>
+      <c r="BI81">
+        <v>1.7</v>
+      </c>
+      <c r="BJ81">
+        <v>2.05</v>
+      </c>
+      <c r="BK81">
+        <v>2.28</v>
+      </c>
+      <c r="BL81">
+        <v>1.55</v>
+      </c>
+      <c r="BM81">
+        <v>2.95</v>
+      </c>
+      <c r="BN81">
+        <v>1.33</v>
+      </c>
+      <c r="BO81">
+        <v>3.95</v>
+      </c>
+      <c r="BP81">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="186">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -469,6 +469,9 @@
     <t>['83', '88']</t>
   </si>
   <si>
+    <t>['87']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -496,9 +499,6 @@
     <t>['80']</t>
   </si>
   <si>
-    <t>['87']</t>
-  </si>
-  <si>
     <t>['84']</t>
   </si>
   <si>
@@ -569,6 +569,9 @@
   </si>
   <si>
     <t>['22', '28', '47']</t>
+  </si>
+  <si>
+    <t>['16', '63']</t>
   </si>
 </sst>
 </file>
@@ -930,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP81"/>
+  <dimension ref="A1:BP82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1186,7 +1189,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1267,7 +1270,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ2">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1598,7 +1601,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1676,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ4">
         <v>2</v>
@@ -1804,7 +1807,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -2010,7 +2013,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2216,7 +2219,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2422,7 +2425,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2628,7 +2631,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2834,7 +2837,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3246,7 +3249,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3658,7 +3661,7 @@
         <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="Q14">
         <v>6.5</v>
@@ -7653,7 +7656,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ33">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR33">
         <v>1.45</v>
@@ -8474,7 +8477,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ37">
         <v>0</v>
@@ -14451,7 +14454,7 @@
         <v>1</v>
       </c>
       <c r="AQ66">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR66">
         <v>1.2</v>
@@ -14654,7 +14657,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ67">
         <v>2.33</v>
@@ -17617,6 +17620,212 @@
       </c>
       <c r="BP81">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:68">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7820396</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45704.70833333334</v>
+      </c>
+      <c r="F82">
+        <v>6</v>
+      </c>
+      <c r="G82" t="s">
+        <v>72</v>
+      </c>
+      <c r="H82" t="s">
+        <v>87</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>2</v>
+      </c>
+      <c r="N82">
+        <v>3</v>
+      </c>
+      <c r="O82" t="s">
+        <v>151</v>
+      </c>
+      <c r="P82" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q82">
+        <v>3.6</v>
+      </c>
+      <c r="R82">
+        <v>1.91</v>
+      </c>
+      <c r="S82">
+        <v>3.6</v>
+      </c>
+      <c r="T82">
+        <v>1.62</v>
+      </c>
+      <c r="U82">
+        <v>2.2</v>
+      </c>
+      <c r="V82">
+        <v>4</v>
+      </c>
+      <c r="W82">
+        <v>1.22</v>
+      </c>
+      <c r="X82">
+        <v>13</v>
+      </c>
+      <c r="Y82">
+        <v>1.04</v>
+      </c>
+      <c r="Z82">
+        <v>2.88</v>
+      </c>
+      <c r="AA82">
+        <v>2.8</v>
+      </c>
+      <c r="AB82">
+        <v>2.88</v>
+      </c>
+      <c r="AC82">
+        <v>1.13</v>
+      </c>
+      <c r="AD82">
+        <v>5.8</v>
+      </c>
+      <c r="AE82">
+        <v>1.5</v>
+      </c>
+      <c r="AF82">
+        <v>2.37</v>
+      </c>
+      <c r="AG82">
+        <v>2.7</v>
+      </c>
+      <c r="AH82">
+        <v>1.44</v>
+      </c>
+      <c r="AI82">
+        <v>2.1</v>
+      </c>
+      <c r="AJ82">
+        <v>1.67</v>
+      </c>
+      <c r="AK82">
+        <v>1.44</v>
+      </c>
+      <c r="AL82">
+        <v>1.4</v>
+      </c>
+      <c r="AM82">
+        <v>1.39</v>
+      </c>
+      <c r="AN82">
+        <v>1</v>
+      </c>
+      <c r="AO82">
+        <v>1.67</v>
+      </c>
+      <c r="AP82">
+        <v>0.75</v>
+      </c>
+      <c r="AQ82">
+        <v>2</v>
+      </c>
+      <c r="AR82">
+        <v>1.71</v>
+      </c>
+      <c r="AS82">
+        <v>1.39</v>
+      </c>
+      <c r="AT82">
+        <v>3.1</v>
+      </c>
+      <c r="AU82">
+        <v>7</v>
+      </c>
+      <c r="AV82">
+        <v>3</v>
+      </c>
+      <c r="AW82">
+        <v>9</v>
+      </c>
+      <c r="AX82">
+        <v>4</v>
+      </c>
+      <c r="AY82">
+        <v>21</v>
+      </c>
+      <c r="AZ82">
+        <v>8</v>
+      </c>
+      <c r="BA82">
+        <v>13</v>
+      </c>
+      <c r="BB82">
+        <v>5</v>
+      </c>
+      <c r="BC82">
+        <v>18</v>
+      </c>
+      <c r="BD82">
+        <v>1.8</v>
+      </c>
+      <c r="BE82">
+        <v>6.7</v>
+      </c>
+      <c r="BF82">
+        <v>2.35</v>
+      </c>
+      <c r="BG82">
+        <v>1.33</v>
+      </c>
+      <c r="BH82">
+        <v>2.98</v>
+      </c>
+      <c r="BI82">
+        <v>1.62</v>
+      </c>
+      <c r="BJ82">
+        <v>2.12</v>
+      </c>
+      <c r="BK82">
+        <v>2.1</v>
+      </c>
+      <c r="BL82">
+        <v>1.62</v>
+      </c>
+      <c r="BM82">
+        <v>2.85</v>
+      </c>
+      <c r="BN82">
+        <v>1.36</v>
+      </c>
+      <c r="BO82">
+        <v>4.1</v>
+      </c>
+      <c r="BP82">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="189">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -472,6 +472,15 @@
     <t>['87']</t>
   </si>
   <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -487,9 +496,6 @@
     <t>['30', '74', '90+2']</t>
   </si>
   <si>
-    <t>['77']</t>
-  </si>
-  <si>
     <t>['38']</t>
   </si>
   <si>
@@ -572,6 +578,9 @@
   </si>
   <si>
     <t>['16', '63']</t>
+  </si>
+  <si>
+    <t>['47']</t>
   </si>
 </sst>
 </file>
@@ -933,7 +942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP82"/>
+  <dimension ref="A1:BP85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1189,7 +1198,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1601,7 +1610,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1807,7 +1816,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -2013,7 +2022,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2219,7 +2228,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2425,7 +2434,7 @@
         <v>103</v>
       </c>
       <c r="P8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2631,7 +2640,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2837,7 +2846,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3249,7 +3258,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -4691,7 +4700,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -4772,7 +4781,7 @@
         <v>3</v>
       </c>
       <c r="AQ19">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5309,7 +5318,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5515,7 +5524,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5593,7 +5602,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ23">
         <v>1.5</v>
@@ -5721,7 +5730,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6005,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6133,7 +6142,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6545,7 +6554,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -8193,7 +8202,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -9017,7 +9026,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9841,7 +9850,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10047,7 +10056,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10253,7 +10262,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10459,7 +10468,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10665,7 +10674,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11155,7 +11164,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11283,7 +11292,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11489,7 +11498,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11901,7 +11910,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12519,7 +12528,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13215,10 +13224,10 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ60">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>2.21</v>
@@ -13343,7 +13352,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14579,7 +14588,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14785,7 +14794,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15609,7 +15618,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15815,7 +15824,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16433,7 +16442,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16639,7 +16648,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16845,7 +16854,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17257,7 +17266,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17463,7 +17472,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17669,7 +17678,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -17826,6 +17835,624 @@
       </c>
       <c r="BP82">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:68">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7820397</v>
+      </c>
+      <c r="C83" t="s">
+        <v>68</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45704.80208333334</v>
+      </c>
+      <c r="F83">
+        <v>6</v>
+      </c>
+      <c r="G83" t="s">
+        <v>95</v>
+      </c>
+      <c r="H83" t="s">
+        <v>74</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>1</v>
+      </c>
+      <c r="O83" t="s">
+        <v>152</v>
+      </c>
+      <c r="P83" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q83">
+        <v>2.38</v>
+      </c>
+      <c r="R83">
+        <v>2.05</v>
+      </c>
+      <c r="S83">
+        <v>6</v>
+      </c>
+      <c r="T83">
+        <v>1.5</v>
+      </c>
+      <c r="U83">
+        <v>2.5</v>
+      </c>
+      <c r="V83">
+        <v>3.4</v>
+      </c>
+      <c r="W83">
+        <v>1.3</v>
+      </c>
+      <c r="X83">
+        <v>10</v>
+      </c>
+      <c r="Y83">
+        <v>1.06</v>
+      </c>
+      <c r="Z83">
+        <v>1.7</v>
+      </c>
+      <c r="AA83">
+        <v>3.6</v>
+      </c>
+      <c r="AB83">
+        <v>5.25</v>
+      </c>
+      <c r="AC83">
+        <v>1.08</v>
+      </c>
+      <c r="AD83">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE83">
+        <v>1.42</v>
+      </c>
+      <c r="AF83">
+        <v>2.8</v>
+      </c>
+      <c r="AG83">
+        <v>2.25</v>
+      </c>
+      <c r="AH83">
+        <v>1.62</v>
+      </c>
+      <c r="AI83">
+        <v>2.1</v>
+      </c>
+      <c r="AJ83">
+        <v>1.67</v>
+      </c>
+      <c r="AK83">
+        <v>1.16</v>
+      </c>
+      <c r="AL83">
+        <v>1.27</v>
+      </c>
+      <c r="AM83">
+        <v>2.1</v>
+      </c>
+      <c r="AN83">
+        <v>3</v>
+      </c>
+      <c r="AO83">
+        <v>1.5</v>
+      </c>
+      <c r="AP83">
+        <v>3</v>
+      </c>
+      <c r="AQ83">
+        <v>1</v>
+      </c>
+      <c r="AR83">
+        <v>1.66</v>
+      </c>
+      <c r="AS83">
+        <v>1.06</v>
+      </c>
+      <c r="AT83">
+        <v>2.72</v>
+      </c>
+      <c r="AU83">
+        <v>5</v>
+      </c>
+      <c r="AV83">
+        <v>5</v>
+      </c>
+      <c r="AW83">
+        <v>9</v>
+      </c>
+      <c r="AX83">
+        <v>4</v>
+      </c>
+      <c r="AY83">
+        <v>17</v>
+      </c>
+      <c r="AZ83">
+        <v>9</v>
+      </c>
+      <c r="BA83">
+        <v>2</v>
+      </c>
+      <c r="BB83">
+        <v>4</v>
+      </c>
+      <c r="BC83">
+        <v>6</v>
+      </c>
+      <c r="BD83">
+        <v>1.28</v>
+      </c>
+      <c r="BE83">
+        <v>8</v>
+      </c>
+      <c r="BF83">
+        <v>3.95</v>
+      </c>
+      <c r="BG83">
+        <v>1.3</v>
+      </c>
+      <c r="BH83">
+        <v>3.15</v>
+      </c>
+      <c r="BI83">
+        <v>1.5</v>
+      </c>
+      <c r="BJ83">
+        <v>2.38</v>
+      </c>
+      <c r="BK83">
+        <v>1.85</v>
+      </c>
+      <c r="BL83">
+        <v>1.85</v>
+      </c>
+      <c r="BM83">
+        <v>2.23</v>
+      </c>
+      <c r="BN83">
+        <v>1.56</v>
+      </c>
+      <c r="BO83">
+        <v>2.8</v>
+      </c>
+      <c r="BP83">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:68">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7820398</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45704.89583333334</v>
+      </c>
+      <c r="F84">
+        <v>6</v>
+      </c>
+      <c r="G84" t="s">
+        <v>93</v>
+      </c>
+      <c r="H84" t="s">
+        <v>94</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
+      </c>
+      <c r="O84" t="s">
+        <v>153</v>
+      </c>
+      <c r="P84" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q84">
+        <v>3</v>
+      </c>
+      <c r="R84">
+        <v>1.83</v>
+      </c>
+      <c r="S84">
+        <v>4.75</v>
+      </c>
+      <c r="T84">
+        <v>1.62</v>
+      </c>
+      <c r="U84">
+        <v>2.2</v>
+      </c>
+      <c r="V84">
+        <v>4</v>
+      </c>
+      <c r="W84">
+        <v>1.22</v>
+      </c>
+      <c r="X84">
+        <v>13</v>
+      </c>
+      <c r="Y84">
+        <v>1.04</v>
+      </c>
+      <c r="Z84">
+        <v>2.15</v>
+      </c>
+      <c r="AA84">
+        <v>2.8</v>
+      </c>
+      <c r="AB84">
+        <v>4.2</v>
+      </c>
+      <c r="AC84">
+        <v>1.14</v>
+      </c>
+      <c r="AD84">
+        <v>5.6</v>
+      </c>
+      <c r="AE84">
+        <v>1.57</v>
+      </c>
+      <c r="AF84">
+        <v>2.25</v>
+      </c>
+      <c r="AG84">
+        <v>2.88</v>
+      </c>
+      <c r="AH84">
+        <v>1.4</v>
+      </c>
+      <c r="AI84">
+        <v>2.2</v>
+      </c>
+      <c r="AJ84">
+        <v>1.62</v>
+      </c>
+      <c r="AK84">
+        <v>1.25</v>
+      </c>
+      <c r="AL84">
+        <v>1.38</v>
+      </c>
+      <c r="AM84">
+        <v>1.66</v>
+      </c>
+      <c r="AN84">
+        <v>2</v>
+      </c>
+      <c r="AO84">
+        <v>0</v>
+      </c>
+      <c r="AP84">
+        <v>2.33</v>
+      </c>
+      <c r="AQ84">
+        <v>0</v>
+      </c>
+      <c r="AR84">
+        <v>1.91</v>
+      </c>
+      <c r="AS84">
+        <v>1.2</v>
+      </c>
+      <c r="AT84">
+        <v>3.11</v>
+      </c>
+      <c r="AU84">
+        <v>5</v>
+      </c>
+      <c r="AV84">
+        <v>5</v>
+      </c>
+      <c r="AW84">
+        <v>5</v>
+      </c>
+      <c r="AX84">
+        <v>9</v>
+      </c>
+      <c r="AY84">
+        <v>12</v>
+      </c>
+      <c r="AZ84">
+        <v>16</v>
+      </c>
+      <c r="BA84">
+        <v>6</v>
+      </c>
+      <c r="BB84">
+        <v>8</v>
+      </c>
+      <c r="BC84">
+        <v>14</v>
+      </c>
+      <c r="BD84">
+        <v>1.73</v>
+      </c>
+      <c r="BE84">
+        <v>6.1</v>
+      </c>
+      <c r="BF84">
+        <v>2.4</v>
+      </c>
+      <c r="BG84">
+        <v>1.57</v>
+      </c>
+      <c r="BH84">
+        <v>2.23</v>
+      </c>
+      <c r="BI84">
+        <v>1.95</v>
+      </c>
+      <c r="BJ84">
+        <v>1.77</v>
+      </c>
+      <c r="BK84">
+        <v>2.5</v>
+      </c>
+      <c r="BL84">
+        <v>1.46</v>
+      </c>
+      <c r="BM84">
+        <v>3.35</v>
+      </c>
+      <c r="BN84">
+        <v>1.27</v>
+      </c>
+      <c r="BO84">
+        <v>4.6</v>
+      </c>
+      <c r="BP84">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:68">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7820399</v>
+      </c>
+      <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45704.89583333334</v>
+      </c>
+      <c r="F85">
+        <v>6</v>
+      </c>
+      <c r="G85" t="s">
+        <v>91</v>
+      </c>
+      <c r="H85" t="s">
+        <v>99</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85">
+        <v>2</v>
+      </c>
+      <c r="O85" t="s">
+        <v>154</v>
+      </c>
+      <c r="P85" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q85">
+        <v>2.75</v>
+      </c>
+      <c r="R85">
+        <v>1.91</v>
+      </c>
+      <c r="S85">
+        <v>5</v>
+      </c>
+      <c r="T85">
+        <v>1.57</v>
+      </c>
+      <c r="U85">
+        <v>2.25</v>
+      </c>
+      <c r="V85">
+        <v>3.75</v>
+      </c>
+      <c r="W85">
+        <v>1.25</v>
+      </c>
+      <c r="X85">
+        <v>13</v>
+      </c>
+      <c r="Y85">
+        <v>1.04</v>
+      </c>
+      <c r="Z85">
+        <v>1.95</v>
+      </c>
+      <c r="AA85">
+        <v>3.2</v>
+      </c>
+      <c r="AB85">
+        <v>4.33</v>
+      </c>
+      <c r="AC85">
+        <v>1.11</v>
+      </c>
+      <c r="AD85">
+        <v>6.6</v>
+      </c>
+      <c r="AE85">
+        <v>1.5</v>
+      </c>
+      <c r="AF85">
+        <v>2.37</v>
+      </c>
+      <c r="AG85">
+        <v>2.6</v>
+      </c>
+      <c r="AH85">
+        <v>1.48</v>
+      </c>
+      <c r="AI85">
+        <v>2.25</v>
+      </c>
+      <c r="AJ85">
+        <v>1.57</v>
+      </c>
+      <c r="AK85">
+        <v>1.22</v>
+      </c>
+      <c r="AL85">
+        <v>1.34</v>
+      </c>
+      <c r="AM85">
+        <v>1.78</v>
+      </c>
+      <c r="AN85">
+        <v>0</v>
+      </c>
+      <c r="AO85">
+        <v>1</v>
+      </c>
+      <c r="AP85">
+        <v>0.33</v>
+      </c>
+      <c r="AQ85">
+        <v>1</v>
+      </c>
+      <c r="AR85">
+        <v>2.29</v>
+      </c>
+      <c r="AS85">
+        <v>1.57</v>
+      </c>
+      <c r="AT85">
+        <v>3.86</v>
+      </c>
+      <c r="AU85">
+        <v>6</v>
+      </c>
+      <c r="AV85">
+        <v>6</v>
+      </c>
+      <c r="AW85">
+        <v>10</v>
+      </c>
+      <c r="AX85">
+        <v>5</v>
+      </c>
+      <c r="AY85">
+        <v>20</v>
+      </c>
+      <c r="AZ85">
+        <v>13</v>
+      </c>
+      <c r="BA85">
+        <v>5</v>
+      </c>
+      <c r="BB85">
+        <v>5</v>
+      </c>
+      <c r="BC85">
+        <v>10</v>
+      </c>
+      <c r="BD85">
+        <v>1.7</v>
+      </c>
+      <c r="BE85">
+        <v>6.4</v>
+      </c>
+      <c r="BF85">
+        <v>2.4</v>
+      </c>
+      <c r="BG85">
+        <v>1.35</v>
+      </c>
+      <c r="BH85">
+        <v>2.88</v>
+      </c>
+      <c r="BI85">
+        <v>1.6</v>
+      </c>
+      <c r="BJ85">
+        <v>2.17</v>
+      </c>
+      <c r="BK85">
+        <v>2.05</v>
+      </c>
+      <c r="BL85">
+        <v>1.7</v>
+      </c>
+      <c r="BM85">
+        <v>2.48</v>
+      </c>
+      <c r="BN85">
+        <v>1.47</v>
+      </c>
+      <c r="BO85">
+        <v>3.2</v>
+      </c>
+      <c r="BP85">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="195">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -481,6 +481,15 @@
     <t>['73']</t>
   </si>
   <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['84', '90+5']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -494,9 +503,6 @@
   </si>
   <si>
     <t>['30', '74', '90+2']</t>
-  </si>
-  <si>
-    <t>['38']</t>
   </si>
   <si>
     <t>['10']</t>
@@ -581,6 +587,18 @@
   </si>
   <si>
     <t>['47']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['18', '28']</t>
+  </si>
+  <si>
+    <t>['45+4']</t>
   </si>
 </sst>
 </file>
@@ -942,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP85"/>
+  <dimension ref="A1:BP90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1198,7 +1216,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1610,7 +1628,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1816,7 +1834,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -2022,7 +2040,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2103,7 +2121,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2228,7 +2246,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2640,7 +2658,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2846,7 +2864,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3258,7 +3276,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3542,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>0.33</v>
@@ -3748,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4575,7 +4593,7 @@
         <v>1</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4700,7 +4718,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -4984,10 +5002,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5318,7 +5336,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5396,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5524,7 +5542,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5605,7 +5623,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ23">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5730,7 +5748,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -5808,10 +5826,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6142,7 +6160,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6554,7 +6572,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -8202,7 +8220,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8692,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
         <v>0</v>
@@ -9026,7 +9044,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9850,7 +9868,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10056,7 +10074,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10137,7 +10155,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR45">
         <v>0</v>
@@ -10262,7 +10280,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10468,7 +10486,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10546,10 +10564,10 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR47">
         <v>1.66</v>
@@ -10674,7 +10692,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11292,7 +11310,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11498,7 +11516,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11782,10 +11800,10 @@
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ53">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR53">
         <v>1.58</v>
@@ -11910,7 +11928,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12197,7 +12215,7 @@
         <v>3</v>
       </c>
       <c r="AQ55">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR55">
         <v>1.6</v>
@@ -12528,7 +12546,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12812,7 +12830,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
         <v>0.33</v>
@@ -13018,10 +13036,10 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ59">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR59">
         <v>1.06</v>
@@ -13352,7 +13370,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14588,7 +14606,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14794,7 +14812,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15618,7 +15636,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15824,7 +15842,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16442,7 +16460,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16648,7 +16666,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16854,7 +16872,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17266,7 +17284,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17472,7 +17490,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17678,7 +17696,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18296,7 +18314,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18453,6 +18471,1036 @@
       </c>
       <c r="BP85">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="86" spans="1:68">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7820401</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45705.70833333334</v>
+      </c>
+      <c r="F86">
+        <v>6</v>
+      </c>
+      <c r="G86" t="s">
+        <v>92</v>
+      </c>
+      <c r="H86" t="s">
+        <v>78</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86" t="s">
+        <v>155</v>
+      </c>
+      <c r="P86" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q86">
+        <v>3.1</v>
+      </c>
+      <c r="R86">
+        <v>1.91</v>
+      </c>
+      <c r="S86">
+        <v>4.33</v>
+      </c>
+      <c r="T86">
+        <v>1.57</v>
+      </c>
+      <c r="U86">
+        <v>2.25</v>
+      </c>
+      <c r="V86">
+        <v>3.75</v>
+      </c>
+      <c r="W86">
+        <v>1.25</v>
+      </c>
+      <c r="X86">
+        <v>13</v>
+      </c>
+      <c r="Y86">
+        <v>1.04</v>
+      </c>
+      <c r="Z86">
+        <v>2.25</v>
+      </c>
+      <c r="AA86">
+        <v>3</v>
+      </c>
+      <c r="AB86">
+        <v>3.6</v>
+      </c>
+      <c r="AC86">
+        <v>1.12</v>
+      </c>
+      <c r="AD86">
+        <v>6.4</v>
+      </c>
+      <c r="AE86">
+        <v>1.5</v>
+      </c>
+      <c r="AF86">
+        <v>2.37</v>
+      </c>
+      <c r="AG86">
+        <v>2.6</v>
+      </c>
+      <c r="AH86">
+        <v>1.48</v>
+      </c>
+      <c r="AI86">
+        <v>2.1</v>
+      </c>
+      <c r="AJ86">
+        <v>1.67</v>
+      </c>
+      <c r="AK86">
+        <v>1.31</v>
+      </c>
+      <c r="AL86">
+        <v>1.36</v>
+      </c>
+      <c r="AM86">
+        <v>1.6</v>
+      </c>
+      <c r="AN86">
+        <v>1.5</v>
+      </c>
+      <c r="AO86">
+        <v>1</v>
+      </c>
+      <c r="AP86">
+        <v>2</v>
+      </c>
+      <c r="AQ86">
+        <v>0.67</v>
+      </c>
+      <c r="AR86">
+        <v>1.31</v>
+      </c>
+      <c r="AS86">
+        <v>1.49</v>
+      </c>
+      <c r="AT86">
+        <v>2.8</v>
+      </c>
+      <c r="AU86">
+        <v>4</v>
+      </c>
+      <c r="AV86">
+        <v>2</v>
+      </c>
+      <c r="AW86">
+        <v>4</v>
+      </c>
+      <c r="AX86">
+        <v>8</v>
+      </c>
+      <c r="AY86">
+        <v>9</v>
+      </c>
+      <c r="AZ86">
+        <v>14</v>
+      </c>
+      <c r="BA86">
+        <v>2</v>
+      </c>
+      <c r="BB86">
+        <v>4</v>
+      </c>
+      <c r="BC86">
+        <v>6</v>
+      </c>
+      <c r="BD86">
+        <v>1.63</v>
+      </c>
+      <c r="BE86">
+        <v>6.4</v>
+      </c>
+      <c r="BF86">
+        <v>2.55</v>
+      </c>
+      <c r="BG86">
+        <v>1.4</v>
+      </c>
+      <c r="BH86">
+        <v>2.65</v>
+      </c>
+      <c r="BI86">
+        <v>1.67</v>
+      </c>
+      <c r="BJ86">
+        <v>2.05</v>
+      </c>
+      <c r="BK86">
+        <v>2.05</v>
+      </c>
+      <c r="BL86">
+        <v>1.65</v>
+      </c>
+      <c r="BM86">
+        <v>2.65</v>
+      </c>
+      <c r="BN86">
+        <v>1.41</v>
+      </c>
+      <c r="BO86">
+        <v>3.45</v>
+      </c>
+      <c r="BP86">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:68">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7820400</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45705.70833333334</v>
+      </c>
+      <c r="F87">
+        <v>6</v>
+      </c>
+      <c r="G87" t="s">
+        <v>88</v>
+      </c>
+      <c r="H87" t="s">
+        <v>86</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>2</v>
+      </c>
+      <c r="M87">
+        <v>1</v>
+      </c>
+      <c r="N87">
+        <v>3</v>
+      </c>
+      <c r="O87" t="s">
+        <v>156</v>
+      </c>
+      <c r="P87" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q87">
+        <v>3.5</v>
+      </c>
+      <c r="R87">
+        <v>1.83</v>
+      </c>
+      <c r="S87">
+        <v>4</v>
+      </c>
+      <c r="T87">
+        <v>1.62</v>
+      </c>
+      <c r="U87">
+        <v>2.2</v>
+      </c>
+      <c r="V87">
+        <v>4</v>
+      </c>
+      <c r="W87">
+        <v>1.22</v>
+      </c>
+      <c r="X87">
+        <v>13</v>
+      </c>
+      <c r="Y87">
+        <v>1.04</v>
+      </c>
+      <c r="Z87">
+        <v>2.6</v>
+      </c>
+      <c r="AA87">
+        <v>2.75</v>
+      </c>
+      <c r="AB87">
+        <v>3.3</v>
+      </c>
+      <c r="AC87">
+        <v>1.14</v>
+      </c>
+      <c r="AD87">
+        <v>5.6</v>
+      </c>
+      <c r="AE87">
+        <v>1.57</v>
+      </c>
+      <c r="AF87">
+        <v>2.25</v>
+      </c>
+      <c r="AG87">
+        <v>2.88</v>
+      </c>
+      <c r="AH87">
+        <v>1.4</v>
+      </c>
+      <c r="AI87">
+        <v>2.2</v>
+      </c>
+      <c r="AJ87">
+        <v>1.62</v>
+      </c>
+      <c r="AK87">
+        <v>1.34</v>
+      </c>
+      <c r="AL87">
+        <v>1.38</v>
+      </c>
+      <c r="AM87">
+        <v>1.52</v>
+      </c>
+      <c r="AN87">
+        <v>1</v>
+      </c>
+      <c r="AO87">
+        <v>3</v>
+      </c>
+      <c r="AP87">
+        <v>1.67</v>
+      </c>
+      <c r="AQ87">
+        <v>2</v>
+      </c>
+      <c r="AR87">
+        <v>1.79</v>
+      </c>
+      <c r="AS87">
+        <v>1.27</v>
+      </c>
+      <c r="AT87">
+        <v>3.06</v>
+      </c>
+      <c r="AU87">
+        <v>9</v>
+      </c>
+      <c r="AV87">
+        <v>4</v>
+      </c>
+      <c r="AW87">
+        <v>7</v>
+      </c>
+      <c r="AX87">
+        <v>1</v>
+      </c>
+      <c r="AY87">
+        <v>18</v>
+      </c>
+      <c r="AZ87">
+        <v>5</v>
+      </c>
+      <c r="BA87">
+        <v>10</v>
+      </c>
+      <c r="BB87">
+        <v>1</v>
+      </c>
+      <c r="BC87">
+        <v>11</v>
+      </c>
+      <c r="BD87">
+        <v>1.72</v>
+      </c>
+      <c r="BE87">
+        <v>6.4</v>
+      </c>
+      <c r="BF87">
+        <v>2.4</v>
+      </c>
+      <c r="BG87">
+        <v>1.5</v>
+      </c>
+      <c r="BH87">
+        <v>2.38</v>
+      </c>
+      <c r="BI87">
+        <v>1.8</v>
+      </c>
+      <c r="BJ87">
+        <v>1.91</v>
+      </c>
+      <c r="BK87">
+        <v>2.33</v>
+      </c>
+      <c r="BL87">
+        <v>1.5</v>
+      </c>
+      <c r="BM87">
+        <v>3.05</v>
+      </c>
+      <c r="BN87">
+        <v>1.3</v>
+      </c>
+      <c r="BO87">
+        <v>4.1</v>
+      </c>
+      <c r="BP87">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="88" spans="1:68">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7820402</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45705.80208333334</v>
+      </c>
+      <c r="F88">
+        <v>6</v>
+      </c>
+      <c r="G88" t="s">
+        <v>82</v>
+      </c>
+      <c r="H88" t="s">
+        <v>76</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>2</v>
+      </c>
+      <c r="O88" t="s">
+        <v>157</v>
+      </c>
+      <c r="P88" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q88">
+        <v>4.33</v>
+      </c>
+      <c r="R88">
+        <v>1.8</v>
+      </c>
+      <c r="S88">
+        <v>3.5</v>
+      </c>
+      <c r="T88">
+        <v>1.73</v>
+      </c>
+      <c r="U88">
+        <v>2</v>
+      </c>
+      <c r="V88">
+        <v>5</v>
+      </c>
+      <c r="W88">
+        <v>1.17</v>
+      </c>
+      <c r="X88">
+        <v>17</v>
+      </c>
+      <c r="Y88">
+        <v>1.03</v>
+      </c>
+      <c r="Z88">
+        <v>3.3</v>
+      </c>
+      <c r="AA88">
+        <v>2.8</v>
+      </c>
+      <c r="AB88">
+        <v>2.55</v>
+      </c>
+      <c r="AC88">
+        <v>1.17</v>
+      </c>
+      <c r="AD88">
+        <v>5</v>
+      </c>
+      <c r="AE88">
+        <v>1.67</v>
+      </c>
+      <c r="AF88">
+        <v>2.1</v>
+      </c>
+      <c r="AG88">
+        <v>3.4</v>
+      </c>
+      <c r="AH88">
+        <v>1.33</v>
+      </c>
+      <c r="AI88">
+        <v>2.5</v>
+      </c>
+      <c r="AJ88">
+        <v>1.5</v>
+      </c>
+      <c r="AK88">
+        <v>1.49</v>
+      </c>
+      <c r="AL88">
+        <v>1.41</v>
+      </c>
+      <c r="AM88">
+        <v>1.34</v>
+      </c>
+      <c r="AN88">
+        <v>2</v>
+      </c>
+      <c r="AO88">
+        <v>1.5</v>
+      </c>
+      <c r="AP88">
+        <v>1.67</v>
+      </c>
+      <c r="AQ88">
+        <v>1.33</v>
+      </c>
+      <c r="AR88">
+        <v>1.23</v>
+      </c>
+      <c r="AS88">
+        <v>0.97</v>
+      </c>
+      <c r="AT88">
+        <v>2.2</v>
+      </c>
+      <c r="AU88">
+        <v>3</v>
+      </c>
+      <c r="AV88">
+        <v>3</v>
+      </c>
+      <c r="AW88">
+        <v>5</v>
+      </c>
+      <c r="AX88">
+        <v>3</v>
+      </c>
+      <c r="AY88">
+        <v>10</v>
+      </c>
+      <c r="AZ88">
+        <v>8</v>
+      </c>
+      <c r="BA88">
+        <v>9</v>
+      </c>
+      <c r="BB88">
+        <v>1</v>
+      </c>
+      <c r="BC88">
+        <v>10</v>
+      </c>
+      <c r="BD88">
+        <v>2.32</v>
+      </c>
+      <c r="BE88">
+        <v>6.4</v>
+      </c>
+      <c r="BF88">
+        <v>1.82</v>
+      </c>
+      <c r="BG88">
+        <v>1.52</v>
+      </c>
+      <c r="BH88">
+        <v>2.32</v>
+      </c>
+      <c r="BI88">
+        <v>1.95</v>
+      </c>
+      <c r="BJ88">
+        <v>1.75</v>
+      </c>
+      <c r="BK88">
+        <v>2.65</v>
+      </c>
+      <c r="BL88">
+        <v>1.41</v>
+      </c>
+      <c r="BM88">
+        <v>3.8</v>
+      </c>
+      <c r="BN88">
+        <v>1.22</v>
+      </c>
+      <c r="BO88">
+        <v>5.15</v>
+      </c>
+      <c r="BP88">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:68">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7820403</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45705.89583333334</v>
+      </c>
+      <c r="F89">
+        <v>6</v>
+      </c>
+      <c r="G89" t="s">
+        <v>90</v>
+      </c>
+      <c r="H89" t="s">
+        <v>70</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2</v>
+      </c>
+      <c r="K89">
+        <v>2</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>2</v>
+      </c>
+      <c r="N89">
+        <v>2</v>
+      </c>
+      <c r="O89" t="s">
+        <v>100</v>
+      </c>
+      <c r="P89" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q89">
+        <v>2.5</v>
+      </c>
+      <c r="R89">
+        <v>2</v>
+      </c>
+      <c r="S89">
+        <v>6</v>
+      </c>
+      <c r="T89">
+        <v>1.53</v>
+      </c>
+      <c r="U89">
+        <v>2.38</v>
+      </c>
+      <c r="V89">
+        <v>3.75</v>
+      </c>
+      <c r="W89">
+        <v>1.25</v>
+      </c>
+      <c r="X89">
+        <v>11</v>
+      </c>
+      <c r="Y89">
+        <v>1.05</v>
+      </c>
+      <c r="Z89">
+        <v>1.73</v>
+      </c>
+      <c r="AA89">
+        <v>3.5</v>
+      </c>
+      <c r="AB89">
+        <v>5.25</v>
+      </c>
+      <c r="AC89">
+        <v>1.1</v>
+      </c>
+      <c r="AD89">
+        <v>7</v>
+      </c>
+      <c r="AE89">
+        <v>1.48</v>
+      </c>
+      <c r="AF89">
+        <v>2.55</v>
+      </c>
+      <c r="AG89">
+        <v>2.4</v>
+      </c>
+      <c r="AH89">
+        <v>1.53</v>
+      </c>
+      <c r="AI89">
+        <v>2.25</v>
+      </c>
+      <c r="AJ89">
+        <v>1.57</v>
+      </c>
+      <c r="AK89">
+        <v>1.16</v>
+      </c>
+      <c r="AL89">
+        <v>1.3</v>
+      </c>
+      <c r="AM89">
+        <v>2</v>
+      </c>
+      <c r="AN89">
+        <v>0.5</v>
+      </c>
+      <c r="AO89">
+        <v>0.5</v>
+      </c>
+      <c r="AP89">
+        <v>0.33</v>
+      </c>
+      <c r="AQ89">
+        <v>1.33</v>
+      </c>
+      <c r="AR89">
+        <v>1.41</v>
+      </c>
+      <c r="AS89">
+        <v>1.11</v>
+      </c>
+      <c r="AT89">
+        <v>2.52</v>
+      </c>
+      <c r="AU89">
+        <v>6</v>
+      </c>
+      <c r="AV89">
+        <v>4</v>
+      </c>
+      <c r="AW89">
+        <v>10</v>
+      </c>
+      <c r="AX89">
+        <v>3</v>
+      </c>
+      <c r="AY89">
+        <v>18</v>
+      </c>
+      <c r="AZ89">
+        <v>8</v>
+      </c>
+      <c r="BA89">
+        <v>6</v>
+      </c>
+      <c r="BB89">
+        <v>4</v>
+      </c>
+      <c r="BC89">
+        <v>10</v>
+      </c>
+      <c r="BD89">
+        <v>1.35</v>
+      </c>
+      <c r="BE89">
+        <v>6.8</v>
+      </c>
+      <c r="BF89">
+        <v>4.2</v>
+      </c>
+      <c r="BG89">
+        <v>1.31</v>
+      </c>
+      <c r="BH89">
+        <v>3.1</v>
+      </c>
+      <c r="BI89">
+        <v>1.55</v>
+      </c>
+      <c r="BJ89">
+        <v>2.22</v>
+      </c>
+      <c r="BK89">
+        <v>2.02</v>
+      </c>
+      <c r="BL89">
+        <v>1.68</v>
+      </c>
+      <c r="BM89">
+        <v>2.72</v>
+      </c>
+      <c r="BN89">
+        <v>1.4</v>
+      </c>
+      <c r="BO89">
+        <v>4</v>
+      </c>
+      <c r="BP89">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:68">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7820404</v>
+      </c>
+      <c r="C90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45705.89583333334</v>
+      </c>
+      <c r="F90">
+        <v>6</v>
+      </c>
+      <c r="G90" t="s">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s">
+        <v>79</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>1</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
+      <c r="O90" t="s">
+        <v>100</v>
+      </c>
+      <c r="P90" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q90">
+        <v>3</v>
+      </c>
+      <c r="R90">
+        <v>1.83</v>
+      </c>
+      <c r="S90">
+        <v>5</v>
+      </c>
+      <c r="T90">
+        <v>1.67</v>
+      </c>
+      <c r="U90">
+        <v>2.1</v>
+      </c>
+      <c r="V90">
+        <v>4.33</v>
+      </c>
+      <c r="W90">
+        <v>1.2</v>
+      </c>
+      <c r="X90">
+        <v>15</v>
+      </c>
+      <c r="Y90">
+        <v>1.03</v>
+      </c>
+      <c r="Z90">
+        <v>2.15</v>
+      </c>
+      <c r="AA90">
+        <v>3.1</v>
+      </c>
+      <c r="AB90">
+        <v>3.8</v>
+      </c>
+      <c r="AC90">
+        <v>1.16</v>
+      </c>
+      <c r="AD90">
+        <v>5.2</v>
+      </c>
+      <c r="AE90">
+        <v>1.67</v>
+      </c>
+      <c r="AF90">
+        <v>2.05</v>
+      </c>
+      <c r="AG90">
+        <v>2.88</v>
+      </c>
+      <c r="AH90">
+        <v>1.4</v>
+      </c>
+      <c r="AI90">
+        <v>2.38</v>
+      </c>
+      <c r="AJ90">
+        <v>1.53</v>
+      </c>
+      <c r="AK90">
+        <v>1.26</v>
+      </c>
+      <c r="AL90">
+        <v>1.39</v>
+      </c>
+      <c r="AM90">
+        <v>1.63</v>
+      </c>
+      <c r="AN90">
+        <v>3</v>
+      </c>
+      <c r="AO90">
+        <v>2</v>
+      </c>
+      <c r="AP90">
+        <v>2</v>
+      </c>
+      <c r="AQ90">
+        <v>2.33</v>
+      </c>
+      <c r="AR90">
+        <v>1.46</v>
+      </c>
+      <c r="AS90">
+        <v>0.8</v>
+      </c>
+      <c r="AT90">
+        <v>2.26</v>
+      </c>
+      <c r="AU90">
+        <v>2</v>
+      </c>
+      <c r="AV90">
+        <v>3</v>
+      </c>
+      <c r="AW90">
+        <v>7</v>
+      </c>
+      <c r="AX90">
+        <v>1</v>
+      </c>
+      <c r="AY90">
+        <v>10</v>
+      </c>
+      <c r="AZ90">
+        <v>4</v>
+      </c>
+      <c r="BA90">
+        <v>4</v>
+      </c>
+      <c r="BB90">
+        <v>1</v>
+      </c>
+      <c r="BC90">
+        <v>5</v>
+      </c>
+      <c r="BD90">
+        <v>1.62</v>
+      </c>
+      <c r="BE90">
+        <v>5.95</v>
+      </c>
+      <c r="BF90">
+        <v>2.85</v>
+      </c>
+      <c r="BG90">
+        <v>1.32</v>
+      </c>
+      <c r="BH90">
+        <v>3</v>
+      </c>
+      <c r="BI90">
+        <v>1.6</v>
+      </c>
+      <c r="BJ90">
+        <v>2.15</v>
+      </c>
+      <c r="BK90">
+        <v>2.05</v>
+      </c>
+      <c r="BL90">
+        <v>1.65</v>
+      </c>
+      <c r="BM90">
+        <v>2.85</v>
+      </c>
+      <c r="BN90">
+        <v>1.36</v>
+      </c>
+      <c r="BO90">
+        <v>4</v>
+      </c>
+      <c r="BP90">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -19249,13 +19249,13 @@
         <v>8</v>
       </c>
       <c r="BA89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB89">
         <v>4</v>
       </c>
       <c r="BC89">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD89">
         <v>1.35</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="198">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -490,6 +490,12 @@
     <t>['89']</t>
   </si>
   <si>
+    <t>['69', '71', '84']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -599,6 +605,9 @@
   </si>
   <si>
     <t>['45+4']</t>
+  </si>
+  <si>
+    <t>['44', '51']</t>
   </si>
 </sst>
 </file>
@@ -960,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP90"/>
+  <dimension ref="A1:BP94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1216,7 +1225,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1294,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ2">
         <v>2</v>
@@ -1503,7 +1512,7 @@
         <v>3</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1628,7 +1637,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1834,7 +1843,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -2040,7 +2049,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2118,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ6">
         <v>2</v>
@@ -2246,7 +2255,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2864,7 +2873,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3151,7 +3160,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3276,7 +3285,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -4718,7 +4727,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5336,7 +5345,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5542,7 +5551,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5748,7 +5757,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6160,7 +6169,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6572,7 +6581,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7886,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ34">
         <v>0</v>
@@ -8220,7 +8229,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8713,7 +8722,7 @@
         <v>2</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AR38">
         <v>1.8</v>
@@ -9044,7 +9053,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9125,7 +9134,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR40">
         <v>1.12</v>
@@ -9868,7 +9877,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10074,7 +10083,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10280,7 +10289,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10486,7 +10495,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10692,7 +10701,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11310,7 +11319,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11516,7 +11525,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11928,7 +11937,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12546,7 +12555,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13370,7 +13379,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13451,7 +13460,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ61">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR61">
         <v>0.96</v>
@@ -14606,7 +14615,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14812,7 +14821,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15099,7 +15108,7 @@
         <v>3</v>
       </c>
       <c r="AQ69">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AR69">
         <v>2.02</v>
@@ -15302,7 +15311,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15508,7 +15517,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ71">
         <v>0.33</v>
@@ -15636,7 +15645,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15717,7 +15726,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ72">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR72">
         <v>1.31</v>
@@ -15842,7 +15851,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16460,7 +16469,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16666,7 +16675,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16872,7 +16881,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17284,7 +17293,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17490,7 +17499,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17696,7 +17705,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18314,7 +18323,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18726,7 +18735,7 @@
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18932,7 +18941,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19138,7 +19147,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19344,7 +19353,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19501,6 +19510,830 @@
       </c>
       <c r="BP90">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:68">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7820405</v>
+      </c>
+      <c r="C91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45709.70833333334</v>
+      </c>
+      <c r="F91">
+        <v>7</v>
+      </c>
+      <c r="G91" t="s">
+        <v>86</v>
+      </c>
+      <c r="H91" t="s">
+        <v>91</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91" t="s">
+        <v>100</v>
+      </c>
+      <c r="P91" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q91">
+        <v>4.5</v>
+      </c>
+      <c r="R91">
+        <v>1.83</v>
+      </c>
+      <c r="S91">
+        <v>3.2</v>
+      </c>
+      <c r="T91">
+        <v>1.67</v>
+      </c>
+      <c r="U91">
+        <v>2.1</v>
+      </c>
+      <c r="V91">
+        <v>4.33</v>
+      </c>
+      <c r="W91">
+        <v>1.2</v>
+      </c>
+      <c r="X91">
+        <v>15</v>
+      </c>
+      <c r="Y91">
+        <v>1.03</v>
+      </c>
+      <c r="Z91">
+        <v>3.6</v>
+      </c>
+      <c r="AA91">
+        <v>3</v>
+      </c>
+      <c r="AB91">
+        <v>2.25</v>
+      </c>
+      <c r="AC91">
+        <v>1.13</v>
+      </c>
+      <c r="AD91">
+        <v>5.75</v>
+      </c>
+      <c r="AE91">
+        <v>1.57</v>
+      </c>
+      <c r="AF91">
+        <v>2.25</v>
+      </c>
+      <c r="AG91">
+        <v>2.88</v>
+      </c>
+      <c r="AH91">
+        <v>1.4</v>
+      </c>
+      <c r="AI91">
+        <v>2.25</v>
+      </c>
+      <c r="AJ91">
+        <v>1.57</v>
+      </c>
+      <c r="AK91">
+        <v>1.62</v>
+      </c>
+      <c r="AL91">
+        <v>1.35</v>
+      </c>
+      <c r="AM91">
+        <v>1.25</v>
+      </c>
+      <c r="AN91">
+        <v>1</v>
+      </c>
+      <c r="AO91">
+        <v>1.5</v>
+      </c>
+      <c r="AP91">
+        <v>1</v>
+      </c>
+      <c r="AQ91">
+        <v>1.33</v>
+      </c>
+      <c r="AR91">
+        <v>1.17</v>
+      </c>
+      <c r="AS91">
+        <v>2.16</v>
+      </c>
+      <c r="AT91">
+        <v>3.33</v>
+      </c>
+      <c r="AU91">
+        <v>5</v>
+      </c>
+      <c r="AV91">
+        <v>4</v>
+      </c>
+      <c r="AW91">
+        <v>8</v>
+      </c>
+      <c r="AX91">
+        <v>10</v>
+      </c>
+      <c r="AY91">
+        <v>18</v>
+      </c>
+      <c r="AZ91">
+        <v>17</v>
+      </c>
+      <c r="BA91">
+        <v>3</v>
+      </c>
+      <c r="BB91">
+        <v>7</v>
+      </c>
+      <c r="BC91">
+        <v>10</v>
+      </c>
+      <c r="BD91">
+        <v>2.3</v>
+      </c>
+      <c r="BE91">
+        <v>6.4</v>
+      </c>
+      <c r="BF91">
+        <v>1.77</v>
+      </c>
+      <c r="BG91">
+        <v>1.53</v>
+      </c>
+      <c r="BH91">
+        <v>2.32</v>
+      </c>
+      <c r="BI91">
+        <v>1.88</v>
+      </c>
+      <c r="BJ91">
+        <v>1.81</v>
+      </c>
+      <c r="BK91">
+        <v>2.4</v>
+      </c>
+      <c r="BL91">
+        <v>1.49</v>
+      </c>
+      <c r="BM91">
+        <v>3.15</v>
+      </c>
+      <c r="BN91">
+        <v>1.29</v>
+      </c>
+      <c r="BO91">
+        <v>4.3</v>
+      </c>
+      <c r="BP91">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7820406</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45709.80208333334</v>
+      </c>
+      <c r="F92">
+        <v>7</v>
+      </c>
+      <c r="G92" t="s">
+        <v>80</v>
+      </c>
+      <c r="H92" t="s">
+        <v>84</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>3</v>
+      </c>
+      <c r="M92">
+        <v>2</v>
+      </c>
+      <c r="N92">
+        <v>5</v>
+      </c>
+      <c r="O92" t="s">
+        <v>158</v>
+      </c>
+      <c r="P92" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q92">
+        <v>2.38</v>
+      </c>
+      <c r="R92">
+        <v>2.03</v>
+      </c>
+      <c r="S92">
+        <v>5.65</v>
+      </c>
+      <c r="T92">
+        <v>1.44</v>
+      </c>
+      <c r="U92">
+        <v>2.53</v>
+      </c>
+      <c r="V92">
+        <v>3.26</v>
+      </c>
+      <c r="W92">
+        <v>1.28</v>
+      </c>
+      <c r="X92">
+        <v>7.9</v>
+      </c>
+      <c r="Y92">
+        <v>1.02</v>
+      </c>
+      <c r="Z92">
+        <v>1.73</v>
+      </c>
+      <c r="AA92">
+        <v>3.58</v>
+      </c>
+      <c r="AB92">
+        <v>5.1</v>
+      </c>
+      <c r="AC92">
+        <v>1.01</v>
+      </c>
+      <c r="AD92">
+        <v>8.6</v>
+      </c>
+      <c r="AE92">
+        <v>1.36</v>
+      </c>
+      <c r="AF92">
+        <v>2.78</v>
+      </c>
+      <c r="AG92">
+        <v>2.29</v>
+      </c>
+      <c r="AH92">
+        <v>1.62</v>
+      </c>
+      <c r="AI92">
+        <v>2.11</v>
+      </c>
+      <c r="AJ92">
+        <v>1.65</v>
+      </c>
+      <c r="AK92">
+        <v>1.16</v>
+      </c>
+      <c r="AL92">
+        <v>1.29</v>
+      </c>
+      <c r="AM92">
+        <v>2.11</v>
+      </c>
+      <c r="AN92">
+        <v>3</v>
+      </c>
+      <c r="AO92">
+        <v>0.5</v>
+      </c>
+      <c r="AP92">
+        <v>3</v>
+      </c>
+      <c r="AQ92">
+        <v>0.33</v>
+      </c>
+      <c r="AR92">
+        <v>1.86</v>
+      </c>
+      <c r="AS92">
+        <v>1.58</v>
+      </c>
+      <c r="AT92">
+        <v>3.44</v>
+      </c>
+      <c r="AU92">
+        <v>7</v>
+      </c>
+      <c r="AV92">
+        <v>4</v>
+      </c>
+      <c r="AW92">
+        <v>9</v>
+      </c>
+      <c r="AX92">
+        <v>4</v>
+      </c>
+      <c r="AY92">
+        <v>19</v>
+      </c>
+      <c r="AZ92">
+        <v>8</v>
+      </c>
+      <c r="BA92">
+        <v>5</v>
+      </c>
+      <c r="BB92">
+        <v>3</v>
+      </c>
+      <c r="BC92">
+        <v>8</v>
+      </c>
+      <c r="BD92">
+        <v>1.54</v>
+      </c>
+      <c r="BE92">
+        <v>6.4</v>
+      </c>
+      <c r="BF92">
+        <v>2.8</v>
+      </c>
+      <c r="BG92">
+        <v>1.49</v>
+      </c>
+      <c r="BH92">
+        <v>2.4</v>
+      </c>
+      <c r="BI92">
+        <v>1.82</v>
+      </c>
+      <c r="BJ92">
+        <v>1.86</v>
+      </c>
+      <c r="BK92">
+        <v>2.32</v>
+      </c>
+      <c r="BL92">
+        <v>1.53</v>
+      </c>
+      <c r="BM92">
+        <v>3.05</v>
+      </c>
+      <c r="BN92">
+        <v>1.32</v>
+      </c>
+      <c r="BO92">
+        <v>4.1</v>
+      </c>
+      <c r="BP92">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:68">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7820407</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45709.80208333334</v>
+      </c>
+      <c r="F93">
+        <v>7</v>
+      </c>
+      <c r="G93" t="s">
+        <v>70</v>
+      </c>
+      <c r="H93" t="s">
+        <v>82</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93">
+        <v>1</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>2</v>
+      </c>
+      <c r="O93" t="s">
+        <v>159</v>
+      </c>
+      <c r="P93" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q93">
+        <v>3.75</v>
+      </c>
+      <c r="R93">
+        <v>1.8</v>
+      </c>
+      <c r="S93">
+        <v>3.75</v>
+      </c>
+      <c r="T93">
+        <v>1.67</v>
+      </c>
+      <c r="U93">
+        <v>2.1</v>
+      </c>
+      <c r="V93">
+        <v>4.5</v>
+      </c>
+      <c r="W93">
+        <v>1.18</v>
+      </c>
+      <c r="X93">
+        <v>15</v>
+      </c>
+      <c r="Y93">
+        <v>1.03</v>
+      </c>
+      <c r="Z93">
+        <v>2.8</v>
+      </c>
+      <c r="AA93">
+        <v>2.8</v>
+      </c>
+      <c r="AB93">
+        <v>2.9</v>
+      </c>
+      <c r="AC93">
+        <v>1.15</v>
+      </c>
+      <c r="AD93">
+        <v>5.25</v>
+      </c>
+      <c r="AE93">
+        <v>1.67</v>
+      </c>
+      <c r="AF93">
+        <v>2.15</v>
+      </c>
+      <c r="AG93">
+        <v>3.1</v>
+      </c>
+      <c r="AH93">
+        <v>1.36</v>
+      </c>
+      <c r="AI93">
+        <v>2.38</v>
+      </c>
+      <c r="AJ93">
+        <v>1.53</v>
+      </c>
+      <c r="AK93">
+        <v>1.36</v>
+      </c>
+      <c r="AL93">
+        <v>1.38</v>
+      </c>
+      <c r="AM93">
+        <v>1.45</v>
+      </c>
+      <c r="AN93">
+        <v>0.5</v>
+      </c>
+      <c r="AO93">
+        <v>1</v>
+      </c>
+      <c r="AP93">
+        <v>0.67</v>
+      </c>
+      <c r="AQ93">
+        <v>1</v>
+      </c>
+      <c r="AR93">
+        <v>1.29</v>
+      </c>
+      <c r="AS93">
+        <v>0.96</v>
+      </c>
+      <c r="AT93">
+        <v>2.25</v>
+      </c>
+      <c r="AU93">
+        <v>4</v>
+      </c>
+      <c r="AV93">
+        <v>3</v>
+      </c>
+      <c r="AW93">
+        <v>4</v>
+      </c>
+      <c r="AX93">
+        <v>6</v>
+      </c>
+      <c r="AY93">
+        <v>9</v>
+      </c>
+      <c r="AZ93">
+        <v>10</v>
+      </c>
+      <c r="BA93">
+        <v>3</v>
+      </c>
+      <c r="BB93">
+        <v>1</v>
+      </c>
+      <c r="BC93">
+        <v>4</v>
+      </c>
+      <c r="BD93">
+        <v>1.84</v>
+      </c>
+      <c r="BE93">
+        <v>6.25</v>
+      </c>
+      <c r="BF93">
+        <v>2.18</v>
+      </c>
+      <c r="BG93">
+        <v>1.56</v>
+      </c>
+      <c r="BH93">
+        <v>2.23</v>
+      </c>
+      <c r="BI93">
+        <v>1.95</v>
+      </c>
+      <c r="BJ93">
+        <v>1.85</v>
+      </c>
+      <c r="BK93">
+        <v>2.5</v>
+      </c>
+      <c r="BL93">
+        <v>1.46</v>
+      </c>
+      <c r="BM93">
+        <v>3.3</v>
+      </c>
+      <c r="BN93">
+        <v>1.27</v>
+      </c>
+      <c r="BO93">
+        <v>4.4</v>
+      </c>
+      <c r="BP93">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7820408</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45709.89583333334</v>
+      </c>
+      <c r="F94">
+        <v>7</v>
+      </c>
+      <c r="G94" t="s">
+        <v>74</v>
+      </c>
+      <c r="H94" t="s">
+        <v>90</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94" t="s">
+        <v>100</v>
+      </c>
+      <c r="P94" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q94">
+        <v>3.2</v>
+      </c>
+      <c r="R94">
+        <v>1.91</v>
+      </c>
+      <c r="S94">
+        <v>4</v>
+      </c>
+      <c r="T94">
+        <v>1.57</v>
+      </c>
+      <c r="U94">
+        <v>2.25</v>
+      </c>
+      <c r="V94">
+        <v>3.75</v>
+      </c>
+      <c r="W94">
+        <v>1.25</v>
+      </c>
+      <c r="X94">
+        <v>13</v>
+      </c>
+      <c r="Y94">
+        <v>1.04</v>
+      </c>
+      <c r="Z94">
+        <v>2.35</v>
+      </c>
+      <c r="AA94">
+        <v>3</v>
+      </c>
+      <c r="AB94">
+        <v>3.4</v>
+      </c>
+      <c r="AC94">
+        <v>1.11</v>
+      </c>
+      <c r="AD94">
+        <v>6.25</v>
+      </c>
+      <c r="AE94">
+        <v>1.5</v>
+      </c>
+      <c r="AF94">
+        <v>2.5</v>
+      </c>
+      <c r="AG94">
+        <v>2.6</v>
+      </c>
+      <c r="AH94">
+        <v>1.48</v>
+      </c>
+      <c r="AI94">
+        <v>2.1</v>
+      </c>
+      <c r="AJ94">
+        <v>1.67</v>
+      </c>
+      <c r="AK94">
+        <v>1.3</v>
+      </c>
+      <c r="AL94">
+        <v>1.33</v>
+      </c>
+      <c r="AM94">
+        <v>1.6</v>
+      </c>
+      <c r="AN94">
+        <v>1.33</v>
+      </c>
+      <c r="AO94">
+        <v>0</v>
+      </c>
+      <c r="AP94">
+        <v>1.25</v>
+      </c>
+      <c r="AQ94">
+        <v>0.25</v>
+      </c>
+      <c r="AR94">
+        <v>1.94</v>
+      </c>
+      <c r="AS94">
+        <v>1.04</v>
+      </c>
+      <c r="AT94">
+        <v>2.98</v>
+      </c>
+      <c r="AU94">
+        <v>7</v>
+      </c>
+      <c r="AV94">
+        <v>2</v>
+      </c>
+      <c r="AW94">
+        <v>7</v>
+      </c>
+      <c r="AX94">
+        <v>4</v>
+      </c>
+      <c r="AY94">
+        <v>16</v>
+      </c>
+      <c r="AZ94">
+        <v>7</v>
+      </c>
+      <c r="BA94">
+        <v>7</v>
+      </c>
+      <c r="BB94">
+        <v>0</v>
+      </c>
+      <c r="BC94">
+        <v>7</v>
+      </c>
+      <c r="BD94">
+        <v>2.02</v>
+      </c>
+      <c r="BE94">
+        <v>6.4</v>
+      </c>
+      <c r="BF94">
+        <v>1.98</v>
+      </c>
+      <c r="BG94">
+        <v>1.44</v>
+      </c>
+      <c r="BH94">
+        <v>2.55</v>
+      </c>
+      <c r="BI94">
+        <v>1.74</v>
+      </c>
+      <c r="BJ94">
+        <v>1.95</v>
+      </c>
+      <c r="BK94">
+        <v>2.18</v>
+      </c>
+      <c r="BL94">
+        <v>1.58</v>
+      </c>
+      <c r="BM94">
+        <v>2.85</v>
+      </c>
+      <c r="BN94">
+        <v>1.36</v>
+      </c>
+      <c r="BO94">
+        <v>3.8</v>
+      </c>
+      <c r="BP94">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="201">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -496,6 +496,15 @@
     <t>['67']</t>
   </si>
   <si>
+    <t>['53', '71']</t>
+  </si>
+  <si>
+    <t>['49', '84']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -559,9 +568,6 @@
     <t>['58', '81']</t>
   </si>
   <si>
-    <t>['6']</t>
-  </si>
-  <si>
     <t>['49']</t>
   </si>
   <si>
@@ -608,6 +614,9 @@
   </si>
   <si>
     <t>['44', '51']</t>
+  </si>
+  <si>
+    <t>['56', '69']</t>
   </si>
 </sst>
 </file>
@@ -969,7 +978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP94"/>
+  <dimension ref="A1:BP98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1225,7 +1234,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1637,7 +1646,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1843,7 +1852,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -2049,7 +2058,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2255,7 +2264,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2873,7 +2882,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -2951,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3285,7 +3294,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3778,7 +3787,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3981,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ15">
         <v>2.33</v>
@@ -4727,7 +4736,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5345,7 +5354,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5551,7 +5560,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5757,7 +5766,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6169,7 +6178,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6456,7 +6465,7 @@
         <v>3</v>
       </c>
       <c r="AQ27">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -6581,7 +6590,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7689,7 +7698,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ33">
         <v>2</v>
@@ -8104,7 +8113,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR35">
         <v>1.24</v>
@@ -8229,7 +8238,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8307,7 +8316,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ36">
         <v>0.67</v>
@@ -9053,7 +9062,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9877,7 +9886,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10083,7 +10092,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10289,7 +10298,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10495,7 +10504,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10701,7 +10710,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11319,7 +11328,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11525,7 +11534,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11937,7 +11946,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12555,7 +12564,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12842,7 +12851,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR58">
         <v>0.73</v>
@@ -13379,7 +13388,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13663,7 +13672,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ62">
         <v>2</v>
@@ -14615,7 +14624,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14821,7 +14830,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15314,7 +15323,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR70">
         <v>1.21</v>
@@ -15645,7 +15654,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15723,7 +15732,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ72">
         <v>1.33</v>
@@ -15851,7 +15860,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16344,7 +16353,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ75">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR75">
         <v>1.66</v>
@@ -16469,7 +16478,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16675,7 +16684,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16881,7 +16890,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17293,7 +17302,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17499,7 +17508,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17705,7 +17714,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18323,7 +18332,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18735,7 +18744,7 @@
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18941,7 +18950,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19147,7 +19156,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19353,7 +19362,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19765,7 +19774,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20334,6 +20343,830 @@
       </c>
       <c r="BP94">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7820409</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45710.75</v>
+      </c>
+      <c r="F95">
+        <v>7</v>
+      </c>
+      <c r="G95" t="s">
+        <v>76</v>
+      </c>
+      <c r="H95" t="s">
+        <v>81</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>2</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>2</v>
+      </c>
+      <c r="O95" t="s">
+        <v>160</v>
+      </c>
+      <c r="P95" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q95">
+        <v>2.4</v>
+      </c>
+      <c r="R95">
+        <v>2</v>
+      </c>
+      <c r="S95">
+        <v>6</v>
+      </c>
+      <c r="T95">
+        <v>1.53</v>
+      </c>
+      <c r="U95">
+        <v>2.38</v>
+      </c>
+      <c r="V95">
+        <v>3.75</v>
+      </c>
+      <c r="W95">
+        <v>1.25</v>
+      </c>
+      <c r="X95">
+        <v>11</v>
+      </c>
+      <c r="Y95">
+        <v>1.05</v>
+      </c>
+      <c r="Z95">
+        <v>1.7</v>
+      </c>
+      <c r="AA95">
+        <v>3.4</v>
+      </c>
+      <c r="AB95">
+        <v>5.25</v>
+      </c>
+      <c r="AC95">
+        <v>1.09</v>
+      </c>
+      <c r="AD95">
+        <v>7</v>
+      </c>
+      <c r="AE95">
+        <v>1.48</v>
+      </c>
+      <c r="AF95">
+        <v>2.6</v>
+      </c>
+      <c r="AG95">
+        <v>2.4</v>
+      </c>
+      <c r="AH95">
+        <v>1.53</v>
+      </c>
+      <c r="AI95">
+        <v>2.25</v>
+      </c>
+      <c r="AJ95">
+        <v>1.57</v>
+      </c>
+      <c r="AK95">
+        <v>1.15</v>
+      </c>
+      <c r="AL95">
+        <v>1.25</v>
+      </c>
+      <c r="AM95">
+        <v>2.05</v>
+      </c>
+      <c r="AN95">
+        <v>3</v>
+      </c>
+      <c r="AO95">
+        <v>0.33</v>
+      </c>
+      <c r="AP95">
+        <v>3</v>
+      </c>
+      <c r="AQ95">
+        <v>0.25</v>
+      </c>
+      <c r="AR95">
+        <v>1.94</v>
+      </c>
+      <c r="AS95">
+        <v>1.19</v>
+      </c>
+      <c r="AT95">
+        <v>3.13</v>
+      </c>
+      <c r="AU95">
+        <v>4</v>
+      </c>
+      <c r="AV95">
+        <v>2</v>
+      </c>
+      <c r="AW95">
+        <v>12</v>
+      </c>
+      <c r="AX95">
+        <v>1</v>
+      </c>
+      <c r="AY95">
+        <v>18</v>
+      </c>
+      <c r="AZ95">
+        <v>3</v>
+      </c>
+      <c r="BA95">
+        <v>1</v>
+      </c>
+      <c r="BB95">
+        <v>2</v>
+      </c>
+      <c r="BC95">
+        <v>3</v>
+      </c>
+      <c r="BD95">
+        <v>1.43</v>
+      </c>
+      <c r="BE95">
+        <v>6.75</v>
+      </c>
+      <c r="BF95">
+        <v>3.15</v>
+      </c>
+      <c r="BG95">
+        <v>1.39</v>
+      </c>
+      <c r="BH95">
+        <v>2.77</v>
+      </c>
+      <c r="BI95">
+        <v>1.68</v>
+      </c>
+      <c r="BJ95">
+        <v>2.12</v>
+      </c>
+      <c r="BK95">
+        <v>2.11</v>
+      </c>
+      <c r="BL95">
+        <v>1.68</v>
+      </c>
+      <c r="BM95">
+        <v>2.7</v>
+      </c>
+      <c r="BN95">
+        <v>1.41</v>
+      </c>
+      <c r="BO95">
+        <v>3.65</v>
+      </c>
+      <c r="BP95">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7820411</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45710.8125</v>
+      </c>
+      <c r="F96">
+        <v>7</v>
+      </c>
+      <c r="G96" t="s">
+        <v>83</v>
+      </c>
+      <c r="H96" t="s">
+        <v>96</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>2</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>3</v>
+      </c>
+      <c r="O96" t="s">
+        <v>161</v>
+      </c>
+      <c r="P96" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q96">
+        <v>2.1</v>
+      </c>
+      <c r="R96">
+        <v>2.1</v>
+      </c>
+      <c r="S96">
+        <v>7.5</v>
+      </c>
+      <c r="T96">
+        <v>1.5</v>
+      </c>
+      <c r="U96">
+        <v>2.5</v>
+      </c>
+      <c r="V96">
+        <v>3.4</v>
+      </c>
+      <c r="W96">
+        <v>1.3</v>
+      </c>
+      <c r="X96">
+        <v>10</v>
+      </c>
+      <c r="Y96">
+        <v>1.06</v>
+      </c>
+      <c r="Z96">
+        <v>1.48</v>
+      </c>
+      <c r="AA96">
+        <v>3.7</v>
+      </c>
+      <c r="AB96">
+        <v>7</v>
+      </c>
+      <c r="AC96">
+        <v>1.08</v>
+      </c>
+      <c r="AD96">
+        <v>8.4</v>
+      </c>
+      <c r="AE96">
+        <v>1.41</v>
+      </c>
+      <c r="AF96">
+        <v>2.85</v>
+      </c>
+      <c r="AG96">
+        <v>2.2</v>
+      </c>
+      <c r="AH96">
+        <v>1.65</v>
+      </c>
+      <c r="AI96">
+        <v>2.25</v>
+      </c>
+      <c r="AJ96">
+        <v>1.57</v>
+      </c>
+      <c r="AK96">
+        <v>1.1</v>
+      </c>
+      <c r="AL96">
+        <v>1.23</v>
+      </c>
+      <c r="AM96">
+        <v>2.5</v>
+      </c>
+      <c r="AN96">
+        <v>2.33</v>
+      </c>
+      <c r="AO96">
+        <v>0</v>
+      </c>
+      <c r="AP96">
+        <v>2.5</v>
+      </c>
+      <c r="AQ96">
+        <v>0</v>
+      </c>
+      <c r="AR96">
+        <v>1.26</v>
+      </c>
+      <c r="AS96">
+        <v>1.35</v>
+      </c>
+      <c r="AT96">
+        <v>2.61</v>
+      </c>
+      <c r="AU96">
+        <v>7</v>
+      </c>
+      <c r="AV96">
+        <v>3</v>
+      </c>
+      <c r="AW96">
+        <v>5</v>
+      </c>
+      <c r="AX96">
+        <v>4</v>
+      </c>
+      <c r="AY96">
+        <v>14</v>
+      </c>
+      <c r="AZ96">
+        <v>8</v>
+      </c>
+      <c r="BA96">
+        <v>4</v>
+      </c>
+      <c r="BB96">
+        <v>5</v>
+      </c>
+      <c r="BC96">
+        <v>9</v>
+      </c>
+      <c r="BD96">
+        <v>1.32</v>
+      </c>
+      <c r="BE96">
+        <v>7.5</v>
+      </c>
+      <c r="BF96">
+        <v>3.65</v>
+      </c>
+      <c r="BG96">
+        <v>1.39</v>
+      </c>
+      <c r="BH96">
+        <v>2.77</v>
+      </c>
+      <c r="BI96">
+        <v>1.68</v>
+      </c>
+      <c r="BJ96">
+        <v>2.12</v>
+      </c>
+      <c r="BK96">
+        <v>2.11</v>
+      </c>
+      <c r="BL96">
+        <v>1.68</v>
+      </c>
+      <c r="BM96">
+        <v>2.7</v>
+      </c>
+      <c r="BN96">
+        <v>1.41</v>
+      </c>
+      <c r="BO96">
+        <v>3.65</v>
+      </c>
+      <c r="BP96">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7820412</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45710.89583333334</v>
+      </c>
+      <c r="F97">
+        <v>7</v>
+      </c>
+      <c r="G97" t="s">
+        <v>78</v>
+      </c>
+      <c r="H97" t="s">
+        <v>95</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>2</v>
+      </c>
+      <c r="N97">
+        <v>2</v>
+      </c>
+      <c r="O97" t="s">
+        <v>100</v>
+      </c>
+      <c r="P97" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q97">
+        <v>6.5</v>
+      </c>
+      <c r="R97">
+        <v>2.05</v>
+      </c>
+      <c r="S97">
+        <v>2.25</v>
+      </c>
+      <c r="T97">
+        <v>1.5</v>
+      </c>
+      <c r="U97">
+        <v>2.5</v>
+      </c>
+      <c r="V97">
+        <v>3.5</v>
+      </c>
+      <c r="W97">
+        <v>1.29</v>
+      </c>
+      <c r="X97">
+        <v>10</v>
+      </c>
+      <c r="Y97">
+        <v>1.06</v>
+      </c>
+      <c r="Z97">
+        <v>5.25</v>
+      </c>
+      <c r="AA97">
+        <v>3.6</v>
+      </c>
+      <c r="AB97">
+        <v>1.57</v>
+      </c>
+      <c r="AC97">
+        <v>1.09</v>
+      </c>
+      <c r="AD97">
+        <v>7.8</v>
+      </c>
+      <c r="AE97">
+        <v>1.45</v>
+      </c>
+      <c r="AF97">
+        <v>2.65</v>
+      </c>
+      <c r="AG97">
+        <v>2.3</v>
+      </c>
+      <c r="AH97">
+        <v>1.6</v>
+      </c>
+      <c r="AI97">
+        <v>2.25</v>
+      </c>
+      <c r="AJ97">
+        <v>1.57</v>
+      </c>
+      <c r="AK97">
+        <v>2.25</v>
+      </c>
+      <c r="AL97">
+        <v>1.27</v>
+      </c>
+      <c r="AM97">
+        <v>1.13</v>
+      </c>
+      <c r="AN97">
+        <v>0.33</v>
+      </c>
+      <c r="AO97">
+        <v>1</v>
+      </c>
+      <c r="AP97">
+        <v>0.25</v>
+      </c>
+      <c r="AQ97">
+        <v>1.5</v>
+      </c>
+      <c r="AR97">
+        <v>1.54</v>
+      </c>
+      <c r="AS97">
+        <v>1.67</v>
+      </c>
+      <c r="AT97">
+        <v>3.21</v>
+      </c>
+      <c r="AU97">
+        <v>3</v>
+      </c>
+      <c r="AV97">
+        <v>5</v>
+      </c>
+      <c r="AW97">
+        <v>6</v>
+      </c>
+      <c r="AX97">
+        <v>6</v>
+      </c>
+      <c r="AY97">
+        <v>10</v>
+      </c>
+      <c r="AZ97">
+        <v>13</v>
+      </c>
+      <c r="BA97">
+        <v>6</v>
+      </c>
+      <c r="BB97">
+        <v>6</v>
+      </c>
+      <c r="BC97">
+        <v>12</v>
+      </c>
+      <c r="BD97">
+        <v>3.05</v>
+      </c>
+      <c r="BE97">
+        <v>6.75</v>
+      </c>
+      <c r="BF97">
+        <v>1.47</v>
+      </c>
+      <c r="BG97">
+        <v>1.43</v>
+      </c>
+      <c r="BH97">
+        <v>2.63</v>
+      </c>
+      <c r="BI97">
+        <v>1.74</v>
+      </c>
+      <c r="BJ97">
+        <v>2.02</v>
+      </c>
+      <c r="BK97">
+        <v>2.22</v>
+      </c>
+      <c r="BL97">
+        <v>1.62</v>
+      </c>
+      <c r="BM97">
+        <v>2.85</v>
+      </c>
+      <c r="BN97">
+        <v>1.37</v>
+      </c>
+      <c r="BO97">
+        <v>3.9</v>
+      </c>
+      <c r="BP97">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7820410</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45710.90625</v>
+      </c>
+      <c r="F98">
+        <v>7</v>
+      </c>
+      <c r="G98" t="s">
+        <v>87</v>
+      </c>
+      <c r="H98" t="s">
+        <v>88</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98" t="s">
+        <v>162</v>
+      </c>
+      <c r="P98" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q98">
+        <v>2.38</v>
+      </c>
+      <c r="R98">
+        <v>2</v>
+      </c>
+      <c r="S98">
+        <v>6.5</v>
+      </c>
+      <c r="T98">
+        <v>1.53</v>
+      </c>
+      <c r="U98">
+        <v>2.38</v>
+      </c>
+      <c r="V98">
+        <v>3.5</v>
+      </c>
+      <c r="W98">
+        <v>1.29</v>
+      </c>
+      <c r="X98">
+        <v>11</v>
+      </c>
+      <c r="Y98">
+        <v>1.05</v>
+      </c>
+      <c r="Z98">
+        <v>1.67</v>
+      </c>
+      <c r="AA98">
+        <v>3.5</v>
+      </c>
+      <c r="AB98">
+        <v>6</v>
+      </c>
+      <c r="AC98">
+        <v>1.09</v>
+      </c>
+      <c r="AD98">
+        <v>7</v>
+      </c>
+      <c r="AE98">
+        <v>1.48</v>
+      </c>
+      <c r="AF98">
+        <v>2.65</v>
+      </c>
+      <c r="AG98">
+        <v>2.4</v>
+      </c>
+      <c r="AH98">
+        <v>1.53</v>
+      </c>
+      <c r="AI98">
+        <v>2.25</v>
+      </c>
+      <c r="AJ98">
+        <v>1.57</v>
+      </c>
+      <c r="AK98">
+        <v>1.15</v>
+      </c>
+      <c r="AL98">
+        <v>1.25</v>
+      </c>
+      <c r="AM98">
+        <v>2.05</v>
+      </c>
+      <c r="AN98">
+        <v>3</v>
+      </c>
+      <c r="AO98">
+        <v>0</v>
+      </c>
+      <c r="AP98">
+        <v>3</v>
+      </c>
+      <c r="AQ98">
+        <v>0</v>
+      </c>
+      <c r="AR98">
+        <v>1.32</v>
+      </c>
+      <c r="AS98">
+        <v>1.23</v>
+      </c>
+      <c r="AT98">
+        <v>2.55</v>
+      </c>
+      <c r="AU98">
+        <v>3</v>
+      </c>
+      <c r="AV98">
+        <v>3</v>
+      </c>
+      <c r="AW98">
+        <v>4</v>
+      </c>
+      <c r="AX98">
+        <v>4</v>
+      </c>
+      <c r="AY98">
+        <v>8</v>
+      </c>
+      <c r="AZ98">
+        <v>10</v>
+      </c>
+      <c r="BA98">
+        <v>3</v>
+      </c>
+      <c r="BB98">
+        <v>3</v>
+      </c>
+      <c r="BC98">
+        <v>6</v>
+      </c>
+      <c r="BD98">
+        <v>1.34</v>
+      </c>
+      <c r="BE98">
+        <v>7</v>
+      </c>
+      <c r="BF98">
+        <v>3.65</v>
+      </c>
+      <c r="BG98">
+        <v>1.36</v>
+      </c>
+      <c r="BH98">
+        <v>2.8</v>
+      </c>
+      <c r="BI98">
+        <v>1.63</v>
+      </c>
+      <c r="BJ98">
+        <v>2.12</v>
+      </c>
+      <c r="BK98">
+        <v>1.98</v>
+      </c>
+      <c r="BL98">
+        <v>1.72</v>
+      </c>
+      <c r="BM98">
+        <v>2.55</v>
+      </c>
+      <c r="BN98">
+        <v>1.44</v>
+      </c>
+      <c r="BO98">
+        <v>3.3</v>
+      </c>
+      <c r="BP98">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="203">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -505,6 +505,12 @@
     <t>['6']</t>
   </si>
   <si>
+    <t>['11', '90']</t>
+  </si>
+  <si>
+    <t>['38', '57']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -978,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP98"/>
+  <dimension ref="A1:BP101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1234,7 +1240,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1646,7 +1652,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1852,7 +1858,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -2058,7 +2064,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2264,7 +2270,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2754,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9">
         <v>0.67</v>
@@ -2882,7 +2888,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3294,7 +3300,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3581,7 +3587,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4736,7 +4742,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5354,7 +5360,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5560,7 +5566,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5766,7 +5772,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -5847,7 +5853,7 @@
         <v>2</v>
       </c>
       <c r="AQ24">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6050,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6178,7 +6184,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6590,7 +6596,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6671,7 +6677,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ28">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -8238,7 +8244,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8937,7 +8943,7 @@
         <v>3</v>
       </c>
       <c r="AQ39">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.95</v>
@@ -9062,7 +9068,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9886,7 +9892,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -9964,7 +9970,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ44">
         <v>2</v>
@@ -10092,7 +10098,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10170,7 +10176,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ45">
         <v>2</v>
@@ -10298,7 +10304,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10504,7 +10510,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10710,7 +10716,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11200,7 +11206,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11328,7 +11334,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11821,7 +11827,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ53">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR53">
         <v>1.58</v>
@@ -11946,7 +11952,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12564,7 +12570,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12645,7 +12651,7 @@
         <v>1</v>
       </c>
       <c r="AQ57">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR57">
         <v>0.9</v>
@@ -13388,7 +13394,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14290,7 +14296,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ65">
         <v>0</v>
@@ -14624,7 +14630,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14705,7 +14711,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ67">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR67">
         <v>1.78</v>
@@ -14830,7 +14836,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15529,7 +15535,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ71">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>1.67</v>
@@ -15654,7 +15660,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15860,7 +15866,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16144,7 +16150,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ74">
         <v>0</v>
@@ -16478,7 +16484,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16684,7 +16690,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16890,7 +16896,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17302,7 +17308,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17508,7 +17514,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17714,7 +17720,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18204,7 +18210,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ84">
         <v>0</v>
@@ -18332,7 +18338,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18744,7 +18750,7 @@
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18950,7 +18956,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19156,7 +19162,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19362,7 +19368,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19443,7 +19449,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR90">
         <v>1.46</v>
@@ -19774,7 +19780,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20598,7 +20604,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20804,7 +20810,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21167,6 +21173,624 @@
       </c>
       <c r="BP98">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7820413</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45711.75</v>
+      </c>
+      <c r="F99">
+        <v>7</v>
+      </c>
+      <c r="G99" t="s">
+        <v>93</v>
+      </c>
+      <c r="H99" t="s">
+        <v>79</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99">
+        <v>2</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>2</v>
+      </c>
+      <c r="O99" t="s">
+        <v>163</v>
+      </c>
+      <c r="P99" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q99">
+        <v>3.25</v>
+      </c>
+      <c r="R99">
+        <v>1.8</v>
+      </c>
+      <c r="S99">
+        <v>4.5</v>
+      </c>
+      <c r="T99">
+        <v>1.67</v>
+      </c>
+      <c r="U99">
+        <v>2.1</v>
+      </c>
+      <c r="V99">
+        <v>4.5</v>
+      </c>
+      <c r="W99">
+        <v>1.18</v>
+      </c>
+      <c r="X99">
+        <v>15</v>
+      </c>
+      <c r="Y99">
+        <v>1.03</v>
+      </c>
+      <c r="Z99">
+        <v>2.25</v>
+      </c>
+      <c r="AA99">
+        <v>2.9</v>
+      </c>
+      <c r="AB99">
+        <v>3.4</v>
+      </c>
+      <c r="AC99">
+        <v>1.16</v>
+      </c>
+      <c r="AD99">
+        <v>5.2</v>
+      </c>
+      <c r="AE99">
+        <v>1.69</v>
+      </c>
+      <c r="AF99">
+        <v>2.09</v>
+      </c>
+      <c r="AG99">
+        <v>3.4</v>
+      </c>
+      <c r="AH99">
+        <v>1.33</v>
+      </c>
+      <c r="AI99">
+        <v>2.5</v>
+      </c>
+      <c r="AJ99">
+        <v>1.5</v>
+      </c>
+      <c r="AK99">
+        <v>1.29</v>
+      </c>
+      <c r="AL99">
+        <v>1.41</v>
+      </c>
+      <c r="AM99">
+        <v>1.55</v>
+      </c>
+      <c r="AN99">
+        <v>2.33</v>
+      </c>
+      <c r="AO99">
+        <v>2.33</v>
+      </c>
+      <c r="AP99">
+        <v>2.5</v>
+      </c>
+      <c r="AQ99">
+        <v>1.75</v>
+      </c>
+      <c r="AR99">
+        <v>1.77</v>
+      </c>
+      <c r="AS99">
+        <v>0.79</v>
+      </c>
+      <c r="AT99">
+        <v>2.56</v>
+      </c>
+      <c r="AU99">
+        <v>5</v>
+      </c>
+      <c r="AV99">
+        <v>3</v>
+      </c>
+      <c r="AW99">
+        <v>7</v>
+      </c>
+      <c r="AX99">
+        <v>7</v>
+      </c>
+      <c r="AY99">
+        <v>16</v>
+      </c>
+      <c r="AZ99">
+        <v>12</v>
+      </c>
+      <c r="BA99">
+        <v>2</v>
+      </c>
+      <c r="BB99">
+        <v>3</v>
+      </c>
+      <c r="BC99">
+        <v>5</v>
+      </c>
+      <c r="BD99">
+        <v>1.77</v>
+      </c>
+      <c r="BE99">
+        <v>6.4</v>
+      </c>
+      <c r="BF99">
+        <v>2.25</v>
+      </c>
+      <c r="BG99">
+        <v>1.55</v>
+      </c>
+      <c r="BH99">
+        <v>2.37</v>
+      </c>
+      <c r="BI99">
+        <v>1.92</v>
+      </c>
+      <c r="BJ99">
+        <v>1.82</v>
+      </c>
+      <c r="BK99">
+        <v>2.46</v>
+      </c>
+      <c r="BL99">
+        <v>1.48</v>
+      </c>
+      <c r="BM99">
+        <v>3.32</v>
+      </c>
+      <c r="BN99">
+        <v>1.26</v>
+      </c>
+      <c r="BO99">
+        <v>4.6</v>
+      </c>
+      <c r="BP99">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7820415</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45711.875</v>
+      </c>
+      <c r="F100">
+        <v>7</v>
+      </c>
+      <c r="G100" t="s">
+        <v>99</v>
+      </c>
+      <c r="H100" t="s">
+        <v>92</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100" t="s">
+        <v>100</v>
+      </c>
+      <c r="P100" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q100">
+        <v>2.88</v>
+      </c>
+      <c r="R100">
+        <v>1.95</v>
+      </c>
+      <c r="S100">
+        <v>4.5</v>
+      </c>
+      <c r="T100">
+        <v>1.53</v>
+      </c>
+      <c r="U100">
+        <v>2.38</v>
+      </c>
+      <c r="V100">
+        <v>3.5</v>
+      </c>
+      <c r="W100">
+        <v>1.29</v>
+      </c>
+      <c r="X100">
+        <v>11</v>
+      </c>
+      <c r="Y100">
+        <v>1.05</v>
+      </c>
+      <c r="Z100">
+        <v>2.05</v>
+      </c>
+      <c r="AA100">
+        <v>3.25</v>
+      </c>
+      <c r="AB100">
+        <v>3.8</v>
+      </c>
+      <c r="AC100">
+        <v>1.1</v>
+      </c>
+      <c r="AD100">
+        <v>7.4</v>
+      </c>
+      <c r="AE100">
+        <v>1.45</v>
+      </c>
+      <c r="AF100">
+        <v>2.65</v>
+      </c>
+      <c r="AG100">
+        <v>2.35</v>
+      </c>
+      <c r="AH100">
+        <v>1.57</v>
+      </c>
+      <c r="AI100">
+        <v>2.05</v>
+      </c>
+      <c r="AJ100">
+        <v>1.7</v>
+      </c>
+      <c r="AK100">
+        <v>1.25</v>
+      </c>
+      <c r="AL100">
+        <v>1.33</v>
+      </c>
+      <c r="AM100">
+        <v>1.75</v>
+      </c>
+      <c r="AN100">
+        <v>1.5</v>
+      </c>
+      <c r="AO100">
+        <v>0.33</v>
+      </c>
+      <c r="AP100">
+        <v>1</v>
+      </c>
+      <c r="AQ100">
+        <v>1</v>
+      </c>
+      <c r="AR100">
+        <v>1.82</v>
+      </c>
+      <c r="AS100">
+        <v>1.13</v>
+      </c>
+      <c r="AT100">
+        <v>2.95</v>
+      </c>
+      <c r="AU100">
+        <v>6</v>
+      </c>
+      <c r="AV100">
+        <v>4</v>
+      </c>
+      <c r="AW100">
+        <v>7</v>
+      </c>
+      <c r="AX100">
+        <v>4</v>
+      </c>
+      <c r="AY100">
+        <v>16</v>
+      </c>
+      <c r="AZ100">
+        <v>10</v>
+      </c>
+      <c r="BA100">
+        <v>5</v>
+      </c>
+      <c r="BB100">
+        <v>4</v>
+      </c>
+      <c r="BC100">
+        <v>9</v>
+      </c>
+      <c r="BD100">
+        <v>1.56</v>
+      </c>
+      <c r="BE100">
+        <v>7</v>
+      </c>
+      <c r="BF100">
+        <v>2.65</v>
+      </c>
+      <c r="BG100">
+        <v>1.28</v>
+      </c>
+      <c r="BH100">
+        <v>3.25</v>
+      </c>
+      <c r="BI100">
+        <v>1.52</v>
+      </c>
+      <c r="BJ100">
+        <v>2.37</v>
+      </c>
+      <c r="BK100">
+        <v>1.87</v>
+      </c>
+      <c r="BL100">
+        <v>1.87</v>
+      </c>
+      <c r="BM100">
+        <v>2.38</v>
+      </c>
+      <c r="BN100">
+        <v>1.54</v>
+      </c>
+      <c r="BO100">
+        <v>3.12</v>
+      </c>
+      <c r="BP100">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7820414</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45711.875</v>
+      </c>
+      <c r="F101">
+        <v>7</v>
+      </c>
+      <c r="G101" t="s">
+        <v>77</v>
+      </c>
+      <c r="H101" t="s">
+        <v>73</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>2</v>
+      </c>
+      <c r="O101" t="s">
+        <v>164</v>
+      </c>
+      <c r="P101" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q101">
+        <v>3.1</v>
+      </c>
+      <c r="R101">
+        <v>2</v>
+      </c>
+      <c r="S101">
+        <v>4</v>
+      </c>
+      <c r="T101">
+        <v>1.53</v>
+      </c>
+      <c r="U101">
+        <v>2.38</v>
+      </c>
+      <c r="V101">
+        <v>3.5</v>
+      </c>
+      <c r="W101">
+        <v>1.29</v>
+      </c>
+      <c r="X101">
+        <v>11</v>
+      </c>
+      <c r="Y101">
+        <v>1.05</v>
+      </c>
+      <c r="Z101">
+        <v>2.38</v>
+      </c>
+      <c r="AA101">
+        <v>3</v>
+      </c>
+      <c r="AB101">
+        <v>3.3</v>
+      </c>
+      <c r="AC101">
+        <v>1.1</v>
+      </c>
+      <c r="AD101">
+        <v>7.4</v>
+      </c>
+      <c r="AE101">
+        <v>1.45</v>
+      </c>
+      <c r="AF101">
+        <v>2.65</v>
+      </c>
+      <c r="AG101">
+        <v>2.35</v>
+      </c>
+      <c r="AH101">
+        <v>1.57</v>
+      </c>
+      <c r="AI101">
+        <v>1.95</v>
+      </c>
+      <c r="AJ101">
+        <v>1.8</v>
+      </c>
+      <c r="AK101">
+        <v>1.34</v>
+      </c>
+      <c r="AL101">
+        <v>1.34</v>
+      </c>
+      <c r="AM101">
+        <v>1.6</v>
+      </c>
+      <c r="AN101">
+        <v>1.33</v>
+      </c>
+      <c r="AO101">
+        <v>2.33</v>
+      </c>
+      <c r="AP101">
+        <v>1.75</v>
+      </c>
+      <c r="AQ101">
+        <v>1.75</v>
+      </c>
+      <c r="AR101">
+        <v>1.73</v>
+      </c>
+      <c r="AS101">
+        <v>1.58</v>
+      </c>
+      <c r="AT101">
+        <v>3.31</v>
+      </c>
+      <c r="AU101">
+        <v>7</v>
+      </c>
+      <c r="AV101">
+        <v>2</v>
+      </c>
+      <c r="AW101">
+        <v>5</v>
+      </c>
+      <c r="AX101">
+        <v>11</v>
+      </c>
+      <c r="AY101">
+        <v>12</v>
+      </c>
+      <c r="AZ101">
+        <v>17</v>
+      </c>
+      <c r="BA101">
+        <v>3</v>
+      </c>
+      <c r="BB101">
+        <v>10</v>
+      </c>
+      <c r="BC101">
+        <v>13</v>
+      </c>
+      <c r="BD101">
+        <v>1.57</v>
+      </c>
+      <c r="BE101">
+        <v>6.75</v>
+      </c>
+      <c r="BF101">
+        <v>2.65</v>
+      </c>
+      <c r="BG101">
+        <v>1.28</v>
+      </c>
+      <c r="BH101">
+        <v>3.25</v>
+      </c>
+      <c r="BI101">
+        <v>1.52</v>
+      </c>
+      <c r="BJ101">
+        <v>2.37</v>
+      </c>
+      <c r="BK101">
+        <v>1.87</v>
+      </c>
+      <c r="BL101">
+        <v>1.87</v>
+      </c>
+      <c r="BM101">
+        <v>2.38</v>
+      </c>
+      <c r="BN101">
+        <v>1.54</v>
+      </c>
+      <c r="BO101">
+        <v>3.12</v>
+      </c>
+      <c r="BP101">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="204">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -511,13 +511,16 @@
     <t>['38', '57']</t>
   </si>
   <si>
+    <t>['2', '90+1']</t>
+  </si>
+  <si>
+    <t>['59']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
     <t>['43']</t>
-  </si>
-  <si>
-    <t>['59']</t>
   </si>
   <si>
     <t>['77', '86']</t>
@@ -984,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP101"/>
+  <dimension ref="A1:BP104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1240,7 +1243,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1318,10 +1321,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1524,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AQ3">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1652,7 +1655,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1730,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AQ4">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1858,7 +1861,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q5">
         <v>2.63</v>
@@ -1936,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -2064,7 +2067,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2142,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AQ6">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2270,7 +2273,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2348,10 +2351,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2554,10 +2557,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2760,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="AQ9">
-        <v>0.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2888,7 +2891,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -2966,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3172,10 +3175,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3300,7 +3303,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3378,10 +3381,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3584,10 +3587,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3790,10 +3793,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AQ14">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3996,10 +3999,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4202,10 +4205,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4402,25 +4405,25 @@
         <v>1.53</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU17">
         <v>6</v>
@@ -4608,25 +4611,25 @@
         <v>1.68</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO18">
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AQ18">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AU18">
         <v>2</v>
@@ -4742,7 +4745,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -4814,25 +4817,25 @@
         <v>1.6</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO19">
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU19">
         <v>3</v>
@@ -5026,19 +5029,19 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU20">
         <v>6</v>
@@ -5226,25 +5229,25 @@
         <v>1.9</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO21">
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AU21">
         <v>5</v>
@@ -5360,7 +5363,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5435,22 +5438,22 @@
         <v>0</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP22">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AU22">
         <v>6</v>
@@ -5566,7 +5569,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5641,22 +5644,22 @@
         <v>0</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>2.29</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AU23">
         <v>9</v>
@@ -5772,7 +5775,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -5847,22 +5850,22 @@
         <v>0</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AQ24">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AU24">
         <v>2</v>
@@ -6050,25 +6053,25 @@
         <v>1.34</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP25">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AU25">
         <v>8</v>
@@ -6184,7 +6187,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6259,22 +6262,22 @@
         <v>0</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6462,25 +6465,25 @@
         <v>2.7</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP27">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AQ27">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AU27">
         <v>6</v>
@@ -6596,7 +6599,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6674,19 +6677,19 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AQ28">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU28">
         <v>8</v>
@@ -6874,25 +6877,25 @@
         <v>2.2</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>0.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU29">
         <v>5</v>
@@ -7080,25 +7083,25 @@
         <v>1.73</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP30">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AU30">
         <v>3</v>
@@ -7292,7 +7295,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7492,25 +7495,25 @@
         <v>1.38</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO32">
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AQ32">
         <v>1</v>
       </c>
       <c r="AR32">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AS32">
-        <v>0.8100000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="AT32">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AU32">
         <v>3</v>
@@ -7698,25 +7701,25 @@
         <v>1.32</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO33">
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="AQ33">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AR33">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AS33">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AT33">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="AU33">
         <v>2</v>
@@ -7907,22 +7910,22 @@
         <v>0</v>
       </c>
       <c r="AO34">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR34">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AS34">
-        <v>0.87</v>
+        <v>1.26</v>
       </c>
       <c r="AT34">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="AU34">
         <v>5</v>
@@ -8113,22 +8116,22 @@
         <v>3</v>
       </c>
       <c r="AO35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP35">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AR35">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AS35">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AT35">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8244,7 +8247,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8322,19 +8325,19 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
-        <v>0.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR36">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="AS36">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AT36">
-        <v>2.4</v>
+        <v>3.11</v>
       </c>
       <c r="AU36">
         <v>4</v>
@@ -8528,19 +8531,19 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AR37">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AS37">
-        <v>1.19</v>
+        <v>1.79</v>
       </c>
       <c r="AT37">
-        <v>3.24</v>
+        <v>3.41</v>
       </c>
       <c r="AU37">
         <v>5</v>
@@ -8728,25 +8731,25 @@
         <v>1.47</v>
       </c>
       <c r="AN38">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ38">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR38">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AS38">
-        <v>0.85</v>
+        <v>1.21</v>
       </c>
       <c r="AT38">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -8940,19 +8943,19 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR39">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AS39">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="AT39">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="AU39">
         <v>7</v>
@@ -9068,7 +9071,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9140,25 +9143,25 @@
         <v>1.68</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ40">
-        <v>0.33</v>
+        <v>1.86</v>
       </c>
       <c r="AR40">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AT40">
-        <v>1.12</v>
+        <v>2.97</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9346,25 +9349,25 @@
         <v>1.53</v>
       </c>
       <c r="AN41">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO41">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR41">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="AS41">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AT41">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU41">
         <v>5</v>
@@ -9552,25 +9555,25 @@
         <v>1.55</v>
       </c>
       <c r="AN42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO42">
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR42">
-        <v>2.46</v>
+        <v>1.6</v>
       </c>
       <c r="AS42">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AT42">
-        <v>4.43</v>
+        <v>3.3</v>
       </c>
       <c r="AU42">
         <v>6</v>
@@ -9758,25 +9761,25 @@
         <v>1.66</v>
       </c>
       <c r="AN43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP43">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR43">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AS43">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AT43">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AU43">
         <v>6</v>
@@ -9892,7 +9895,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -9964,25 +9967,25 @@
         <v>1.83</v>
       </c>
       <c r="AN44">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="AQ44">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AR44">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AS44">
         <v>1.47</v>
       </c>
       <c r="AT44">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="AU44">
         <v>5</v>
@@ -10098,7 +10101,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10170,25 +10173,25 @@
         <v>1.83</v>
       </c>
       <c r="AN45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP45">
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS45">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="AT45">
-        <v>1.09</v>
+        <v>2.4</v>
       </c>
       <c r="AU45">
         <v>5</v>
@@ -10304,7 +10307,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10379,22 +10382,22 @@
         <v>0</v>
       </c>
       <c r="AO46">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AQ46">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR46">
-        <v>2.39</v>
+        <v>1.77</v>
       </c>
       <c r="AS46">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="AT46">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AU46">
         <v>9</v>
@@ -10510,7 +10513,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10582,25 +10585,25 @@
         <v>1.51</v>
       </c>
       <c r="AN47">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO47">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP47">
-        <v>1.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ47">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="AR47">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AS47">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AT47">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="AU47">
         <v>6</v>
@@ -10716,7 +10719,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -10788,25 +10791,25 @@
         <v>1.57</v>
       </c>
       <c r="AN48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO48">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
-        <v>0.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR48">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AS48">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="AT48">
-        <v>2.7</v>
+        <v>3.07</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -10994,25 +10997,25 @@
         <v>1.68</v>
       </c>
       <c r="AN49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP49">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AR49">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AS49">
-        <v>1.19</v>
+        <v>1.58</v>
       </c>
       <c r="AT49">
-        <v>2.79</v>
+        <v>3.11</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11200,25 +11203,25 @@
         <v>1.66</v>
       </c>
       <c r="AN50">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="AR50">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="AS50">
-        <v>0.8100000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="AT50">
-        <v>3.31</v>
+        <v>2.94</v>
       </c>
       <c r="AU50">
         <v>6</v>
@@ -11334,7 +11337,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11406,25 +11409,25 @@
         <v>1.33</v>
       </c>
       <c r="AN51">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AO51">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="AR51">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AS51">
-        <v>0.74</v>
+        <v>1.56</v>
       </c>
       <c r="AT51">
-        <v>2.21</v>
+        <v>3.04</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11612,25 +11615,25 @@
         <v>1.37</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO52">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AP52">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AQ52">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR52">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AS52">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AT52">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -11821,22 +11824,22 @@
         <v>0</v>
       </c>
       <c r="AO53">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ53">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR53">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AS53">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AT53">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -11952,7 +11955,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12024,25 +12027,25 @@
         <v>1.87</v>
       </c>
       <c r="AN54">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO54">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP54">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AQ54">
         <v>1</v>
       </c>
       <c r="AR54">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="AS54">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AT54">
-        <v>2.46</v>
+        <v>2.86</v>
       </c>
       <c r="AU54">
         <v>7</v>
@@ -12230,25 +12233,25 @@
         <v>2.1</v>
       </c>
       <c r="AN55">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AO55">
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>2.29</v>
       </c>
       <c r="AR55">
+        <v>1.64</v>
+      </c>
+      <c r="AS55">
         <v>1.6</v>
       </c>
-      <c r="AS55">
-        <v>0.77</v>
-      </c>
       <c r="AT55">
-        <v>2.37</v>
+        <v>3.24</v>
       </c>
       <c r="AU55">
         <v>6</v>
@@ -12436,25 +12439,25 @@
         <v>1.75</v>
       </c>
       <c r="AN56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO56">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AR56">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AS56">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AT56">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="AU56">
         <v>4</v>
@@ -12570,7 +12573,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12642,25 +12645,25 @@
         <v>1.44</v>
       </c>
       <c r="AN57">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AO57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP57">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AQ57">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AR57">
-        <v>0.9</v>
+        <v>1.15</v>
       </c>
       <c r="AS57">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AT57">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -12848,25 +12851,25 @@
         <v>1.46</v>
       </c>
       <c r="AN58">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AQ58">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AR58">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="AS58">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AT58">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AU58">
         <v>5</v>
@@ -13057,19 +13060,19 @@
         <v>0</v>
       </c>
       <c r="AO59">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AQ59">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR59">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AS59">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AT59">
         <v>2.33</v>
@@ -13263,22 +13266,22 @@
         <v>0</v>
       </c>
       <c r="AO60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP60">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR60">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AS60">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="AT60">
-        <v>3.43</v>
+        <v>3.67</v>
       </c>
       <c r="AU60">
         <v>7</v>
@@ -13394,7 +13397,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13466,25 +13469,25 @@
         <v>1.32</v>
       </c>
       <c r="AN61">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO61">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AP61">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AQ61">
-        <v>0.33</v>
+        <v>1.86</v>
       </c>
       <c r="AR61">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="AS61">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AT61">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13672,25 +13675,25 @@
         <v>2.05</v>
       </c>
       <c r="AN62">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AO62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP62">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AR62">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AS62">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AT62">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -13878,25 +13881,25 @@
         <v>2.3</v>
       </c>
       <c r="AN63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO63">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AQ63">
         <v>1</v>
       </c>
       <c r="AR63">
-        <v>1.97</v>
+        <v>1.49</v>
       </c>
       <c r="AS63">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AT63">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="AU63">
         <v>5</v>
@@ -14084,25 +14087,25 @@
         <v>1.32</v>
       </c>
       <c r="AN64">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO64">
+        <v>2.25</v>
+      </c>
+      <c r="AP64">
+        <v>2.14</v>
+      </c>
+      <c r="AQ64">
         <v>1.5</v>
       </c>
-      <c r="AP64">
-        <v>3</v>
-      </c>
-      <c r="AQ64">
-        <v>1</v>
-      </c>
       <c r="AR64">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AS64">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AT64">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="AU64">
         <v>5</v>
@@ -14296,19 +14299,19 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="AQ65">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AR65">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="AS65">
-        <v>1.46</v>
+        <v>1.97</v>
       </c>
       <c r="AT65">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14496,25 +14499,25 @@
         <v>1.4</v>
       </c>
       <c r="AN66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO66">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AQ66">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AR66">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AS66">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AT66">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -14630,7 +14633,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14702,25 +14705,25 @@
         <v>1.6</v>
       </c>
       <c r="AN67">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO67">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP67">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AQ67">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AR67">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AS67">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AT67">
-        <v>3.27</v>
+        <v>3.03</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -14836,7 +14839,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -14908,25 +14911,25 @@
         <v>1.75</v>
       </c>
       <c r="AN68">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AO68">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP68">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ68">
-        <v>0.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR68">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AS68">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AT68">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="AU68">
         <v>4</v>
@@ -15114,25 +15117,25 @@
         <v>1.71</v>
       </c>
       <c r="AN69">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO69">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP69">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AQ69">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR69">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
       <c r="AS69">
-        <v>0.9</v>
+        <v>1.15</v>
       </c>
       <c r="AT69">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15320,25 +15323,25 @@
         <v>1.17</v>
       </c>
       <c r="AN70">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP70">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AR70">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AS70">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AT70">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15529,22 +15532,22 @@
         <v>1.5</v>
       </c>
       <c r="AO71">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR71">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AS71">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AT71">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15660,7 +15663,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15732,25 +15735,25 @@
         <v>1.26</v>
       </c>
       <c r="AN72">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO72">
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AR72">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AS72">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AT72">
-        <v>3.41</v>
+        <v>3.63</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -15866,7 +15869,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -15941,22 +15944,22 @@
         <v>2</v>
       </c>
       <c r="AO73">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR73">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AS73">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="AT73">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AU73">
         <v>8</v>
@@ -16144,25 +16147,25 @@
         <v>1.93</v>
       </c>
       <c r="AN74">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO74">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP74">
         <v>1</v>
       </c>
       <c r="AQ74">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR74">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AS74">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AT74">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="AU74">
         <v>11</v>
@@ -16350,25 +16353,25 @@
         <v>1.49</v>
       </c>
       <c r="AN75">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AO75">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP75">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AQ75">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AR75">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AS75">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="AT75">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="AU75">
         <v>2</v>
@@ -16484,7 +16487,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16556,25 +16559,25 @@
         <v>1.32</v>
       </c>
       <c r="AN76">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO76">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP76">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AR76">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AS76">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AT76">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -16690,7 +16693,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16762,25 +16765,25 @@
         <v>1.65</v>
       </c>
       <c r="AN77">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO77">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP77">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ77">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR77">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AS77">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AT77">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="AU77">
         <v>8</v>
@@ -16896,7 +16899,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -16971,22 +16974,22 @@
         <v>0</v>
       </c>
       <c r="AO78">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="AP78">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AQ78">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="AR78">
-        <v>2.48</v>
+        <v>1.8</v>
       </c>
       <c r="AS78">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="AT78">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AU78">
         <v>5</v>
@@ -17174,25 +17177,25 @@
         <v>1.6</v>
       </c>
       <c r="AN79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO79">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP79">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="AQ79">
-        <v>0.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR79">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AS79">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AT79">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="AU79">
         <v>13</v>
@@ -17308,7 +17311,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17380,25 +17383,25 @@
         <v>1.53</v>
       </c>
       <c r="AN80">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AO80">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AP80">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AQ80">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="AR80">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AS80">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AT80">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="AU80">
         <v>10</v>
@@ -17514,7 +17517,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17586,25 +17589,25 @@
         <v>1.8</v>
       </c>
       <c r="AN81">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO81">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR81">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AS81">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AT81">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -17720,7 +17723,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -17792,25 +17795,25 @@
         <v>1.39</v>
       </c>
       <c r="AN82">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AO82">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AP82">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AQ82">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AR82">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AS82">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AT82">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -17998,25 +18001,25 @@
         <v>2.1</v>
       </c>
       <c r="AN83">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO83">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP83">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR83">
         <v>1.66</v>
       </c>
       <c r="AS83">
-        <v>1.06</v>
+        <v>1.59</v>
       </c>
       <c r="AT83">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="AU83">
         <v>5</v>
@@ -18204,25 +18207,25 @@
         <v>1.66</v>
       </c>
       <c r="AN84">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AO84">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AP84">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ84">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR84">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AS84">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AT84">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="AU84">
         <v>5</v>
@@ -18338,7 +18341,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18410,25 +18413,25 @@
         <v>1.78</v>
       </c>
       <c r="AN85">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO85">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP85">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="AQ85">
         <v>1</v>
       </c>
       <c r="AR85">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AS85">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AT85">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18616,25 +18619,25 @@
         <v>1.6</v>
       </c>
       <c r="AN86">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AO86">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AP86">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AQ86">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="AR86">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AS86">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AT86">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AU86">
         <v>4</v>
@@ -18750,7 +18753,7 @@
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18822,25 +18825,25 @@
         <v>1.52</v>
       </c>
       <c r="AN87">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AO87">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AP87">
-        <v>1.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ87">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AR87">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="AS87">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AT87">
-        <v>3.06</v>
+        <v>2.67</v>
       </c>
       <c r="AU87">
         <v>9</v>
@@ -18956,7 +18959,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19028,25 +19031,25 @@
         <v>1.34</v>
       </c>
       <c r="AN88">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO88">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AP88">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>2.29</v>
       </c>
       <c r="AR88">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AS88">
-        <v>0.97</v>
+        <v>1.55</v>
       </c>
       <c r="AT88">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AU88">
         <v>3</v>
@@ -19162,7 +19165,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19234,25 +19237,25 @@
         <v>2</v>
       </c>
       <c r="AN89">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AO89">
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR89">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AS89">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AT89">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="AU89">
         <v>6</v>
@@ -19368,7 +19371,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19440,25 +19443,25 @@
         <v>1.63</v>
       </c>
       <c r="AN90">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="AO90">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR90">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AS90">
-        <v>0.8</v>
+        <v>1.19</v>
       </c>
       <c r="AT90">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="AU90">
         <v>2</v>
@@ -19646,25 +19649,25 @@
         <v>1.25</v>
       </c>
       <c r="AN91">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO91">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AQ91">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AR91">
         <v>1.17</v>
       </c>
       <c r="AS91">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AT91">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -19780,7 +19783,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19852,25 +19855,25 @@
         <v>2.11</v>
       </c>
       <c r="AN92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO92">
-        <v>0.5</v>
+        <v>2.17</v>
       </c>
       <c r="AP92">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AQ92">
-        <v>0.33</v>
+        <v>1.86</v>
       </c>
       <c r="AR92">
-        <v>1.86</v>
+        <v>1.46</v>
       </c>
       <c r="AS92">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AT92">
-        <v>3.44</v>
+        <v>3.37</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20058,25 +20061,25 @@
         <v>1.45</v>
       </c>
       <c r="AN93">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO93">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP93">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR93">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AS93">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
       <c r="AT93">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AU93">
         <v>4</v>
@@ -20264,25 +20267,25 @@
         <v>1.6</v>
       </c>
       <c r="AN94">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO94">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AP94">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AQ94">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR94">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AS94">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="AT94">
-        <v>2.98</v>
+        <v>2.87</v>
       </c>
       <c r="AU94">
         <v>7</v>
@@ -20470,25 +20473,25 @@
         <v>2.05</v>
       </c>
       <c r="AN95">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AO95">
-        <v>0.33</v>
+        <v>1.17</v>
       </c>
       <c r="AP95">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AQ95">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AR95">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AS95">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AT95">
-        <v>3.13</v>
+        <v>2.71</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -20604,7 +20607,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20676,25 +20679,25 @@
         <v>2.5</v>
       </c>
       <c r="AN96">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="AO96">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AP96">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AR96">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AS96">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AT96">
-        <v>2.61</v>
+        <v>3.06</v>
       </c>
       <c r="AU96">
         <v>7</v>
@@ -20810,7 +20813,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -20882,25 +20885,25 @@
         <v>1.13</v>
       </c>
       <c r="AN97">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AO97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP97">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="AQ97">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AR97">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AS97">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AT97">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="AU97">
         <v>3</v>
@@ -21088,25 +21091,25 @@
         <v>2.05</v>
       </c>
       <c r="AN98">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO98">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AP98">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AQ98">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR98">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AS98">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="AT98">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="AU98">
         <v>3</v>
@@ -21294,25 +21297,25 @@
         <v>1.55</v>
       </c>
       <c r="AN99">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO99">
         <v>2.33</v>
       </c>
       <c r="AP99">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ99">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR99">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AS99">
-        <v>0.79</v>
+        <v>1.12</v>
       </c>
       <c r="AT99">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AU99">
         <v>5</v>
@@ -21428,7 +21431,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21500,25 +21503,25 @@
         <v>1.75</v>
       </c>
       <c r="AN100">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AO100">
-        <v>0.33</v>
+        <v>1.17</v>
       </c>
       <c r="AP100">
         <v>1</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR100">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AS100">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AT100">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="AU100">
         <v>6</v>
@@ -21706,25 +21709,25 @@
         <v>1.6</v>
       </c>
       <c r="AN101">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AO101">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="AP101">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="AQ101">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AR101">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AS101">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AT101">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="AU101">
         <v>7</v>
@@ -21791,6 +21794,624 @@
       </c>
       <c r="BP101">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7820417</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45712.70833333334</v>
+      </c>
+      <c r="F102">
+        <v>7</v>
+      </c>
+      <c r="G102" t="s">
+        <v>75</v>
+      </c>
+      <c r="H102" t="s">
+        <v>72</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>2</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>2</v>
+      </c>
+      <c r="O102" t="s">
+        <v>165</v>
+      </c>
+      <c r="P102" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q102">
+        <v>3.6</v>
+      </c>
+      <c r="R102">
+        <v>1.91</v>
+      </c>
+      <c r="S102">
+        <v>3.75</v>
+      </c>
+      <c r="T102">
+        <v>1.57</v>
+      </c>
+      <c r="U102">
+        <v>2.25</v>
+      </c>
+      <c r="V102">
+        <v>4</v>
+      </c>
+      <c r="W102">
+        <v>1.22</v>
+      </c>
+      <c r="X102">
+        <v>13</v>
+      </c>
+      <c r="Y102">
+        <v>1.04</v>
+      </c>
+      <c r="Z102">
+        <v>2.81</v>
+      </c>
+      <c r="AA102">
+        <v>2.64</v>
+      </c>
+      <c r="AB102">
+        <v>2.97</v>
+      </c>
+      <c r="AC102">
+        <v>1.12</v>
+      </c>
+      <c r="AD102">
+        <v>6.4</v>
+      </c>
+      <c r="AE102">
+        <v>1.53</v>
+      </c>
+      <c r="AF102">
+        <v>2.37</v>
+      </c>
+      <c r="AG102">
+        <v>2.7</v>
+      </c>
+      <c r="AH102">
+        <v>1.44</v>
+      </c>
+      <c r="AI102">
+        <v>2.1</v>
+      </c>
+      <c r="AJ102">
+        <v>1.67</v>
+      </c>
+      <c r="AK102">
+        <v>1.42</v>
+      </c>
+      <c r="AL102">
+        <v>1.36</v>
+      </c>
+      <c r="AM102">
+        <v>1.46</v>
+      </c>
+      <c r="AN102">
+        <v>1.5</v>
+      </c>
+      <c r="AO102">
+        <v>0.5</v>
+      </c>
+      <c r="AP102">
+        <v>1.71</v>
+      </c>
+      <c r="AQ102">
+        <v>0.43</v>
+      </c>
+      <c r="AR102">
+        <v>1.13</v>
+      </c>
+      <c r="AS102">
+        <v>1.65</v>
+      </c>
+      <c r="AT102">
+        <v>2.78</v>
+      </c>
+      <c r="AU102">
+        <v>7</v>
+      </c>
+      <c r="AV102">
+        <v>6</v>
+      </c>
+      <c r="AW102">
+        <v>4</v>
+      </c>
+      <c r="AX102">
+        <v>10</v>
+      </c>
+      <c r="AY102">
+        <v>11</v>
+      </c>
+      <c r="AZ102">
+        <v>17</v>
+      </c>
+      <c r="BA102">
+        <v>3</v>
+      </c>
+      <c r="BB102">
+        <v>3</v>
+      </c>
+      <c r="BC102">
+        <v>6</v>
+      </c>
+      <c r="BD102">
+        <v>1.95</v>
+      </c>
+      <c r="BE102">
+        <v>6.4</v>
+      </c>
+      <c r="BF102">
+        <v>2.05</v>
+      </c>
+      <c r="BG102">
+        <v>1.43</v>
+      </c>
+      <c r="BH102">
+        <v>2.6</v>
+      </c>
+      <c r="BI102">
+        <v>1.72</v>
+      </c>
+      <c r="BJ102">
+        <v>1.98</v>
+      </c>
+      <c r="BK102">
+        <v>2.14</v>
+      </c>
+      <c r="BL102">
+        <v>1.62</v>
+      </c>
+      <c r="BM102">
+        <v>2.7</v>
+      </c>
+      <c r="BN102">
+        <v>1.38</v>
+      </c>
+      <c r="BO102">
+        <v>3.65</v>
+      </c>
+      <c r="BP102">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7820418</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45712.79166666666</v>
+      </c>
+      <c r="F103">
+        <v>7</v>
+      </c>
+      <c r="G103" t="s">
+        <v>98</v>
+      </c>
+      <c r="H103" t="s">
+        <v>89</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103" t="s">
+        <v>100</v>
+      </c>
+      <c r="P103" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q103">
+        <v>2.4</v>
+      </c>
+      <c r="R103">
+        <v>2</v>
+      </c>
+      <c r="S103">
+        <v>6.5</v>
+      </c>
+      <c r="T103">
+        <v>1.57</v>
+      </c>
+      <c r="U103">
+        <v>2.25</v>
+      </c>
+      <c r="V103">
+        <v>3.75</v>
+      </c>
+      <c r="W103">
+        <v>1.25</v>
+      </c>
+      <c r="X103">
+        <v>11</v>
+      </c>
+      <c r="Y103">
+        <v>1.05</v>
+      </c>
+      <c r="Z103">
+        <v>1.62</v>
+      </c>
+      <c r="AA103">
+        <v>3.51</v>
+      </c>
+      <c r="AB103">
+        <v>5.75</v>
+      </c>
+      <c r="AC103">
+        <v>1.1</v>
+      </c>
+      <c r="AD103">
+        <v>6.8</v>
+      </c>
+      <c r="AE103">
+        <v>1.49</v>
+      </c>
+      <c r="AF103">
+        <v>2.4</v>
+      </c>
+      <c r="AG103">
+        <v>2.5</v>
+      </c>
+      <c r="AH103">
+        <v>1.5</v>
+      </c>
+      <c r="AI103">
+        <v>2.38</v>
+      </c>
+      <c r="AJ103">
+        <v>1.53</v>
+      </c>
+      <c r="AK103">
+        <v>1.15</v>
+      </c>
+      <c r="AL103">
+        <v>1.3</v>
+      </c>
+      <c r="AM103">
+        <v>2.1</v>
+      </c>
+      <c r="AN103">
+        <v>2.33</v>
+      </c>
+      <c r="AO103">
+        <v>1.33</v>
+      </c>
+      <c r="AP103">
+        <v>2.14</v>
+      </c>
+      <c r="AQ103">
+        <v>1.29</v>
+      </c>
+      <c r="AR103">
+        <v>1.55</v>
+      </c>
+      <c r="AS103">
+        <v>1.68</v>
+      </c>
+      <c r="AT103">
+        <v>3.23</v>
+      </c>
+      <c r="AU103">
+        <v>8</v>
+      </c>
+      <c r="AV103">
+        <v>2</v>
+      </c>
+      <c r="AW103">
+        <v>12</v>
+      </c>
+      <c r="AX103">
+        <v>4</v>
+      </c>
+      <c r="AY103">
+        <v>26</v>
+      </c>
+      <c r="AZ103">
+        <v>7</v>
+      </c>
+      <c r="BA103">
+        <v>10</v>
+      </c>
+      <c r="BB103">
+        <v>2</v>
+      </c>
+      <c r="BC103">
+        <v>12</v>
+      </c>
+      <c r="BD103">
+        <v>1.29</v>
+      </c>
+      <c r="BE103">
+        <v>7.5</v>
+      </c>
+      <c r="BF103">
+        <v>3.95</v>
+      </c>
+      <c r="BG103">
+        <v>1.37</v>
+      </c>
+      <c r="BH103">
+        <v>2.8</v>
+      </c>
+      <c r="BI103">
+        <v>1.62</v>
+      </c>
+      <c r="BJ103">
+        <v>2.14</v>
+      </c>
+      <c r="BK103">
+        <v>1.98</v>
+      </c>
+      <c r="BL103">
+        <v>1.72</v>
+      </c>
+      <c r="BM103">
+        <v>2.55</v>
+      </c>
+      <c r="BN103">
+        <v>1.44</v>
+      </c>
+      <c r="BO103">
+        <v>3.3</v>
+      </c>
+      <c r="BP103">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7820419</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45712.875</v>
+      </c>
+      <c r="F104">
+        <v>7</v>
+      </c>
+      <c r="G104" t="s">
+        <v>71</v>
+      </c>
+      <c r="H104" t="s">
+        <v>85</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>1</v>
+      </c>
+      <c r="O104" t="s">
+        <v>166</v>
+      </c>
+      <c r="P104" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q104">
+        <v>2.88</v>
+      </c>
+      <c r="R104">
+        <v>1.91</v>
+      </c>
+      <c r="S104">
+        <v>5</v>
+      </c>
+      <c r="T104">
+        <v>1.62</v>
+      </c>
+      <c r="U104">
+        <v>2.2</v>
+      </c>
+      <c r="V104">
+        <v>4</v>
+      </c>
+      <c r="W104">
+        <v>1.22</v>
+      </c>
+      <c r="X104">
+        <v>13</v>
+      </c>
+      <c r="Y104">
+        <v>1.04</v>
+      </c>
+      <c r="Z104">
+        <v>2.06</v>
+      </c>
+      <c r="AA104">
+        <v>2.94</v>
+      </c>
+      <c r="AB104">
+        <v>4.06</v>
+      </c>
+      <c r="AC104">
+        <v>1.12</v>
+      </c>
+      <c r="AD104">
+        <v>6.2</v>
+      </c>
+      <c r="AE104">
+        <v>1.53</v>
+      </c>
+      <c r="AF104">
+        <v>2.3</v>
+      </c>
+      <c r="AG104">
+        <v>2.7</v>
+      </c>
+      <c r="AH104">
+        <v>1.44</v>
+      </c>
+      <c r="AI104">
+        <v>2.25</v>
+      </c>
+      <c r="AJ104">
+        <v>1.57</v>
+      </c>
+      <c r="AK104">
+        <v>1.24</v>
+      </c>
+      <c r="AL104">
+        <v>1.36</v>
+      </c>
+      <c r="AM104">
+        <v>1.72</v>
+      </c>
+      <c r="AN104">
+        <v>2</v>
+      </c>
+      <c r="AO104">
+        <v>1.17</v>
+      </c>
+      <c r="AP104">
+        <v>2.14</v>
+      </c>
+      <c r="AQ104">
+        <v>1</v>
+      </c>
+      <c r="AR104">
+        <v>1.49</v>
+      </c>
+      <c r="AS104">
+        <v>1.34</v>
+      </c>
+      <c r="AT104">
+        <v>2.83</v>
+      </c>
+      <c r="AU104">
+        <v>-1</v>
+      </c>
+      <c r="AV104">
+        <v>-1</v>
+      </c>
+      <c r="AW104">
+        <v>-1</v>
+      </c>
+      <c r="AX104">
+        <v>-1</v>
+      </c>
+      <c r="AY104">
+        <v>-1</v>
+      </c>
+      <c r="AZ104">
+        <v>-1</v>
+      </c>
+      <c r="BA104">
+        <v>-1</v>
+      </c>
+      <c r="BB104">
+        <v>-1</v>
+      </c>
+      <c r="BC104">
+        <v>-1</v>
+      </c>
+      <c r="BD104">
+        <v>1.88</v>
+      </c>
+      <c r="BE104">
+        <v>6.25</v>
+      </c>
+      <c r="BF104">
+        <v>2.15</v>
+      </c>
+      <c r="BG104">
+        <v>1.63</v>
+      </c>
+      <c r="BH104">
+        <v>2.12</v>
+      </c>
+      <c r="BI104">
+        <v>2.04</v>
+      </c>
+      <c r="BJ104">
+        <v>1.68</v>
+      </c>
+      <c r="BK104">
+        <v>2.65</v>
+      </c>
+      <c r="BL104">
+        <v>1.41</v>
+      </c>
+      <c r="BM104">
+        <v>3.55</v>
+      </c>
+      <c r="BN104">
+        <v>1.24</v>
+      </c>
+      <c r="BO104">
+        <v>4.9</v>
+      </c>
+      <c r="BP104">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -1321,10 +1321,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ2">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AQ3">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ4">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1939,10 +1939,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AQ6">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2351,10 +2351,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2557,10 +2557,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AQ8">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9">
-        <v>1.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3175,10 +3175,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3381,10 +3381,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AQ12">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3587,10 +3587,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3793,10 +3793,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3999,10 +3999,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ15">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4205,10 +4205,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="AQ16">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4405,25 +4405,25 @@
         <v>1.53</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU17">
         <v>6</v>
@@ -4611,25 +4611,25 @@
         <v>1.68</v>
       </c>
       <c r="AN18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AQ18">
-        <v>0.43</v>
+        <v>0.67</v>
       </c>
       <c r="AR18">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AS18">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AT18">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AU18">
         <v>2</v>
@@ -4817,25 +4817,25 @@
         <v>1.6</v>
       </c>
       <c r="AN19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO19">
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="AQ19">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR19">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AS19">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU19">
         <v>3</v>
@@ -5029,19 +5029,19 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR20">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="AS20">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AT20">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU20">
         <v>6</v>
@@ -5229,25 +5229,25 @@
         <v>1.9</v>
       </c>
       <c r="AN21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="AQ21">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR21">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AS21">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AU21">
         <v>5</v>
@@ -5438,22 +5438,22 @@
         <v>0</v>
       </c>
       <c r="AO22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ22">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR22">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AU22">
         <v>6</v>
@@ -5644,22 +5644,22 @@
         <v>0</v>
       </c>
       <c r="AO23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="AQ23">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="AR23">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AU23">
         <v>9</v>
@@ -5850,22 +5850,22 @@
         <v>0</v>
       </c>
       <c r="AO24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR24">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="AS24">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AT24">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AU24">
         <v>2</v>
@@ -6053,25 +6053,25 @@
         <v>1.34</v>
       </c>
       <c r="AN25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="AQ25">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="AR25">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AS25">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT25">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AU25">
         <v>8</v>
@@ -6262,22 +6262,22 @@
         <v>0</v>
       </c>
       <c r="AO26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AQ26">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AS26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT26">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6465,25 +6465,25 @@
         <v>2.7</v>
       </c>
       <c r="AN27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AR27">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS27">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="AU27">
         <v>6</v>
@@ -6677,19 +6677,19 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="AQ28">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR28">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AS28">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AT28">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AU28">
         <v>8</v>
@@ -6877,25 +6877,25 @@
         <v>2.2</v>
       </c>
       <c r="AN29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
-        <v>1.14</v>
+        <v>0.33</v>
       </c>
       <c r="AR29">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS29">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AT29">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU29">
         <v>5</v>
@@ -7083,25 +7083,25 @@
         <v>1.73</v>
       </c>
       <c r="AN30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="AR30">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AS30">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AT30">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AU30">
         <v>3</v>
@@ -7295,7 +7295,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7495,25 +7495,25 @@
         <v>1.38</v>
       </c>
       <c r="AN32">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR32">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AS32">
-        <v>1.17</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT32">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AU32">
         <v>3</v>
@@ -7701,25 +7701,25 @@
         <v>1.32</v>
       </c>
       <c r="AN33">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO33">
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="AQ33">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AR33">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AS33">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AT33">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="AU33">
         <v>2</v>
@@ -7910,22 +7910,22 @@
         <v>0</v>
       </c>
       <c r="AO34">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AQ34">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AR34">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AS34">
-        <v>1.26</v>
+        <v>0.87</v>
       </c>
       <c r="AT34">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="AU34">
         <v>5</v>
@@ -8116,22 +8116,22 @@
         <v>3</v>
       </c>
       <c r="AO35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ35">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="AR35">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AS35">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AT35">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8325,19 +8325,19 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ36">
-        <v>1.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR36">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="AS36">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AT36">
-        <v>3.11</v>
+        <v>2.4</v>
       </c>
       <c r="AU36">
         <v>4</v>
@@ -8531,19 +8531,19 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ37">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AR37">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AS37">
-        <v>1.79</v>
+        <v>1.19</v>
       </c>
       <c r="AT37">
-        <v>3.41</v>
+        <v>3.24</v>
       </c>
       <c r="AU37">
         <v>5</v>
@@ -8731,25 +8731,25 @@
         <v>1.47</v>
       </c>
       <c r="AN38">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR38">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AS38">
-        <v>1.21</v>
+        <v>0.85</v>
       </c>
       <c r="AT38">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -8943,19 +8943,19 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AQ39">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AR39">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AS39">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="AT39">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="AU39">
         <v>7</v>
@@ -9143,25 +9143,25 @@
         <v>1.68</v>
       </c>
       <c r="AN40">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AQ40">
-        <v>1.86</v>
+        <v>0.33</v>
       </c>
       <c r="AR40">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="AS40">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AT40">
-        <v>2.97</v>
+        <v>1.12</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9349,25 +9349,25 @@
         <v>1.53</v>
       </c>
       <c r="AN41">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO41">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP41">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AQ41">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR41">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AS41">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AT41">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AU41">
         <v>5</v>
@@ -9555,25 +9555,25 @@
         <v>1.55</v>
       </c>
       <c r="AN42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO42">
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR42">
-        <v>1.6</v>
+        <v>2.46</v>
       </c>
       <c r="AS42">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AT42">
-        <v>3.3</v>
+        <v>4.43</v>
       </c>
       <c r="AU42">
         <v>6</v>
@@ -9761,25 +9761,25 @@
         <v>1.66</v>
       </c>
       <c r="AN43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP43">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR43">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AS43">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AT43">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AU43">
         <v>6</v>
@@ -9967,25 +9967,25 @@
         <v>1.83</v>
       </c>
       <c r="AN44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP44">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AQ44">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AR44">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AS44">
         <v>1.47</v>
       </c>
       <c r="AT44">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="AU44">
         <v>5</v>
@@ -10173,25 +10173,25 @@
         <v>1.83</v>
       </c>
       <c r="AN45">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP45">
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AR45">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AS45">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="AT45">
-        <v>2.4</v>
+        <v>1.09</v>
       </c>
       <c r="AU45">
         <v>5</v>
@@ -10382,22 +10382,22 @@
         <v>0</v>
       </c>
       <c r="AO46">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP46">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="AQ46">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR46">
-        <v>1.77</v>
+        <v>2.39</v>
       </c>
       <c r="AS46">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="AT46">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AU46">
         <v>9</v>
@@ -10585,25 +10585,25 @@
         <v>1.51</v>
       </c>
       <c r="AN47">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO47">
+        <v>1</v>
+      </c>
+      <c r="AP47">
+        <v>1.67</v>
+      </c>
+      <c r="AQ47">
         <v>0.67</v>
       </c>
-      <c r="AP47">
-        <v>0.71</v>
-      </c>
-      <c r="AQ47">
-        <v>0.43</v>
-      </c>
       <c r="AR47">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AS47">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AT47">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="AU47">
         <v>6</v>
@@ -10791,25 +10791,25 @@
         <v>1.57</v>
       </c>
       <c r="AN48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO48">
+        <v>0</v>
+      </c>
+      <c r="AP48">
+        <v>1.33</v>
+      </c>
+      <c r="AQ48">
         <v>0.33</v>
       </c>
-      <c r="AP48">
-        <v>1</v>
-      </c>
-      <c r="AQ48">
-        <v>1.14</v>
-      </c>
       <c r="AR48">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AS48">
-        <v>1.71</v>
+        <v>1.17</v>
       </c>
       <c r="AT48">
-        <v>3.07</v>
+        <v>2.7</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -10997,25 +10997,25 @@
         <v>1.68</v>
       </c>
       <c r="AN49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="AQ49">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="AR49">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AS49">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="AT49">
-        <v>3.11</v>
+        <v>2.79</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11203,25 +11203,25 @@
         <v>1.66</v>
       </c>
       <c r="AN50">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="AQ50">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="AR50">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="AS50">
-        <v>1.22</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT50">
-        <v>2.94</v>
+        <v>3.31</v>
       </c>
       <c r="AU50">
         <v>6</v>
@@ -11409,25 +11409,25 @@
         <v>1.33</v>
       </c>
       <c r="AN51">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AO51">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="AQ51">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="AR51">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AS51">
-        <v>1.56</v>
+        <v>0.74</v>
       </c>
       <c r="AT51">
-        <v>3.04</v>
+        <v>2.21</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11615,25 +11615,25 @@
         <v>1.37</v>
       </c>
       <c r="AN52">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO52">
+        <v>1</v>
+      </c>
+      <c r="AP52">
+        <v>0.67</v>
+      </c>
+      <c r="AQ52">
         <v>2.33</v>
       </c>
-      <c r="AP52">
-        <v>0.33</v>
-      </c>
-      <c r="AQ52">
-        <v>2.14</v>
-      </c>
       <c r="AR52">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AS52">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AT52">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -11824,22 +11824,22 @@
         <v>0</v>
       </c>
       <c r="AO53">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP53">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ53">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR53">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AS53">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AT53">
-        <v>2.32</v>
+        <v>2.76</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12027,25 +12027,25 @@
         <v>1.87</v>
       </c>
       <c r="AN54">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO54">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="AQ54">
         <v>1</v>
       </c>
       <c r="AR54">
-        <v>1.39</v>
+        <v>1.05</v>
       </c>
       <c r="AS54">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AT54">
-        <v>2.86</v>
+        <v>2.46</v>
       </c>
       <c r="AU54">
         <v>7</v>
@@ -12233,25 +12233,25 @@
         <v>2.1</v>
       </c>
       <c r="AN55">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AO55">
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AQ55">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="AR55">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AS55">
-        <v>1.6</v>
+        <v>0.77</v>
       </c>
       <c r="AT55">
-        <v>3.24</v>
+        <v>2.37</v>
       </c>
       <c r="AU55">
         <v>6</v>
@@ -12439,25 +12439,25 @@
         <v>1.75</v>
       </c>
       <c r="AN56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO56">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR56">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AS56">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AT56">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AU56">
         <v>4</v>
@@ -12645,25 +12645,25 @@
         <v>1.44</v>
       </c>
       <c r="AN57">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AO57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AQ57">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR57">
-        <v>1.15</v>
+        <v>0.9</v>
       </c>
       <c r="AS57">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AT57">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -12851,25 +12851,25 @@
         <v>1.46</v>
       </c>
       <c r="AN58">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AR58">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AS58">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AT58">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="AU58">
         <v>5</v>
@@ -13060,19 +13060,19 @@
         <v>0</v>
       </c>
       <c r="AO59">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR59">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AS59">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AT59">
         <v>2.33</v>
@@ -13266,22 +13266,22 @@
         <v>0</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="AQ60">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR60">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AS60">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="AT60">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="AU60">
         <v>7</v>
@@ -13469,25 +13469,25 @@
         <v>1.32</v>
       </c>
       <c r="AN61">
+        <v>1.5</v>
+      </c>
+      <c r="AO61">
+        <v>0</v>
+      </c>
+      <c r="AP61">
         <v>1.75</v>
       </c>
-      <c r="AO61">
-        <v>2.25</v>
-      </c>
-      <c r="AP61">
-        <v>1.71</v>
-      </c>
       <c r="AQ61">
-        <v>1.86</v>
+        <v>0.33</v>
       </c>
       <c r="AR61">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="AS61">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AT61">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13675,25 +13675,25 @@
         <v>2.05</v>
       </c>
       <c r="AN62">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AO62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ62">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AR62">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AS62">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AT62">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -13881,25 +13881,25 @@
         <v>2.3</v>
       </c>
       <c r="AN63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO63">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AQ63">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR63">
-        <v>1.49</v>
+        <v>1.97</v>
       </c>
       <c r="AS63">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AT63">
-        <v>2.81</v>
+        <v>3.25</v>
       </c>
       <c r="AU63">
         <v>5</v>
@@ -14087,25 +14087,25 @@
         <v>1.32</v>
       </c>
       <c r="AN64">
+        <v>3</v>
+      </c>
+      <c r="AO64">
         <v>1.5</v>
       </c>
-      <c r="AO64">
-        <v>2.25</v>
-      </c>
       <c r="AP64">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AQ64">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR64">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AS64">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AT64">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="AU64">
         <v>5</v>
@@ -14299,19 +14299,19 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AQ65">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AR65">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="AS65">
-        <v>1.97</v>
+        <v>1.46</v>
       </c>
       <c r="AT65">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14499,25 +14499,25 @@
         <v>1.4</v>
       </c>
       <c r="AN66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO66">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AR66">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AS66">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AT66">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -14705,25 +14705,25 @@
         <v>1.6</v>
       </c>
       <c r="AN67">
+        <v>1.5</v>
+      </c>
+      <c r="AO67">
+        <v>2</v>
+      </c>
+      <c r="AP67">
         <v>0.75</v>
       </c>
-      <c r="AO67">
+      <c r="AQ67">
         <v>1.75</v>
       </c>
-      <c r="AP67">
-        <v>0.43</v>
-      </c>
-      <c r="AQ67">
-        <v>1.57</v>
-      </c>
       <c r="AR67">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AS67">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AT67">
-        <v>3.03</v>
+        <v>3.27</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -14911,25 +14911,25 @@
         <v>1.75</v>
       </c>
       <c r="AN68">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AO68">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
-        <v>1.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR68">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AS68">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AT68">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="AU68">
         <v>4</v>
@@ -15117,25 +15117,25 @@
         <v>1.71</v>
       </c>
       <c r="AN69">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AO69">
+        <v>0</v>
+      </c>
+      <c r="AP69">
+        <v>3</v>
+      </c>
+      <c r="AQ69">
         <v>0.25</v>
       </c>
-      <c r="AP69">
-        <v>2.29</v>
-      </c>
-      <c r="AQ69">
-        <v>0.29</v>
-      </c>
       <c r="AR69">
-        <v>1.49</v>
+        <v>2.02</v>
       </c>
       <c r="AS69">
-        <v>1.15</v>
+        <v>0.9</v>
       </c>
       <c r="AT69">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15323,25 +15323,25 @@
         <v>1.17</v>
       </c>
       <c r="AN70">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP70">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ70">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="AR70">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AS70">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AT70">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15532,22 +15532,22 @@
         <v>1.5</v>
       </c>
       <c r="AO71">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AQ71">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AR71">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AS71">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AT71">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15735,25 +15735,25 @@
         <v>1.26</v>
       </c>
       <c r="AN72">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AO72">
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="AQ72">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AR72">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AS72">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AT72">
-        <v>3.63</v>
+        <v>3.41</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -15944,22 +15944,22 @@
         <v>2</v>
       </c>
       <c r="AO73">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ73">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR73">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AS73">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT73">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AU73">
         <v>8</v>
@@ -16147,25 +16147,25 @@
         <v>1.93</v>
       </c>
       <c r="AN74">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO74">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP74">
         <v>1</v>
       </c>
       <c r="AQ74">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AR74">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AS74">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AT74">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="AU74">
         <v>11</v>
@@ -16353,25 +16353,25 @@
         <v>1.49</v>
       </c>
       <c r="AN75">
+        <v>0.5</v>
+      </c>
+      <c r="AO75">
+        <v>0</v>
+      </c>
+      <c r="AP75">
+        <v>0.67</v>
+      </c>
+      <c r="AQ75">
         <v>0.25</v>
       </c>
-      <c r="AO75">
-        <v>1.5</v>
-      </c>
-      <c r="AP75">
-        <v>0.33</v>
-      </c>
-      <c r="AQ75">
-        <v>1</v>
-      </c>
       <c r="AR75">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="AS75">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="AT75">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="AU75">
         <v>2</v>
@@ -16559,25 +16559,25 @@
         <v>1.32</v>
       </c>
       <c r="AN76">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO76">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ76">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR76">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AS76">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AT76">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -16765,25 +16765,25 @@
         <v>1.65</v>
       </c>
       <c r="AN77">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO77">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AQ77">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR77">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AS77">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AT77">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="AU77">
         <v>8</v>
@@ -16974,22 +16974,22 @@
         <v>0</v>
       </c>
       <c r="AO78">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="AP78">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="AQ78">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="AR78">
-        <v>1.8</v>
+        <v>2.48</v>
       </c>
       <c r="AS78">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="AT78">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AU78">
         <v>5</v>
@@ -17177,25 +17177,25 @@
         <v>1.6</v>
       </c>
       <c r="AN79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO79">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="AQ79">
-        <v>1.14</v>
+        <v>0.33</v>
       </c>
       <c r="AR79">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AS79">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AT79">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="AU79">
         <v>13</v>
@@ -17383,25 +17383,25 @@
         <v>1.53</v>
       </c>
       <c r="AN80">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AO80">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="AQ80">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="AR80">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AS80">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AT80">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="AU80">
         <v>10</v>
@@ -17589,25 +17589,25 @@
         <v>1.8</v>
       </c>
       <c r="AN81">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO81">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="AR81">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AS81">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AT81">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -17795,25 +17795,25 @@
         <v>1.39</v>
       </c>
       <c r="AN82">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AO82">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AP82">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ82">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AR82">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AS82">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AT82">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18001,25 +18001,25 @@
         <v>2.1</v>
       </c>
       <c r="AN83">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO83">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AQ83">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR83">
         <v>1.66</v>
       </c>
       <c r="AS83">
-        <v>1.59</v>
+        <v>1.06</v>
       </c>
       <c r="AT83">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="AU83">
         <v>5</v>
@@ -18207,25 +18207,25 @@
         <v>1.66</v>
       </c>
       <c r="AN84">
+        <v>2</v>
+      </c>
+      <c r="AO84">
+        <v>0</v>
+      </c>
+      <c r="AP84">
+        <v>2.5</v>
+      </c>
+      <c r="AQ84">
+        <v>0</v>
+      </c>
+      <c r="AR84">
+        <v>1.91</v>
+      </c>
+      <c r="AS84">
         <v>1.2</v>
       </c>
-      <c r="AO84">
-        <v>0.4</v>
-      </c>
-      <c r="AP84">
-        <v>1.71</v>
-      </c>
-      <c r="AQ84">
-        <v>0.33</v>
-      </c>
-      <c r="AR84">
-        <v>1.45</v>
-      </c>
-      <c r="AS84">
-        <v>1.35</v>
-      </c>
       <c r="AT84">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="AU84">
         <v>5</v>
@@ -18413,25 +18413,25 @@
         <v>1.78</v>
       </c>
       <c r="AN85">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO85">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP85">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="AQ85">
         <v>1</v>
       </c>
       <c r="AR85">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AS85">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AT85">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18619,25 +18619,25 @@
         <v>1.6</v>
       </c>
       <c r="AN86">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AO86">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AQ86">
-        <v>0.43</v>
+        <v>0.67</v>
       </c>
       <c r="AR86">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AS86">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AT86">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AU86">
         <v>4</v>
@@ -18825,25 +18825,25 @@
         <v>1.52</v>
       </c>
       <c r="AN87">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AO87">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AP87">
-        <v>0.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ87">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AR87">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="AS87">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AT87">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
       <c r="AU87">
         <v>9</v>
@@ -19031,25 +19031,25 @@
         <v>1.34</v>
       </c>
       <c r="AN88">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO88">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AQ88">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="AR88">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AS88">
-        <v>1.55</v>
+        <v>0.97</v>
       </c>
       <c r="AT88">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AU88">
         <v>3</v>
@@ -19237,25 +19237,25 @@
         <v>2</v>
       </c>
       <c r="AN89">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AO89">
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR89">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AS89">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AT89">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="AU89">
         <v>6</v>
@@ -19443,25 +19443,25 @@
         <v>1.63</v>
       </c>
       <c r="AN90">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AO90">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR90">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AS90">
-        <v>1.19</v>
+        <v>0.8</v>
       </c>
       <c r="AT90">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="AU90">
         <v>2</v>
@@ -19649,25 +19649,25 @@
         <v>1.25</v>
       </c>
       <c r="AN91">
+        <v>1</v>
+      </c>
+      <c r="AO91">
         <v>1.5</v>
       </c>
-      <c r="AO91">
-        <v>0.8</v>
-      </c>
       <c r="AP91">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AQ91">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AR91">
         <v>1.17</v>
       </c>
       <c r="AS91">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AT91">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -19855,25 +19855,25 @@
         <v>2.11</v>
       </c>
       <c r="AN92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO92">
-        <v>2.17</v>
+        <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AQ92">
+        <v>0.33</v>
+      </c>
+      <c r="AR92">
         <v>1.86</v>
       </c>
-      <c r="AR92">
-        <v>1.46</v>
-      </c>
       <c r="AS92">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AT92">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20061,25 +20061,25 @@
         <v>1.45</v>
       </c>
       <c r="AN93">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO93">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP93">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ93">
+        <v>1</v>
+      </c>
+      <c r="AR93">
         <v>1.29</v>
       </c>
-      <c r="AR93">
-        <v>1.17</v>
-      </c>
       <c r="AS93">
-        <v>1.1</v>
+        <v>0.96</v>
       </c>
       <c r="AT93">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AU93">
         <v>4</v>
@@ -20267,25 +20267,25 @@
         <v>1.6</v>
       </c>
       <c r="AN94">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO94">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AP94">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AQ94">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR94">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AS94">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="AT94">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="AU94">
         <v>7</v>
@@ -20473,25 +20473,25 @@
         <v>2.05</v>
       </c>
       <c r="AN95">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="AO95">
-        <v>1.17</v>
+        <v>0.33</v>
       </c>
       <c r="AP95">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AR95">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AS95">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AT95">
-        <v>2.71</v>
+        <v>3.13</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -20679,25 +20679,25 @@
         <v>2.5</v>
       </c>
       <c r="AN96">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AO96">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ96">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AR96">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AS96">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="AT96">
-        <v>3.06</v>
+        <v>2.61</v>
       </c>
       <c r="AU96">
         <v>7</v>
@@ -20885,25 +20885,25 @@
         <v>1.13</v>
       </c>
       <c r="AN97">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AO97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP97">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="AQ97">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="AR97">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AS97">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AT97">
-        <v>3.12</v>
+        <v>3.21</v>
       </c>
       <c r="AU97">
         <v>3</v>
@@ -21091,25 +21091,25 @@
         <v>2.05</v>
       </c>
       <c r="AN98">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO98">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="AP98">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="AQ98">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AR98">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AS98">
-        <v>1.63</v>
+        <v>1.23</v>
       </c>
       <c r="AT98">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="AU98">
         <v>3</v>
@@ -21297,25 +21297,25 @@
         <v>1.55</v>
       </c>
       <c r="AN99">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="AO99">
         <v>2.33</v>
       </c>
       <c r="AP99">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="AQ99">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR99">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AS99">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="AT99">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AU99">
         <v>5</v>
@@ -21503,25 +21503,25 @@
         <v>1.75</v>
       </c>
       <c r="AN100">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AO100">
-        <v>1.17</v>
+        <v>0.33</v>
       </c>
       <c r="AP100">
         <v>1</v>
       </c>
       <c r="AQ100">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AR100">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AS100">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AT100">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="AU100">
         <v>6</v>
@@ -21709,25 +21709,25 @@
         <v>1.6</v>
       </c>
       <c r="AN101">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AO101">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AP101">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AQ101">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR101">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AS101">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AT101">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="AU101">
         <v>7</v>
@@ -21915,25 +21915,25 @@
         <v>1.46</v>
       </c>
       <c r="AN102">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AO102">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP102">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AQ102">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="AR102">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AS102">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AT102">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="AU102">
         <v>7</v>
@@ -22124,22 +22124,22 @@
         <v>2.33</v>
       </c>
       <c r="AO103">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AP103">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ103">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AR103">
         <v>1.55</v>
       </c>
       <c r="AS103">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="AT103">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22327,25 +22327,25 @@
         <v>1.72</v>
       </c>
       <c r="AN104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO104">
+        <v>1</v>
+      </c>
+      <c r="AP104">
+        <v>3</v>
+      </c>
+      <c r="AQ104">
+        <v>0.75</v>
+      </c>
+      <c r="AR104">
+        <v>1.38</v>
+      </c>
+      <c r="AS104">
         <v>1.17</v>
       </c>
-      <c r="AP104">
-        <v>2.14</v>
-      </c>
-      <c r="AQ104">
-        <v>1</v>
-      </c>
-      <c r="AR104">
-        <v>1.49</v>
-      </c>
-      <c r="AS104">
-        <v>1.34</v>
-      </c>
       <c r="AT104">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="AU104">
         <v>-1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -22348,31 +22348,31 @@
         <v>2.55</v>
       </c>
       <c r="AU104">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV104">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AW104">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AX104">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY104">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AZ104">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BA104">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB104">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC104">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BD104">
         <v>1.88</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="205">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,9 @@
     <t>['59']</t>
   </si>
   <si>
+    <t>['53', '55', '90+2']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -987,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP104"/>
+  <dimension ref="A1:BP107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1243,7 +1246,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1324,7 +1327,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1655,7 +1658,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2067,7 +2070,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2148,7 +2151,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ6">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2273,7 +2276,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2891,7 +2894,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -2969,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3303,7 +3306,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3999,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ15">
         <v>2.33</v>
@@ -4205,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ16">
         <v>0</v>
@@ -4745,7 +4748,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5363,7 +5366,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5569,7 +5572,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5775,7 +5778,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6187,7 +6190,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6599,7 +6602,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6886,7 +6889,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7295,7 +7298,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7707,10 +7710,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ33">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR33">
         <v>1.45</v>
@@ -8247,7 +8250,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8325,7 +8328,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ36">
         <v>0.67</v>
@@ -9071,7 +9074,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9895,7 +9898,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10101,7 +10104,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10182,7 +10185,7 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR45">
         <v>0</v>
@@ -10307,7 +10310,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10513,7 +10516,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10719,7 +10722,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -10800,7 +10803,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ48">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR48">
         <v>1.53</v>
@@ -11003,7 +11006,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ49">
         <v>0</v>
@@ -11337,7 +11340,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11955,7 +11958,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12573,7 +12576,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13397,7 +13400,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13681,7 +13684,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ62">
         <v>1.75</v>
@@ -14508,7 +14511,7 @@
         <v>1</v>
       </c>
       <c r="AQ66">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR66">
         <v>1.2</v>
@@ -14633,7 +14636,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14839,7 +14842,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15663,7 +15666,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15741,7 +15744,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ72">
         <v>1.33</v>
@@ -15869,7 +15872,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16487,7 +16490,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16693,7 +16696,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16899,7 +16902,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17183,10 +17186,10 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ79">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR79">
         <v>1.81</v>
@@ -17311,7 +17314,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17517,7 +17520,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17723,7 +17726,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -17804,7 +17807,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ82">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR82">
         <v>1.71</v>
@@ -18341,7 +18344,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18753,7 +18756,7 @@
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18834,7 +18837,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ87">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR87">
         <v>1.79</v>
@@ -18959,7 +18962,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19165,7 +19168,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19371,7 +19374,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19783,7 +19786,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20607,7 +20610,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20685,7 +20688,7 @@
         <v>0</v>
       </c>
       <c r="AP96">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ96">
         <v>0</v>
@@ -20813,7 +20816,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -20891,7 +20894,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ97">
         <v>1.5</v>
@@ -21431,7 +21434,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22412,6 +22415,624 @@
       </c>
       <c r="BP104">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7820420</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45716.83333333334</v>
+      </c>
+      <c r="F105">
+        <v>8</v>
+      </c>
+      <c r="G105" t="s">
+        <v>83</v>
+      </c>
+      <c r="H105" t="s">
+        <v>87</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>142</v>
+      </c>
+      <c r="P105" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q105">
+        <v>2.88</v>
+      </c>
+      <c r="R105">
+        <v>1.91</v>
+      </c>
+      <c r="S105">
+        <v>4.75</v>
+      </c>
+      <c r="T105">
+        <v>1.57</v>
+      </c>
+      <c r="U105">
+        <v>2.25</v>
+      </c>
+      <c r="V105">
+        <v>3.75</v>
+      </c>
+      <c r="W105">
+        <v>1.25</v>
+      </c>
+      <c r="X105">
+        <v>13</v>
+      </c>
+      <c r="Y105">
+        <v>1.04</v>
+      </c>
+      <c r="Z105">
+        <v>2.05</v>
+      </c>
+      <c r="AA105">
+        <v>3.3</v>
+      </c>
+      <c r="AB105">
+        <v>3.75</v>
+      </c>
+      <c r="AC105">
+        <v>1.11</v>
+      </c>
+      <c r="AD105">
+        <v>6.6</v>
+      </c>
+      <c r="AE105">
+        <v>1.5</v>
+      </c>
+      <c r="AF105">
+        <v>2.4</v>
+      </c>
+      <c r="AG105">
+        <v>2.6</v>
+      </c>
+      <c r="AH105">
+        <v>1.48</v>
+      </c>
+      <c r="AI105">
+        <v>2.2</v>
+      </c>
+      <c r="AJ105">
+        <v>1.62</v>
+      </c>
+      <c r="AK105">
+        <v>1.24</v>
+      </c>
+      <c r="AL105">
+        <v>1.35</v>
+      </c>
+      <c r="AM105">
+        <v>1.73</v>
+      </c>
+      <c r="AN105">
+        <v>2.5</v>
+      </c>
+      <c r="AO105">
+        <v>2</v>
+      </c>
+      <c r="AP105">
+        <v>2.6</v>
+      </c>
+      <c r="AQ105">
+        <v>1.6</v>
+      </c>
+      <c r="AR105">
+        <v>1.4</v>
+      </c>
+      <c r="AS105">
+        <v>1.3</v>
+      </c>
+      <c r="AT105">
+        <v>2.7</v>
+      </c>
+      <c r="AU105">
+        <v>6</v>
+      </c>
+      <c r="AV105">
+        <v>3</v>
+      </c>
+      <c r="AW105">
+        <v>13</v>
+      </c>
+      <c r="AX105">
+        <v>8</v>
+      </c>
+      <c r="AY105">
+        <v>24</v>
+      </c>
+      <c r="AZ105">
+        <v>14</v>
+      </c>
+      <c r="BA105">
+        <v>5</v>
+      </c>
+      <c r="BB105">
+        <v>4</v>
+      </c>
+      <c r="BC105">
+        <v>9</v>
+      </c>
+      <c r="BD105">
+        <v>1.58</v>
+      </c>
+      <c r="BE105">
+        <v>6.5</v>
+      </c>
+      <c r="BF105">
+        <v>2.65</v>
+      </c>
+      <c r="BG105">
+        <v>1.41</v>
+      </c>
+      <c r="BH105">
+        <v>2.65</v>
+      </c>
+      <c r="BI105">
+        <v>1.71</v>
+      </c>
+      <c r="BJ105">
+        <v>2</v>
+      </c>
+      <c r="BK105">
+        <v>2.1</v>
+      </c>
+      <c r="BL105">
+        <v>1.64</v>
+      </c>
+      <c r="BM105">
+        <v>2.7</v>
+      </c>
+      <c r="BN105">
+        <v>1.4</v>
+      </c>
+      <c r="BO105">
+        <v>3.55</v>
+      </c>
+      <c r="BP105">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7820421</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45716.92708333334</v>
+      </c>
+      <c r="F106">
+        <v>8</v>
+      </c>
+      <c r="G106" t="s">
+        <v>84</v>
+      </c>
+      <c r="H106" t="s">
+        <v>86</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106" t="s">
+        <v>100</v>
+      </c>
+      <c r="P106" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q106">
+        <v>2.75</v>
+      </c>
+      <c r="R106">
+        <v>1.91</v>
+      </c>
+      <c r="S106">
+        <v>5.5</v>
+      </c>
+      <c r="T106">
+        <v>1.57</v>
+      </c>
+      <c r="U106">
+        <v>2.25</v>
+      </c>
+      <c r="V106">
+        <v>3.75</v>
+      </c>
+      <c r="W106">
+        <v>1.25</v>
+      </c>
+      <c r="X106">
+        <v>13</v>
+      </c>
+      <c r="Y106">
+        <v>1.04</v>
+      </c>
+      <c r="Z106">
+        <v>1.91</v>
+      </c>
+      <c r="AA106">
+        <v>3.3</v>
+      </c>
+      <c r="AB106">
+        <v>4.33</v>
+      </c>
+      <c r="AC106">
+        <v>1.11</v>
+      </c>
+      <c r="AD106">
+        <v>6.6</v>
+      </c>
+      <c r="AE106">
+        <v>1.53</v>
+      </c>
+      <c r="AF106">
+        <v>2.42</v>
+      </c>
+      <c r="AG106">
+        <v>2.6</v>
+      </c>
+      <c r="AH106">
+        <v>1.48</v>
+      </c>
+      <c r="AI106">
+        <v>2.25</v>
+      </c>
+      <c r="AJ106">
+        <v>1.57</v>
+      </c>
+      <c r="AK106">
+        <v>1.26</v>
+      </c>
+      <c r="AL106">
+        <v>1.33</v>
+      </c>
+      <c r="AM106">
+        <v>1.73</v>
+      </c>
+      <c r="AN106">
+        <v>3</v>
+      </c>
+      <c r="AO106">
+        <v>2</v>
+      </c>
+      <c r="AP106">
+        <v>2.6</v>
+      </c>
+      <c r="AQ106">
+        <v>1.75</v>
+      </c>
+      <c r="AR106">
+        <v>2.07</v>
+      </c>
+      <c r="AS106">
+        <v>1.17</v>
+      </c>
+      <c r="AT106">
+        <v>3.24</v>
+      </c>
+      <c r="AU106">
+        <v>-1</v>
+      </c>
+      <c r="AV106">
+        <v>-1</v>
+      </c>
+      <c r="AW106">
+        <v>-1</v>
+      </c>
+      <c r="AX106">
+        <v>-1</v>
+      </c>
+      <c r="AY106">
+        <v>-1</v>
+      </c>
+      <c r="AZ106">
+        <v>-1</v>
+      </c>
+      <c r="BA106">
+        <v>-1</v>
+      </c>
+      <c r="BB106">
+        <v>-1</v>
+      </c>
+      <c r="BC106">
+        <v>-1</v>
+      </c>
+      <c r="BD106">
+        <v>1.38</v>
+      </c>
+      <c r="BE106">
+        <v>7</v>
+      </c>
+      <c r="BF106">
+        <v>3.4</v>
+      </c>
+      <c r="BG106">
+        <v>1.5</v>
+      </c>
+      <c r="BH106">
+        <v>2.38</v>
+      </c>
+      <c r="BI106">
+        <v>1.83</v>
+      </c>
+      <c r="BJ106">
+        <v>1.85</v>
+      </c>
+      <c r="BK106">
+        <v>2.32</v>
+      </c>
+      <c r="BL106">
+        <v>1.52</v>
+      </c>
+      <c r="BM106">
+        <v>3.05</v>
+      </c>
+      <c r="BN106">
+        <v>1.32</v>
+      </c>
+      <c r="BO106">
+        <v>4</v>
+      </c>
+      <c r="BP106">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7820422</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45716.92708333334</v>
+      </c>
+      <c r="F107">
+        <v>8</v>
+      </c>
+      <c r="G107" t="s">
+        <v>78</v>
+      </c>
+      <c r="H107" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>3</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>4</v>
+      </c>
+      <c r="O107" t="s">
+        <v>167</v>
+      </c>
+      <c r="P107" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q107">
+        <v>3.5</v>
+      </c>
+      <c r="R107">
+        <v>1.83</v>
+      </c>
+      <c r="S107">
+        <v>4</v>
+      </c>
+      <c r="T107">
+        <v>1.62</v>
+      </c>
+      <c r="U107">
+        <v>2.2</v>
+      </c>
+      <c r="V107">
+        <v>4</v>
+      </c>
+      <c r="W107">
+        <v>1.22</v>
+      </c>
+      <c r="X107">
+        <v>15</v>
+      </c>
+      <c r="Y107">
+        <v>1.03</v>
+      </c>
+      <c r="Z107">
+        <v>2.7</v>
+      </c>
+      <c r="AA107">
+        <v>2.75</v>
+      </c>
+      <c r="AB107">
+        <v>3.1</v>
+      </c>
+      <c r="AC107">
+        <v>1.14</v>
+      </c>
+      <c r="AD107">
+        <v>5.6</v>
+      </c>
+      <c r="AE107">
+        <v>1.57</v>
+      </c>
+      <c r="AF107">
+        <v>2.25</v>
+      </c>
+      <c r="AG107">
+        <v>2.88</v>
+      </c>
+      <c r="AH107">
+        <v>1.4</v>
+      </c>
+      <c r="AI107">
+        <v>2.2</v>
+      </c>
+      <c r="AJ107">
+        <v>1.62</v>
+      </c>
+      <c r="AK107">
+        <v>1.38</v>
+      </c>
+      <c r="AL107">
+        <v>1.39</v>
+      </c>
+      <c r="AM107">
+        <v>1.47</v>
+      </c>
+      <c r="AN107">
+        <v>0.25</v>
+      </c>
+      <c r="AO107">
+        <v>0.33</v>
+      </c>
+      <c r="AP107">
+        <v>0.8</v>
+      </c>
+      <c r="AQ107">
+        <v>0.25</v>
+      </c>
+      <c r="AR107">
+        <v>1.43</v>
+      </c>
+      <c r="AS107">
+        <v>1.41</v>
+      </c>
+      <c r="AT107">
+        <v>2.84</v>
+      </c>
+      <c r="AU107">
+        <v>-1</v>
+      </c>
+      <c r="AV107">
+        <v>-1</v>
+      </c>
+      <c r="AW107">
+        <v>-1</v>
+      </c>
+      <c r="AX107">
+        <v>-1</v>
+      </c>
+      <c r="AY107">
+        <v>-1</v>
+      </c>
+      <c r="AZ107">
+        <v>-1</v>
+      </c>
+      <c r="BA107">
+        <v>-1</v>
+      </c>
+      <c r="BB107">
+        <v>-1</v>
+      </c>
+      <c r="BC107">
+        <v>-1</v>
+      </c>
+      <c r="BD107">
+        <v>1.8</v>
+      </c>
+      <c r="BE107">
+        <v>6.4</v>
+      </c>
+      <c r="BF107">
+        <v>2.23</v>
+      </c>
+      <c r="BG107">
+        <v>1.54</v>
+      </c>
+      <c r="BH107">
+        <v>2.3</v>
+      </c>
+      <c r="BI107">
+        <v>1.9</v>
+      </c>
+      <c r="BJ107">
+        <v>1.79</v>
+      </c>
+      <c r="BK107">
+        <v>2.4</v>
+      </c>
+      <c r="BL107">
+        <v>1.49</v>
+      </c>
+      <c r="BM107">
+        <v>3.15</v>
+      </c>
+      <c r="BN107">
+        <v>1.29</v>
+      </c>
+      <c r="BO107">
+        <v>4.3</v>
+      </c>
+      <c r="BP107">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -22763,31 +22763,31 @@
         <v>3.24</v>
       </c>
       <c r="AU106">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV106">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW106">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AX106">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY106">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AZ106">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BA106">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BB106">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC106">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD106">
         <v>1.38</v>
@@ -22969,31 +22969,31 @@
         <v>2.84</v>
       </c>
       <c r="AU107">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV107">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW107">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX107">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY107">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ107">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BA107">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB107">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC107">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD107">
         <v>1.8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="207">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -520,6 +520,9 @@
     <t>['53', '55', '90+2']</t>
   </si>
   <si>
+    <t>['3', '7']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -629,6 +632,9 @@
   </si>
   <si>
     <t>['56', '69']</t>
+  </si>
+  <si>
+    <t>['23', '37']</t>
   </si>
 </sst>
 </file>
@@ -990,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP107"/>
+  <dimension ref="A1:BP108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1246,7 +1252,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1658,7 +1664,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2070,7 +2076,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2276,7 +2282,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2563,7 +2569,7 @@
         <v>3</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2894,7 +2900,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3306,7 +3312,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -4748,7 +4754,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5366,7 +5372,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5572,7 +5578,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5778,7 +5784,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6190,7 +6196,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6602,7 +6608,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6680,7 +6686,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ28">
         <v>1.75</v>
@@ -7919,7 +7925,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AR34">
         <v>1.61</v>
@@ -8250,7 +8256,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -9074,7 +9080,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9898,7 +9904,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10104,7 +10110,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10310,7 +10316,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10388,7 +10394,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ46">
         <v>1.67</v>
@@ -10516,7 +10522,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10722,7 +10728,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11340,7 +11346,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11958,7 +11964,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12576,7 +12582,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13400,7 +13406,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14636,7 +14642,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14842,7 +14848,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15666,7 +15672,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15872,7 +15878,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16159,7 +16165,7 @@
         <v>1</v>
       </c>
       <c r="AQ74">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AR74">
         <v>1.59</v>
@@ -16490,7 +16496,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16696,7 +16702,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16902,7 +16908,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -16980,7 +16986,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ78">
         <v>1</v>
@@ -17314,7 +17320,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17520,7 +17526,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17726,7 +17732,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18344,7 +18350,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18756,7 +18762,7 @@
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18962,7 +18968,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19168,7 +19174,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19374,7 +19380,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19786,7 +19792,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20610,7 +20616,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20816,7 +20822,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21103,7 +21109,7 @@
         <v>3</v>
       </c>
       <c r="AQ98">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AR98">
         <v>1.32</v>
@@ -21434,7 +21440,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23033,6 +23039,212 @@
       </c>
       <c r="BP107">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7820423</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45717.70833333334</v>
+      </c>
+      <c r="F108">
+        <v>8</v>
+      </c>
+      <c r="G108" t="s">
+        <v>96</v>
+      </c>
+      <c r="H108" t="s">
+        <v>88</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+      <c r="J108">
+        <v>2</v>
+      </c>
+      <c r="K108">
+        <v>4</v>
+      </c>
+      <c r="L108">
+        <v>2</v>
+      </c>
+      <c r="M108">
+        <v>2</v>
+      </c>
+      <c r="N108">
+        <v>4</v>
+      </c>
+      <c r="O108" t="s">
+        <v>168</v>
+      </c>
+      <c r="P108" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q108">
+        <v>3.4</v>
+      </c>
+      <c r="R108">
+        <v>1.91</v>
+      </c>
+      <c r="S108">
+        <v>4</v>
+      </c>
+      <c r="T108">
+        <v>1.62</v>
+      </c>
+      <c r="U108">
+        <v>2.2</v>
+      </c>
+      <c r="V108">
+        <v>4</v>
+      </c>
+      <c r="W108">
+        <v>1.22</v>
+      </c>
+      <c r="X108">
+        <v>13</v>
+      </c>
+      <c r="Y108">
+        <v>1.04</v>
+      </c>
+      <c r="Z108">
+        <v>2.5</v>
+      </c>
+      <c r="AA108">
+        <v>3</v>
+      </c>
+      <c r="AB108">
+        <v>3.1</v>
+      </c>
+      <c r="AC108">
+        <v>1.06</v>
+      </c>
+      <c r="AD108">
+        <v>6.55</v>
+      </c>
+      <c r="AE108">
+        <v>1.54</v>
+      </c>
+      <c r="AF108">
+        <v>2.47</v>
+      </c>
+      <c r="AG108">
+        <v>2.7</v>
+      </c>
+      <c r="AH108">
+        <v>1.44</v>
+      </c>
+      <c r="AI108">
+        <v>2.1</v>
+      </c>
+      <c r="AJ108">
+        <v>1.67</v>
+      </c>
+      <c r="AK108">
+        <v>1.37</v>
+      </c>
+      <c r="AL108">
+        <v>1.37</v>
+      </c>
+      <c r="AM108">
+        <v>1.5</v>
+      </c>
+      <c r="AN108">
+        <v>0.33</v>
+      </c>
+      <c r="AO108">
+        <v>0</v>
+      </c>
+      <c r="AP108">
+        <v>0.5</v>
+      </c>
+      <c r="AQ108">
+        <v>0.2</v>
+      </c>
+      <c r="AR108">
+        <v>2.14</v>
+      </c>
+      <c r="AS108">
+        <v>1.17</v>
+      </c>
+      <c r="AT108">
+        <v>3.31</v>
+      </c>
+      <c r="AU108">
+        <v>13</v>
+      </c>
+      <c r="AV108">
+        <v>4</v>
+      </c>
+      <c r="AW108">
+        <v>6</v>
+      </c>
+      <c r="AX108">
+        <v>7</v>
+      </c>
+      <c r="AY108">
+        <v>21</v>
+      </c>
+      <c r="AZ108">
+        <v>14</v>
+      </c>
+      <c r="BA108">
+        <v>6</v>
+      </c>
+      <c r="BB108">
+        <v>0</v>
+      </c>
+      <c r="BC108">
+        <v>6</v>
+      </c>
+      <c r="BD108">
+        <v>1.64</v>
+      </c>
+      <c r="BE108">
+        <v>6.75</v>
+      </c>
+      <c r="BF108">
+        <v>2.5</v>
+      </c>
+      <c r="BG108">
+        <v>1.35</v>
+      </c>
+      <c r="BH108">
+        <v>2.88</v>
+      </c>
+      <c r="BI108">
+        <v>1.6</v>
+      </c>
+      <c r="BJ108">
+        <v>2.17</v>
+      </c>
+      <c r="BK108">
+        <v>1.97</v>
+      </c>
+      <c r="BL108">
+        <v>1.73</v>
+      </c>
+      <c r="BM108">
+        <v>2.48</v>
+      </c>
+      <c r="BN108">
+        <v>1.47</v>
+      </c>
+      <c r="BO108">
+        <v>3.15</v>
+      </c>
+      <c r="BP108">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="208">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -636,6 +636,9 @@
   <si>
     <t>['23', '37']</t>
   </si>
+  <si>
+    <t>['9', '90+4']</t>
+  </si>
 </sst>
 </file>
 
@@ -996,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP108"/>
+  <dimension ref="A1:BP109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -6071,7 +6074,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6480,7 +6483,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AQ27">
         <v>0.25</v>
@@ -11427,7 +11430,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR51">
         <v>1.47</v>
@@ -12248,7 +12251,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AQ55">
         <v>1.33</v>
@@ -16989,7 +16992,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ78">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR78">
         <v>2.48</v>
@@ -18016,7 +18019,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -23245,6 +23248,212 @@
       </c>
       <c r="BP108">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7820424</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45717.80208333334</v>
+      </c>
+      <c r="F109">
+        <v>8</v>
+      </c>
+      <c r="G109" t="s">
+        <v>95</v>
+      </c>
+      <c r="H109" t="s">
+        <v>80</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>2</v>
+      </c>
+      <c r="N109">
+        <v>2</v>
+      </c>
+      <c r="O109" t="s">
+        <v>100</v>
+      </c>
+      <c r="P109" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q109">
+        <v>2.38</v>
+      </c>
+      <c r="R109">
+        <v>2.1</v>
+      </c>
+      <c r="S109">
+        <v>5.5</v>
+      </c>
+      <c r="T109">
+        <v>1.44</v>
+      </c>
+      <c r="U109">
+        <v>2.63</v>
+      </c>
+      <c r="V109">
+        <v>3.25</v>
+      </c>
+      <c r="W109">
+        <v>1.33</v>
+      </c>
+      <c r="X109">
+        <v>9</v>
+      </c>
+      <c r="Y109">
+        <v>1.07</v>
+      </c>
+      <c r="Z109">
+        <v>1.7</v>
+      </c>
+      <c r="AA109">
+        <v>3.6</v>
+      </c>
+      <c r="AB109">
+        <v>5.5</v>
+      </c>
+      <c r="AC109">
+        <v>1.07</v>
+      </c>
+      <c r="AD109">
+        <v>9</v>
+      </c>
+      <c r="AE109">
+        <v>1.36</v>
+      </c>
+      <c r="AF109">
+        <v>3.1</v>
+      </c>
+      <c r="AG109">
+        <v>2.05</v>
+      </c>
+      <c r="AH109">
+        <v>1.75</v>
+      </c>
+      <c r="AI109">
+        <v>1.95</v>
+      </c>
+      <c r="AJ109">
+        <v>1.8</v>
+      </c>
+      <c r="AK109">
+        <v>1.18</v>
+      </c>
+      <c r="AL109">
+        <v>1.28</v>
+      </c>
+      <c r="AM109">
+        <v>2.05</v>
+      </c>
+      <c r="AN109">
+        <v>3</v>
+      </c>
+      <c r="AO109">
+        <v>1</v>
+      </c>
+      <c r="AP109">
+        <v>2.25</v>
+      </c>
+      <c r="AQ109">
+        <v>1.5</v>
+      </c>
+      <c r="AR109">
+        <v>1.66</v>
+      </c>
+      <c r="AS109">
+        <v>1.06</v>
+      </c>
+      <c r="AT109">
+        <v>2.72</v>
+      </c>
+      <c r="AU109">
+        <v>4</v>
+      </c>
+      <c r="AV109">
+        <v>5</v>
+      </c>
+      <c r="AW109">
+        <v>9</v>
+      </c>
+      <c r="AX109">
+        <v>4</v>
+      </c>
+      <c r="AY109">
+        <v>14</v>
+      </c>
+      <c r="AZ109">
+        <v>11</v>
+      </c>
+      <c r="BA109">
+        <v>7</v>
+      </c>
+      <c r="BB109">
+        <v>2</v>
+      </c>
+      <c r="BC109">
+        <v>9</v>
+      </c>
+      <c r="BD109">
+        <v>1.43</v>
+      </c>
+      <c r="BE109">
+        <v>7</v>
+      </c>
+      <c r="BF109">
+        <v>3.15</v>
+      </c>
+      <c r="BG109">
+        <v>1.32</v>
+      </c>
+      <c r="BH109">
+        <v>3.05</v>
+      </c>
+      <c r="BI109">
+        <v>1.55</v>
+      </c>
+      <c r="BJ109">
+        <v>2.28</v>
+      </c>
+      <c r="BK109">
+        <v>1.89</v>
+      </c>
+      <c r="BL109">
+        <v>1.8</v>
+      </c>
+      <c r="BM109">
+        <v>2.38</v>
+      </c>
+      <c r="BN109">
+        <v>1.5</v>
+      </c>
+      <c r="BO109">
+        <v>3.05</v>
+      </c>
+      <c r="BP109">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="210">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -523,6 +523,9 @@
     <t>['3', '7']</t>
   </si>
   <si>
+    <t>['44']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -638,6 +641,9 @@
   </si>
   <si>
     <t>['9', '90+4']</t>
+  </si>
+  <si>
+    <t>['36', '66']</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1255,7 +1261,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1667,7 +1673,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2079,7 +2085,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2285,7 +2291,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2903,7 +2909,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3315,7 +3321,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -3602,7 +3608,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4757,7 +4763,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5375,7 +5381,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5581,7 +5587,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5659,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ23">
         <v>1.33</v>
@@ -5787,7 +5793,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6199,7 +6205,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6277,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ26">
         <v>1.33</v>
@@ -6611,7 +6617,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7104,7 +7110,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -8259,7 +8265,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8958,7 +8964,7 @@
         <v>3</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR39">
         <v>1.95</v>
@@ -9083,7 +9089,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9907,7 +9913,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10113,7 +10119,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10319,7 +10325,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10525,7 +10531,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10731,7 +10737,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11224,7 +11230,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR50">
         <v>2.5</v>
@@ -11349,7 +11355,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11633,7 +11639,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ52">
         <v>2.33</v>
@@ -11967,7 +11973,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12585,7 +12591,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13281,7 +13287,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13409,7 +13415,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14645,7 +14651,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14851,7 +14857,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15550,7 +15556,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR71">
         <v>1.67</v>
@@ -15675,7 +15681,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15881,7 +15887,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16371,7 +16377,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ75">
         <v>0.25</v>
@@ -16499,7 +16505,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16705,7 +16711,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16911,7 +16917,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17323,7 +17329,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17404,7 +17410,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ80">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
         <v>1.76</v>
@@ -17529,7 +17535,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17735,7 +17741,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18353,7 +18359,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18431,7 +18437,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ85">
         <v>1</v>
@@ -18765,7 +18771,7 @@
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18971,7 +18977,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19177,7 +19183,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19383,7 +19389,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19795,7 +19801,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20619,7 +20625,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20825,7 +20831,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21443,7 +21449,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21524,7 +21530,7 @@
         <v>1</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR100">
         <v>1.82</v>
@@ -23091,7 +23097,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23297,7 +23303,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23454,6 +23460,418 @@
       </c>
       <c r="BP109">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7820425</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45717.89583333334</v>
+      </c>
+      <c r="F110">
+        <v>8</v>
+      </c>
+      <c r="G110" t="s">
+        <v>94</v>
+      </c>
+      <c r="H110" t="s">
+        <v>92</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>105</v>
+      </c>
+      <c r="P110" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q110">
+        <v>3.25</v>
+      </c>
+      <c r="R110">
+        <v>1.83</v>
+      </c>
+      <c r="S110">
+        <v>4.33</v>
+      </c>
+      <c r="T110">
+        <v>1.62</v>
+      </c>
+      <c r="U110">
+        <v>2.2</v>
+      </c>
+      <c r="V110">
+        <v>4</v>
+      </c>
+      <c r="W110">
+        <v>1.22</v>
+      </c>
+      <c r="X110">
+        <v>15</v>
+      </c>
+      <c r="Y110">
+        <v>1.03</v>
+      </c>
+      <c r="Z110">
+        <v>2.38</v>
+      </c>
+      <c r="AA110">
+        <v>3</v>
+      </c>
+      <c r="AB110">
+        <v>3.3</v>
+      </c>
+      <c r="AC110">
+        <v>1.13</v>
+      </c>
+      <c r="AD110">
+        <v>6</v>
+      </c>
+      <c r="AE110">
+        <v>1.57</v>
+      </c>
+      <c r="AF110">
+        <v>2.3</v>
+      </c>
+      <c r="AG110">
+        <v>2.88</v>
+      </c>
+      <c r="AH110">
+        <v>1.4</v>
+      </c>
+      <c r="AI110">
+        <v>2.25</v>
+      </c>
+      <c r="AJ110">
+        <v>1.57</v>
+      </c>
+      <c r="AK110">
+        <v>1.33</v>
+      </c>
+      <c r="AL110">
+        <v>1.37</v>
+      </c>
+      <c r="AM110">
+        <v>1.55</v>
+      </c>
+      <c r="AN110">
+        <v>0.67</v>
+      </c>
+      <c r="AO110">
+        <v>1</v>
+      </c>
+      <c r="AP110">
+        <v>1.25</v>
+      </c>
+      <c r="AQ110">
+        <v>0.8</v>
+      </c>
+      <c r="AR110">
+        <v>1.45</v>
+      </c>
+      <c r="AS110">
+        <v>1.14</v>
+      </c>
+      <c r="AT110">
+        <v>2.59</v>
+      </c>
+      <c r="AU110">
+        <v>4</v>
+      </c>
+      <c r="AV110">
+        <v>0</v>
+      </c>
+      <c r="AW110">
+        <v>13</v>
+      </c>
+      <c r="AX110">
+        <v>6</v>
+      </c>
+      <c r="AY110">
+        <v>25</v>
+      </c>
+      <c r="AZ110">
+        <v>6</v>
+      </c>
+      <c r="BA110">
+        <v>8</v>
+      </c>
+      <c r="BB110">
+        <v>1</v>
+      </c>
+      <c r="BC110">
+        <v>9</v>
+      </c>
+      <c r="BD110">
+        <v>1.67</v>
+      </c>
+      <c r="BE110">
+        <v>6.5</v>
+      </c>
+      <c r="BF110">
+        <v>2.48</v>
+      </c>
+      <c r="BG110">
+        <v>1.38</v>
+      </c>
+      <c r="BH110">
+        <v>2.7</v>
+      </c>
+      <c r="BI110">
+        <v>1.65</v>
+      </c>
+      <c r="BJ110">
+        <v>2.08</v>
+      </c>
+      <c r="BK110">
+        <v>2.06</v>
+      </c>
+      <c r="BL110">
+        <v>1.66</v>
+      </c>
+      <c r="BM110">
+        <v>2.65</v>
+      </c>
+      <c r="BN110">
+        <v>1.41</v>
+      </c>
+      <c r="BO110">
+        <v>3.4</v>
+      </c>
+      <c r="BP110">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7820426</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45717.89583333334</v>
+      </c>
+      <c r="F111">
+        <v>8</v>
+      </c>
+      <c r="G111" t="s">
+        <v>91</v>
+      </c>
+      <c r="H111" t="s">
+        <v>71</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>2</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="M111">
+        <v>2</v>
+      </c>
+      <c r="N111">
+        <v>3</v>
+      </c>
+      <c r="O111" t="s">
+        <v>169</v>
+      </c>
+      <c r="P111" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q111">
+        <v>2.38</v>
+      </c>
+      <c r="R111">
+        <v>2.05</v>
+      </c>
+      <c r="S111">
+        <v>6</v>
+      </c>
+      <c r="T111">
+        <v>1.5</v>
+      </c>
+      <c r="U111">
+        <v>2.5</v>
+      </c>
+      <c r="V111">
+        <v>3.5</v>
+      </c>
+      <c r="W111">
+        <v>1.29</v>
+      </c>
+      <c r="X111">
+        <v>11</v>
+      </c>
+      <c r="Y111">
+        <v>1.05</v>
+      </c>
+      <c r="Z111">
+        <v>1.7</v>
+      </c>
+      <c r="AA111">
+        <v>3.5</v>
+      </c>
+      <c r="AB111">
+        <v>5.5</v>
+      </c>
+      <c r="AC111">
+        <v>1.09</v>
+      </c>
+      <c r="AD111">
+        <v>7.6</v>
+      </c>
+      <c r="AE111">
+        <v>1.43</v>
+      </c>
+      <c r="AF111">
+        <v>2.7</v>
+      </c>
+      <c r="AG111">
+        <v>2.35</v>
+      </c>
+      <c r="AH111">
+        <v>1.57</v>
+      </c>
+      <c r="AI111">
+        <v>2.2</v>
+      </c>
+      <c r="AJ111">
+        <v>1.62</v>
+      </c>
+      <c r="AK111">
+        <v>1.15</v>
+      </c>
+      <c r="AL111">
+        <v>1.29</v>
+      </c>
+      <c r="AM111">
+        <v>2.1</v>
+      </c>
+      <c r="AN111">
+        <v>0.33</v>
+      </c>
+      <c r="AO111">
+        <v>1</v>
+      </c>
+      <c r="AP111">
+        <v>0.25</v>
+      </c>
+      <c r="AQ111">
+        <v>1.5</v>
+      </c>
+      <c r="AR111">
+        <v>2.19</v>
+      </c>
+      <c r="AS111">
+        <v>1.6</v>
+      </c>
+      <c r="AT111">
+        <v>3.79</v>
+      </c>
+      <c r="AU111">
+        <v>7</v>
+      </c>
+      <c r="AV111">
+        <v>5</v>
+      </c>
+      <c r="AW111">
+        <v>15</v>
+      </c>
+      <c r="AX111">
+        <v>2</v>
+      </c>
+      <c r="AY111">
+        <v>28</v>
+      </c>
+      <c r="AZ111">
+        <v>8</v>
+      </c>
+      <c r="BA111">
+        <v>8</v>
+      </c>
+      <c r="BB111">
+        <v>1</v>
+      </c>
+      <c r="BC111">
+        <v>9</v>
+      </c>
+      <c r="BD111">
+        <v>1.6</v>
+      </c>
+      <c r="BE111">
+        <v>6.4</v>
+      </c>
+      <c r="BF111">
+        <v>2.6</v>
+      </c>
+      <c r="BG111">
+        <v>1.44</v>
+      </c>
+      <c r="BH111">
+        <v>2.55</v>
+      </c>
+      <c r="BI111">
+        <v>1.75</v>
+      </c>
+      <c r="BJ111">
+        <v>1.95</v>
+      </c>
+      <c r="BK111">
+        <v>2.2</v>
+      </c>
+      <c r="BL111">
+        <v>1.58</v>
+      </c>
+      <c r="BM111">
+        <v>2.9</v>
+      </c>
+      <c r="BN111">
+        <v>1.35</v>
+      </c>
+      <c r="BO111">
+        <v>3.9</v>
+      </c>
+      <c r="BP111">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="213">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,12 @@
     <t>['44']</t>
   </si>
   <si>
+    <t>['46']</t>
+  </si>
+  <si>
+    <t>['55', '74']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -644,6 +650,9 @@
   </si>
   <si>
     <t>['36', '66']</t>
+  </si>
+  <si>
+    <t>['71']</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP111"/>
+  <dimension ref="A1:BP113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1261,7 +1270,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1673,7 +1682,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2085,7 +2094,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2291,7 +2300,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2909,7 +2918,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3321,7 +3330,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -4763,7 +4772,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5253,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ21">
         <v>1.67</v>
@@ -5381,7 +5390,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5587,7 +5596,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5793,7 +5802,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6205,7 +6214,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6492,7 +6501,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ27">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -6617,7 +6626,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7107,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ30">
         <v>1.5</v>
@@ -8265,7 +8274,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -9089,7 +9098,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9785,7 +9794,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -9913,7 +9922,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10119,7 +10128,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10325,7 +10334,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10531,7 +10540,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10737,7 +10746,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11355,7 +11364,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11433,7 +11442,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ51">
         <v>1.5</v>
@@ -11973,7 +11982,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12591,7 +12600,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12878,7 +12887,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR58">
         <v>0.73</v>
@@ -13415,7 +13424,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14651,7 +14660,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14857,7 +14866,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -14935,7 +14944,7 @@
         <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ68">
         <v>0.67</v>
@@ -15681,7 +15690,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15887,7 +15896,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16380,7 +16389,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ75">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR75">
         <v>1.66</v>
@@ -16505,7 +16514,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16711,7 +16720,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16917,7 +16926,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17329,7 +17338,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17407,7 +17416,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ80">
         <v>1.5</v>
@@ -17535,7 +17544,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17741,7 +17750,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18359,7 +18368,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18771,7 +18780,7 @@
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18977,7 +18986,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19183,7 +19192,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19389,7 +19398,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19801,7 +19810,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20500,7 +20509,7 @@
         <v>3</v>
       </c>
       <c r="AQ95">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR95">
         <v>1.94</v>
@@ -20625,7 +20634,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20831,7 +20840,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21449,7 +21458,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22145,7 +22154,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ103">
         <v>1.75</v>
@@ -23097,7 +23106,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23303,7 +23312,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23715,7 +23724,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -23872,6 +23881,418 @@
       </c>
       <c r="BP111">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7820427</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45718.70833333334</v>
+      </c>
+      <c r="F112">
+        <v>8</v>
+      </c>
+      <c r="G112" t="s">
+        <v>89</v>
+      </c>
+      <c r="H112" t="s">
+        <v>74</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="M112">
+        <v>1</v>
+      </c>
+      <c r="N112">
+        <v>2</v>
+      </c>
+      <c r="O112" t="s">
+        <v>170</v>
+      </c>
+      <c r="P112" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q112">
+        <v>3.6</v>
+      </c>
+      <c r="R112">
+        <v>1.91</v>
+      </c>
+      <c r="S112">
+        <v>3.6</v>
+      </c>
+      <c r="T112">
+        <v>1.62</v>
+      </c>
+      <c r="U112">
+        <v>2.2</v>
+      </c>
+      <c r="V112">
+        <v>4</v>
+      </c>
+      <c r="W112">
+        <v>1.22</v>
+      </c>
+      <c r="X112">
+        <v>13</v>
+      </c>
+      <c r="Y112">
+        <v>1.04</v>
+      </c>
+      <c r="Z112">
+        <v>2.75</v>
+      </c>
+      <c r="AA112">
+        <v>3</v>
+      </c>
+      <c r="AB112">
+        <v>2.8</v>
+      </c>
+      <c r="AC112">
+        <v>1.12</v>
+      </c>
+      <c r="AD112">
+        <v>6.2</v>
+      </c>
+      <c r="AE112">
+        <v>1.52</v>
+      </c>
+      <c r="AF112">
+        <v>2.35</v>
+      </c>
+      <c r="AG112">
+        <v>2.7</v>
+      </c>
+      <c r="AH112">
+        <v>1.44</v>
+      </c>
+      <c r="AI112">
+        <v>2.1</v>
+      </c>
+      <c r="AJ112">
+        <v>1.67</v>
+      </c>
+      <c r="AK112">
+        <v>1.36</v>
+      </c>
+      <c r="AL112">
+        <v>1.36</v>
+      </c>
+      <c r="AM112">
+        <v>1.52</v>
+      </c>
+      <c r="AN112">
+        <v>0.67</v>
+      </c>
+      <c r="AO112">
+        <v>1</v>
+      </c>
+      <c r="AP112">
+        <v>0.75</v>
+      </c>
+      <c r="AQ112">
+        <v>1</v>
+      </c>
+      <c r="AR112">
+        <v>1.94</v>
+      </c>
+      <c r="AS112">
+        <v>1.12</v>
+      </c>
+      <c r="AT112">
+        <v>3.06</v>
+      </c>
+      <c r="AU112">
+        <v>-1</v>
+      </c>
+      <c r="AV112">
+        <v>-1</v>
+      </c>
+      <c r="AW112">
+        <v>-1</v>
+      </c>
+      <c r="AX112">
+        <v>-1</v>
+      </c>
+      <c r="AY112">
+        <v>-1</v>
+      </c>
+      <c r="AZ112">
+        <v>-1</v>
+      </c>
+      <c r="BA112">
+        <v>-1</v>
+      </c>
+      <c r="BB112">
+        <v>-1</v>
+      </c>
+      <c r="BC112">
+        <v>-1</v>
+      </c>
+      <c r="BD112">
+        <v>1.74</v>
+      </c>
+      <c r="BE112">
+        <v>6.4</v>
+      </c>
+      <c r="BF112">
+        <v>2.32</v>
+      </c>
+      <c r="BG112">
+        <v>1.41</v>
+      </c>
+      <c r="BH112">
+        <v>2.65</v>
+      </c>
+      <c r="BI112">
+        <v>1.7</v>
+      </c>
+      <c r="BJ112">
+        <v>2</v>
+      </c>
+      <c r="BK112">
+        <v>2.12</v>
+      </c>
+      <c r="BL112">
+        <v>1.63</v>
+      </c>
+      <c r="BM112">
+        <v>2.7</v>
+      </c>
+      <c r="BN112">
+        <v>1.38</v>
+      </c>
+      <c r="BO112">
+        <v>3.65</v>
+      </c>
+      <c r="BP112">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7820428</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45718.70833333334</v>
+      </c>
+      <c r="F113">
+        <v>8</v>
+      </c>
+      <c r="G113" t="s">
+        <v>98</v>
+      </c>
+      <c r="H113" t="s">
+        <v>81</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>2</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>2</v>
+      </c>
+      <c r="O113" t="s">
+        <v>171</v>
+      </c>
+      <c r="P113" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q113">
+        <v>2.75</v>
+      </c>
+      <c r="R113">
+        <v>1.91</v>
+      </c>
+      <c r="S113">
+        <v>5.5</v>
+      </c>
+      <c r="T113">
+        <v>1.62</v>
+      </c>
+      <c r="U113">
+        <v>2.2</v>
+      </c>
+      <c r="V113">
+        <v>4</v>
+      </c>
+      <c r="W113">
+        <v>1.22</v>
+      </c>
+      <c r="X113">
+        <v>13</v>
+      </c>
+      <c r="Y113">
+        <v>1.04</v>
+      </c>
+      <c r="Z113">
+        <v>1.91</v>
+      </c>
+      <c r="AA113">
+        <v>3.25</v>
+      </c>
+      <c r="AB113">
+        <v>4.5</v>
+      </c>
+      <c r="AC113">
+        <v>1.12</v>
+      </c>
+      <c r="AD113">
+        <v>6.4</v>
+      </c>
+      <c r="AE113">
+        <v>1.51</v>
+      </c>
+      <c r="AF113">
+        <v>2.37</v>
+      </c>
+      <c r="AG113">
+        <v>2.7</v>
+      </c>
+      <c r="AH113">
+        <v>1.44</v>
+      </c>
+      <c r="AI113">
+        <v>2.25</v>
+      </c>
+      <c r="AJ113">
+        <v>1.57</v>
+      </c>
+      <c r="AK113">
+        <v>1.21</v>
+      </c>
+      <c r="AL113">
+        <v>1.34</v>
+      </c>
+      <c r="AM113">
+        <v>1.83</v>
+      </c>
+      <c r="AN113">
+        <v>2</v>
+      </c>
+      <c r="AO113">
+        <v>0.25</v>
+      </c>
+      <c r="AP113">
+        <v>2.2</v>
+      </c>
+      <c r="AQ113">
+        <v>0.2</v>
+      </c>
+      <c r="AR113">
+        <v>1.81</v>
+      </c>
+      <c r="AS113">
+        <v>1.06</v>
+      </c>
+      <c r="AT113">
+        <v>2.87</v>
+      </c>
+      <c r="AU113">
+        <v>5</v>
+      </c>
+      <c r="AV113">
+        <v>4</v>
+      </c>
+      <c r="AW113">
+        <v>11</v>
+      </c>
+      <c r="AX113">
+        <v>2</v>
+      </c>
+      <c r="AY113">
+        <v>20</v>
+      </c>
+      <c r="AZ113">
+        <v>7</v>
+      </c>
+      <c r="BA113">
+        <v>7</v>
+      </c>
+      <c r="BB113">
+        <v>4</v>
+      </c>
+      <c r="BC113">
+        <v>11</v>
+      </c>
+      <c r="BD113">
+        <v>1.43</v>
+      </c>
+      <c r="BE113">
+        <v>6.75</v>
+      </c>
+      <c r="BF113">
+        <v>3.15</v>
+      </c>
+      <c r="BG113">
+        <v>1.38</v>
+      </c>
+      <c r="BH113">
+        <v>2.75</v>
+      </c>
+      <c r="BI113">
+        <v>1.65</v>
+      </c>
+      <c r="BJ113">
+        <v>2.08</v>
+      </c>
+      <c r="BK113">
+        <v>2.04</v>
+      </c>
+      <c r="BL113">
+        <v>1.67</v>
+      </c>
+      <c r="BM113">
+        <v>2.6</v>
+      </c>
+      <c r="BN113">
+        <v>1.43</v>
+      </c>
+      <c r="BO113">
+        <v>3.4</v>
+      </c>
+      <c r="BP113">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -654,6 +654,9 @@
   <si>
     <t>['71']</t>
   </si>
+  <si>
+    <t>['22', '80']</t>
+  </si>
 </sst>
 </file>
 
@@ -1014,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP113"/>
+  <dimension ref="A1:BP114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2793,7 +2796,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ9">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -5468,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -8355,7 +8358,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ36">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR36">
         <v>1</v>
@@ -11854,7 +11857,7 @@
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ53">
         <v>1.75</v>
@@ -14947,7 +14950,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ68">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR68">
         <v>1.54</v>
@@ -19270,7 +19273,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ89">
         <v>1.33</v>
@@ -24023,31 +24026,31 @@
         <v>3.06</v>
       </c>
       <c r="AU112">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV112">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW112">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX112">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY112">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AZ112">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BA112">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB112">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC112">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD112">
         <v>1.74</v>
@@ -24293,6 +24296,212 @@
       </c>
       <c r="BP113">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7820429</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45718.80208333334</v>
+      </c>
+      <c r="F114">
+        <v>8</v>
+      </c>
+      <c r="G114" t="s">
+        <v>90</v>
+      </c>
+      <c r="H114" t="s">
+        <v>93</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>2</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>100</v>
+      </c>
+      <c r="P114" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q114">
+        <v>3.25</v>
+      </c>
+      <c r="R114">
+        <v>1.83</v>
+      </c>
+      <c r="S114">
+        <v>4.33</v>
+      </c>
+      <c r="T114">
+        <v>1.67</v>
+      </c>
+      <c r="U114">
+        <v>2.1</v>
+      </c>
+      <c r="V114">
+        <v>4.33</v>
+      </c>
+      <c r="W114">
+        <v>1.2</v>
+      </c>
+      <c r="X114">
+        <v>15</v>
+      </c>
+      <c r="Y114">
+        <v>1.03</v>
+      </c>
+      <c r="Z114">
+        <v>2.35</v>
+      </c>
+      <c r="AA114">
+        <v>2.7</v>
+      </c>
+      <c r="AB114">
+        <v>3.8</v>
+      </c>
+      <c r="AC114">
+        <v>1.14</v>
+      </c>
+      <c r="AD114">
+        <v>5.6</v>
+      </c>
+      <c r="AE114">
+        <v>1.6</v>
+      </c>
+      <c r="AF114">
+        <v>2.2</v>
+      </c>
+      <c r="AG114">
+        <v>2.88</v>
+      </c>
+      <c r="AH114">
+        <v>1.4</v>
+      </c>
+      <c r="AI114">
+        <v>2.25</v>
+      </c>
+      <c r="AJ114">
+        <v>1.57</v>
+      </c>
+      <c r="AK114">
+        <v>1.28</v>
+      </c>
+      <c r="AL114">
+        <v>1.4</v>
+      </c>
+      <c r="AM114">
+        <v>1.58</v>
+      </c>
+      <c r="AN114">
+        <v>0.33</v>
+      </c>
+      <c r="AO114">
+        <v>0.67</v>
+      </c>
+      <c r="AP114">
+        <v>0.25</v>
+      </c>
+      <c r="AQ114">
+        <v>1.25</v>
+      </c>
+      <c r="AR114">
+        <v>1.64</v>
+      </c>
+      <c r="AS114">
+        <v>1.15</v>
+      </c>
+      <c r="AT114">
+        <v>2.79</v>
+      </c>
+      <c r="AU114">
+        <v>-1</v>
+      </c>
+      <c r="AV114">
+        <v>-1</v>
+      </c>
+      <c r="AW114">
+        <v>-1</v>
+      </c>
+      <c r="AX114">
+        <v>-1</v>
+      </c>
+      <c r="AY114">
+        <v>-1</v>
+      </c>
+      <c r="AZ114">
+        <v>-1</v>
+      </c>
+      <c r="BA114">
+        <v>-1</v>
+      </c>
+      <c r="BB114">
+        <v>-1</v>
+      </c>
+      <c r="BC114">
+        <v>-1</v>
+      </c>
+      <c r="BD114">
+        <v>1.58</v>
+      </c>
+      <c r="BE114">
+        <v>6.75</v>
+      </c>
+      <c r="BF114">
+        <v>2.65</v>
+      </c>
+      <c r="BG114">
+        <v>1.43</v>
+      </c>
+      <c r="BH114">
+        <v>2.55</v>
+      </c>
+      <c r="BI114">
+        <v>1.73</v>
+      </c>
+      <c r="BJ114">
+        <v>1.96</v>
+      </c>
+      <c r="BK114">
+        <v>2.17</v>
+      </c>
+      <c r="BL114">
+        <v>1.6</v>
+      </c>
+      <c r="BM114">
+        <v>2.8</v>
+      </c>
+      <c r="BN114">
+        <v>1.37</v>
+      </c>
+      <c r="BO114">
+        <v>3.65</v>
+      </c>
+      <c r="BP114">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -24438,31 +24438,31 @@
         <v>2.79</v>
       </c>
       <c r="AU114">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV114">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AW114">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AX114">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AY114">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AZ114">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BA114">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BB114">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC114">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BD114">
         <v>1.58</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="215">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -657,6 +657,9 @@
   <si>
     <t>['22', '80']</t>
   </si>
+  <si>
+    <t>['26', '90']</t>
+  </si>
 </sst>
 </file>
 
@@ -1017,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP114"/>
+  <dimension ref="A1:BP115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2381,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -5062,7 +5065,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -7531,7 +7534,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ32">
         <v>0.75</v>
@@ -13096,7 +13099,7 @@
         <v>2</v>
       </c>
       <c r="AQ59">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR59">
         <v>1.06</v>
@@ -13505,7 +13508,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ61">
         <v>0.33</v>
@@ -19276,7 +19279,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -21951,7 +21954,7 @@
         <v>0</v>
       </c>
       <c r="AP102">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ102">
         <v>0</v>
@@ -24501,6 +24504,212 @@
         <v>3.65</v>
       </c>
       <c r="BP114">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7820432</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45719.70833333334</v>
+      </c>
+      <c r="F115">
+        <v>8</v>
+      </c>
+      <c r="G115" t="s">
+        <v>75</v>
+      </c>
+      <c r="H115" t="s">
+        <v>70</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>2</v>
+      </c>
+      <c r="N115">
+        <v>3</v>
+      </c>
+      <c r="O115" t="s">
+        <v>153</v>
+      </c>
+      <c r="P115" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q115">
+        <v>3.5</v>
+      </c>
+      <c r="R115">
+        <v>1.83</v>
+      </c>
+      <c r="S115">
+        <v>3.75</v>
+      </c>
+      <c r="T115">
+        <v>1.62</v>
+      </c>
+      <c r="U115">
+        <v>2.2</v>
+      </c>
+      <c r="V115">
+        <v>4</v>
+      </c>
+      <c r="W115">
+        <v>1.22</v>
+      </c>
+      <c r="X115">
+        <v>13</v>
+      </c>
+      <c r="Y115">
+        <v>1.04</v>
+      </c>
+      <c r="Z115">
+        <v>2.61</v>
+      </c>
+      <c r="AA115">
+        <v>2.88</v>
+      </c>
+      <c r="AB115">
+        <v>2.92</v>
+      </c>
+      <c r="AC115">
+        <v>1.06</v>
+      </c>
+      <c r="AD115">
+        <v>6.5</v>
+      </c>
+      <c r="AE115">
+        <v>1.56</v>
+      </c>
+      <c r="AF115">
+        <v>2.42</v>
+      </c>
+      <c r="AG115">
+        <v>2.7</v>
+      </c>
+      <c r="AH115">
+        <v>1.44</v>
+      </c>
+      <c r="AI115">
+        <v>2.2</v>
+      </c>
+      <c r="AJ115">
+        <v>1.62</v>
+      </c>
+      <c r="AK115">
+        <v>1.38</v>
+      </c>
+      <c r="AL115">
+        <v>1.36</v>
+      </c>
+      <c r="AM115">
+        <v>1.5</v>
+      </c>
+      <c r="AN115">
+        <v>1.75</v>
+      </c>
+      <c r="AO115">
+        <v>1.33</v>
+      </c>
+      <c r="AP115">
+        <v>1.4</v>
+      </c>
+      <c r="AQ115">
+        <v>1.75</v>
+      </c>
+      <c r="AR115">
+        <v>1.19</v>
+      </c>
+      <c r="AS115">
+        <v>1.09</v>
+      </c>
+      <c r="AT115">
+        <v>2.28</v>
+      </c>
+      <c r="AU115">
+        <v>4</v>
+      </c>
+      <c r="AV115">
+        <v>7</v>
+      </c>
+      <c r="AW115">
+        <v>3</v>
+      </c>
+      <c r="AX115">
+        <v>8</v>
+      </c>
+      <c r="AY115">
+        <v>7</v>
+      </c>
+      <c r="AZ115">
+        <v>17</v>
+      </c>
+      <c r="BA115">
+        <v>2</v>
+      </c>
+      <c r="BB115">
+        <v>4</v>
+      </c>
+      <c r="BC115">
+        <v>6</v>
+      </c>
+      <c r="BD115">
+        <v>1.95</v>
+      </c>
+      <c r="BE115">
+        <v>6.4</v>
+      </c>
+      <c r="BF115">
+        <v>2.05</v>
+      </c>
+      <c r="BG115">
+        <v>1.43</v>
+      </c>
+      <c r="BH115">
+        <v>2.55</v>
+      </c>
+      <c r="BI115">
+        <v>1.72</v>
+      </c>
+      <c r="BJ115">
+        <v>1.97</v>
+      </c>
+      <c r="BK115">
+        <v>2.17</v>
+      </c>
+      <c r="BL115">
+        <v>1.6</v>
+      </c>
+      <c r="BM115">
+        <v>2.75</v>
+      </c>
+      <c r="BN115">
+        <v>1.38</v>
+      </c>
+      <c r="BO115">
+        <v>3.65</v>
+      </c>
+      <c r="BP115">
         <v>1.23</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="219">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -532,6 +532,12 @@
     <t>['55', '74']</t>
   </si>
   <si>
+    <t>['2', '86', '90+1']</t>
+  </si>
+  <si>
+    <t>['41']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -659,6 +665,12 @@
   </si>
   <si>
     <t>['26', '90']</t>
+  </si>
+  <si>
+    <t>['30', '50']</t>
+  </si>
+  <si>
+    <t>['4', '45+1']</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP115"/>
+  <dimension ref="A1:BP117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1276,7 +1288,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1688,7 +1700,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2100,7 +2112,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2306,7 +2318,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2387,7 +2399,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2924,7 +2936,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3208,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11">
         <v>1.33</v>
@@ -3336,7 +3348,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -4447,7 +4459,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4778,7 +4790,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5396,7 +5408,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5602,7 +5614,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5808,7 +5820,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6220,7 +6232,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6632,7 +6644,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -8152,7 +8164,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ35">
         <v>1.5</v>
@@ -8280,7 +8292,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -9104,7 +9116,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9597,7 +9609,7 @@
         <v>3</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR42">
         <v>2.46</v>
@@ -9928,7 +9940,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10134,7 +10146,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10212,7 +10224,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ45">
         <v>1.75</v>
@@ -10340,7 +10352,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10546,7 +10558,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10752,7 +10764,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11039,7 +11051,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR49">
         <v>1.6</v>
@@ -11370,7 +11382,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11988,7 +12000,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12606,7 +12618,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13430,7 +13442,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14129,7 +14141,7 @@
         <v>3</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR64">
         <v>1.42</v>
@@ -14666,7 +14678,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14872,7 +14884,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15696,7 +15708,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15902,7 +15914,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -15980,7 +15992,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -16186,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ74">
         <v>0.2</v>
@@ -16520,7 +16532,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16726,7 +16738,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16932,7 +16944,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17344,7 +17356,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17550,7 +17562,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17756,7 +17768,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18374,7 +18386,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18786,7 +18798,7 @@
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18992,7 +19004,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19198,7 +19210,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19404,7 +19416,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19816,7 +19828,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20640,7 +20652,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20846,7 +20858,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21464,7 +21476,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21542,7 +21554,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ100">
         <v>0.8</v>
@@ -21957,7 +21969,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ102">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR102">
         <v>1.05</v>
@@ -23112,7 +23124,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23318,7 +23330,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23730,7 +23742,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -23936,7 +23948,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24348,7 +24360,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24554,7 +24566,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24711,6 +24723,418 @@
       </c>
       <c r="BP115">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7820433</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45719.79166666666</v>
+      </c>
+      <c r="F116">
+        <v>8</v>
+      </c>
+      <c r="G116" t="s">
+        <v>79</v>
+      </c>
+      <c r="H116" t="s">
+        <v>97</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="K116">
+        <v>2</v>
+      </c>
+      <c r="L116">
+        <v>3</v>
+      </c>
+      <c r="M116">
+        <v>2</v>
+      </c>
+      <c r="N116">
+        <v>5</v>
+      </c>
+      <c r="O116" t="s">
+        <v>172</v>
+      </c>
+      <c r="P116" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q116">
+        <v>3.4</v>
+      </c>
+      <c r="R116">
+        <v>1.91</v>
+      </c>
+      <c r="S116">
+        <v>3.75</v>
+      </c>
+      <c r="T116">
+        <v>1.62</v>
+      </c>
+      <c r="U116">
+        <v>2.2</v>
+      </c>
+      <c r="V116">
+        <v>4</v>
+      </c>
+      <c r="W116">
+        <v>1.22</v>
+      </c>
+      <c r="X116">
+        <v>13</v>
+      </c>
+      <c r="Y116">
+        <v>1.04</v>
+      </c>
+      <c r="Z116">
+        <v>2.43</v>
+      </c>
+      <c r="AA116">
+        <v>3.07</v>
+      </c>
+      <c r="AB116">
+        <v>2.98</v>
+      </c>
+      <c r="AC116">
+        <v>1.05</v>
+      </c>
+      <c r="AD116">
+        <v>6.95</v>
+      </c>
+      <c r="AE116">
+        <v>1.55</v>
+      </c>
+      <c r="AF116">
+        <v>2.45</v>
+      </c>
+      <c r="AG116">
+        <v>2.7</v>
+      </c>
+      <c r="AH116">
+        <v>1.44</v>
+      </c>
+      <c r="AI116">
+        <v>2.2</v>
+      </c>
+      <c r="AJ116">
+        <v>1.62</v>
+      </c>
+      <c r="AK116">
+        <v>1.37</v>
+      </c>
+      <c r="AL116">
+        <v>1.37</v>
+      </c>
+      <c r="AM116">
+        <v>1.5</v>
+      </c>
+      <c r="AN116">
+        <v>2.33</v>
+      </c>
+      <c r="AO116">
+        <v>1</v>
+      </c>
+      <c r="AP116">
+        <v>2.5</v>
+      </c>
+      <c r="AQ116">
+        <v>0.75</v>
+      </c>
+      <c r="AR116">
+        <v>1.45</v>
+      </c>
+      <c r="AS116">
+        <v>1.39</v>
+      </c>
+      <c r="AT116">
+        <v>2.84</v>
+      </c>
+      <c r="AU116">
+        <v>12</v>
+      </c>
+      <c r="AV116">
+        <v>9</v>
+      </c>
+      <c r="AW116">
+        <v>7</v>
+      </c>
+      <c r="AX116">
+        <v>0</v>
+      </c>
+      <c r="AY116">
+        <v>21</v>
+      </c>
+      <c r="AZ116">
+        <v>9</v>
+      </c>
+      <c r="BA116">
+        <v>10</v>
+      </c>
+      <c r="BB116">
+        <v>6</v>
+      </c>
+      <c r="BC116">
+        <v>16</v>
+      </c>
+      <c r="BD116">
+        <v>1.97</v>
+      </c>
+      <c r="BE116">
+        <v>6.5</v>
+      </c>
+      <c r="BF116">
+        <v>2</v>
+      </c>
+      <c r="BG116">
+        <v>1.46</v>
+      </c>
+      <c r="BH116">
+        <v>2.5</v>
+      </c>
+      <c r="BI116">
+        <v>1.76</v>
+      </c>
+      <c r="BJ116">
+        <v>1.94</v>
+      </c>
+      <c r="BK116">
+        <v>2.2</v>
+      </c>
+      <c r="BL116">
+        <v>1.57</v>
+      </c>
+      <c r="BM116">
+        <v>2.9</v>
+      </c>
+      <c r="BN116">
+        <v>1.35</v>
+      </c>
+      <c r="BO116">
+        <v>3.8</v>
+      </c>
+      <c r="BP116">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7820434</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45719.875</v>
+      </c>
+      <c r="F117">
+        <v>8</v>
+      </c>
+      <c r="G117" t="s">
+        <v>99</v>
+      </c>
+      <c r="H117" t="s">
+        <v>72</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>2</v>
+      </c>
+      <c r="K117">
+        <v>3</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <v>2</v>
+      </c>
+      <c r="N117">
+        <v>3</v>
+      </c>
+      <c r="O117" t="s">
+        <v>173</v>
+      </c>
+      <c r="P117" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q117">
+        <v>2.75</v>
+      </c>
+      <c r="R117">
+        <v>1.95</v>
+      </c>
+      <c r="S117">
+        <v>5</v>
+      </c>
+      <c r="T117">
+        <v>1.53</v>
+      </c>
+      <c r="U117">
+        <v>2.38</v>
+      </c>
+      <c r="V117">
+        <v>3.75</v>
+      </c>
+      <c r="W117">
+        <v>1.25</v>
+      </c>
+      <c r="X117">
+        <v>11</v>
+      </c>
+      <c r="Y117">
+        <v>1.05</v>
+      </c>
+      <c r="Z117">
+        <v>1.93</v>
+      </c>
+      <c r="AA117">
+        <v>3.16</v>
+      </c>
+      <c r="AB117">
+        <v>4.2</v>
+      </c>
+      <c r="AC117">
+        <v>1.07</v>
+      </c>
+      <c r="AD117">
+        <v>6.35</v>
+      </c>
+      <c r="AE117">
+        <v>1.49</v>
+      </c>
+      <c r="AF117">
+        <v>2.61</v>
+      </c>
+      <c r="AG117">
+        <v>2.5</v>
+      </c>
+      <c r="AH117">
+        <v>1.5</v>
+      </c>
+      <c r="AI117">
+        <v>2.1</v>
+      </c>
+      <c r="AJ117">
+        <v>1.67</v>
+      </c>
+      <c r="AK117">
+        <v>1.24</v>
+      </c>
+      <c r="AL117">
+        <v>1.33</v>
+      </c>
+      <c r="AM117">
+        <v>1.77</v>
+      </c>
+      <c r="AN117">
+        <v>1</v>
+      </c>
+      <c r="AO117">
+        <v>0</v>
+      </c>
+      <c r="AP117">
+        <v>0.75</v>
+      </c>
+      <c r="AQ117">
+        <v>0.75</v>
+      </c>
+      <c r="AR117">
+        <v>1.81</v>
+      </c>
+      <c r="AS117">
+        <v>1.54</v>
+      </c>
+      <c r="AT117">
+        <v>3.35</v>
+      </c>
+      <c r="AU117">
+        <v>5</v>
+      </c>
+      <c r="AV117">
+        <v>4</v>
+      </c>
+      <c r="AW117">
+        <v>12</v>
+      </c>
+      <c r="AX117">
+        <v>6</v>
+      </c>
+      <c r="AY117">
+        <v>21</v>
+      </c>
+      <c r="AZ117">
+        <v>12</v>
+      </c>
+      <c r="BA117">
+        <v>7</v>
+      </c>
+      <c r="BB117">
+        <v>3</v>
+      </c>
+      <c r="BC117">
+        <v>10</v>
+      </c>
+      <c r="BD117">
+        <v>1.61</v>
+      </c>
+      <c r="BE117">
+        <v>6.75</v>
+      </c>
+      <c r="BF117">
+        <v>2.55</v>
+      </c>
+      <c r="BG117">
+        <v>1.37</v>
+      </c>
+      <c r="BH117">
+        <v>2.8</v>
+      </c>
+      <c r="BI117">
+        <v>1.63</v>
+      </c>
+      <c r="BJ117">
+        <v>2.12</v>
+      </c>
+      <c r="BK117">
+        <v>2</v>
+      </c>
+      <c r="BL117">
+        <v>1.71</v>
+      </c>
+      <c r="BM117">
+        <v>2.55</v>
+      </c>
+      <c r="BN117">
+        <v>1.44</v>
+      </c>
+      <c r="BO117">
+        <v>3.4</v>
+      </c>
+      <c r="BP117">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -538,6 +538,15 @@
     <t>['41']</t>
   </si>
   <si>
+    <t>['7']</t>
+  </si>
+  <si>
+    <t>['80']</t>
+  </si>
+  <si>
+    <t>['22']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -551,9 +560,6 @@
   </si>
   <si>
     <t>['10']</t>
-  </si>
-  <si>
-    <t>['80']</t>
   </si>
   <si>
     <t>['84']</t>
@@ -671,6 +677,18 @@
   </si>
   <si>
     <t>['4', '45+1']</t>
+  </si>
+  <si>
+    <t>['62', '90+1']</t>
+  </si>
+  <si>
+    <t>['16', '36', '89']</t>
+  </si>
+  <si>
+    <t>['12', '74']</t>
+  </si>
+  <si>
+    <t>['25']</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP117"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1288,7 +1306,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1700,7 +1718,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2112,7 +2130,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2318,7 +2336,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2811,7 +2829,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ9">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2936,7 +2954,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3220,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>1.33</v>
@@ -3348,7 +3366,7 @@
         <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -4047,7 +4065,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ15">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4250,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ16">
         <v>0</v>
@@ -4456,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ17">
         <v>0.75</v>
@@ -4665,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="AQ18">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4790,7 +4808,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5408,7 +5426,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5486,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5614,7 +5632,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5695,7 +5713,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5820,7 +5838,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6232,7 +6250,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6313,7 +6331,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6644,7 +6662,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6928,7 +6946,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>0.25</v>
@@ -7340,7 +7358,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -8164,7 +8182,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>1.5</v>
@@ -8292,7 +8310,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8373,7 +8391,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ36">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR36">
         <v>1</v>
@@ -9116,7 +9134,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9940,7 +9958,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10146,7 +10164,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10352,7 +10370,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10558,7 +10576,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10639,7 +10657,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ47">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR47">
         <v>1.66</v>
@@ -10764,7 +10782,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -10842,7 +10860,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
         <v>0.25</v>
@@ -11048,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ49">
         <v>0.75</v>
@@ -11382,7 +11400,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11669,7 +11687,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ52">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AR52">
         <v>1.64</v>
@@ -11872,7 +11890,7 @@
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ53">
         <v>1.75</v>
@@ -12000,7 +12018,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12287,7 +12305,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR55">
         <v>1.6</v>
@@ -12490,10 +12508,10 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR56">
         <v>1.44</v>
@@ -12618,7 +12636,7 @@
         <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13442,7 +13460,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14678,7 +14696,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14884,7 +14902,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -14965,7 +14983,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ68">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR68">
         <v>1.54</v>
@@ -15708,7 +15726,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15914,7 +15932,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -15992,7 +16010,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -16532,7 +16550,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16610,10 +16628,10 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR76">
         <v>1.36</v>
@@ -16738,7 +16756,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16944,7 +16962,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17228,7 +17246,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ79">
         <v>0.25</v>
@@ -17356,7 +17374,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17562,7 +17580,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17640,10 +17658,10 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AR81">
         <v>1.47</v>
@@ -17768,7 +17786,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18386,7 +18404,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18673,7 +18691,7 @@
         <v>2</v>
       </c>
       <c r="AQ86">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR86">
         <v>1.31</v>
@@ -18798,7 +18816,7 @@
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -19004,7 +19022,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19085,7 +19103,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR88">
         <v>1.23</v>
@@ -19210,7 +19228,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19288,7 +19306,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ89">
         <v>1.75</v>
@@ -19416,7 +19434,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19828,7 +19846,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20652,7 +20670,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20858,7 +20876,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21476,7 +21494,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22790,7 +22808,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ106">
         <v>1.75</v>
@@ -23124,7 +23142,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23330,7 +23348,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23742,7 +23760,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -23948,7 +23966,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24360,7 +24378,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24438,10 +24456,10 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ114">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR114">
         <v>1.64</v>
@@ -24566,7 +24584,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24772,7 +24790,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -24850,7 +24868,7 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
         <v>0.75</v>
@@ -24978,7 +24996,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25135,6 +25153,1036 @@
       </c>
       <c r="BP117">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7820435</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45723.79166666666</v>
+      </c>
+      <c r="F118">
+        <v>9</v>
+      </c>
+      <c r="G118" t="s">
+        <v>85</v>
+      </c>
+      <c r="H118" t="s">
+        <v>98</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <v>2</v>
+      </c>
+      <c r="N118">
+        <v>3</v>
+      </c>
+      <c r="O118" t="s">
+        <v>174</v>
+      </c>
+      <c r="P118" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q118">
+        <v>4.33</v>
+      </c>
+      <c r="R118">
+        <v>1.83</v>
+      </c>
+      <c r="S118">
+        <v>3.2</v>
+      </c>
+      <c r="T118">
+        <v>1.62</v>
+      </c>
+      <c r="U118">
+        <v>2.2</v>
+      </c>
+      <c r="V118">
+        <v>4</v>
+      </c>
+      <c r="W118">
+        <v>1.22</v>
+      </c>
+      <c r="X118">
+        <v>15</v>
+      </c>
+      <c r="Y118">
+        <v>1.03</v>
+      </c>
+      <c r="Z118">
+        <v>3.57</v>
+      </c>
+      <c r="AA118">
+        <v>2.83</v>
+      </c>
+      <c r="AB118">
+        <v>2.28</v>
+      </c>
+      <c r="AC118">
+        <v>1.1</v>
+      </c>
+      <c r="AD118">
+        <v>7</v>
+      </c>
+      <c r="AE118">
+        <v>1.57</v>
+      </c>
+      <c r="AF118">
+        <v>2.25</v>
+      </c>
+      <c r="AG118">
+        <v>2.88</v>
+      </c>
+      <c r="AH118">
+        <v>1.4</v>
+      </c>
+      <c r="AI118">
+        <v>2.25</v>
+      </c>
+      <c r="AJ118">
+        <v>1.57</v>
+      </c>
+      <c r="AK118">
+        <v>1.55</v>
+      </c>
+      <c r="AL118">
+        <v>1.39</v>
+      </c>
+      <c r="AM118">
+        <v>1.31</v>
+      </c>
+      <c r="AN118">
+        <v>1.33</v>
+      </c>
+      <c r="AO118">
+        <v>2.33</v>
+      </c>
+      <c r="AP118">
+        <v>1</v>
+      </c>
+      <c r="AQ118">
+        <v>2.5</v>
+      </c>
+      <c r="AR118">
+        <v>1.5</v>
+      </c>
+      <c r="AS118">
+        <v>1.55</v>
+      </c>
+      <c r="AT118">
+        <v>3.05</v>
+      </c>
+      <c r="AU118">
+        <v>7</v>
+      </c>
+      <c r="AV118">
+        <v>8</v>
+      </c>
+      <c r="AW118">
+        <v>4</v>
+      </c>
+      <c r="AX118">
+        <v>4</v>
+      </c>
+      <c r="AY118">
+        <v>12</v>
+      </c>
+      <c r="AZ118">
+        <v>13</v>
+      </c>
+      <c r="BA118">
+        <v>2</v>
+      </c>
+      <c r="BB118">
+        <v>3</v>
+      </c>
+      <c r="BC118">
+        <v>5</v>
+      </c>
+      <c r="BD118">
+        <v>2.4</v>
+      </c>
+      <c r="BE118">
+        <v>6.4</v>
+      </c>
+      <c r="BF118">
+        <v>1.72</v>
+      </c>
+      <c r="BG118">
+        <v>1.49</v>
+      </c>
+      <c r="BH118">
+        <v>2.4</v>
+      </c>
+      <c r="BI118">
+        <v>1.82</v>
+      </c>
+      <c r="BJ118">
+        <v>1.86</v>
+      </c>
+      <c r="BK118">
+        <v>2.32</v>
+      </c>
+      <c r="BL118">
+        <v>1.53</v>
+      </c>
+      <c r="BM118">
+        <v>3.05</v>
+      </c>
+      <c r="BN118">
+        <v>1.32</v>
+      </c>
+      <c r="BO118">
+        <v>3.95</v>
+      </c>
+      <c r="BP118">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7820436</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45723.79166666666</v>
+      </c>
+      <c r="F119">
+        <v>9</v>
+      </c>
+      <c r="G119" t="s">
+        <v>90</v>
+      </c>
+      <c r="H119" t="s">
+        <v>78</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>1</v>
+      </c>
+      <c r="O119" t="s">
+        <v>175</v>
+      </c>
+      <c r="P119" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q119">
+        <v>2.4</v>
+      </c>
+      <c r="R119">
+        <v>1.91</v>
+      </c>
+      <c r="S119">
+        <v>7</v>
+      </c>
+      <c r="T119">
+        <v>1.62</v>
+      </c>
+      <c r="U119">
+        <v>2.2</v>
+      </c>
+      <c r="V119">
+        <v>4</v>
+      </c>
+      <c r="W119">
+        <v>1.22</v>
+      </c>
+      <c r="X119">
+        <v>13</v>
+      </c>
+      <c r="Y119">
+        <v>1.04</v>
+      </c>
+      <c r="Z119">
+        <v>1.7</v>
+      </c>
+      <c r="AA119">
+        <v>3.4</v>
+      </c>
+      <c r="AB119">
+        <v>5.5</v>
+      </c>
+      <c r="AC119">
+        <v>1.12</v>
+      </c>
+      <c r="AD119">
+        <v>6.2</v>
+      </c>
+      <c r="AE119">
+        <v>1.53</v>
+      </c>
+      <c r="AF119">
+        <v>2.3</v>
+      </c>
+      <c r="AG119">
+        <v>2.7</v>
+      </c>
+      <c r="AH119">
+        <v>1.44</v>
+      </c>
+      <c r="AI119">
+        <v>2.63</v>
+      </c>
+      <c r="AJ119">
+        <v>1.44</v>
+      </c>
+      <c r="AK119">
+        <v>1.18</v>
+      </c>
+      <c r="AL119">
+        <v>1.32</v>
+      </c>
+      <c r="AM119">
+        <v>1.93</v>
+      </c>
+      <c r="AN119">
+        <v>0.25</v>
+      </c>
+      <c r="AO119">
+        <v>0.67</v>
+      </c>
+      <c r="AP119">
+        <v>0.8</v>
+      </c>
+      <c r="AQ119">
+        <v>0.5</v>
+      </c>
+      <c r="AR119">
+        <v>1.33</v>
+      </c>
+      <c r="AS119">
+        <v>1.38</v>
+      </c>
+      <c r="AT119">
+        <v>2.71</v>
+      </c>
+      <c r="AU119">
+        <v>7</v>
+      </c>
+      <c r="AV119">
+        <v>4</v>
+      </c>
+      <c r="AW119">
+        <v>9</v>
+      </c>
+      <c r="AX119">
+        <v>6</v>
+      </c>
+      <c r="AY119">
+        <v>20</v>
+      </c>
+      <c r="AZ119">
+        <v>11</v>
+      </c>
+      <c r="BA119">
+        <v>5</v>
+      </c>
+      <c r="BB119">
+        <v>6</v>
+      </c>
+      <c r="BC119">
+        <v>11</v>
+      </c>
+      <c r="BD119">
+        <v>1.5</v>
+      </c>
+      <c r="BE119">
+        <v>6.75</v>
+      </c>
+      <c r="BF119">
+        <v>2.9</v>
+      </c>
+      <c r="BG119">
+        <v>1.49</v>
+      </c>
+      <c r="BH119">
+        <v>2.4</v>
+      </c>
+      <c r="BI119">
+        <v>1.81</v>
+      </c>
+      <c r="BJ119">
+        <v>1.88</v>
+      </c>
+      <c r="BK119">
+        <v>2.28</v>
+      </c>
+      <c r="BL119">
+        <v>1.54</v>
+      </c>
+      <c r="BM119">
+        <v>2.95</v>
+      </c>
+      <c r="BN119">
+        <v>1.33</v>
+      </c>
+      <c r="BO119">
+        <v>3.95</v>
+      </c>
+      <c r="BP119">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7820437</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45723.88541666666</v>
+      </c>
+      <c r="F120">
+        <v>9</v>
+      </c>
+      <c r="G120" t="s">
+        <v>84</v>
+      </c>
+      <c r="H120" t="s">
+        <v>83</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>2</v>
+      </c>
+      <c r="K120">
+        <v>2</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>3</v>
+      </c>
+      <c r="N120">
+        <v>3</v>
+      </c>
+      <c r="O120" t="s">
+        <v>100</v>
+      </c>
+      <c r="P120" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q120">
+        <v>4</v>
+      </c>
+      <c r="R120">
+        <v>1.91</v>
+      </c>
+      <c r="S120">
+        <v>3.25</v>
+      </c>
+      <c r="T120">
+        <v>1.57</v>
+      </c>
+      <c r="U120">
+        <v>2.25</v>
+      </c>
+      <c r="V120">
+        <v>3.75</v>
+      </c>
+      <c r="W120">
+        <v>1.25</v>
+      </c>
+      <c r="X120">
+        <v>11</v>
+      </c>
+      <c r="Y120">
+        <v>1.05</v>
+      </c>
+      <c r="Z120">
+        <v>3</v>
+      </c>
+      <c r="AA120">
+        <v>3.2</v>
+      </c>
+      <c r="AB120">
+        <v>2.4</v>
+      </c>
+      <c r="AC120">
+        <v>1.07</v>
+      </c>
+      <c r="AD120">
+        <v>9</v>
+      </c>
+      <c r="AE120">
+        <v>1.35</v>
+      </c>
+      <c r="AF120">
+        <v>3.15</v>
+      </c>
+      <c r="AG120">
+        <v>2.5</v>
+      </c>
+      <c r="AH120">
+        <v>1.5</v>
+      </c>
+      <c r="AI120">
+        <v>2.1</v>
+      </c>
+      <c r="AJ120">
+        <v>1.67</v>
+      </c>
+      <c r="AK120">
+        <v>1.55</v>
+      </c>
+      <c r="AL120">
+        <v>1.36</v>
+      </c>
+      <c r="AM120">
+        <v>1.33</v>
+      </c>
+      <c r="AN120">
+        <v>2.6</v>
+      </c>
+      <c r="AO120">
+        <v>1.33</v>
+      </c>
+      <c r="AP120">
+        <v>2.17</v>
+      </c>
+      <c r="AQ120">
+        <v>1.75</v>
+      </c>
+      <c r="AR120">
+        <v>2.07</v>
+      </c>
+      <c r="AS120">
+        <v>1.38</v>
+      </c>
+      <c r="AT120">
+        <v>3.45</v>
+      </c>
+      <c r="AU120">
+        <v>6</v>
+      </c>
+      <c r="AV120">
+        <v>6</v>
+      </c>
+      <c r="AW120">
+        <v>6</v>
+      </c>
+      <c r="AX120">
+        <v>2</v>
+      </c>
+      <c r="AY120">
+        <v>13</v>
+      </c>
+      <c r="AZ120">
+        <v>9</v>
+      </c>
+      <c r="BA120">
+        <v>5</v>
+      </c>
+      <c r="BB120">
+        <v>2</v>
+      </c>
+      <c r="BC120">
+        <v>7</v>
+      </c>
+      <c r="BD120">
+        <v>1.95</v>
+      </c>
+      <c r="BE120">
+        <v>6.25</v>
+      </c>
+      <c r="BF120">
+        <v>2.07</v>
+      </c>
+      <c r="BG120">
+        <v>1.5</v>
+      </c>
+      <c r="BH120">
+        <v>2.38</v>
+      </c>
+      <c r="BI120">
+        <v>1.95</v>
+      </c>
+      <c r="BJ120">
+        <v>1.85</v>
+      </c>
+      <c r="BK120">
+        <v>2.35</v>
+      </c>
+      <c r="BL120">
+        <v>1.5</v>
+      </c>
+      <c r="BM120">
+        <v>3.05</v>
+      </c>
+      <c r="BN120">
+        <v>1.3</v>
+      </c>
+      <c r="BO120">
+        <v>4.1</v>
+      </c>
+      <c r="BP120">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7820438</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45724.70833333334</v>
+      </c>
+      <c r="F121">
+        <v>9</v>
+      </c>
+      <c r="G121" t="s">
+        <v>79</v>
+      </c>
+      <c r="H121" t="s">
+        <v>76</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>2</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <v>2</v>
+      </c>
+      <c r="N121">
+        <v>3</v>
+      </c>
+      <c r="O121" t="s">
+        <v>176</v>
+      </c>
+      <c r="P121" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q121">
+        <v>4</v>
+      </c>
+      <c r="R121">
+        <v>1.8</v>
+      </c>
+      <c r="S121">
+        <v>3.75</v>
+      </c>
+      <c r="T121">
+        <v>1.73</v>
+      </c>
+      <c r="U121">
+        <v>2</v>
+      </c>
+      <c r="V121">
+        <v>5</v>
+      </c>
+      <c r="W121">
+        <v>1.17</v>
+      </c>
+      <c r="X121">
+        <v>17</v>
+      </c>
+      <c r="Y121">
+        <v>1.03</v>
+      </c>
+      <c r="Z121">
+        <v>2.92</v>
+      </c>
+      <c r="AA121">
+        <v>2.74</v>
+      </c>
+      <c r="AB121">
+        <v>2.75</v>
+      </c>
+      <c r="AC121">
+        <v>1.12</v>
+      </c>
+      <c r="AD121">
+        <v>6.2</v>
+      </c>
+      <c r="AE121">
+        <v>1.55</v>
+      </c>
+      <c r="AF121">
+        <v>2.25</v>
+      </c>
+      <c r="AG121">
+        <v>3.4</v>
+      </c>
+      <c r="AH121">
+        <v>1.33</v>
+      </c>
+      <c r="AI121">
+        <v>2.5</v>
+      </c>
+      <c r="AJ121">
+        <v>1.5</v>
+      </c>
+      <c r="AK121">
+        <v>1.37</v>
+      </c>
+      <c r="AL121">
+        <v>1.38</v>
+      </c>
+      <c r="AM121">
+        <v>1.5</v>
+      </c>
+      <c r="AN121">
+        <v>2.5</v>
+      </c>
+      <c r="AO121">
+        <v>1.33</v>
+      </c>
+      <c r="AP121">
+        <v>2</v>
+      </c>
+      <c r="AQ121">
+        <v>1.75</v>
+      </c>
+      <c r="AR121">
+        <v>1.76</v>
+      </c>
+      <c r="AS121">
+        <v>0.95</v>
+      </c>
+      <c r="AT121">
+        <v>2.71</v>
+      </c>
+      <c r="AU121">
+        <v>5</v>
+      </c>
+      <c r="AV121">
+        <v>4</v>
+      </c>
+      <c r="AW121">
+        <v>7</v>
+      </c>
+      <c r="AX121">
+        <v>4</v>
+      </c>
+      <c r="AY121">
+        <v>15</v>
+      </c>
+      <c r="AZ121">
+        <v>9</v>
+      </c>
+      <c r="BA121">
+        <v>3</v>
+      </c>
+      <c r="BB121">
+        <v>6</v>
+      </c>
+      <c r="BC121">
+        <v>9</v>
+      </c>
+      <c r="BD121">
+        <v>1.98</v>
+      </c>
+      <c r="BE121">
+        <v>6.4</v>
+      </c>
+      <c r="BF121">
+        <v>2</v>
+      </c>
+      <c r="BG121">
+        <v>1.43</v>
+      </c>
+      <c r="BH121">
+        <v>2.63</v>
+      </c>
+      <c r="BI121">
+        <v>1.74</v>
+      </c>
+      <c r="BJ121">
+        <v>2.02</v>
+      </c>
+      <c r="BK121">
+        <v>2.22</v>
+      </c>
+      <c r="BL121">
+        <v>1.62</v>
+      </c>
+      <c r="BM121">
+        <v>2.85</v>
+      </c>
+      <c r="BN121">
+        <v>1.37</v>
+      </c>
+      <c r="BO121">
+        <v>3.9</v>
+      </c>
+      <c r="BP121">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7820439</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45724.80208333334</v>
+      </c>
+      <c r="F122">
+        <v>9</v>
+      </c>
+      <c r="G122" t="s">
+        <v>97</v>
+      </c>
+      <c r="H122" t="s">
+        <v>93</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>1</v>
+      </c>
+      <c r="N122">
+        <v>1</v>
+      </c>
+      <c r="O122" t="s">
+        <v>100</v>
+      </c>
+      <c r="P122" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q122">
+        <v>2.63</v>
+      </c>
+      <c r="R122">
+        <v>2</v>
+      </c>
+      <c r="S122">
+        <v>5</v>
+      </c>
+      <c r="T122">
+        <v>1.53</v>
+      </c>
+      <c r="U122">
+        <v>2.38</v>
+      </c>
+      <c r="V122">
+        <v>3.75</v>
+      </c>
+      <c r="W122">
+        <v>1.25</v>
+      </c>
+      <c r="X122">
+        <v>11</v>
+      </c>
+      <c r="Y122">
+        <v>1.05</v>
+      </c>
+      <c r="Z122">
+        <v>1.9</v>
+      </c>
+      <c r="AA122">
+        <v>3.24</v>
+      </c>
+      <c r="AB122">
+        <v>4.18</v>
+      </c>
+      <c r="AC122">
+        <v>1.08</v>
+      </c>
+      <c r="AD122">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE122">
+        <v>1.38</v>
+      </c>
+      <c r="AF122">
+        <v>2.95</v>
+      </c>
+      <c r="AG122">
+        <v>2.4</v>
+      </c>
+      <c r="AH122">
+        <v>1.53</v>
+      </c>
+      <c r="AI122">
+        <v>2.1</v>
+      </c>
+      <c r="AJ122">
+        <v>1.67</v>
+      </c>
+      <c r="AK122">
+        <v>1.22</v>
+      </c>
+      <c r="AL122">
+        <v>1.32</v>
+      </c>
+      <c r="AM122">
+        <v>1.83</v>
+      </c>
+      <c r="AN122">
+        <v>2</v>
+      </c>
+      <c r="AO122">
+        <v>1.25</v>
+      </c>
+      <c r="AP122">
+        <v>1.5</v>
+      </c>
+      <c r="AQ122">
+        <v>1.6</v>
+      </c>
+      <c r="AR122">
+        <v>1.45</v>
+      </c>
+      <c r="AS122">
+        <v>1.28</v>
+      </c>
+      <c r="AT122">
+        <v>2.73</v>
+      </c>
+      <c r="AU122">
+        <v>-1</v>
+      </c>
+      <c r="AV122">
+        <v>-1</v>
+      </c>
+      <c r="AW122">
+        <v>-1</v>
+      </c>
+      <c r="AX122">
+        <v>-1</v>
+      </c>
+      <c r="AY122">
+        <v>-1</v>
+      </c>
+      <c r="AZ122">
+        <v>-1</v>
+      </c>
+      <c r="BA122">
+        <v>-1</v>
+      </c>
+      <c r="BB122">
+        <v>-1</v>
+      </c>
+      <c r="BC122">
+        <v>-1</v>
+      </c>
+      <c r="BD122">
+        <v>1.41</v>
+      </c>
+      <c r="BE122">
+        <v>7</v>
+      </c>
+      <c r="BF122">
+        <v>3.2</v>
+      </c>
+      <c r="BG122">
+        <v>1.39</v>
+      </c>
+      <c r="BH122">
+        <v>2.77</v>
+      </c>
+      <c r="BI122">
+        <v>1.68</v>
+      </c>
+      <c r="BJ122">
+        <v>2.11</v>
+      </c>
+      <c r="BK122">
+        <v>2.11</v>
+      </c>
+      <c r="BL122">
+        <v>1.68</v>
+      </c>
+      <c r="BM122">
+        <v>2.7</v>
+      </c>
+      <c r="BN122">
+        <v>1.41</v>
+      </c>
+      <c r="BO122">
+        <v>3.65</v>
+      </c>
+      <c r="BP122">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="227">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -364,10 +364,10 @@
     <t>['20', '62', '68', '82']</t>
   </si>
   <si>
-    <t>['20']</t>
+    <t>['44', '55']</t>
   </si>
   <si>
-    <t>['44', '55']</t>
+    <t>['20']</t>
   </si>
   <si>
     <t>['18']</t>
@@ -481,10 +481,10 @@
     <t>['73']</t>
   </si>
   <si>
-    <t>['38']</t>
+    <t>['84', '90+5']</t>
   </si>
   <si>
-    <t>['84', '90+5']</t>
+    <t>['38']</t>
   </si>
   <si>
     <t>['89']</t>
@@ -545,6 +545,9 @@
   </si>
   <si>
     <t>['22']</t>
+  </si>
+  <si>
+    <t>['65']</t>
   </si>
   <si>
     <t>['18', '26', '48']</t>
@@ -677,6 +680,9 @@
   </si>
   <si>
     <t>['4', '45+1']</t>
+  </si>
+  <si>
+    <t>['11']</t>
   </si>
   <si>
     <t>['62', '90+1']</t>
@@ -1050,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP122"/>
+  <dimension ref="A1:BP126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1306,7 +1312,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1718,7 +1724,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2130,7 +2136,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2336,7 +2342,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2748,7 +2754,7 @@
         <v>104</v>
       </c>
       <c r="P9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2954,7 +2960,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3856,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ14">
         <v>1.5</v>
@@ -4808,7 +4814,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5092,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
         <v>1.75</v>
@@ -5301,7 +5307,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ21">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5426,7 +5432,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5632,7 +5638,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5713,7 +5719,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ23">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5838,7 +5844,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6250,7 +6256,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6662,7 +6668,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6743,7 +6749,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ28">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -7032,7 +7038,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>7820343</v>
+        <v>7820344</v>
       </c>
       <c r="C30" t="s">
         <v>68</v>
@@ -7047,10 +7053,10 @@
         <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -7062,13 +7068,13 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" t="s">
         <v>116</v>
@@ -7077,13 +7083,13 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="R30">
         <v>1.91</v>
       </c>
       <c r="S30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30">
         <v>1.62</v>
@@ -7104,13 +7110,13 @@
         <v>1.04</v>
       </c>
       <c r="Z30">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AA30">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB30">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AC30">
         <v>1.12</v>
@@ -7119,118 +7125,118 @@
         <v>5.75</v>
       </c>
       <c r="AE30">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF30">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG30">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AH30">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI30">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AJ30">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK30">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AL30">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AM30">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP30">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU30">
+        <v>7</v>
+      </c>
+      <c r="AV30">
         <v>3</v>
       </c>
-      <c r="AV30">
-        <v>0</v>
-      </c>
       <c r="AW30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX30">
         <v>6</v>
       </c>
       <c r="AY30">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA30">
+        <v>4</v>
+      </c>
+      <c r="BB30">
+        <v>1</v>
+      </c>
+      <c r="BC30">
         <v>5</v>
       </c>
-      <c r="BB30">
-        <v>2</v>
-      </c>
-      <c r="BC30">
-        <v>7</v>
-      </c>
       <c r="BD30">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="BE30">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="BF30">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="BG30">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="BH30">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="BI30">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BJ30">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="BK30">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="BL30">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BM30">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="BN30">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BO30">
-        <v>3.88</v>
+        <v>4.3</v>
       </c>
       <c r="BP30">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="31" spans="1:68">
@@ -7238,7 +7244,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>7820344</v>
+        <v>7820343</v>
       </c>
       <c r="C31" t="s">
         <v>68</v>
@@ -7253,10 +7259,10 @@
         <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H31" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -7268,13 +7274,13 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" t="s">
         <v>117</v>
@@ -7283,13 +7289,13 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="R31">
         <v>1.91</v>
       </c>
       <c r="S31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>1.62</v>
@@ -7310,13 +7316,13 @@
         <v>1.04</v>
       </c>
       <c r="Z31">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA31">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB31">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC31">
         <v>1.12</v>
@@ -7325,118 +7331,118 @@
         <v>5.75</v>
       </c>
       <c r="AE31">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AF31">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG31">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH31">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AI31">
+        <v>2.25</v>
+      </c>
+      <c r="AJ31">
+        <v>1.57</v>
+      </c>
+      <c r="AK31">
+        <v>1.23</v>
+      </c>
+      <c r="AL31">
+        <v>1.36</v>
+      </c>
+      <c r="AM31">
+        <v>1.73</v>
+      </c>
+      <c r="AN31">
+        <v>0</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
         <v>2.2</v>
       </c>
-      <c r="AJ31">
-        <v>1.62</v>
-      </c>
-      <c r="AK31">
-        <v>1.33</v>
-      </c>
-      <c r="AL31">
-        <v>1.39</v>
-      </c>
-      <c r="AM31">
-        <v>1.53</v>
-      </c>
-      <c r="AN31">
+      <c r="AQ31">
+        <v>1.5</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31">
         <v>3</v>
       </c>
-      <c r="AO31">
-        <v>3</v>
-      </c>
-      <c r="AP31">
-        <v>2.17</v>
-      </c>
-      <c r="AQ31">
-        <v>1</v>
-      </c>
-      <c r="AR31">
-        <v>1.4</v>
-      </c>
-      <c r="AS31">
-        <v>1.7</v>
-      </c>
-      <c r="AT31">
-        <v>3.1</v>
-      </c>
-      <c r="AU31">
-        <v>7</v>
-      </c>
       <c r="AV31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX31">
         <v>6</v>
       </c>
       <c r="AY31">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD31">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="BE31">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF31">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="BG31">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BH31">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="BI31">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="BJ31">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BK31">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="BL31">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="BM31">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="BN31">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BO31">
-        <v>4.3</v>
+        <v>3.88</v>
       </c>
       <c r="BP31">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="32" spans="1:68">
@@ -8310,7 +8316,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -9134,7 +9140,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9710,7 +9716,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>7820357</v>
+        <v>7820356</v>
       </c>
       <c r="C43" t="s">
         <v>68</v>
@@ -9725,190 +9731,190 @@
         <v>3</v>
       </c>
       <c r="G43" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O43" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="P43" t="s">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="Q43">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="R43">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="S43">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="T43">
+        <v>1.57</v>
+      </c>
+      <c r="U43">
+        <v>2.25</v>
+      </c>
+      <c r="V43">
+        <v>3.75</v>
+      </c>
+      <c r="W43">
+        <v>1.25</v>
+      </c>
+      <c r="X43">
+        <v>11</v>
+      </c>
+      <c r="Y43">
+        <v>1.05</v>
+      </c>
+      <c r="Z43">
+        <v>1.9</v>
+      </c>
+      <c r="AA43">
+        <v>3.3</v>
+      </c>
+      <c r="AB43">
+        <v>4.5</v>
+      </c>
+      <c r="AC43">
+        <v>1.08</v>
+      </c>
+      <c r="AD43">
+        <v>7.37</v>
+      </c>
+      <c r="AE43">
+        <v>1.48</v>
+      </c>
+      <c r="AF43">
+        <v>2.63</v>
+      </c>
+      <c r="AG43">
+        <v>2.5</v>
+      </c>
+      <c r="AH43">
+        <v>1.5</v>
+      </c>
+      <c r="AI43">
+        <v>2.2</v>
+      </c>
+      <c r="AJ43">
+        <v>1.62</v>
+      </c>
+      <c r="AK43">
+        <v>1.2</v>
+      </c>
+      <c r="AL43">
+        <v>1.34</v>
+      </c>
+      <c r="AM43">
         <v>1.83</v>
       </c>
-      <c r="U43">
-        <v>1.83</v>
-      </c>
-      <c r="V43">
-        <v>6</v>
-      </c>
-      <c r="W43">
-        <v>1.13</v>
-      </c>
-      <c r="X43">
-        <v>21</v>
-      </c>
-      <c r="Y43">
-        <v>1.02</v>
-      </c>
-      <c r="Z43">
-        <v>2.15</v>
-      </c>
-      <c r="AA43">
-        <v>2.7</v>
-      </c>
-      <c r="AB43">
-        <v>4.33</v>
-      </c>
-      <c r="AC43">
-        <v>1.18</v>
-      </c>
-      <c r="AD43">
-        <v>4.56</v>
-      </c>
-      <c r="AE43">
-        <v>1.94</v>
-      </c>
-      <c r="AF43">
-        <v>1.89</v>
-      </c>
-      <c r="AG43">
-        <v>4</v>
-      </c>
-      <c r="AH43">
-        <v>1.25</v>
-      </c>
-      <c r="AI43">
-        <v>3</v>
-      </c>
-      <c r="AJ43">
-        <v>1.36</v>
-      </c>
-      <c r="AK43">
-        <v>1.21</v>
-      </c>
-      <c r="AL43">
-        <v>1.44</v>
-      </c>
-      <c r="AM43">
-        <v>1.66</v>
-      </c>
       <c r="AN43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO43">
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AR43">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="AS43">
-        <v>0.6899999999999999</v>
+        <v>1.47</v>
       </c>
       <c r="AT43">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="AU43">
+        <v>5</v>
+      </c>
+      <c r="AV43">
         <v>6</v>
       </c>
-      <c r="AV43">
-        <v>4</v>
-      </c>
       <c r="AW43">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX43">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY43">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AZ43">
+        <v>12</v>
+      </c>
+      <c r="BA43">
         <v>6</v>
       </c>
-      <c r="BA43">
-        <v>5</v>
-      </c>
       <c r="BB43">
         <v>2</v>
       </c>
       <c r="BC43">
+        <v>8</v>
+      </c>
+      <c r="BD43">
+        <v>1.43</v>
+      </c>
+      <c r="BE43">
         <v>7</v>
       </c>
-      <c r="BD43">
-        <v>1.42</v>
-      </c>
-      <c r="BE43">
-        <v>6.75</v>
-      </c>
       <c r="BF43">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG43">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="BH43">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="BI43">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="BJ43">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="BK43">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="BL43">
-        <v>1.49</v>
+        <v>1.86</v>
       </c>
       <c r="BM43">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="BN43">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="BO43">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="BP43">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="44" spans="1:68">
@@ -9916,7 +9922,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>7820356</v>
+        <v>7820357</v>
       </c>
       <c r="C44" t="s">
         <v>68</v>
@@ -9931,190 +9937,190 @@
         <v>3</v>
       </c>
       <c r="G44" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="H44" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44" t="s">
+        <v>113</v>
+      </c>
+      <c r="P44" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q44">
+        <v>3.1</v>
+      </c>
+      <c r="R44">
+        <v>1.73</v>
+      </c>
+      <c r="S44">
+        <v>5.5</v>
+      </c>
+      <c r="T44">
+        <v>1.83</v>
+      </c>
+      <c r="U44">
+        <v>1.83</v>
+      </c>
+      <c r="V44">
+        <v>6</v>
+      </c>
+      <c r="W44">
+        <v>1.13</v>
+      </c>
+      <c r="X44">
+        <v>21</v>
+      </c>
+      <c r="Y44">
+        <v>1.02</v>
+      </c>
+      <c r="Z44">
+        <v>2.15</v>
+      </c>
+      <c r="AA44">
+        <v>2.7</v>
+      </c>
+      <c r="AB44">
+        <v>4.33</v>
+      </c>
+      <c r="AC44">
+        <v>1.18</v>
+      </c>
+      <c r="AD44">
+        <v>4.56</v>
+      </c>
+      <c r="AE44">
+        <v>1.94</v>
+      </c>
+      <c r="AF44">
+        <v>1.89</v>
+      </c>
+      <c r="AG44">
+        <v>4</v>
+      </c>
+      <c r="AH44">
+        <v>1.25</v>
+      </c>
+      <c r="AI44">
         <v>3</v>
       </c>
-      <c r="K44">
+      <c r="AJ44">
+        <v>1.36</v>
+      </c>
+      <c r="AK44">
+        <v>1.21</v>
+      </c>
+      <c r="AL44">
+        <v>1.44</v>
+      </c>
+      <c r="AM44">
+        <v>1.66</v>
+      </c>
+      <c r="AN44">
         <v>3</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>3</v>
-      </c>
-      <c r="N44">
-        <v>3</v>
-      </c>
-      <c r="O44" t="s">
-        <v>100</v>
-      </c>
-      <c r="P44" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q44">
-        <v>2.63</v>
-      </c>
-      <c r="R44">
-        <v>1.95</v>
-      </c>
-      <c r="S44">
-        <v>5</v>
-      </c>
-      <c r="T44">
-        <v>1.57</v>
-      </c>
-      <c r="U44">
-        <v>2.25</v>
-      </c>
-      <c r="V44">
-        <v>3.75</v>
-      </c>
-      <c r="W44">
-        <v>1.25</v>
-      </c>
-      <c r="X44">
-        <v>11</v>
-      </c>
-      <c r="Y44">
-        <v>1.05</v>
-      </c>
-      <c r="Z44">
-        <v>1.9</v>
-      </c>
-      <c r="AA44">
-        <v>3.3</v>
-      </c>
-      <c r="AB44">
-        <v>4.5</v>
-      </c>
-      <c r="AC44">
-        <v>1.08</v>
-      </c>
-      <c r="AD44">
-        <v>7.37</v>
-      </c>
-      <c r="AE44">
-        <v>1.48</v>
-      </c>
-      <c r="AF44">
-        <v>2.63</v>
-      </c>
-      <c r="AG44">
-        <v>2.5</v>
-      </c>
-      <c r="AH44">
-        <v>1.5</v>
-      </c>
-      <c r="AI44">
-        <v>2.2</v>
-      </c>
-      <c r="AJ44">
-        <v>1.62</v>
-      </c>
-      <c r="AK44">
-        <v>1.2</v>
-      </c>
-      <c r="AL44">
-        <v>1.34</v>
-      </c>
-      <c r="AM44">
-        <v>1.83</v>
-      </c>
-      <c r="AN44">
-        <v>1</v>
       </c>
       <c r="AO44">
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AQ44">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AR44">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="AS44">
-        <v>1.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AT44">
-        <v>3.4</v>
+        <v>2.02</v>
       </c>
       <c r="AU44">
+        <v>6</v>
+      </c>
+      <c r="AV44">
+        <v>4</v>
+      </c>
+      <c r="AW44">
+        <v>9</v>
+      </c>
+      <c r="AX44">
+        <v>2</v>
+      </c>
+      <c r="AY44">
+        <v>19</v>
+      </c>
+      <c r="AZ44">
+        <v>6</v>
+      </c>
+      <c r="BA44">
         <v>5</v>
       </c>
-      <c r="AV44">
-        <v>6</v>
-      </c>
-      <c r="AW44">
-        <v>13</v>
-      </c>
-      <c r="AX44">
-        <v>6</v>
-      </c>
-      <c r="AY44">
-        <v>23</v>
-      </c>
-      <c r="AZ44">
-        <v>12</v>
-      </c>
-      <c r="BA44">
-        <v>6</v>
-      </c>
       <c r="BB44">
         <v>2</v>
       </c>
       <c r="BC44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD44">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BE44">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF44">
+        <v>3.2</v>
+      </c>
+      <c r="BG44">
+        <v>1.53</v>
+      </c>
+      <c r="BH44">
+        <v>2.32</v>
+      </c>
+      <c r="BI44">
+        <v>1.89</v>
+      </c>
+      <c r="BJ44">
+        <v>1.8</v>
+      </c>
+      <c r="BK44">
+        <v>2.4</v>
+      </c>
+      <c r="BL44">
+        <v>1.49</v>
+      </c>
+      <c r="BM44">
         <v>3.15</v>
       </c>
-      <c r="BG44">
-        <v>1.29</v>
-      </c>
-      <c r="BH44">
-        <v>3.15</v>
-      </c>
-      <c r="BI44">
-        <v>1.5</v>
-      </c>
-      <c r="BJ44">
-        <v>2.38</v>
-      </c>
-      <c r="BK44">
-        <v>1.82</v>
-      </c>
-      <c r="BL44">
-        <v>1.86</v>
-      </c>
-      <c r="BM44">
-        <v>2.28</v>
-      </c>
       <c r="BN44">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="BO44">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP44">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="45" spans="1:68">
@@ -10164,7 +10170,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10370,7 +10376,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10451,7 +10457,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ46">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR46">
         <v>2.39</v>
@@ -10576,7 +10582,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10654,7 +10660,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
         <v>0.5</v>
@@ -10782,7 +10788,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11400,7 +11406,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -12018,7 +12024,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12305,7 +12311,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ55">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR55">
         <v>1.6</v>
@@ -12594,7 +12600,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>7820372</v>
+        <v>7820371</v>
       </c>
       <c r="C57" t="s">
         <v>68</v>
@@ -12609,10 +12615,10 @@
         <v>4</v>
       </c>
       <c r="G57" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -12627,172 +12633,172 @@
         <v>1</v>
       </c>
       <c r="M57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>100</v>
       </c>
       <c r="Q57">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R57">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S57">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T57">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="U57">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V57">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="W57">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X57">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y57">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z57">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AA57">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB57">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AC57">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AD57">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AE57">
+        <v>1.67</v>
+      </c>
+      <c r="AF57">
+        <v>2.05</v>
+      </c>
+      <c r="AG57">
+        <v>3.4</v>
+      </c>
+      <c r="AH57">
+        <v>1.33</v>
+      </c>
+      <c r="AI57">
+        <v>2.5</v>
+      </c>
+      <c r="AJ57">
         <v>1.5</v>
       </c>
-      <c r="AF57">
-        <v>2.45</v>
-      </c>
-      <c r="AG57">
+      <c r="AK57">
+        <v>1.37</v>
+      </c>
+      <c r="AL57">
+        <v>1.41</v>
+      </c>
+      <c r="AM57">
+        <v>1.46</v>
+      </c>
+      <c r="AN57">
+        <v>1</v>
+      </c>
+      <c r="AO57">
+        <v>0</v>
+      </c>
+      <c r="AP57">
+        <v>1.2</v>
+      </c>
+      <c r="AQ57">
+        <v>0.2</v>
+      </c>
+      <c r="AR57">
+        <v>0.73</v>
+      </c>
+      <c r="AS57">
+        <v>1.21</v>
+      </c>
+      <c r="AT57">
+        <v>1.94</v>
+      </c>
+      <c r="AU57">
+        <v>5</v>
+      </c>
+      <c r="AV57">
+        <v>3</v>
+      </c>
+      <c r="AW57">
+        <v>9</v>
+      </c>
+      <c r="AX57">
+        <v>1</v>
+      </c>
+      <c r="AY57">
+        <v>17</v>
+      </c>
+      <c r="AZ57">
+        <v>4</v>
+      </c>
+      <c r="BA57">
+        <v>3</v>
+      </c>
+      <c r="BB57">
+        <v>2</v>
+      </c>
+      <c r="BC57">
+        <v>5</v>
+      </c>
+      <c r="BD57">
+        <v>1.92</v>
+      </c>
+      <c r="BE57">
+        <v>6.15</v>
+      </c>
+      <c r="BF57">
+        <v>2.49</v>
+      </c>
+      <c r="BG57">
+        <v>1.43</v>
+      </c>
+      <c r="BH57">
         <v>2.5</v>
       </c>
-      <c r="AH57">
-        <v>1.5</v>
-      </c>
-      <c r="AI57">
-        <v>2.1</v>
-      </c>
-      <c r="AJ57">
-        <v>1.67</v>
-      </c>
-      <c r="AK57">
-        <v>1.43</v>
-      </c>
-      <c r="AL57">
-        <v>1.36</v>
-      </c>
-      <c r="AM57">
-        <v>1.44</v>
-      </c>
-      <c r="AN57">
-        <v>1</v>
-      </c>
-      <c r="AO57">
-        <v>3</v>
-      </c>
-      <c r="AP57">
-        <v>1</v>
-      </c>
-      <c r="AQ57">
-        <v>1.75</v>
-      </c>
-      <c r="AR57">
-        <v>0.9</v>
-      </c>
-      <c r="AS57">
-        <v>1.63</v>
-      </c>
-      <c r="AT57">
-        <v>2.53</v>
-      </c>
-      <c r="AU57">
-        <v>4</v>
-      </c>
-      <c r="AV57">
-        <v>4</v>
-      </c>
-      <c r="AW57">
-        <v>6</v>
-      </c>
-      <c r="AX57">
-        <v>5</v>
-      </c>
-      <c r="AY57">
-        <v>13</v>
-      </c>
-      <c r="AZ57">
-        <v>12</v>
-      </c>
-      <c r="BA57">
-        <v>8</v>
-      </c>
-      <c r="BB57">
-        <v>6</v>
-      </c>
-      <c r="BC57">
-        <v>14</v>
-      </c>
-      <c r="BD57">
-        <v>2.06</v>
-      </c>
-      <c r="BE57">
-        <v>6.35</v>
-      </c>
-      <c r="BF57">
-        <v>2.22</v>
-      </c>
-      <c r="BG57">
-        <v>1.31</v>
-      </c>
-      <c r="BH57">
-        <v>3.1</v>
-      </c>
       <c r="BI57">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="BJ57">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="BK57">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="BL57">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="BM57">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="BN57">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="BO57">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP57">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="58" spans="1:68">
@@ -12800,7 +12806,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>7820371</v>
+        <v>7820372</v>
       </c>
       <c r="C58" t="s">
         <v>68</v>
@@ -12815,10 +12821,10 @@
         <v>4</v>
       </c>
       <c r="G58" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -12833,172 +12839,172 @@
         <v>1</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>100</v>
+        <v>197</v>
       </c>
       <c r="Q58">
+        <v>3.5</v>
+      </c>
+      <c r="R58">
+        <v>1.91</v>
+      </c>
+      <c r="S58">
         <v>3.6</v>
       </c>
-      <c r="R58">
-        <v>1.8</v>
-      </c>
-      <c r="S58">
+      <c r="T58">
+        <v>1.57</v>
+      </c>
+      <c r="U58">
+        <v>2.25</v>
+      </c>
+      <c r="V58">
+        <v>3.75</v>
+      </c>
+      <c r="W58">
+        <v>1.25</v>
+      </c>
+      <c r="X58">
+        <v>13</v>
+      </c>
+      <c r="Y58">
+        <v>1.04</v>
+      </c>
+      <c r="Z58">
+        <v>2.63</v>
+      </c>
+      <c r="AA58">
+        <v>3.1</v>
+      </c>
+      <c r="AB58">
+        <v>2.75</v>
+      </c>
+      <c r="AC58">
+        <v>1.11</v>
+      </c>
+      <c r="AD58">
+        <v>6.6</v>
+      </c>
+      <c r="AE58">
+        <v>1.5</v>
+      </c>
+      <c r="AF58">
+        <v>2.45</v>
+      </c>
+      <c r="AG58">
+        <v>2.5</v>
+      </c>
+      <c r="AH58">
+        <v>1.5</v>
+      </c>
+      <c r="AI58">
+        <v>2.1</v>
+      </c>
+      <c r="AJ58">
+        <v>1.67</v>
+      </c>
+      <c r="AK58">
+        <v>1.43</v>
+      </c>
+      <c r="AL58">
+        <v>1.36</v>
+      </c>
+      <c r="AM58">
+        <v>1.44</v>
+      </c>
+      <c r="AN58">
+        <v>1</v>
+      </c>
+      <c r="AO58">
+        <v>3</v>
+      </c>
+      <c r="AP58">
+        <v>1</v>
+      </c>
+      <c r="AQ58">
+        <v>2</v>
+      </c>
+      <c r="AR58">
+        <v>0.9</v>
+      </c>
+      <c r="AS58">
+        <v>1.63</v>
+      </c>
+      <c r="AT58">
+        <v>2.53</v>
+      </c>
+      <c r="AU58">
         <v>4</v>
       </c>
-      <c r="T58">
-        <v>1.73</v>
-      </c>
-      <c r="U58">
-        <v>2</v>
-      </c>
-      <c r="V58">
-        <v>4.5</v>
-      </c>
-      <c r="W58">
-        <v>1.18</v>
-      </c>
-      <c r="X58">
-        <v>17</v>
-      </c>
-      <c r="Y58">
-        <v>1.03</v>
-      </c>
-      <c r="Z58">
-        <v>2.6</v>
-      </c>
-      <c r="AA58">
-        <v>3</v>
-      </c>
-      <c r="AB58">
-        <v>2.9</v>
-      </c>
-      <c r="AC58">
-        <v>1.15</v>
-      </c>
-      <c r="AD58">
-        <v>5.2</v>
-      </c>
-      <c r="AE58">
-        <v>1.67</v>
-      </c>
-      <c r="AF58">
-        <v>2.05</v>
-      </c>
-      <c r="AG58">
-        <v>3.4</v>
-      </c>
-      <c r="AH58">
-        <v>1.33</v>
-      </c>
-      <c r="AI58">
-        <v>2.5</v>
-      </c>
-      <c r="AJ58">
-        <v>1.5</v>
-      </c>
-      <c r="AK58">
-        <v>1.37</v>
-      </c>
-      <c r="AL58">
-        <v>1.41</v>
-      </c>
-      <c r="AM58">
-        <v>1.46</v>
-      </c>
-      <c r="AN58">
-        <v>1</v>
-      </c>
-      <c r="AO58">
-        <v>0</v>
-      </c>
-      <c r="AP58">
-        <v>1.67</v>
-      </c>
-      <c r="AQ58">
-        <v>0.2</v>
-      </c>
-      <c r="AR58">
-        <v>0.73</v>
-      </c>
-      <c r="AS58">
+      <c r="AV58">
+        <v>4</v>
+      </c>
+      <c r="AW58">
+        <v>6</v>
+      </c>
+      <c r="AX58">
+        <v>5</v>
+      </c>
+      <c r="AY58">
+        <v>13</v>
+      </c>
+      <c r="AZ58">
+        <v>12</v>
+      </c>
+      <c r="BA58">
+        <v>8</v>
+      </c>
+      <c r="BB58">
+        <v>6</v>
+      </c>
+      <c r="BC58">
+        <v>14</v>
+      </c>
+      <c r="BD58">
+        <v>2.06</v>
+      </c>
+      <c r="BE58">
+        <v>6.35</v>
+      </c>
+      <c r="BF58">
+        <v>2.22</v>
+      </c>
+      <c r="BG58">
+        <v>1.31</v>
+      </c>
+      <c r="BH58">
+        <v>3.1</v>
+      </c>
+      <c r="BI58">
+        <v>1.57</v>
+      </c>
+      <c r="BJ58">
+        <v>2.15</v>
+      </c>
+      <c r="BK58">
+        <v>2</v>
+      </c>
+      <c r="BL58">
+        <v>1.68</v>
+      </c>
+      <c r="BM58">
+        <v>2.7</v>
+      </c>
+      <c r="BN58">
+        <v>1.38</v>
+      </c>
+      <c r="BO58">
+        <v>3.8</v>
+      </c>
+      <c r="BP58">
         <v>1.21</v>
-      </c>
-      <c r="AT58">
-        <v>1.94</v>
-      </c>
-      <c r="AU58">
-        <v>5</v>
-      </c>
-      <c r="AV58">
-        <v>3</v>
-      </c>
-      <c r="AW58">
-        <v>9</v>
-      </c>
-      <c r="AX58">
-        <v>1</v>
-      </c>
-      <c r="AY58">
-        <v>17</v>
-      </c>
-      <c r="AZ58">
-        <v>4</v>
-      </c>
-      <c r="BA58">
-        <v>3</v>
-      </c>
-      <c r="BB58">
-        <v>2</v>
-      </c>
-      <c r="BC58">
-        <v>5</v>
-      </c>
-      <c r="BD58">
-        <v>1.92</v>
-      </c>
-      <c r="BE58">
-        <v>6.15</v>
-      </c>
-      <c r="BF58">
-        <v>2.49</v>
-      </c>
-      <c r="BG58">
-        <v>1.43</v>
-      </c>
-      <c r="BH58">
-        <v>2.5</v>
-      </c>
-      <c r="BI58">
-        <v>1.8</v>
-      </c>
-      <c r="BJ58">
-        <v>1.85</v>
-      </c>
-      <c r="BK58">
-        <v>2.4</v>
-      </c>
-      <c r="BL58">
-        <v>1.47</v>
-      </c>
-      <c r="BM58">
-        <v>3.4</v>
-      </c>
-      <c r="BN58">
-        <v>1.26</v>
-      </c>
-      <c r="BO58">
-        <v>4.7</v>
-      </c>
-      <c r="BP58">
-        <v>1.12</v>
       </c>
     </row>
     <row r="59" spans="1:68">
@@ -13460,7 +13466,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14696,7 +14702,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14777,7 +14783,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ67">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR67">
         <v>1.78</v>
@@ -14902,7 +14908,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15726,7 +15732,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15932,7 +15938,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16550,7 +16556,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16756,7 +16762,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16837,7 +16843,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ77">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR77">
         <v>1.47</v>
@@ -16962,7 +16968,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17374,7 +17380,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17580,7 +17586,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17786,7 +17792,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18404,7 +18410,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18568,7 +18574,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>7820401</v>
+        <v>7820400</v>
       </c>
       <c r="C86" t="s">
         <v>68</v>
@@ -18583,55 +18589,55 @@
         <v>6</v>
       </c>
       <c r="G86" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H86" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86">
         <v>1</v>
       </c>
       <c r="L86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O86" t="s">
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="Q86">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R86">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="S86">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="T86">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U86">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V86">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="W86">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X86">
         <v>13</v>
@@ -18640,133 +18646,133 @@
         <v>1.04</v>
       </c>
       <c r="Z86">
+        <v>2.6</v>
+      </c>
+      <c r="AA86">
+        <v>2.75</v>
+      </c>
+      <c r="AB86">
+        <v>3.3</v>
+      </c>
+      <c r="AC86">
+        <v>1.14</v>
+      </c>
+      <c r="AD86">
+        <v>5.6</v>
+      </c>
+      <c r="AE86">
+        <v>1.57</v>
+      </c>
+      <c r="AF86">
         <v>2.25</v>
       </c>
-      <c r="AA86">
+      <c r="AG86">
+        <v>2.88</v>
+      </c>
+      <c r="AH86">
+        <v>1.4</v>
+      </c>
+      <c r="AI86">
+        <v>2.2</v>
+      </c>
+      <c r="AJ86">
+        <v>1.62</v>
+      </c>
+      <c r="AK86">
+        <v>1.34</v>
+      </c>
+      <c r="AL86">
+        <v>1.38</v>
+      </c>
+      <c r="AM86">
+        <v>1.52</v>
+      </c>
+      <c r="AN86">
+        <v>1</v>
+      </c>
+      <c r="AO86">
         <v>3</v>
       </c>
-      <c r="AB86">
-        <v>3.6</v>
-      </c>
-      <c r="AC86">
-        <v>1.12</v>
-      </c>
-      <c r="AD86">
-        <v>6.4</v>
-      </c>
-      <c r="AE86">
+      <c r="AP86">
         <v>1.5</v>
       </c>
-      <c r="AF86">
-        <v>2.37</v>
-      </c>
-      <c r="AG86">
-        <v>2.6</v>
-      </c>
-      <c r="AH86">
-        <v>1.48</v>
-      </c>
-      <c r="AI86">
-        <v>2.1</v>
-      </c>
-      <c r="AJ86">
-        <v>1.67</v>
-      </c>
-      <c r="AK86">
-        <v>1.31</v>
-      </c>
-      <c r="AL86">
-        <v>1.36</v>
-      </c>
-      <c r="AM86">
-        <v>1.6</v>
-      </c>
-      <c r="AN86">
-        <v>1.5</v>
-      </c>
-      <c r="AO86">
-        <v>1</v>
-      </c>
-      <c r="AP86">
-        <v>2</v>
-      </c>
       <c r="AQ86">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AR86">
-        <v>1.31</v>
+        <v>1.79</v>
       </c>
       <c r="AS86">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AT86">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="AU86">
+        <v>9</v>
+      </c>
+      <c r="AV86">
         <v>4</v>
       </c>
-      <c r="AV86">
-        <v>2</v>
-      </c>
       <c r="AW86">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX86">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AY86">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AZ86">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="BA86">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BB86">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC86">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD86">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="BE86">
         <v>6.4</v>
       </c>
       <c r="BF86">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="BG86">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BH86">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="BI86">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BJ86">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BK86">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="BL86">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="BM86">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="BN86">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="BO86">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BP86">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="87" spans="1:68">
@@ -18774,7 +18780,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>7820400</v>
+        <v>7820401</v>
       </c>
       <c r="C87" t="s">
         <v>68</v>
@@ -18789,55 +18795,55 @@
         <v>6</v>
       </c>
       <c r="G87" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H87" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87">
         <v>1</v>
       </c>
       <c r="L87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O87" t="s">
         <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>207</v>
+        <v>100</v>
       </c>
       <c r="Q87">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R87">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S87">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="T87">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="U87">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V87">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W87">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X87">
         <v>13</v>
@@ -18846,133 +18852,133 @@
         <v>1.04</v>
       </c>
       <c r="Z87">
+        <v>2.25</v>
+      </c>
+      <c r="AA87">
+        <v>3</v>
+      </c>
+      <c r="AB87">
+        <v>3.6</v>
+      </c>
+      <c r="AC87">
+        <v>1.12</v>
+      </c>
+      <c r="AD87">
+        <v>6.4</v>
+      </c>
+      <c r="AE87">
+        <v>1.5</v>
+      </c>
+      <c r="AF87">
+        <v>2.37</v>
+      </c>
+      <c r="AG87">
         <v>2.6</v>
       </c>
-      <c r="AA87">
-        <v>2.75</v>
-      </c>
-      <c r="AB87">
-        <v>3.3</v>
-      </c>
-      <c r="AC87">
-        <v>1.14</v>
-      </c>
-      <c r="AD87">
-        <v>5.6</v>
-      </c>
-      <c r="AE87">
-        <v>1.57</v>
-      </c>
-      <c r="AF87">
-        <v>2.25</v>
-      </c>
-      <c r="AG87">
-        <v>2.88</v>
-      </c>
       <c r="AH87">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AI87">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ87">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AK87">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AL87">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AM87">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AN87">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AR87">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="AS87">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AT87">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AU87">
+        <v>4</v>
+      </c>
+      <c r="AV87">
+        <v>2</v>
+      </c>
+      <c r="AW87">
+        <v>4</v>
+      </c>
+      <c r="AX87">
+        <v>8</v>
+      </c>
+      <c r="AY87">
         <v>9</v>
       </c>
-      <c r="AV87">
+      <c r="AZ87">
+        <v>14</v>
+      </c>
+      <c r="BA87">
+        <v>2</v>
+      </c>
+      <c r="BB87">
         <v>4</v>
       </c>
-      <c r="AW87">
-        <v>7</v>
-      </c>
-      <c r="AX87">
-        <v>1</v>
-      </c>
-      <c r="AY87">
-        <v>18</v>
-      </c>
-      <c r="AZ87">
-        <v>5</v>
-      </c>
-      <c r="BA87">
-        <v>10</v>
-      </c>
-      <c r="BB87">
-        <v>1</v>
-      </c>
       <c r="BC87">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BD87">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="BE87">
         <v>6.4</v>
       </c>
       <c r="BF87">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BG87">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BH87">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="BI87">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BJ87">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="BK87">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="BL87">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="BM87">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="BN87">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="BO87">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP87">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="88" spans="1:68">
@@ -19022,7 +19028,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19100,10 +19106,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ88">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR88">
         <v>1.23</v>
@@ -19228,7 +19234,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19434,7 +19440,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19846,7 +19852,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20052,7 +20058,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q93">
         <v>3.75</v>
@@ -20670,7 +20676,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20876,7 +20882,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21452,7 +21458,7 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>7820415</v>
+        <v>7820414</v>
       </c>
       <c r="C100" t="s">
         <v>68</v>
@@ -21467,43 +21473,43 @@
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="H100" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O100" t="s">
+        <v>164</v>
+      </c>
+      <c r="P100" t="s">
         <v>100</v>
       </c>
-      <c r="P100" t="s">
-        <v>186</v>
-      </c>
       <c r="Q100">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R100">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S100">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T100">
         <v>1.53</v>
@@ -21524,13 +21530,13 @@
         <v>1.05</v>
       </c>
       <c r="Z100">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AA100">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AB100">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AC100">
         <v>1.1</v>
@@ -21551,73 +21557,73 @@
         <v>1.57</v>
       </c>
       <c r="AI100">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AJ100">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AK100">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AL100">
+        <v>1.34</v>
+      </c>
+      <c r="AM100">
+        <v>1.6</v>
+      </c>
+      <c r="AN100">
         <v>1.33</v>
       </c>
-      <c r="AM100">
+      <c r="AO100">
+        <v>2.33</v>
+      </c>
+      <c r="AP100">
         <v>1.75</v>
       </c>
-      <c r="AN100">
-        <v>1.5</v>
-      </c>
-      <c r="AO100">
-        <v>0.33</v>
-      </c>
-      <c r="AP100">
-        <v>0.75</v>
-      </c>
       <c r="AQ100">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="AR100">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AS100">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="AT100">
-        <v>2.95</v>
+        <v>3.31</v>
       </c>
       <c r="AU100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV100">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW100">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX100">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY100">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ100">
+        <v>17</v>
+      </c>
+      <c r="BA100">
+        <v>3</v>
+      </c>
+      <c r="BB100">
         <v>10</v>
       </c>
-      <c r="BA100">
-        <v>5</v>
-      </c>
-      <c r="BB100">
-        <v>4</v>
-      </c>
       <c r="BC100">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD100">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BE100">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF100">
         <v>2.65</v>
@@ -21658,7 +21664,7 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>7820414</v>
+        <v>7820415</v>
       </c>
       <c r="C101" t="s">
         <v>68</v>
@@ -21673,43 +21679,43 @@
         <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="H101" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101">
         <v>1</v>
       </c>
       <c r="L101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="Q101">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R101">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S101">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T101">
         <v>1.53</v>
@@ -21730,13 +21736,13 @@
         <v>1.05</v>
       </c>
       <c r="Z101">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AA101">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB101">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AC101">
         <v>1.1</v>
@@ -21757,73 +21763,73 @@
         <v>1.57</v>
       </c>
       <c r="AI101">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AJ101">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AK101">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AL101">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AM101">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AN101">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO101">
-        <v>2.33</v>
+        <v>0.33</v>
       </c>
       <c r="AP101">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="AQ101">
-        <v>1.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR101">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AS101">
-        <v>1.58</v>
+        <v>1.13</v>
       </c>
       <c r="AT101">
-        <v>3.31</v>
+        <v>2.95</v>
       </c>
       <c r="AU101">
+        <v>6</v>
+      </c>
+      <c r="AV101">
+        <v>4</v>
+      </c>
+      <c r="AW101">
         <v>7</v>
       </c>
-      <c r="AV101">
-        <v>2</v>
-      </c>
-      <c r="AW101">
+      <c r="AX101">
+        <v>4</v>
+      </c>
+      <c r="AY101">
+        <v>16</v>
+      </c>
+      <c r="AZ101">
+        <v>10</v>
+      </c>
+      <c r="BA101">
         <v>5</v>
       </c>
-      <c r="AX101">
-        <v>11</v>
-      </c>
-      <c r="AY101">
-        <v>12</v>
-      </c>
-      <c r="AZ101">
-        <v>17</v>
-      </c>
-      <c r="BA101">
-        <v>3</v>
-      </c>
       <c r="BB101">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BC101">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BD101">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BE101">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BF101">
         <v>2.65</v>
@@ -23142,7 +23148,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23348,7 +23354,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23760,7 +23766,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -23966,7 +23972,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24378,7 +24384,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24584,7 +24590,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24790,7 +24796,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -24996,7 +25002,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25160,7 +25166,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>7820435</v>
+        <v>7820430</v>
       </c>
       <c r="C118" t="s">
         <v>68</v>
@@ -25169,40 +25175,40 @@
         <v>69</v>
       </c>
       <c r="E118" s="2">
-        <v>45723.79166666666</v>
+        <v>45720.8125</v>
       </c>
       <c r="F118">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G118" t="s">
         <v>85</v>
       </c>
       <c r="H118" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="I118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N118">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O118" t="s">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="P118" t="s">
-        <v>221</v>
+        <v>100</v>
       </c>
       <c r="Q118">
         <v>4.33</v>
@@ -25211,19 +25217,19 @@
         <v>1.83</v>
       </c>
       <c r="S118">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T118">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U118">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V118">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="W118">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X118">
         <v>15</v>
@@ -25232,25 +25238,25 @@
         <v>1.03</v>
       </c>
       <c r="Z118">
-        <v>3.57</v>
+        <v>3.1</v>
       </c>
       <c r="AA118">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AB118">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AC118">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AD118">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AE118">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF118">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG118">
         <v>2.88</v>
@@ -25259,106 +25265,106 @@
         <v>1.4</v>
       </c>
       <c r="AI118">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AJ118">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK118">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL118">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AM118">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AN118">
         <v>1.33</v>
       </c>
       <c r="AO118">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="AP118">
         <v>1</v>
       </c>
       <c r="AQ118">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR118">
         <v>1.5</v>
       </c>
       <c r="AS118">
-        <v>1.55</v>
+        <v>0.95</v>
       </c>
       <c r="AT118">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="AU118">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="AV118">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="AW118">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="AX118">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="AY118">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="AZ118">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="BA118">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BB118">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BC118">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BD118">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="BE118">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="BF118">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="BG118">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BH118">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="BI118">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="BJ118">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="BK118">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="BL118">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="BM118">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BN118">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BO118">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BP118">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="119" spans="1:68">
@@ -25366,7 +25372,7 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>7820436</v>
+        <v>7820431</v>
       </c>
       <c r="C119" t="s">
         <v>68</v>
@@ -25375,166 +25381,166 @@
         <v>69</v>
       </c>
       <c r="E119" s="2">
-        <v>45723.79166666666</v>
+        <v>45720.83333333334</v>
       </c>
       <c r="F119">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G119" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H119" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I119">
         <v>0</v>
       </c>
       <c r="J119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N119">
         <v>1</v>
       </c>
       <c r="O119" t="s">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
       <c r="Q119">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R119">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S119">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="T119">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="U119">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V119">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="W119">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X119">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y119">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z119">
-        <v>1.7</v>
+        <v>2.41</v>
       </c>
       <c r="AA119">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB119">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="AC119">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AD119">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AE119">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AF119">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG119">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AH119">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AI119">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AJ119">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AK119">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AL119">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AM119">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="AN119">
-        <v>0.25</v>
+        <v>1.67</v>
       </c>
       <c r="AO119">
-        <v>0.67</v>
+        <v>1.75</v>
       </c>
       <c r="AP119">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AQ119">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AR119">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AS119">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AT119">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="AU119">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="AV119">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="AW119">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="AX119">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AY119">
-        <v>20</v>
+        <v>-1</v>
       </c>
       <c r="AZ119">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="BA119">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BB119">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BC119">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="BD119">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="BE119">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF119">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="BG119">
         <v>1.49</v>
@@ -25543,28 +25549,28 @@
         <v>2.4</v>
       </c>
       <c r="BI119">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BJ119">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="BK119">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BL119">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BM119">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BN119">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO119">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP119">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="120" spans="1:68">
@@ -25572,7 +25578,7 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>7820437</v>
+        <v>7820435</v>
       </c>
       <c r="C120" t="s">
         <v>68</v>
@@ -25581,196 +25587,196 @@
         <v>69</v>
       </c>
       <c r="E120" s="2">
-        <v>45723.88541666666</v>
+        <v>45723.79166666666</v>
       </c>
       <c r="F120">
         <v>9</v>
       </c>
       <c r="G120" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H120" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N120">
         <v>3</v>
       </c>
       <c r="O120" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q120">
+        <v>4.33</v>
+      </c>
+      <c r="R120">
+        <v>1.83</v>
+      </c>
+      <c r="S120">
+        <v>3.2</v>
+      </c>
+      <c r="T120">
+        <v>1.62</v>
+      </c>
+      <c r="U120">
+        <v>2.2</v>
+      </c>
+      <c r="V120">
         <v>4</v>
       </c>
-      <c r="R120">
-        <v>1.91</v>
-      </c>
-      <c r="S120">
-        <v>3.25</v>
-      </c>
-      <c r="T120">
+      <c r="W120">
+        <v>1.22</v>
+      </c>
+      <c r="X120">
+        <v>15</v>
+      </c>
+      <c r="Y120">
+        <v>1.03</v>
+      </c>
+      <c r="Z120">
+        <v>3.57</v>
+      </c>
+      <c r="AA120">
+        <v>2.83</v>
+      </c>
+      <c r="AB120">
+        <v>2.28</v>
+      </c>
+      <c r="AC120">
+        <v>1.1</v>
+      </c>
+      <c r="AD120">
+        <v>7</v>
+      </c>
+      <c r="AE120">
         <v>1.57</v>
       </c>
-      <c r="U120">
+      <c r="AF120">
         <v>2.25</v>
       </c>
-      <c r="V120">
-        <v>3.75</v>
-      </c>
-      <c r="W120">
-        <v>1.25</v>
-      </c>
-      <c r="X120">
-        <v>11</v>
-      </c>
-      <c r="Y120">
-        <v>1.05</v>
-      </c>
-      <c r="Z120">
-        <v>3</v>
-      </c>
-      <c r="AA120">
-        <v>3.2</v>
-      </c>
-      <c r="AB120">
-        <v>2.4</v>
-      </c>
-      <c r="AC120">
-        <v>1.07</v>
-      </c>
-      <c r="AD120">
-        <v>9</v>
-      </c>
-      <c r="AE120">
-        <v>1.35</v>
-      </c>
-      <c r="AF120">
-        <v>3.15</v>
-      </c>
       <c r="AG120">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AH120">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI120">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AJ120">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AK120">
         <v>1.55</v>
       </c>
       <c r="AL120">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AM120">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN120">
-        <v>2.6</v>
+        <v>1.25</v>
       </c>
       <c r="AO120">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="AP120">
-        <v>2.17</v>
+        <v>1</v>
       </c>
       <c r="AQ120">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AR120">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AS120">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AT120">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="AU120">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV120">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW120">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX120">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY120">
+        <v>12</v>
+      </c>
+      <c r="AZ120">
         <v>13</v>
       </c>
-      <c r="AZ120">
-        <v>9</v>
-      </c>
       <c r="BA120">
+        <v>2</v>
+      </c>
+      <c r="BB120">
+        <v>3</v>
+      </c>
+      <c r="BC120">
         <v>5</v>
       </c>
-      <c r="BB120">
-        <v>2</v>
-      </c>
-      <c r="BC120">
-        <v>7</v>
-      </c>
       <c r="BD120">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="BE120">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="BF120">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="BG120">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BH120">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BI120">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="BJ120">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BK120">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="BL120">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BM120">
         <v>3.05</v>
       </c>
       <c r="BN120">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="BO120">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BP120">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="121" spans="1:68">
@@ -25778,7 +25784,7 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>7820438</v>
+        <v>7820436</v>
       </c>
       <c r="C121" t="s">
         <v>68</v>
@@ -25787,76 +25793,76 @@
         <v>69</v>
       </c>
       <c r="E121" s="2">
-        <v>45724.70833333334</v>
+        <v>45723.79166666666</v>
       </c>
       <c r="F121">
         <v>9</v>
       </c>
       <c r="G121" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H121" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L121">
         <v>1</v>
       </c>
       <c r="M121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O121" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P121" t="s">
-        <v>223</v>
+        <v>100</v>
       </c>
       <c r="Q121">
+        <v>2.4</v>
+      </c>
+      <c r="R121">
+        <v>1.91</v>
+      </c>
+      <c r="S121">
+        <v>7</v>
+      </c>
+      <c r="T121">
+        <v>1.62</v>
+      </c>
+      <c r="U121">
+        <v>2.2</v>
+      </c>
+      <c r="V121">
         <v>4</v>
       </c>
-      <c r="R121">
-        <v>1.8</v>
-      </c>
-      <c r="S121">
-        <v>3.75</v>
-      </c>
-      <c r="T121">
-        <v>1.73</v>
-      </c>
-      <c r="U121">
-        <v>2</v>
-      </c>
-      <c r="V121">
-        <v>5</v>
-      </c>
       <c r="W121">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X121">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Y121">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z121">
-        <v>2.92</v>
+        <v>1.7</v>
       </c>
       <c r="AA121">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AB121">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="AC121">
         <v>1.12</v>
@@ -25865,118 +25871,118 @@
         <v>6.2</v>
       </c>
       <c r="AE121">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF121">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG121">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AH121">
+        <v>1.44</v>
+      </c>
+      <c r="AI121">
+        <v>2.63</v>
+      </c>
+      <c r="AJ121">
+        <v>1.44</v>
+      </c>
+      <c r="AK121">
+        <v>1.18</v>
+      </c>
+      <c r="AL121">
+        <v>1.32</v>
+      </c>
+      <c r="AM121">
+        <v>1.93</v>
+      </c>
+      <c r="AN121">
+        <v>0.25</v>
+      </c>
+      <c r="AO121">
+        <v>0.67</v>
+      </c>
+      <c r="AP121">
+        <v>0.8</v>
+      </c>
+      <c r="AQ121">
+        <v>0.5</v>
+      </c>
+      <c r="AR121">
         <v>1.33</v>
       </c>
-      <c r="AI121">
-        <v>2.5</v>
-      </c>
-      <c r="AJ121">
-        <v>1.5</v>
-      </c>
-      <c r="AK121">
-        <v>1.37</v>
-      </c>
-      <c r="AL121">
+      <c r="AS121">
         <v>1.38</v>
-      </c>
-      <c r="AM121">
-        <v>1.5</v>
-      </c>
-      <c r="AN121">
-        <v>2.5</v>
-      </c>
-      <c r="AO121">
-        <v>1.33</v>
-      </c>
-      <c r="AP121">
-        <v>2</v>
-      </c>
-      <c r="AQ121">
-        <v>1.75</v>
-      </c>
-      <c r="AR121">
-        <v>1.76</v>
-      </c>
-      <c r="AS121">
-        <v>0.95</v>
       </c>
       <c r="AT121">
         <v>2.71</v>
       </c>
       <c r="AU121">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV121">
         <v>4</v>
       </c>
       <c r="AW121">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX121">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY121">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AZ121">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA121">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB121">
         <v>6</v>
       </c>
       <c r="BC121">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD121">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="BE121">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF121">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="BG121">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="BH121">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="BI121">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="BJ121">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="BK121">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="BL121">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="BM121">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="BN121">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="BO121">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP121">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="122" spans="1:68">
@@ -25984,7 +25990,7 @@
         <v>121</v>
       </c>
       <c r="B122">
-        <v>7820439</v>
+        <v>7820437</v>
       </c>
       <c r="C122" t="s">
         <v>68</v>
@@ -25993,34 +25999,34 @@
         <v>69</v>
       </c>
       <c r="E122" s="2">
-        <v>45724.80208333334</v>
+        <v>45723.88541666666</v>
       </c>
       <c r="F122">
         <v>9</v>
       </c>
       <c r="G122" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H122" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I122">
         <v>0</v>
       </c>
       <c r="J122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="M122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O122" t="s">
         <v>100</v>
@@ -26029,19 +26035,19 @@
         <v>224</v>
       </c>
       <c r="Q122">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="R122">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S122">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="T122">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="U122">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V122">
         <v>3.75</v>
@@ -26056,31 +26062,31 @@
         <v>1.05</v>
       </c>
       <c r="Z122">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="AA122">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AB122">
-        <v>4.18</v>
+        <v>2.4</v>
       </c>
       <c r="AC122">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AD122">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AE122">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF122">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="AG122">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH122">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI122">
         <v>2.1</v>
@@ -26089,99 +26095,923 @@
         <v>1.67</v>
       </c>
       <c r="AK122">
+        <v>1.55</v>
+      </c>
+      <c r="AL122">
+        <v>1.36</v>
+      </c>
+      <c r="AM122">
+        <v>1.33</v>
+      </c>
+      <c r="AN122">
+        <v>2.6</v>
+      </c>
+      <c r="AO122">
+        <v>1.33</v>
+      </c>
+      <c r="AP122">
+        <v>2.17</v>
+      </c>
+      <c r="AQ122">
+        <v>1.75</v>
+      </c>
+      <c r="AR122">
+        <v>2.07</v>
+      </c>
+      <c r="AS122">
+        <v>1.38</v>
+      </c>
+      <c r="AT122">
+        <v>3.45</v>
+      </c>
+      <c r="AU122">
+        <v>6</v>
+      </c>
+      <c r="AV122">
+        <v>6</v>
+      </c>
+      <c r="AW122">
+        <v>6</v>
+      </c>
+      <c r="AX122">
+        <v>2</v>
+      </c>
+      <c r="AY122">
+        <v>13</v>
+      </c>
+      <c r="AZ122">
+        <v>9</v>
+      </c>
+      <c r="BA122">
+        <v>5</v>
+      </c>
+      <c r="BB122">
+        <v>2</v>
+      </c>
+      <c r="BC122">
+        <v>7</v>
+      </c>
+      <c r="BD122">
+        <v>1.95</v>
+      </c>
+      <c r="BE122">
+        <v>6.25</v>
+      </c>
+      <c r="BF122">
+        <v>2.07</v>
+      </c>
+      <c r="BG122">
+        <v>1.5</v>
+      </c>
+      <c r="BH122">
+        <v>2.38</v>
+      </c>
+      <c r="BI122">
+        <v>1.95</v>
+      </c>
+      <c r="BJ122">
+        <v>1.85</v>
+      </c>
+      <c r="BK122">
+        <v>2.35</v>
+      </c>
+      <c r="BL122">
+        <v>1.5</v>
+      </c>
+      <c r="BM122">
+        <v>3.05</v>
+      </c>
+      <c r="BN122">
+        <v>1.3</v>
+      </c>
+      <c r="BO122">
+        <v>4.1</v>
+      </c>
+      <c r="BP122">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7820438</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45724.70833333334</v>
+      </c>
+      <c r="F123">
+        <v>9</v>
+      </c>
+      <c r="G123" t="s">
+        <v>79</v>
+      </c>
+      <c r="H123" t="s">
+        <v>76</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>2</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>2</v>
+      </c>
+      <c r="N123">
+        <v>3</v>
+      </c>
+      <c r="O123" t="s">
+        <v>176</v>
+      </c>
+      <c r="P123" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q123">
+        <v>4</v>
+      </c>
+      <c r="R123">
+        <v>1.8</v>
+      </c>
+      <c r="S123">
+        <v>3.75</v>
+      </c>
+      <c r="T123">
+        <v>1.73</v>
+      </c>
+      <c r="U123">
+        <v>2</v>
+      </c>
+      <c r="V123">
+        <v>5</v>
+      </c>
+      <c r="W123">
+        <v>1.17</v>
+      </c>
+      <c r="X123">
+        <v>17</v>
+      </c>
+      <c r="Y123">
+        <v>1.03</v>
+      </c>
+      <c r="Z123">
+        <v>2.92</v>
+      </c>
+      <c r="AA123">
+        <v>2.74</v>
+      </c>
+      <c r="AB123">
+        <v>2.75</v>
+      </c>
+      <c r="AC123">
+        <v>1.12</v>
+      </c>
+      <c r="AD123">
+        <v>6.2</v>
+      </c>
+      <c r="AE123">
+        <v>1.55</v>
+      </c>
+      <c r="AF123">
+        <v>2.25</v>
+      </c>
+      <c r="AG123">
+        <v>3.4</v>
+      </c>
+      <c r="AH123">
+        <v>1.33</v>
+      </c>
+      <c r="AI123">
+        <v>2.5</v>
+      </c>
+      <c r="AJ123">
+        <v>1.5</v>
+      </c>
+      <c r="AK123">
+        <v>1.37</v>
+      </c>
+      <c r="AL123">
+        <v>1.38</v>
+      </c>
+      <c r="AM123">
+        <v>1.5</v>
+      </c>
+      <c r="AN123">
+        <v>2.5</v>
+      </c>
+      <c r="AO123">
+        <v>1.25</v>
+      </c>
+      <c r="AP123">
+        <v>2</v>
+      </c>
+      <c r="AQ123">
+        <v>1.6</v>
+      </c>
+      <c r="AR123">
+        <v>1.76</v>
+      </c>
+      <c r="AS123">
+        <v>0.95</v>
+      </c>
+      <c r="AT123">
+        <v>2.71</v>
+      </c>
+      <c r="AU123">
+        <v>5</v>
+      </c>
+      <c r="AV123">
+        <v>4</v>
+      </c>
+      <c r="AW123">
+        <v>7</v>
+      </c>
+      <c r="AX123">
+        <v>4</v>
+      </c>
+      <c r="AY123">
+        <v>15</v>
+      </c>
+      <c r="AZ123">
+        <v>9</v>
+      </c>
+      <c r="BA123">
+        <v>3</v>
+      </c>
+      <c r="BB123">
+        <v>6</v>
+      </c>
+      <c r="BC123">
+        <v>9</v>
+      </c>
+      <c r="BD123">
+        <v>1.98</v>
+      </c>
+      <c r="BE123">
+        <v>6.4</v>
+      </c>
+      <c r="BF123">
+        <v>2</v>
+      </c>
+      <c r="BG123">
+        <v>1.43</v>
+      </c>
+      <c r="BH123">
+        <v>2.63</v>
+      </c>
+      <c r="BI123">
+        <v>1.74</v>
+      </c>
+      <c r="BJ123">
+        <v>2.02</v>
+      </c>
+      <c r="BK123">
+        <v>2.22</v>
+      </c>
+      <c r="BL123">
+        <v>1.62</v>
+      </c>
+      <c r="BM123">
+        <v>2.85</v>
+      </c>
+      <c r="BN123">
+        <v>1.37</v>
+      </c>
+      <c r="BO123">
+        <v>3.9</v>
+      </c>
+      <c r="BP123">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7820439</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45724.80208333334</v>
+      </c>
+      <c r="F124">
+        <v>9</v>
+      </c>
+      <c r="G124" t="s">
+        <v>97</v>
+      </c>
+      <c r="H124" t="s">
+        <v>93</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>1</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
+        <v>100</v>
+      </c>
+      <c r="P124" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q124">
+        <v>2.63</v>
+      </c>
+      <c r="R124">
+        <v>2</v>
+      </c>
+      <c r="S124">
+        <v>5</v>
+      </c>
+      <c r="T124">
+        <v>1.53</v>
+      </c>
+      <c r="U124">
+        <v>2.38</v>
+      </c>
+      <c r="V124">
+        <v>3.75</v>
+      </c>
+      <c r="W124">
+        <v>1.25</v>
+      </c>
+      <c r="X124">
+        <v>11</v>
+      </c>
+      <c r="Y124">
+        <v>1.05</v>
+      </c>
+      <c r="Z124">
+        <v>1.9</v>
+      </c>
+      <c r="AA124">
+        <v>3.24</v>
+      </c>
+      <c r="AB124">
+        <v>4.18</v>
+      </c>
+      <c r="AC124">
+        <v>1.08</v>
+      </c>
+      <c r="AD124">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE124">
+        <v>1.38</v>
+      </c>
+      <c r="AF124">
+        <v>2.95</v>
+      </c>
+      <c r="AG124">
+        <v>2.4</v>
+      </c>
+      <c r="AH124">
+        <v>1.53</v>
+      </c>
+      <c r="AI124">
+        <v>2.1</v>
+      </c>
+      <c r="AJ124">
+        <v>1.67</v>
+      </c>
+      <c r="AK124">
         <v>1.22</v>
       </c>
-      <c r="AL122">
+      <c r="AL124">
         <v>1.32</v>
       </c>
-      <c r="AM122">
+      <c r="AM124">
         <v>1.83</v>
       </c>
-      <c r="AN122">
-        <v>2</v>
-      </c>
-      <c r="AO122">
+      <c r="AN124">
+        <v>2</v>
+      </c>
+      <c r="AO124">
         <v>1.25</v>
       </c>
-      <c r="AP122">
+      <c r="AP124">
         <v>1.5</v>
       </c>
-      <c r="AQ122">
+      <c r="AQ124">
         <v>1.6</v>
       </c>
-      <c r="AR122">
+      <c r="AR124">
         <v>1.45</v>
       </c>
-      <c r="AS122">
+      <c r="AS124">
         <v>1.28</v>
       </c>
-      <c r="AT122">
+      <c r="AT124">
         <v>2.73</v>
       </c>
-      <c r="AU122">
-        <v>-1</v>
-      </c>
-      <c r="AV122">
-        <v>-1</v>
-      </c>
-      <c r="AW122">
-        <v>-1</v>
-      </c>
-      <c r="AX122">
-        <v>-1</v>
-      </c>
-      <c r="AY122">
-        <v>-1</v>
-      </c>
-      <c r="AZ122">
-        <v>-1</v>
-      </c>
-      <c r="BA122">
-        <v>-1</v>
-      </c>
-      <c r="BB122">
-        <v>-1</v>
-      </c>
-      <c r="BC122">
-        <v>-1</v>
-      </c>
-      <c r="BD122">
+      <c r="AU124">
+        <v>4</v>
+      </c>
+      <c r="AV124">
+        <v>6</v>
+      </c>
+      <c r="AW124">
+        <v>13</v>
+      </c>
+      <c r="AX124">
+        <v>7</v>
+      </c>
+      <c r="AY124">
+        <v>24</v>
+      </c>
+      <c r="AZ124">
+        <v>16</v>
+      </c>
+      <c r="BA124">
+        <v>6</v>
+      </c>
+      <c r="BB124">
+        <v>1</v>
+      </c>
+      <c r="BC124">
+        <v>7</v>
+      </c>
+      <c r="BD124">
         <v>1.41</v>
       </c>
-      <c r="BE122">
+      <c r="BE124">
         <v>7</v>
       </c>
-      <c r="BF122">
+      <c r="BF124">
         <v>3.2</v>
       </c>
-      <c r="BG122">
+      <c r="BG124">
         <v>1.39</v>
       </c>
-      <c r="BH122">
+      <c r="BH124">
         <v>2.77</v>
       </c>
-      <c r="BI122">
+      <c r="BI124">
         <v>1.68</v>
       </c>
-      <c r="BJ122">
+      <c r="BJ124">
         <v>2.11</v>
       </c>
-      <c r="BK122">
+      <c r="BK124">
         <v>2.11</v>
       </c>
-      <c r="BL122">
+      <c r="BL124">
         <v>1.68</v>
       </c>
-      <c r="BM122">
+      <c r="BM124">
         <v>2.7</v>
       </c>
-      <c r="BN122">
+      <c r="BN124">
         <v>1.41</v>
       </c>
-      <c r="BO122">
+      <c r="BO124">
         <v>3.65</v>
       </c>
-      <c r="BP122">
+      <c r="BP124">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7820440</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45724.89583333334</v>
+      </c>
+      <c r="F125">
+        <v>9</v>
+      </c>
+      <c r="G125" t="s">
+        <v>82</v>
+      </c>
+      <c r="H125" t="s">
+        <v>74</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125" t="s">
+        <v>100</v>
+      </c>
+      <c r="P125" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q125">
+        <v>3.75</v>
+      </c>
+      <c r="R125">
+        <v>1.8</v>
+      </c>
+      <c r="S125">
+        <v>4</v>
+      </c>
+      <c r="T125">
+        <v>1.73</v>
+      </c>
+      <c r="U125">
+        <v>2</v>
+      </c>
+      <c r="V125">
+        <v>5</v>
+      </c>
+      <c r="W125">
+        <v>1.17</v>
+      </c>
+      <c r="X125">
+        <v>17</v>
+      </c>
+      <c r="Y125">
+        <v>1.03</v>
+      </c>
+      <c r="Z125">
+        <v>2.7</v>
+      </c>
+      <c r="AA125">
+        <v>2.7</v>
+      </c>
+      <c r="AB125">
+        <v>3.1</v>
+      </c>
+      <c r="AC125">
+        <v>1.14</v>
+      </c>
+      <c r="AD125">
+        <v>5.6</v>
+      </c>
+      <c r="AE125">
+        <v>1.73</v>
+      </c>
+      <c r="AF125">
+        <v>1.98</v>
+      </c>
+      <c r="AG125">
+        <v>3.5</v>
+      </c>
+      <c r="AH125">
+        <v>1.3</v>
+      </c>
+      <c r="AI125">
+        <v>2.5</v>
+      </c>
+      <c r="AJ125">
+        <v>1.5</v>
+      </c>
+      <c r="AK125">
+        <v>1.36</v>
+      </c>
+      <c r="AL125">
+        <v>1.43</v>
+      </c>
+      <c r="AM125">
+        <v>1.44</v>
+      </c>
+      <c r="AN125">
+        <v>1.25</v>
+      </c>
+      <c r="AO125">
+        <v>1</v>
+      </c>
+      <c r="AP125">
+        <v>1.2</v>
+      </c>
+      <c r="AQ125">
+        <v>1</v>
+      </c>
+      <c r="AR125">
+        <v>1.24</v>
+      </c>
+      <c r="AS125">
+        <v>1.2</v>
+      </c>
+      <c r="AT125">
+        <v>2.44</v>
+      </c>
+      <c r="AU125">
+        <v>5</v>
+      </c>
+      <c r="AV125">
+        <v>6</v>
+      </c>
+      <c r="AW125">
+        <v>4</v>
+      </c>
+      <c r="AX125">
+        <v>7</v>
+      </c>
+      <c r="AY125">
+        <v>9</v>
+      </c>
+      <c r="AZ125">
+        <v>16</v>
+      </c>
+      <c r="BA125">
+        <v>2</v>
+      </c>
+      <c r="BB125">
+        <v>4</v>
+      </c>
+      <c r="BC125">
+        <v>6</v>
+      </c>
+      <c r="BD125">
+        <v>1.67</v>
+      </c>
+      <c r="BE125">
+        <v>6.4</v>
+      </c>
+      <c r="BF125">
+        <v>2.48</v>
+      </c>
+      <c r="BG125">
+        <v>1.43</v>
+      </c>
+      <c r="BH125">
+        <v>2.63</v>
+      </c>
+      <c r="BI125">
+        <v>1.74</v>
+      </c>
+      <c r="BJ125">
+        <v>2.02</v>
+      </c>
+      <c r="BK125">
+        <v>2.22</v>
+      </c>
+      <c r="BL125">
+        <v>1.62</v>
+      </c>
+      <c r="BM125">
+        <v>2.85</v>
+      </c>
+      <c r="BN125">
+        <v>1.37</v>
+      </c>
+      <c r="BO125">
+        <v>3.9</v>
+      </c>
+      <c r="BP125">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7820441</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45724.89583333334</v>
+      </c>
+      <c r="F126">
+        <v>9</v>
+      </c>
+      <c r="G126" t="s">
+        <v>88</v>
+      </c>
+      <c r="H126" t="s">
+        <v>75</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>1</v>
+      </c>
+      <c r="N126">
+        <v>2</v>
+      </c>
+      <c r="O126" t="s">
+        <v>177</v>
+      </c>
+      <c r="P126" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q126">
+        <v>3.25</v>
+      </c>
+      <c r="R126">
+        <v>1.83</v>
+      </c>
+      <c r="S126">
+        <v>4.33</v>
+      </c>
+      <c r="T126">
+        <v>1.67</v>
+      </c>
+      <c r="U126">
+        <v>2.1</v>
+      </c>
+      <c r="V126">
+        <v>4.33</v>
+      </c>
+      <c r="W126">
+        <v>1.2</v>
+      </c>
+      <c r="X126">
+        <v>15</v>
+      </c>
+      <c r="Y126">
+        <v>1.03</v>
+      </c>
+      <c r="Z126">
+        <v>2.32</v>
+      </c>
+      <c r="AA126">
+        <v>2.63</v>
+      </c>
+      <c r="AB126">
+        <v>3.84</v>
+      </c>
+      <c r="AC126">
+        <v>1.07</v>
+      </c>
+      <c r="AD126">
+        <v>9</v>
+      </c>
+      <c r="AE126">
+        <v>1.55</v>
+      </c>
+      <c r="AF126">
+        <v>2.25</v>
+      </c>
+      <c r="AG126">
+        <v>2.88</v>
+      </c>
+      <c r="AH126">
+        <v>1.4</v>
+      </c>
+      <c r="AI126">
+        <v>2.25</v>
+      </c>
+      <c r="AJ126">
+        <v>1.57</v>
+      </c>
+      <c r="AK126">
+        <v>1.28</v>
+      </c>
+      <c r="AL126">
+        <v>1.39</v>
+      </c>
+      <c r="AM126">
+        <v>1.6</v>
+      </c>
+      <c r="AN126">
+        <v>1.67</v>
+      </c>
+      <c r="AO126">
+        <v>1.67</v>
+      </c>
+      <c r="AP126">
+        <v>1.5</v>
+      </c>
+      <c r="AQ126">
+        <v>1.5</v>
+      </c>
+      <c r="AR126">
+        <v>2.03</v>
+      </c>
+      <c r="AS126">
+        <v>1.21</v>
+      </c>
+      <c r="AT126">
+        <v>3.24</v>
+      </c>
+      <c r="AU126">
+        <v>4</v>
+      </c>
+      <c r="AV126">
+        <v>12</v>
+      </c>
+      <c r="AW126">
+        <v>13</v>
+      </c>
+      <c r="AX126">
+        <v>11</v>
+      </c>
+      <c r="AY126">
+        <v>23</v>
+      </c>
+      <c r="AZ126">
+        <v>27</v>
+      </c>
+      <c r="BA126">
+        <v>4</v>
+      </c>
+      <c r="BB126">
+        <v>5</v>
+      </c>
+      <c r="BC126">
+        <v>9</v>
+      </c>
+      <c r="BD126">
+        <v>1.7</v>
+      </c>
+      <c r="BE126">
+        <v>6.5</v>
+      </c>
+      <c r="BF126">
+        <v>2.4</v>
+      </c>
+      <c r="BG126">
+        <v>1.39</v>
+      </c>
+      <c r="BH126">
+        <v>2.77</v>
+      </c>
+      <c r="BI126">
+        <v>1.68</v>
+      </c>
+      <c r="BJ126">
+        <v>2.11</v>
+      </c>
+      <c r="BK126">
+        <v>2.11</v>
+      </c>
+      <c r="BL126">
+        <v>1.68</v>
+      </c>
+      <c r="BM126">
+        <v>2.7</v>
+      </c>
+      <c r="BN126">
+        <v>1.41</v>
+      </c>
+      <c r="BO126">
+        <v>3.65</v>
+      </c>
+      <c r="BP126">
         <v>1.22</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -550,6 +550,9 @@
     <t>['65']</t>
   </si>
   <si>
+    <t>['79']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -695,6 +698,9 @@
   </si>
   <si>
     <t>['25']</t>
+  </si>
+  <si>
+    <t>['7', '81']</t>
   </si>
 </sst>
 </file>
@@ -1056,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1312,7 +1318,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1724,7 +1730,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1802,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ4">
         <v>1.75</v>
@@ -2008,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ5">
         <v>0.75</v>
@@ -2136,7 +2142,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2342,7 +2348,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2960,7 +2966,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3041,7 +3047,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3656,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13">
         <v>0.8</v>
@@ -4814,7 +4820,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5101,7 +5107,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ20">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5432,7 +5438,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5638,7 +5644,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5844,7 +5850,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6131,7 +6137,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ25">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6256,7 +6262,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6540,7 +6546,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ27">
         <v>0.2</v>
@@ -6668,7 +6674,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6746,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ28">
         <v>2</v>
@@ -6955,7 +6961,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7161,7 +7167,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR30">
         <v>1.4</v>
@@ -7367,7 +7373,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ31">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -8316,7 +8322,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8600,7 +8606,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ37">
         <v>0</v>
@@ -8806,7 +8812,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ38">
         <v>0.25</v>
@@ -9140,7 +9146,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9218,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ40">
         <v>0.33</v>
@@ -9758,7 +9764,7 @@
         <v>100</v>
       </c>
       <c r="P43" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q43">
         <v>2.63</v>
@@ -10170,7 +10176,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10376,7 +10382,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10454,7 +10460,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ46">
         <v>1.5</v>
@@ -10582,7 +10588,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10788,7 +10794,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -10869,7 +10875,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AR48">
         <v>1.53</v>
@@ -11281,7 +11287,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ50">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR50">
         <v>2.5</v>
@@ -11406,7 +11412,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11487,7 +11493,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ51">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR51">
         <v>1.47</v>
@@ -12024,7 +12030,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12105,7 +12111,7 @@
         <v>3</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR54">
         <v>1.05</v>
@@ -12308,7 +12314,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ55">
         <v>1.6</v>
@@ -12848,7 +12854,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13135,7 +13141,7 @@
         <v>2</v>
       </c>
       <c r="AQ59">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR59">
         <v>1.06</v>
@@ -13466,7 +13472,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14702,7 +14708,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14780,7 +14786,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ67">
         <v>2</v>
@@ -14908,7 +14914,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15732,7 +15738,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15938,7 +15944,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16556,7 +16562,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16762,7 +16768,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16840,7 +16846,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ77">
         <v>1.5</v>
@@ -16968,7 +16974,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17046,10 +17052,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ78">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR78">
         <v>2.48</v>
@@ -17255,7 +17261,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ79">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AR79">
         <v>1.81</v>
@@ -17380,7 +17386,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17461,7 +17467,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR80">
         <v>1.76</v>
@@ -17586,7 +17592,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17792,7 +17798,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -17870,7 +17876,7 @@
         <v>1.67</v>
       </c>
       <c r="AP82">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ82">
         <v>1.6</v>
@@ -18076,7 +18082,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18410,7 +18416,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18491,7 +18497,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR85">
         <v>2.29</v>
@@ -18616,7 +18622,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -19028,7 +19034,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19234,7 +19240,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19315,7 +19321,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ89">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -19440,7 +19446,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19518,7 +19524,7 @@
         <v>2</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ90">
         <v>1.75</v>
@@ -19852,7 +19858,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20676,7 +20682,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20882,7 +20888,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21706,7 +21712,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -23023,7 +23029,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ107">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AR107">
         <v>1.43</v>
@@ -23148,7 +23154,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23226,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="AP108">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ108">
         <v>0.2</v>
@@ -23354,7 +23360,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23432,10 +23438,10 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ109">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR109">
         <v>1.66</v>
@@ -23766,7 +23772,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -23847,7 +23853,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ111">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR111">
         <v>2.19</v>
@@ -23972,7 +23978,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24384,7 +24390,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24590,7 +24596,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24671,7 +24677,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ115">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR115">
         <v>1.19</v>
@@ -24796,7 +24802,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25002,7 +25008,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25301,31 +25307,31 @@
         <v>2.45</v>
       </c>
       <c r="AU118">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV118">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW118">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX118">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY118">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AZ118">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BA118">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB118">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC118">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD118">
         <v>2.05</v>
@@ -25414,7 +25420,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25507,31 +25513,31 @@
         <v>2.8</v>
       </c>
       <c r="AU119">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV119">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW119">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX119">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY119">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AZ119">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BA119">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB119">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC119">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BD119">
         <v>1.63</v>
@@ -25620,7 +25626,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -25704,13 +25710,13 @@
         <v>2.5</v>
       </c>
       <c r="AR120">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AS120">
         <v>1.55</v>
       </c>
       <c r="AT120">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="AU120">
         <v>7</v>
@@ -26032,7 +26038,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26238,7 +26244,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26325,10 +26331,10 @@
         <v>1.76</v>
       </c>
       <c r="AS123">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="AT123">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="AU123">
         <v>5</v>
@@ -26444,7 +26450,7 @@
         <v>100</v>
       </c>
       <c r="P124" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q124">
         <v>2.63</v>
@@ -26734,13 +26740,13 @@
         <v>1</v>
       </c>
       <c r="AR125">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AS125">
         <v>1.2</v>
       </c>
       <c r="AT125">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AU125">
         <v>5</v>
@@ -27013,6 +27019,1036 @@
       </c>
       <c r="BP126">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7820442</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45725.70833333334</v>
+      </c>
+      <c r="F127">
+        <v>9</v>
+      </c>
+      <c r="G127" t="s">
+        <v>73</v>
+      </c>
+      <c r="H127" t="s">
+        <v>80</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
+        <v>151</v>
+      </c>
+      <c r="P127" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q127">
+        <v>3.75</v>
+      </c>
+      <c r="R127">
+        <v>2</v>
+      </c>
+      <c r="S127">
+        <v>3.25</v>
+      </c>
+      <c r="T127">
+        <v>1.5</v>
+      </c>
+      <c r="U127">
+        <v>2.5</v>
+      </c>
+      <c r="V127">
+        <v>3.5</v>
+      </c>
+      <c r="W127">
+        <v>1.29</v>
+      </c>
+      <c r="X127">
+        <v>11</v>
+      </c>
+      <c r="Y127">
+        <v>1.05</v>
+      </c>
+      <c r="Z127">
+        <v>3.2</v>
+      </c>
+      <c r="AA127">
+        <v>2.78</v>
+      </c>
+      <c r="AB127">
+        <v>2.5</v>
+      </c>
+      <c r="AC127">
+        <v>1.07</v>
+      </c>
+      <c r="AD127">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE127">
+        <v>1.35</v>
+      </c>
+      <c r="AF127">
+        <v>3.1</v>
+      </c>
+      <c r="AG127">
+        <v>2.3</v>
+      </c>
+      <c r="AH127">
+        <v>1.6</v>
+      </c>
+      <c r="AI127">
+        <v>1.95</v>
+      </c>
+      <c r="AJ127">
+        <v>1.8</v>
+      </c>
+      <c r="AK127">
+        <v>1.51</v>
+      </c>
+      <c r="AL127">
+        <v>1.36</v>
+      </c>
+      <c r="AM127">
+        <v>1.37</v>
+      </c>
+      <c r="AN127">
+        <v>1.33</v>
+      </c>
+      <c r="AO127">
+        <v>1.5</v>
+      </c>
+      <c r="AP127">
+        <v>1.75</v>
+      </c>
+      <c r="AQ127">
+        <v>1.2</v>
+      </c>
+      <c r="AR127">
+        <v>1.66</v>
+      </c>
+      <c r="AS127">
+        <v>1.11</v>
+      </c>
+      <c r="AT127">
+        <v>2.77</v>
+      </c>
+      <c r="AU127">
+        <v>7</v>
+      </c>
+      <c r="AV127">
+        <v>5</v>
+      </c>
+      <c r="AW127">
+        <v>12</v>
+      </c>
+      <c r="AX127">
+        <v>7</v>
+      </c>
+      <c r="AY127">
+        <v>28</v>
+      </c>
+      <c r="AZ127">
+        <v>16</v>
+      </c>
+      <c r="BA127">
+        <v>6</v>
+      </c>
+      <c r="BB127">
+        <v>4</v>
+      </c>
+      <c r="BC127">
+        <v>10</v>
+      </c>
+      <c r="BD127">
+        <v>1.98</v>
+      </c>
+      <c r="BE127">
+        <v>6.4</v>
+      </c>
+      <c r="BF127">
+        <v>1.98</v>
+      </c>
+      <c r="BG127">
+        <v>1.33</v>
+      </c>
+      <c r="BH127">
+        <v>2.95</v>
+      </c>
+      <c r="BI127">
+        <v>1.56</v>
+      </c>
+      <c r="BJ127">
+        <v>2.23</v>
+      </c>
+      <c r="BK127">
+        <v>1.92</v>
+      </c>
+      <c r="BL127">
+        <v>1.77</v>
+      </c>
+      <c r="BM127">
+        <v>2.4</v>
+      </c>
+      <c r="BN127">
+        <v>1.49</v>
+      </c>
+      <c r="BO127">
+        <v>3.15</v>
+      </c>
+      <c r="BP127">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7820443</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45725.70833333334</v>
+      </c>
+      <c r="F128">
+        <v>9</v>
+      </c>
+      <c r="G128" t="s">
+        <v>96</v>
+      </c>
+      <c r="H128" t="s">
+        <v>71</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>1</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>2</v>
+      </c>
+      <c r="N128">
+        <v>2</v>
+      </c>
+      <c r="O128" t="s">
+        <v>100</v>
+      </c>
+      <c r="P128" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q128">
+        <v>4</v>
+      </c>
+      <c r="R128">
+        <v>1.83</v>
+      </c>
+      <c r="S128">
+        <v>3.5</v>
+      </c>
+      <c r="T128">
+        <v>1.62</v>
+      </c>
+      <c r="U128">
+        <v>2.2</v>
+      </c>
+      <c r="V128">
+        <v>4</v>
+      </c>
+      <c r="W128">
+        <v>1.22</v>
+      </c>
+      <c r="X128">
+        <v>15</v>
+      </c>
+      <c r="Y128">
+        <v>1.03</v>
+      </c>
+      <c r="Z128">
+        <v>2.99</v>
+      </c>
+      <c r="AA128">
+        <v>2.85</v>
+      </c>
+      <c r="AB128">
+        <v>2.59</v>
+      </c>
+      <c r="AC128">
+        <v>1.08</v>
+      </c>
+      <c r="AD128">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE128">
+        <v>1.57</v>
+      </c>
+      <c r="AF128">
+        <v>2.25</v>
+      </c>
+      <c r="AG128">
+        <v>2.7</v>
+      </c>
+      <c r="AH128">
+        <v>1.44</v>
+      </c>
+      <c r="AI128">
+        <v>2.25</v>
+      </c>
+      <c r="AJ128">
+        <v>1.57</v>
+      </c>
+      <c r="AK128">
+        <v>1.49</v>
+      </c>
+      <c r="AL128">
+        <v>1.38</v>
+      </c>
+      <c r="AM128">
+        <v>1.36</v>
+      </c>
+      <c r="AN128">
+        <v>0.5</v>
+      </c>
+      <c r="AO128">
+        <v>1.5</v>
+      </c>
+      <c r="AP128">
+        <v>0.4</v>
+      </c>
+      <c r="AQ128">
+        <v>1.8</v>
+      </c>
+      <c r="AR128">
+        <v>2.27</v>
+      </c>
+      <c r="AS128">
+        <v>1.48</v>
+      </c>
+      <c r="AT128">
+        <v>3.75</v>
+      </c>
+      <c r="AU128">
+        <v>7</v>
+      </c>
+      <c r="AV128">
+        <v>5</v>
+      </c>
+      <c r="AW128">
+        <v>8</v>
+      </c>
+      <c r="AX128">
+        <v>7</v>
+      </c>
+      <c r="AY128">
+        <v>17</v>
+      </c>
+      <c r="AZ128">
+        <v>14</v>
+      </c>
+      <c r="BA128">
+        <v>4</v>
+      </c>
+      <c r="BB128">
+        <v>4</v>
+      </c>
+      <c r="BC128">
+        <v>8</v>
+      </c>
+      <c r="BD128">
+        <v>1.88</v>
+      </c>
+      <c r="BE128">
+        <v>6.4</v>
+      </c>
+      <c r="BF128">
+        <v>2.15</v>
+      </c>
+      <c r="BG128">
+        <v>1.48</v>
+      </c>
+      <c r="BH128">
+        <v>2.45</v>
+      </c>
+      <c r="BI128">
+        <v>1.79</v>
+      </c>
+      <c r="BJ128">
+        <v>1.9</v>
+      </c>
+      <c r="BK128">
+        <v>2.28</v>
+      </c>
+      <c r="BL128">
+        <v>1.54</v>
+      </c>
+      <c r="BM128">
+        <v>2.9</v>
+      </c>
+      <c r="BN128">
+        <v>1.34</v>
+      </c>
+      <c r="BO128">
+        <v>3.95</v>
+      </c>
+      <c r="BP128">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7820444</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45725.80208333334</v>
+      </c>
+      <c r="F129">
+        <v>9</v>
+      </c>
+      <c r="G129" t="s">
+        <v>95</v>
+      </c>
+      <c r="H129" t="s">
+        <v>99</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>1</v>
+      </c>
+      <c r="O129" t="s">
+        <v>178</v>
+      </c>
+      <c r="P129" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q129">
+        <v>1.83</v>
+      </c>
+      <c r="R129">
+        <v>2.3</v>
+      </c>
+      <c r="S129">
+        <v>8.5</v>
+      </c>
+      <c r="T129">
+        <v>1.4</v>
+      </c>
+      <c r="U129">
+        <v>2.75</v>
+      </c>
+      <c r="V129">
+        <v>2.75</v>
+      </c>
+      <c r="W129">
+        <v>1.4</v>
+      </c>
+      <c r="X129">
+        <v>8</v>
+      </c>
+      <c r="Y129">
+        <v>1.08</v>
+      </c>
+      <c r="Z129">
+        <v>1.33</v>
+      </c>
+      <c r="AA129">
+        <v>4.5</v>
+      </c>
+      <c r="AB129">
+        <v>10</v>
+      </c>
+      <c r="AC129">
+        <v>1.08</v>
+      </c>
+      <c r="AD129">
+        <v>8.6</v>
+      </c>
+      <c r="AE129">
+        <v>1.39</v>
+      </c>
+      <c r="AF129">
+        <v>2.9</v>
+      </c>
+      <c r="AG129">
+        <v>1.95</v>
+      </c>
+      <c r="AH129">
+        <v>1.85</v>
+      </c>
+      <c r="AI129">
+        <v>2.25</v>
+      </c>
+      <c r="AJ129">
+        <v>1.57</v>
+      </c>
+      <c r="AK129">
+        <v>1.08</v>
+      </c>
+      <c r="AL129">
+        <v>1.2</v>
+      </c>
+      <c r="AM129">
+        <v>2.8</v>
+      </c>
+      <c r="AN129">
+        <v>2.25</v>
+      </c>
+      <c r="AO129">
+        <v>1</v>
+      </c>
+      <c r="AP129">
+        <v>2.4</v>
+      </c>
+      <c r="AQ129">
+        <v>0.8</v>
+      </c>
+      <c r="AR129">
+        <v>1.71</v>
+      </c>
+      <c r="AS129">
+        <v>1.54</v>
+      </c>
+      <c r="AT129">
+        <v>3.25</v>
+      </c>
+      <c r="AU129">
+        <v>9</v>
+      </c>
+      <c r="AV129">
+        <v>2</v>
+      </c>
+      <c r="AW129">
+        <v>19</v>
+      </c>
+      <c r="AX129">
+        <v>2</v>
+      </c>
+      <c r="AY129">
+        <v>32</v>
+      </c>
+      <c r="AZ129">
+        <v>5</v>
+      </c>
+      <c r="BA129">
+        <v>9</v>
+      </c>
+      <c r="BB129">
+        <v>3</v>
+      </c>
+      <c r="BC129">
+        <v>12</v>
+      </c>
+      <c r="BD129">
+        <v>1.27</v>
+      </c>
+      <c r="BE129">
+        <v>8.5</v>
+      </c>
+      <c r="BF129">
+        <v>4.1</v>
+      </c>
+      <c r="BG129">
+        <v>1.28</v>
+      </c>
+      <c r="BH129">
+        <v>3.3</v>
+      </c>
+      <c r="BI129">
+        <v>1.49</v>
+      </c>
+      <c r="BJ129">
+        <v>2.4</v>
+      </c>
+      <c r="BK129">
+        <v>1.79</v>
+      </c>
+      <c r="BL129">
+        <v>1.9</v>
+      </c>
+      <c r="BM129">
+        <v>2.23</v>
+      </c>
+      <c r="BN129">
+        <v>1.57</v>
+      </c>
+      <c r="BO129">
+        <v>2.8</v>
+      </c>
+      <c r="BP129">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7820446</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45725.89583333334</v>
+      </c>
+      <c r="F130">
+        <v>9</v>
+      </c>
+      <c r="G130" t="s">
+        <v>81</v>
+      </c>
+      <c r="H130" t="s">
+        <v>70</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>2</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
+      </c>
+      <c r="M130">
+        <v>1</v>
+      </c>
+      <c r="N130">
+        <v>2</v>
+      </c>
+      <c r="O130" t="s">
+        <v>125</v>
+      </c>
+      <c r="P130" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q130">
+        <v>2.75</v>
+      </c>
+      <c r="R130">
+        <v>1.83</v>
+      </c>
+      <c r="S130">
+        <v>5.5</v>
+      </c>
+      <c r="T130">
+        <v>1.67</v>
+      </c>
+      <c r="U130">
+        <v>2.1</v>
+      </c>
+      <c r="V130">
+        <v>4.33</v>
+      </c>
+      <c r="W130">
+        <v>1.2</v>
+      </c>
+      <c r="X130">
+        <v>15</v>
+      </c>
+      <c r="Y130">
+        <v>1.03</v>
+      </c>
+      <c r="Z130">
+        <v>1.94</v>
+      </c>
+      <c r="AA130">
+        <v>3.01</v>
+      </c>
+      <c r="AB130">
+        <v>4.45</v>
+      </c>
+      <c r="AC130">
+        <v>1.14</v>
+      </c>
+      <c r="AD130">
+        <v>5.8</v>
+      </c>
+      <c r="AE130">
+        <v>1.6</v>
+      </c>
+      <c r="AF130">
+        <v>2.2</v>
+      </c>
+      <c r="AG130">
+        <v>2.88</v>
+      </c>
+      <c r="AH130">
+        <v>1.4</v>
+      </c>
+      <c r="AI130">
+        <v>2.5</v>
+      </c>
+      <c r="AJ130">
+        <v>1.5</v>
+      </c>
+      <c r="AK130">
+        <v>1.22</v>
+      </c>
+      <c r="AL130">
+        <v>1.36</v>
+      </c>
+      <c r="AM130">
+        <v>1.77</v>
+      </c>
+      <c r="AN130">
+        <v>2</v>
+      </c>
+      <c r="AO130">
+        <v>1.75</v>
+      </c>
+      <c r="AP130">
+        <v>1.75</v>
+      </c>
+      <c r="AQ130">
+        <v>1.6</v>
+      </c>
+      <c r="AR130">
+        <v>1.36</v>
+      </c>
+      <c r="AS130">
+        <v>1.31</v>
+      </c>
+      <c r="AT130">
+        <v>2.67</v>
+      </c>
+      <c r="AU130">
+        <v>7</v>
+      </c>
+      <c r="AV130">
+        <v>2</v>
+      </c>
+      <c r="AW130">
+        <v>8</v>
+      </c>
+      <c r="AX130">
+        <v>3</v>
+      </c>
+      <c r="AY130">
+        <v>18</v>
+      </c>
+      <c r="AZ130">
+        <v>7</v>
+      </c>
+      <c r="BA130">
+        <v>11</v>
+      </c>
+      <c r="BB130">
+        <v>1</v>
+      </c>
+      <c r="BC130">
+        <v>12</v>
+      </c>
+      <c r="BD130">
+        <v>1.61</v>
+      </c>
+      <c r="BE130">
+        <v>6.4</v>
+      </c>
+      <c r="BF130">
+        <v>2.55</v>
+      </c>
+      <c r="BG130">
+        <v>1.48</v>
+      </c>
+      <c r="BH130">
+        <v>2.43</v>
+      </c>
+      <c r="BI130">
+        <v>1.8</v>
+      </c>
+      <c r="BJ130">
+        <v>1.89</v>
+      </c>
+      <c r="BK130">
+        <v>2.22</v>
+      </c>
+      <c r="BL130">
+        <v>1.61</v>
+      </c>
+      <c r="BM130">
+        <v>2.87</v>
+      </c>
+      <c r="BN130">
+        <v>1.37</v>
+      </c>
+      <c r="BO130">
+        <v>3.95</v>
+      </c>
+      <c r="BP130">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7820445</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45725.89583333334</v>
+      </c>
+      <c r="F131">
+        <v>9</v>
+      </c>
+      <c r="G131" t="s">
+        <v>72</v>
+      </c>
+      <c r="H131" t="s">
+        <v>77</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131" t="s">
+        <v>100</v>
+      </c>
+      <c r="P131" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q131">
+        <v>3.1</v>
+      </c>
+      <c r="R131">
+        <v>1.91</v>
+      </c>
+      <c r="S131">
+        <v>4.33</v>
+      </c>
+      <c r="T131">
+        <v>1.57</v>
+      </c>
+      <c r="U131">
+        <v>2.25</v>
+      </c>
+      <c r="V131">
+        <v>3.75</v>
+      </c>
+      <c r="W131">
+        <v>1.25</v>
+      </c>
+      <c r="X131">
+        <v>13</v>
+      </c>
+      <c r="Y131">
+        <v>1.04</v>
+      </c>
+      <c r="Z131">
+        <v>2.23</v>
+      </c>
+      <c r="AA131">
+        <v>2.91</v>
+      </c>
+      <c r="AB131">
+        <v>3.55</v>
+      </c>
+      <c r="AC131">
+        <v>1.09</v>
+      </c>
+      <c r="AD131">
+        <v>7.6</v>
+      </c>
+      <c r="AE131">
+        <v>1.53</v>
+      </c>
+      <c r="AF131">
+        <v>2.37</v>
+      </c>
+      <c r="AG131">
+        <v>2.5</v>
+      </c>
+      <c r="AH131">
+        <v>1.5</v>
+      </c>
+      <c r="AI131">
+        <v>2.2</v>
+      </c>
+      <c r="AJ131">
+        <v>1.62</v>
+      </c>
+      <c r="AK131">
+        <v>1.3</v>
+      </c>
+      <c r="AL131">
+        <v>1.36</v>
+      </c>
+      <c r="AM131">
+        <v>1.61</v>
+      </c>
+      <c r="AN131">
+        <v>0.75</v>
+      </c>
+      <c r="AO131">
+        <v>0.25</v>
+      </c>
+      <c r="AP131">
+        <v>0.8</v>
+      </c>
+      <c r="AQ131">
+        <v>0.4</v>
+      </c>
+      <c r="AR131">
+        <v>1.81</v>
+      </c>
+      <c r="AS131">
+        <v>1.5</v>
+      </c>
+      <c r="AT131">
+        <v>3.31</v>
+      </c>
+      <c r="AU131">
+        <v>5</v>
+      </c>
+      <c r="AV131">
+        <v>4</v>
+      </c>
+      <c r="AW131">
+        <v>10</v>
+      </c>
+      <c r="AX131">
+        <v>2</v>
+      </c>
+      <c r="AY131">
+        <v>17</v>
+      </c>
+      <c r="AZ131">
+        <v>6</v>
+      </c>
+      <c r="BA131">
+        <v>5</v>
+      </c>
+      <c r="BB131">
+        <v>3</v>
+      </c>
+      <c r="BC131">
+        <v>8</v>
+      </c>
+      <c r="BD131">
+        <v>1.63</v>
+      </c>
+      <c r="BE131">
+        <v>6.4</v>
+      </c>
+      <c r="BF131">
+        <v>2.55</v>
+      </c>
+      <c r="BG131">
+        <v>1.4</v>
+      </c>
+      <c r="BH131">
+        <v>2.65</v>
+      </c>
+      <c r="BI131">
+        <v>1.67</v>
+      </c>
+      <c r="BJ131">
+        <v>2.04</v>
+      </c>
+      <c r="BK131">
+        <v>2.08</v>
+      </c>
+      <c r="BL131">
+        <v>1.65</v>
+      </c>
+      <c r="BM131">
+        <v>2.65</v>
+      </c>
+      <c r="BN131">
+        <v>1.41</v>
+      </c>
+      <c r="BO131">
+        <v>3.55</v>
+      </c>
+      <c r="BP131">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="232">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -553,6 +553,12 @@
     <t>['79']</t>
   </si>
   <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['38', '55']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -701,6 +707,9 @@
   </si>
   <si>
     <t>['7', '81']</t>
+  </si>
+  <si>
+    <t>['2']</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1318,7 +1327,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1399,7 +1408,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ2">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1730,7 +1739,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2142,7 +2151,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2223,7 +2232,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ6">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2348,7 +2357,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2966,7 +2975,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -4820,7 +4829,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5310,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ21">
         <v>1.5</v>
@@ -5438,7 +5447,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5644,7 +5653,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5722,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ23">
         <v>1.6</v>
@@ -5850,7 +5859,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -5928,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ24">
         <v>1.75</v>
@@ -6262,7 +6271,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6674,7 +6683,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7785,7 +7794,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ33">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR33">
         <v>1.45</v>
@@ -8322,7 +8331,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -9146,7 +9155,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9764,7 +9773,7 @@
         <v>100</v>
       </c>
       <c r="P43" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q43">
         <v>2.63</v>
@@ -10176,7 +10185,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10257,7 +10266,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ45">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR45">
         <v>0</v>
@@ -10382,7 +10391,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10588,7 +10597,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10794,7 +10803,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11412,7 +11421,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11490,7 +11499,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ51">
         <v>1.2</v>
@@ -12030,7 +12039,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12854,7 +12863,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13138,7 +13147,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ59">
         <v>1.6</v>
@@ -13344,7 +13353,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13472,7 +13481,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14583,7 +14592,7 @@
         <v>1</v>
       </c>
       <c r="AQ66">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR66">
         <v>1.2</v>
@@ -14708,7 +14717,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14914,7 +14923,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15738,7 +15747,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15944,7 +15953,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16562,7 +16571,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16768,7 +16777,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16974,7 +16983,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17386,7 +17395,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17464,7 +17473,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ80">
         <v>1.8</v>
@@ -17592,7 +17601,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17798,7 +17807,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -17879,7 +17888,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ82">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR82">
         <v>1.71</v>
@@ -18416,7 +18425,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18494,7 +18503,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ85">
         <v>0.8</v>
@@ -18622,7 +18631,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -18703,7 +18712,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ86">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR86">
         <v>1.79</v>
@@ -18906,7 +18915,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ87">
         <v>0.5</v>
@@ -19034,7 +19043,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19240,7 +19249,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19446,7 +19455,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19858,7 +19867,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20682,7 +20691,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20888,7 +20897,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21712,7 +21721,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -22617,7 +22626,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ105">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR105">
         <v>1.4</v>
@@ -22823,7 +22832,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ106">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR106">
         <v>2.07</v>
@@ -23154,7 +23163,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23360,7 +23369,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23772,7 +23781,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -23850,7 +23859,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ111">
         <v>1.8</v>
@@ -23978,7 +23987,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24056,7 +24065,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24390,7 +24399,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24596,7 +24605,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24802,7 +24811,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25008,7 +25017,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25420,7 +25429,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25626,7 +25635,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -26038,7 +26047,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26244,7 +26253,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26450,7 +26459,7 @@
         <v>100</v>
       </c>
       <c r="P124" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q124">
         <v>2.63</v>
@@ -27274,7 +27283,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28049,6 +28058,624 @@
       </c>
       <c r="BP131">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7820447</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45726.79166666666</v>
+      </c>
+      <c r="F132">
+        <v>9</v>
+      </c>
+      <c r="G132" t="s">
+        <v>92</v>
+      </c>
+      <c r="H132" t="s">
+        <v>86</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>2</v>
+      </c>
+      <c r="O132" t="s">
+        <v>179</v>
+      </c>
+      <c r="P132" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q132">
+        <v>2.75</v>
+      </c>
+      <c r="R132">
+        <v>1.91</v>
+      </c>
+      <c r="S132">
+        <v>5</v>
+      </c>
+      <c r="T132">
+        <v>1.57</v>
+      </c>
+      <c r="U132">
+        <v>2.25</v>
+      </c>
+      <c r="V132">
+        <v>3.75</v>
+      </c>
+      <c r="W132">
+        <v>1.25</v>
+      </c>
+      <c r="X132">
+        <v>13</v>
+      </c>
+      <c r="Y132">
+        <v>1.04</v>
+      </c>
+      <c r="Z132">
+        <v>1.91</v>
+      </c>
+      <c r="AA132">
+        <v>2.9</v>
+      </c>
+      <c r="AB132">
+        <v>4.83</v>
+      </c>
+      <c r="AC132">
+        <v>1.13</v>
+      </c>
+      <c r="AD132">
+        <v>6</v>
+      </c>
+      <c r="AE132">
+        <v>1.53</v>
+      </c>
+      <c r="AF132">
+        <v>2.37</v>
+      </c>
+      <c r="AG132">
+        <v>2.6</v>
+      </c>
+      <c r="AH132">
+        <v>1.48</v>
+      </c>
+      <c r="AI132">
+        <v>2.2</v>
+      </c>
+      <c r="AJ132">
+        <v>1.62</v>
+      </c>
+      <c r="AK132">
+        <v>1.2</v>
+      </c>
+      <c r="AL132">
+        <v>1.36</v>
+      </c>
+      <c r="AM132">
+        <v>1.8</v>
+      </c>
+      <c r="AN132">
+        <v>2</v>
+      </c>
+      <c r="AO132">
+        <v>1.75</v>
+      </c>
+      <c r="AP132">
+        <v>1.75</v>
+      </c>
+      <c r="AQ132">
+        <v>1.6</v>
+      </c>
+      <c r="AR132">
+        <v>1.22</v>
+      </c>
+      <c r="AS132">
+        <v>1.12</v>
+      </c>
+      <c r="AT132">
+        <v>2.34</v>
+      </c>
+      <c r="AU132">
+        <v>5</v>
+      </c>
+      <c r="AV132">
+        <v>2</v>
+      </c>
+      <c r="AW132">
+        <v>8</v>
+      </c>
+      <c r="AX132">
+        <v>2</v>
+      </c>
+      <c r="AY132">
+        <v>16</v>
+      </c>
+      <c r="AZ132">
+        <v>4</v>
+      </c>
+      <c r="BA132">
+        <v>7</v>
+      </c>
+      <c r="BB132">
+        <v>2</v>
+      </c>
+      <c r="BC132">
+        <v>9</v>
+      </c>
+      <c r="BD132">
+        <v>1.38</v>
+      </c>
+      <c r="BE132">
+        <v>7</v>
+      </c>
+      <c r="BF132">
+        <v>3.4</v>
+      </c>
+      <c r="BG132">
+        <v>1.36</v>
+      </c>
+      <c r="BH132">
+        <v>2.9</v>
+      </c>
+      <c r="BI132">
+        <v>1.62</v>
+      </c>
+      <c r="BJ132">
+        <v>2.21</v>
+      </c>
+      <c r="BK132">
+        <v>2.02</v>
+      </c>
+      <c r="BL132">
+        <v>1.74</v>
+      </c>
+      <c r="BM132">
+        <v>2.57</v>
+      </c>
+      <c r="BN132">
+        <v>1.45</v>
+      </c>
+      <c r="BO132">
+        <v>3.45</v>
+      </c>
+      <c r="BP132">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7820448</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45726.88541666666</v>
+      </c>
+      <c r="F133">
+        <v>9</v>
+      </c>
+      <c r="G133" t="s">
+        <v>89</v>
+      </c>
+      <c r="H133" t="s">
+        <v>94</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>2</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>2</v>
+      </c>
+      <c r="O133" t="s">
+        <v>180</v>
+      </c>
+      <c r="P133" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q133">
+        <v>3.1</v>
+      </c>
+      <c r="R133">
+        <v>1.91</v>
+      </c>
+      <c r="S133">
+        <v>4.33</v>
+      </c>
+      <c r="T133">
+        <v>1.62</v>
+      </c>
+      <c r="U133">
+        <v>2.2</v>
+      </c>
+      <c r="V133">
+        <v>4</v>
+      </c>
+      <c r="W133">
+        <v>1.22</v>
+      </c>
+      <c r="X133">
+        <v>13</v>
+      </c>
+      <c r="Y133">
+        <v>1.04</v>
+      </c>
+      <c r="Z133">
+        <v>2.21</v>
+      </c>
+      <c r="AA133">
+        <v>2.87</v>
+      </c>
+      <c r="AB133">
+        <v>3.69</v>
+      </c>
+      <c r="AC133">
+        <v>1.11</v>
+      </c>
+      <c r="AD133">
+        <v>6.6</v>
+      </c>
+      <c r="AE133">
+        <v>1.55</v>
+      </c>
+      <c r="AF133">
+        <v>2.3</v>
+      </c>
+      <c r="AG133">
+        <v>2.7</v>
+      </c>
+      <c r="AH133">
+        <v>1.44</v>
+      </c>
+      <c r="AI133">
+        <v>2.2</v>
+      </c>
+      <c r="AJ133">
+        <v>1.62</v>
+      </c>
+      <c r="AK133">
+        <v>1.29</v>
+      </c>
+      <c r="AL133">
+        <v>1.37</v>
+      </c>
+      <c r="AM133">
+        <v>1.62</v>
+      </c>
+      <c r="AN133">
+        <v>0.75</v>
+      </c>
+      <c r="AO133">
+        <v>0</v>
+      </c>
+      <c r="AP133">
+        <v>1.2</v>
+      </c>
+      <c r="AQ133">
+        <v>0</v>
+      </c>
+      <c r="AR133">
+        <v>1.65</v>
+      </c>
+      <c r="AS133">
+        <v>1.36</v>
+      </c>
+      <c r="AT133">
+        <v>3.01</v>
+      </c>
+      <c r="AU133">
+        <v>10</v>
+      </c>
+      <c r="AV133">
+        <v>3</v>
+      </c>
+      <c r="AW133">
+        <v>1</v>
+      </c>
+      <c r="AX133">
+        <v>8</v>
+      </c>
+      <c r="AY133">
+        <v>11</v>
+      </c>
+      <c r="AZ133">
+        <v>13</v>
+      </c>
+      <c r="BA133">
+        <v>5</v>
+      </c>
+      <c r="BB133">
+        <v>4</v>
+      </c>
+      <c r="BC133">
+        <v>9</v>
+      </c>
+      <c r="BD133">
+        <v>1.81</v>
+      </c>
+      <c r="BE133">
+        <v>6.25</v>
+      </c>
+      <c r="BF133">
+        <v>2.23</v>
+      </c>
+      <c r="BG133">
+        <v>1.57</v>
+      </c>
+      <c r="BH133">
+        <v>2.23</v>
+      </c>
+      <c r="BI133">
+        <v>1.85</v>
+      </c>
+      <c r="BJ133">
+        <v>1.85</v>
+      </c>
+      <c r="BK133">
+        <v>2.5</v>
+      </c>
+      <c r="BL133">
+        <v>1.46</v>
+      </c>
+      <c r="BM133">
+        <v>3.4</v>
+      </c>
+      <c r="BN133">
+        <v>1.26</v>
+      </c>
+      <c r="BO133">
+        <v>4.6</v>
+      </c>
+      <c r="BP133">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7820449</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45726.88541666666</v>
+      </c>
+      <c r="F134">
+        <v>9</v>
+      </c>
+      <c r="G134" t="s">
+        <v>91</v>
+      </c>
+      <c r="H134" t="s">
+        <v>87</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134" t="s">
+        <v>100</v>
+      </c>
+      <c r="P134" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q134">
+        <v>2.75</v>
+      </c>
+      <c r="R134">
+        <v>1.95</v>
+      </c>
+      <c r="S134">
+        <v>5</v>
+      </c>
+      <c r="T134">
+        <v>1.57</v>
+      </c>
+      <c r="U134">
+        <v>2.25</v>
+      </c>
+      <c r="V134">
+        <v>3.75</v>
+      </c>
+      <c r="W134">
+        <v>1.25</v>
+      </c>
+      <c r="X134">
+        <v>13</v>
+      </c>
+      <c r="Y134">
+        <v>1.04</v>
+      </c>
+      <c r="Z134">
+        <v>2</v>
+      </c>
+      <c r="AA134">
+        <v>3</v>
+      </c>
+      <c r="AB134">
+        <v>4.5</v>
+      </c>
+      <c r="AC134">
+        <v>1.13</v>
+      </c>
+      <c r="AD134">
+        <v>6</v>
+      </c>
+      <c r="AE134">
+        <v>1.5</v>
+      </c>
+      <c r="AF134">
+        <v>2.4</v>
+      </c>
+      <c r="AG134">
+        <v>2.5</v>
+      </c>
+      <c r="AH134">
+        <v>1.5</v>
+      </c>
+      <c r="AI134">
+        <v>2.2</v>
+      </c>
+      <c r="AJ134">
+        <v>1.62</v>
+      </c>
+      <c r="AK134">
+        <v>1.23</v>
+      </c>
+      <c r="AL134">
+        <v>1.35</v>
+      </c>
+      <c r="AM134">
+        <v>1.77</v>
+      </c>
+      <c r="AN134">
+        <v>0.25</v>
+      </c>
+      <c r="AO134">
+        <v>1.6</v>
+      </c>
+      <c r="AP134">
+        <v>0.4</v>
+      </c>
+      <c r="AQ134">
+        <v>1.5</v>
+      </c>
+      <c r="AR134">
+        <v>2.28</v>
+      </c>
+      <c r="AS134">
+        <v>1.31</v>
+      </c>
+      <c r="AT134">
+        <v>3.59</v>
+      </c>
+      <c r="AU134">
+        <v>5</v>
+      </c>
+      <c r="AV134">
+        <v>3</v>
+      </c>
+      <c r="AW134">
+        <v>12</v>
+      </c>
+      <c r="AX134">
+        <v>2</v>
+      </c>
+      <c r="AY134">
+        <v>19</v>
+      </c>
+      <c r="AZ134">
+        <v>6</v>
+      </c>
+      <c r="BA134">
+        <v>6</v>
+      </c>
+      <c r="BB134">
+        <v>2</v>
+      </c>
+      <c r="BC134">
+        <v>8</v>
+      </c>
+      <c r="BD134">
+        <v>1.74</v>
+      </c>
+      <c r="BE134">
+        <v>6.4</v>
+      </c>
+      <c r="BF134">
+        <v>2.33</v>
+      </c>
+      <c r="BG134">
+        <v>1.49</v>
+      </c>
+      <c r="BH134">
+        <v>2.4</v>
+      </c>
+      <c r="BI134">
+        <v>1.73</v>
+      </c>
+      <c r="BJ134">
+        <v>2</v>
+      </c>
+      <c r="BK134">
+        <v>2.32</v>
+      </c>
+      <c r="BL134">
+        <v>1.53</v>
+      </c>
+      <c r="BM134">
+        <v>3</v>
+      </c>
+      <c r="BN134">
+        <v>1.32</v>
+      </c>
+      <c r="BO134">
+        <v>4</v>
+      </c>
+      <c r="BP134">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -28427,10 +28427,10 @@
         <v>5</v>
       </c>
       <c r="BB133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC133">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD133">
         <v>1.81</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="233">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -711,6 +711,9 @@
   <si>
     <t>['2']</t>
   </si>
+  <si>
+    <t>['10', '89']</t>
+  </si>
 </sst>
 </file>
 
@@ -1071,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1405,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ2">
         <v>1.5</v>
@@ -3880,7 +3883,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ14">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4292,7 +4295,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5940,7 +5943,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ24">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -7379,7 +7382,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ31">
         <v>1.8</v>
@@ -8206,7 +8209,7 @@
         <v>2</v>
       </c>
       <c r="AQ35">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR35">
         <v>1.24</v>
@@ -8618,7 +8621,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AR37">
         <v>2.05</v>
@@ -10057,7 +10060,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -11914,7 +11917,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ53">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR53">
         <v>1.58</v>
@@ -14386,7 +14389,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ65">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AR65">
         <v>1.99</v>
@@ -15001,7 +15004,7 @@
         <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ68">
         <v>1.6</v>
@@ -15413,10 +15416,10 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR70">
         <v>1.21</v>
@@ -19536,7 +19539,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ90">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR90">
         <v>1.46</v>
@@ -20151,7 +20154,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20772,7 +20775,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ96">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AR96">
         <v>1.26</v>
@@ -20978,7 +20981,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ97">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR97">
         <v>1.54</v>
@@ -21390,7 +21393,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ99">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR99">
         <v>1.77</v>
@@ -22211,7 +22214,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ103">
         <v>1.75</v>
@@ -24271,7 +24274,7 @@
         <v>0.25</v>
       </c>
       <c r="AP113">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ113">
         <v>0.2</v>
@@ -28676,6 +28679,624 @@
       </c>
       <c r="BP134">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7820450</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45730.79166666666</v>
+      </c>
+      <c r="F135">
+        <v>10</v>
+      </c>
+      <c r="G135" t="s">
+        <v>98</v>
+      </c>
+      <c r="H135" t="s">
+        <v>96</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>2</v>
+      </c>
+      <c r="N135">
+        <v>2</v>
+      </c>
+      <c r="O135" t="s">
+        <v>100</v>
+      </c>
+      <c r="P135" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q135">
+        <v>2.05</v>
+      </c>
+      <c r="R135">
+        <v>2.1</v>
+      </c>
+      <c r="S135">
+        <v>8</v>
+      </c>
+      <c r="T135">
+        <v>1.44</v>
+      </c>
+      <c r="U135">
+        <v>2.63</v>
+      </c>
+      <c r="V135">
+        <v>3.4</v>
+      </c>
+      <c r="W135">
+        <v>1.3</v>
+      </c>
+      <c r="X135">
+        <v>10</v>
+      </c>
+      <c r="Y135">
+        <v>1.06</v>
+      </c>
+      <c r="Z135">
+        <v>1.45</v>
+      </c>
+      <c r="AA135">
+        <v>4.2</v>
+      </c>
+      <c r="AB135">
+        <v>7.5</v>
+      </c>
+      <c r="AC135">
+        <v>1.06</v>
+      </c>
+      <c r="AD135">
+        <v>8.5</v>
+      </c>
+      <c r="AE135">
+        <v>1.38</v>
+      </c>
+      <c r="AF135">
+        <v>3</v>
+      </c>
+      <c r="AG135">
+        <v>2.2</v>
+      </c>
+      <c r="AH135">
+        <v>1.65</v>
+      </c>
+      <c r="AI135">
+        <v>2.5</v>
+      </c>
+      <c r="AJ135">
+        <v>1.5</v>
+      </c>
+      <c r="AK135">
+        <v>1.09</v>
+      </c>
+      <c r="AL135">
+        <v>1.22</v>
+      </c>
+      <c r="AM135">
+        <v>2.65</v>
+      </c>
+      <c r="AN135">
+        <v>2.2</v>
+      </c>
+      <c r="AO135">
+        <v>0</v>
+      </c>
+      <c r="AP135">
+        <v>1.83</v>
+      </c>
+      <c r="AQ135">
+        <v>0.6</v>
+      </c>
+      <c r="AR135">
+        <v>1.84</v>
+      </c>
+      <c r="AS135">
+        <v>1.25</v>
+      </c>
+      <c r="AT135">
+        <v>3.09</v>
+      </c>
+      <c r="AU135">
+        <v>4</v>
+      </c>
+      <c r="AV135">
+        <v>8</v>
+      </c>
+      <c r="AW135">
+        <v>5</v>
+      </c>
+      <c r="AX135">
+        <v>8</v>
+      </c>
+      <c r="AY135">
+        <v>9</v>
+      </c>
+      <c r="AZ135">
+        <v>18</v>
+      </c>
+      <c r="BA135">
+        <v>10</v>
+      </c>
+      <c r="BB135">
+        <v>2</v>
+      </c>
+      <c r="BC135">
+        <v>12</v>
+      </c>
+      <c r="BD135">
+        <v>1.24</v>
+      </c>
+      <c r="BE135">
+        <v>8</v>
+      </c>
+      <c r="BF135">
+        <v>4.4</v>
+      </c>
+      <c r="BG135">
+        <v>1.35</v>
+      </c>
+      <c r="BH135">
+        <v>2.9</v>
+      </c>
+      <c r="BI135">
+        <v>1.6</v>
+      </c>
+      <c r="BJ135">
+        <v>2.17</v>
+      </c>
+      <c r="BK135">
+        <v>1.96</v>
+      </c>
+      <c r="BL135">
+        <v>1.74</v>
+      </c>
+      <c r="BM135">
+        <v>2.48</v>
+      </c>
+      <c r="BN135">
+        <v>1.46</v>
+      </c>
+      <c r="BO135">
+        <v>3.15</v>
+      </c>
+      <c r="BP135">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7820451</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45730.875</v>
+      </c>
+      <c r="F136">
+        <v>10</v>
+      </c>
+      <c r="G136" t="s">
+        <v>70</v>
+      </c>
+      <c r="H136" t="s">
+        <v>79</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136" t="s">
+        <v>100</v>
+      </c>
+      <c r="P136" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q136">
+        <v>3.75</v>
+      </c>
+      <c r="R136">
+        <v>1.8</v>
+      </c>
+      <c r="S136">
+        <v>4</v>
+      </c>
+      <c r="T136">
+        <v>1.73</v>
+      </c>
+      <c r="U136">
+        <v>2</v>
+      </c>
+      <c r="V136">
+        <v>5</v>
+      </c>
+      <c r="W136">
+        <v>1.17</v>
+      </c>
+      <c r="X136">
+        <v>17</v>
+      </c>
+      <c r="Y136">
+        <v>1.03</v>
+      </c>
+      <c r="Z136">
+        <v>2.7</v>
+      </c>
+      <c r="AA136">
+        <v>2.75</v>
+      </c>
+      <c r="AB136">
+        <v>3.1</v>
+      </c>
+      <c r="AC136">
+        <v>1.15</v>
+      </c>
+      <c r="AD136">
+        <v>5.25</v>
+      </c>
+      <c r="AE136">
+        <v>1.7</v>
+      </c>
+      <c r="AF136">
+        <v>2.05</v>
+      </c>
+      <c r="AG136">
+        <v>3.4</v>
+      </c>
+      <c r="AH136">
+        <v>1.33</v>
+      </c>
+      <c r="AI136">
+        <v>2.5</v>
+      </c>
+      <c r="AJ136">
+        <v>1.5</v>
+      </c>
+      <c r="AK136">
+        <v>1.35</v>
+      </c>
+      <c r="AL136">
+        <v>1.42</v>
+      </c>
+      <c r="AM136">
+        <v>1.47</v>
+      </c>
+      <c r="AN136">
+        <v>0.67</v>
+      </c>
+      <c r="AO136">
+        <v>1.75</v>
+      </c>
+      <c r="AP136">
+        <v>0.75</v>
+      </c>
+      <c r="AQ136">
+        <v>1.6</v>
+      </c>
+      <c r="AR136">
+        <v>1.23</v>
+      </c>
+      <c r="AS136">
+        <v>0.91</v>
+      </c>
+      <c r="AT136">
+        <v>2.14</v>
+      </c>
+      <c r="AU136">
+        <v>2</v>
+      </c>
+      <c r="AV136">
+        <v>3</v>
+      </c>
+      <c r="AW136">
+        <v>5</v>
+      </c>
+      <c r="AX136">
+        <v>9</v>
+      </c>
+      <c r="AY136">
+        <v>7</v>
+      </c>
+      <c r="AZ136">
+        <v>15</v>
+      </c>
+      <c r="BA136">
+        <v>3</v>
+      </c>
+      <c r="BB136">
+        <v>6</v>
+      </c>
+      <c r="BC136">
+        <v>9</v>
+      </c>
+      <c r="BD136">
+        <v>1.72</v>
+      </c>
+      <c r="BE136">
+        <v>6.4</v>
+      </c>
+      <c r="BF136">
+        <v>2.38</v>
+      </c>
+      <c r="BG136">
+        <v>1.54</v>
+      </c>
+      <c r="BH136">
+        <v>2.3</v>
+      </c>
+      <c r="BI136">
+        <v>1.91</v>
+      </c>
+      <c r="BJ136">
+        <v>1.78</v>
+      </c>
+      <c r="BK136">
+        <v>2.43</v>
+      </c>
+      <c r="BL136">
+        <v>1.48</v>
+      </c>
+      <c r="BM136">
+        <v>3.2</v>
+      </c>
+      <c r="BN136">
+        <v>1.28</v>
+      </c>
+      <c r="BO136">
+        <v>4.35</v>
+      </c>
+      <c r="BP136">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7820452</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45731.66666666666</v>
+      </c>
+      <c r="F137">
+        <v>10</v>
+      </c>
+      <c r="G137" t="s">
+        <v>86</v>
+      </c>
+      <c r="H137" t="s">
+        <v>95</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137" t="s">
+        <v>100</v>
+      </c>
+      <c r="P137" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q137">
+        <v>6.5</v>
+      </c>
+      <c r="R137">
+        <v>2.05</v>
+      </c>
+      <c r="S137">
+        <v>2.25</v>
+      </c>
+      <c r="T137">
+        <v>1.5</v>
+      </c>
+      <c r="U137">
+        <v>2.5</v>
+      </c>
+      <c r="V137">
+        <v>3.5</v>
+      </c>
+      <c r="W137">
+        <v>1.29</v>
+      </c>
+      <c r="X137">
+        <v>10</v>
+      </c>
+      <c r="Y137">
+        <v>1.06</v>
+      </c>
+      <c r="Z137">
+        <v>6.99</v>
+      </c>
+      <c r="AA137">
+        <v>3.52</v>
+      </c>
+      <c r="AB137">
+        <v>1.54</v>
+      </c>
+      <c r="AC137">
+        <v>1.07</v>
+      </c>
+      <c r="AD137">
+        <v>8</v>
+      </c>
+      <c r="AE137">
+        <v>1.42</v>
+      </c>
+      <c r="AF137">
+        <v>2.8</v>
+      </c>
+      <c r="AG137">
+        <v>2.3</v>
+      </c>
+      <c r="AH137">
+        <v>1.6</v>
+      </c>
+      <c r="AI137">
+        <v>2.25</v>
+      </c>
+      <c r="AJ137">
+        <v>1.57</v>
+      </c>
+      <c r="AK137">
+        <v>2.2</v>
+      </c>
+      <c r="AL137">
+        <v>1.27</v>
+      </c>
+      <c r="AM137">
+        <v>1.13</v>
+      </c>
+      <c r="AN137">
+        <v>1</v>
+      </c>
+      <c r="AO137">
+        <v>1.5</v>
+      </c>
+      <c r="AP137">
+        <v>1</v>
+      </c>
+      <c r="AQ137">
+        <v>1.4</v>
+      </c>
+      <c r="AR137">
+        <v>1.28</v>
+      </c>
+      <c r="AS137">
+        <v>1.61</v>
+      </c>
+      <c r="AT137">
+        <v>2.89</v>
+      </c>
+      <c r="AU137">
+        <v>2</v>
+      </c>
+      <c r="AV137">
+        <v>4</v>
+      </c>
+      <c r="AW137">
+        <v>3</v>
+      </c>
+      <c r="AX137">
+        <v>14</v>
+      </c>
+      <c r="AY137">
+        <v>6</v>
+      </c>
+      <c r="AZ137">
+        <v>23</v>
+      </c>
+      <c r="BA137">
+        <v>5</v>
+      </c>
+      <c r="BB137">
+        <v>6</v>
+      </c>
+      <c r="BC137">
+        <v>11</v>
+      </c>
+      <c r="BD137">
+        <v>3.05</v>
+      </c>
+      <c r="BE137">
+        <v>6.75</v>
+      </c>
+      <c r="BF137">
+        <v>1.46</v>
+      </c>
+      <c r="BG137">
+        <v>1.46</v>
+      </c>
+      <c r="BH137">
+        <v>2.5</v>
+      </c>
+      <c r="BI137">
+        <v>1.74</v>
+      </c>
+      <c r="BJ137">
+        <v>1.96</v>
+      </c>
+      <c r="BK137">
+        <v>2.2</v>
+      </c>
+      <c r="BL137">
+        <v>1.58</v>
+      </c>
+      <c r="BM137">
+        <v>2.9</v>
+      </c>
+      <c r="BN137">
+        <v>1.34</v>
+      </c>
+      <c r="BO137">
+        <v>3.9</v>
+      </c>
+      <c r="BP137">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="236">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -559,6 +559,15 @@
     <t>['38', '55']</t>
   </si>
   <si>
+    <t>['25']</t>
+  </si>
+  <si>
+    <t>['33', '54']</t>
+  </si>
+  <si>
+    <t>['69', '88']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -703,9 +712,6 @@
     <t>['12', '74']</t>
   </si>
   <si>
-    <t>['25']</t>
-  </si>
-  <si>
     <t>['7', '81']</t>
   </si>
   <si>
@@ -713,6 +719,9 @@
   </si>
   <si>
     <t>['10', '89']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP137"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1330,7 +1339,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1742,7 +1751,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1823,7 +1832,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ4">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2154,7 +2163,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2360,7 +2369,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2978,7 +2987,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3265,7 +3274,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3468,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ12">
         <v>0</v>
@@ -3677,7 +3686,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ13">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4501,7 +4510,7 @@
         <v>1</v>
       </c>
       <c r="AQ17">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4832,7 +4841,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5116,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20">
         <v>1.6</v>
@@ -5450,7 +5459,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5656,7 +5665,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5862,7 +5871,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6146,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ25">
         <v>1.2</v>
@@ -6274,7 +6283,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6686,7 +6695,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -8334,7 +8343,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -9033,7 +9042,7 @@
         <v>3</v>
       </c>
       <c r="AQ39">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR39">
         <v>1.95</v>
@@ -9158,7 +9167,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9648,7 +9657,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ42">
         <v>0.75</v>
@@ -9776,7 +9785,7 @@
         <v>100</v>
       </c>
       <c r="P43" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q43">
         <v>2.63</v>
@@ -9857,7 +9866,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR43">
         <v>1.93</v>
@@ -10188,7 +10197,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10394,7 +10403,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10600,7 +10609,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10678,7 +10687,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ47">
         <v>0.5</v>
@@ -10806,7 +10815,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11093,7 +11102,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ49">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR49">
         <v>1.6</v>
@@ -11296,7 +11305,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ50">
         <v>1.8</v>
@@ -11424,7 +11433,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -12042,7 +12051,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12866,7 +12875,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13484,7 +13493,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13771,7 +13780,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ62">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR62">
         <v>1.19</v>
@@ -13974,7 +13983,7 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ63">
         <v>0.75</v>
@@ -14720,7 +14729,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14926,7 +14935,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15625,7 +15634,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ71">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR71">
         <v>1.67</v>
@@ -15750,7 +15759,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -15831,7 +15840,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR72">
         <v>1.31</v>
@@ -15956,7 +15965,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q73">
         <v>3.25</v>
@@ -16574,7 +16583,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16780,7 +16789,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16986,7 +16995,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17398,7 +17407,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17604,7 +17613,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17810,7 +17819,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18300,7 +18309,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ84">
         <v>0</v>
@@ -18428,7 +18437,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18634,7 +18643,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -18712,7 +18721,7 @@
         <v>3</v>
       </c>
       <c r="AP86">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ86">
         <v>1.6</v>
@@ -19046,7 +19055,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19252,7 +19261,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19458,7 +19467,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19745,7 +19754,7 @@
         <v>1</v>
       </c>
       <c r="AQ91">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR91">
         <v>1.17</v>
@@ -19870,7 +19879,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19948,7 +19957,7 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ92">
         <v>0.33</v>
@@ -20694,7 +20703,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20900,7 +20909,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21390,7 +21399,7 @@
         <v>2.33</v>
       </c>
       <c r="AP99">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ99">
         <v>1.6</v>
@@ -21724,7 +21733,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -21805,7 +21814,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ101">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR101">
         <v>1.82</v>
@@ -22011,7 +22020,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ102">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR102">
         <v>1.05</v>
@@ -22217,7 +22226,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ103">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR103">
         <v>1.55</v>
@@ -23166,7 +23175,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23372,7 +23381,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23659,7 +23668,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ110">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR110">
         <v>1.45</v>
@@ -23784,7 +23793,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -23990,7 +23999,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24402,7 +24411,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24608,7 +24617,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24814,7 +24823,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25020,7 +25029,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25101,7 +25110,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ117">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR117">
         <v>1.81</v>
@@ -25432,7 +25441,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25638,7 +25647,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -26050,7 +26059,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26256,7 +26265,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26462,7 +26471,7 @@
         <v>100</v>
       </c>
       <c r="P124" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="Q124">
         <v>2.63</v>
@@ -26952,7 +26961,7 @@
         <v>1.67</v>
       </c>
       <c r="AP126">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ126">
         <v>1.5</v>
@@ -27286,7 +27295,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28110,7 +28119,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28728,7 +28737,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -29297,6 +29306,830 @@
       </c>
       <c r="BP137">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7820453</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45731.77083333334</v>
+      </c>
+      <c r="F138">
+        <v>10</v>
+      </c>
+      <c r="G138" t="s">
+        <v>80</v>
+      </c>
+      <c r="H138" t="s">
+        <v>72</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>2</v>
+      </c>
+      <c r="L138">
+        <v>1</v>
+      </c>
+      <c r="M138">
+        <v>1</v>
+      </c>
+      <c r="N138">
+        <v>2</v>
+      </c>
+      <c r="O138" t="s">
+        <v>181</v>
+      </c>
+      <c r="P138" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q138">
+        <v>2.3</v>
+      </c>
+      <c r="R138">
+        <v>2.05</v>
+      </c>
+      <c r="S138">
+        <v>6.5</v>
+      </c>
+      <c r="T138">
+        <v>1.5</v>
+      </c>
+      <c r="U138">
+        <v>2.5</v>
+      </c>
+      <c r="V138">
+        <v>3.5</v>
+      </c>
+      <c r="W138">
+        <v>1.29</v>
+      </c>
+      <c r="X138">
+        <v>11</v>
+      </c>
+      <c r="Y138">
+        <v>1.05</v>
+      </c>
+      <c r="Z138">
+        <v>1.62</v>
+      </c>
+      <c r="AA138">
+        <v>3.6</v>
+      </c>
+      <c r="AB138">
+        <v>6</v>
+      </c>
+      <c r="AC138">
+        <v>1.07</v>
+      </c>
+      <c r="AD138">
+        <v>8</v>
+      </c>
+      <c r="AE138">
+        <v>1.42</v>
+      </c>
+      <c r="AF138">
+        <v>2.8</v>
+      </c>
+      <c r="AG138">
+        <v>2.3</v>
+      </c>
+      <c r="AH138">
+        <v>1.6</v>
+      </c>
+      <c r="AI138">
+        <v>2.2</v>
+      </c>
+      <c r="AJ138">
+        <v>1.62</v>
+      </c>
+      <c r="AK138">
+        <v>1.14</v>
+      </c>
+      <c r="AL138">
+        <v>1.27</v>
+      </c>
+      <c r="AM138">
+        <v>2.2</v>
+      </c>
+      <c r="AN138">
+        <v>3</v>
+      </c>
+      <c r="AO138">
+        <v>0.75</v>
+      </c>
+      <c r="AP138">
+        <v>2.6</v>
+      </c>
+      <c r="AQ138">
+        <v>0.8</v>
+      </c>
+      <c r="AR138">
+        <v>1.9</v>
+      </c>
+      <c r="AS138">
+        <v>1.47</v>
+      </c>
+      <c r="AT138">
+        <v>3.37</v>
+      </c>
+      <c r="AU138">
+        <v>7</v>
+      </c>
+      <c r="AV138">
+        <v>3</v>
+      </c>
+      <c r="AW138">
+        <v>10</v>
+      </c>
+      <c r="AX138">
+        <v>5</v>
+      </c>
+      <c r="AY138">
+        <v>24</v>
+      </c>
+      <c r="AZ138">
+        <v>10</v>
+      </c>
+      <c r="BA138">
+        <v>9</v>
+      </c>
+      <c r="BB138">
+        <v>4</v>
+      </c>
+      <c r="BC138">
+        <v>13</v>
+      </c>
+      <c r="BD138">
+        <v>1.48</v>
+      </c>
+      <c r="BE138">
+        <v>6.75</v>
+      </c>
+      <c r="BF138">
+        <v>2.95</v>
+      </c>
+      <c r="BG138">
+        <v>1.44</v>
+      </c>
+      <c r="BH138">
+        <v>2.55</v>
+      </c>
+      <c r="BI138">
+        <v>1.73</v>
+      </c>
+      <c r="BJ138">
+        <v>1.97</v>
+      </c>
+      <c r="BK138">
+        <v>2.15</v>
+      </c>
+      <c r="BL138">
+        <v>1.61</v>
+      </c>
+      <c r="BM138">
+        <v>2.8</v>
+      </c>
+      <c r="BN138">
+        <v>1.37</v>
+      </c>
+      <c r="BO138">
+        <v>3.65</v>
+      </c>
+      <c r="BP138">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7820454</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45731.77083333334</v>
+      </c>
+      <c r="F139">
+        <v>10</v>
+      </c>
+      <c r="G139" t="s">
+        <v>87</v>
+      </c>
+      <c r="H139" t="s">
+        <v>92</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>1</v>
+      </c>
+      <c r="K139">
+        <v>2</v>
+      </c>
+      <c r="L139">
+        <v>2</v>
+      </c>
+      <c r="M139">
+        <v>1</v>
+      </c>
+      <c r="N139">
+        <v>3</v>
+      </c>
+      <c r="O139" t="s">
+        <v>182</v>
+      </c>
+      <c r="P139" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q139">
+        <v>2.75</v>
+      </c>
+      <c r="R139">
+        <v>1.91</v>
+      </c>
+      <c r="S139">
+        <v>5.5</v>
+      </c>
+      <c r="T139">
+        <v>1.62</v>
+      </c>
+      <c r="U139">
+        <v>2.2</v>
+      </c>
+      <c r="V139">
+        <v>4</v>
+      </c>
+      <c r="W139">
+        <v>1.22</v>
+      </c>
+      <c r="X139">
+        <v>13</v>
+      </c>
+      <c r="Y139">
+        <v>1.04</v>
+      </c>
+      <c r="Z139">
+        <v>1.91</v>
+      </c>
+      <c r="AA139">
+        <v>3.1</v>
+      </c>
+      <c r="AB139">
+        <v>4.75</v>
+      </c>
+      <c r="AC139">
+        <v>1.11</v>
+      </c>
+      <c r="AD139">
+        <v>6.25</v>
+      </c>
+      <c r="AE139">
+        <v>1.51</v>
+      </c>
+      <c r="AF139">
+        <v>2.35</v>
+      </c>
+      <c r="AG139">
+        <v>2.7</v>
+      </c>
+      <c r="AH139">
+        <v>1.44</v>
+      </c>
+      <c r="AI139">
+        <v>2.25</v>
+      </c>
+      <c r="AJ139">
+        <v>1.57</v>
+      </c>
+      <c r="AK139">
+        <v>1.2</v>
+      </c>
+      <c r="AL139">
+        <v>1.34</v>
+      </c>
+      <c r="AM139">
+        <v>1.85</v>
+      </c>
+      <c r="AN139">
+        <v>3</v>
+      </c>
+      <c r="AO139">
+        <v>0.8</v>
+      </c>
+      <c r="AP139">
+        <v>3</v>
+      </c>
+      <c r="AQ139">
+        <v>0.67</v>
+      </c>
+      <c r="AR139">
+        <v>1.28</v>
+      </c>
+      <c r="AS139">
+        <v>1.07</v>
+      </c>
+      <c r="AT139">
+        <v>2.35</v>
+      </c>
+      <c r="AU139">
+        <v>6</v>
+      </c>
+      <c r="AV139">
+        <v>6</v>
+      </c>
+      <c r="AW139">
+        <v>3</v>
+      </c>
+      <c r="AX139">
+        <v>5</v>
+      </c>
+      <c r="AY139">
+        <v>11</v>
+      </c>
+      <c r="AZ139">
+        <v>12</v>
+      </c>
+      <c r="BA139">
+        <v>4</v>
+      </c>
+      <c r="BB139">
+        <v>3</v>
+      </c>
+      <c r="BC139">
+        <v>7</v>
+      </c>
+      <c r="BD139">
+        <v>1.56</v>
+      </c>
+      <c r="BE139">
+        <v>6.75</v>
+      </c>
+      <c r="BF139">
+        <v>2.65</v>
+      </c>
+      <c r="BG139">
+        <v>1.4</v>
+      </c>
+      <c r="BH139">
+        <v>2.7</v>
+      </c>
+      <c r="BI139">
+        <v>1.66</v>
+      </c>
+      <c r="BJ139">
+        <v>2.07</v>
+      </c>
+      <c r="BK139">
+        <v>2.05</v>
+      </c>
+      <c r="BL139">
+        <v>1.67</v>
+      </c>
+      <c r="BM139">
+        <v>2.55</v>
+      </c>
+      <c r="BN139">
+        <v>1.43</v>
+      </c>
+      <c r="BO139">
+        <v>3.4</v>
+      </c>
+      <c r="BP139">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7820456</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45731.875</v>
+      </c>
+      <c r="F140">
+        <v>10</v>
+      </c>
+      <c r="G140" t="s">
+        <v>88</v>
+      </c>
+      <c r="H140" t="s">
+        <v>91</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140" t="s">
+        <v>100</v>
+      </c>
+      <c r="P140" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q140">
+        <v>4.75</v>
+      </c>
+      <c r="R140">
+        <v>1.95</v>
+      </c>
+      <c r="S140">
+        <v>2.75</v>
+      </c>
+      <c r="T140">
+        <v>1.57</v>
+      </c>
+      <c r="U140">
+        <v>2.25</v>
+      </c>
+      <c r="V140">
+        <v>3.75</v>
+      </c>
+      <c r="W140">
+        <v>1.25</v>
+      </c>
+      <c r="X140">
+        <v>11</v>
+      </c>
+      <c r="Y140">
+        <v>1.05</v>
+      </c>
+      <c r="Z140">
+        <v>4</v>
+      </c>
+      <c r="AA140">
+        <v>3.3</v>
+      </c>
+      <c r="AB140">
+        <v>2</v>
+      </c>
+      <c r="AC140">
+        <v>1.1</v>
+      </c>
+      <c r="AD140">
+        <v>6.5</v>
+      </c>
+      <c r="AE140">
+        <v>1.5</v>
+      </c>
+      <c r="AF140">
+        <v>2.55</v>
+      </c>
+      <c r="AG140">
+        <v>2.5</v>
+      </c>
+      <c r="AH140">
+        <v>1.5</v>
+      </c>
+      <c r="AI140">
+        <v>2.2</v>
+      </c>
+      <c r="AJ140">
+        <v>1.62</v>
+      </c>
+      <c r="AK140">
+        <v>1.51</v>
+      </c>
+      <c r="AL140">
+        <v>1.35</v>
+      </c>
+      <c r="AM140">
+        <v>1.38</v>
+      </c>
+      <c r="AN140">
+        <v>1.5</v>
+      </c>
+      <c r="AO140">
+        <v>1.33</v>
+      </c>
+      <c r="AP140">
+        <v>1.4</v>
+      </c>
+      <c r="AQ140">
+        <v>1.25</v>
+      </c>
+      <c r="AR140">
+        <v>1.98</v>
+      </c>
+      <c r="AS140">
+        <v>2.04</v>
+      </c>
+      <c r="AT140">
+        <v>4.02</v>
+      </c>
+      <c r="AU140">
+        <v>3</v>
+      </c>
+      <c r="AV140">
+        <v>8</v>
+      </c>
+      <c r="AW140">
+        <v>6</v>
+      </c>
+      <c r="AX140">
+        <v>8</v>
+      </c>
+      <c r="AY140">
+        <v>10</v>
+      </c>
+      <c r="AZ140">
+        <v>18</v>
+      </c>
+      <c r="BA140">
+        <v>2</v>
+      </c>
+      <c r="BB140">
+        <v>7</v>
+      </c>
+      <c r="BC140">
+        <v>9</v>
+      </c>
+      <c r="BD140">
+        <v>2.23</v>
+      </c>
+      <c r="BE140">
+        <v>6.4</v>
+      </c>
+      <c r="BF140">
+        <v>1.8</v>
+      </c>
+      <c r="BG140">
+        <v>1.41</v>
+      </c>
+      <c r="BH140">
+        <v>2.65</v>
+      </c>
+      <c r="BI140">
+        <v>1.71</v>
+      </c>
+      <c r="BJ140">
+        <v>2</v>
+      </c>
+      <c r="BK140">
+        <v>2.1</v>
+      </c>
+      <c r="BL140">
+        <v>1.64</v>
+      </c>
+      <c r="BM140">
+        <v>2.7</v>
+      </c>
+      <c r="BN140">
+        <v>1.4</v>
+      </c>
+      <c r="BO140">
+        <v>3.55</v>
+      </c>
+      <c r="BP140">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7820455</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45731.875</v>
+      </c>
+      <c r="F141">
+        <v>10</v>
+      </c>
+      <c r="G141" t="s">
+        <v>93</v>
+      </c>
+      <c r="H141" t="s">
+        <v>89</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>2</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>2</v>
+      </c>
+      <c r="O141" t="s">
+        <v>183</v>
+      </c>
+      <c r="P141" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q141">
+        <v>2.5</v>
+      </c>
+      <c r="R141">
+        <v>1.91</v>
+      </c>
+      <c r="S141">
+        <v>6</v>
+      </c>
+      <c r="T141">
+        <v>1.57</v>
+      </c>
+      <c r="U141">
+        <v>2.25</v>
+      </c>
+      <c r="V141">
+        <v>4</v>
+      </c>
+      <c r="W141">
+        <v>1.22</v>
+      </c>
+      <c r="X141">
+        <v>13</v>
+      </c>
+      <c r="Y141">
+        <v>1.04</v>
+      </c>
+      <c r="Z141">
+        <v>1.75</v>
+      </c>
+      <c r="AA141">
+        <v>3.5</v>
+      </c>
+      <c r="AB141">
+        <v>5</v>
+      </c>
+      <c r="AC141">
+        <v>1.11</v>
+      </c>
+      <c r="AD141">
+        <v>6.25</v>
+      </c>
+      <c r="AE141">
+        <v>1.53</v>
+      </c>
+      <c r="AF141">
+        <v>2.3</v>
+      </c>
+      <c r="AG141">
+        <v>2.6</v>
+      </c>
+      <c r="AH141">
+        <v>1.48</v>
+      </c>
+      <c r="AI141">
+        <v>2.5</v>
+      </c>
+      <c r="AJ141">
+        <v>1.5</v>
+      </c>
+      <c r="AK141">
+        <v>1.17</v>
+      </c>
+      <c r="AL141">
+        <v>1.34</v>
+      </c>
+      <c r="AM141">
+        <v>1.93</v>
+      </c>
+      <c r="AN141">
+        <v>2.5</v>
+      </c>
+      <c r="AO141">
+        <v>1.75</v>
+      </c>
+      <c r="AP141">
+        <v>2.6</v>
+      </c>
+      <c r="AQ141">
+        <v>1.4</v>
+      </c>
+      <c r="AR141">
+        <v>1.7</v>
+      </c>
+      <c r="AS141">
+        <v>1.26</v>
+      </c>
+      <c r="AT141">
+        <v>2.96</v>
+      </c>
+      <c r="AU141">
+        <v>6</v>
+      </c>
+      <c r="AV141">
+        <v>2</v>
+      </c>
+      <c r="AW141">
+        <v>2</v>
+      </c>
+      <c r="AX141">
+        <v>4</v>
+      </c>
+      <c r="AY141">
+        <v>8</v>
+      </c>
+      <c r="AZ141">
+        <v>7</v>
+      </c>
+      <c r="BA141">
+        <v>1</v>
+      </c>
+      <c r="BB141">
+        <v>4</v>
+      </c>
+      <c r="BC141">
+        <v>5</v>
+      </c>
+      <c r="BD141">
+        <v>1.5</v>
+      </c>
+      <c r="BE141">
+        <v>6.4</v>
+      </c>
+      <c r="BF141">
+        <v>2.9</v>
+      </c>
+      <c r="BG141">
+        <v>1.49</v>
+      </c>
+      <c r="BH141">
+        <v>2.4</v>
+      </c>
+      <c r="BI141">
+        <v>1.83</v>
+      </c>
+      <c r="BJ141">
+        <v>1.85</v>
+      </c>
+      <c r="BK141">
+        <v>2.32</v>
+      </c>
+      <c r="BL141">
+        <v>1.53</v>
+      </c>
+      <c r="BM141">
+        <v>3</v>
+      </c>
+      <c r="BN141">
+        <v>1.32</v>
+      </c>
+      <c r="BO141">
+        <v>4.1</v>
+      </c>
+      <c r="BP141">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="236">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -364,10 +364,10 @@
     <t>['20', '62', '68', '82']</t>
   </si>
   <si>
-    <t>['44', '55']</t>
+    <t>['20']</t>
   </si>
   <si>
-    <t>['20']</t>
+    <t>['44', '55']</t>
   </si>
   <si>
     <t>['18']</t>
@@ -475,10 +475,10 @@
     <t>['77']</t>
   </si>
   <si>
-    <t>['51']</t>
+    <t>['73']</t>
   </si>
   <si>
-    <t>['73']</t>
+    <t>['51']</t>
   </si>
   <si>
     <t>['84', '90+5']</t>
@@ -559,10 +559,10 @@
     <t>['38', '55']</t>
   </si>
   <si>
-    <t>['25']</t>
+    <t>['33', '54']</t>
   </si>
   <si>
-    <t>['33', '54']</t>
+    <t>['25']</t>
   </si>
   <si>
     <t>['69', '88']</t>
@@ -634,10 +634,10 @@
     <t>['57']</t>
   </si>
   <si>
-    <t>['64']</t>
+    <t>['31']</t>
   </si>
   <si>
-    <t>['31']</t>
+    <t>['64']</t>
   </si>
   <si>
     <t>['86']</t>
@@ -1083,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP141"/>
+  <dimension ref="A1:BP142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2450,7 +2450,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ7">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ8">
         <v>0.2</v>
@@ -7065,7 +7065,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>7820344</v>
+        <v>7820343</v>
       </c>
       <c r="C30" t="s">
         <v>68</v>
@@ -7080,10 +7080,10 @@
         <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H30" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -7095,13 +7095,13 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" t="s">
         <v>116</v>
@@ -7110,13 +7110,13 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="R30">
         <v>1.91</v>
       </c>
       <c r="S30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>1.62</v>
@@ -7137,13 +7137,13 @@
         <v>1.04</v>
       </c>
       <c r="Z30">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA30">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB30">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC30">
         <v>1.12</v>
@@ -7152,118 +7152,118 @@
         <v>5.75</v>
       </c>
       <c r="AE30">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AF30">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG30">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH30">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AI30">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AJ30">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AK30">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AL30">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AM30">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>1.83</v>
+      </c>
+      <c r="AQ30">
+        <v>1.8</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
         <v>3</v>
       </c>
-      <c r="AO30">
-        <v>3</v>
-      </c>
-      <c r="AP30">
-        <v>2.17</v>
-      </c>
-      <c r="AQ30">
-        <v>0.8</v>
-      </c>
-      <c r="AR30">
-        <v>1.4</v>
-      </c>
-      <c r="AS30">
-        <v>1.7</v>
-      </c>
-      <c r="AT30">
-        <v>3.1</v>
-      </c>
-      <c r="AU30">
-        <v>7</v>
-      </c>
       <c r="AV30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX30">
         <v>6</v>
       </c>
       <c r="AY30">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD30">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="BE30">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF30">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="BG30">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BH30">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="BI30">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="BJ30">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BK30">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="BL30">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="BM30">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="BN30">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BO30">
-        <v>4.3</v>
+        <v>3.88</v>
       </c>
       <c r="BP30">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="31" spans="1:68">
@@ -7271,7 +7271,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>7820343</v>
+        <v>7820344</v>
       </c>
       <c r="C31" t="s">
         <v>68</v>
@@ -7286,10 +7286,10 @@
         <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -7301,13 +7301,13 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" t="s">
         <v>117</v>
@@ -7316,13 +7316,13 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="R31">
         <v>1.91</v>
       </c>
       <c r="S31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31">
         <v>1.62</v>
@@ -7343,13 +7343,13 @@
         <v>1.04</v>
       </c>
       <c r="Z31">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AA31">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB31">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AC31">
         <v>1.12</v>
@@ -7358,118 +7358,118 @@
         <v>5.75</v>
       </c>
       <c r="AE31">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF31">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG31">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AH31">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI31">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AJ31">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK31">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AL31">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AM31">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AQ31">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU31">
+        <v>7</v>
+      </c>
+      <c r="AV31">
         <v>3</v>
       </c>
-      <c r="AV31">
-        <v>0</v>
-      </c>
       <c r="AW31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX31">
         <v>6</v>
       </c>
       <c r="AY31">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA31">
+        <v>4</v>
+      </c>
+      <c r="BB31">
+        <v>1</v>
+      </c>
+      <c r="BC31">
         <v>5</v>
       </c>
-      <c r="BB31">
-        <v>2</v>
-      </c>
-      <c r="BC31">
-        <v>7</v>
-      </c>
       <c r="BD31">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="BE31">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="BF31">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="BG31">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="BH31">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="BI31">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BJ31">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="BK31">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="BL31">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BM31">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="BN31">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BO31">
-        <v>3.88</v>
+        <v>4.3</v>
       </c>
       <c r="BP31">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="32" spans="1:68">
@@ -9039,7 +9039,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ39">
         <v>0.67</v>
@@ -9660,7 +9660,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ42">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR42">
         <v>2.46</v>
@@ -9743,7 +9743,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>7820356</v>
+        <v>7820357</v>
       </c>
       <c r="C43" t="s">
         <v>68</v>
@@ -9758,190 +9758,190 @@
         <v>3</v>
       </c>
       <c r="G43" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="H43" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
       <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43" t="s">
+        <v>113</v>
+      </c>
+      <c r="P43" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q43">
+        <v>3.1</v>
+      </c>
+      <c r="R43">
+        <v>1.73</v>
+      </c>
+      <c r="S43">
+        <v>5.5</v>
+      </c>
+      <c r="T43">
+        <v>1.83</v>
+      </c>
+      <c r="U43">
+        <v>1.83</v>
+      </c>
+      <c r="V43">
+        <v>6</v>
+      </c>
+      <c r="W43">
+        <v>1.13</v>
+      </c>
+      <c r="X43">
+        <v>21</v>
+      </c>
+      <c r="Y43">
+        <v>1.02</v>
+      </c>
+      <c r="Z43">
+        <v>2.15</v>
+      </c>
+      <c r="AA43">
+        <v>2.7</v>
+      </c>
+      <c r="AB43">
+        <v>4.33</v>
+      </c>
+      <c r="AC43">
+        <v>1.18</v>
+      </c>
+      <c r="AD43">
+        <v>4.56</v>
+      </c>
+      <c r="AE43">
+        <v>1.94</v>
+      </c>
+      <c r="AF43">
+        <v>1.89</v>
+      </c>
+      <c r="AG43">
+        <v>4</v>
+      </c>
+      <c r="AH43">
+        <v>1.25</v>
+      </c>
+      <c r="AI43">
         <v>3</v>
       </c>
-      <c r="K43">
+      <c r="AJ43">
+        <v>1.36</v>
+      </c>
+      <c r="AK43">
+        <v>1.21</v>
+      </c>
+      <c r="AL43">
+        <v>1.44</v>
+      </c>
+      <c r="AM43">
+        <v>1.66</v>
+      </c>
+      <c r="AN43">
         <v>3</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>3</v>
-      </c>
-      <c r="N43">
-        <v>3</v>
-      </c>
-      <c r="O43" t="s">
-        <v>100</v>
-      </c>
-      <c r="P43" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q43">
-        <v>2.63</v>
-      </c>
-      <c r="R43">
-        <v>1.95</v>
-      </c>
-      <c r="S43">
-        <v>5</v>
-      </c>
-      <c r="T43">
-        <v>1.57</v>
-      </c>
-      <c r="U43">
-        <v>2.25</v>
-      </c>
-      <c r="V43">
-        <v>3.75</v>
-      </c>
-      <c r="W43">
-        <v>1.25</v>
-      </c>
-      <c r="X43">
-        <v>11</v>
-      </c>
-      <c r="Y43">
-        <v>1.05</v>
-      </c>
-      <c r="Z43">
-        <v>1.9</v>
-      </c>
-      <c r="AA43">
-        <v>3.3</v>
-      </c>
-      <c r="AB43">
-        <v>4.5</v>
-      </c>
-      <c r="AC43">
-        <v>1.08</v>
-      </c>
-      <c r="AD43">
-        <v>7.37</v>
-      </c>
-      <c r="AE43">
-        <v>1.48</v>
-      </c>
-      <c r="AF43">
-        <v>2.63</v>
-      </c>
-      <c r="AG43">
-        <v>2.5</v>
-      </c>
-      <c r="AH43">
-        <v>1.5</v>
-      </c>
-      <c r="AI43">
-        <v>2.2</v>
-      </c>
-      <c r="AJ43">
-        <v>1.62</v>
-      </c>
-      <c r="AK43">
-        <v>1.2</v>
-      </c>
-      <c r="AL43">
-        <v>1.34</v>
-      </c>
-      <c r="AM43">
-        <v>1.83</v>
-      </c>
-      <c r="AN43">
-        <v>1</v>
       </c>
       <c r="AO43">
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AQ43">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR43">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="AS43">
-        <v>1.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AT43">
-        <v>3.4</v>
+        <v>2.02</v>
       </c>
       <c r="AU43">
+        <v>6</v>
+      </c>
+      <c r="AV43">
+        <v>4</v>
+      </c>
+      <c r="AW43">
+        <v>9</v>
+      </c>
+      <c r="AX43">
+        <v>2</v>
+      </c>
+      <c r="AY43">
+        <v>19</v>
+      </c>
+      <c r="AZ43">
+        <v>6</v>
+      </c>
+      <c r="BA43">
         <v>5</v>
       </c>
-      <c r="AV43">
-        <v>6</v>
-      </c>
-      <c r="AW43">
-        <v>13</v>
-      </c>
-      <c r="AX43">
-        <v>6</v>
-      </c>
-      <c r="AY43">
-        <v>23</v>
-      </c>
-      <c r="AZ43">
-        <v>12</v>
-      </c>
-      <c r="BA43">
-        <v>6</v>
-      </c>
       <c r="BB43">
         <v>2</v>
       </c>
       <c r="BC43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD43">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BE43">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF43">
+        <v>3.2</v>
+      </c>
+      <c r="BG43">
+        <v>1.53</v>
+      </c>
+      <c r="BH43">
+        <v>2.32</v>
+      </c>
+      <c r="BI43">
+        <v>1.89</v>
+      </c>
+      <c r="BJ43">
+        <v>1.8</v>
+      </c>
+      <c r="BK43">
+        <v>2.4</v>
+      </c>
+      <c r="BL43">
+        <v>1.49</v>
+      </c>
+      <c r="BM43">
         <v>3.15</v>
       </c>
-      <c r="BG43">
-        <v>1.29</v>
-      </c>
-      <c r="BH43">
-        <v>3.15</v>
-      </c>
-      <c r="BI43">
-        <v>1.5</v>
-      </c>
-      <c r="BJ43">
-        <v>2.38</v>
-      </c>
-      <c r="BK43">
-        <v>1.82</v>
-      </c>
-      <c r="BL43">
-        <v>1.86</v>
-      </c>
-      <c r="BM43">
-        <v>2.28</v>
-      </c>
       <c r="BN43">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="BO43">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP43">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="44" spans="1:68">
@@ -9949,7 +9949,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>7820357</v>
+        <v>7820356</v>
       </c>
       <c r="C44" t="s">
         <v>68</v>
@@ -9964,190 +9964,190 @@
         <v>3</v>
       </c>
       <c r="G44" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O44" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>100</v>
+        <v>197</v>
       </c>
       <c r="Q44">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="R44">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="S44">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="T44">
+        <v>1.57</v>
+      </c>
+      <c r="U44">
+        <v>2.25</v>
+      </c>
+      <c r="V44">
+        <v>3.75</v>
+      </c>
+      <c r="W44">
+        <v>1.25</v>
+      </c>
+      <c r="X44">
+        <v>11</v>
+      </c>
+      <c r="Y44">
+        <v>1.05</v>
+      </c>
+      <c r="Z44">
+        <v>1.9</v>
+      </c>
+      <c r="AA44">
+        <v>3.3</v>
+      </c>
+      <c r="AB44">
+        <v>4.5</v>
+      </c>
+      <c r="AC44">
+        <v>1.08</v>
+      </c>
+      <c r="AD44">
+        <v>7.37</v>
+      </c>
+      <c r="AE44">
+        <v>1.48</v>
+      </c>
+      <c r="AF44">
+        <v>2.63</v>
+      </c>
+      <c r="AG44">
+        <v>2.5</v>
+      </c>
+      <c r="AH44">
+        <v>1.5</v>
+      </c>
+      <c r="AI44">
+        <v>2.2</v>
+      </c>
+      <c r="AJ44">
+        <v>1.62</v>
+      </c>
+      <c r="AK44">
+        <v>1.2</v>
+      </c>
+      <c r="AL44">
+        <v>1.34</v>
+      </c>
+      <c r="AM44">
         <v>1.83</v>
       </c>
-      <c r="U44">
-        <v>1.83</v>
-      </c>
-      <c r="V44">
-        <v>6</v>
-      </c>
-      <c r="W44">
-        <v>1.13</v>
-      </c>
-      <c r="X44">
-        <v>21</v>
-      </c>
-      <c r="Y44">
-        <v>1.02</v>
-      </c>
-      <c r="Z44">
-        <v>2.15</v>
-      </c>
-      <c r="AA44">
-        <v>2.7</v>
-      </c>
-      <c r="AB44">
-        <v>4.33</v>
-      </c>
-      <c r="AC44">
-        <v>1.18</v>
-      </c>
-      <c r="AD44">
-        <v>4.56</v>
-      </c>
-      <c r="AE44">
-        <v>1.94</v>
-      </c>
-      <c r="AF44">
-        <v>1.89</v>
-      </c>
-      <c r="AG44">
-        <v>4</v>
-      </c>
-      <c r="AH44">
-        <v>1.25</v>
-      </c>
-      <c r="AI44">
-        <v>3</v>
-      </c>
-      <c r="AJ44">
-        <v>1.36</v>
-      </c>
-      <c r="AK44">
-        <v>1.21</v>
-      </c>
-      <c r="AL44">
-        <v>1.44</v>
-      </c>
-      <c r="AM44">
-        <v>1.66</v>
-      </c>
       <c r="AN44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO44">
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR44">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="AS44">
-        <v>0.6899999999999999</v>
+        <v>1.47</v>
       </c>
       <c r="AT44">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="AU44">
+        <v>5</v>
+      </c>
+      <c r="AV44">
         <v>6</v>
       </c>
-      <c r="AV44">
-        <v>4</v>
-      </c>
       <c r="AW44">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX44">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY44">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AZ44">
+        <v>12</v>
+      </c>
+      <c r="BA44">
         <v>6</v>
       </c>
-      <c r="BA44">
-        <v>5</v>
-      </c>
       <c r="BB44">
         <v>2</v>
       </c>
       <c r="BC44">
+        <v>8</v>
+      </c>
+      <c r="BD44">
+        <v>1.43</v>
+      </c>
+      <c r="BE44">
         <v>7</v>
       </c>
-      <c r="BD44">
-        <v>1.42</v>
-      </c>
-      <c r="BE44">
-        <v>6.75</v>
-      </c>
       <c r="BF44">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG44">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="BH44">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="BI44">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="BJ44">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="BK44">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="BL44">
-        <v>1.49</v>
+        <v>1.86</v>
       </c>
       <c r="BM44">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="BN44">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="BO44">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="BP44">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="45" spans="1:68">
@@ -14192,7 +14192,7 @@
         <v>3</v>
       </c>
       <c r="AQ64">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR64">
         <v>1.42</v>
@@ -15219,7 +15219,7 @@
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ69">
         <v>0.25</v>
@@ -15717,7 +15717,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>7820387</v>
+        <v>7820386</v>
       </c>
       <c r="C72" t="s">
         <v>68</v>
@@ -15732,190 +15732,190 @@
         <v>5</v>
       </c>
       <c r="G72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72">
         <v>1</v>
       </c>
       <c r="N72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O72" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="P72" t="s">
         <v>206</v>
       </c>
       <c r="Q72">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="R72">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S72">
+        <v>4.75</v>
+      </c>
+      <c r="T72">
+        <v>1.73</v>
+      </c>
+      <c r="U72">
+        <v>2</v>
+      </c>
+      <c r="V72">
+        <v>5</v>
+      </c>
+      <c r="W72">
+        <v>1.17</v>
+      </c>
+      <c r="X72">
+        <v>17</v>
+      </c>
+      <c r="Y72">
+        <v>1.03</v>
+      </c>
+      <c r="Z72">
+        <v>2.25</v>
+      </c>
+      <c r="AA72">
+        <v>2.63</v>
+      </c>
+      <c r="AB72">
+        <v>4</v>
+      </c>
+      <c r="AC72">
+        <v>1.17</v>
+      </c>
+      <c r="AD72">
+        <v>4.6</v>
+      </c>
+      <c r="AE72">
+        <v>1.7</v>
+      </c>
+      <c r="AF72">
+        <v>2</v>
+      </c>
+      <c r="AG72">
+        <v>3.5</v>
+      </c>
+      <c r="AH72">
+        <v>1.3</v>
+      </c>
+      <c r="AI72">
+        <v>2.63</v>
+      </c>
+      <c r="AJ72">
+        <v>1.44</v>
+      </c>
+      <c r="AK72">
+        <v>1.26</v>
+      </c>
+      <c r="AL72">
+        <v>1.44</v>
+      </c>
+      <c r="AM72">
+        <v>1.57</v>
+      </c>
+      <c r="AN72">
+        <v>2</v>
+      </c>
+      <c r="AO72">
+        <v>1.5</v>
+      </c>
+      <c r="AP72">
+        <v>2</v>
+      </c>
+      <c r="AQ72">
+        <v>1</v>
+      </c>
+      <c r="AR72">
+        <v>1.21</v>
+      </c>
+      <c r="AS72">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AT72">
+        <v>2.02</v>
+      </c>
+      <c r="AU72">
+        <v>8</v>
+      </c>
+      <c r="AV72">
+        <v>4</v>
+      </c>
+      <c r="AW72">
+        <v>7</v>
+      </c>
+      <c r="AX72">
+        <v>5</v>
+      </c>
+      <c r="AY72">
+        <v>16</v>
+      </c>
+      <c r="AZ72">
+        <v>10</v>
+      </c>
+      <c r="BA72">
         <v>3</v>
       </c>
-      <c r="T72">
-        <v>1.62</v>
-      </c>
-      <c r="U72">
-        <v>2.2</v>
-      </c>
-      <c r="V72">
+      <c r="BB72">
         <v>4</v>
       </c>
-      <c r="W72">
+      <c r="BC72">
+        <v>7</v>
+      </c>
+      <c r="BD72">
+        <v>1.61</v>
+      </c>
+      <c r="BE72">
+        <v>6.45</v>
+      </c>
+      <c r="BF72">
+        <v>3.15</v>
+      </c>
+      <c r="BG72">
+        <v>1.51</v>
+      </c>
+      <c r="BH72">
+        <v>2.32</v>
+      </c>
+      <c r="BI72">
+        <v>1.95</v>
+      </c>
+      <c r="BJ72">
+        <v>1.77</v>
+      </c>
+      <c r="BK72">
+        <v>2.54</v>
+      </c>
+      <c r="BL72">
+        <v>1.43</v>
+      </c>
+      <c r="BM72">
+        <v>3.5</v>
+      </c>
+      <c r="BN72">
         <v>1.22</v>
       </c>
-      <c r="X72">
-        <v>13</v>
-      </c>
-      <c r="Y72">
-        <v>1.04</v>
-      </c>
-      <c r="Z72">
-        <v>3.75</v>
-      </c>
-      <c r="AA72">
-        <v>3.1</v>
-      </c>
-      <c r="AB72">
-        <v>2.1</v>
-      </c>
-      <c r="AC72">
-        <v>1.12</v>
-      </c>
-      <c r="AD72">
-        <v>5.75</v>
-      </c>
-      <c r="AE72">
-        <v>1.55</v>
-      </c>
-      <c r="AF72">
-        <v>2.25</v>
-      </c>
-      <c r="AG72">
-        <v>2.7</v>
-      </c>
-      <c r="AH72">
-        <v>1.44</v>
-      </c>
-      <c r="AI72">
-        <v>2.2</v>
-      </c>
-      <c r="AJ72">
-        <v>1.62</v>
-      </c>
-      <c r="AK72">
-        <v>1.66</v>
-      </c>
-      <c r="AL72">
-        <v>1.37</v>
-      </c>
-      <c r="AM72">
-        <v>1.26</v>
-      </c>
-      <c r="AN72">
-        <v>0.5</v>
-      </c>
-      <c r="AO72">
-        <v>0</v>
-      </c>
-      <c r="AP72">
-        <v>0.8</v>
-      </c>
-      <c r="AQ72">
-        <v>1.25</v>
-      </c>
-      <c r="AR72">
-        <v>1.31</v>
-      </c>
-      <c r="AS72">
-        <v>2.1</v>
-      </c>
-      <c r="AT72">
-        <v>3.41</v>
-      </c>
-      <c r="AU72">
-        <v>7</v>
-      </c>
-      <c r="AV72">
-        <v>9</v>
-      </c>
-      <c r="AW72">
-        <v>8</v>
-      </c>
-      <c r="AX72">
-        <v>8</v>
-      </c>
-      <c r="AY72">
-        <v>18</v>
-      </c>
-      <c r="AZ72">
-        <v>19</v>
-      </c>
-      <c r="BA72">
-        <v>4</v>
-      </c>
-      <c r="BB72">
-        <v>2</v>
-      </c>
-      <c r="BC72">
-        <v>6</v>
-      </c>
-      <c r="BD72">
-        <v>2.09</v>
-      </c>
-      <c r="BE72">
-        <v>6.15</v>
-      </c>
-      <c r="BF72">
-        <v>2.21</v>
-      </c>
-      <c r="BG72">
-        <v>1.45</v>
-      </c>
-      <c r="BH72">
-        <v>2.48</v>
-      </c>
-      <c r="BI72">
-        <v>1.83</v>
-      </c>
-      <c r="BJ72">
-        <v>1.87</v>
-      </c>
-      <c r="BK72">
-        <v>2.38</v>
-      </c>
-      <c r="BL72">
-        <v>1.49</v>
-      </c>
-      <c r="BM72">
-        <v>3.2</v>
-      </c>
-      <c r="BN72">
-        <v>1.26</v>
-      </c>
       <c r="BO72">
-        <v>4.65</v>
+        <v>5.1</v>
       </c>
       <c r="BP72">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="73" spans="1:68">
@@ -15923,7 +15923,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>7820386</v>
+        <v>7820387</v>
       </c>
       <c r="C73" t="s">
         <v>68</v>
@@ -15938,190 +15938,190 @@
         <v>5</v>
       </c>
       <c r="G73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H73" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M73">
         <v>1</v>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="P73" t="s">
         <v>207</v>
       </c>
       <c r="Q73">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R73">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="S73">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="T73">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="U73">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W73">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X73">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Y73">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z73">
+        <v>3.75</v>
+      </c>
+      <c r="AA73">
+        <v>3.1</v>
+      </c>
+      <c r="AB73">
+        <v>2.1</v>
+      </c>
+      <c r="AC73">
+        <v>1.12</v>
+      </c>
+      <c r="AD73">
+        <v>5.75</v>
+      </c>
+      <c r="AE73">
+        <v>1.55</v>
+      </c>
+      <c r="AF73">
         <v>2.25</v>
       </c>
-      <c r="AA73">
-        <v>2.63</v>
-      </c>
-      <c r="AB73">
+      <c r="AG73">
+        <v>2.7</v>
+      </c>
+      <c r="AH73">
+        <v>1.44</v>
+      </c>
+      <c r="AI73">
+        <v>2.2</v>
+      </c>
+      <c r="AJ73">
+        <v>1.62</v>
+      </c>
+      <c r="AK73">
+        <v>1.66</v>
+      </c>
+      <c r="AL73">
+        <v>1.37</v>
+      </c>
+      <c r="AM73">
+        <v>1.26</v>
+      </c>
+      <c r="AN73">
+        <v>0.5</v>
+      </c>
+      <c r="AO73">
+        <v>0</v>
+      </c>
+      <c r="AP73">
+        <v>0.8</v>
+      </c>
+      <c r="AQ73">
+        <v>1.25</v>
+      </c>
+      <c r="AR73">
+        <v>1.31</v>
+      </c>
+      <c r="AS73">
+        <v>2.1</v>
+      </c>
+      <c r="AT73">
+        <v>3.41</v>
+      </c>
+      <c r="AU73">
+        <v>7</v>
+      </c>
+      <c r="AV73">
+        <v>9</v>
+      </c>
+      <c r="AW73">
+        <v>8</v>
+      </c>
+      <c r="AX73">
+        <v>8</v>
+      </c>
+      <c r="AY73">
+        <v>18</v>
+      </c>
+      <c r="AZ73">
+        <v>19</v>
+      </c>
+      <c r="BA73">
         <v>4</v>
       </c>
-      <c r="AC73">
-        <v>1.17</v>
-      </c>
-      <c r="AD73">
-        <v>4.6</v>
-      </c>
-      <c r="AE73">
-        <v>1.7</v>
-      </c>
-      <c r="AF73">
-        <v>2</v>
-      </c>
-      <c r="AG73">
-        <v>3.5</v>
-      </c>
-      <c r="AH73">
-        <v>1.3</v>
-      </c>
-      <c r="AI73">
-        <v>2.63</v>
-      </c>
-      <c r="AJ73">
-        <v>1.44</v>
-      </c>
-      <c r="AK73">
+      <c r="BB73">
+        <v>2</v>
+      </c>
+      <c r="BC73">
+        <v>6</v>
+      </c>
+      <c r="BD73">
+        <v>2.09</v>
+      </c>
+      <c r="BE73">
+        <v>6.15</v>
+      </c>
+      <c r="BF73">
+        <v>2.21</v>
+      </c>
+      <c r="BG73">
+        <v>1.45</v>
+      </c>
+      <c r="BH73">
+        <v>2.48</v>
+      </c>
+      <c r="BI73">
+        <v>1.83</v>
+      </c>
+      <c r="BJ73">
+        <v>1.87</v>
+      </c>
+      <c r="BK73">
+        <v>2.38</v>
+      </c>
+      <c r="BL73">
+        <v>1.49</v>
+      </c>
+      <c r="BM73">
+        <v>3.2</v>
+      </c>
+      <c r="BN73">
         <v>1.26</v>
       </c>
-      <c r="AL73">
-        <v>1.44</v>
-      </c>
-      <c r="AM73">
-        <v>1.57</v>
-      </c>
-      <c r="AN73">
-        <v>2</v>
-      </c>
-      <c r="AO73">
-        <v>1.5</v>
-      </c>
-      <c r="AP73">
-        <v>2</v>
-      </c>
-      <c r="AQ73">
-        <v>1</v>
-      </c>
-      <c r="AR73">
-        <v>1.21</v>
-      </c>
-      <c r="AS73">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AT73">
-        <v>2.02</v>
-      </c>
-      <c r="AU73">
-        <v>8</v>
-      </c>
-      <c r="AV73">
-        <v>4</v>
-      </c>
-      <c r="AW73">
-        <v>7</v>
-      </c>
-      <c r="AX73">
-        <v>5</v>
-      </c>
-      <c r="AY73">
-        <v>16</v>
-      </c>
-      <c r="AZ73">
-        <v>10</v>
-      </c>
-      <c r="BA73">
-        <v>3</v>
-      </c>
-      <c r="BB73">
-        <v>4</v>
-      </c>
-      <c r="BC73">
-        <v>7</v>
-      </c>
-      <c r="BD73">
-        <v>1.61</v>
-      </c>
-      <c r="BE73">
-        <v>6.45</v>
-      </c>
-      <c r="BF73">
-        <v>3.15</v>
-      </c>
-      <c r="BG73">
-        <v>1.51</v>
-      </c>
-      <c r="BH73">
-        <v>2.32</v>
-      </c>
-      <c r="BI73">
-        <v>1.95</v>
-      </c>
-      <c r="BJ73">
-        <v>1.77</v>
-      </c>
-      <c r="BK73">
-        <v>2.54</v>
-      </c>
-      <c r="BL73">
-        <v>1.43</v>
-      </c>
-      <c r="BM73">
-        <v>3.5</v>
-      </c>
-      <c r="BN73">
-        <v>1.22</v>
-      </c>
       <c r="BO73">
-        <v>5.1</v>
+        <v>4.65</v>
       </c>
       <c r="BP73">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="74" spans="1:68">
@@ -18189,7 +18189,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>7820398</v>
+        <v>7820399</v>
       </c>
       <c r="C84" t="s">
         <v>68</v>
@@ -18204,10 +18204,10 @@
         <v>6</v>
       </c>
       <c r="G84" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H84" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -18222,37 +18222,37 @@
         <v>1</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O84" t="s">
         <v>153</v>
       </c>
       <c r="P84" t="s">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="Q84">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R84">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S84">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="T84">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="U84">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V84">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W84">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X84">
         <v>13</v>
@@ -18261,133 +18261,133 @@
         <v>1.04</v>
       </c>
       <c r="Z84">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AA84">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB84">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AC84">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AD84">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AE84">
+        <v>1.5</v>
+      </c>
+      <c r="AF84">
+        <v>2.37</v>
+      </c>
+      <c r="AG84">
+        <v>2.6</v>
+      </c>
+      <c r="AH84">
+        <v>1.48</v>
+      </c>
+      <c r="AI84">
+        <v>2.25</v>
+      </c>
+      <c r="AJ84">
         <v>1.57</v>
       </c>
-      <c r="AF84">
-        <v>2.25</v>
-      </c>
-      <c r="AG84">
-        <v>2.88</v>
-      </c>
-      <c r="AH84">
-        <v>1.4</v>
-      </c>
-      <c r="AI84">
-        <v>2.2</v>
-      </c>
-      <c r="AJ84">
-        <v>1.62</v>
-      </c>
       <c r="AK84">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL84">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AM84">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AN84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP84">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="AQ84">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AR84">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AS84">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AT84">
-        <v>3.11</v>
+        <v>3.86</v>
       </c>
       <c r="AU84">
+        <v>6</v>
+      </c>
+      <c r="AV84">
+        <v>6</v>
+      </c>
+      <c r="AW84">
+        <v>10</v>
+      </c>
+      <c r="AX84">
         <v>5</v>
       </c>
-      <c r="AV84">
+      <c r="AY84">
+        <v>20</v>
+      </c>
+      <c r="AZ84">
+        <v>13</v>
+      </c>
+      <c r="BA84">
         <v>5</v>
       </c>
-      <c r="AW84">
+      <c r="BB84">
         <v>5</v>
       </c>
-      <c r="AX84">
-        <v>9</v>
-      </c>
-      <c r="AY84">
-        <v>12</v>
-      </c>
-      <c r="AZ84">
-        <v>16</v>
-      </c>
-      <c r="BA84">
-        <v>6</v>
-      </c>
-      <c r="BB84">
-        <v>8</v>
-      </c>
       <c r="BC84">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BD84">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BE84">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="BF84">
         <v>2.4</v>
       </c>
       <c r="BG84">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="BH84">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="BI84">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="BJ84">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="BK84">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="BL84">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="BM84">
-        <v>3.35</v>
+        <v>2.48</v>
       </c>
       <c r="BN84">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="BO84">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="BP84">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="85" spans="1:68">
@@ -18395,7 +18395,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>7820399</v>
+        <v>7820398</v>
       </c>
       <c r="C85" t="s">
         <v>68</v>
@@ -18410,10 +18410,10 @@
         <v>6</v>
       </c>
       <c r="G85" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H85" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -18428,37 +18428,37 @@
         <v>1</v>
       </c>
       <c r="M85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O85" t="s">
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>213</v>
+        <v>100</v>
       </c>
       <c r="Q85">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R85">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="S85">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="T85">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U85">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V85">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="W85">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X85">
         <v>13</v>
@@ -18467,133 +18467,133 @@
         <v>1.04</v>
       </c>
       <c r="Z85">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA85">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AB85">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AC85">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AD85">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AE85">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF85">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AG85">
+        <v>2.88</v>
+      </c>
+      <c r="AH85">
+        <v>1.4</v>
+      </c>
+      <c r="AI85">
+        <v>2.2</v>
+      </c>
+      <c r="AJ85">
+        <v>1.62</v>
+      </c>
+      <c r="AK85">
+        <v>1.25</v>
+      </c>
+      <c r="AL85">
+        <v>1.38</v>
+      </c>
+      <c r="AM85">
+        <v>1.66</v>
+      </c>
+      <c r="AN85">
+        <v>2</v>
+      </c>
+      <c r="AO85">
+        <v>0</v>
+      </c>
+      <c r="AP85">
         <v>2.6</v>
       </c>
-      <c r="AH85">
-        <v>1.48</v>
-      </c>
-      <c r="AI85">
-        <v>2.25</v>
-      </c>
-      <c r="AJ85">
-        <v>1.57</v>
-      </c>
-      <c r="AK85">
-        <v>1.22</v>
-      </c>
-      <c r="AL85">
-        <v>1.34</v>
-      </c>
-      <c r="AM85">
-        <v>1.78</v>
-      </c>
-      <c r="AN85">
-        <v>0</v>
-      </c>
-      <c r="AO85">
-        <v>1</v>
-      </c>
-      <c r="AP85">
-        <v>0.4</v>
-      </c>
       <c r="AQ85">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AR85">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="AS85">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AT85">
-        <v>3.86</v>
+        <v>3.11</v>
       </c>
       <c r="AU85">
+        <v>5</v>
+      </c>
+      <c r="AV85">
+        <v>5</v>
+      </c>
+      <c r="AW85">
+        <v>5</v>
+      </c>
+      <c r="AX85">
+        <v>9</v>
+      </c>
+      <c r="AY85">
+        <v>12</v>
+      </c>
+      <c r="AZ85">
+        <v>16</v>
+      </c>
+      <c r="BA85">
         <v>6</v>
       </c>
-      <c r="AV85">
-        <v>6</v>
-      </c>
-      <c r="AW85">
-        <v>10</v>
-      </c>
-      <c r="AX85">
-        <v>5</v>
-      </c>
-      <c r="AY85">
-        <v>20</v>
-      </c>
-      <c r="AZ85">
-        <v>13</v>
-      </c>
-      <c r="BA85">
-        <v>5</v>
-      </c>
       <c r="BB85">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BC85">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BD85">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BE85">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="BF85">
         <v>2.4</v>
       </c>
       <c r="BG85">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="BH85">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="BI85">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="BJ85">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="BK85">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="BL85">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="BM85">
-        <v>2.48</v>
+        <v>3.35</v>
       </c>
       <c r="BN85">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="BO85">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP85">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="86" spans="1:68">
@@ -20575,7 +20575,7 @@
         <v>0.33</v>
       </c>
       <c r="AP95">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ95">
         <v>0.2</v>
@@ -22969,7 +22969,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23545,7 +23545,7 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>7820425</v>
+        <v>7820426</v>
       </c>
       <c r="C110" t="s">
         <v>68</v>
@@ -23560,142 +23560,142 @@
         <v>8</v>
       </c>
       <c r="G110" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H110" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="I110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110">
         <v>1</v>
       </c>
       <c r="M110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O110" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
       <c r="Q110">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="R110">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="S110">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="T110">
+        <v>1.5</v>
+      </c>
+      <c r="U110">
+        <v>2.5</v>
+      </c>
+      <c r="V110">
+        <v>3.5</v>
+      </c>
+      <c r="W110">
+        <v>1.29</v>
+      </c>
+      <c r="X110">
+        <v>11</v>
+      </c>
+      <c r="Y110">
+        <v>1.05</v>
+      </c>
+      <c r="Z110">
+        <v>1.7</v>
+      </c>
+      <c r="AA110">
+        <v>3.5</v>
+      </c>
+      <c r="AB110">
+        <v>5.5</v>
+      </c>
+      <c r="AC110">
+        <v>1.09</v>
+      </c>
+      <c r="AD110">
+        <v>7.6</v>
+      </c>
+      <c r="AE110">
+        <v>1.43</v>
+      </c>
+      <c r="AF110">
+        <v>2.7</v>
+      </c>
+      <c r="AG110">
+        <v>2.35</v>
+      </c>
+      <c r="AH110">
+        <v>1.57</v>
+      </c>
+      <c r="AI110">
+        <v>2.2</v>
+      </c>
+      <c r="AJ110">
         <v>1.62</v>
       </c>
-      <c r="U110">
-        <v>2.2</v>
-      </c>
-      <c r="V110">
-        <v>4</v>
-      </c>
-      <c r="W110">
-        <v>1.22</v>
-      </c>
-      <c r="X110">
+      <c r="AK110">
+        <v>1.15</v>
+      </c>
+      <c r="AL110">
+        <v>1.29</v>
+      </c>
+      <c r="AM110">
+        <v>2.1</v>
+      </c>
+      <c r="AN110">
+        <v>0.33</v>
+      </c>
+      <c r="AO110">
+        <v>1</v>
+      </c>
+      <c r="AP110">
+        <v>0.4</v>
+      </c>
+      <c r="AQ110">
+        <v>1.8</v>
+      </c>
+      <c r="AR110">
+        <v>2.19</v>
+      </c>
+      <c r="AS110">
+        <v>1.6</v>
+      </c>
+      <c r="AT110">
+        <v>3.79</v>
+      </c>
+      <c r="AU110">
+        <v>7</v>
+      </c>
+      <c r="AV110">
+        <v>5</v>
+      </c>
+      <c r="AW110">
         <v>15</v>
       </c>
-      <c r="Y110">
-        <v>1.03</v>
-      </c>
-      <c r="Z110">
-        <v>2.38</v>
-      </c>
-      <c r="AA110">
-        <v>3</v>
-      </c>
-      <c r="AB110">
-        <v>3.3</v>
-      </c>
-      <c r="AC110">
-        <v>1.13</v>
-      </c>
-      <c r="AD110">
-        <v>6</v>
-      </c>
-      <c r="AE110">
-        <v>1.57</v>
-      </c>
-      <c r="AF110">
-        <v>2.3</v>
-      </c>
-      <c r="AG110">
-        <v>2.88</v>
-      </c>
-      <c r="AH110">
-        <v>1.4</v>
-      </c>
-      <c r="AI110">
-        <v>2.25</v>
-      </c>
-      <c r="AJ110">
-        <v>1.57</v>
-      </c>
-      <c r="AK110">
-        <v>1.33</v>
-      </c>
-      <c r="AL110">
-        <v>1.37</v>
-      </c>
-      <c r="AM110">
-        <v>1.55</v>
-      </c>
-      <c r="AN110">
-        <v>0.67</v>
-      </c>
-      <c r="AO110">
-        <v>1</v>
-      </c>
-      <c r="AP110">
-        <v>1.25</v>
-      </c>
-      <c r="AQ110">
-        <v>0.67</v>
-      </c>
-      <c r="AR110">
-        <v>1.45</v>
-      </c>
-      <c r="AS110">
-        <v>1.14</v>
-      </c>
-      <c r="AT110">
-        <v>2.59</v>
-      </c>
-      <c r="AU110">
-        <v>4</v>
-      </c>
-      <c r="AV110">
-        <v>0</v>
-      </c>
-      <c r="AW110">
-        <v>13</v>
-      </c>
       <c r="AX110">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY110">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AZ110">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA110">
         <v>8</v>
@@ -23707,43 +23707,43 @@
         <v>9</v>
       </c>
       <c r="BD110">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BE110">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF110">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="BG110">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BH110">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BI110">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="BJ110">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="BK110">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="BL110">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BM110">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="BN110">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BO110">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BP110">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="111" spans="1:68">
@@ -23751,7 +23751,7 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>7820426</v>
+        <v>7820425</v>
       </c>
       <c r="C111" t="s">
         <v>68</v>
@@ -23766,142 +23766,142 @@
         <v>8</v>
       </c>
       <c r="G111" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H111" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111">
         <v>1</v>
       </c>
       <c r="M111">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111" t="s">
+        <v>105</v>
+      </c>
+      <c r="P111" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q111">
+        <v>3.25</v>
+      </c>
+      <c r="R111">
+        <v>1.83</v>
+      </c>
+      <c r="S111">
+        <v>4.33</v>
+      </c>
+      <c r="T111">
+        <v>1.62</v>
+      </c>
+      <c r="U111">
+        <v>2.2</v>
+      </c>
+      <c r="V111">
+        <v>4</v>
+      </c>
+      <c r="W111">
+        <v>1.22</v>
+      </c>
+      <c r="X111">
+        <v>15</v>
+      </c>
+      <c r="Y111">
+        <v>1.03</v>
+      </c>
+      <c r="Z111">
+        <v>2.38</v>
+      </c>
+      <c r="AA111">
         <v>3</v>
       </c>
-      <c r="O111" t="s">
-        <v>169</v>
-      </c>
-      <c r="P111" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q111">
-        <v>2.38</v>
-      </c>
-      <c r="R111">
-        <v>2.05</v>
-      </c>
-      <c r="S111">
+      <c r="AB111">
+        <v>3.3</v>
+      </c>
+      <c r="AC111">
+        <v>1.13</v>
+      </c>
+      <c r="AD111">
         <v>6</v>
       </c>
-      <c r="T111">
-        <v>1.5</v>
-      </c>
-      <c r="U111">
-        <v>2.5</v>
-      </c>
-      <c r="V111">
-        <v>3.5</v>
-      </c>
-      <c r="W111">
-        <v>1.29</v>
-      </c>
-      <c r="X111">
-        <v>11</v>
-      </c>
-      <c r="Y111">
-        <v>1.05</v>
-      </c>
-      <c r="Z111">
-        <v>1.7</v>
-      </c>
-      <c r="AA111">
-        <v>3.5</v>
-      </c>
-      <c r="AB111">
-        <v>5.5</v>
-      </c>
-      <c r="AC111">
-        <v>1.09</v>
-      </c>
-      <c r="AD111">
-        <v>7.6</v>
-      </c>
       <c r="AE111">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AF111">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AG111">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AH111">
+        <v>1.4</v>
+      </c>
+      <c r="AI111">
+        <v>2.25</v>
+      </c>
+      <c r="AJ111">
         <v>1.57</v>
       </c>
-      <c r="AI111">
-        <v>2.2</v>
-      </c>
-      <c r="AJ111">
-        <v>1.62</v>
-      </c>
       <c r="AK111">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AL111">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AM111">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AN111">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AO111">
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>0.4</v>
+        <v>1.25</v>
       </c>
       <c r="AQ111">
-        <v>1.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR111">
-        <v>2.19</v>
+        <v>1.45</v>
       </c>
       <c r="AS111">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="AT111">
-        <v>3.79</v>
+        <v>2.59</v>
       </c>
       <c r="AU111">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV111">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW111">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX111">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY111">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AZ111">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA111">
         <v>8</v>
@@ -23913,43 +23913,43 @@
         <v>9</v>
       </c>
       <c r="BD111">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BE111">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF111">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="BG111">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BH111">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="BI111">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="BJ111">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="BK111">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="BL111">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BM111">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="BN111">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="BO111">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BP111">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="112" spans="1:68">
@@ -24614,7 +24614,7 @@
         <v>3</v>
       </c>
       <c r="O115" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P115" t="s">
         <v>225</v>
@@ -24904,7 +24904,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR116">
         <v>1.45</v>
@@ -26471,7 +26471,7 @@
         <v>100</v>
       </c>
       <c r="P124" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q124">
         <v>2.63</v>
@@ -27665,7 +27665,7 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>7820446</v>
+        <v>7820445</v>
       </c>
       <c r="C130" t="s">
         <v>68</v>
@@ -27680,154 +27680,154 @@
         <v>9</v>
       </c>
       <c r="G130" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H130" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O130" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="P130" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="Q130">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R130">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S130">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="T130">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="U130">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V130">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="W130">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X130">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y130">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z130">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AA130">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="AB130">
-        <v>4.45</v>
+        <v>3.55</v>
       </c>
       <c r="AC130">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AD130">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AE130">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF130">
+        <v>2.37</v>
+      </c>
+      <c r="AG130">
+        <v>2.5</v>
+      </c>
+      <c r="AH130">
+        <v>1.5</v>
+      </c>
+      <c r="AI130">
         <v>2.2</v>
       </c>
-      <c r="AG130">
-        <v>2.88</v>
-      </c>
-      <c r="AH130">
-        <v>1.4</v>
-      </c>
-      <c r="AI130">
-        <v>2.5</v>
-      </c>
       <c r="AJ130">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AK130">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL130">
         <v>1.36</v>
       </c>
       <c r="AM130">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AN130">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="AO130">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="AP130">
-        <v>1.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ130">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="AR130">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="AS130">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AT130">
-        <v>2.67</v>
+        <v>3.31</v>
       </c>
       <c r="AU130">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV130">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW130">
+        <v>10</v>
+      </c>
+      <c r="AX130">
+        <v>2</v>
+      </c>
+      <c r="AY130">
+        <v>17</v>
+      </c>
+      <c r="AZ130">
+        <v>6</v>
+      </c>
+      <c r="BA130">
+        <v>5</v>
+      </c>
+      <c r="BB130">
+        <v>3</v>
+      </c>
+      <c r="BC130">
         <v>8</v>
       </c>
-      <c r="AX130">
-        <v>3</v>
-      </c>
-      <c r="AY130">
-        <v>18</v>
-      </c>
-      <c r="AZ130">
-        <v>7</v>
-      </c>
-      <c r="BA130">
-        <v>11</v>
-      </c>
-      <c r="BB130">
-        <v>1</v>
-      </c>
-      <c r="BC130">
-        <v>12</v>
-      </c>
       <c r="BD130">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BE130">
         <v>6.4</v>
@@ -27836,34 +27836,34 @@
         <v>2.55</v>
       </c>
       <c r="BG130">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BH130">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="BI130">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BJ130">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="BK130">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="BL130">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BM130">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="BN130">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="BO130">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BP130">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="131" spans="1:68">
@@ -27871,7 +27871,7 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>7820445</v>
+        <v>7820446</v>
       </c>
       <c r="C131" t="s">
         <v>68</v>
@@ -27886,154 +27886,154 @@
         <v>9</v>
       </c>
       <c r="G131" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H131" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O131" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="P131" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="Q131">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R131">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="S131">
+        <v>5.5</v>
+      </c>
+      <c r="T131">
+        <v>1.67</v>
+      </c>
+      <c r="U131">
+        <v>2.1</v>
+      </c>
+      <c r="V131">
         <v>4.33</v>
       </c>
-      <c r="T131">
-        <v>1.57</v>
-      </c>
-      <c r="U131">
-        <v>2.25</v>
-      </c>
-      <c r="V131">
-        <v>3.75</v>
-      </c>
       <c r="W131">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X131">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y131">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z131">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AA131">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="AB131">
-        <v>3.55</v>
+        <v>4.45</v>
       </c>
       <c r="AC131">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AD131">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AE131">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF131">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AG131">
+        <v>2.88</v>
+      </c>
+      <c r="AH131">
+        <v>1.4</v>
+      </c>
+      <c r="AI131">
         <v>2.5</v>
       </c>
-      <c r="AH131">
+      <c r="AJ131">
         <v>1.5</v>
       </c>
-      <c r="AI131">
-        <v>2.2</v>
-      </c>
-      <c r="AJ131">
-        <v>1.62</v>
-      </c>
       <c r="AK131">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL131">
         <v>1.36</v>
       </c>
       <c r="AM131">
+        <v>1.77</v>
+      </c>
+      <c r="AN131">
+        <v>2</v>
+      </c>
+      <c r="AO131">
+        <v>1.75</v>
+      </c>
+      <c r="AP131">
+        <v>1.75</v>
+      </c>
+      <c r="AQ131">
+        <v>1.6</v>
+      </c>
+      <c r="AR131">
+        <v>1.36</v>
+      </c>
+      <c r="AS131">
+        <v>1.31</v>
+      </c>
+      <c r="AT131">
+        <v>2.67</v>
+      </c>
+      <c r="AU131">
+        <v>7</v>
+      </c>
+      <c r="AV131">
+        <v>2</v>
+      </c>
+      <c r="AW131">
+        <v>8</v>
+      </c>
+      <c r="AX131">
+        <v>3</v>
+      </c>
+      <c r="AY131">
+        <v>18</v>
+      </c>
+      <c r="AZ131">
+        <v>7</v>
+      </c>
+      <c r="BA131">
+        <v>11</v>
+      </c>
+      <c r="BB131">
+        <v>1</v>
+      </c>
+      <c r="BC131">
+        <v>12</v>
+      </c>
+      <c r="BD131">
         <v>1.61</v>
-      </c>
-      <c r="AN131">
-        <v>0.75</v>
-      </c>
-      <c r="AO131">
-        <v>0.25</v>
-      </c>
-      <c r="AP131">
-        <v>0.8</v>
-      </c>
-      <c r="AQ131">
-        <v>0.4</v>
-      </c>
-      <c r="AR131">
-        <v>1.81</v>
-      </c>
-      <c r="AS131">
-        <v>1.5</v>
-      </c>
-      <c r="AT131">
-        <v>3.31</v>
-      </c>
-      <c r="AU131">
-        <v>5</v>
-      </c>
-      <c r="AV131">
-        <v>4</v>
-      </c>
-      <c r="AW131">
-        <v>10</v>
-      </c>
-      <c r="AX131">
-        <v>2</v>
-      </c>
-      <c r="AY131">
-        <v>17</v>
-      </c>
-      <c r="AZ131">
-        <v>6</v>
-      </c>
-      <c r="BA131">
-        <v>5</v>
-      </c>
-      <c r="BB131">
-        <v>3</v>
-      </c>
-      <c r="BC131">
-        <v>8</v>
-      </c>
-      <c r="BD131">
-        <v>1.63</v>
       </c>
       <c r="BE131">
         <v>6.4</v>
@@ -28042,34 +28042,34 @@
         <v>2.55</v>
       </c>
       <c r="BG131">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BH131">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="BI131">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BJ131">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="BK131">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="BL131">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BM131">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="BN131">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BO131">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP131">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="132" spans="1:68">
@@ -29313,7 +29313,7 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>7820453</v>
+        <v>7820454</v>
       </c>
       <c r="C138" t="s">
         <v>68</v>
@@ -29328,10 +29328,10 @@
         <v>10</v>
       </c>
       <c r="G138" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H138" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="I138">
         <v>1</v>
@@ -29343,175 +29343,175 @@
         <v>2</v>
       </c>
       <c r="L138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M138">
         <v>1</v>
       </c>
       <c r="N138">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O138" t="s">
         <v>181</v>
       </c>
       <c r="P138" t="s">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="Q138">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R138">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S138">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="T138">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="U138">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V138">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="W138">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X138">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y138">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z138">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AA138">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AB138">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AC138">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AD138">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="AE138">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AF138">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AG138">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH138">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AI138">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AJ138">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AK138">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL138">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AM138">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AN138">
         <v>3</v>
       </c>
       <c r="AO138">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AP138">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AQ138">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR138">
-        <v>1.9</v>
+        <v>1.28</v>
       </c>
       <c r="AS138">
-        <v>1.47</v>
+        <v>1.07</v>
       </c>
       <c r="AT138">
-        <v>3.37</v>
+        <v>2.35</v>
       </c>
       <c r="AU138">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV138">
+        <v>6</v>
+      </c>
+      <c r="AW138">
         <v>3</v>
-      </c>
-      <c r="AW138">
-        <v>10</v>
       </c>
       <c r="AX138">
         <v>5</v>
       </c>
       <c r="AY138">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AZ138">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA138">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BB138">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC138">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD138">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="BE138">
         <v>6.75</v>
       </c>
       <c r="BF138">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="BG138">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BH138">
+        <v>2.7</v>
+      </c>
+      <c r="BI138">
+        <v>1.66</v>
+      </c>
+      <c r="BJ138">
+        <v>2.07</v>
+      </c>
+      <c r="BK138">
+        <v>2.05</v>
+      </c>
+      <c r="BL138">
+        <v>1.67</v>
+      </c>
+      <c r="BM138">
         <v>2.55</v>
       </c>
-      <c r="BI138">
-        <v>1.73</v>
-      </c>
-      <c r="BJ138">
-        <v>1.97</v>
-      </c>
-      <c r="BK138">
-        <v>2.15</v>
-      </c>
-      <c r="BL138">
-        <v>1.61</v>
-      </c>
-      <c r="BM138">
-        <v>2.8</v>
-      </c>
       <c r="BN138">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="BO138">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BP138">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="139" spans="1:68">
@@ -29519,7 +29519,7 @@
         <v>138</v>
       </c>
       <c r="B139">
-        <v>7820454</v>
+        <v>7820453</v>
       </c>
       <c r="C139" t="s">
         <v>68</v>
@@ -29534,10 +29534,10 @@
         <v>10</v>
       </c>
       <c r="G139" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="I139">
         <v>1</v>
@@ -29549,175 +29549,175 @@
         <v>2</v>
       </c>
       <c r="L139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M139">
         <v>1</v>
       </c>
       <c r="N139">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O139" t="s">
         <v>182</v>
       </c>
       <c r="P139" t="s">
-        <v>156</v>
+        <v>235</v>
       </c>
       <c r="Q139">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R139">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S139">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="T139">
+        <v>1.5</v>
+      </c>
+      <c r="U139">
+        <v>2.5</v>
+      </c>
+      <c r="V139">
+        <v>3.5</v>
+      </c>
+      <c r="W139">
+        <v>1.29</v>
+      </c>
+      <c r="X139">
+        <v>11</v>
+      </c>
+      <c r="Y139">
+        <v>1.05</v>
+      </c>
+      <c r="Z139">
         <v>1.62</v>
       </c>
-      <c r="U139">
+      <c r="AA139">
+        <v>3.6</v>
+      </c>
+      <c r="AB139">
+        <v>6</v>
+      </c>
+      <c r="AC139">
+        <v>1.07</v>
+      </c>
+      <c r="AD139">
+        <v>8</v>
+      </c>
+      <c r="AE139">
+        <v>1.42</v>
+      </c>
+      <c r="AF139">
+        <v>2.8</v>
+      </c>
+      <c r="AG139">
+        <v>2.3</v>
+      </c>
+      <c r="AH139">
+        <v>1.6</v>
+      </c>
+      <c r="AI139">
         <v>2.2</v>
       </c>
-      <c r="V139">
-        <v>4</v>
-      </c>
-      <c r="W139">
-        <v>1.22</v>
-      </c>
-      <c r="X139">
-        <v>13</v>
-      </c>
-      <c r="Y139">
-        <v>1.04</v>
-      </c>
-      <c r="Z139">
-        <v>1.91</v>
-      </c>
-      <c r="AA139">
-        <v>3.1</v>
-      </c>
-      <c r="AB139">
-        <v>4.75</v>
-      </c>
-      <c r="AC139">
-        <v>1.11</v>
-      </c>
-      <c r="AD139">
-        <v>6.25</v>
-      </c>
-      <c r="AE139">
-        <v>1.51</v>
-      </c>
-      <c r="AF139">
-        <v>2.35</v>
-      </c>
-      <c r="AG139">
-        <v>2.7</v>
-      </c>
-      <c r="AH139">
-        <v>1.44</v>
-      </c>
-      <c r="AI139">
-        <v>2.25</v>
-      </c>
       <c r="AJ139">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK139">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL139">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AM139">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AN139">
         <v>3</v>
       </c>
       <c r="AO139">
+        <v>0.75</v>
+      </c>
+      <c r="AP139">
+        <v>2.6</v>
+      </c>
+      <c r="AQ139">
         <v>0.8</v>
       </c>
-      <c r="AP139">
+      <c r="AR139">
+        <v>1.9</v>
+      </c>
+      <c r="AS139">
+        <v>1.47</v>
+      </c>
+      <c r="AT139">
+        <v>3.37</v>
+      </c>
+      <c r="AU139">
+        <v>7</v>
+      </c>
+      <c r="AV139">
         <v>3</v>
       </c>
-      <c r="AQ139">
-        <v>0.67</v>
-      </c>
-      <c r="AR139">
-        <v>1.28</v>
-      </c>
-      <c r="AS139">
-        <v>1.07</v>
-      </c>
-      <c r="AT139">
-        <v>2.35</v>
-      </c>
-      <c r="AU139">
-        <v>6</v>
-      </c>
-      <c r="AV139">
-        <v>6</v>
-      </c>
       <c r="AW139">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AX139">
         <v>5</v>
       </c>
       <c r="AY139">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AZ139">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA139">
+        <v>9</v>
+      </c>
+      <c r="BB139">
         <v>4</v>
       </c>
-      <c r="BB139">
-        <v>3</v>
-      </c>
       <c r="BC139">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD139">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="BE139">
         <v>6.75</v>
       </c>
       <c r="BF139">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="BG139">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BH139">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BI139">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="BJ139">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="BK139">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="BL139">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="BM139">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="BN139">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="BO139">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BP139">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="140" spans="1:68">
@@ -29725,7 +29725,7 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>7820456</v>
+        <v>7820455</v>
       </c>
       <c r="C140" t="s">
         <v>68</v>
@@ -29740,10 +29740,10 @@
         <v>10</v>
       </c>
       <c r="G140" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H140" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -29755,28 +29755,28 @@
         <v>0</v>
       </c>
       <c r="L140">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M140">
         <v>0</v>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O140" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="P140" t="s">
         <v>100</v>
       </c>
       <c r="Q140">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="R140">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S140">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="T140">
         <v>1.57</v>
@@ -29785,145 +29785,145 @@
         <v>2.25</v>
       </c>
       <c r="V140">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="W140">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X140">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y140">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z140">
+        <v>1.75</v>
+      </c>
+      <c r="AA140">
+        <v>3.5</v>
+      </c>
+      <c r="AB140">
+        <v>5</v>
+      </c>
+      <c r="AC140">
+        <v>1.11</v>
+      </c>
+      <c r="AD140">
+        <v>6.25</v>
+      </c>
+      <c r="AE140">
+        <v>1.53</v>
+      </c>
+      <c r="AF140">
+        <v>2.3</v>
+      </c>
+      <c r="AG140">
+        <v>2.6</v>
+      </c>
+      <c r="AH140">
+        <v>1.48</v>
+      </c>
+      <c r="AI140">
+        <v>2.5</v>
+      </c>
+      <c r="AJ140">
+        <v>1.5</v>
+      </c>
+      <c r="AK140">
+        <v>1.17</v>
+      </c>
+      <c r="AL140">
+        <v>1.34</v>
+      </c>
+      <c r="AM140">
+        <v>1.93</v>
+      </c>
+      <c r="AN140">
+        <v>2.5</v>
+      </c>
+      <c r="AO140">
+        <v>1.75</v>
+      </c>
+      <c r="AP140">
+        <v>2.6</v>
+      </c>
+      <c r="AQ140">
+        <v>1.4</v>
+      </c>
+      <c r="AR140">
+        <v>1.7</v>
+      </c>
+      <c r="AS140">
+        <v>1.26</v>
+      </c>
+      <c r="AT140">
+        <v>2.96</v>
+      </c>
+      <c r="AU140">
+        <v>6</v>
+      </c>
+      <c r="AV140">
+        <v>2</v>
+      </c>
+      <c r="AW140">
+        <v>2</v>
+      </c>
+      <c r="AX140">
         <v>4</v>
       </c>
-      <c r="AA140">
-        <v>3.3</v>
-      </c>
-      <c r="AB140">
-        <v>2</v>
-      </c>
-      <c r="AC140">
-        <v>1.1</v>
-      </c>
-      <c r="AD140">
-        <v>6.5</v>
-      </c>
-      <c r="AE140">
+      <c r="AY140">
+        <v>8</v>
+      </c>
+      <c r="AZ140">
+        <v>7</v>
+      </c>
+      <c r="BA140">
+        <v>1</v>
+      </c>
+      <c r="BB140">
+        <v>4</v>
+      </c>
+      <c r="BC140">
+        <v>5</v>
+      </c>
+      <c r="BD140">
         <v>1.5</v>
-      </c>
-      <c r="AF140">
-        <v>2.55</v>
-      </c>
-      <c r="AG140">
-        <v>2.5</v>
-      </c>
-      <c r="AH140">
-        <v>1.5</v>
-      </c>
-      <c r="AI140">
-        <v>2.2</v>
-      </c>
-      <c r="AJ140">
-        <v>1.62</v>
-      </c>
-      <c r="AK140">
-        <v>1.51</v>
-      </c>
-      <c r="AL140">
-        <v>1.35</v>
-      </c>
-      <c r="AM140">
-        <v>1.38</v>
-      </c>
-      <c r="AN140">
-        <v>1.5</v>
-      </c>
-      <c r="AO140">
-        <v>1.33</v>
-      </c>
-      <c r="AP140">
-        <v>1.4</v>
-      </c>
-      <c r="AQ140">
-        <v>1.25</v>
-      </c>
-      <c r="AR140">
-        <v>1.98</v>
-      </c>
-      <c r="AS140">
-        <v>2.04</v>
-      </c>
-      <c r="AT140">
-        <v>4.02</v>
-      </c>
-      <c r="AU140">
-        <v>3</v>
-      </c>
-      <c r="AV140">
-        <v>8</v>
-      </c>
-      <c r="AW140">
-        <v>6</v>
-      </c>
-      <c r="AX140">
-        <v>8</v>
-      </c>
-      <c r="AY140">
-        <v>10</v>
-      </c>
-      <c r="AZ140">
-        <v>18</v>
-      </c>
-      <c r="BA140">
-        <v>2</v>
-      </c>
-      <c r="BB140">
-        <v>7</v>
-      </c>
-      <c r="BC140">
-        <v>9</v>
-      </c>
-      <c r="BD140">
-        <v>2.23</v>
       </c>
       <c r="BE140">
         <v>6.4</v>
       </c>
       <c r="BF140">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="BG140">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="BH140">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="BI140">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="BJ140">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BK140">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="BL140">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BM140">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="BN140">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="BO140">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP140">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="141" spans="1:68">
@@ -29931,7 +29931,7 @@
         <v>140</v>
       </c>
       <c r="B141">
-        <v>7820455</v>
+        <v>7820456</v>
       </c>
       <c r="C141" t="s">
         <v>68</v>
@@ -29946,10 +29946,10 @@
         <v>10</v>
       </c>
       <c r="G141" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H141" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -29961,28 +29961,28 @@
         <v>0</v>
       </c>
       <c r="L141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M141">
         <v>0</v>
       </c>
       <c r="N141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O141" t="s">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="P141" t="s">
         <v>100</v>
       </c>
       <c r="Q141">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="R141">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S141">
-        <v>6</v>
+        <v>2.75</v>
       </c>
       <c r="T141">
         <v>1.57</v>
@@ -29991,144 +29991,350 @@
         <v>2.25</v>
       </c>
       <c r="V141">
+        <v>3.75</v>
+      </c>
+      <c r="W141">
+        <v>1.25</v>
+      </c>
+      <c r="X141">
+        <v>11</v>
+      </c>
+      <c r="Y141">
+        <v>1.05</v>
+      </c>
+      <c r="Z141">
         <v>4</v>
       </c>
-      <c r="W141">
-        <v>1.22</v>
-      </c>
-      <c r="X141">
-        <v>13</v>
-      </c>
-      <c r="Y141">
-        <v>1.04</v>
-      </c>
-      <c r="Z141">
-        <v>1.75</v>
-      </c>
       <c r="AA141">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB141">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC141">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AD141">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AE141">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF141">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AG141">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH141">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AI141">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ141">
+        <v>1.62</v>
+      </c>
+      <c r="AK141">
+        <v>1.51</v>
+      </c>
+      <c r="AL141">
+        <v>1.35</v>
+      </c>
+      <c r="AM141">
+        <v>1.38</v>
+      </c>
+      <c r="AN141">
         <v>1.5</v>
       </c>
-      <c r="AK141">
-        <v>1.17</v>
-      </c>
-      <c r="AL141">
-        <v>1.34</v>
-      </c>
-      <c r="AM141">
-        <v>1.93</v>
-      </c>
-      <c r="AN141">
-        <v>2.5</v>
-      </c>
       <c r="AO141">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AP141">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="AQ141">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AR141">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AS141">
-        <v>1.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT141">
-        <v>2.96</v>
+        <v>4.02</v>
       </c>
       <c r="AU141">
+        <v>3</v>
+      </c>
+      <c r="AV141">
+        <v>8</v>
+      </c>
+      <c r="AW141">
         <v>6</v>
       </c>
-      <c r="AV141">
-        <v>2</v>
-      </c>
-      <c r="AW141">
-        <v>2</v>
-      </c>
       <c r="AX141">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY141">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ141">
+        <v>18</v>
+      </c>
+      <c r="BA141">
+        <v>2</v>
+      </c>
+      <c r="BB141">
         <v>7</v>
       </c>
-      <c r="BA141">
-        <v>1</v>
-      </c>
-      <c r="BB141">
-        <v>4</v>
-      </c>
       <c r="BC141">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BD141">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="BE141">
         <v>6.4</v>
       </c>
       <c r="BF141">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="BG141">
+        <v>1.41</v>
+      </c>
+      <c r="BH141">
+        <v>2.65</v>
+      </c>
+      <c r="BI141">
+        <v>1.71</v>
+      </c>
+      <c r="BJ141">
+        <v>2</v>
+      </c>
+      <c r="BK141">
+        <v>2.1</v>
+      </c>
+      <c r="BL141">
+        <v>1.64</v>
+      </c>
+      <c r="BM141">
+        <v>2.7</v>
+      </c>
+      <c r="BN141">
+        <v>1.4</v>
+      </c>
+      <c r="BO141">
+        <v>3.55</v>
+      </c>
+      <c r="BP141">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7820457</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45732.66666666666</v>
+      </c>
+      <c r="F142">
+        <v>10</v>
+      </c>
+      <c r="G142" t="s">
+        <v>76</v>
+      </c>
+      <c r="H142" t="s">
+        <v>97</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="L142">
+        <v>1</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="N142">
+        <v>2</v>
+      </c>
+      <c r="O142" t="s">
+        <v>139</v>
+      </c>
+      <c r="P142" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q142">
+        <v>2.88</v>
+      </c>
+      <c r="R142">
+        <v>1.95</v>
+      </c>
+      <c r="S142">
+        <v>4.5</v>
+      </c>
+      <c r="T142">
+        <v>1.57</v>
+      </c>
+      <c r="U142">
+        <v>2.25</v>
+      </c>
+      <c r="V142">
+        <v>3.75</v>
+      </c>
+      <c r="W142">
+        <v>1.25</v>
+      </c>
+      <c r="X142">
+        <v>11</v>
+      </c>
+      <c r="Y142">
+        <v>1.05</v>
+      </c>
+      <c r="Z142">
+        <v>2.1</v>
+      </c>
+      <c r="AA142">
+        <v>3</v>
+      </c>
+      <c r="AB142">
+        <v>4</v>
+      </c>
+      <c r="AC142">
+        <v>1.11</v>
+      </c>
+      <c r="AD142">
+        <v>6.25</v>
+      </c>
+      <c r="AE142">
+        <v>1.5</v>
+      </c>
+      <c r="AF142">
+        <v>2.5</v>
+      </c>
+      <c r="AG142">
+        <v>2.5</v>
+      </c>
+      <c r="AH142">
+        <v>1.5</v>
+      </c>
+      <c r="AI142">
+        <v>2.05</v>
+      </c>
+      <c r="AJ142">
+        <v>1.7</v>
+      </c>
+      <c r="AK142">
+        <v>1.25</v>
+      </c>
+      <c r="AL142">
+        <v>1.36</v>
+      </c>
+      <c r="AM142">
+        <v>1.71</v>
+      </c>
+      <c r="AN142">
+        <v>3</v>
+      </c>
+      <c r="AO142">
+        <v>0.75</v>
+      </c>
+      <c r="AP142">
+        <v>2.6</v>
+      </c>
+      <c r="AQ142">
+        <v>0.8</v>
+      </c>
+      <c r="AR142">
+        <v>1.88</v>
+      </c>
+      <c r="AS142">
+        <v>1.48</v>
+      </c>
+      <c r="AT142">
+        <v>3.36</v>
+      </c>
+      <c r="AU142">
+        <v>3</v>
+      </c>
+      <c r="AV142">
+        <v>7</v>
+      </c>
+      <c r="AW142">
+        <v>9</v>
+      </c>
+      <c r="AX142">
+        <v>2</v>
+      </c>
+      <c r="AY142">
+        <v>14</v>
+      </c>
+      <c r="AZ142">
+        <v>9</v>
+      </c>
+      <c r="BA142">
+        <v>7</v>
+      </c>
+      <c r="BB142">
+        <v>4</v>
+      </c>
+      <c r="BC142">
+        <v>11</v>
+      </c>
+      <c r="BD142">
+        <v>1.74</v>
+      </c>
+      <c r="BE142">
+        <v>6.4</v>
+      </c>
+      <c r="BF142">
+        <v>2.35</v>
+      </c>
+      <c r="BG142">
         <v>1.49</v>
       </c>
-      <c r="BH141">
+      <c r="BH142">
         <v>2.4</v>
       </c>
-      <c r="BI141">
+      <c r="BI142">
         <v>1.83</v>
       </c>
-      <c r="BJ141">
+      <c r="BJ142">
         <v>1.85</v>
       </c>
-      <c r="BK141">
-        <v>2.32</v>
-      </c>
-      <c r="BL141">
-        <v>1.53</v>
-      </c>
-      <c r="BM141">
-        <v>3</v>
-      </c>
-      <c r="BN141">
+      <c r="BK142">
+        <v>2.33</v>
+      </c>
+      <c r="BL142">
+        <v>1.52</v>
+      </c>
+      <c r="BM142">
+        <v>3.05</v>
+      </c>
+      <c r="BN142">
         <v>1.32</v>
       </c>
-      <c r="BO141">
+      <c r="BO142">
         <v>4.1</v>
       </c>
-      <c r="BP141">
+      <c r="BP142">
         <v>1.19</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -568,6 +568,15 @@
     <t>['69', '88']</t>
   </si>
   <si>
+    <t>['9', '32', '50', '81']</t>
+  </si>
+  <si>
+    <t>['44', '61', '70', '90+2']</t>
+  </si>
+  <si>
+    <t>['31']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -632,9 +641,6 @@
   </si>
   <si>
     <t>['57']</t>
-  </si>
-  <si>
-    <t>['31']</t>
   </si>
   <si>
     <t>['64']</t>
@@ -722,6 +728,9 @@
   </si>
   <si>
     <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['36']</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP142"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1339,7 +1348,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1751,7 +1760,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2163,7 +2172,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2241,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ6">
         <v>1.6</v>
@@ -2369,7 +2378,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2859,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9">
         <v>1.6</v>
@@ -2987,7 +2996,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -4095,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ15">
         <v>2.5</v>
@@ -4841,7 +4850,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5334,7 +5343,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5459,7 +5468,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5665,7 +5674,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5871,7 +5880,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6283,7 +6292,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6570,7 +6579,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ27">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -6695,7 +6704,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6776,7 +6785,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -8009,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34">
         <v>0.2</v>
@@ -8343,7 +8352,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8421,7 +8430,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ36">
         <v>1.6</v>
@@ -9167,7 +9176,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9991,7 +10000,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10069,7 +10078,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ44">
         <v>1.4</v>
@@ -10197,7 +10206,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10403,7 +10412,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10484,7 +10493,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ46">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR46">
         <v>2.39</v>
@@ -10609,7 +10618,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10815,7 +10824,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11433,7 +11442,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -12051,7 +12060,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12750,7 +12759,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ57">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR57">
         <v>0.73</v>
@@ -12875,7 +12884,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -12956,7 +12965,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR58">
         <v>0.9</v>
@@ -13493,7 +13502,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13777,7 +13786,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ62">
         <v>1.4</v>
@@ -14395,7 +14404,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ65">
         <v>0.6</v>
@@ -14729,7 +14738,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14810,7 +14819,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ67">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR67">
         <v>1.78</v>
@@ -14935,7 +14944,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15631,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ71">
         <v>0.67</v>
@@ -15759,7 +15768,7 @@
         <v>144</v>
       </c>
       <c r="P72" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="Q72">
         <v>3.25</v>
@@ -15965,7 +15974,7 @@
         <v>100</v>
       </c>
       <c r="P73" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q73">
         <v>4.5</v>
@@ -16458,7 +16467,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ75">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR75">
         <v>1.66</v>
@@ -16583,7 +16592,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16789,7 +16798,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16870,7 +16879,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ77">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR77">
         <v>1.47</v>
@@ -16995,7 +17004,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17407,7 +17416,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17613,7 +17622,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17819,7 +17828,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18231,7 +18240,7 @@
         <v>153</v>
       </c>
       <c r="P84" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q84">
         <v>2.75</v>
@@ -18643,7 +18652,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -19055,7 +19064,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19261,7 +19270,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19467,7 +19476,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19879,7 +19888,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20369,7 +20378,7 @@
         <v>0</v>
       </c>
       <c r="AP94">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ94">
         <v>0.25</v>
@@ -20578,7 +20587,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ95">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR95">
         <v>1.94</v>
@@ -20703,7 +20712,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20781,7 +20790,7 @@
         <v>0</v>
       </c>
       <c r="AP96">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ96">
         <v>0.6</v>
@@ -20909,7 +20918,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21605,10 +21614,10 @@
         <v>2.33</v>
       </c>
       <c r="AP100">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ100">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR100">
         <v>1.73</v>
@@ -21733,7 +21742,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -22635,7 +22644,7 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ105">
         <v>1.5</v>
@@ -23175,7 +23184,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23381,7 +23390,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23587,7 +23596,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -23999,7 +24008,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24286,7 +24295,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ113">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR113">
         <v>1.81</v>
@@ -24411,7 +24420,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24617,7 +24626,7 @@
         <v>154</v>
       </c>
       <c r="P115" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24823,7 +24832,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25029,7 +25038,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25441,7 +25450,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25522,7 +25531,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ119">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR119">
         <v>1.24</v>
@@ -25647,7 +25656,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -26059,7 +26068,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26265,7 +26274,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26964,7 +26973,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ126">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR126">
         <v>2.03</v>
@@ -27295,7 +27304,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28119,7 +28128,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28737,7 +28746,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -29561,7 +29570,7 @@
         <v>182</v>
       </c>
       <c r="P139" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -30336,6 +30345,624 @@
       </c>
       <c r="BP142">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7820458</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45732.76041666666</v>
+      </c>
+      <c r="F143">
+        <v>10</v>
+      </c>
+      <c r="G143" t="s">
+        <v>83</v>
+      </c>
+      <c r="H143" t="s">
+        <v>73</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>2</v>
+      </c>
+      <c r="L143">
+        <v>4</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>4</v>
+      </c>
+      <c r="O143" t="s">
+        <v>184</v>
+      </c>
+      <c r="P143" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q143">
+        <v>2.4</v>
+      </c>
+      <c r="R143">
+        <v>2.1</v>
+      </c>
+      <c r="S143">
+        <v>5.5</v>
+      </c>
+      <c r="T143">
+        <v>1.44</v>
+      </c>
+      <c r="U143">
+        <v>2.63</v>
+      </c>
+      <c r="V143">
+        <v>3.25</v>
+      </c>
+      <c r="W143">
+        <v>1.33</v>
+      </c>
+      <c r="X143">
+        <v>10</v>
+      </c>
+      <c r="Y143">
+        <v>1.06</v>
+      </c>
+      <c r="Z143">
+        <v>1.7</v>
+      </c>
+      <c r="AA143">
+        <v>3.5</v>
+      </c>
+      <c r="AB143">
+        <v>4.94</v>
+      </c>
+      <c r="AC143">
+        <v>1.07</v>
+      </c>
+      <c r="AD143">
+        <v>8</v>
+      </c>
+      <c r="AE143">
+        <v>1.38</v>
+      </c>
+      <c r="AF143">
+        <v>3</v>
+      </c>
+      <c r="AG143">
+        <v>2.15</v>
+      </c>
+      <c r="AH143">
+        <v>1.67</v>
+      </c>
+      <c r="AI143">
+        <v>2.05</v>
+      </c>
+      <c r="AJ143">
+        <v>1.7</v>
+      </c>
+      <c r="AK143">
+        <v>1.17</v>
+      </c>
+      <c r="AL143">
+        <v>1.28</v>
+      </c>
+      <c r="AM143">
+        <v>2.05</v>
+      </c>
+      <c r="AN143">
+        <v>2.6</v>
+      </c>
+      <c r="AO143">
+        <v>2</v>
+      </c>
+      <c r="AP143">
+        <v>2.67</v>
+      </c>
+      <c r="AQ143">
+        <v>1.67</v>
+      </c>
+      <c r="AR143">
+        <v>1.56</v>
+      </c>
+      <c r="AS143">
+        <v>1.37</v>
+      </c>
+      <c r="AT143">
+        <v>2.93</v>
+      </c>
+      <c r="AU143">
+        <v>7</v>
+      </c>
+      <c r="AV143">
+        <v>3</v>
+      </c>
+      <c r="AW143">
+        <v>5</v>
+      </c>
+      <c r="AX143">
+        <v>6</v>
+      </c>
+      <c r="AY143">
+        <v>13</v>
+      </c>
+      <c r="AZ143">
+        <v>13</v>
+      </c>
+      <c r="BA143">
+        <v>3</v>
+      </c>
+      <c r="BB143">
+        <v>3</v>
+      </c>
+      <c r="BC143">
+        <v>6</v>
+      </c>
+      <c r="BD143">
+        <v>1.44</v>
+      </c>
+      <c r="BE143">
+        <v>7</v>
+      </c>
+      <c r="BF143">
+        <v>3.15</v>
+      </c>
+      <c r="BG143">
+        <v>1.33</v>
+      </c>
+      <c r="BH143">
+        <v>3</v>
+      </c>
+      <c r="BI143">
+        <v>1.56</v>
+      </c>
+      <c r="BJ143">
+        <v>2.23</v>
+      </c>
+      <c r="BK143">
+        <v>1.92</v>
+      </c>
+      <c r="BL143">
+        <v>1.77</v>
+      </c>
+      <c r="BM143">
+        <v>2.43</v>
+      </c>
+      <c r="BN143">
+        <v>1.48</v>
+      </c>
+      <c r="BO143">
+        <v>3.15</v>
+      </c>
+      <c r="BP143">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7820460</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45732.875</v>
+      </c>
+      <c r="F144">
+        <v>10</v>
+      </c>
+      <c r="G144" t="s">
+        <v>74</v>
+      </c>
+      <c r="H144" t="s">
+        <v>81</v>
+      </c>
+      <c r="I144">
+        <v>1</v>
+      </c>
+      <c r="J144">
+        <v>1</v>
+      </c>
+      <c r="K144">
+        <v>2</v>
+      </c>
+      <c r="L144">
+        <v>4</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>5</v>
+      </c>
+      <c r="O144" t="s">
+        <v>185</v>
+      </c>
+      <c r="P144" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q144">
+        <v>2.5</v>
+      </c>
+      <c r="R144">
+        <v>1.95</v>
+      </c>
+      <c r="S144">
+        <v>6</v>
+      </c>
+      <c r="T144">
+        <v>1.57</v>
+      </c>
+      <c r="U144">
+        <v>2.25</v>
+      </c>
+      <c r="V144">
+        <v>3.75</v>
+      </c>
+      <c r="W144">
+        <v>1.25</v>
+      </c>
+      <c r="X144">
+        <v>13</v>
+      </c>
+      <c r="Y144">
+        <v>1.04</v>
+      </c>
+      <c r="Z144">
+        <v>1.83</v>
+      </c>
+      <c r="AA144">
+        <v>3.21</v>
+      </c>
+      <c r="AB144">
+        <v>4.62</v>
+      </c>
+      <c r="AC144">
+        <v>1.05</v>
+      </c>
+      <c r="AD144">
+        <v>7.1</v>
+      </c>
+      <c r="AE144">
+        <v>1.54</v>
+      </c>
+      <c r="AF144">
+        <v>2.47</v>
+      </c>
+      <c r="AG144">
+        <v>2.6</v>
+      </c>
+      <c r="AH144">
+        <v>1.48</v>
+      </c>
+      <c r="AI144">
+        <v>2.38</v>
+      </c>
+      <c r="AJ144">
+        <v>1.53</v>
+      </c>
+      <c r="AK144">
+        <v>1.18</v>
+      </c>
+      <c r="AL144">
+        <v>1.32</v>
+      </c>
+      <c r="AM144">
+        <v>1.93</v>
+      </c>
+      <c r="AN144">
+        <v>1.25</v>
+      </c>
+      <c r="AO144">
+        <v>0.2</v>
+      </c>
+      <c r="AP144">
+        <v>1.6</v>
+      </c>
+      <c r="AQ144">
+        <v>0.17</v>
+      </c>
+      <c r="AR144">
+        <v>1.91</v>
+      </c>
+      <c r="AS144">
+        <v>1.05</v>
+      </c>
+      <c r="AT144">
+        <v>2.96</v>
+      </c>
+      <c r="AU144">
+        <v>11</v>
+      </c>
+      <c r="AV144">
+        <v>5</v>
+      </c>
+      <c r="AW144">
+        <v>11</v>
+      </c>
+      <c r="AX144">
+        <v>2</v>
+      </c>
+      <c r="AY144">
+        <v>25</v>
+      </c>
+      <c r="AZ144">
+        <v>8</v>
+      </c>
+      <c r="BA144">
+        <v>6</v>
+      </c>
+      <c r="BB144">
+        <v>2</v>
+      </c>
+      <c r="BC144">
+        <v>8</v>
+      </c>
+      <c r="BD144">
+        <v>1.5</v>
+      </c>
+      <c r="BE144">
+        <v>6.75</v>
+      </c>
+      <c r="BF144">
+        <v>2.8</v>
+      </c>
+      <c r="BG144">
+        <v>1.35</v>
+      </c>
+      <c r="BH144">
+        <v>2.9</v>
+      </c>
+      <c r="BI144">
+        <v>1.58</v>
+      </c>
+      <c r="BJ144">
+        <v>2.18</v>
+      </c>
+      <c r="BK144">
+        <v>1.96</v>
+      </c>
+      <c r="BL144">
+        <v>1.74</v>
+      </c>
+      <c r="BM144">
+        <v>2.48</v>
+      </c>
+      <c r="BN144">
+        <v>1.47</v>
+      </c>
+      <c r="BO144">
+        <v>3.2</v>
+      </c>
+      <c r="BP144">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7820459</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45732.875</v>
+      </c>
+      <c r="F145">
+        <v>10</v>
+      </c>
+      <c r="G145" t="s">
+        <v>77</v>
+      </c>
+      <c r="H145" t="s">
+        <v>75</v>
+      </c>
+      <c r="I145">
+        <v>1</v>
+      </c>
+      <c r="J145">
+        <v>1</v>
+      </c>
+      <c r="K145">
+        <v>2</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145">
+        <v>1</v>
+      </c>
+      <c r="N145">
+        <v>2</v>
+      </c>
+      <c r="O145" t="s">
+        <v>186</v>
+      </c>
+      <c r="P145" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q145">
+        <v>2.5</v>
+      </c>
+      <c r="R145">
+        <v>2.05</v>
+      </c>
+      <c r="S145">
+        <v>5.5</v>
+      </c>
+      <c r="T145">
+        <v>1.5</v>
+      </c>
+      <c r="U145">
+        <v>2.5</v>
+      </c>
+      <c r="V145">
+        <v>3.4</v>
+      </c>
+      <c r="W145">
+        <v>1.3</v>
+      </c>
+      <c r="X145">
+        <v>10</v>
+      </c>
+      <c r="Y145">
+        <v>1.06</v>
+      </c>
+      <c r="Z145">
+        <v>1.76</v>
+      </c>
+      <c r="AA145">
+        <v>3.46</v>
+      </c>
+      <c r="AB145">
+        <v>4.55</v>
+      </c>
+      <c r="AC145">
+        <v>1.03</v>
+      </c>
+      <c r="AD145">
+        <v>7.2</v>
+      </c>
+      <c r="AE145">
+        <v>1.36</v>
+      </c>
+      <c r="AF145">
+        <v>2.78</v>
+      </c>
+      <c r="AG145">
+        <v>2.25</v>
+      </c>
+      <c r="AH145">
+        <v>1.62</v>
+      </c>
+      <c r="AI145">
+        <v>2.05</v>
+      </c>
+      <c r="AJ145">
+        <v>1.7</v>
+      </c>
+      <c r="AK145">
+        <v>1.19</v>
+      </c>
+      <c r="AL145">
+        <v>1.3</v>
+      </c>
+      <c r="AM145">
+        <v>1.95</v>
+      </c>
+      <c r="AN145">
+        <v>1.75</v>
+      </c>
+      <c r="AO145">
+        <v>1.5</v>
+      </c>
+      <c r="AP145">
+        <v>1.6</v>
+      </c>
+      <c r="AQ145">
+        <v>1.4</v>
+      </c>
+      <c r="AR145">
+        <v>1.68</v>
+      </c>
+      <c r="AS145">
+        <v>1.62</v>
+      </c>
+      <c r="AT145">
+        <v>3.3</v>
+      </c>
+      <c r="AU145">
+        <v>4</v>
+      </c>
+      <c r="AV145">
+        <v>3</v>
+      </c>
+      <c r="AW145">
+        <v>6</v>
+      </c>
+      <c r="AX145">
+        <v>1</v>
+      </c>
+      <c r="AY145">
+        <v>11</v>
+      </c>
+      <c r="AZ145">
+        <v>4</v>
+      </c>
+      <c r="BA145">
+        <v>8</v>
+      </c>
+      <c r="BB145">
+        <v>6</v>
+      </c>
+      <c r="BC145">
+        <v>14</v>
+      </c>
+      <c r="BD145">
+        <v>1.45</v>
+      </c>
+      <c r="BE145">
+        <v>7</v>
+      </c>
+      <c r="BF145">
+        <v>3.05</v>
+      </c>
+      <c r="BG145">
+        <v>1.3</v>
+      </c>
+      <c r="BH145">
+        <v>3.05</v>
+      </c>
+      <c r="BI145">
+        <v>1.53</v>
+      </c>
+      <c r="BJ145">
+        <v>2.3</v>
+      </c>
+      <c r="BK145">
+        <v>1.84</v>
+      </c>
+      <c r="BL145">
+        <v>1.84</v>
+      </c>
+      <c r="BM145">
+        <v>2.32</v>
+      </c>
+      <c r="BN145">
+        <v>1.53</v>
+      </c>
+      <c r="BO145">
+        <v>2.9</v>
+      </c>
+      <c r="BP145">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="244">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -577,6 +577,12 @@
     <t>['31']</t>
   </si>
   <si>
+    <t>['45+2', '79', '90+4']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -731,6 +737,15 @@
   </si>
   <si>
     <t>['36']</t>
+  </si>
+  <si>
+    <t>['80', '90+1']</t>
+  </si>
+  <si>
+    <t>['11', '31']</t>
+  </si>
+  <si>
+    <t>['27', '68']</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1348,7 +1363,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1632,10 +1647,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AQ3">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1760,7 +1775,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2047,7 +2062,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ5">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2172,7 +2187,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2378,7 +2393,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2996,7 +3011,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3074,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ10">
         <v>0.8</v>
@@ -4850,7 +4865,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5468,7 +5483,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5549,7 +5564,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5674,7 +5689,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5880,7 +5895,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6292,7 +6307,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6370,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ26">
         <v>1.75</v>
@@ -6704,7 +6719,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7609,7 +7624,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ32">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR32">
         <v>1.19</v>
@@ -7812,7 +7827,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ33">
         <v>1.5</v>
@@ -8352,7 +8367,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8845,7 +8860,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ38">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR38">
         <v>1.8</v>
@@ -9176,7 +9191,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9257,7 +9272,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ40">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>1.12</v>
@@ -9460,7 +9475,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AQ41">
         <v>0</v>
@@ -9875,7 +9890,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -10000,7 +10015,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10206,7 +10221,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10284,7 +10299,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ45">
         <v>1.6</v>
@@ -10412,7 +10427,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10618,7 +10633,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10824,7 +10839,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11442,7 +11457,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11726,7 +11741,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ52">
         <v>2.5</v>
@@ -12060,7 +12075,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12884,7 +12899,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13502,7 +13517,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13583,7 +13598,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ61">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR61">
         <v>0.96</v>
@@ -13995,7 +14010,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ63">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR63">
         <v>1.97</v>
@@ -14198,7 +14213,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AQ64">
         <v>0.8</v>
@@ -14738,7 +14753,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14944,7 +14959,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15231,7 +15246,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ69">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR69">
         <v>2.02</v>
@@ -15849,7 +15864,7 @@
         <v>2</v>
       </c>
       <c r="AQ72">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR72">
         <v>1.21</v>
@@ -15974,7 +15989,7 @@
         <v>100</v>
       </c>
       <c r="P73" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q73">
         <v>4.5</v>
@@ -16052,7 +16067,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ73">
         <v>1.25</v>
@@ -16258,7 +16273,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ74">
         <v>0.2</v>
@@ -16464,7 +16479,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ75">
         <v>0.17</v>
@@ -16592,7 +16607,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16798,7 +16813,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17004,7 +17019,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17416,7 +17431,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17622,7 +17637,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17828,7 +17843,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18240,7 +18255,7 @@
         <v>153</v>
       </c>
       <c r="P84" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q84">
         <v>2.75</v>
@@ -18652,7 +18667,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -19064,7 +19079,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19270,7 +19285,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19476,7 +19491,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19888,7 +19903,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19969,7 +19984,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ92">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.86</v>
@@ -20175,7 +20190,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR93">
         <v>1.29</v>
@@ -20381,7 +20396,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ94">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR94">
         <v>1.94</v>
@@ -20712,7 +20727,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20918,7 +20933,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -20996,7 +21011,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ97">
         <v>1.4</v>
@@ -21742,7 +21757,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -21820,7 +21835,7 @@
         <v>0.33</v>
       </c>
       <c r="AP101">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ101">
         <v>0.67</v>
@@ -22438,10 +22453,10 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AQ104">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR104">
         <v>1.38</v>
@@ -23056,7 +23071,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ107">
         <v>0.4</v>
@@ -23184,7 +23199,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23390,7 +23405,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23596,7 +23611,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -23880,7 +23895,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ111">
         <v>0.67</v>
@@ -24008,7 +24023,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24420,7 +24435,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24626,7 +24641,7 @@
         <v>154</v>
       </c>
       <c r="P115" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24832,7 +24847,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25038,7 +25053,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25116,7 +25131,7 @@
         <v>0</v>
       </c>
       <c r="AP117">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ117">
         <v>0.8</v>
@@ -25450,7 +25465,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25656,7 +25671,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -26068,7 +26083,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26274,7 +26289,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -27304,7 +27319,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28128,7 +28143,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28746,7 +28761,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -29570,7 +29585,7 @@
         <v>182</v>
       </c>
       <c r="P139" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -30806,7 +30821,7 @@
         <v>186</v>
       </c>
       <c r="P145" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -30963,6 +30978,830 @@
       </c>
       <c r="BP145">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7820461</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45733.79166666666</v>
+      </c>
+      <c r="F146">
+        <v>10</v>
+      </c>
+      <c r="G146" t="s">
+        <v>94</v>
+      </c>
+      <c r="H146" t="s">
+        <v>85</v>
+      </c>
+      <c r="I146">
+        <v>1</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>1</v>
+      </c>
+      <c r="L146">
+        <v>3</v>
+      </c>
+      <c r="M146">
+        <v>1</v>
+      </c>
+      <c r="N146">
+        <v>4</v>
+      </c>
+      <c r="O146" t="s">
+        <v>187</v>
+      </c>
+      <c r="P146" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q146">
+        <v>2.88</v>
+      </c>
+      <c r="R146">
+        <v>1.83</v>
+      </c>
+      <c r="S146">
+        <v>5</v>
+      </c>
+      <c r="T146">
+        <v>1.62</v>
+      </c>
+      <c r="U146">
+        <v>2.2</v>
+      </c>
+      <c r="V146">
+        <v>4</v>
+      </c>
+      <c r="W146">
+        <v>1.22</v>
+      </c>
+      <c r="X146">
+        <v>13</v>
+      </c>
+      <c r="Y146">
+        <v>1.04</v>
+      </c>
+      <c r="Z146">
+        <v>1.99</v>
+      </c>
+      <c r="AA146">
+        <v>3</v>
+      </c>
+      <c r="AB146">
+        <v>4.2</v>
+      </c>
+      <c r="AC146">
+        <v>1.14</v>
+      </c>
+      <c r="AD146">
+        <v>5.5</v>
+      </c>
+      <c r="AE146">
+        <v>1.6</v>
+      </c>
+      <c r="AF146">
+        <v>2.15</v>
+      </c>
+      <c r="AG146">
+        <v>3.1</v>
+      </c>
+      <c r="AH146">
+        <v>1.36</v>
+      </c>
+      <c r="AI146">
+        <v>2.38</v>
+      </c>
+      <c r="AJ146">
+        <v>1.53</v>
+      </c>
+      <c r="AK146">
+        <v>1.21</v>
+      </c>
+      <c r="AL146">
+        <v>1.38</v>
+      </c>
+      <c r="AM146">
+        <v>1.75</v>
+      </c>
+      <c r="AN146">
+        <v>1.25</v>
+      </c>
+      <c r="AO146">
+        <v>0.75</v>
+      </c>
+      <c r="AP146">
+        <v>1.6</v>
+      </c>
+      <c r="AQ146">
+        <v>0.6</v>
+      </c>
+      <c r="AR146">
+        <v>1.61</v>
+      </c>
+      <c r="AS146">
+        <v>1.17</v>
+      </c>
+      <c r="AT146">
+        <v>2.78</v>
+      </c>
+      <c r="AU146">
+        <v>7</v>
+      </c>
+      <c r="AV146">
+        <v>4</v>
+      </c>
+      <c r="AW146">
+        <v>5</v>
+      </c>
+      <c r="AX146">
+        <v>10</v>
+      </c>
+      <c r="AY146">
+        <v>15</v>
+      </c>
+      <c r="AZ146">
+        <v>17</v>
+      </c>
+      <c r="BA146">
+        <v>5</v>
+      </c>
+      <c r="BB146">
+        <v>3</v>
+      </c>
+      <c r="BC146">
+        <v>8</v>
+      </c>
+      <c r="BD146">
+        <v>1.55</v>
+      </c>
+      <c r="BE146">
+        <v>8</v>
+      </c>
+      <c r="BF146">
+        <v>3.02</v>
+      </c>
+      <c r="BG146">
+        <v>1.5</v>
+      </c>
+      <c r="BH146">
+        <v>2.41</v>
+      </c>
+      <c r="BI146">
+        <v>1.87</v>
+      </c>
+      <c r="BJ146">
+        <v>1.87</v>
+      </c>
+      <c r="BK146">
+        <v>2.42</v>
+      </c>
+      <c r="BL146">
+        <v>1.53</v>
+      </c>
+      <c r="BM146">
+        <v>3.25</v>
+      </c>
+      <c r="BN146">
+        <v>1.29</v>
+      </c>
+      <c r="BO146">
+        <v>4.4</v>
+      </c>
+      <c r="BP146">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7820462</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45733.79166666666</v>
+      </c>
+      <c r="F147">
+        <v>10</v>
+      </c>
+      <c r="G147" t="s">
+        <v>71</v>
+      </c>
+      <c r="H147" t="s">
+        <v>84</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="M147">
+        <v>2</v>
+      </c>
+      <c r="N147">
+        <v>3</v>
+      </c>
+      <c r="O147" t="s">
+        <v>188</v>
+      </c>
+      <c r="P147" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q147">
+        <v>3.25</v>
+      </c>
+      <c r="R147">
+        <v>1.91</v>
+      </c>
+      <c r="S147">
+        <v>4</v>
+      </c>
+      <c r="T147">
+        <v>1.57</v>
+      </c>
+      <c r="U147">
+        <v>2.25</v>
+      </c>
+      <c r="V147">
+        <v>3.75</v>
+      </c>
+      <c r="W147">
+        <v>1.25</v>
+      </c>
+      <c r="X147">
+        <v>13</v>
+      </c>
+      <c r="Y147">
+        <v>1.04</v>
+      </c>
+      <c r="Z147">
+        <v>2.33</v>
+      </c>
+      <c r="AA147">
+        <v>2.82</v>
+      </c>
+      <c r="AB147">
+        <v>3.47</v>
+      </c>
+      <c r="AC147">
+        <v>1.11</v>
+      </c>
+      <c r="AD147">
+        <v>6.25</v>
+      </c>
+      <c r="AE147">
+        <v>1.5</v>
+      </c>
+      <c r="AF147">
+        <v>2.37</v>
+      </c>
+      <c r="AG147">
+        <v>2.6</v>
+      </c>
+      <c r="AH147">
+        <v>1.48</v>
+      </c>
+      <c r="AI147">
+        <v>2.1</v>
+      </c>
+      <c r="AJ147">
+        <v>1.67</v>
+      </c>
+      <c r="AK147">
+        <v>1.33</v>
+      </c>
+      <c r="AL147">
+        <v>1.37</v>
+      </c>
+      <c r="AM147">
+        <v>1.55</v>
+      </c>
+      <c r="AN147">
+        <v>3</v>
+      </c>
+      <c r="AO147">
+        <v>0.33</v>
+      </c>
+      <c r="AP147">
+        <v>2.4</v>
+      </c>
+      <c r="AQ147">
+        <v>1</v>
+      </c>
+      <c r="AR147">
+        <v>1.38</v>
+      </c>
+      <c r="AS147">
+        <v>1.42</v>
+      </c>
+      <c r="AT147">
+        <v>2.8</v>
+      </c>
+      <c r="AU147">
+        <v>2</v>
+      </c>
+      <c r="AV147">
+        <v>5</v>
+      </c>
+      <c r="AW147">
+        <v>2</v>
+      </c>
+      <c r="AX147">
+        <v>1</v>
+      </c>
+      <c r="AY147">
+        <v>4</v>
+      </c>
+      <c r="AZ147">
+        <v>6</v>
+      </c>
+      <c r="BA147">
+        <v>5</v>
+      </c>
+      <c r="BB147">
+        <v>2</v>
+      </c>
+      <c r="BC147">
+        <v>7</v>
+      </c>
+      <c r="BD147">
+        <v>2.05</v>
+      </c>
+      <c r="BE147">
+        <v>7.5</v>
+      </c>
+      <c r="BF147">
+        <v>2</v>
+      </c>
+      <c r="BG147">
+        <v>1.55</v>
+      </c>
+      <c r="BH147">
+        <v>2.37</v>
+      </c>
+      <c r="BI147">
+        <v>1.92</v>
+      </c>
+      <c r="BJ147">
+        <v>1.82</v>
+      </c>
+      <c r="BK147">
+        <v>2.46</v>
+      </c>
+      <c r="BL147">
+        <v>1.48</v>
+      </c>
+      <c r="BM147">
+        <v>3.32</v>
+      </c>
+      <c r="BN147">
+        <v>1.26</v>
+      </c>
+      <c r="BO147">
+        <v>4.6</v>
+      </c>
+      <c r="BP147">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7820463</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45733.88541666666</v>
+      </c>
+      <c r="F148">
+        <v>10</v>
+      </c>
+      <c r="G148" t="s">
+        <v>78</v>
+      </c>
+      <c r="H148" t="s">
+        <v>82</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>2</v>
+      </c>
+      <c r="K148">
+        <v>2</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>2</v>
+      </c>
+      <c r="N148">
+        <v>2</v>
+      </c>
+      <c r="O148" t="s">
+        <v>100</v>
+      </c>
+      <c r="P148" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q148">
+        <v>3.75</v>
+      </c>
+      <c r="R148">
+        <v>1.73</v>
+      </c>
+      <c r="S148">
+        <v>4</v>
+      </c>
+      <c r="T148">
+        <v>1.8</v>
+      </c>
+      <c r="U148">
+        <v>1.91</v>
+      </c>
+      <c r="V148">
+        <v>5.5</v>
+      </c>
+      <c r="W148">
+        <v>1.14</v>
+      </c>
+      <c r="X148">
+        <v>19</v>
+      </c>
+      <c r="Y148">
+        <v>1.02</v>
+      </c>
+      <c r="Z148">
+        <v>2.74</v>
+      </c>
+      <c r="AA148">
+        <v>2.57</v>
+      </c>
+      <c r="AB148">
+        <v>3.14</v>
+      </c>
+      <c r="AC148">
+        <v>1.18</v>
+      </c>
+      <c r="AD148">
+        <v>4.75</v>
+      </c>
+      <c r="AE148">
+        <v>1.8</v>
+      </c>
+      <c r="AF148">
+        <v>1.96</v>
+      </c>
+      <c r="AG148">
+        <v>3.6</v>
+      </c>
+      <c r="AH148">
+        <v>1.29</v>
+      </c>
+      <c r="AI148">
+        <v>2.63</v>
+      </c>
+      <c r="AJ148">
+        <v>1.44</v>
+      </c>
+      <c r="AK148">
+        <v>1.37</v>
+      </c>
+      <c r="AL148">
+        <v>1.46</v>
+      </c>
+      <c r="AM148">
+        <v>1.41</v>
+      </c>
+      <c r="AN148">
+        <v>0.8</v>
+      </c>
+      <c r="AO148">
+        <v>1</v>
+      </c>
+      <c r="AP148">
+        <v>0.67</v>
+      </c>
+      <c r="AQ148">
+        <v>1.4</v>
+      </c>
+      <c r="AR148">
+        <v>1.46</v>
+      </c>
+      <c r="AS148">
+        <v>1</v>
+      </c>
+      <c r="AT148">
+        <v>2.46</v>
+      </c>
+      <c r="AU148">
+        <v>6</v>
+      </c>
+      <c r="AV148">
+        <v>7</v>
+      </c>
+      <c r="AW148">
+        <v>9</v>
+      </c>
+      <c r="AX148">
+        <v>6</v>
+      </c>
+      <c r="AY148">
+        <v>19</v>
+      </c>
+      <c r="AZ148">
+        <v>13</v>
+      </c>
+      <c r="BA148">
+        <v>3</v>
+      </c>
+      <c r="BB148">
+        <v>2</v>
+      </c>
+      <c r="BC148">
+        <v>5</v>
+      </c>
+      <c r="BD148">
+        <v>1.82</v>
+      </c>
+      <c r="BE148">
+        <v>7.5</v>
+      </c>
+      <c r="BF148">
+        <v>2.4</v>
+      </c>
+      <c r="BG148">
+        <v>1.55</v>
+      </c>
+      <c r="BH148">
+        <v>2.37</v>
+      </c>
+      <c r="BI148">
+        <v>1.92</v>
+      </c>
+      <c r="BJ148">
+        <v>1.82</v>
+      </c>
+      <c r="BK148">
+        <v>2.46</v>
+      </c>
+      <c r="BL148">
+        <v>1.48</v>
+      </c>
+      <c r="BM148">
+        <v>3.32</v>
+      </c>
+      <c r="BN148">
+        <v>1.26</v>
+      </c>
+      <c r="BO148">
+        <v>4.6</v>
+      </c>
+      <c r="BP148">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7820464</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45733.88541666666</v>
+      </c>
+      <c r="F149">
+        <v>10</v>
+      </c>
+      <c r="G149" t="s">
+        <v>99</v>
+      </c>
+      <c r="H149" t="s">
+        <v>90</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149">
+        <v>1</v>
+      </c>
+      <c r="K149">
+        <v>2</v>
+      </c>
+      <c r="L149">
+        <v>1</v>
+      </c>
+      <c r="M149">
+        <v>2</v>
+      </c>
+      <c r="N149">
+        <v>3</v>
+      </c>
+      <c r="O149" t="s">
+        <v>102</v>
+      </c>
+      <c r="P149" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q149">
+        <v>3.25</v>
+      </c>
+      <c r="R149">
+        <v>1.91</v>
+      </c>
+      <c r="S149">
+        <v>4</v>
+      </c>
+      <c r="T149">
+        <v>1.57</v>
+      </c>
+      <c r="U149">
+        <v>2.25</v>
+      </c>
+      <c r="V149">
+        <v>3.75</v>
+      </c>
+      <c r="W149">
+        <v>1.25</v>
+      </c>
+      <c r="X149">
+        <v>13</v>
+      </c>
+      <c r="Y149">
+        <v>1.04</v>
+      </c>
+      <c r="Z149">
+        <v>2.4</v>
+      </c>
+      <c r="AA149">
+        <v>2.81</v>
+      </c>
+      <c r="AB149">
+        <v>3.35</v>
+      </c>
+      <c r="AC149">
+        <v>1.1</v>
+      </c>
+      <c r="AD149">
+        <v>6.5</v>
+      </c>
+      <c r="AE149">
+        <v>1.5</v>
+      </c>
+      <c r="AF149">
+        <v>2.55</v>
+      </c>
+      <c r="AG149">
+        <v>2.5</v>
+      </c>
+      <c r="AH149">
+        <v>1.5</v>
+      </c>
+      <c r="AI149">
+        <v>2.1</v>
+      </c>
+      <c r="AJ149">
+        <v>1.67</v>
+      </c>
+      <c r="AK149">
+        <v>1.34</v>
+      </c>
+      <c r="AL149">
+        <v>1.37</v>
+      </c>
+      <c r="AM149">
+        <v>1.55</v>
+      </c>
+      <c r="AN149">
+        <v>0.75</v>
+      </c>
+      <c r="AO149">
+        <v>0.25</v>
+      </c>
+      <c r="AP149">
+        <v>0.6</v>
+      </c>
+      <c r="AQ149">
+        <v>0.8</v>
+      </c>
+      <c r="AR149">
+        <v>1.84</v>
+      </c>
+      <c r="AS149">
+        <v>0.96</v>
+      </c>
+      <c r="AT149">
+        <v>2.8</v>
+      </c>
+      <c r="AU149">
+        <v>4</v>
+      </c>
+      <c r="AV149">
+        <v>3</v>
+      </c>
+      <c r="AW149">
+        <v>7</v>
+      </c>
+      <c r="AX149">
+        <v>4</v>
+      </c>
+      <c r="AY149">
+        <v>14</v>
+      </c>
+      <c r="AZ149">
+        <v>9</v>
+      </c>
+      <c r="BA149">
+        <v>7</v>
+      </c>
+      <c r="BB149">
+        <v>1</v>
+      </c>
+      <c r="BC149">
+        <v>8</v>
+      </c>
+      <c r="BD149">
+        <v>1.85</v>
+      </c>
+      <c r="BE149">
+        <v>8.4</v>
+      </c>
+      <c r="BF149">
+        <v>2.35</v>
+      </c>
+      <c r="BG149">
+        <v>1.24</v>
+      </c>
+      <c r="BH149">
+        <v>3.34</v>
+      </c>
+      <c r="BI149">
+        <v>1.47</v>
+      </c>
+      <c r="BJ149">
+        <v>2.42</v>
+      </c>
+      <c r="BK149">
+        <v>1.83</v>
+      </c>
+      <c r="BL149">
+        <v>1.87</v>
+      </c>
+      <c r="BM149">
+        <v>2.34</v>
+      </c>
+      <c r="BN149">
+        <v>1.5</v>
+      </c>
+      <c r="BO149">
+        <v>3.08</v>
+      </c>
+      <c r="BP149">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="245">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -747,6 +747,9 @@
   <si>
     <t>['27', '68']</t>
   </si>
+  <si>
+    <t>['58']</t>
+  </si>
 </sst>
 </file>
 
@@ -1107,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP149"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2474,7 +2477,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ7">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -6385,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26">
         <v>1.75</v>
@@ -9684,7 +9687,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ42">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR42">
         <v>2.46</v>
@@ -11741,7 +11744,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ52">
         <v>2.5</v>
@@ -14216,7 +14219,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ64">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR64">
         <v>1.42</v>
@@ -16479,7 +16482,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ75">
         <v>0.17</v>
@@ -23895,7 +23898,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ111">
         <v>0.67</v>
@@ -24928,7 +24931,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR116">
         <v>1.45</v>
@@ -30284,7 +30287,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ142">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR142">
         <v>1.88</v>
@@ -31105,7 +31108,7 @@
         <v>0.75</v>
       </c>
       <c r="AP146">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ146">
         <v>0.6</v>
@@ -31802,6 +31805,212 @@
       </c>
       <c r="BP149">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7820416</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45736.875</v>
+      </c>
+      <c r="F150">
+        <v>7</v>
+      </c>
+      <c r="G150" t="s">
+        <v>94</v>
+      </c>
+      <c r="H150" t="s">
+        <v>97</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>1</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150" t="s">
+        <v>100</v>
+      </c>
+      <c r="P150" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q150">
+        <v>3.6</v>
+      </c>
+      <c r="R150">
+        <v>1.91</v>
+      </c>
+      <c r="S150">
+        <v>3.6</v>
+      </c>
+      <c r="T150">
+        <v>1.57</v>
+      </c>
+      <c r="U150">
+        <v>2.25</v>
+      </c>
+      <c r="V150">
+        <v>4</v>
+      </c>
+      <c r="W150">
+        <v>1.22</v>
+      </c>
+      <c r="X150">
+        <v>13</v>
+      </c>
+      <c r="Y150">
+        <v>1.04</v>
+      </c>
+      <c r="Z150">
+        <v>2.75</v>
+      </c>
+      <c r="AA150">
+        <v>3.1</v>
+      </c>
+      <c r="AB150">
+        <v>2.75</v>
+      </c>
+      <c r="AC150">
+        <v>1.09</v>
+      </c>
+      <c r="AD150">
+        <v>7</v>
+      </c>
+      <c r="AE150">
+        <v>1.5</v>
+      </c>
+      <c r="AF150">
+        <v>2.4</v>
+      </c>
+      <c r="AG150">
+        <v>2.6</v>
+      </c>
+      <c r="AH150">
+        <v>1.48</v>
+      </c>
+      <c r="AI150">
+        <v>2.1</v>
+      </c>
+      <c r="AJ150">
+        <v>1.67</v>
+      </c>
+      <c r="AK150">
+        <v>1.51</v>
+      </c>
+      <c r="AL150">
+        <v>1.34</v>
+      </c>
+      <c r="AM150">
+        <v>1.39</v>
+      </c>
+      <c r="AN150">
+        <v>1.6</v>
+      </c>
+      <c r="AO150">
+        <v>0.8</v>
+      </c>
+      <c r="AP150">
+        <v>1.33</v>
+      </c>
+      <c r="AQ150">
+        <v>1.17</v>
+      </c>
+      <c r="AR150">
+        <v>1.62</v>
+      </c>
+      <c r="AS150">
+        <v>1.45</v>
+      </c>
+      <c r="AT150">
+        <v>3.07</v>
+      </c>
+      <c r="AU150">
+        <v>8</v>
+      </c>
+      <c r="AV150">
+        <v>2</v>
+      </c>
+      <c r="AW150">
+        <v>17</v>
+      </c>
+      <c r="AX150">
+        <v>4</v>
+      </c>
+      <c r="AY150">
+        <v>35</v>
+      </c>
+      <c r="AZ150">
+        <v>6</v>
+      </c>
+      <c r="BA150">
+        <v>10</v>
+      </c>
+      <c r="BB150">
+        <v>1</v>
+      </c>
+      <c r="BC150">
+        <v>11</v>
+      </c>
+      <c r="BD150">
+        <v>2.05</v>
+      </c>
+      <c r="BE150">
+        <v>6.25</v>
+      </c>
+      <c r="BF150">
+        <v>1.95</v>
+      </c>
+      <c r="BG150">
+        <v>1.54</v>
+      </c>
+      <c r="BH150">
+        <v>2.3</v>
+      </c>
+      <c r="BI150">
+        <v>1.9</v>
+      </c>
+      <c r="BJ150">
+        <v>1.79</v>
+      </c>
+      <c r="BK150">
+        <v>2.43</v>
+      </c>
+      <c r="BL150">
+        <v>1.47</v>
+      </c>
+      <c r="BM150">
+        <v>3.2</v>
+      </c>
+      <c r="BN150">
+        <v>1.28</v>
+      </c>
+      <c r="BO150">
+        <v>4.35</v>
+      </c>
+      <c r="BP150">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="245">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1110,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP150"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ2">
         <v>1.5</v>
@@ -3301,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -15452,7 +15452,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ70">
         <v>1.4</v>
@@ -16073,7 +16073,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ73">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR73">
         <v>1.31</v>
@@ -19781,7 +19781,7 @@
         <v>1</v>
       </c>
       <c r="AQ91">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR91">
         <v>1.17</v>
@@ -20190,7 +20190,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ93">
         <v>1.4</v>
@@ -29048,7 +29048,7 @@
         <v>1.75</v>
       </c>
       <c r="AP136">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ136">
         <v>1.6</v>
@@ -30081,7 +30081,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ141">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR141">
         <v>1.98</v>
@@ -32011,6 +32011,212 @@
       </c>
       <c r="BP150">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7820358</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45738.70833333334</v>
+      </c>
+      <c r="F151">
+        <v>3</v>
+      </c>
+      <c r="G151" t="s">
+        <v>70</v>
+      </c>
+      <c r="H151" t="s">
+        <v>91</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151" t="s">
+        <v>100</v>
+      </c>
+      <c r="P151" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q151">
+        <v>5</v>
+      </c>
+      <c r="R151">
+        <v>1.95</v>
+      </c>
+      <c r="S151">
+        <v>2.63</v>
+      </c>
+      <c r="T151">
+        <v>1.53</v>
+      </c>
+      <c r="U151">
+        <v>2.38</v>
+      </c>
+      <c r="V151">
+        <v>3.75</v>
+      </c>
+      <c r="W151">
+        <v>1.25</v>
+      </c>
+      <c r="X151">
+        <v>11</v>
+      </c>
+      <c r="Y151">
+        <v>1.05</v>
+      </c>
+      <c r="Z151">
+        <v>4.5</v>
+      </c>
+      <c r="AA151">
+        <v>3.25</v>
+      </c>
+      <c r="AB151">
+        <v>1.91</v>
+      </c>
+      <c r="AC151">
+        <v>1.08</v>
+      </c>
+      <c r="AD151">
+        <v>7</v>
+      </c>
+      <c r="AE151">
+        <v>1.48</v>
+      </c>
+      <c r="AF151">
+        <v>2.62</v>
+      </c>
+      <c r="AG151">
+        <v>2.4</v>
+      </c>
+      <c r="AH151">
+        <v>1.53</v>
+      </c>
+      <c r="AI151">
+        <v>2.1</v>
+      </c>
+      <c r="AJ151">
+        <v>1.67</v>
+      </c>
+      <c r="AK151">
+        <v>1.8</v>
+      </c>
+      <c r="AL151">
+        <v>1.34</v>
+      </c>
+      <c r="AM151">
+        <v>1.22</v>
+      </c>
+      <c r="AN151">
+        <v>0.75</v>
+      </c>
+      <c r="AO151">
+        <v>1.25</v>
+      </c>
+      <c r="AP151">
+        <v>0.8</v>
+      </c>
+      <c r="AQ151">
+        <v>1.2</v>
+      </c>
+      <c r="AR151">
+        <v>1.16</v>
+      </c>
+      <c r="AS151">
+        <v>2.08</v>
+      </c>
+      <c r="AT151">
+        <v>3.24</v>
+      </c>
+      <c r="AU151">
+        <v>2</v>
+      </c>
+      <c r="AV151">
+        <v>4</v>
+      </c>
+      <c r="AW151">
+        <v>5</v>
+      </c>
+      <c r="AX151">
+        <v>2</v>
+      </c>
+      <c r="AY151">
+        <v>11</v>
+      </c>
+      <c r="AZ151">
+        <v>8</v>
+      </c>
+      <c r="BA151">
+        <v>0</v>
+      </c>
+      <c r="BB151">
+        <v>2</v>
+      </c>
+      <c r="BC151">
+        <v>2</v>
+      </c>
+      <c r="BD151">
+        <v>2.05</v>
+      </c>
+      <c r="BE151">
+        <v>6.25</v>
+      </c>
+      <c r="BF151">
+        <v>1.96</v>
+      </c>
+      <c r="BG151">
+        <v>1.41</v>
+      </c>
+      <c r="BH151">
+        <v>2.65</v>
+      </c>
+      <c r="BI151">
+        <v>1.71</v>
+      </c>
+      <c r="BJ151">
+        <v>2</v>
+      </c>
+      <c r="BK151">
+        <v>2.14</v>
+      </c>
+      <c r="BL151">
+        <v>1.62</v>
+      </c>
+      <c r="BM151">
+        <v>2.75</v>
+      </c>
+      <c r="BN151">
+        <v>1.38</v>
+      </c>
+      <c r="BO151">
+        <v>3.65</v>
+      </c>
+      <c r="BP151">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -27692,7 +27692,7 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>7820445</v>
+        <v>7820446</v>
       </c>
       <c r="C130" t="s">
         <v>68</v>
@@ -27707,154 +27707,154 @@
         <v>9</v>
       </c>
       <c r="G130" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H130" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O130" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="P130" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="Q130">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R130">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="S130">
+        <v>5.5</v>
+      </c>
+      <c r="T130">
+        <v>1.67</v>
+      </c>
+      <c r="U130">
+        <v>2.1</v>
+      </c>
+      <c r="V130">
         <v>4.33</v>
       </c>
-      <c r="T130">
-        <v>1.57</v>
-      </c>
-      <c r="U130">
-        <v>2.25</v>
-      </c>
-      <c r="V130">
-        <v>3.75</v>
-      </c>
       <c r="W130">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X130">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y130">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z130">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AA130">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="AB130">
-        <v>3.55</v>
+        <v>4.45</v>
       </c>
       <c r="AC130">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AD130">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AE130">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF130">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AG130">
+        <v>2.88</v>
+      </c>
+      <c r="AH130">
+        <v>1.4</v>
+      </c>
+      <c r="AI130">
         <v>2.5</v>
       </c>
-      <c r="AH130">
+      <c r="AJ130">
         <v>1.5</v>
       </c>
-      <c r="AI130">
-        <v>2.2</v>
-      </c>
-      <c r="AJ130">
-        <v>1.62</v>
-      </c>
       <c r="AK130">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL130">
         <v>1.36</v>
       </c>
       <c r="AM130">
+        <v>1.77</v>
+      </c>
+      <c r="AN130">
+        <v>2</v>
+      </c>
+      <c r="AO130">
+        <v>1.75</v>
+      </c>
+      <c r="AP130">
+        <v>1.75</v>
+      </c>
+      <c r="AQ130">
+        <v>1.6</v>
+      </c>
+      <c r="AR130">
+        <v>1.36</v>
+      </c>
+      <c r="AS130">
+        <v>1.31</v>
+      </c>
+      <c r="AT130">
+        <v>2.67</v>
+      </c>
+      <c r="AU130">
+        <v>7</v>
+      </c>
+      <c r="AV130">
+        <v>2</v>
+      </c>
+      <c r="AW130">
+        <v>8</v>
+      </c>
+      <c r="AX130">
+        <v>3</v>
+      </c>
+      <c r="AY130">
+        <v>18</v>
+      </c>
+      <c r="AZ130">
+        <v>7</v>
+      </c>
+      <c r="BA130">
+        <v>11</v>
+      </c>
+      <c r="BB130">
+        <v>1</v>
+      </c>
+      <c r="BC130">
+        <v>12</v>
+      </c>
+      <c r="BD130">
         <v>1.61</v>
-      </c>
-      <c r="AN130">
-        <v>0.75</v>
-      </c>
-      <c r="AO130">
-        <v>0.25</v>
-      </c>
-      <c r="AP130">
-        <v>0.8</v>
-      </c>
-      <c r="AQ130">
-        <v>0.4</v>
-      </c>
-      <c r="AR130">
-        <v>1.81</v>
-      </c>
-      <c r="AS130">
-        <v>1.5</v>
-      </c>
-      <c r="AT130">
-        <v>3.31</v>
-      </c>
-      <c r="AU130">
-        <v>5</v>
-      </c>
-      <c r="AV130">
-        <v>4</v>
-      </c>
-      <c r="AW130">
-        <v>10</v>
-      </c>
-      <c r="AX130">
-        <v>2</v>
-      </c>
-      <c r="AY130">
-        <v>17</v>
-      </c>
-      <c r="AZ130">
-        <v>6</v>
-      </c>
-      <c r="BA130">
-        <v>5</v>
-      </c>
-      <c r="BB130">
-        <v>3</v>
-      </c>
-      <c r="BC130">
-        <v>8</v>
-      </c>
-      <c r="BD130">
-        <v>1.63</v>
       </c>
       <c r="BE130">
         <v>6.4</v>
@@ -27863,34 +27863,34 @@
         <v>2.55</v>
       </c>
       <c r="BG130">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BH130">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="BI130">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BJ130">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="BK130">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="BL130">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BM130">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="BN130">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BO130">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP130">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="131" spans="1:68">
@@ -27898,7 +27898,7 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>7820446</v>
+        <v>7820445</v>
       </c>
       <c r="C131" t="s">
         <v>68</v>
@@ -27913,154 +27913,154 @@
         <v>9</v>
       </c>
       <c r="G131" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H131" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O131" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="P131" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="Q131">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R131">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S131">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="T131">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="U131">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V131">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="W131">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X131">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y131">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z131">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AA131">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="AB131">
-        <v>4.45</v>
+        <v>3.55</v>
       </c>
       <c r="AC131">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AD131">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AE131">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF131">
+        <v>2.37</v>
+      </c>
+      <c r="AG131">
+        <v>2.5</v>
+      </c>
+      <c r="AH131">
+        <v>1.5</v>
+      </c>
+      <c r="AI131">
         <v>2.2</v>
       </c>
-      <c r="AG131">
-        <v>2.88</v>
-      </c>
-      <c r="AH131">
-        <v>1.4</v>
-      </c>
-      <c r="AI131">
-        <v>2.5</v>
-      </c>
       <c r="AJ131">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AK131">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL131">
         <v>1.36</v>
       </c>
       <c r="AM131">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AN131">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="AO131">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="AP131">
-        <v>1.75</v>
+        <v>0.8</v>
       </c>
       <c r="AQ131">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="AR131">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="AS131">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AT131">
-        <v>2.67</v>
+        <v>3.31</v>
       </c>
       <c r="AU131">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV131">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW131">
+        <v>10</v>
+      </c>
+      <c r="AX131">
+        <v>2</v>
+      </c>
+      <c r="AY131">
+        <v>17</v>
+      </c>
+      <c r="AZ131">
+        <v>6</v>
+      </c>
+      <c r="BA131">
+        <v>5</v>
+      </c>
+      <c r="BB131">
+        <v>3</v>
+      </c>
+      <c r="BC131">
         <v>8</v>
       </c>
-      <c r="AX131">
-        <v>3</v>
-      </c>
-      <c r="AY131">
-        <v>18</v>
-      </c>
-      <c r="AZ131">
-        <v>7</v>
-      </c>
-      <c r="BA131">
-        <v>11</v>
-      </c>
-      <c r="BB131">
-        <v>1</v>
-      </c>
-      <c r="BC131">
-        <v>12</v>
-      </c>
       <c r="BD131">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BE131">
         <v>6.4</v>
@@ -28069,34 +28069,34 @@
         <v>2.55</v>
       </c>
       <c r="BG131">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BH131">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="BI131">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BJ131">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="BK131">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="BL131">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BM131">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="BN131">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="BO131">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BP131">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="132" spans="1:68">
@@ -29752,7 +29752,7 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>7820455</v>
+        <v>7820456</v>
       </c>
       <c r="C140" t="s">
         <v>68</v>
@@ -29767,10 +29767,10 @@
         <v>10</v>
       </c>
       <c r="G140" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H140" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -29782,28 +29782,28 @@
         <v>0</v>
       </c>
       <c r="L140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M140">
         <v>0</v>
       </c>
       <c r="N140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O140" t="s">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="P140" t="s">
         <v>100</v>
       </c>
       <c r="Q140">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="R140">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S140">
-        <v>6</v>
+        <v>2.75</v>
       </c>
       <c r="T140">
         <v>1.57</v>
@@ -29812,145 +29812,145 @@
         <v>2.25</v>
       </c>
       <c r="V140">
+        <v>3.75</v>
+      </c>
+      <c r="W140">
+        <v>1.25</v>
+      </c>
+      <c r="X140">
+        <v>11</v>
+      </c>
+      <c r="Y140">
+        <v>1.05</v>
+      </c>
+      <c r="Z140">
         <v>4</v>
       </c>
-      <c r="W140">
-        <v>1.22</v>
-      </c>
-      <c r="X140">
-        <v>13</v>
-      </c>
-      <c r="Y140">
-        <v>1.04</v>
-      </c>
-      <c r="Z140">
-        <v>1.75</v>
-      </c>
       <c r="AA140">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB140">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC140">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AD140">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AE140">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF140">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AG140">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH140">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AI140">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ140">
+        <v>1.62</v>
+      </c>
+      <c r="AK140">
+        <v>1.51</v>
+      </c>
+      <c r="AL140">
+        <v>1.35</v>
+      </c>
+      <c r="AM140">
+        <v>1.38</v>
+      </c>
+      <c r="AN140">
         <v>1.5</v>
       </c>
-      <c r="AK140">
-        <v>1.17</v>
-      </c>
-      <c r="AL140">
-        <v>1.34</v>
-      </c>
-      <c r="AM140">
-        <v>1.93</v>
-      </c>
-      <c r="AN140">
-        <v>2.5</v>
-      </c>
       <c r="AO140">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AP140">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="AQ140">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AR140">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AS140">
-        <v>1.26</v>
+        <v>2.04</v>
       </c>
       <c r="AT140">
-        <v>2.96</v>
+        <v>4.02</v>
       </c>
       <c r="AU140">
+        <v>3</v>
+      </c>
+      <c r="AV140">
+        <v>8</v>
+      </c>
+      <c r="AW140">
         <v>6</v>
       </c>
-      <c r="AV140">
-        <v>2</v>
-      </c>
-      <c r="AW140">
-        <v>2</v>
-      </c>
       <c r="AX140">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY140">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ140">
+        <v>18</v>
+      </c>
+      <c r="BA140">
+        <v>2</v>
+      </c>
+      <c r="BB140">
         <v>7</v>
       </c>
-      <c r="BA140">
-        <v>1</v>
-      </c>
-      <c r="BB140">
-        <v>4</v>
-      </c>
       <c r="BC140">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BD140">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="BE140">
         <v>6.4</v>
       </c>
       <c r="BF140">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="BG140">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="BH140">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="BI140">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BJ140">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="BK140">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="BL140">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="BM140">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="BN140">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="BO140">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BP140">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="141" spans="1:68">
@@ -29958,7 +29958,7 @@
         <v>140</v>
       </c>
       <c r="B141">
-        <v>7820456</v>
+        <v>7820455</v>
       </c>
       <c r="C141" t="s">
         <v>68</v>
@@ -29973,10 +29973,10 @@
         <v>10</v>
       </c>
       <c r="G141" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H141" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -29988,28 +29988,28 @@
         <v>0</v>
       </c>
       <c r="L141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M141">
         <v>0</v>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O141" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="P141" t="s">
         <v>100</v>
       </c>
       <c r="Q141">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="R141">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S141">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="T141">
         <v>1.57</v>
@@ -30018,145 +30018,145 @@
         <v>2.25</v>
       </c>
       <c r="V141">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="W141">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X141">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y141">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z141">
+        <v>1.75</v>
+      </c>
+      <c r="AA141">
+        <v>3.5</v>
+      </c>
+      <c r="AB141">
+        <v>5</v>
+      </c>
+      <c r="AC141">
+        <v>1.11</v>
+      </c>
+      <c r="AD141">
+        <v>6.25</v>
+      </c>
+      <c r="AE141">
+        <v>1.53</v>
+      </c>
+      <c r="AF141">
+        <v>2.3</v>
+      </c>
+      <c r="AG141">
+        <v>2.6</v>
+      </c>
+      <c r="AH141">
+        <v>1.48</v>
+      </c>
+      <c r="AI141">
+        <v>2.5</v>
+      </c>
+      <c r="AJ141">
+        <v>1.5</v>
+      </c>
+      <c r="AK141">
+        <v>1.17</v>
+      </c>
+      <c r="AL141">
+        <v>1.34</v>
+      </c>
+      <c r="AM141">
+        <v>1.93</v>
+      </c>
+      <c r="AN141">
+        <v>2.5</v>
+      </c>
+      <c r="AO141">
+        <v>1.75</v>
+      </c>
+      <c r="AP141">
+        <v>2.6</v>
+      </c>
+      <c r="AQ141">
+        <v>1.4</v>
+      </c>
+      <c r="AR141">
+        <v>1.7</v>
+      </c>
+      <c r="AS141">
+        <v>1.26</v>
+      </c>
+      <c r="AT141">
+        <v>2.96</v>
+      </c>
+      <c r="AU141">
+        <v>6</v>
+      </c>
+      <c r="AV141">
+        <v>2</v>
+      </c>
+      <c r="AW141">
+        <v>2</v>
+      </c>
+      <c r="AX141">
         <v>4</v>
       </c>
-      <c r="AA141">
-        <v>3.3</v>
-      </c>
-      <c r="AB141">
-        <v>2</v>
-      </c>
-      <c r="AC141">
-        <v>1.1</v>
-      </c>
-      <c r="AD141">
-        <v>6.5</v>
-      </c>
-      <c r="AE141">
+      <c r="AY141">
+        <v>8</v>
+      </c>
+      <c r="AZ141">
+        <v>7</v>
+      </c>
+      <c r="BA141">
+        <v>1</v>
+      </c>
+      <c r="BB141">
+        <v>4</v>
+      </c>
+      <c r="BC141">
+        <v>5</v>
+      </c>
+      <c r="BD141">
         <v>1.5</v>
-      </c>
-      <c r="AF141">
-        <v>2.55</v>
-      </c>
-      <c r="AG141">
-        <v>2.5</v>
-      </c>
-      <c r="AH141">
-        <v>1.5</v>
-      </c>
-      <c r="AI141">
-        <v>2.2</v>
-      </c>
-      <c r="AJ141">
-        <v>1.62</v>
-      </c>
-      <c r="AK141">
-        <v>1.51</v>
-      </c>
-      <c r="AL141">
-        <v>1.35</v>
-      </c>
-      <c r="AM141">
-        <v>1.38</v>
-      </c>
-      <c r="AN141">
-        <v>1.5</v>
-      </c>
-      <c r="AO141">
-        <v>1.33</v>
-      </c>
-      <c r="AP141">
-        <v>1.4</v>
-      </c>
-      <c r="AQ141">
-        <v>1.2</v>
-      </c>
-      <c r="AR141">
-        <v>1.98</v>
-      </c>
-      <c r="AS141">
-        <v>2.04</v>
-      </c>
-      <c r="AT141">
-        <v>4.02</v>
-      </c>
-      <c r="AU141">
-        <v>3</v>
-      </c>
-      <c r="AV141">
-        <v>8</v>
-      </c>
-      <c r="AW141">
-        <v>6</v>
-      </c>
-      <c r="AX141">
-        <v>8</v>
-      </c>
-      <c r="AY141">
-        <v>10</v>
-      </c>
-      <c r="AZ141">
-        <v>18</v>
-      </c>
-      <c r="BA141">
-        <v>2</v>
-      </c>
-      <c r="BB141">
-        <v>7</v>
-      </c>
-      <c r="BC141">
-        <v>9</v>
-      </c>
-      <c r="BD141">
-        <v>2.23</v>
       </c>
       <c r="BE141">
         <v>6.4</v>
       </c>
       <c r="BF141">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="BG141">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="BH141">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="BI141">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="BJ141">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BK141">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="BL141">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BM141">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="BN141">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="BO141">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP141">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="142" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="252">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -592,6 +592,12 @@
     <t>['69', '79']</t>
   </si>
   <si>
+    <t>['52']</t>
+  </si>
+  <si>
+    <t>['8', '77']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -761,6 +767,9 @@
   </si>
   <si>
     <t>['83']</t>
+  </si>
+  <si>
+    <t>['58', '79']</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP154"/>
+  <dimension ref="A1:BP158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1378,7 +1387,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1790,7 +1799,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2074,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ5">
         <v>0.6</v>
@@ -2202,7 +2211,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2283,7 +2292,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ6">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2408,7 +2417,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2901,7 +2910,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ9">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3026,7 +3035,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3107,7 +3116,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ10">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3928,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ14">
         <v>1.4</v>
@@ -4880,7 +4889,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5498,7 +5507,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5576,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ22">
         <v>1.4</v>
@@ -5704,7 +5713,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5910,7 +5919,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6322,7 +6331,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6734,7 +6743,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7227,7 +7236,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ30">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7433,7 +7442,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ31">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR31">
         <v>1.4</v>
@@ -8382,7 +8391,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8463,7 +8472,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ36">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR36">
         <v>1</v>
@@ -9206,7 +9215,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9284,7 +9293,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -10030,7 +10039,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10236,7 +10245,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10317,7 +10326,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ45">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR45">
         <v>0</v>
@@ -10442,7 +10451,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10648,7 +10657,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10854,7 +10863,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11347,7 +11356,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ50">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR50">
         <v>2.5</v>
@@ -11472,7 +11481,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11962,7 +11971,7 @@
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ53">
         <v>1.6</v>
@@ -12090,7 +12099,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12171,7 +12180,7 @@
         <v>3</v>
       </c>
       <c r="AQ54">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR54">
         <v>1.05</v>
@@ -12786,7 +12795,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ57">
         <v>0.17</v>
@@ -12914,7 +12923,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13532,7 +13541,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14768,7 +14777,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14974,7 +14983,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15055,7 +15064,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ68">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR68">
         <v>1.54</v>
@@ -16004,7 +16013,7 @@
         <v>100</v>
       </c>
       <c r="P73" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q73">
         <v>4.5</v>
@@ -16622,7 +16631,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16828,7 +16837,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16906,7 +16915,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ77">
         <v>1.4</v>
@@ -17034,7 +17043,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17446,7 +17455,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17527,7 +17536,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ80">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR80">
         <v>1.76</v>
@@ -17652,7 +17661,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17858,7 +17867,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18270,7 +18279,7 @@
         <v>153</v>
       </c>
       <c r="P84" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q84">
         <v>2.75</v>
@@ -18351,7 +18360,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ84">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR84">
         <v>2.29</v>
@@ -18682,7 +18691,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -18763,7 +18772,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ86">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR86">
         <v>1.79</v>
@@ -19094,7 +19103,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19172,7 +19181,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ88">
         <v>1.6</v>
@@ -19300,7 +19309,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19378,7 +19387,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ89">
         <v>1.6</v>
@@ -19506,7 +19515,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19918,7 +19927,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20742,7 +20751,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20948,7 +20957,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21772,7 +21781,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -22883,7 +22892,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ106">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR106">
         <v>2.07</v>
@@ -23214,7 +23223,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23420,7 +23429,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23626,7 +23635,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -23707,7 +23716,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ110">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR110">
         <v>2.19</v>
@@ -24038,7 +24047,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24450,7 +24459,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24528,10 +24537,10 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ114">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR114">
         <v>1.64</v>
@@ -24656,7 +24665,7 @@
         <v>154</v>
       </c>
       <c r="P115" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24862,7 +24871,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25068,7 +25077,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25480,7 +25489,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25558,7 +25567,7 @@
         <v>1.75</v>
       </c>
       <c r="AP119">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ119">
         <v>1.67</v>
@@ -25686,7 +25695,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -25970,7 +25979,7 @@
         <v>0.67</v>
       </c>
       <c r="AP121">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ121">
         <v>0.5</v>
@@ -26098,7 +26107,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26304,7 +26313,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26591,7 +26600,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ124">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR124">
         <v>1.45</v>
@@ -26794,7 +26803,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27206,7 +27215,7 @@
         <v>1.5</v>
       </c>
       <c r="AP127">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ127">
         <v>1</v>
@@ -27334,7 +27343,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -27415,7 +27424,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ128">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR128">
         <v>2.27</v>
@@ -27621,7 +27630,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ129">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR129">
         <v>1.71</v>
@@ -28158,7 +28167,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28239,7 +28248,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ132">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR132">
         <v>1.22</v>
@@ -28776,7 +28785,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -29600,7 +29609,7 @@
         <v>182</v>
       </c>
       <c r="P139" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -30836,7 +30845,7 @@
         <v>186</v>
       </c>
       <c r="P145" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31042,7 +31051,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31248,7 +31257,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31454,7 +31463,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31660,7 +31669,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -31866,7 +31875,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32484,7 +32493,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32847,6 +32856,830 @@
       </c>
       <c r="BP154">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7820467</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45744.70833333334</v>
+      </c>
+      <c r="F155">
+        <v>11</v>
+      </c>
+      <c r="G155" t="s">
+        <v>73</v>
+      </c>
+      <c r="H155" t="s">
+        <v>71</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>1</v>
+      </c>
+      <c r="M155">
+        <v>2</v>
+      </c>
+      <c r="N155">
+        <v>3</v>
+      </c>
+      <c r="O155" t="s">
+        <v>192</v>
+      </c>
+      <c r="P155" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q155">
+        <v>3.1</v>
+      </c>
+      <c r="R155">
+        <v>1.95</v>
+      </c>
+      <c r="S155">
+        <v>4.33</v>
+      </c>
+      <c r="T155">
+        <v>1.57</v>
+      </c>
+      <c r="U155">
+        <v>2.25</v>
+      </c>
+      <c r="V155">
+        <v>3.75</v>
+      </c>
+      <c r="W155">
+        <v>1.25</v>
+      </c>
+      <c r="X155">
+        <v>11</v>
+      </c>
+      <c r="Y155">
+        <v>1.05</v>
+      </c>
+      <c r="Z155">
+        <v>2.25</v>
+      </c>
+      <c r="AA155">
+        <v>3</v>
+      </c>
+      <c r="AB155">
+        <v>3.6</v>
+      </c>
+      <c r="AC155">
+        <v>1.09</v>
+      </c>
+      <c r="AD155">
+        <v>6</v>
+      </c>
+      <c r="AE155">
+        <v>1.48</v>
+      </c>
+      <c r="AF155">
+        <v>2.5</v>
+      </c>
+      <c r="AG155">
+        <v>2.5</v>
+      </c>
+      <c r="AH155">
+        <v>1.5</v>
+      </c>
+      <c r="AI155">
+        <v>2.05</v>
+      </c>
+      <c r="AJ155">
+        <v>1.7</v>
+      </c>
+      <c r="AK155">
+        <v>1.29</v>
+      </c>
+      <c r="AL155">
+        <v>1.36</v>
+      </c>
+      <c r="AM155">
+        <v>1.62</v>
+      </c>
+      <c r="AN155">
+        <v>1.75</v>
+      </c>
+      <c r="AO155">
+        <v>1.8</v>
+      </c>
+      <c r="AP155">
+        <v>1.4</v>
+      </c>
+      <c r="AQ155">
+        <v>2</v>
+      </c>
+      <c r="AR155">
+        <v>1.88</v>
+      </c>
+      <c r="AS155">
+        <v>1.49</v>
+      </c>
+      <c r="AT155">
+        <v>3.37</v>
+      </c>
+      <c r="AU155">
+        <v>4</v>
+      </c>
+      <c r="AV155">
+        <v>6</v>
+      </c>
+      <c r="AW155">
+        <v>4</v>
+      </c>
+      <c r="AX155">
+        <v>7</v>
+      </c>
+      <c r="AY155">
+        <v>8</v>
+      </c>
+      <c r="AZ155">
+        <v>15</v>
+      </c>
+      <c r="BA155">
+        <v>0</v>
+      </c>
+      <c r="BB155">
+        <v>7</v>
+      </c>
+      <c r="BC155">
+        <v>7</v>
+      </c>
+      <c r="BD155">
+        <v>1.67</v>
+      </c>
+      <c r="BE155">
+        <v>6.55</v>
+      </c>
+      <c r="BF155">
+        <v>2.94</v>
+      </c>
+      <c r="BG155">
+        <v>1.38</v>
+      </c>
+      <c r="BH155">
+        <v>2.71</v>
+      </c>
+      <c r="BI155">
+        <v>1.73</v>
+      </c>
+      <c r="BJ155">
+        <v>2</v>
+      </c>
+      <c r="BK155">
+        <v>2.15</v>
+      </c>
+      <c r="BL155">
+        <v>1.59</v>
+      </c>
+      <c r="BM155">
+        <v>2.88</v>
+      </c>
+      <c r="BN155">
+        <v>1.32</v>
+      </c>
+      <c r="BO155">
+        <v>4.1</v>
+      </c>
+      <c r="BP155">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7820470</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45744.80208333334</v>
+      </c>
+      <c r="F156">
+        <v>11</v>
+      </c>
+      <c r="G156" t="s">
+        <v>85</v>
+      </c>
+      <c r="H156" t="s">
+        <v>93</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156" t="s">
+        <v>100</v>
+      </c>
+      <c r="P156" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q156">
+        <v>4</v>
+      </c>
+      <c r="R156">
+        <v>1.8</v>
+      </c>
+      <c r="S156">
+        <v>3.5</v>
+      </c>
+      <c r="T156">
+        <v>1.67</v>
+      </c>
+      <c r="U156">
+        <v>2.1</v>
+      </c>
+      <c r="V156">
+        <v>4.33</v>
+      </c>
+      <c r="W156">
+        <v>1.2</v>
+      </c>
+      <c r="X156">
+        <v>15</v>
+      </c>
+      <c r="Y156">
+        <v>1.03</v>
+      </c>
+      <c r="Z156">
+        <v>3.1</v>
+      </c>
+      <c r="AA156">
+        <v>2.9</v>
+      </c>
+      <c r="AB156">
+        <v>2.55</v>
+      </c>
+      <c r="AC156">
+        <v>1.12</v>
+      </c>
+      <c r="AD156">
+        <v>5.25</v>
+      </c>
+      <c r="AE156">
+        <v>1.52</v>
+      </c>
+      <c r="AF156">
+        <v>2.45</v>
+      </c>
+      <c r="AG156">
+        <v>3.1</v>
+      </c>
+      <c r="AH156">
+        <v>1.36</v>
+      </c>
+      <c r="AI156">
+        <v>2.38</v>
+      </c>
+      <c r="AJ156">
+        <v>1.53</v>
+      </c>
+      <c r="AK156">
+        <v>1.49</v>
+      </c>
+      <c r="AL156">
+        <v>1.4</v>
+      </c>
+      <c r="AM156">
+        <v>1.35</v>
+      </c>
+      <c r="AN156">
+        <v>1</v>
+      </c>
+      <c r="AO156">
+        <v>1.6</v>
+      </c>
+      <c r="AP156">
+        <v>1</v>
+      </c>
+      <c r="AQ156">
+        <v>1.5</v>
+      </c>
+      <c r="AR156">
+        <v>1.34</v>
+      </c>
+      <c r="AS156">
+        <v>1.34</v>
+      </c>
+      <c r="AT156">
+        <v>2.68</v>
+      </c>
+      <c r="AU156">
+        <v>3</v>
+      </c>
+      <c r="AV156">
+        <v>3</v>
+      </c>
+      <c r="AW156">
+        <v>7</v>
+      </c>
+      <c r="AX156">
+        <v>2</v>
+      </c>
+      <c r="AY156">
+        <v>15</v>
+      </c>
+      <c r="AZ156">
+        <v>5</v>
+      </c>
+      <c r="BA156">
+        <v>3</v>
+      </c>
+      <c r="BB156">
+        <v>4</v>
+      </c>
+      <c r="BC156">
+        <v>7</v>
+      </c>
+      <c r="BD156">
+        <v>1.84</v>
+      </c>
+      <c r="BE156">
+        <v>6.4</v>
+      </c>
+      <c r="BF156">
+        <v>2.18</v>
+      </c>
+      <c r="BG156">
+        <v>1.55</v>
+      </c>
+      <c r="BH156">
+        <v>2.28</v>
+      </c>
+      <c r="BI156">
+        <v>1.85</v>
+      </c>
+      <c r="BJ156">
+        <v>1.85</v>
+      </c>
+      <c r="BK156">
+        <v>2.43</v>
+      </c>
+      <c r="BL156">
+        <v>1.47</v>
+      </c>
+      <c r="BM156">
+        <v>3.2</v>
+      </c>
+      <c r="BN156">
+        <v>1.29</v>
+      </c>
+      <c r="BO156">
+        <v>4.35</v>
+      </c>
+      <c r="BP156">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7820474</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45744.89583333334</v>
+      </c>
+      <c r="F157">
+        <v>11</v>
+      </c>
+      <c r="G157" t="s">
+        <v>90</v>
+      </c>
+      <c r="H157" t="s">
+        <v>86</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>1</v>
+      </c>
+      <c r="N157">
+        <v>1</v>
+      </c>
+      <c r="O157" t="s">
+        <v>100</v>
+      </c>
+      <c r="P157" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q157">
+        <v>2.75</v>
+      </c>
+      <c r="R157">
+        <v>1.83</v>
+      </c>
+      <c r="S157">
+        <v>5.5</v>
+      </c>
+      <c r="T157">
+        <v>1.67</v>
+      </c>
+      <c r="U157">
+        <v>2.1</v>
+      </c>
+      <c r="V157">
+        <v>4.33</v>
+      </c>
+      <c r="W157">
+        <v>1.2</v>
+      </c>
+      <c r="X157">
+        <v>15</v>
+      </c>
+      <c r="Y157">
+        <v>1.03</v>
+      </c>
+      <c r="Z157">
+        <v>1.91</v>
+      </c>
+      <c r="AA157">
+        <v>3.1</v>
+      </c>
+      <c r="AB157">
+        <v>4.5</v>
+      </c>
+      <c r="AC157">
+        <v>1.11</v>
+      </c>
+      <c r="AD157">
+        <v>5.5</v>
+      </c>
+      <c r="AE157">
+        <v>1.6</v>
+      </c>
+      <c r="AF157">
+        <v>2.15</v>
+      </c>
+      <c r="AG157">
+        <v>2.88</v>
+      </c>
+      <c r="AH157">
+        <v>1.4</v>
+      </c>
+      <c r="AI157">
+        <v>2.5</v>
+      </c>
+      <c r="AJ157">
+        <v>1.5</v>
+      </c>
+      <c r="AK157">
+        <v>1.18</v>
+      </c>
+      <c r="AL157">
+        <v>1.38</v>
+      </c>
+      <c r="AM157">
+        <v>1.82</v>
+      </c>
+      <c r="AN157">
+        <v>0.8</v>
+      </c>
+      <c r="AO157">
+        <v>1.6</v>
+      </c>
+      <c r="AP157">
+        <v>0.67</v>
+      </c>
+      <c r="AQ157">
+        <v>1.83</v>
+      </c>
+      <c r="AR157">
+        <v>1.5</v>
+      </c>
+      <c r="AS157">
+        <v>1.02</v>
+      </c>
+      <c r="AT157">
+        <v>2.52</v>
+      </c>
+      <c r="AU157">
+        <v>2</v>
+      </c>
+      <c r="AV157">
+        <v>4</v>
+      </c>
+      <c r="AW157">
+        <v>3</v>
+      </c>
+      <c r="AX157">
+        <v>3</v>
+      </c>
+      <c r="AY157">
+        <v>5</v>
+      </c>
+      <c r="AZ157">
+        <v>7</v>
+      </c>
+      <c r="BA157">
+        <v>4</v>
+      </c>
+      <c r="BB157">
+        <v>1</v>
+      </c>
+      <c r="BC157">
+        <v>5</v>
+      </c>
+      <c r="BD157">
+        <v>1.43</v>
+      </c>
+      <c r="BE157">
+        <v>7</v>
+      </c>
+      <c r="BF157">
+        <v>3.15</v>
+      </c>
+      <c r="BG157">
+        <v>1.35</v>
+      </c>
+      <c r="BH157">
+        <v>2.88</v>
+      </c>
+      <c r="BI157">
+        <v>1.7</v>
+      </c>
+      <c r="BJ157">
+        <v>2.05</v>
+      </c>
+      <c r="BK157">
+        <v>2.05</v>
+      </c>
+      <c r="BL157">
+        <v>1.7</v>
+      </c>
+      <c r="BM157">
+        <v>2.48</v>
+      </c>
+      <c r="BN157">
+        <v>1.47</v>
+      </c>
+      <c r="BO157">
+        <v>3.2</v>
+      </c>
+      <c r="BP157">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7820475</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45744.89583333334</v>
+      </c>
+      <c r="F158">
+        <v>11</v>
+      </c>
+      <c r="G158" t="s">
+        <v>82</v>
+      </c>
+      <c r="H158" t="s">
+        <v>99</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>2</v>
+      </c>
+      <c r="L158">
+        <v>2</v>
+      </c>
+      <c r="M158">
+        <v>1</v>
+      </c>
+      <c r="N158">
+        <v>3</v>
+      </c>
+      <c r="O158" t="s">
+        <v>193</v>
+      </c>
+      <c r="P158" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q158">
+        <v>3</v>
+      </c>
+      <c r="R158">
+        <v>1.8</v>
+      </c>
+      <c r="S158">
+        <v>5</v>
+      </c>
+      <c r="T158">
+        <v>1.67</v>
+      </c>
+      <c r="U158">
+        <v>2.1</v>
+      </c>
+      <c r="V158">
+        <v>4.5</v>
+      </c>
+      <c r="W158">
+        <v>1.18</v>
+      </c>
+      <c r="X158">
+        <v>15</v>
+      </c>
+      <c r="Y158">
+        <v>1.03</v>
+      </c>
+      <c r="Z158">
+        <v>2.1</v>
+      </c>
+      <c r="AA158">
+        <v>3</v>
+      </c>
+      <c r="AB158">
+        <v>3.9</v>
+      </c>
+      <c r="AC158">
+        <v>1.12</v>
+      </c>
+      <c r="AD158">
+        <v>5.25</v>
+      </c>
+      <c r="AE158">
+        <v>1.65</v>
+      </c>
+      <c r="AF158">
+        <v>2.1</v>
+      </c>
+      <c r="AG158">
+        <v>3.1</v>
+      </c>
+      <c r="AH158">
+        <v>1.36</v>
+      </c>
+      <c r="AI158">
+        <v>2.5</v>
+      </c>
+      <c r="AJ158">
+        <v>1.5</v>
+      </c>
+      <c r="AK158">
+        <v>1.23</v>
+      </c>
+      <c r="AL158">
+        <v>1.39</v>
+      </c>
+      <c r="AM158">
+        <v>1.7</v>
+      </c>
+      <c r="AN158">
+        <v>1.2</v>
+      </c>
+      <c r="AO158">
+        <v>0.8</v>
+      </c>
+      <c r="AP158">
+        <v>1.5</v>
+      </c>
+      <c r="AQ158">
+        <v>0.67</v>
+      </c>
+      <c r="AR158">
+        <v>1.13</v>
+      </c>
+      <c r="AS158">
+        <v>1.37</v>
+      </c>
+      <c r="AT158">
+        <v>2.5</v>
+      </c>
+      <c r="AU158">
+        <v>7</v>
+      </c>
+      <c r="AV158">
+        <v>3</v>
+      </c>
+      <c r="AW158">
+        <v>5</v>
+      </c>
+      <c r="AX158">
+        <v>5</v>
+      </c>
+      <c r="AY158">
+        <v>14</v>
+      </c>
+      <c r="AZ158">
+        <v>9</v>
+      </c>
+      <c r="BA158">
+        <v>3</v>
+      </c>
+      <c r="BB158">
+        <v>3</v>
+      </c>
+      <c r="BC158">
+        <v>6</v>
+      </c>
+      <c r="BD158">
+        <v>1.58</v>
+      </c>
+      <c r="BE158">
+        <v>6.75</v>
+      </c>
+      <c r="BF158">
+        <v>2.6</v>
+      </c>
+      <c r="BG158">
+        <v>1.43</v>
+      </c>
+      <c r="BH158">
+        <v>2.55</v>
+      </c>
+      <c r="BI158">
+        <v>1.7</v>
+      </c>
+      <c r="BJ158">
+        <v>2.05</v>
+      </c>
+      <c r="BK158">
+        <v>2.1</v>
+      </c>
+      <c r="BL158">
+        <v>1.67</v>
+      </c>
+      <c r="BM158">
+        <v>2.8</v>
+      </c>
+      <c r="BN158">
+        <v>1.36</v>
+      </c>
+      <c r="BO158">
+        <v>3.7</v>
+      </c>
+      <c r="BP158">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="257">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -598,6 +598,15 @@
     <t>['8', '77']</t>
   </si>
   <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['2', '18', '25', '35']</t>
+  </si>
+  <si>
+    <t>['18', '61']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -665,9 +674,6 @@
   </si>
   <si>
     <t>['64']</t>
-  </si>
-  <si>
-    <t>['86']</t>
   </si>
   <si>
     <t>['12', '81']</t>
@@ -770,6 +776,15 @@
   </si>
   <si>
     <t>['58', '79']</t>
+  </si>
+  <si>
+    <t>['82']</t>
+  </si>
+  <si>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['8', '85']</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP158"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1387,7 +1402,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1468,7 +1483,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ2">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1799,7 +1814,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2211,7 +2226,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2417,7 +2432,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2701,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ8">
         <v>0.2</v>
@@ -3035,7 +3050,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3319,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ11">
         <v>1.2</v>
@@ -3731,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>0.67</v>
@@ -4146,7 +4161,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ15">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4349,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>0.6</v>
@@ -4764,7 +4779,7 @@
         <v>1</v>
       </c>
       <c r="AQ18">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4889,7 +4904,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5176,7 +5191,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ20">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5507,7 +5522,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5713,7 +5728,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5919,7 +5934,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6331,7 +6346,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6615,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ27">
         <v>0.17</v>
@@ -6743,7 +6758,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7439,7 +7454,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>0.67</v>
@@ -7854,7 +7869,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ33">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR33">
         <v>1.45</v>
@@ -8263,7 +8278,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ35">
         <v>1.4</v>
@@ -8391,7 +8406,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8881,7 +8896,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
         <v>0.8</v>
@@ -9087,7 +9102,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ39">
         <v>0.67</v>
@@ -9215,7 +9230,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -10039,7 +10054,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10245,7 +10260,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10451,7 +10466,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10657,7 +10672,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10738,7 +10753,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ47">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR47">
         <v>1.66</v>
@@ -10863,7 +10878,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11147,7 +11162,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ49">
         <v>0.8</v>
@@ -11481,7 +11496,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11768,7 +11783,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ52">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR52">
         <v>1.64</v>
@@ -12099,7 +12114,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12383,7 +12398,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ55">
         <v>1.6</v>
@@ -12923,7 +12938,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13210,7 +13225,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ59">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR59">
         <v>1.06</v>
@@ -13541,7 +13556,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14652,7 +14667,7 @@
         <v>1</v>
       </c>
       <c r="AQ66">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR66">
         <v>1.2</v>
@@ -14777,7 +14792,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14983,7 +14998,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15267,7 +15282,7 @@
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ69">
         <v>0.8</v>
@@ -15885,7 +15900,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ72">
         <v>1.4</v>
@@ -16013,7 +16028,7 @@
         <v>100</v>
       </c>
       <c r="P73" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q73">
         <v>4.5</v>
@@ -16631,7 +16646,7 @@
         <v>100</v>
       </c>
       <c r="P76" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16837,7 +16852,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17043,7 +17058,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17327,7 +17342,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>0.4</v>
@@ -17455,7 +17470,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17661,7 +17676,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17742,7 +17757,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR81">
         <v>1.47</v>
@@ -17867,7 +17882,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -17948,7 +17963,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ82">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR82">
         <v>1.71</v>
@@ -18151,7 +18166,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18279,7 +18294,7 @@
         <v>153</v>
       </c>
       <c r="P84" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q84">
         <v>2.75</v>
@@ -18691,7 +18706,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -18978,7 +18993,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ87">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR87">
         <v>1.31</v>
@@ -19103,7 +19118,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19309,7 +19324,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19390,7 +19405,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ89">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -19515,7 +19530,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19593,7 +19608,7 @@
         <v>2</v>
       </c>
       <c r="AP90">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>1.6</v>
@@ -19927,7 +19942,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20623,7 +20638,7 @@
         <v>0.33</v>
       </c>
       <c r="AP95">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ95">
         <v>0.17</v>
@@ -20751,7 +20766,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20957,7 +20972,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21781,7 +21796,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -22686,7 +22701,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ105">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR105">
         <v>1.4</v>
@@ -22889,7 +22904,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>1.83</v>
@@ -23223,7 +23238,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23429,7 +23444,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23507,7 +23522,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23635,7 +23650,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -24047,7 +24062,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24459,7 +24474,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24665,7 +24680,7 @@
         <v>154</v>
       </c>
       <c r="P115" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24746,7 +24761,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ115">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
         <v>1.19</v>
@@ -24871,7 +24886,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -24949,7 +24964,7 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ116">
         <v>1</v>
@@ -25077,7 +25092,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25489,7 +25504,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25695,7 +25710,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -25776,7 +25791,7 @@
         <v>1</v>
       </c>
       <c r="AQ120">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR120">
         <v>1.31</v>
@@ -25982,7 +25997,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ121">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR121">
         <v>1.33</v>
@@ -26107,7 +26122,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26185,7 +26200,7 @@
         <v>1.33</v>
       </c>
       <c r="AP122">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ122">
         <v>1.75</v>
@@ -26313,7 +26328,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26391,7 +26406,7 @@
         <v>1.25</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ123">
         <v>1.6</v>
@@ -27343,7 +27358,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -27627,7 +27642,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ129">
         <v>0.67</v>
@@ -27833,10 +27848,10 @@
         <v>1.75</v>
       </c>
       <c r="AP130">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ130">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR130">
         <v>1.36</v>
@@ -28167,7 +28182,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28660,7 +28675,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ134">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR134">
         <v>2.28</v>
@@ -28785,7 +28800,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -29609,7 +29624,7 @@
         <v>182</v>
       </c>
       <c r="P139" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -30305,7 +30320,7 @@
         <v>0.75</v>
       </c>
       <c r="AP142">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ142">
         <v>1</v>
@@ -30845,7 +30860,7 @@
         <v>186</v>
       </c>
       <c r="P145" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31051,7 +31066,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31257,7 +31272,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31463,7 +31478,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31669,7 +31684,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -31875,7 +31890,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32493,7 +32508,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32905,7 +32920,7 @@
         <v>192</v>
       </c>
       <c r="P155" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33069,7 +33084,7 @@
         <v>155</v>
       </c>
       <c r="B156">
-        <v>7820470</v>
+        <v>7820477</v>
       </c>
       <c r="C156" t="s">
         <v>68</v>
@@ -33084,10 +33099,10 @@
         <v>11</v>
       </c>
       <c r="G156" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H156" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -33099,175 +33114,175 @@
         <v>0</v>
       </c>
       <c r="L156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O156" t="s">
-        <v>100</v>
+        <v>177</v>
       </c>
       <c r="P156" t="s">
-        <v>100</v>
+        <v>254</v>
       </c>
       <c r="Q156">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R156">
         <v>1.8</v>
       </c>
       <c r="S156">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T156">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="U156">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V156">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="W156">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X156">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y156">
         <v>1.03</v>
       </c>
       <c r="Z156">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA156">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AB156">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="AC156">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AD156">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AE156">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AF156">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AG156">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AH156">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI156">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AJ156">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AK156">
+        <v>1.34</v>
+      </c>
+      <c r="AL156">
+        <v>1.41</v>
+      </c>
+      <c r="AM156">
         <v>1.49</v>
       </c>
-      <c r="AL156">
-        <v>1.4</v>
-      </c>
-      <c r="AM156">
-        <v>1.35</v>
-      </c>
       <c r="AN156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO156">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AP156">
-        <v>1</v>
+        <v>1.83</v>
       </c>
       <c r="AQ156">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR156">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="AS156">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AT156">
-        <v>2.68</v>
+        <v>3.04</v>
       </c>
       <c r="AU156">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV156">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW156">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX156">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AY156">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ156">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BA156">
         <v>3</v>
       </c>
       <c r="BB156">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC156">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD156">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="BE156">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF156">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="BG156">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="BH156">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="BI156">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="BJ156">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="BK156">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="BL156">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="BM156">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="BN156">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BO156">
-        <v>4.35</v>
+        <v>3.55</v>
       </c>
       <c r="BP156">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="157" spans="1:68">
@@ -33275,7 +33290,7 @@
         <v>156</v>
       </c>
       <c r="B157">
-        <v>7820474</v>
+        <v>7820470</v>
       </c>
       <c r="C157" t="s">
         <v>68</v>
@@ -33284,49 +33299,49 @@
         <v>69</v>
       </c>
       <c r="E157" s="2">
-        <v>45744.89583333334</v>
+        <v>45744.80208333334</v>
       </c>
       <c r="F157">
         <v>11</v>
       </c>
       <c r="G157" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H157" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I157">
         <v>0</v>
       </c>
       <c r="J157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157">
         <v>0</v>
       </c>
       <c r="M157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O157" t="s">
         <v>100</v>
       </c>
       <c r="P157" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="Q157">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="R157">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S157">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="T157">
         <v>1.67</v>
@@ -33347,133 +33362,133 @@
         <v>1.03</v>
       </c>
       <c r="Z157">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="AA157">
+        <v>2.9</v>
+      </c>
+      <c r="AB157">
+        <v>2.55</v>
+      </c>
+      <c r="AC157">
+        <v>1.12</v>
+      </c>
+      <c r="AD157">
+        <v>5.25</v>
+      </c>
+      <c r="AE157">
+        <v>1.52</v>
+      </c>
+      <c r="AF157">
+        <v>2.45</v>
+      </c>
+      <c r="AG157">
         <v>3.1</v>
       </c>
-      <c r="AB157">
-        <v>4.5</v>
-      </c>
-      <c r="AC157">
-        <v>1.11</v>
-      </c>
-      <c r="AD157">
-        <v>5.5</v>
-      </c>
-      <c r="AE157">
-        <v>1.6</v>
-      </c>
-      <c r="AF157">
-        <v>2.15</v>
-      </c>
-      <c r="AG157">
-        <v>2.88</v>
-      </c>
       <c r="AH157">
+        <v>1.36</v>
+      </c>
+      <c r="AI157">
+        <v>2.38</v>
+      </c>
+      <c r="AJ157">
+        <v>1.53</v>
+      </c>
+      <c r="AK157">
+        <v>1.49</v>
+      </c>
+      <c r="AL157">
         <v>1.4</v>
       </c>
-      <c r="AI157">
-        <v>2.5</v>
-      </c>
-      <c r="AJ157">
-        <v>1.5</v>
-      </c>
-      <c r="AK157">
-        <v>1.18</v>
-      </c>
-      <c r="AL157">
-        <v>1.38</v>
-      </c>
       <c r="AM157">
-        <v>1.82</v>
+        <v>1.35</v>
       </c>
       <c r="AN157">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO157">
         <v>1.6</v>
       </c>
       <c r="AP157">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ157">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AR157">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AS157">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="AT157">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="AU157">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV157">
+        <v>3</v>
+      </c>
+      <c r="AW157">
+        <v>7</v>
+      </c>
+      <c r="AX157">
+        <v>2</v>
+      </c>
+      <c r="AY157">
+        <v>15</v>
+      </c>
+      <c r="AZ157">
+        <v>5</v>
+      </c>
+      <c r="BA157">
+        <v>3</v>
+      </c>
+      <c r="BB157">
         <v>4</v>
       </c>
-      <c r="AW157">
-        <v>3</v>
-      </c>
-      <c r="AX157">
-        <v>3</v>
-      </c>
-      <c r="AY157">
-        <v>5</v>
-      </c>
-      <c r="AZ157">
+      <c r="BC157">
         <v>7</v>
       </c>
-      <c r="BA157">
-        <v>4</v>
-      </c>
-      <c r="BB157">
-        <v>1</v>
-      </c>
-      <c r="BC157">
-        <v>5</v>
-      </c>
       <c r="BD157">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="BE157">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BF157">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="BG157">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="BH157">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="BI157">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="BJ157">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="BK157">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="BL157">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="BM157">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="BN157">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="BO157">
-        <v>3.2</v>
+        <v>4.35</v>
       </c>
       <c r="BP157">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="158" spans="1:68">
@@ -33481,7 +33496,7 @@
         <v>157</v>
       </c>
       <c r="B158">
-        <v>7820475</v>
+        <v>7820474</v>
       </c>
       <c r="C158" t="s">
         <v>68</v>
@@ -33496,43 +33511,43 @@
         <v>11</v>
       </c>
       <c r="G158" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H158" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="I158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158">
         <v>1</v>
       </c>
       <c r="K158">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L158">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M158">
         <v>1</v>
       </c>
       <c r="N158">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O158" t="s">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="P158" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="Q158">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R158">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S158">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T158">
         <v>1.67</v>
@@ -33541,10 +33556,10 @@
         <v>2.1</v>
       </c>
       <c r="V158">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="W158">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X158">
         <v>15</v>
@@ -33553,31 +33568,31 @@
         <v>1.03</v>
       </c>
       <c r="Z158">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AA158">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB158">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AC158">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AD158">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AE158">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF158">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG158">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH158">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI158">
         <v>2.5</v>
@@ -33586,76 +33601,76 @@
         <v>1.5</v>
       </c>
       <c r="AK158">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AL158">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AM158">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AN158">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AO158">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="AP158">
+        <v>0.67</v>
+      </c>
+      <c r="AQ158">
+        <v>1.83</v>
+      </c>
+      <c r="AR158">
         <v>1.5</v>
       </c>
-      <c r="AQ158">
-        <v>0.67</v>
-      </c>
-      <c r="AR158">
-        <v>1.13</v>
-      </c>
       <c r="AS158">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="AT158">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AU158">
+        <v>2</v>
+      </c>
+      <c r="AV158">
+        <v>4</v>
+      </c>
+      <c r="AW158">
+        <v>3</v>
+      </c>
+      <c r="AX158">
+        <v>3</v>
+      </c>
+      <c r="AY158">
+        <v>5</v>
+      </c>
+      <c r="AZ158">
         <v>7</v>
       </c>
-      <c r="AV158">
-        <v>3</v>
-      </c>
-      <c r="AW158">
+      <c r="BA158">
+        <v>4</v>
+      </c>
+      <c r="BB158">
+        <v>1</v>
+      </c>
+      <c r="BC158">
         <v>5</v>
       </c>
-      <c r="AX158">
-        <v>5</v>
-      </c>
-      <c r="AY158">
-        <v>14</v>
-      </c>
-      <c r="AZ158">
-        <v>9</v>
-      </c>
-      <c r="BA158">
-        <v>3</v>
-      </c>
-      <c r="BB158">
-        <v>3</v>
-      </c>
-      <c r="BC158">
-        <v>6</v>
-      </c>
       <c r="BD158">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="BE158">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BF158">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="BG158">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="BH158">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="BI158">
         <v>1.7</v>
@@ -33664,22 +33679,1052 @@
         <v>2.05</v>
       </c>
       <c r="BK158">
+        <v>2.05</v>
+      </c>
+      <c r="BL158">
+        <v>1.7</v>
+      </c>
+      <c r="BM158">
+        <v>2.48</v>
+      </c>
+      <c r="BN158">
+        <v>1.47</v>
+      </c>
+      <c r="BO158">
+        <v>3.2</v>
+      </c>
+      <c r="BP158">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7820475</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45744.89583333334</v>
+      </c>
+      <c r="F159">
+        <v>11</v>
+      </c>
+      <c r="G159" t="s">
+        <v>82</v>
+      </c>
+      <c r="H159" t="s">
+        <v>99</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>2</v>
+      </c>
+      <c r="L159">
+        <v>2</v>
+      </c>
+      <c r="M159">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>3</v>
+      </c>
+      <c r="O159" t="s">
+        <v>193</v>
+      </c>
+      <c r="P159" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q159">
+        <v>3</v>
+      </c>
+      <c r="R159">
+        <v>1.8</v>
+      </c>
+      <c r="S159">
+        <v>5</v>
+      </c>
+      <c r="T159">
+        <v>1.67</v>
+      </c>
+      <c r="U159">
         <v>2.1</v>
       </c>
-      <c r="BL158">
+      <c r="V159">
+        <v>4.5</v>
+      </c>
+      <c r="W159">
+        <v>1.18</v>
+      </c>
+      <c r="X159">
+        <v>15</v>
+      </c>
+      <c r="Y159">
+        <v>1.03</v>
+      </c>
+      <c r="Z159">
+        <v>2.1</v>
+      </c>
+      <c r="AA159">
+        <v>3</v>
+      </c>
+      <c r="AB159">
+        <v>3.9</v>
+      </c>
+      <c r="AC159">
+        <v>1.12</v>
+      </c>
+      <c r="AD159">
+        <v>5.25</v>
+      </c>
+      <c r="AE159">
+        <v>1.65</v>
+      </c>
+      <c r="AF159">
+        <v>2.1</v>
+      </c>
+      <c r="AG159">
+        <v>3.1</v>
+      </c>
+      <c r="AH159">
+        <v>1.36</v>
+      </c>
+      <c r="AI159">
+        <v>2.5</v>
+      </c>
+      <c r="AJ159">
+        <v>1.5</v>
+      </c>
+      <c r="AK159">
+        <v>1.23</v>
+      </c>
+      <c r="AL159">
+        <v>1.39</v>
+      </c>
+      <c r="AM159">
+        <v>1.7</v>
+      </c>
+      <c r="AN159">
+        <v>1.2</v>
+      </c>
+      <c r="AO159">
+        <v>0.8</v>
+      </c>
+      <c r="AP159">
+        <v>1.5</v>
+      </c>
+      <c r="AQ159">
+        <v>0.67</v>
+      </c>
+      <c r="AR159">
+        <v>1.13</v>
+      </c>
+      <c r="AS159">
+        <v>1.37</v>
+      </c>
+      <c r="AT159">
+        <v>2.5</v>
+      </c>
+      <c r="AU159">
+        <v>7</v>
+      </c>
+      <c r="AV159">
+        <v>3</v>
+      </c>
+      <c r="AW159">
+        <v>5</v>
+      </c>
+      <c r="AX159">
+        <v>5</v>
+      </c>
+      <c r="AY159">
+        <v>14</v>
+      </c>
+      <c r="AZ159">
+        <v>9</v>
+      </c>
+      <c r="BA159">
+        <v>3</v>
+      </c>
+      <c r="BB159">
+        <v>3</v>
+      </c>
+      <c r="BC159">
+        <v>6</v>
+      </c>
+      <c r="BD159">
+        <v>1.58</v>
+      </c>
+      <c r="BE159">
+        <v>6.75</v>
+      </c>
+      <c r="BF159">
+        <v>2.6</v>
+      </c>
+      <c r="BG159">
+        <v>1.43</v>
+      </c>
+      <c r="BH159">
+        <v>2.55</v>
+      </c>
+      <c r="BI159">
+        <v>1.7</v>
+      </c>
+      <c r="BJ159">
+        <v>2.05</v>
+      </c>
+      <c r="BK159">
+        <v>2.1</v>
+      </c>
+      <c r="BL159">
         <v>1.67</v>
       </c>
-      <c r="BM158">
+      <c r="BM159">
         <v>2.8</v>
       </c>
-      <c r="BN158">
+      <c r="BN159">
         <v>1.36</v>
       </c>
-      <c r="BO158">
+      <c r="BO159">
         <v>3.7</v>
       </c>
-      <c r="BP158">
+      <c r="BP159">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7820476</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45745.6875</v>
+      </c>
+      <c r="F160">
+        <v>11</v>
+      </c>
+      <c r="G160" t="s">
+        <v>81</v>
+      </c>
+      <c r="H160" t="s">
+        <v>78</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>1</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>1</v>
+      </c>
+      <c r="O160" t="s">
+        <v>194</v>
+      </c>
+      <c r="P160" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q160">
+        <v>2.63</v>
+      </c>
+      <c r="R160">
+        <v>1.83</v>
+      </c>
+      <c r="S160">
+        <v>6</v>
+      </c>
+      <c r="T160">
+        <v>1.67</v>
+      </c>
+      <c r="U160">
+        <v>2.1</v>
+      </c>
+      <c r="V160">
+        <v>4.33</v>
+      </c>
+      <c r="W160">
+        <v>1.2</v>
+      </c>
+      <c r="X160">
+        <v>15</v>
+      </c>
+      <c r="Y160">
+        <v>1.03</v>
+      </c>
+      <c r="Z160">
+        <v>1.8</v>
+      </c>
+      <c r="AA160">
+        <v>3.1</v>
+      </c>
+      <c r="AB160">
+        <v>5.5</v>
+      </c>
+      <c r="AC160">
+        <v>1.12</v>
+      </c>
+      <c r="AD160">
+        <v>5.75</v>
+      </c>
+      <c r="AE160">
+        <v>1.61</v>
+      </c>
+      <c r="AF160">
+        <v>2.15</v>
+      </c>
+      <c r="AG160">
+        <v>3.1</v>
+      </c>
+      <c r="AH160">
+        <v>1.36</v>
+      </c>
+      <c r="AI160">
+        <v>2.63</v>
+      </c>
+      <c r="AJ160">
+        <v>1.44</v>
+      </c>
+      <c r="AK160">
+        <v>1.16</v>
+      </c>
+      <c r="AL160">
+        <v>1.35</v>
+      </c>
+      <c r="AM160">
+        <v>1.93</v>
+      </c>
+      <c r="AN160">
+        <v>1.75</v>
+      </c>
+      <c r="AO160">
+        <v>0.5</v>
+      </c>
+      <c r="AP160">
+        <v>2</v>
+      </c>
+      <c r="AQ160">
+        <v>0.4</v>
+      </c>
+      <c r="AR160">
+        <v>1.59</v>
+      </c>
+      <c r="AS160">
+        <v>1.4</v>
+      </c>
+      <c r="AT160">
+        <v>2.99</v>
+      </c>
+      <c r="AU160">
+        <v>4</v>
+      </c>
+      <c r="AV160">
+        <v>2</v>
+      </c>
+      <c r="AW160">
+        <v>11</v>
+      </c>
+      <c r="AX160">
+        <v>3</v>
+      </c>
+      <c r="AY160">
+        <v>16</v>
+      </c>
+      <c r="AZ160">
+        <v>5</v>
+      </c>
+      <c r="BA160">
+        <v>10</v>
+      </c>
+      <c r="BB160">
+        <v>1</v>
+      </c>
+      <c r="BC160">
+        <v>11</v>
+      </c>
+      <c r="BD160">
+        <v>1.44</v>
+      </c>
+      <c r="BE160">
+        <v>6.75</v>
+      </c>
+      <c r="BF160">
+        <v>3.15</v>
+      </c>
+      <c r="BG160">
+        <v>1.5</v>
+      </c>
+      <c r="BH160">
+        <v>2.38</v>
+      </c>
+      <c r="BI160">
+        <v>1.8</v>
+      </c>
+      <c r="BJ160">
+        <v>1.91</v>
+      </c>
+      <c r="BK160">
+        <v>2.32</v>
+      </c>
+      <c r="BL160">
+        <v>1.52</v>
+      </c>
+      <c r="BM160">
+        <v>3.05</v>
+      </c>
+      <c r="BN160">
+        <v>1.32</v>
+      </c>
+      <c r="BO160">
+        <v>4.1</v>
+      </c>
+      <c r="BP160">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7820468</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45745.77083333334</v>
+      </c>
+      <c r="F161">
+        <v>11</v>
+      </c>
+      <c r="G161" t="s">
+        <v>84</v>
+      </c>
+      <c r="H161" t="s">
+        <v>98</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>1</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+      <c r="N161">
+        <v>2</v>
+      </c>
+      <c r="O161" t="s">
+        <v>175</v>
+      </c>
+      <c r="P161" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q161">
+        <v>4</v>
+      </c>
+      <c r="R161">
+        <v>1.91</v>
+      </c>
+      <c r="S161">
+        <v>3.25</v>
+      </c>
+      <c r="T161">
+        <v>1.57</v>
+      </c>
+      <c r="U161">
+        <v>2.25</v>
+      </c>
+      <c r="V161">
+        <v>3.75</v>
+      </c>
+      <c r="W161">
+        <v>1.25</v>
+      </c>
+      <c r="X161">
+        <v>13</v>
+      </c>
+      <c r="Y161">
+        <v>1.04</v>
+      </c>
+      <c r="Z161">
+        <v>3</v>
+      </c>
+      <c r="AA161">
+        <v>3.3</v>
+      </c>
+      <c r="AB161">
+        <v>2.35</v>
+      </c>
+      <c r="AC161">
+        <v>1.09</v>
+      </c>
+      <c r="AD161">
+        <v>6</v>
+      </c>
+      <c r="AE161">
+        <v>1.5</v>
+      </c>
+      <c r="AF161">
+        <v>2.45</v>
+      </c>
+      <c r="AG161">
+        <v>2.5</v>
+      </c>
+      <c r="AH161">
+        <v>1.5</v>
+      </c>
+      <c r="AI161">
+        <v>2.1</v>
+      </c>
+      <c r="AJ161">
+        <v>1.67</v>
+      </c>
+      <c r="AK161">
+        <v>1.52</v>
+      </c>
+      <c r="AL161">
+        <v>1.36</v>
+      </c>
+      <c r="AM161">
+        <v>1.37</v>
+      </c>
+      <c r="AN161">
+        <v>2.17</v>
+      </c>
+      <c r="AO161">
+        <v>2.5</v>
+      </c>
+      <c r="AP161">
+        <v>2</v>
+      </c>
+      <c r="AQ161">
+        <v>2.2</v>
+      </c>
+      <c r="AR161">
+        <v>2</v>
+      </c>
+      <c r="AS161">
+        <v>1.62</v>
+      </c>
+      <c r="AT161">
+        <v>3.62</v>
+      </c>
+      <c r="AU161">
+        <v>3</v>
+      </c>
+      <c r="AV161">
+        <v>3</v>
+      </c>
+      <c r="AW161">
+        <v>3</v>
+      </c>
+      <c r="AX161">
+        <v>7</v>
+      </c>
+      <c r="AY161">
+        <v>7</v>
+      </c>
+      <c r="AZ161">
+        <v>11</v>
+      </c>
+      <c r="BA161">
+        <v>2</v>
+      </c>
+      <c r="BB161">
+        <v>3</v>
+      </c>
+      <c r="BC161">
+        <v>5</v>
+      </c>
+      <c r="BD161">
+        <v>2.18</v>
+      </c>
+      <c r="BE161">
+        <v>6.4</v>
+      </c>
+      <c r="BF161">
+        <v>1.84</v>
+      </c>
+      <c r="BG161">
+        <v>1.4</v>
+      </c>
+      <c r="BH161">
+        <v>2.7</v>
+      </c>
+      <c r="BI161">
+        <v>1.85</v>
+      </c>
+      <c r="BJ161">
+        <v>1.85</v>
+      </c>
+      <c r="BK161">
+        <v>2.06</v>
+      </c>
+      <c r="BL161">
+        <v>1.66</v>
+      </c>
+      <c r="BM161">
+        <v>2.65</v>
+      </c>
+      <c r="BN161">
+        <v>1.41</v>
+      </c>
+      <c r="BO161">
+        <v>3.45</v>
+      </c>
+      <c r="BP161">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7820478</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45745.78125</v>
+      </c>
+      <c r="F162">
+        <v>11</v>
+      </c>
+      <c r="G162" t="s">
+        <v>76</v>
+      </c>
+      <c r="H162" t="s">
+        <v>70</v>
+      </c>
+      <c r="I162">
+        <v>4</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>4</v>
+      </c>
+      <c r="L162">
+        <v>4</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="N162">
+        <v>4</v>
+      </c>
+      <c r="O162" t="s">
+        <v>195</v>
+      </c>
+      <c r="P162" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q162">
+        <v>2.2</v>
+      </c>
+      <c r="R162">
+        <v>2</v>
+      </c>
+      <c r="S162">
+        <v>7.5</v>
+      </c>
+      <c r="T162">
+        <v>1.57</v>
+      </c>
+      <c r="U162">
+        <v>2.25</v>
+      </c>
+      <c r="V162">
+        <v>3.75</v>
+      </c>
+      <c r="W162">
+        <v>1.25</v>
+      </c>
+      <c r="X162">
+        <v>11</v>
+      </c>
+      <c r="Y162">
+        <v>1.05</v>
+      </c>
+      <c r="Z162">
+        <v>1.55</v>
+      </c>
+      <c r="AA162">
+        <v>3.8</v>
+      </c>
+      <c r="AB162">
+        <v>7</v>
+      </c>
+      <c r="AC162">
+        <v>1.09</v>
+      </c>
+      <c r="AD162">
+        <v>7</v>
+      </c>
+      <c r="AE162">
+        <v>1.47</v>
+      </c>
+      <c r="AF162">
+        <v>2.6</v>
+      </c>
+      <c r="AG162">
+        <v>2.5</v>
+      </c>
+      <c r="AH162">
+        <v>1.5</v>
+      </c>
+      <c r="AI162">
+        <v>2.63</v>
+      </c>
+      <c r="AJ162">
+        <v>1.44</v>
+      </c>
+      <c r="AK162">
+        <v>1.1</v>
+      </c>
+      <c r="AL162">
+        <v>1.27</v>
+      </c>
+      <c r="AM162">
+        <v>2.37</v>
+      </c>
+      <c r="AN162">
+        <v>2.6</v>
+      </c>
+      <c r="AO162">
+        <v>1.6</v>
+      </c>
+      <c r="AP162">
+        <v>2.67</v>
+      </c>
+      <c r="AQ162">
+        <v>1.33</v>
+      </c>
+      <c r="AR162">
+        <v>1.78</v>
+      </c>
+      <c r="AS162">
+        <v>1.23</v>
+      </c>
+      <c r="AT162">
+        <v>3.01</v>
+      </c>
+      <c r="AU162">
+        <v>9</v>
+      </c>
+      <c r="AV162">
+        <v>5</v>
+      </c>
+      <c r="AW162">
+        <v>2</v>
+      </c>
+      <c r="AX162">
+        <v>3</v>
+      </c>
+      <c r="AY162">
+        <v>13</v>
+      </c>
+      <c r="AZ162">
+        <v>9</v>
+      </c>
+      <c r="BA162">
+        <v>3</v>
+      </c>
+      <c r="BB162">
+        <v>2</v>
+      </c>
+      <c r="BC162">
+        <v>5</v>
+      </c>
+      <c r="BD162">
+        <v>1.3</v>
+      </c>
+      <c r="BE162">
+        <v>7.5</v>
+      </c>
+      <c r="BF162">
+        <v>3.8</v>
+      </c>
+      <c r="BG162">
+        <v>1.41</v>
+      </c>
+      <c r="BH162">
+        <v>2.65</v>
+      </c>
+      <c r="BI162">
+        <v>1.77</v>
+      </c>
+      <c r="BJ162">
+        <v>1.93</v>
+      </c>
+      <c r="BK162">
+        <v>2.08</v>
+      </c>
+      <c r="BL162">
+        <v>1.65</v>
+      </c>
+      <c r="BM162">
+        <v>2.65</v>
+      </c>
+      <c r="BN162">
+        <v>1.41</v>
+      </c>
+      <c r="BO162">
+        <v>3.55</v>
+      </c>
+      <c r="BP162">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7820473</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45745.875</v>
+      </c>
+      <c r="F163">
+        <v>11</v>
+      </c>
+      <c r="G163" t="s">
+        <v>95</v>
+      </c>
+      <c r="H163" t="s">
+        <v>87</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>2</v>
+      </c>
+      <c r="L163">
+        <v>2</v>
+      </c>
+      <c r="M163">
+        <v>2</v>
+      </c>
+      <c r="N163">
+        <v>4</v>
+      </c>
+      <c r="O163" t="s">
+        <v>196</v>
+      </c>
+      <c r="P163" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q163">
+        <v>2.1</v>
+      </c>
+      <c r="R163">
+        <v>2.1</v>
+      </c>
+      <c r="S163">
+        <v>7.5</v>
+      </c>
+      <c r="T163">
+        <v>1.5</v>
+      </c>
+      <c r="U163">
+        <v>2.5</v>
+      </c>
+      <c r="V163">
+        <v>3.5</v>
+      </c>
+      <c r="W163">
+        <v>1.29</v>
+      </c>
+      <c r="X163">
+        <v>11</v>
+      </c>
+      <c r="Y163">
+        <v>1.05</v>
+      </c>
+      <c r="Z163">
+        <v>1.48</v>
+      </c>
+      <c r="AA163">
+        <v>3.8</v>
+      </c>
+      <c r="AB163">
+        <v>8.5</v>
+      </c>
+      <c r="AC163">
+        <v>1.07</v>
+      </c>
+      <c r="AD163">
+        <v>8</v>
+      </c>
+      <c r="AE163">
+        <v>1.42</v>
+      </c>
+      <c r="AF163">
+        <v>2.8</v>
+      </c>
+      <c r="AG163">
+        <v>2.35</v>
+      </c>
+      <c r="AH163">
+        <v>1.57</v>
+      </c>
+      <c r="AI163">
+        <v>2.5</v>
+      </c>
+      <c r="AJ163">
+        <v>1.5</v>
+      </c>
+      <c r="AK163">
+        <v>1.1</v>
+      </c>
+      <c r="AL163">
+        <v>1.2</v>
+      </c>
+      <c r="AM163">
+        <v>2.5</v>
+      </c>
+      <c r="AN163">
+        <v>2.4</v>
+      </c>
+      <c r="AO163">
+        <v>1.5</v>
+      </c>
+      <c r="AP163">
+        <v>2.17</v>
+      </c>
+      <c r="AQ163">
+        <v>1.43</v>
+      </c>
+      <c r="AR163">
+        <v>1.96</v>
+      </c>
+      <c r="AS163">
+        <v>1.23</v>
+      </c>
+      <c r="AT163">
+        <v>3.19</v>
+      </c>
+      <c r="AU163">
+        <v>8</v>
+      </c>
+      <c r="AV163">
+        <v>5</v>
+      </c>
+      <c r="AW163">
+        <v>13</v>
+      </c>
+      <c r="AX163">
+        <v>4</v>
+      </c>
+      <c r="AY163">
+        <v>25</v>
+      </c>
+      <c r="AZ163">
+        <v>10</v>
+      </c>
+      <c r="BA163">
+        <v>4</v>
+      </c>
+      <c r="BB163">
+        <v>4</v>
+      </c>
+      <c r="BC163">
+        <v>8</v>
+      </c>
+      <c r="BD163">
+        <v>1.26</v>
+      </c>
+      <c r="BE163">
+        <v>8</v>
+      </c>
+      <c r="BF163">
+        <v>4.1</v>
+      </c>
+      <c r="BG163">
+        <v>1.3</v>
+      </c>
+      <c r="BH163">
+        <v>3.05</v>
+      </c>
+      <c r="BI163">
+        <v>1.7</v>
+      </c>
+      <c r="BJ163">
+        <v>2.05</v>
+      </c>
+      <c r="BK163">
+        <v>2.05</v>
+      </c>
+      <c r="BL163">
+        <v>1.7</v>
+      </c>
+      <c r="BM163">
+        <v>2.32</v>
+      </c>
+      <c r="BN163">
+        <v>1.53</v>
+      </c>
+      <c r="BO163">
+        <v>2.95</v>
+      </c>
+      <c r="BP163">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="260">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -607,6 +607,12 @@
     <t>['18', '61']</t>
   </si>
   <si>
+    <t>['66']</t>
+  </si>
+  <si>
+    <t>['5', '45+3']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -785,6 +791,9 @@
   </si>
   <si>
     <t>['8', '85']</t>
+  </si>
+  <si>
+    <t>['19']</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP166"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1402,7 +1411,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1814,7 +1823,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1892,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ4">
         <v>1.4</v>
@@ -2226,7 +2235,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2432,7 +2441,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2719,7 +2728,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ8">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2922,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
         <v>1.5</v>
@@ -3050,7 +3059,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3337,7 +3346,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ11">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4904,7 +4913,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5522,7 +5531,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5728,7 +5737,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5934,7 +5943,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6012,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ24">
         <v>1.6</v>
@@ -6346,7 +6355,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6427,7 +6436,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6758,7 +6767,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -8075,7 +8084,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ34">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR34">
         <v>1.61</v>
@@ -8406,7 +8415,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8690,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37">
         <v>0.6</v>
@@ -9230,7 +9239,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -10054,7 +10063,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10132,7 +10141,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ44">
         <v>1.4</v>
@@ -10260,7 +10269,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10466,7 +10475,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10672,7 +10681,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10878,7 +10887,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11496,7 +11505,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -12114,7 +12123,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12607,7 +12616,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR56">
         <v>1.44</v>
@@ -12938,7 +12947,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13222,7 +13231,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ59">
         <v>1.33</v>
@@ -13556,7 +13565,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14458,7 +14467,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65">
         <v>0.6</v>
@@ -14792,7 +14801,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14870,7 +14879,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ67">
         <v>1.67</v>
@@ -14998,7 +15007,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -16028,7 +16037,7 @@
         <v>100</v>
       </c>
       <c r="P73" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q73">
         <v>4.5</v>
@@ -16109,7 +16118,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ73">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR73">
         <v>1.31</v>
@@ -16315,7 +16324,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ74">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR74">
         <v>1.59</v>
@@ -16727,7 +16736,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR76">
         <v>1.36</v>
@@ -16852,7 +16861,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17058,7 +17067,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17470,7 +17479,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17676,7 +17685,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17882,7 +17891,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -17960,7 +17969,7 @@
         <v>1.67</v>
       </c>
       <c r="AP82">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ82">
         <v>1.43</v>
@@ -18294,7 +18303,7 @@
         <v>153</v>
       </c>
       <c r="P84" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q84">
         <v>2.75</v>
@@ -18706,7 +18715,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -18990,7 +18999,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ87">
         <v>0.4</v>
@@ -19118,7 +19127,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19324,7 +19333,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19530,7 +19539,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19817,7 +19826,7 @@
         <v>1</v>
       </c>
       <c r="AQ91">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR91">
         <v>1.17</v>
@@ -19942,7 +19951,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20766,7 +20775,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20972,7 +20981,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21259,7 +21268,7 @@
         <v>3</v>
       </c>
       <c r="AQ98">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR98">
         <v>1.32</v>
@@ -21668,7 +21677,7 @@
         <v>2.33</v>
       </c>
       <c r="AP100">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ100">
         <v>1.67</v>
@@ -21796,7 +21805,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -23238,7 +23247,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23319,7 +23328,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ108">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR108">
         <v>2.14</v>
@@ -23444,7 +23453,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23650,7 +23659,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -24062,7 +24071,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24474,7 +24483,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24680,7 +24689,7 @@
         <v>154</v>
       </c>
       <c r="P115" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24886,7 +24895,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25092,7 +25101,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25504,7 +25513,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25710,7 +25719,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -26122,7 +26131,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26203,7 +26212,7 @@
         <v>2</v>
       </c>
       <c r="AQ122">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR122">
         <v>2.07</v>
@@ -26328,7 +26337,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -27358,7 +27367,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28054,7 +28063,7 @@
         <v>0.25</v>
       </c>
       <c r="AP131">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ131">
         <v>0.4</v>
@@ -28182,7 +28191,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28260,7 +28269,7 @@
         <v>1.75</v>
       </c>
       <c r="AP132">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ132">
         <v>1.83</v>
@@ -28800,7 +28809,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -29624,7 +29633,7 @@
         <v>182</v>
       </c>
       <c r="P139" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -29911,7 +29920,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ140">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR140">
         <v>1.98</v>
@@ -30860,7 +30869,7 @@
         <v>186</v>
       </c>
       <c r="P145" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -30938,7 +30947,7 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ145">
         <v>1.4</v>
@@ -31066,7 +31075,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31272,7 +31281,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31478,7 +31487,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31684,7 +31693,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -31890,7 +31899,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32177,7 +32186,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ151">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR151">
         <v>1.16</v>
@@ -32508,7 +32517,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32920,7 +32929,7 @@
         <v>192</v>
       </c>
       <c r="P155" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33126,7 +33135,7 @@
         <v>177</v>
       </c>
       <c r="P156" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -34156,7 +34165,7 @@
         <v>175</v>
       </c>
       <c r="P161" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34568,7 +34577,7 @@
         <v>196</v>
       </c>
       <c r="P163" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q163">
         <v>2.1</v>
@@ -34725,6 +34734,624 @@
       </c>
       <c r="BP163">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7820479</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45746.625</v>
+      </c>
+      <c r="F164">
+        <v>11</v>
+      </c>
+      <c r="G164" t="s">
+        <v>77</v>
+      </c>
+      <c r="H164" t="s">
+        <v>91</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>1</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>2</v>
+      </c>
+      <c r="O164" t="s">
+        <v>197</v>
+      </c>
+      <c r="P164" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q164">
+        <v>3.75</v>
+      </c>
+      <c r="R164">
+        <v>1.95</v>
+      </c>
+      <c r="S164">
+        <v>3.4</v>
+      </c>
+      <c r="T164">
+        <v>1.53</v>
+      </c>
+      <c r="U164">
+        <v>2.38</v>
+      </c>
+      <c r="V164">
+        <v>3.75</v>
+      </c>
+      <c r="W164">
+        <v>1.25</v>
+      </c>
+      <c r="X164">
+        <v>11</v>
+      </c>
+      <c r="Y164">
+        <v>1.05</v>
+      </c>
+      <c r="Z164">
+        <v>3.1</v>
+      </c>
+      <c r="AA164">
+        <v>2.8</v>
+      </c>
+      <c r="AB164">
+        <v>2.63</v>
+      </c>
+      <c r="AC164">
+        <v>1.08</v>
+      </c>
+      <c r="AD164">
+        <v>6.5</v>
+      </c>
+      <c r="AE164">
+        <v>1.44</v>
+      </c>
+      <c r="AF164">
+        <v>2.6</v>
+      </c>
+      <c r="AG164">
+        <v>2.4</v>
+      </c>
+      <c r="AH164">
+        <v>1.53</v>
+      </c>
+      <c r="AI164">
+        <v>2</v>
+      </c>
+      <c r="AJ164">
+        <v>1.75</v>
+      </c>
+      <c r="AK164">
+        <v>1.49</v>
+      </c>
+      <c r="AL164">
+        <v>1.38</v>
+      </c>
+      <c r="AM164">
+        <v>1.37</v>
+      </c>
+      <c r="AN164">
+        <v>1.6</v>
+      </c>
+      <c r="AO164">
+        <v>1.2</v>
+      </c>
+      <c r="AP164">
+        <v>1.5</v>
+      </c>
+      <c r="AQ164">
+        <v>1.17</v>
+      </c>
+      <c r="AR164">
+        <v>1.65</v>
+      </c>
+      <c r="AS164">
+        <v>1.85</v>
+      </c>
+      <c r="AT164">
+        <v>3.5</v>
+      </c>
+      <c r="AU164">
+        <v>3</v>
+      </c>
+      <c r="AV164">
+        <v>3</v>
+      </c>
+      <c r="AW164">
+        <v>9</v>
+      </c>
+      <c r="AX164">
+        <v>7</v>
+      </c>
+      <c r="AY164">
+        <v>14</v>
+      </c>
+      <c r="AZ164">
+        <v>14</v>
+      </c>
+      <c r="BA164">
+        <v>5</v>
+      </c>
+      <c r="BB164">
+        <v>1</v>
+      </c>
+      <c r="BC164">
+        <v>6</v>
+      </c>
+      <c r="BD164">
+        <v>1.8</v>
+      </c>
+      <c r="BE164">
+        <v>6.75</v>
+      </c>
+      <c r="BF164">
+        <v>2.23</v>
+      </c>
+      <c r="BG164">
+        <v>1.29</v>
+      </c>
+      <c r="BH164">
+        <v>3.15</v>
+      </c>
+      <c r="BI164">
+        <v>1.49</v>
+      </c>
+      <c r="BJ164">
+        <v>2.4</v>
+      </c>
+      <c r="BK164">
+        <v>2</v>
+      </c>
+      <c r="BL164">
+        <v>1.73</v>
+      </c>
+      <c r="BM164">
+        <v>2.23</v>
+      </c>
+      <c r="BN164">
+        <v>1.57</v>
+      </c>
+      <c r="BO164">
+        <v>2.8</v>
+      </c>
+      <c r="BP164">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7820472</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45746.66666666666</v>
+      </c>
+      <c r="F165">
+        <v>11</v>
+      </c>
+      <c r="G165" t="s">
+        <v>92</v>
+      </c>
+      <c r="H165" t="s">
+        <v>88</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>0</v>
+      </c>
+      <c r="O165" t="s">
+        <v>100</v>
+      </c>
+      <c r="P165" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q165">
+        <v>2.63</v>
+      </c>
+      <c r="R165">
+        <v>1.91</v>
+      </c>
+      <c r="S165">
+        <v>6</v>
+      </c>
+      <c r="T165">
+        <v>1.62</v>
+      </c>
+      <c r="U165">
+        <v>2.2</v>
+      </c>
+      <c r="V165">
+        <v>4</v>
+      </c>
+      <c r="W165">
+        <v>1.22</v>
+      </c>
+      <c r="X165">
+        <v>13</v>
+      </c>
+      <c r="Y165">
+        <v>1.04</v>
+      </c>
+      <c r="Z165">
+        <v>1.8</v>
+      </c>
+      <c r="AA165">
+        <v>3.3</v>
+      </c>
+      <c r="AB165">
+        <v>5</v>
+      </c>
+      <c r="AC165">
+        <v>1.1</v>
+      </c>
+      <c r="AD165">
+        <v>5.75</v>
+      </c>
+      <c r="AE165">
+        <v>1.57</v>
+      </c>
+      <c r="AF165">
+        <v>2.25</v>
+      </c>
+      <c r="AG165">
+        <v>2.88</v>
+      </c>
+      <c r="AH165">
+        <v>1.4</v>
+      </c>
+      <c r="AI165">
+        <v>2.5</v>
+      </c>
+      <c r="AJ165">
+        <v>1.5</v>
+      </c>
+      <c r="AK165">
+        <v>1.17</v>
+      </c>
+      <c r="AL165">
+        <v>1.33</v>
+      </c>
+      <c r="AM165">
+        <v>1.93</v>
+      </c>
+      <c r="AN165">
+        <v>1.75</v>
+      </c>
+      <c r="AO165">
+        <v>0.2</v>
+      </c>
+      <c r="AP165">
+        <v>1.6</v>
+      </c>
+      <c r="AQ165">
+        <v>0.33</v>
+      </c>
+      <c r="AR165">
+        <v>1.38</v>
+      </c>
+      <c r="AS165">
+        <v>1.19</v>
+      </c>
+      <c r="AT165">
+        <v>2.57</v>
+      </c>
+      <c r="AU165">
+        <v>5</v>
+      </c>
+      <c r="AV165">
+        <v>4</v>
+      </c>
+      <c r="AW165">
+        <v>18</v>
+      </c>
+      <c r="AX165">
+        <v>6</v>
+      </c>
+      <c r="AY165">
+        <v>31</v>
+      </c>
+      <c r="AZ165">
+        <v>11</v>
+      </c>
+      <c r="BA165">
+        <v>8</v>
+      </c>
+      <c r="BB165">
+        <v>2</v>
+      </c>
+      <c r="BC165">
+        <v>10</v>
+      </c>
+      <c r="BD165">
+        <v>1.4</v>
+      </c>
+      <c r="BE165">
+        <v>7</v>
+      </c>
+      <c r="BF165">
+        <v>3.3</v>
+      </c>
+      <c r="BG165">
+        <v>1.36</v>
+      </c>
+      <c r="BH165">
+        <v>2.8</v>
+      </c>
+      <c r="BI165">
+        <v>1.62</v>
+      </c>
+      <c r="BJ165">
+        <v>2.14</v>
+      </c>
+      <c r="BK165">
+        <v>2.05</v>
+      </c>
+      <c r="BL165">
+        <v>1.7</v>
+      </c>
+      <c r="BM165">
+        <v>2.5</v>
+      </c>
+      <c r="BN165">
+        <v>1.46</v>
+      </c>
+      <c r="BO165">
+        <v>3.3</v>
+      </c>
+      <c r="BP165">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7820466</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45746.8125</v>
+      </c>
+      <c r="F166">
+        <v>11</v>
+      </c>
+      <c r="G166" t="s">
+        <v>72</v>
+      </c>
+      <c r="H166" t="s">
+        <v>83</v>
+      </c>
+      <c r="I166">
+        <v>2</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>2</v>
+      </c>
+      <c r="L166">
+        <v>2</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>2</v>
+      </c>
+      <c r="O166" t="s">
+        <v>198</v>
+      </c>
+      <c r="P166" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q166">
+        <v>4</v>
+      </c>
+      <c r="R166">
+        <v>1.91</v>
+      </c>
+      <c r="S166">
+        <v>3.25</v>
+      </c>
+      <c r="T166">
+        <v>1.57</v>
+      </c>
+      <c r="U166">
+        <v>2.25</v>
+      </c>
+      <c r="V166">
+        <v>3.75</v>
+      </c>
+      <c r="W166">
+        <v>1.25</v>
+      </c>
+      <c r="X166">
+        <v>13</v>
+      </c>
+      <c r="Y166">
+        <v>1.04</v>
+      </c>
+      <c r="Z166">
+        <v>3.1</v>
+      </c>
+      <c r="AA166">
+        <v>3.1</v>
+      </c>
+      <c r="AB166">
+        <v>2.4</v>
+      </c>
+      <c r="AC166">
+        <v>1.09</v>
+      </c>
+      <c r="AD166">
+        <v>6</v>
+      </c>
+      <c r="AE166">
+        <v>1.5</v>
+      </c>
+      <c r="AF166">
+        <v>2.37</v>
+      </c>
+      <c r="AG166">
+        <v>2.6</v>
+      </c>
+      <c r="AH166">
+        <v>1.48</v>
+      </c>
+      <c r="AI166">
+        <v>2.2</v>
+      </c>
+      <c r="AJ166">
+        <v>1.62</v>
+      </c>
+      <c r="AK166">
+        <v>1.53</v>
+      </c>
+      <c r="AL166">
+        <v>1.37</v>
+      </c>
+      <c r="AM166">
+        <v>1.34</v>
+      </c>
+      <c r="AN166">
+        <v>0.8</v>
+      </c>
+      <c r="AO166">
+        <v>1.75</v>
+      </c>
+      <c r="AP166">
+        <v>1.17</v>
+      </c>
+      <c r="AQ166">
+        <v>1.4</v>
+      </c>
+      <c r="AR166">
+        <v>1.8</v>
+      </c>
+      <c r="AS166">
+        <v>1.37</v>
+      </c>
+      <c r="AT166">
+        <v>3.17</v>
+      </c>
+      <c r="AU166">
+        <v>5</v>
+      </c>
+      <c r="AV166">
+        <v>2</v>
+      </c>
+      <c r="AW166">
+        <v>3</v>
+      </c>
+      <c r="AX166">
+        <v>9</v>
+      </c>
+      <c r="AY166">
+        <v>8</v>
+      </c>
+      <c r="AZ166">
+        <v>12</v>
+      </c>
+      <c r="BA166">
+        <v>3</v>
+      </c>
+      <c r="BB166">
+        <v>7</v>
+      </c>
+      <c r="BC166">
+        <v>10</v>
+      </c>
+      <c r="BD166">
+        <v>2.05</v>
+      </c>
+      <c r="BE166">
+        <v>6.4</v>
+      </c>
+      <c r="BF166">
+        <v>1.95</v>
+      </c>
+      <c r="BG166">
+        <v>1.35</v>
+      </c>
+      <c r="BH166">
+        <v>2.88</v>
+      </c>
+      <c r="BI166">
+        <v>1.67</v>
+      </c>
+      <c r="BJ166">
+        <v>2</v>
+      </c>
+      <c r="BK166">
+        <v>2.1</v>
+      </c>
+      <c r="BL166">
+        <v>1.67</v>
+      </c>
+      <c r="BM166">
+        <v>2.48</v>
+      </c>
+      <c r="BN166">
+        <v>1.46</v>
+      </c>
+      <c r="BO166">
+        <v>3.2</v>
+      </c>
+      <c r="BP166">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="263">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -613,6 +613,9 @@
     <t>['5', '45+3']</t>
   </si>
   <si>
+    <t>['24', '48', '68']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -794,6 +797,12 @@
   </si>
   <si>
     <t>['19']</t>
+  </si>
+  <si>
+    <t>['69']</t>
+  </si>
+  <si>
+    <t>['20', '63', '80']</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP166"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1411,7 +1420,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1823,7 +1832,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2235,7 +2244,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2441,7 +2450,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -3059,7 +3068,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3137,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AQ10">
         <v>0.67</v>
@@ -3549,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ12">
         <v>0</v>
@@ -4376,7 +4385,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4913,7 +4922,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5531,7 +5540,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5737,7 +5746,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5943,7 +5952,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6024,7 +6033,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ24">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6227,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6355,7 +6364,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6767,7 +6776,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7054,7 +7063,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7875,7 +7884,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AQ33">
         <v>1.43</v>
@@ -8415,7 +8424,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8702,7 +8711,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ37">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR37">
         <v>2.05</v>
@@ -9239,7 +9248,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9729,7 +9738,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -10063,7 +10072,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10269,7 +10278,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10475,7 +10484,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10681,7 +10690,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10887,7 +10896,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -10968,7 +10977,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR48">
         <v>1.53</v>
@@ -11377,7 +11386,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ50">
         <v>2</v>
@@ -11505,7 +11514,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11998,7 +12007,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ53">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR53">
         <v>1.58</v>
@@ -12123,7 +12132,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12947,7 +12956,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13565,7 +13574,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14055,7 +14064,7 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ63">
         <v>0.6</v>
@@ -14470,7 +14479,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR65">
         <v>1.99</v>
@@ -14801,7 +14810,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -15007,7 +15016,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -16037,7 +16046,7 @@
         <v>100</v>
       </c>
       <c r="P73" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q73">
         <v>4.5</v>
@@ -16115,7 +16124,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AQ73">
         <v>1.17</v>
@@ -16861,7 +16870,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17067,7 +17076,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17354,7 +17363,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR79">
         <v>1.81</v>
@@ -17479,7 +17488,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17685,7 +17694,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17891,7 +17900,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18303,7 +18312,7 @@
         <v>153</v>
       </c>
       <c r="P84" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q84">
         <v>2.75</v>
@@ -18587,7 +18596,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ85">
         <v>0</v>
@@ -18715,7 +18724,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -19127,7 +19136,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19333,7 +19342,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19539,7 +19548,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19620,7 +19629,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR90">
         <v>1.46</v>
@@ -19951,7 +19960,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20029,7 +20038,7 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20775,7 +20784,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20856,7 +20865,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ96">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR96">
         <v>1.26</v>
@@ -20981,7 +20990,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21059,7 +21068,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AQ97">
         <v>1.4</v>
@@ -21471,10 +21480,10 @@
         <v>2.33</v>
       </c>
       <c r="AP99">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ99">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR99">
         <v>1.77</v>
@@ -21805,7 +21814,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -23119,10 +23128,10 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AQ107">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR107">
         <v>1.43</v>
@@ -23247,7 +23256,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23453,7 +23462,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23659,7 +23668,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -24071,7 +24080,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24483,7 +24492,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24689,7 +24698,7 @@
         <v>154</v>
       </c>
       <c r="P115" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24895,7 +24904,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25101,7 +25110,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25513,7 +25522,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25719,7 +25728,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -26131,7 +26140,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26337,7 +26346,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -27367,7 +27376,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28066,7 +28075,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ131">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR131">
         <v>1.81</v>
@@ -28191,7 +28200,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28809,7 +28818,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -28890,7 +28899,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ135">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR135">
         <v>1.84</v>
@@ -29096,7 +29105,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ136">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR136">
         <v>1.23</v>
@@ -29633,7 +29642,7 @@
         <v>182</v>
       </c>
       <c r="P139" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -29711,7 +29720,7 @@
         <v>0.75</v>
       </c>
       <c r="AP139">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ139">
         <v>0.8</v>
@@ -30123,7 +30132,7 @@
         <v>1.75</v>
       </c>
       <c r="AP141">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ141">
         <v>1.4</v>
@@ -30869,7 +30878,7 @@
         <v>186</v>
       </c>
       <c r="P145" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31075,7 +31084,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31281,7 +31290,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31487,7 +31496,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31565,7 +31574,7 @@
         <v>1</v>
       </c>
       <c r="AP148">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AQ148">
         <v>1.4</v>
@@ -31693,7 +31702,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -31899,7 +31908,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32517,7 +32526,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32929,7 +32938,7 @@
         <v>192</v>
       </c>
       <c r="P155" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33135,7 +33144,7 @@
         <v>177</v>
       </c>
       <c r="P156" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -34165,7 +34174,7 @@
         <v>175</v>
       </c>
       <c r="P161" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34577,7 +34586,7 @@
         <v>196</v>
       </c>
       <c r="P163" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q163">
         <v>2.1</v>
@@ -34783,7 +34792,7 @@
         <v>197</v>
       </c>
       <c r="P164" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q164">
         <v>3.75</v>
@@ -35352,6 +35361,624 @@
       </c>
       <c r="BP166">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7820486</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45751.79166666666</v>
+      </c>
+      <c r="F167">
+        <v>12</v>
+      </c>
+      <c r="G167" t="s">
+        <v>80</v>
+      </c>
+      <c r="H167" t="s">
+        <v>77</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>1</v>
+      </c>
+      <c r="N167">
+        <v>1</v>
+      </c>
+      <c r="O167" t="s">
+        <v>100</v>
+      </c>
+      <c r="P167" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q167">
+        <v>2.38</v>
+      </c>
+      <c r="R167">
+        <v>2.1</v>
+      </c>
+      <c r="S167">
+        <v>5.5</v>
+      </c>
+      <c r="T167">
+        <v>1.44</v>
+      </c>
+      <c r="U167">
+        <v>2.63</v>
+      </c>
+      <c r="V167">
+        <v>3.25</v>
+      </c>
+      <c r="W167">
+        <v>1.33</v>
+      </c>
+      <c r="X167">
+        <v>9</v>
+      </c>
+      <c r="Y167">
+        <v>1.07</v>
+      </c>
+      <c r="Z167">
+        <v>1.73</v>
+      </c>
+      <c r="AA167">
+        <v>3.4</v>
+      </c>
+      <c r="AB167">
+        <v>5.5</v>
+      </c>
+      <c r="AC167">
+        <v>1.02</v>
+      </c>
+      <c r="AD167">
+        <v>8</v>
+      </c>
+      <c r="AE167">
+        <v>1.32</v>
+      </c>
+      <c r="AF167">
+        <v>2.97</v>
+      </c>
+      <c r="AG167">
+        <v>2.08</v>
+      </c>
+      <c r="AH167">
+        <v>1.73</v>
+      </c>
+      <c r="AI167">
+        <v>1.95</v>
+      </c>
+      <c r="AJ167">
+        <v>1.8</v>
+      </c>
+      <c r="AK167">
+        <v>1.19</v>
+      </c>
+      <c r="AL167">
+        <v>1.29</v>
+      </c>
+      <c r="AM167">
+        <v>1.98</v>
+      </c>
+      <c r="AN167">
+        <v>2.6</v>
+      </c>
+      <c r="AO167">
+        <v>0.4</v>
+      </c>
+      <c r="AP167">
+        <v>2.17</v>
+      </c>
+      <c r="AQ167">
+        <v>0.83</v>
+      </c>
+      <c r="AR167">
+        <v>1.93</v>
+      </c>
+      <c r="AS167">
+        <v>1.4</v>
+      </c>
+      <c r="AT167">
+        <v>3.33</v>
+      </c>
+      <c r="AU167">
+        <v>7</v>
+      </c>
+      <c r="AV167">
+        <v>2</v>
+      </c>
+      <c r="AW167">
+        <v>9</v>
+      </c>
+      <c r="AX167">
+        <v>4</v>
+      </c>
+      <c r="AY167">
+        <v>19</v>
+      </c>
+      <c r="AZ167">
+        <v>8</v>
+      </c>
+      <c r="BA167">
+        <v>9</v>
+      </c>
+      <c r="BB167">
+        <v>5</v>
+      </c>
+      <c r="BC167">
+        <v>14</v>
+      </c>
+      <c r="BD167">
+        <v>1.52</v>
+      </c>
+      <c r="BE167">
+        <v>6.75</v>
+      </c>
+      <c r="BF167">
+        <v>2.8</v>
+      </c>
+      <c r="BG167">
+        <v>1.35</v>
+      </c>
+      <c r="BH167">
+        <v>2.9</v>
+      </c>
+      <c r="BI167">
+        <v>1.6</v>
+      </c>
+      <c r="BJ167">
+        <v>2.17</v>
+      </c>
+      <c r="BK167">
+        <v>1.96</v>
+      </c>
+      <c r="BL167">
+        <v>1.73</v>
+      </c>
+      <c r="BM167">
+        <v>2.48</v>
+      </c>
+      <c r="BN167">
+        <v>1.46</v>
+      </c>
+      <c r="BO167">
+        <v>3.2</v>
+      </c>
+      <c r="BP167">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7820488</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45751.91666666666</v>
+      </c>
+      <c r="F168">
+        <v>12</v>
+      </c>
+      <c r="G168" t="s">
+        <v>78</v>
+      </c>
+      <c r="H168" t="s">
+        <v>79</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>1</v>
+      </c>
+      <c r="N168">
+        <v>1</v>
+      </c>
+      <c r="O168" t="s">
+        <v>100</v>
+      </c>
+      <c r="P168" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q168">
+        <v>4.33</v>
+      </c>
+      <c r="R168">
+        <v>1.8</v>
+      </c>
+      <c r="S168">
+        <v>3.6</v>
+      </c>
+      <c r="T168">
+        <v>1.73</v>
+      </c>
+      <c r="U168">
+        <v>2</v>
+      </c>
+      <c r="V168">
+        <v>5</v>
+      </c>
+      <c r="W168">
+        <v>1.17</v>
+      </c>
+      <c r="X168">
+        <v>17</v>
+      </c>
+      <c r="Y168">
+        <v>1.03</v>
+      </c>
+      <c r="Z168">
+        <v>3</v>
+      </c>
+      <c r="AA168">
+        <v>3</v>
+      </c>
+      <c r="AB168">
+        <v>2.6</v>
+      </c>
+      <c r="AC168">
+        <v>0</v>
+      </c>
+      <c r="AD168">
+        <v>0</v>
+      </c>
+      <c r="AE168">
+        <v>1.73</v>
+      </c>
+      <c r="AF168">
+        <v>2</v>
+      </c>
+      <c r="AG168">
+        <v>3.4</v>
+      </c>
+      <c r="AH168">
+        <v>1.33</v>
+      </c>
+      <c r="AI168">
+        <v>2.63</v>
+      </c>
+      <c r="AJ168">
+        <v>1.44</v>
+      </c>
+      <c r="AK168">
+        <v>0</v>
+      </c>
+      <c r="AL168">
+        <v>0</v>
+      </c>
+      <c r="AM168">
+        <v>0</v>
+      </c>
+      <c r="AN168">
+        <v>0.67</v>
+      </c>
+      <c r="AO168">
+        <v>1.6</v>
+      </c>
+      <c r="AP168">
+        <v>0.57</v>
+      </c>
+      <c r="AQ168">
+        <v>1.83</v>
+      </c>
+      <c r="AR168">
+        <v>1.54</v>
+      </c>
+      <c r="AS168">
+        <v>1.03</v>
+      </c>
+      <c r="AT168">
+        <v>2.57</v>
+      </c>
+      <c r="AU168">
+        <v>6</v>
+      </c>
+      <c r="AV168">
+        <v>3</v>
+      </c>
+      <c r="AW168">
+        <v>5</v>
+      </c>
+      <c r="AX168">
+        <v>2</v>
+      </c>
+      <c r="AY168">
+        <v>12</v>
+      </c>
+      <c r="AZ168">
+        <v>5</v>
+      </c>
+      <c r="BA168">
+        <v>4</v>
+      </c>
+      <c r="BB168">
+        <v>7</v>
+      </c>
+      <c r="BC168">
+        <v>11</v>
+      </c>
+      <c r="BD168">
+        <v>0</v>
+      </c>
+      <c r="BE168">
+        <v>0</v>
+      </c>
+      <c r="BF168">
+        <v>0</v>
+      </c>
+      <c r="BG168">
+        <v>0</v>
+      </c>
+      <c r="BH168">
+        <v>0</v>
+      </c>
+      <c r="BI168">
+        <v>0</v>
+      </c>
+      <c r="BJ168">
+        <v>0</v>
+      </c>
+      <c r="BK168">
+        <v>0</v>
+      </c>
+      <c r="BL168">
+        <v>0</v>
+      </c>
+      <c r="BM168">
+        <v>0</v>
+      </c>
+      <c r="BN168">
+        <v>0</v>
+      </c>
+      <c r="BO168">
+        <v>0</v>
+      </c>
+      <c r="BP168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7820481</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45752.75</v>
+      </c>
+      <c r="F169">
+        <v>12</v>
+      </c>
+      <c r="G169" t="s">
+        <v>93</v>
+      </c>
+      <c r="H169" t="s">
+        <v>96</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+      <c r="J169">
+        <v>1</v>
+      </c>
+      <c r="K169">
+        <v>2</v>
+      </c>
+      <c r="L169">
+        <v>3</v>
+      </c>
+      <c r="M169">
+        <v>3</v>
+      </c>
+      <c r="N169">
+        <v>6</v>
+      </c>
+      <c r="O169" t="s">
+        <v>199</v>
+      </c>
+      <c r="P169" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q169">
+        <v>2.38</v>
+      </c>
+      <c r="R169">
+        <v>1.95</v>
+      </c>
+      <c r="S169">
+        <v>6.5</v>
+      </c>
+      <c r="T169">
+        <v>1.57</v>
+      </c>
+      <c r="U169">
+        <v>2.25</v>
+      </c>
+      <c r="V169">
+        <v>3.75</v>
+      </c>
+      <c r="W169">
+        <v>1.25</v>
+      </c>
+      <c r="X169">
+        <v>13</v>
+      </c>
+      <c r="Y169">
+        <v>1.04</v>
+      </c>
+      <c r="Z169">
+        <v>1.67</v>
+      </c>
+      <c r="AA169">
+        <v>3.6</v>
+      </c>
+      <c r="AB169">
+        <v>5.75</v>
+      </c>
+      <c r="AC169">
+        <v>1.11</v>
+      </c>
+      <c r="AD169">
+        <v>6.87</v>
+      </c>
+      <c r="AE169">
+        <v>1.5</v>
+      </c>
+      <c r="AF169">
+        <v>2.4</v>
+      </c>
+      <c r="AG169">
+        <v>2.6</v>
+      </c>
+      <c r="AH169">
+        <v>1.48</v>
+      </c>
+      <c r="AI169">
+        <v>2.5</v>
+      </c>
+      <c r="AJ169">
+        <v>1.5</v>
+      </c>
+      <c r="AK169">
+        <v>1.13</v>
+      </c>
+      <c r="AL169">
+        <v>1.25</v>
+      </c>
+      <c r="AM169">
+        <v>2.15</v>
+      </c>
+      <c r="AN169">
+        <v>2.6</v>
+      </c>
+      <c r="AO169">
+        <v>0.6</v>
+      </c>
+      <c r="AP169">
+        <v>2.33</v>
+      </c>
+      <c r="AQ169">
+        <v>0.67</v>
+      </c>
+      <c r="AR169">
+        <v>1.62</v>
+      </c>
+      <c r="AS169">
+        <v>1.36</v>
+      </c>
+      <c r="AT169">
+        <v>2.98</v>
+      </c>
+      <c r="AU169">
+        <v>8</v>
+      </c>
+      <c r="AV169">
+        <v>8</v>
+      </c>
+      <c r="AW169">
+        <v>8</v>
+      </c>
+      <c r="AX169">
+        <v>3</v>
+      </c>
+      <c r="AY169">
+        <v>18</v>
+      </c>
+      <c r="AZ169">
+        <v>14</v>
+      </c>
+      <c r="BA169">
+        <v>5</v>
+      </c>
+      <c r="BB169">
+        <v>5</v>
+      </c>
+      <c r="BC169">
+        <v>10</v>
+      </c>
+      <c r="BD169">
+        <v>1.44</v>
+      </c>
+      <c r="BE169">
+        <v>9</v>
+      </c>
+      <c r="BF169">
+        <v>3.1</v>
+      </c>
+      <c r="BG169">
+        <v>1.31</v>
+      </c>
+      <c r="BH169">
+        <v>2.92</v>
+      </c>
+      <c r="BI169">
+        <v>1.7</v>
+      </c>
+      <c r="BJ169">
+        <v>2.05</v>
+      </c>
+      <c r="BK169">
+        <v>2.03</v>
+      </c>
+      <c r="BL169">
+        <v>1.7</v>
+      </c>
+      <c r="BM169">
+        <v>2.64</v>
+      </c>
+      <c r="BN169">
+        <v>1.4</v>
+      </c>
+      <c r="BO169">
+        <v>3.58</v>
+      </c>
+      <c r="BP169">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="265">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -613,7 +613,16 @@
     <t>['5', '45+3']</t>
   </si>
   <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['58', '90+1']</t>
+  </si>
+  <si>
     <t>['24', '48', '68']</t>
+  </si>
+  <si>
+    <t>['16', '65']</t>
   </si>
   <si>
     <t>['18', '26', '48']</t>
@@ -761,9 +770,6 @@
   </si>
   <si>
     <t>['10', '89']</t>
-  </si>
-  <si>
-    <t>['45+1']</t>
   </si>
   <si>
     <t>['36']</t>
@@ -1164,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1420,7 +1426,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1498,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ2">
         <v>1.43</v>
@@ -1707,7 +1713,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ3">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1832,7 +1838,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1913,7 +1919,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ4">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2244,7 +2250,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2450,7 +2456,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -3068,7 +3074,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -3767,7 +3773,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3973,7 +3979,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4922,7 +4928,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5206,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20">
         <v>1.33</v>
@@ -5540,7 +5546,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5746,7 +5752,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5824,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ23">
         <v>1.6</v>
@@ -5952,7 +5958,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6364,7 +6370,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6776,7 +6782,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -8299,7 +8305,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ35">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR35">
         <v>1.24</v>
@@ -8424,7 +8430,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8917,7 +8923,7 @@
         <v>2</v>
       </c>
       <c r="AQ38">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR38">
         <v>1.8</v>
@@ -9123,7 +9129,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ39">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR39">
         <v>1.95</v>
@@ -9248,7 +9254,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -10072,7 +10078,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10153,7 +10159,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.93</v>
@@ -10278,7 +10284,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10484,7 +10490,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10690,7 +10696,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10768,7 +10774,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ47">
         <v>0.4</v>
@@ -10896,7 +10902,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11514,7 +11520,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -12132,7 +12138,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12956,7 +12962,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13446,7 +13452,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13574,7 +13580,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13861,7 +13867,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ62">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR62">
         <v>1.19</v>
@@ -14810,7 +14816,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -15016,7 +15022,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15303,7 +15309,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ69">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR69">
         <v>2.02</v>
@@ -15506,10 +15512,10 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ70">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>1.21</v>
@@ -15715,7 +15721,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ71">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR71">
         <v>1.67</v>
@@ -16046,7 +16052,7 @@
         <v>100</v>
       </c>
       <c r="P73" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q73">
         <v>4.5</v>
@@ -16870,7 +16876,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17076,7 +17082,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17488,7 +17494,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17694,7 +17700,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17900,7 +17906,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18312,7 +18318,7 @@
         <v>153</v>
       </c>
       <c r="P84" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q84">
         <v>2.75</v>
@@ -18390,7 +18396,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ84">
         <v>0.67</v>
@@ -18724,7 +18730,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -18802,7 +18808,7 @@
         <v>3</v>
       </c>
       <c r="AP86">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ86">
         <v>1.83</v>
@@ -19136,7 +19142,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19342,7 +19348,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19548,7 +19554,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19960,7 +19966,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20244,7 +20250,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ93">
         <v>1.4</v>
@@ -20453,7 +20459,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ94">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR94">
         <v>1.94</v>
@@ -20784,7 +20790,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20990,7 +20996,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21071,7 +21077,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ97">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR97">
         <v>1.54</v>
@@ -21814,7 +21820,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -21895,7 +21901,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ101">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR101">
         <v>1.82</v>
@@ -22307,7 +22313,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ103">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR103">
         <v>1.55</v>
@@ -23256,7 +23262,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23462,7 +23468,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23668,7 +23674,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -23746,7 +23752,7 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ110">
         <v>2</v>
@@ -23955,7 +23961,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ111">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR111">
         <v>1.45</v>
@@ -24080,7 +24086,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24492,7 +24498,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24698,7 +24704,7 @@
         <v>154</v>
       </c>
       <c r="P115" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24904,7 +24910,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25110,7 +25116,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25522,7 +25528,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25728,7 +25734,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -26140,7 +26146,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26346,7 +26352,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -27042,7 +27048,7 @@
         <v>1.67</v>
       </c>
       <c r="AP126">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ126">
         <v>1.4</v>
@@ -27376,7 +27382,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28200,7 +28206,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28690,7 +28696,7 @@
         <v>1.6</v>
       </c>
       <c r="AP134">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ134">
         <v>1.43</v>
@@ -28818,7 +28824,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -29102,7 +29108,7 @@
         <v>1.75</v>
       </c>
       <c r="AP136">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ136">
         <v>1.83</v>
@@ -29311,7 +29317,7 @@
         <v>1</v>
       </c>
       <c r="AQ137">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR137">
         <v>1.28</v>
@@ -29517,7 +29523,7 @@
         <v>3</v>
       </c>
       <c r="AQ138">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR138">
         <v>1.28</v>
@@ -29642,7 +29648,7 @@
         <v>182</v>
       </c>
       <c r="P139" t="s">
-        <v>249</v>
+        <v>199</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -29926,7 +29932,7 @@
         <v>1.33</v>
       </c>
       <c r="AP140">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ140">
         <v>1.17</v>
@@ -30135,7 +30141,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ141">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR141">
         <v>1.7</v>
@@ -30878,7 +30884,7 @@
         <v>186</v>
       </c>
       <c r="P145" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31084,7 +31090,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31290,7 +31296,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31496,7 +31502,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31702,7 +31708,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -31783,7 +31789,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ149">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR149">
         <v>1.84</v>
@@ -31908,7 +31914,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32192,7 +32198,7 @@
         <v>1.25</v>
       </c>
       <c r="AP151">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ151">
         <v>1.17</v>
@@ -32526,7 +32532,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32938,7 +32944,7 @@
         <v>192</v>
       </c>
       <c r="P155" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33144,7 +33150,7 @@
         <v>177</v>
       </c>
       <c r="P156" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -34174,7 +34180,7 @@
         <v>175</v>
       </c>
       <c r="P161" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34586,7 +34592,7 @@
         <v>196</v>
       </c>
       <c r="P163" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q163">
         <v>2.1</v>
@@ -34792,7 +34798,7 @@
         <v>197</v>
       </c>
       <c r="P164" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q164">
         <v>3.75</v>
@@ -35616,7 +35622,7 @@
         <v>100</v>
       </c>
       <c r="P168" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q168">
         <v>4.33</v>
@@ -35780,7 +35786,7 @@
         <v>168</v>
       </c>
       <c r="B169">
-        <v>7820481</v>
+        <v>7820494</v>
       </c>
       <c r="C169" t="s">
         <v>68</v>
@@ -35789,166 +35795,166 @@
         <v>69</v>
       </c>
       <c r="E169" s="2">
-        <v>45752.75</v>
+        <v>45752.64583333334</v>
       </c>
       <c r="F169">
         <v>12</v>
       </c>
       <c r="G169" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="H169" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I169">
         <v>1</v>
       </c>
       <c r="J169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L169">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M169">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N169">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O169" t="s">
         <v>199</v>
       </c>
       <c r="P169" t="s">
-        <v>262</v>
+        <v>109</v>
       </c>
       <c r="Q169">
+        <v>3.75</v>
+      </c>
+      <c r="R169">
+        <v>1.8</v>
+      </c>
+      <c r="S169">
+        <v>4</v>
+      </c>
+      <c r="T169">
+        <v>1.73</v>
+      </c>
+      <c r="U169">
+        <v>2</v>
+      </c>
+      <c r="V169">
+        <v>4.5</v>
+      </c>
+      <c r="W169">
+        <v>1.18</v>
+      </c>
+      <c r="X169">
+        <v>17</v>
+      </c>
+      <c r="Y169">
+        <v>1.03</v>
+      </c>
+      <c r="Z169">
+        <v>3</v>
+      </c>
+      <c r="AA169">
+        <v>2.6</v>
+      </c>
+      <c r="AB169">
+        <v>3</v>
+      </c>
+      <c r="AC169">
+        <v>1.17</v>
+      </c>
+      <c r="AD169">
+        <v>5.36</v>
+      </c>
+      <c r="AE169">
+        <v>1.67</v>
+      </c>
+      <c r="AF169">
+        <v>2.05</v>
+      </c>
+      <c r="AG169">
+        <v>3.4</v>
+      </c>
+      <c r="AH169">
+        <v>1.33</v>
+      </c>
+      <c r="AI169">
         <v>2.38</v>
       </c>
-      <c r="R169">
-        <v>1.95</v>
-      </c>
-      <c r="S169">
-        <v>6.5</v>
-      </c>
-      <c r="T169">
-        <v>1.57</v>
-      </c>
-      <c r="U169">
-        <v>2.25</v>
-      </c>
-      <c r="V169">
-        <v>3.75</v>
-      </c>
-      <c r="W169">
-        <v>1.25</v>
-      </c>
-      <c r="X169">
-        <v>13</v>
-      </c>
-      <c r="Y169">
-        <v>1.04</v>
-      </c>
-      <c r="Z169">
-        <v>1.67</v>
-      </c>
-      <c r="AA169">
-        <v>3.6</v>
-      </c>
-      <c r="AB169">
-        <v>5.75</v>
-      </c>
-      <c r="AC169">
-        <v>1.11</v>
-      </c>
-      <c r="AD169">
-        <v>6.87</v>
-      </c>
-      <c r="AE169">
-        <v>1.5</v>
-      </c>
-      <c r="AF169">
-        <v>2.4</v>
-      </c>
-      <c r="AG169">
-        <v>2.6</v>
-      </c>
-      <c r="AH169">
-        <v>1.48</v>
-      </c>
-      <c r="AI169">
-        <v>2.5</v>
-      </c>
       <c r="AJ169">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AK169">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AL169">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AM169">
-        <v>2.15</v>
+        <v>1.38</v>
       </c>
       <c r="AN169">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="AO169">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="AP169">
-        <v>2.33</v>
+        <v>0.83</v>
       </c>
       <c r="AQ169">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="AR169">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="AS169">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AT169">
-        <v>2.98</v>
+        <v>2.24</v>
       </c>
       <c r="AU169">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AV169">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW169">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX169">
         <v>3</v>
       </c>
       <c r="AY169">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AZ169">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA169">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB169">
         <v>5</v>
       </c>
       <c r="BC169">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD169">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="BE169">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BF169">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="BG169">
         <v>1.31</v>
@@ -35957,28 +35963,852 @@
         <v>2.92</v>
       </c>
       <c r="BI169">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="BJ169">
+        <v>2.16</v>
+      </c>
+      <c r="BK169">
         <v>2.05</v>
-      </c>
-      <c r="BK169">
-        <v>2.03</v>
       </c>
       <c r="BL169">
         <v>1.7</v>
       </c>
       <c r="BM169">
+        <v>2.67</v>
+      </c>
+      <c r="BN169">
+        <v>1.39</v>
+      </c>
+      <c r="BO169">
+        <v>3.68</v>
+      </c>
+      <c r="BP169">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7820491</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45752.64583333334</v>
+      </c>
+      <c r="F170">
+        <v>12</v>
+      </c>
+      <c r="G170" t="s">
+        <v>87</v>
+      </c>
+      <c r="H170" t="s">
+        <v>90</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>2</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="N170">
+        <v>3</v>
+      </c>
+      <c r="O170" t="s">
+        <v>200</v>
+      </c>
+      <c r="P170" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q170">
+        <v>2.75</v>
+      </c>
+      <c r="R170">
+        <v>1.91</v>
+      </c>
+      <c r="S170">
+        <v>5</v>
+      </c>
+      <c r="T170">
+        <v>1.62</v>
+      </c>
+      <c r="U170">
+        <v>2.2</v>
+      </c>
+      <c r="V170">
+        <v>4</v>
+      </c>
+      <c r="W170">
+        <v>1.22</v>
+      </c>
+      <c r="X170">
+        <v>13</v>
+      </c>
+      <c r="Y170">
+        <v>1.04</v>
+      </c>
+      <c r="Z170">
+        <v>2</v>
+      </c>
+      <c r="AA170">
+        <v>3</v>
+      </c>
+      <c r="AB170">
+        <v>4.5</v>
+      </c>
+      <c r="AC170">
+        <v>1.14</v>
+      </c>
+      <c r="AD170">
+        <v>6.21</v>
+      </c>
+      <c r="AE170">
+        <v>1.53</v>
+      </c>
+      <c r="AF170">
+        <v>2.3</v>
+      </c>
+      <c r="AG170">
+        <v>2.7</v>
+      </c>
+      <c r="AH170">
+        <v>1.44</v>
+      </c>
+      <c r="AI170">
+        <v>2.25</v>
+      </c>
+      <c r="AJ170">
+        <v>1.57</v>
+      </c>
+      <c r="AK170">
+        <v>1.22</v>
+      </c>
+      <c r="AL170">
+        <v>1.33</v>
+      </c>
+      <c r="AM170">
+        <v>1.73</v>
+      </c>
+      <c r="AN170">
+        <v>3</v>
+      </c>
+      <c r="AO170">
+        <v>0.8</v>
+      </c>
+      <c r="AP170">
+        <v>3</v>
+      </c>
+      <c r="AQ170">
+        <v>0.67</v>
+      </c>
+      <c r="AR170">
+        <v>1.32</v>
+      </c>
+      <c r="AS170">
+        <v>0.98</v>
+      </c>
+      <c r="AT170">
+        <v>2.3</v>
+      </c>
+      <c r="AU170">
+        <v>5</v>
+      </c>
+      <c r="AV170">
+        <v>4</v>
+      </c>
+      <c r="AW170">
+        <v>4</v>
+      </c>
+      <c r="AX170">
+        <v>1</v>
+      </c>
+      <c r="AY170">
+        <v>9</v>
+      </c>
+      <c r="AZ170">
+        <v>5</v>
+      </c>
+      <c r="BA170">
+        <v>10</v>
+      </c>
+      <c r="BB170">
+        <v>3</v>
+      </c>
+      <c r="BC170">
+        <v>13</v>
+      </c>
+      <c r="BD170">
+        <v>1.67</v>
+      </c>
+      <c r="BE170">
+        <v>8.5</v>
+      </c>
+      <c r="BF170">
+        <v>2.45</v>
+      </c>
+      <c r="BG170">
+        <v>1.31</v>
+      </c>
+      <c r="BH170">
+        <v>2.92</v>
+      </c>
+      <c r="BI170">
+        <v>1.67</v>
+      </c>
+      <c r="BJ170">
+        <v>2.1</v>
+      </c>
+      <c r="BK170">
+        <v>2.04</v>
+      </c>
+      <c r="BL170">
+        <v>1.69</v>
+      </c>
+      <c r="BM170">
+        <v>2.71</v>
+      </c>
+      <c r="BN170">
+        <v>1.38</v>
+      </c>
+      <c r="BO170">
+        <v>3.72</v>
+      </c>
+      <c r="BP170">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7820481</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45752.75</v>
+      </c>
+      <c r="F171">
+        <v>12</v>
+      </c>
+      <c r="G171" t="s">
+        <v>93</v>
+      </c>
+      <c r="H171" t="s">
+        <v>96</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>2</v>
+      </c>
+      <c r="L171">
+        <v>3</v>
+      </c>
+      <c r="M171">
+        <v>3</v>
+      </c>
+      <c r="N171">
+        <v>6</v>
+      </c>
+      <c r="O171" t="s">
+        <v>201</v>
+      </c>
+      <c r="P171" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q171">
+        <v>2.38</v>
+      </c>
+      <c r="R171">
+        <v>1.95</v>
+      </c>
+      <c r="S171">
+        <v>6.5</v>
+      </c>
+      <c r="T171">
+        <v>1.57</v>
+      </c>
+      <c r="U171">
+        <v>2.25</v>
+      </c>
+      <c r="V171">
+        <v>3.75</v>
+      </c>
+      <c r="W171">
+        <v>1.25</v>
+      </c>
+      <c r="X171">
+        <v>13</v>
+      </c>
+      <c r="Y171">
+        <v>1.04</v>
+      </c>
+      <c r="Z171">
+        <v>1.67</v>
+      </c>
+      <c r="AA171">
+        <v>3.6</v>
+      </c>
+      <c r="AB171">
+        <v>5.75</v>
+      </c>
+      <c r="AC171">
+        <v>1.11</v>
+      </c>
+      <c r="AD171">
+        <v>6.87</v>
+      </c>
+      <c r="AE171">
+        <v>1.5</v>
+      </c>
+      <c r="AF171">
+        <v>2.4</v>
+      </c>
+      <c r="AG171">
+        <v>2.6</v>
+      </c>
+      <c r="AH171">
+        <v>1.48</v>
+      </c>
+      <c r="AI171">
+        <v>2.5</v>
+      </c>
+      <c r="AJ171">
+        <v>1.5</v>
+      </c>
+      <c r="AK171">
+        <v>1.13</v>
+      </c>
+      <c r="AL171">
+        <v>1.25</v>
+      </c>
+      <c r="AM171">
+        <v>2.15</v>
+      </c>
+      <c r="AN171">
+        <v>2.6</v>
+      </c>
+      <c r="AO171">
+        <v>0.6</v>
+      </c>
+      <c r="AP171">
+        <v>2.33</v>
+      </c>
+      <c r="AQ171">
+        <v>0.67</v>
+      </c>
+      <c r="AR171">
+        <v>1.62</v>
+      </c>
+      <c r="AS171">
+        <v>1.36</v>
+      </c>
+      <c r="AT171">
+        <v>2.98</v>
+      </c>
+      <c r="AU171">
+        <v>8</v>
+      </c>
+      <c r="AV171">
+        <v>8</v>
+      </c>
+      <c r="AW171">
+        <v>8</v>
+      </c>
+      <c r="AX171">
+        <v>3</v>
+      </c>
+      <c r="AY171">
+        <v>18</v>
+      </c>
+      <c r="AZ171">
+        <v>14</v>
+      </c>
+      <c r="BA171">
+        <v>5</v>
+      </c>
+      <c r="BB171">
+        <v>5</v>
+      </c>
+      <c r="BC171">
+        <v>10</v>
+      </c>
+      <c r="BD171">
+        <v>1.44</v>
+      </c>
+      <c r="BE171">
+        <v>9</v>
+      </c>
+      <c r="BF171">
+        <v>3.1</v>
+      </c>
+      <c r="BG171">
+        <v>1.31</v>
+      </c>
+      <c r="BH171">
+        <v>2.92</v>
+      </c>
+      <c r="BI171">
+        <v>1.7</v>
+      </c>
+      <c r="BJ171">
+        <v>2.05</v>
+      </c>
+      <c r="BK171">
+        <v>2.03</v>
+      </c>
+      <c r="BL171">
+        <v>1.7</v>
+      </c>
+      <c r="BM171">
         <v>2.64</v>
       </c>
-      <c r="BN169">
+      <c r="BN171">
         <v>1.4</v>
       </c>
-      <c r="BO169">
+      <c r="BO171">
         <v>3.58</v>
       </c>
-      <c r="BP169">
+      <c r="BP171">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7820493</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45752.75</v>
+      </c>
+      <c r="F172">
+        <v>12</v>
+      </c>
+      <c r="G172" t="s">
+        <v>91</v>
+      </c>
+      <c r="H172" t="s">
+        <v>92</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>2</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>2</v>
+      </c>
+      <c r="O172" t="s">
+        <v>202</v>
+      </c>
+      <c r="P172" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q172">
+        <v>2.63</v>
+      </c>
+      <c r="R172">
+        <v>1.95</v>
+      </c>
+      <c r="S172">
+        <v>5.5</v>
+      </c>
+      <c r="T172">
+        <v>1.53</v>
+      </c>
+      <c r="U172">
+        <v>2.38</v>
+      </c>
+      <c r="V172">
+        <v>3.75</v>
+      </c>
+      <c r="W172">
+        <v>1.25</v>
+      </c>
+      <c r="X172">
+        <v>11</v>
+      </c>
+      <c r="Y172">
+        <v>1.05</v>
+      </c>
+      <c r="Z172">
+        <v>1.85</v>
+      </c>
+      <c r="AA172">
+        <v>3</v>
+      </c>
+      <c r="AB172">
+        <v>5.25</v>
+      </c>
+      <c r="AC172">
+        <v>1.11</v>
+      </c>
+      <c r="AD172">
+        <v>7.2</v>
+      </c>
+      <c r="AE172">
+        <v>1.49</v>
+      </c>
+      <c r="AF172">
+        <v>2.55</v>
+      </c>
+      <c r="AG172">
+        <v>2.5</v>
+      </c>
+      <c r="AH172">
+        <v>1.5</v>
+      </c>
+      <c r="AI172">
+        <v>2.2</v>
+      </c>
+      <c r="AJ172">
+        <v>1.62</v>
+      </c>
+      <c r="AK172">
+        <v>1.18</v>
+      </c>
+      <c r="AL172">
+        <v>1.28</v>
+      </c>
+      <c r="AM172">
+        <v>1.85</v>
+      </c>
+      <c r="AN172">
+        <v>0.4</v>
+      </c>
+      <c r="AO172">
+        <v>0.67</v>
+      </c>
+      <c r="AP172">
+        <v>0.83</v>
+      </c>
+      <c r="AQ172">
+        <v>0.57</v>
+      </c>
+      <c r="AR172">
+        <v>2.19</v>
+      </c>
+      <c r="AS172">
+        <v>1.14</v>
+      </c>
+      <c r="AT172">
+        <v>3.33</v>
+      </c>
+      <c r="AU172">
+        <v>7</v>
+      </c>
+      <c r="AV172">
+        <v>3</v>
+      </c>
+      <c r="AW172">
+        <v>9</v>
+      </c>
+      <c r="AX172">
+        <v>17</v>
+      </c>
+      <c r="AY172">
+        <v>17</v>
+      </c>
+      <c r="AZ172">
+        <v>22</v>
+      </c>
+      <c r="BA172">
+        <v>9</v>
+      </c>
+      <c r="BB172">
+        <v>5</v>
+      </c>
+      <c r="BC172">
+        <v>14</v>
+      </c>
+      <c r="BD172">
+        <v>1.44</v>
+      </c>
+      <c r="BE172">
+        <v>9</v>
+      </c>
+      <c r="BF172">
+        <v>3.1</v>
+      </c>
+      <c r="BG172">
+        <v>1.24</v>
+      </c>
+      <c r="BH172">
+        <v>3.34</v>
+      </c>
+      <c r="BI172">
+        <v>1.48</v>
+      </c>
+      <c r="BJ172">
+        <v>2.4</v>
+      </c>
+      <c r="BK172">
+        <v>1.85</v>
+      </c>
+      <c r="BL172">
+        <v>1.85</v>
+      </c>
+      <c r="BM172">
+        <v>2.38</v>
+      </c>
+      <c r="BN172">
+        <v>1.49</v>
+      </c>
+      <c r="BO172">
+        <v>3.14</v>
+      </c>
+      <c r="BP172">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7820492</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45752.85416666666</v>
+      </c>
+      <c r="F173">
+        <v>12</v>
+      </c>
+      <c r="G173" t="s">
+        <v>88</v>
+      </c>
+      <c r="H173" t="s">
+        <v>95</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="K173">
+        <v>2</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <v>1</v>
+      </c>
+      <c r="N173">
+        <v>2</v>
+      </c>
+      <c r="O173" t="s">
+        <v>169</v>
+      </c>
+      <c r="P173" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q173">
+        <v>5.5</v>
+      </c>
+      <c r="R173">
+        <v>2</v>
+      </c>
+      <c r="S173">
+        <v>2.4</v>
+      </c>
+      <c r="T173">
+        <v>1.5</v>
+      </c>
+      <c r="U173">
+        <v>2.5</v>
+      </c>
+      <c r="V173">
+        <v>3.5</v>
+      </c>
+      <c r="W173">
+        <v>1.29</v>
+      </c>
+      <c r="X173">
+        <v>11</v>
+      </c>
+      <c r="Y173">
+        <v>1.05</v>
+      </c>
+      <c r="Z173">
+        <v>5.5</v>
+      </c>
+      <c r="AA173">
+        <v>3.1</v>
+      </c>
+      <c r="AB173">
+        <v>1.75</v>
+      </c>
+      <c r="AC173">
+        <v>1.1</v>
+      </c>
+      <c r="AD173">
+        <v>7.43</v>
+      </c>
+      <c r="AE173">
+        <v>1.4</v>
+      </c>
+      <c r="AF173">
+        <v>3.02</v>
+      </c>
+      <c r="AG173">
+        <v>2.3</v>
+      </c>
+      <c r="AH173">
+        <v>1.6</v>
+      </c>
+      <c r="AI173">
+        <v>2.1</v>
+      </c>
+      <c r="AJ173">
+        <v>1.67</v>
+      </c>
+      <c r="AK173">
+        <v>1.95</v>
+      </c>
+      <c r="AL173">
+        <v>1.25</v>
+      </c>
+      <c r="AM173">
+        <v>1.18</v>
+      </c>
+      <c r="AN173">
+        <v>1.4</v>
+      </c>
+      <c r="AO173">
+        <v>1.4</v>
+      </c>
+      <c r="AP173">
+        <v>1.33</v>
+      </c>
+      <c r="AQ173">
+        <v>1.33</v>
+      </c>
+      <c r="AR173">
+        <v>1.82</v>
+      </c>
+      <c r="AS173">
+        <v>1.7</v>
+      </c>
+      <c r="AT173">
+        <v>3.52</v>
+      </c>
+      <c r="AU173">
+        <v>7</v>
+      </c>
+      <c r="AV173">
+        <v>8</v>
+      </c>
+      <c r="AW173">
+        <v>8</v>
+      </c>
+      <c r="AX173">
+        <v>5</v>
+      </c>
+      <c r="AY173">
+        <v>20</v>
+      </c>
+      <c r="AZ173">
+        <v>15</v>
+      </c>
+      <c r="BA173">
+        <v>4</v>
+      </c>
+      <c r="BB173">
+        <v>5</v>
+      </c>
+      <c r="BC173">
+        <v>9</v>
+      </c>
+      <c r="BD173">
+        <v>3.1</v>
+      </c>
+      <c r="BE173">
+        <v>9</v>
+      </c>
+      <c r="BF173">
+        <v>1.44</v>
+      </c>
+      <c r="BG173">
+        <v>1.29</v>
+      </c>
+      <c r="BH173">
+        <v>3.04</v>
+      </c>
+      <c r="BI173">
+        <v>1.57</v>
+      </c>
+      <c r="BJ173">
+        <v>2.19</v>
+      </c>
+      <c r="BK173">
+        <v>2.05</v>
+      </c>
+      <c r="BL173">
+        <v>1.7</v>
+      </c>
+      <c r="BM173">
+        <v>2.6</v>
+      </c>
+      <c r="BN173">
+        <v>1.41</v>
+      </c>
+      <c r="BO173">
+        <v>3.5</v>
+      </c>
+      <c r="BP173">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="274">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -625,6 +625,27 @@
     <t>['16', '65']</t>
   </si>
   <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['61']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
+    <t>['5', '12', '24', '31']</t>
+  </si>
+  <si>
+    <t>['42', '46', '55', '75']</t>
+  </si>
+  <si>
+    <t>['57']</t>
+  </si>
+  <si>
+    <t>['45', '49', '90+1']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -686,9 +707,6 @@
   </si>
   <si>
     <t>['62', '75', '80']</t>
-  </si>
-  <si>
-    <t>['57']</t>
   </si>
   <si>
     <t>['64']</t>
@@ -809,6 +827,15 @@
   </si>
   <si>
     <t>['20', '63', '80']</t>
+  </si>
+  <si>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['56', '81']</t>
+  </si>
+  <si>
+    <t>['13', '74']</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1426,7 +1453,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1710,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0.67</v>
@@ -1838,7 +1865,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2125,7 +2152,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2250,7 +2277,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2328,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
         <v>1.83</v>
@@ -2456,7 +2483,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -3074,7 +3101,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -4182,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ15">
         <v>2.2</v>
@@ -4597,7 +4624,7 @@
         <v>1</v>
       </c>
       <c r="AQ17">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4800,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18">
         <v>0.4</v>
@@ -4928,7 +4955,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5421,7 +5448,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ21">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5546,7 +5573,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="Q22">
         <v>2.63</v>
@@ -5627,7 +5654,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ22">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5752,7 +5779,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5833,7 +5860,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ23">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5958,7 +5985,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6370,7 +6397,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6448,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ26">
         <v>1.4</v>
@@ -6657,7 +6684,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ27">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -6782,7 +6809,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6863,7 +6890,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ28">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -7066,7 +7093,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ29">
         <v>0.83</v>
@@ -7272,7 +7299,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>2</v>
@@ -7687,7 +7714,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ32">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR32">
         <v>1.19</v>
@@ -8096,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34">
         <v>0.33</v>
@@ -8430,7 +8457,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8508,7 +8535,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ36">
         <v>1.5</v>
@@ -9254,7 +9281,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9335,7 +9362,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR40">
         <v>1.12</v>
@@ -9538,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ41">
         <v>0</v>
@@ -9950,10 +9977,10 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -10078,7 +10105,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10284,7 +10311,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10362,7 +10389,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ45">
         <v>1.83</v>
@@ -10490,7 +10517,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10571,7 +10598,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ46">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR46">
         <v>2.39</v>
@@ -10696,7 +10723,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10902,7 +10929,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11189,7 +11216,7 @@
         <v>2</v>
       </c>
       <c r="AQ49">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR49">
         <v>1.6</v>
@@ -11520,7 +11547,7 @@
         <v>131</v>
       </c>
       <c r="P51" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="Q51">
         <v>4</v>
@@ -11804,7 +11831,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ52">
         <v>2.2</v>
@@ -12138,7 +12165,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12425,7 +12452,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ55">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR55">
         <v>1.6</v>
@@ -12628,7 +12655,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ56">
         <v>1.4</v>
@@ -12837,7 +12864,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ57">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR57">
         <v>0.73</v>
@@ -12962,7 +12989,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13040,10 +13067,10 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR58">
         <v>0.9</v>
@@ -13580,7 +13607,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13661,7 +13688,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR61">
         <v>0.96</v>
@@ -13864,7 +13891,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ62">
         <v>1.33</v>
@@ -14073,7 +14100,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ63">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR63">
         <v>1.97</v>
@@ -14276,7 +14303,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14688,7 +14715,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ66">
         <v>1.43</v>
@@ -14816,7 +14843,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -14897,7 +14924,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ67">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR67">
         <v>1.78</v>
@@ -15022,7 +15049,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15100,7 +15127,7 @@
         <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
         <v>1.5</v>
@@ -15718,7 +15745,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ71">
         <v>0.57</v>
@@ -15927,7 +15954,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ72">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR72">
         <v>1.21</v>
@@ -16052,7 +16079,7 @@
         <v>100</v>
       </c>
       <c r="P73" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q73">
         <v>4.5</v>
@@ -16336,7 +16363,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ74">
         <v>0.33</v>
@@ -16542,10 +16569,10 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ75">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR75">
         <v>1.66</v>
@@ -16876,7 +16903,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16957,7 +16984,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ77">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR77">
         <v>1.47</v>
@@ -17082,7 +17109,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17494,7 +17521,7 @@
         <v>149</v>
       </c>
       <c r="P80" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q80">
         <v>3.2</v>
@@ -17700,7 +17727,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17778,7 +17805,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ81">
         <v>2.2</v>
@@ -17906,7 +17933,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18318,7 +18345,7 @@
         <v>153</v>
       </c>
       <c r="P84" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q84">
         <v>2.75</v>
@@ -18730,7 +18757,7 @@
         <v>155</v>
       </c>
       <c r="P86" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q86">
         <v>3.5</v>
@@ -19142,7 +19169,7 @@
         <v>157</v>
       </c>
       <c r="P88" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19223,7 +19250,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ88">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR88">
         <v>1.23</v>
@@ -19348,7 +19375,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19554,7 +19581,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19838,7 +19865,7 @@
         <v>1.5</v>
       </c>
       <c r="AP91">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ91">
         <v>1.17</v>
@@ -19966,7 +19993,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20047,7 +20074,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR92">
         <v>1.86</v>
@@ -20253,7 +20280,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ93">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR93">
         <v>1.29</v>
@@ -20456,7 +20483,7 @@
         <v>0</v>
       </c>
       <c r="AP94">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ94">
         <v>0.67</v>
@@ -20665,7 +20692,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ95">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR95">
         <v>1.94</v>
@@ -20790,7 +20817,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -20868,7 +20895,7 @@
         <v>0</v>
       </c>
       <c r="AP96">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ96">
         <v>0.67</v>
@@ -20996,7 +21023,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21695,7 +21722,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ100">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR100">
         <v>1.73</v>
@@ -21820,7 +21847,7 @@
         <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="Q101">
         <v>2.88</v>
@@ -21898,7 +21925,7 @@
         <v>0.33</v>
       </c>
       <c r="AP101">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ101">
         <v>0.57</v>
@@ -22107,7 +22134,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ102">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR102">
         <v>1.05</v>
@@ -22310,7 +22337,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ103">
         <v>1.33</v>
@@ -22516,10 +22543,10 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ104">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR104">
         <v>1.38</v>
@@ -22722,7 +22749,7 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ105">
         <v>1.43</v>
@@ -23262,7 +23289,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23468,7 +23495,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23674,7 +23701,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -23958,7 +23985,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ111">
         <v>0.57</v>
@@ -24086,7 +24113,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24370,10 +24397,10 @@
         <v>0.25</v>
       </c>
       <c r="AP113">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ113">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR113">
         <v>1.81</v>
@@ -24498,7 +24525,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24704,7 +24731,7 @@
         <v>154</v>
       </c>
       <c r="P115" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24910,7 +24937,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25116,7 +25143,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25194,10 +25221,10 @@
         <v>0</v>
       </c>
       <c r="AP117">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ117">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR117">
         <v>1.81</v>
@@ -25403,7 +25430,7 @@
         <v>1</v>
       </c>
       <c r="AQ118">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR118">
         <v>1.5</v>
@@ -25528,7 +25555,7 @@
         <v>100</v>
       </c>
       <c r="P119" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25609,7 +25636,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ119">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR119">
         <v>1.24</v>
@@ -25734,7 +25761,7 @@
         <v>174</v>
       </c>
       <c r="P120" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -26146,7 +26173,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26352,7 +26379,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26433,7 +26460,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ123">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR123">
         <v>1.76</v>
@@ -26636,7 +26663,7 @@
         <v>1.25</v>
       </c>
       <c r="AP124">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ124">
         <v>1.5</v>
@@ -27051,7 +27078,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ126">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR126">
         <v>2.03</v>
@@ -27382,7 +27409,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28206,7 +28233,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28824,7 +28851,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -28902,7 +28929,7 @@
         <v>0</v>
       </c>
       <c r="AP135">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ135">
         <v>0.67</v>
@@ -29314,7 +29341,7 @@
         <v>1.5</v>
       </c>
       <c r="AP137">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ137">
         <v>1.33</v>
@@ -29729,7 +29756,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ139">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR139">
         <v>1.9</v>
@@ -30550,10 +30577,10 @@
         <v>2</v>
       </c>
       <c r="AP143">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ143">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR143">
         <v>1.56</v>
@@ -30756,10 +30783,10 @@
         <v>0.2</v>
       </c>
       <c r="AP144">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ144">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR144">
         <v>1.91</v>
@@ -30884,7 +30911,7 @@
         <v>186</v>
       </c>
       <c r="P145" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -30965,7 +30992,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ145">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR145">
         <v>1.68</v>
@@ -31090,7 +31117,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31168,10 +31195,10 @@
         <v>0.75</v>
       </c>
       <c r="AP146">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ146">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR146">
         <v>1.61</v>
@@ -31296,7 +31323,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31374,10 +31401,10 @@
         <v>0.33</v>
       </c>
       <c r="AP147">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ147">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR147">
         <v>1.38</v>
@@ -31502,7 +31529,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31583,7 +31610,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ148">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR148">
         <v>1.46</v>
@@ -31708,7 +31735,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -31786,7 +31813,7 @@
         <v>0.25</v>
       </c>
       <c r="AP149">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ149">
         <v>0.67</v>
@@ -31914,7 +31941,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -31992,7 +32019,7 @@
         <v>0.8</v>
       </c>
       <c r="AP150">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ150">
         <v>1</v>
@@ -32532,7 +32559,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32944,7 +32971,7 @@
         <v>192</v>
       </c>
       <c r="P155" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33150,7 +33177,7 @@
         <v>177</v>
       </c>
       <c r="P156" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -34180,7 +34207,7 @@
         <v>175</v>
       </c>
       <c r="P161" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34592,7 +34619,7 @@
         <v>196</v>
       </c>
       <c r="P163" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="Q163">
         <v>2.1</v>
@@ -34798,7 +34825,7 @@
         <v>197</v>
       </c>
       <c r="P164" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Q164">
         <v>3.75</v>
@@ -35622,7 +35649,7 @@
         <v>100</v>
       </c>
       <c r="P168" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Q168">
         <v>4.33</v>
@@ -36034,7 +36061,7 @@
         <v>200</v>
       </c>
       <c r="P170" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="Q170">
         <v>2.75</v>
@@ -36240,7 +36267,7 @@
         <v>201</v>
       </c>
       <c r="P171" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="Q171">
         <v>2.38</v>
@@ -36652,7 +36679,7 @@
         <v>169</v>
       </c>
       <c r="P173" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="Q173">
         <v>5.5</v>
@@ -36809,6 +36836,1654 @@
       </c>
       <c r="BP173">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7820482</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45753.64583333334</v>
+      </c>
+      <c r="F174">
+        <v>12</v>
+      </c>
+      <c r="G174" t="s">
+        <v>94</v>
+      </c>
+      <c r="H174" t="s">
+        <v>84</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>1</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="N174">
+        <v>1</v>
+      </c>
+      <c r="O174" t="s">
+        <v>203</v>
+      </c>
+      <c r="P174" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q174">
+        <v>2.88</v>
+      </c>
+      <c r="R174">
+        <v>1.95</v>
+      </c>
+      <c r="S174">
+        <v>4.5</v>
+      </c>
+      <c r="T174">
+        <v>1.57</v>
+      </c>
+      <c r="U174">
+        <v>2.25</v>
+      </c>
+      <c r="V174">
+        <v>3.75</v>
+      </c>
+      <c r="W174">
+        <v>1.25</v>
+      </c>
+      <c r="X174">
+        <v>11</v>
+      </c>
+      <c r="Y174">
+        <v>1.05</v>
+      </c>
+      <c r="Z174">
+        <v>2.05</v>
+      </c>
+      <c r="AA174">
+        <v>3.4</v>
+      </c>
+      <c r="AB174">
+        <v>3.6</v>
+      </c>
+      <c r="AC174">
+        <v>1.09</v>
+      </c>
+      <c r="AD174">
+        <v>7</v>
+      </c>
+      <c r="AE174">
+        <v>1.48</v>
+      </c>
+      <c r="AF174">
+        <v>2.62</v>
+      </c>
+      <c r="AG174">
+        <v>2.4</v>
+      </c>
+      <c r="AH174">
+        <v>1.53</v>
+      </c>
+      <c r="AI174">
+        <v>2.2</v>
+      </c>
+      <c r="AJ174">
+        <v>1.62</v>
+      </c>
+      <c r="AK174">
+        <v>1.29</v>
+      </c>
+      <c r="AL174">
+        <v>1.34</v>
+      </c>
+      <c r="AM174">
+        <v>1.68</v>
+      </c>
+      <c r="AN174">
+        <v>1.33</v>
+      </c>
+      <c r="AO174">
+        <v>1</v>
+      </c>
+      <c r="AP174">
+        <v>1.57</v>
+      </c>
+      <c r="AQ174">
+        <v>0.8</v>
+      </c>
+      <c r="AR174">
+        <v>1.83</v>
+      </c>
+      <c r="AS174">
+        <v>1.36</v>
+      </c>
+      <c r="AT174">
+        <v>3.19</v>
+      </c>
+      <c r="AU174">
+        <v>2</v>
+      </c>
+      <c r="AV174">
+        <v>2</v>
+      </c>
+      <c r="AW174">
+        <v>8</v>
+      </c>
+      <c r="AX174">
+        <v>3</v>
+      </c>
+      <c r="AY174">
+        <v>10</v>
+      </c>
+      <c r="AZ174">
+        <v>5</v>
+      </c>
+      <c r="BA174">
+        <v>8</v>
+      </c>
+      <c r="BB174">
+        <v>2</v>
+      </c>
+      <c r="BC174">
+        <v>10</v>
+      </c>
+      <c r="BD174">
+        <v>1.58</v>
+      </c>
+      <c r="BE174">
+        <v>6.5</v>
+      </c>
+      <c r="BF174">
+        <v>2.63</v>
+      </c>
+      <c r="BG174">
+        <v>1.49</v>
+      </c>
+      <c r="BH174">
+        <v>2.4</v>
+      </c>
+      <c r="BI174">
+        <v>1.8</v>
+      </c>
+      <c r="BJ174">
+        <v>1.89</v>
+      </c>
+      <c r="BK174">
+        <v>2.28</v>
+      </c>
+      <c r="BL174">
+        <v>1.54</v>
+      </c>
+      <c r="BM174">
+        <v>2.95</v>
+      </c>
+      <c r="BN174">
+        <v>1.33</v>
+      </c>
+      <c r="BO174">
+        <v>3.95</v>
+      </c>
+      <c r="BP174">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7820487</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45753.64583333334</v>
+      </c>
+      <c r="F175">
+        <v>12</v>
+      </c>
+      <c r="G175" t="s">
+        <v>74</v>
+      </c>
+      <c r="H175" t="s">
+        <v>76</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <v>1</v>
+      </c>
+      <c r="N175">
+        <v>2</v>
+      </c>
+      <c r="O175" t="s">
+        <v>204</v>
+      </c>
+      <c r="P175" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q175">
+        <v>3.25</v>
+      </c>
+      <c r="R175">
+        <v>1.91</v>
+      </c>
+      <c r="S175">
+        <v>4</v>
+      </c>
+      <c r="T175">
+        <v>1.57</v>
+      </c>
+      <c r="U175">
+        <v>2.25</v>
+      </c>
+      <c r="V175">
+        <v>3.75</v>
+      </c>
+      <c r="W175">
+        <v>1.25</v>
+      </c>
+      <c r="X175">
+        <v>13</v>
+      </c>
+      <c r="Y175">
+        <v>1.04</v>
+      </c>
+      <c r="Z175">
+        <v>2.38</v>
+      </c>
+      <c r="AA175">
+        <v>3.2</v>
+      </c>
+      <c r="AB175">
+        <v>3.1</v>
+      </c>
+      <c r="AC175">
+        <v>1.1</v>
+      </c>
+      <c r="AD175">
+        <v>6.5</v>
+      </c>
+      <c r="AE175">
+        <v>1.5</v>
+      </c>
+      <c r="AF175">
+        <v>2.4</v>
+      </c>
+      <c r="AG175">
+        <v>2.6</v>
+      </c>
+      <c r="AH175">
+        <v>1.48</v>
+      </c>
+      <c r="AI175">
+        <v>2.1</v>
+      </c>
+      <c r="AJ175">
+        <v>1.67</v>
+      </c>
+      <c r="AK175">
+        <v>1.35</v>
+      </c>
+      <c r="AL175">
+        <v>1.35</v>
+      </c>
+      <c r="AM175">
+        <v>1.55</v>
+      </c>
+      <c r="AN175">
+        <v>1.6</v>
+      </c>
+      <c r="AO175">
+        <v>1.6</v>
+      </c>
+      <c r="AP175">
+        <v>1.5</v>
+      </c>
+      <c r="AQ175">
+        <v>1.5</v>
+      </c>
+      <c r="AR175">
+        <v>2.03</v>
+      </c>
+      <c r="AS175">
+        <v>0.99</v>
+      </c>
+      <c r="AT175">
+        <v>3.02</v>
+      </c>
+      <c r="AU175">
+        <v>5</v>
+      </c>
+      <c r="AV175">
+        <v>10</v>
+      </c>
+      <c r="AW175">
+        <v>2</v>
+      </c>
+      <c r="AX175">
+        <v>2</v>
+      </c>
+      <c r="AY175">
+        <v>7</v>
+      </c>
+      <c r="AZ175">
+        <v>12</v>
+      </c>
+      <c r="BA175">
+        <v>2</v>
+      </c>
+      <c r="BB175">
+        <v>2</v>
+      </c>
+      <c r="BC175">
+        <v>4</v>
+      </c>
+      <c r="BD175">
+        <v>1.94</v>
+      </c>
+      <c r="BE175">
+        <v>6.4</v>
+      </c>
+      <c r="BF175">
+        <v>2.07</v>
+      </c>
+      <c r="BG175">
+        <v>1.44</v>
+      </c>
+      <c r="BH175">
+        <v>2.55</v>
+      </c>
+      <c r="BI175">
+        <v>1.75</v>
+      </c>
+      <c r="BJ175">
+        <v>1.95</v>
+      </c>
+      <c r="BK175">
+        <v>2.2</v>
+      </c>
+      <c r="BL175">
+        <v>1.58</v>
+      </c>
+      <c r="BM175">
+        <v>2.85</v>
+      </c>
+      <c r="BN175">
+        <v>1.36</v>
+      </c>
+      <c r="BO175">
+        <v>3.8</v>
+      </c>
+      <c r="BP175">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7820485</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45753.75</v>
+      </c>
+      <c r="F176">
+        <v>12</v>
+      </c>
+      <c r="G176" t="s">
+        <v>83</v>
+      </c>
+      <c r="H176" t="s">
+        <v>75</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
+        <v>205</v>
+      </c>
+      <c r="P176" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q176">
+        <v>2.05</v>
+      </c>
+      <c r="R176">
+        <v>2.1</v>
+      </c>
+      <c r="S176">
+        <v>8</v>
+      </c>
+      <c r="T176">
+        <v>1.44</v>
+      </c>
+      <c r="U176">
+        <v>2.63</v>
+      </c>
+      <c r="V176">
+        <v>3.4</v>
+      </c>
+      <c r="W176">
+        <v>1.3</v>
+      </c>
+      <c r="X176">
+        <v>10</v>
+      </c>
+      <c r="Y176">
+        <v>1.06</v>
+      </c>
+      <c r="Z176">
+        <v>1.45</v>
+      </c>
+      <c r="AA176">
+        <v>4</v>
+      </c>
+      <c r="AB176">
+        <v>8.5</v>
+      </c>
+      <c r="AC176">
+        <v>1.06</v>
+      </c>
+      <c r="AD176">
+        <v>8.5</v>
+      </c>
+      <c r="AE176">
+        <v>1.38</v>
+      </c>
+      <c r="AF176">
+        <v>3</v>
+      </c>
+      <c r="AG176">
+        <v>2.2</v>
+      </c>
+      <c r="AH176">
+        <v>1.65</v>
+      </c>
+      <c r="AI176">
+        <v>2.38</v>
+      </c>
+      <c r="AJ176">
+        <v>1.53</v>
+      </c>
+      <c r="AK176">
+        <v>1.1</v>
+      </c>
+      <c r="AL176">
+        <v>1.22</v>
+      </c>
+      <c r="AM176">
+        <v>2.65</v>
+      </c>
+      <c r="AN176">
+        <v>2.67</v>
+      </c>
+      <c r="AO176">
+        <v>1.4</v>
+      </c>
+      <c r="AP176">
+        <v>2.71</v>
+      </c>
+      <c r="AQ176">
+        <v>1.17</v>
+      </c>
+      <c r="AR176">
+        <v>1.58</v>
+      </c>
+      <c r="AS176">
+        <v>1.5</v>
+      </c>
+      <c r="AT176">
+        <v>3.08</v>
+      </c>
+      <c r="AU176">
+        <v>6</v>
+      </c>
+      <c r="AV176">
+        <v>0</v>
+      </c>
+      <c r="AW176">
+        <v>5</v>
+      </c>
+      <c r="AX176">
+        <v>8</v>
+      </c>
+      <c r="AY176">
+        <v>13</v>
+      </c>
+      <c r="AZ176">
+        <v>9</v>
+      </c>
+      <c r="BA176">
+        <v>6</v>
+      </c>
+      <c r="BB176">
+        <v>2</v>
+      </c>
+      <c r="BC176">
+        <v>8</v>
+      </c>
+      <c r="BD176">
+        <v>1.26</v>
+      </c>
+      <c r="BE176">
+        <v>7.5</v>
+      </c>
+      <c r="BF176">
+        <v>4.1</v>
+      </c>
+      <c r="BG176">
+        <v>1.38</v>
+      </c>
+      <c r="BH176">
+        <v>2.75</v>
+      </c>
+      <c r="BI176">
+        <v>1.64</v>
+      </c>
+      <c r="BJ176">
+        <v>2.1</v>
+      </c>
+      <c r="BK176">
+        <v>2</v>
+      </c>
+      <c r="BL176">
+        <v>1.71</v>
+      </c>
+      <c r="BM176">
+        <v>2.55</v>
+      </c>
+      <c r="BN176">
+        <v>1.44</v>
+      </c>
+      <c r="BO176">
+        <v>3.3</v>
+      </c>
+      <c r="BP176">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7820483</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45753.84375</v>
+      </c>
+      <c r="F177">
+        <v>12</v>
+      </c>
+      <c r="G177" t="s">
+        <v>98</v>
+      </c>
+      <c r="H177" t="s">
+        <v>73</v>
+      </c>
+      <c r="I177">
+        <v>4</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>4</v>
+      </c>
+      <c r="L177">
+        <v>4</v>
+      </c>
+      <c r="M177">
+        <v>1</v>
+      </c>
+      <c r="N177">
+        <v>5</v>
+      </c>
+      <c r="O177" t="s">
+        <v>206</v>
+      </c>
+      <c r="P177" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q177">
+        <v>2.38</v>
+      </c>
+      <c r="R177">
+        <v>2.1</v>
+      </c>
+      <c r="S177">
+        <v>5.5</v>
+      </c>
+      <c r="T177">
+        <v>1.44</v>
+      </c>
+      <c r="U177">
+        <v>2.63</v>
+      </c>
+      <c r="V177">
+        <v>3.25</v>
+      </c>
+      <c r="W177">
+        <v>1.33</v>
+      </c>
+      <c r="X177">
+        <v>10</v>
+      </c>
+      <c r="Y177">
+        <v>1.06</v>
+      </c>
+      <c r="Z177">
+        <v>1.67</v>
+      </c>
+      <c r="AA177">
+        <v>3.6</v>
+      </c>
+      <c r="AB177">
+        <v>5.5</v>
+      </c>
+      <c r="AC177">
+        <v>1.07</v>
+      </c>
+      <c r="AD177">
+        <v>8</v>
+      </c>
+      <c r="AE177">
+        <v>1.38</v>
+      </c>
+      <c r="AF177">
+        <v>2.95</v>
+      </c>
+      <c r="AG177">
+        <v>2.15</v>
+      </c>
+      <c r="AH177">
+        <v>1.67</v>
+      </c>
+      <c r="AI177">
+        <v>2.05</v>
+      </c>
+      <c r="AJ177">
+        <v>1.7</v>
+      </c>
+      <c r="AK177">
+        <v>1.17</v>
+      </c>
+      <c r="AL177">
+        <v>1.27</v>
+      </c>
+      <c r="AM177">
+        <v>2.1</v>
+      </c>
+      <c r="AN177">
+        <v>1.83</v>
+      </c>
+      <c r="AO177">
+        <v>1.67</v>
+      </c>
+      <c r="AP177">
+        <v>2</v>
+      </c>
+      <c r="AQ177">
+        <v>1.43</v>
+      </c>
+      <c r="AR177">
+        <v>1.78</v>
+      </c>
+      <c r="AS177">
+        <v>1.35</v>
+      </c>
+      <c r="AT177">
+        <v>3.13</v>
+      </c>
+      <c r="AU177">
+        <v>9</v>
+      </c>
+      <c r="AV177">
+        <v>5</v>
+      </c>
+      <c r="AW177">
+        <v>4</v>
+      </c>
+      <c r="AX177">
+        <v>4</v>
+      </c>
+      <c r="AY177">
+        <v>15</v>
+      </c>
+      <c r="AZ177">
+        <v>10</v>
+      </c>
+      <c r="BA177">
+        <v>2</v>
+      </c>
+      <c r="BB177">
+        <v>3</v>
+      </c>
+      <c r="BC177">
+        <v>5</v>
+      </c>
+      <c r="BD177">
+        <v>1.23</v>
+      </c>
+      <c r="BE177">
+        <v>8</v>
+      </c>
+      <c r="BF177">
+        <v>4.6</v>
+      </c>
+      <c r="BG177">
+        <v>1.4</v>
+      </c>
+      <c r="BH177">
+        <v>2.7</v>
+      </c>
+      <c r="BI177">
+        <v>1.67</v>
+      </c>
+      <c r="BJ177">
+        <v>2.05</v>
+      </c>
+      <c r="BK177">
+        <v>2.07</v>
+      </c>
+      <c r="BL177">
+        <v>1.66</v>
+      </c>
+      <c r="BM177">
+        <v>2.65</v>
+      </c>
+      <c r="BN177">
+        <v>1.41</v>
+      </c>
+      <c r="BO177">
+        <v>3.4</v>
+      </c>
+      <c r="BP177">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7820480</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45753.84375</v>
+      </c>
+      <c r="F178">
+        <v>12</v>
+      </c>
+      <c r="G178" t="s">
+        <v>97</v>
+      </c>
+      <c r="H178" t="s">
+        <v>85</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>4</v>
+      </c>
+      <c r="M178">
+        <v>1</v>
+      </c>
+      <c r="N178">
+        <v>5</v>
+      </c>
+      <c r="O178" t="s">
+        <v>207</v>
+      </c>
+      <c r="P178" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q178">
+        <v>2.38</v>
+      </c>
+      <c r="R178">
+        <v>2.1</v>
+      </c>
+      <c r="S178">
+        <v>5.5</v>
+      </c>
+      <c r="T178">
+        <v>1.44</v>
+      </c>
+      <c r="U178">
+        <v>2.63</v>
+      </c>
+      <c r="V178">
+        <v>3.25</v>
+      </c>
+      <c r="W178">
+        <v>1.33</v>
+      </c>
+      <c r="X178">
+        <v>10</v>
+      </c>
+      <c r="Y178">
+        <v>1.06</v>
+      </c>
+      <c r="Z178">
+        <v>1.7</v>
+      </c>
+      <c r="AA178">
+        <v>3.5</v>
+      </c>
+      <c r="AB178">
+        <v>5.5</v>
+      </c>
+      <c r="AC178">
+        <v>1.07</v>
+      </c>
+      <c r="AD178">
+        <v>8</v>
+      </c>
+      <c r="AE178">
+        <v>1.38</v>
+      </c>
+      <c r="AF178">
+        <v>3</v>
+      </c>
+      <c r="AG178">
+        <v>2.15</v>
+      </c>
+      <c r="AH178">
+        <v>1.67</v>
+      </c>
+      <c r="AI178">
+        <v>2.05</v>
+      </c>
+      <c r="AJ178">
+        <v>1.7</v>
+      </c>
+      <c r="AK178">
+        <v>1.17</v>
+      </c>
+      <c r="AL178">
+        <v>1.28</v>
+      </c>
+      <c r="AM178">
+        <v>2.05</v>
+      </c>
+      <c r="AN178">
+        <v>1.5</v>
+      </c>
+      <c r="AO178">
+        <v>0.6</v>
+      </c>
+      <c r="AP178">
+        <v>1.8</v>
+      </c>
+      <c r="AQ178">
+        <v>0.5</v>
+      </c>
+      <c r="AR178">
+        <v>1.59</v>
+      </c>
+      <c r="AS178">
+        <v>1.27</v>
+      </c>
+      <c r="AT178">
+        <v>2.86</v>
+      </c>
+      <c r="AU178">
+        <v>7</v>
+      </c>
+      <c r="AV178">
+        <v>3</v>
+      </c>
+      <c r="AW178">
+        <v>9</v>
+      </c>
+      <c r="AX178">
+        <v>3</v>
+      </c>
+      <c r="AY178">
+        <v>17</v>
+      </c>
+      <c r="AZ178">
+        <v>6</v>
+      </c>
+      <c r="BA178">
+        <v>7</v>
+      </c>
+      <c r="BB178">
+        <v>0</v>
+      </c>
+      <c r="BC178">
+        <v>7</v>
+      </c>
+      <c r="BD178">
+        <v>1.42</v>
+      </c>
+      <c r="BE178">
+        <v>6.75</v>
+      </c>
+      <c r="BF178">
+        <v>3.3</v>
+      </c>
+      <c r="BG178">
+        <v>1.4</v>
+      </c>
+      <c r="BH178">
+        <v>2.7</v>
+      </c>
+      <c r="BI178">
+        <v>1.68</v>
+      </c>
+      <c r="BJ178">
+        <v>2.04</v>
+      </c>
+      <c r="BK178">
+        <v>2.08</v>
+      </c>
+      <c r="BL178">
+        <v>1.65</v>
+      </c>
+      <c r="BM178">
+        <v>2.65</v>
+      </c>
+      <c r="BN178">
+        <v>1.4</v>
+      </c>
+      <c r="BO178">
+        <v>3.45</v>
+      </c>
+      <c r="BP178">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7820490</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45754.64583333334</v>
+      </c>
+      <c r="F179">
+        <v>12</v>
+      </c>
+      <c r="G179" t="s">
+        <v>86</v>
+      </c>
+      <c r="H179" t="s">
+        <v>82</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>1</v>
+      </c>
+      <c r="O179" t="s">
+        <v>208</v>
+      </c>
+      <c r="P179" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q179">
+        <v>4</v>
+      </c>
+      <c r="R179">
+        <v>1.73</v>
+      </c>
+      <c r="S179">
+        <v>4</v>
+      </c>
+      <c r="T179">
+        <v>1.83</v>
+      </c>
+      <c r="U179">
+        <v>1.83</v>
+      </c>
+      <c r="V179">
+        <v>6</v>
+      </c>
+      <c r="W179">
+        <v>1.13</v>
+      </c>
+      <c r="X179">
+        <v>21</v>
+      </c>
+      <c r="Y179">
+        <v>1.02</v>
+      </c>
+      <c r="Z179">
+        <v>3</v>
+      </c>
+      <c r="AA179">
+        <v>2.75</v>
+      </c>
+      <c r="AB179">
+        <v>2.8</v>
+      </c>
+      <c r="AC179">
+        <v>1.2</v>
+      </c>
+      <c r="AD179">
+        <v>4.33</v>
+      </c>
+      <c r="AE179">
+        <v>1.84</v>
+      </c>
+      <c r="AF179">
+        <v>1.91</v>
+      </c>
+      <c r="AG179">
+        <v>4</v>
+      </c>
+      <c r="AH179">
+        <v>1.25</v>
+      </c>
+      <c r="AI179">
+        <v>2.75</v>
+      </c>
+      <c r="AJ179">
+        <v>1.4</v>
+      </c>
+      <c r="AK179">
+        <v>1.38</v>
+      </c>
+      <c r="AL179">
+        <v>1.49</v>
+      </c>
+      <c r="AM179">
+        <v>1.38</v>
+      </c>
+      <c r="AN179">
+        <v>1</v>
+      </c>
+      <c r="AO179">
+        <v>1.4</v>
+      </c>
+      <c r="AP179">
+        <v>1.33</v>
+      </c>
+      <c r="AQ179">
+        <v>1.17</v>
+      </c>
+      <c r="AR179">
+        <v>1.19</v>
+      </c>
+      <c r="AS179">
+        <v>1.16</v>
+      </c>
+      <c r="AT179">
+        <v>2.35</v>
+      </c>
+      <c r="AU179">
+        <v>4</v>
+      </c>
+      <c r="AV179">
+        <v>2</v>
+      </c>
+      <c r="AW179">
+        <v>4</v>
+      </c>
+      <c r="AX179">
+        <v>4</v>
+      </c>
+      <c r="AY179">
+        <v>8</v>
+      </c>
+      <c r="AZ179">
+        <v>9</v>
+      </c>
+      <c r="BA179">
+        <v>1</v>
+      </c>
+      <c r="BB179">
+        <v>5</v>
+      </c>
+      <c r="BC179">
+        <v>6</v>
+      </c>
+      <c r="BD179">
+        <v>2.05</v>
+      </c>
+      <c r="BE179">
+        <v>5.8</v>
+      </c>
+      <c r="BF179">
+        <v>1.98</v>
+      </c>
+      <c r="BG179">
+        <v>1.65</v>
+      </c>
+      <c r="BH179">
+        <v>2.08</v>
+      </c>
+      <c r="BI179">
+        <v>2.06</v>
+      </c>
+      <c r="BJ179">
+        <v>1.66</v>
+      </c>
+      <c r="BK179">
+        <v>2.65</v>
+      </c>
+      <c r="BL179">
+        <v>1.41</v>
+      </c>
+      <c r="BM179">
+        <v>3.55</v>
+      </c>
+      <c r="BN179">
+        <v>1.24</v>
+      </c>
+      <c r="BO179">
+        <v>4.8</v>
+      </c>
+      <c r="BP179">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7820489</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45754.875</v>
+      </c>
+      <c r="F180">
+        <v>12</v>
+      </c>
+      <c r="G180" t="s">
+        <v>99</v>
+      </c>
+      <c r="H180" t="s">
+        <v>81</v>
+      </c>
+      <c r="I180">
+        <v>1</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+      <c r="L180">
+        <v>3</v>
+      </c>
+      <c r="M180">
+        <v>2</v>
+      </c>
+      <c r="N180">
+        <v>5</v>
+      </c>
+      <c r="O180" t="s">
+        <v>209</v>
+      </c>
+      <c r="P180" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q180">
+        <v>3.4</v>
+      </c>
+      <c r="R180">
+        <v>1.91</v>
+      </c>
+      <c r="S180">
+        <v>4</v>
+      </c>
+      <c r="T180">
+        <v>1.62</v>
+      </c>
+      <c r="U180">
+        <v>2.2</v>
+      </c>
+      <c r="V180">
+        <v>4</v>
+      </c>
+      <c r="W180">
+        <v>1.22</v>
+      </c>
+      <c r="X180">
+        <v>13</v>
+      </c>
+      <c r="Y180">
+        <v>1.04</v>
+      </c>
+      <c r="Z180">
+        <v>2.45</v>
+      </c>
+      <c r="AA180">
+        <v>3</v>
+      </c>
+      <c r="AB180">
+        <v>3.2</v>
+      </c>
+      <c r="AC180">
+        <v>1.11</v>
+      </c>
+      <c r="AD180">
+        <v>6.25</v>
+      </c>
+      <c r="AE180">
+        <v>1.53</v>
+      </c>
+      <c r="AF180">
+        <v>2.3</v>
+      </c>
+      <c r="AG180">
+        <v>2.7</v>
+      </c>
+      <c r="AH180">
+        <v>1.44</v>
+      </c>
+      <c r="AI180">
+        <v>2.2</v>
+      </c>
+      <c r="AJ180">
+        <v>1.62</v>
+      </c>
+      <c r="AK180">
+        <v>1.34</v>
+      </c>
+      <c r="AL180">
+        <v>1.36</v>
+      </c>
+      <c r="AM180">
+        <v>1.55</v>
+      </c>
+      <c r="AN180">
+        <v>0.6</v>
+      </c>
+      <c r="AO180">
+        <v>0.17</v>
+      </c>
+      <c r="AP180">
+        <v>1</v>
+      </c>
+      <c r="AQ180">
+        <v>0.14</v>
+      </c>
+      <c r="AR180">
+        <v>1.79</v>
+      </c>
+      <c r="AS180">
+        <v>1.05</v>
+      </c>
+      <c r="AT180">
+        <v>2.84</v>
+      </c>
+      <c r="AU180">
+        <v>5</v>
+      </c>
+      <c r="AV180">
+        <v>7</v>
+      </c>
+      <c r="AW180">
+        <v>10</v>
+      </c>
+      <c r="AX180">
+        <v>6</v>
+      </c>
+      <c r="AY180">
+        <v>16</v>
+      </c>
+      <c r="AZ180">
+        <v>16</v>
+      </c>
+      <c r="BA180">
+        <v>4</v>
+      </c>
+      <c r="BB180">
+        <v>5</v>
+      </c>
+      <c r="BC180">
+        <v>9</v>
+      </c>
+      <c r="BD180">
+        <v>1.82</v>
+      </c>
+      <c r="BE180">
+        <v>8</v>
+      </c>
+      <c r="BF180">
+        <v>2.33</v>
+      </c>
+      <c r="BG180">
+        <v>1.28</v>
+      </c>
+      <c r="BH180">
+        <v>3.25</v>
+      </c>
+      <c r="BI180">
+        <v>1.52</v>
+      </c>
+      <c r="BJ180">
+        <v>2.37</v>
+      </c>
+      <c r="BK180">
+        <v>1.8</v>
+      </c>
+      <c r="BL180">
+        <v>1.91</v>
+      </c>
+      <c r="BM180">
+        <v>2.38</v>
+      </c>
+      <c r="BN180">
+        <v>1.54</v>
+      </c>
+      <c r="BO180">
+        <v>3.12</v>
+      </c>
+      <c r="BP180">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7820484</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45754.875</v>
+      </c>
+      <c r="F181">
+        <v>12</v>
+      </c>
+      <c r="G181" t="s">
+        <v>71</v>
+      </c>
+      <c r="H181" t="s">
+        <v>72</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>1</v>
+      </c>
+      <c r="K181">
+        <v>1</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="M181">
+        <v>2</v>
+      </c>
+      <c r="N181">
+        <v>2</v>
+      </c>
+      <c r="O181" t="s">
+        <v>100</v>
+      </c>
+      <c r="P181" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q181">
+        <v>2.75</v>
+      </c>
+      <c r="R181">
+        <v>1.95</v>
+      </c>
+      <c r="S181">
+        <v>4.75</v>
+      </c>
+      <c r="T181">
+        <v>1.57</v>
+      </c>
+      <c r="U181">
+        <v>2.25</v>
+      </c>
+      <c r="V181">
+        <v>3.75</v>
+      </c>
+      <c r="W181">
+        <v>1.25</v>
+      </c>
+      <c r="X181">
+        <v>11</v>
+      </c>
+      <c r="Y181">
+        <v>1.05</v>
+      </c>
+      <c r="Z181">
+        <v>2</v>
+      </c>
+      <c r="AA181">
+        <v>3.2</v>
+      </c>
+      <c r="AB181">
+        <v>4.2</v>
+      </c>
+      <c r="AC181">
+        <v>1.06</v>
+      </c>
+      <c r="AD181">
+        <v>6.75</v>
+      </c>
+      <c r="AE181">
+        <v>1.46</v>
+      </c>
+      <c r="AF181">
+        <v>2.71</v>
+      </c>
+      <c r="AG181">
+        <v>2.5</v>
+      </c>
+      <c r="AH181">
+        <v>1.5</v>
+      </c>
+      <c r="AI181">
+        <v>2.1</v>
+      </c>
+      <c r="AJ181">
+        <v>1.67</v>
+      </c>
+      <c r="AK181">
+        <v>1.24</v>
+      </c>
+      <c r="AL181">
+        <v>1.32</v>
+      </c>
+      <c r="AM181">
+        <v>1.78</v>
+      </c>
+      <c r="AN181">
+        <v>2.4</v>
+      </c>
+      <c r="AO181">
+        <v>0.8</v>
+      </c>
+      <c r="AP181">
+        <v>2</v>
+      </c>
+      <c r="AQ181">
+        <v>1.17</v>
+      </c>
+      <c r="AR181">
+        <v>1.25</v>
+      </c>
+      <c r="AS181">
+        <v>1.39</v>
+      </c>
+      <c r="AT181">
+        <v>2.64</v>
+      </c>
+      <c r="AU181">
+        <v>10</v>
+      </c>
+      <c r="AV181">
+        <v>3</v>
+      </c>
+      <c r="AW181">
+        <v>7</v>
+      </c>
+      <c r="AX181">
+        <v>3</v>
+      </c>
+      <c r="AY181">
+        <v>18</v>
+      </c>
+      <c r="AZ181">
+        <v>7</v>
+      </c>
+      <c r="BA181">
+        <v>7</v>
+      </c>
+      <c r="BB181">
+        <v>3</v>
+      </c>
+      <c r="BC181">
+        <v>10</v>
+      </c>
+      <c r="BD181">
+        <v>1.7</v>
+      </c>
+      <c r="BE181">
+        <v>6.4</v>
+      </c>
+      <c r="BF181">
+        <v>2.4</v>
+      </c>
+      <c r="BG181">
+        <v>1.48</v>
+      </c>
+      <c r="BH181">
+        <v>2.43</v>
+      </c>
+      <c r="BI181">
+        <v>1.8</v>
+      </c>
+      <c r="BJ181">
+        <v>1.89</v>
+      </c>
+      <c r="BK181">
+        <v>2.3</v>
+      </c>
+      <c r="BL181">
+        <v>1.53</v>
+      </c>
+      <c r="BM181">
+        <v>3</v>
+      </c>
+      <c r="BN181">
+        <v>1.32</v>
+      </c>
+      <c r="BO181">
+        <v>4</v>
+      </c>
+      <c r="BP181">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1329,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP256"/>
+  <dimension ref="A1:BP255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -5786,7 +5786,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ22">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>0.7</v>
@@ -10112,7 +10112,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ43">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -11551,7 +11551,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
         <v>1.44</v>
@@ -16086,7 +16086,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ72">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AR72">
         <v>1.21</v>
@@ -18555,7 +18555,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>0.14</v>
@@ -20206,7 +20206,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ92">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AR92">
         <v>1.29</v>
@@ -21645,7 +21645,7 @@
         <v>2.33</v>
       </c>
       <c r="AP99">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
         <v>1.56</v>
@@ -30297,7 +30297,7 @@
         <v>1.75</v>
       </c>
       <c r="AP141">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ141">
         <v>1.33</v>
@@ -31948,7 +31948,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ149">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AR149">
         <v>1.46</v>
@@ -36683,7 +36683,7 @@
         <v>0.6</v>
       </c>
       <c r="AP172">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ172">
         <v>0.88</v>
@@ -38128,7 +38128,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ179">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AR179">
         <v>1.19</v>
@@ -42863,7 +42863,7 @@
         <v>1.43</v>
       </c>
       <c r="AP202">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ202">
         <v>1.22</v>
@@ -43690,7 +43690,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ206">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AR206">
         <v>1.83</v>
@@ -49867,7 +49867,7 @@
         <v>1</v>
       </c>
       <c r="AP236">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ236">
         <v>1.11</v>
@@ -50282,7 +50282,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ238">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AR238">
         <v>1.5</v>
@@ -51518,7 +51518,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ244">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR244">
         <v>1.6</v>
@@ -52339,7 +52339,7 @@
         <v>1.5</v>
       </c>
       <c r="AP248">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AQ248">
         <v>1.41</v>
@@ -52754,7 +52754,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ250">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AR250">
         <v>1.42</v>
@@ -53372,7 +53372,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ253">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR253">
         <v>1.9</v>
@@ -53578,7 +53578,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ254">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AR254">
         <v>1.51</v>
@@ -53784,7 +53784,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ255">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR255">
         <v>1.27</v>
@@ -53859,212 +53859,6 @@
         <v>4.65</v>
       </c>
       <c r="BP255">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="256" spans="1:68">
-      <c r="A256" s="1">
-        <v>255</v>
-      </c>
-      <c r="B256">
-        <v>7905546</v>
-      </c>
-      <c r="C256" t="s">
-        <v>68</v>
-      </c>
-      <c r="D256" t="s">
-        <v>69</v>
-      </c>
-      <c r="E256" s="2">
-        <v>45809.70833333334</v>
-      </c>
-      <c r="F256">
-        <v>0</v>
-      </c>
-      <c r="G256" t="s">
-        <v>93</v>
-      </c>
-      <c r="H256" t="s">
-        <v>82</v>
-      </c>
-      <c r="I256">
-        <v>0</v>
-      </c>
-      <c r="J256">
-        <v>0</v>
-      </c>
-      <c r="K256">
-        <v>0</v>
-      </c>
-      <c r="L256">
-        <v>0</v>
-      </c>
-      <c r="M256">
-        <v>1</v>
-      </c>
-      <c r="N256">
-        <v>1</v>
-      </c>
-      <c r="O256" t="s">
-        <v>100</v>
-      </c>
-      <c r="P256" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q256">
-        <v>3.2</v>
-      </c>
-      <c r="R256">
-        <v>1.78</v>
-      </c>
-      <c r="S256">
-        <v>4</v>
-      </c>
-      <c r="T256">
-        <v>1.65</v>
-      </c>
-      <c r="U256">
-        <v>2.05</v>
-      </c>
-      <c r="V256">
-        <v>4.2</v>
-      </c>
-      <c r="W256">
-        <v>1.2</v>
-      </c>
-      <c r="X256">
-        <v>13</v>
-      </c>
-      <c r="Y256">
-        <v>1.02</v>
-      </c>
-      <c r="Z256">
-        <v>2.4</v>
-      </c>
-      <c r="AA256">
-        <v>2.8</v>
-      </c>
-      <c r="AB256">
-        <v>3.2</v>
-      </c>
-      <c r="AC256">
-        <v>1.15</v>
-      </c>
-      <c r="AD256">
-        <v>4.75</v>
-      </c>
-      <c r="AE256">
-        <v>1.73</v>
-      </c>
-      <c r="AF256">
-        <v>2</v>
-      </c>
-      <c r="AG256">
-        <v>3.2</v>
-      </c>
-      <c r="AH256">
-        <v>1.3</v>
-      </c>
-      <c r="AI256">
-        <v>2.5</v>
-      </c>
-      <c r="AJ256">
-        <v>1.47</v>
-      </c>
-      <c r="AK256">
-        <v>1.32</v>
-      </c>
-      <c r="AL256">
-        <v>1.41</v>
-      </c>
-      <c r="AM256">
-        <v>1.53</v>
-      </c>
-      <c r="AN256">
-        <v>1.79</v>
-      </c>
-      <c r="AO256">
-        <v>1.58</v>
-      </c>
-      <c r="AP256">
-        <v>1.7</v>
-      </c>
-      <c r="AQ256">
-        <v>1.65</v>
-      </c>
-      <c r="AR256">
-        <v>1.48</v>
-      </c>
-      <c r="AS256">
-        <v>1.25</v>
-      </c>
-      <c r="AT256">
-        <v>2.73</v>
-      </c>
-      <c r="AU256">
-        <v>4</v>
-      </c>
-      <c r="AV256">
-        <v>4</v>
-      </c>
-      <c r="AW256">
-        <v>3</v>
-      </c>
-      <c r="AX256">
-        <v>8</v>
-      </c>
-      <c r="AY256">
-        <v>7</v>
-      </c>
-      <c r="AZ256">
-        <v>12</v>
-      </c>
-      <c r="BA256">
-        <v>1</v>
-      </c>
-      <c r="BB256">
-        <v>3</v>
-      </c>
-      <c r="BC256">
-        <v>4</v>
-      </c>
-      <c r="BD256">
-        <v>1.8</v>
-      </c>
-      <c r="BE256">
-        <v>6.1</v>
-      </c>
-      <c r="BF256">
-        <v>2.23</v>
-      </c>
-      <c r="BG256">
-        <v>1.68</v>
-      </c>
-      <c r="BH256">
-        <v>2.04</v>
-      </c>
-      <c r="BI256">
-        <v>2.1</v>
-      </c>
-      <c r="BJ256">
-        <v>1.64</v>
-      </c>
-      <c r="BK256">
-        <v>2.75</v>
-      </c>
-      <c r="BL256">
-        <v>1.38</v>
-      </c>
-      <c r="BM256">
-        <v>3.7</v>
-      </c>
-      <c r="BN256">
-        <v>1.21</v>
-      </c>
-      <c r="BO256">
-        <v>5.1</v>
-      </c>
-      <c r="BP256">
         <v>1.12</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="320">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,9 @@
     <t>['90+12']</t>
   </si>
   <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -968,6 +971,9 @@
   </si>
   <si>
     <t>['59', '82']</t>
+  </si>
+  <si>
+    <t>['3', '85']</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP256"/>
+  <dimension ref="A1:BP258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1585,7 +1591,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1997,7 +2003,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2409,7 +2415,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2615,7 +2621,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -3233,7 +3239,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -5087,7 +5093,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5499,7 +5505,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q21">
         <v>2.63</v>
@@ -5911,7 +5917,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5989,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ23">
         <v>1.33</v>
@@ -6117,7 +6123,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6198,7 +6204,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6529,7 +6535,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6941,7 +6947,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -9413,7 +9419,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9494,7 +9500,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ40">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR40">
         <v>1.12</v>
@@ -10237,7 +10243,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10443,7 +10449,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10649,7 +10655,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10855,7 +10861,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -11061,7 +11067,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11885,7 +11891,7 @@
         <v>131</v>
       </c>
       <c r="P52" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -12172,7 +12178,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ53">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR53">
         <v>1.58</v>
@@ -12297,7 +12303,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -13121,7 +13127,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13611,7 +13617,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ60">
         <v>0.89</v>
@@ -13739,7 +13745,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13820,7 +13826,7 @@
         <v>2</v>
       </c>
       <c r="AQ61">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR61">
         <v>0.96</v>
@@ -14975,7 +14981,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -16005,7 +16011,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -17035,7 +17041,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q77">
         <v>5</v>
@@ -17241,7 +17247,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q78">
         <v>2.5</v>
@@ -17447,7 +17453,7 @@
         <v>148</v>
       </c>
       <c r="P79" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q79">
         <v>3.2</v>
@@ -17859,7 +17865,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -18065,7 +18071,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18683,7 +18689,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18761,7 +18767,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ85">
         <v>0.5</v>
@@ -19507,7 +19513,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19713,7 +19719,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19794,7 +19800,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR90">
         <v>1.46</v>
@@ -20331,7 +20337,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20412,7 +20418,7 @@
         <v>2</v>
       </c>
       <c r="AQ93">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR93">
         <v>1.86</v>
@@ -20949,7 +20955,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -21155,7 +21161,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21648,7 +21654,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ99">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR99">
         <v>1.77</v>
@@ -21773,7 +21779,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23421,7 +23427,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23627,7 +23633,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23833,7 +23839,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -23911,7 +23917,7 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ110">
         <v>1.44</v>
@@ -24245,7 +24251,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24657,7 +24663,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24863,7 +24869,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -25069,7 +25075,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25275,7 +25281,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -26099,7 +26105,7 @@
         <v>175</v>
       </c>
       <c r="P121" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q121">
         <v>4.33</v>
@@ -26305,7 +26311,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26511,7 +26517,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -27541,7 +27547,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28365,7 +28371,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28855,7 +28861,7 @@
         <v>1.6</v>
       </c>
       <c r="AP134">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ134">
         <v>1.56</v>
@@ -28983,7 +28989,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -29270,7 +29276,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ136">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR136">
         <v>1.23</v>
@@ -31249,7 +31255,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31455,7 +31461,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31536,7 +31542,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ147">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR147">
         <v>1.38</v>
@@ -31661,7 +31667,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31867,7 +31873,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -32073,7 +32079,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32691,7 +32697,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33103,7 +33109,7 @@
         <v>192</v>
       </c>
       <c r="P155" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33515,7 +33521,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -34339,7 +34345,7 @@
         <v>174</v>
       </c>
       <c r="P161" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34751,7 +34757,7 @@
         <v>196</v>
       </c>
       <c r="P163" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q163">
         <v>2.1</v>
@@ -34957,7 +34963,7 @@
         <v>197</v>
       </c>
       <c r="P164" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q164">
         <v>3.75</v>
@@ -35781,7 +35787,7 @@
         <v>100</v>
       </c>
       <c r="P168" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q168">
         <v>4.33</v>
@@ -35862,7 +35868,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ168">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR168">
         <v>1.54</v>
@@ -35987,7 +35993,7 @@
         <v>199</v>
       </c>
       <c r="P169" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q169">
         <v>2.75</v>
@@ -36477,7 +36483,7 @@
         <v>0.67</v>
       </c>
       <c r="AP171">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ171">
         <v>0.5</v>
@@ -36605,7 +36611,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q172">
         <v>2.38</v>
@@ -37017,7 +37023,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q174">
         <v>3.25</v>
@@ -37304,7 +37310,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ175">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR175">
         <v>1.83</v>
@@ -38253,7 +38259,7 @@
         <v>209</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38459,7 +38465,7 @@
         <v>100</v>
       </c>
       <c r="P181" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38665,7 +38671,7 @@
         <v>108</v>
       </c>
       <c r="P182" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39489,7 +39495,7 @@
         <v>203</v>
       </c>
       <c r="P186" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39695,7 +39701,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q187">
         <v>4</v>
@@ -40313,7 +40319,7 @@
         <v>151</v>
       </c>
       <c r="P190" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q190">
         <v>2.2</v>
@@ -40519,7 +40525,7 @@
         <v>100</v>
       </c>
       <c r="P191" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q191">
         <v>4</v>
@@ -40725,7 +40731,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41137,7 +41143,7 @@
         <v>100</v>
       </c>
       <c r="P194" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q194">
         <v>2.4</v>
@@ -41755,7 +41761,7 @@
         <v>100</v>
       </c>
       <c r="P197" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q197">
         <v>4.75</v>
@@ -41961,7 +41967,7 @@
         <v>100</v>
       </c>
       <c r="P198" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q198">
         <v>3.1</v>
@@ -42039,7 +42045,7 @@
         <v>0.67</v>
       </c>
       <c r="AP198">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ198">
         <v>0.88</v>
@@ -42248,7 +42254,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ199">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR199">
         <v>1.67</v>
@@ -43278,7 +43284,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ204">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR204">
         <v>1.17</v>
@@ -44845,7 +44851,7 @@
         <v>100</v>
       </c>
       <c r="P212" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45051,7 +45057,7 @@
         <v>102</v>
       </c>
       <c r="P213" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -46493,7 +46499,7 @@
         <v>226</v>
       </c>
       <c r="P220" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47111,7 +47117,7 @@
         <v>188</v>
       </c>
       <c r="P223" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -48016,7 +48022,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ227">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR227">
         <v>1.33</v>
@@ -48141,7 +48147,7 @@
         <v>232</v>
       </c>
       <c r="P228" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q228">
         <v>4.33</v>
@@ -48759,7 +48765,7 @@
         <v>156</v>
       </c>
       <c r="P231" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q231">
         <v>3.75</v>
@@ -49252,7 +49258,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ233">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR233">
         <v>1.8</v>
@@ -49377,7 +49383,7 @@
         <v>236</v>
       </c>
       <c r="P234" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q234">
         <v>2.75</v>
@@ -49455,7 +49461,7 @@
         <v>0.13</v>
       </c>
       <c r="AP234">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ234">
         <v>0.4</v>
@@ -49789,7 +49795,7 @@
         <v>100</v>
       </c>
       <c r="P236" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q236">
         <v>2.25</v>
@@ -50407,7 +50413,7 @@
         <v>100</v>
       </c>
       <c r="P239" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q239">
         <v>3.6</v>
@@ -51025,7 +51031,7 @@
         <v>239</v>
       </c>
       <c r="P242" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q242">
         <v>2.95</v>
@@ -51103,7 +51109,7 @@
         <v>1.69</v>
       </c>
       <c r="AP242">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AQ242">
         <v>1.59</v>
@@ -51437,7 +51443,7 @@
         <v>100</v>
       </c>
       <c r="P244" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q244">
         <v>2.4</v>
@@ -52055,7 +52061,7 @@
         <v>241</v>
       </c>
       <c r="P247" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q247">
         <v>2.2</v>
@@ -52261,7 +52267,7 @@
         <v>242</v>
       </c>
       <c r="P248" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q248">
         <v>2.63</v>
@@ -52879,7 +52885,7 @@
         <v>179</v>
       </c>
       <c r="P251" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q251">
         <v>2.6</v>
@@ -52960,7 +52966,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ251">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AR251">
         <v>1.67</v>
@@ -53085,7 +53091,7 @@
         <v>100</v>
       </c>
       <c r="P252" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q252">
         <v>2.88</v>
@@ -53781,7 +53787,7 @@
         <v>1.5</v>
       </c>
       <c r="AP255">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AQ255">
         <v>1.65</v>
@@ -53909,7 +53915,7 @@
         <v>100</v>
       </c>
       <c r="P256" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q256">
         <v>3.2</v>
@@ -54065,6 +54071,418 @@
         <v>5.1</v>
       </c>
       <c r="BP256">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7820561</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45849.64583333334</v>
+      </c>
+      <c r="F257">
+        <v>1</v>
+      </c>
+      <c r="G257" t="s">
+        <v>96</v>
+      </c>
+      <c r="H257" t="s">
+        <v>84</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>0</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>0</v>
+      </c>
+      <c r="O257" t="s">
+        <v>100</v>
+      </c>
+      <c r="P257" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q257">
+        <v>3.4</v>
+      </c>
+      <c r="R257">
+        <v>1.95</v>
+      </c>
+      <c r="S257">
+        <v>3.6</v>
+      </c>
+      <c r="T257">
+        <v>1.53</v>
+      </c>
+      <c r="U257">
+        <v>2.38</v>
+      </c>
+      <c r="V257">
+        <v>3.5</v>
+      </c>
+      <c r="W257">
+        <v>1.29</v>
+      </c>
+      <c r="X257">
+        <v>11</v>
+      </c>
+      <c r="Y257">
+        <v>1.05</v>
+      </c>
+      <c r="Z257">
+        <v>2.7</v>
+      </c>
+      <c r="AA257">
+        <v>2.75</v>
+      </c>
+      <c r="AB257">
+        <v>3</v>
+      </c>
+      <c r="AC257">
+        <v>1.1</v>
+      </c>
+      <c r="AD257">
+        <v>6.5</v>
+      </c>
+      <c r="AE257">
+        <v>1.5</v>
+      </c>
+      <c r="AF257">
+        <v>2.55</v>
+      </c>
+      <c r="AG257">
+        <v>2.5</v>
+      </c>
+      <c r="AH257">
+        <v>1.5</v>
+      </c>
+      <c r="AI257">
+        <v>2</v>
+      </c>
+      <c r="AJ257">
+        <v>1.75</v>
+      </c>
+      <c r="AK257">
+        <v>1.37</v>
+      </c>
+      <c r="AL257">
+        <v>1.36</v>
+      </c>
+      <c r="AM257">
+        <v>1.51</v>
+      </c>
+      <c r="AN257">
+        <v>1</v>
+      </c>
+      <c r="AO257">
+        <v>0.57</v>
+      </c>
+      <c r="AP257">
+        <v>1</v>
+      </c>
+      <c r="AQ257">
+        <v>0.63</v>
+      </c>
+      <c r="AR257">
+        <v>1.93</v>
+      </c>
+      <c r="AS257">
+        <v>1.4</v>
+      </c>
+      <c r="AT257">
+        <v>3.33</v>
+      </c>
+      <c r="AU257">
+        <v>2</v>
+      </c>
+      <c r="AV257">
+        <v>2</v>
+      </c>
+      <c r="AW257">
+        <v>13</v>
+      </c>
+      <c r="AX257">
+        <v>5</v>
+      </c>
+      <c r="AY257">
+        <v>15</v>
+      </c>
+      <c r="AZ257">
+        <v>7</v>
+      </c>
+      <c r="BA257">
+        <v>5</v>
+      </c>
+      <c r="BB257">
+        <v>2</v>
+      </c>
+      <c r="BC257">
+        <v>7</v>
+      </c>
+      <c r="BD257">
+        <v>1.82</v>
+      </c>
+      <c r="BE257">
+        <v>6.25</v>
+      </c>
+      <c r="BF257">
+        <v>2.37</v>
+      </c>
+      <c r="BG257">
+        <v>1.37</v>
+      </c>
+      <c r="BH257">
+        <v>2.75</v>
+      </c>
+      <c r="BI257">
+        <v>1.68</v>
+      </c>
+      <c r="BJ257">
+        <v>1.98</v>
+      </c>
+      <c r="BK257">
+        <v>2.2</v>
+      </c>
+      <c r="BL257">
+        <v>1.55</v>
+      </c>
+      <c r="BM257">
+        <v>3.1</v>
+      </c>
+      <c r="BN257">
+        <v>1.31</v>
+      </c>
+      <c r="BO257">
+        <v>4.1</v>
+      </c>
+      <c r="BP257">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="258" spans="1:68">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>7820565</v>
+      </c>
+      <c r="C258" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" t="s">
+        <v>69</v>
+      </c>
+      <c r="E258" s="2">
+        <v>45849.83333333334</v>
+      </c>
+      <c r="F258">
+        <v>1</v>
+      </c>
+      <c r="G258" t="s">
+        <v>91</v>
+      </c>
+      <c r="H258" t="s">
+        <v>79</v>
+      </c>
+      <c r="I258">
+        <v>1</v>
+      </c>
+      <c r="J258">
+        <v>1</v>
+      </c>
+      <c r="K258">
+        <v>2</v>
+      </c>
+      <c r="L258">
+        <v>1</v>
+      </c>
+      <c r="M258">
+        <v>2</v>
+      </c>
+      <c r="N258">
+        <v>3</v>
+      </c>
+      <c r="O258" t="s">
+        <v>245</v>
+      </c>
+      <c r="P258" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q258">
+        <v>2.88</v>
+      </c>
+      <c r="R258">
+        <v>1.83</v>
+      </c>
+      <c r="S258">
+        <v>5.5</v>
+      </c>
+      <c r="T258">
+        <v>1.67</v>
+      </c>
+      <c r="U258">
+        <v>2.1</v>
+      </c>
+      <c r="V258">
+        <v>4.5</v>
+      </c>
+      <c r="W258">
+        <v>1.18</v>
+      </c>
+      <c r="X258">
+        <v>15</v>
+      </c>
+      <c r="Y258">
+        <v>1.03</v>
+      </c>
+      <c r="Z258">
+        <v>2.05</v>
+      </c>
+      <c r="AA258">
+        <v>3.2</v>
+      </c>
+      <c r="AB258">
+        <v>4</v>
+      </c>
+      <c r="AC258">
+        <v>1.15</v>
+      </c>
+      <c r="AD258">
+        <v>5.25</v>
+      </c>
+      <c r="AE258">
+        <v>1.7</v>
+      </c>
+      <c r="AF258">
+        <v>2.06</v>
+      </c>
+      <c r="AG258">
+        <v>3.4</v>
+      </c>
+      <c r="AH258">
+        <v>1.33</v>
+      </c>
+      <c r="AI258">
+        <v>2.63</v>
+      </c>
+      <c r="AJ258">
+        <v>1.44</v>
+      </c>
+      <c r="AK258">
+        <v>1.22</v>
+      </c>
+      <c r="AL258">
+        <v>1.41</v>
+      </c>
+      <c r="AM258">
+        <v>1.7</v>
+      </c>
+      <c r="AN258">
+        <v>0.63</v>
+      </c>
+      <c r="AO258">
+        <v>1.56</v>
+      </c>
+      <c r="AP258">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ258">
+        <v>1.7</v>
+      </c>
+      <c r="AR258">
+        <v>2.03</v>
+      </c>
+      <c r="AS258">
+        <v>1.1</v>
+      </c>
+      <c r="AT258">
+        <v>3.13</v>
+      </c>
+      <c r="AU258">
+        <v>3</v>
+      </c>
+      <c r="AV258">
+        <v>4</v>
+      </c>
+      <c r="AW258">
+        <v>6</v>
+      </c>
+      <c r="AX258">
+        <v>6</v>
+      </c>
+      <c r="AY258">
+        <v>9</v>
+      </c>
+      <c r="AZ258">
+        <v>10</v>
+      </c>
+      <c r="BA258">
+        <v>1</v>
+      </c>
+      <c r="BB258">
+        <v>5</v>
+      </c>
+      <c r="BC258">
+        <v>6</v>
+      </c>
+      <c r="BD258">
+        <v>1.78</v>
+      </c>
+      <c r="BE258">
+        <v>6</v>
+      </c>
+      <c r="BF258">
+        <v>2.45</v>
+      </c>
+      <c r="BG258">
+        <v>1.44</v>
+      </c>
+      <c r="BH258">
+        <v>2.45</v>
+      </c>
+      <c r="BI258">
+        <v>1.82</v>
+      </c>
+      <c r="BJ258">
+        <v>1.82</v>
+      </c>
+      <c r="BK258">
+        <v>2.45</v>
+      </c>
+      <c r="BL258">
+        <v>1.46</v>
+      </c>
+      <c r="BM258">
+        <v>3.4</v>
+      </c>
+      <c r="BN258">
+        <v>1.25</v>
+      </c>
+      <c r="BO258">
+        <v>4.75</v>
+      </c>
+      <c r="BP258">
         <v>1.12</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="321">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -975,6 +975,9 @@
   <si>
     <t>['3', '85']</t>
   </si>
+  <si>
+    <t>['4', '56', '90+5']</t>
+  </si>
 </sst>
 </file>
 
@@ -1335,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP258"/>
+  <dimension ref="A1:BP261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -5171,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ19">
         <v>0.89</v>
@@ -6201,7 +6204,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
         <v>1.7</v>
@@ -6407,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ25">
         <v>0.7</v>
@@ -6822,7 +6825,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ27">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -7234,7 +7237,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ29">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -11148,7 +11151,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ48">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR48">
         <v>1.53</v>
@@ -11557,7 +11560,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ50">
         <v>1.44</v>
@@ -12381,7 +12384,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ54">
         <v>0.5</v>
@@ -13002,7 +13005,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ57">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR57">
         <v>0.73</v>
@@ -13411,7 +13414,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -16710,7 +16713,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ75">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR75">
         <v>1.66</v>
@@ -17740,7 +17743,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ80">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR80">
         <v>1.81</v>
@@ -18561,7 +18564,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ84">
         <v>0.14</v>
@@ -19179,7 +19182,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ87">
         <v>0.29</v>
@@ -20830,7 +20833,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ95">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR95">
         <v>1.94</v>
@@ -21445,7 +21448,7 @@
         <v>0</v>
       </c>
       <c r="AP98">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ98">
         <v>0.75</v>
@@ -21651,7 +21654,7 @@
         <v>2.33</v>
       </c>
       <c r="AP99">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ99">
         <v>1.7</v>
@@ -23302,7 +23305,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ107">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR107">
         <v>1.43</v>
@@ -24538,7 +24541,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ113">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR113">
         <v>1.81</v>
@@ -28040,7 +28043,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ130">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR130">
         <v>1.81</v>
@@ -28449,7 +28452,7 @@
         <v>1.75</v>
       </c>
       <c r="AP132">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ132">
         <v>1.33</v>
@@ -29891,7 +29894,7 @@
         <v>0.8</v>
       </c>
       <c r="AP139">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ139">
         <v>0.5</v>
@@ -30097,7 +30100,7 @@
         <v>1.75</v>
       </c>
       <c r="AP140">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ140">
         <v>1.33</v>
@@ -30924,7 +30927,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ144">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR144">
         <v>1.91</v>
@@ -35247,7 +35250,7 @@
         <v>0.2</v>
       </c>
       <c r="AP165">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ165">
         <v>0.75</v>
@@ -35662,7 +35665,7 @@
         <v>2</v>
       </c>
       <c r="AQ167">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR167">
         <v>1.93</v>
@@ -36071,7 +36074,7 @@
         <v>0.8</v>
       </c>
       <c r="AP169">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ169">
         <v>0.88</v>
@@ -36689,7 +36692,7 @@
         <v>0.6</v>
       </c>
       <c r="AP172">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ172">
         <v>0.88</v>
@@ -38340,7 +38343,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ180">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR180">
         <v>1.79</v>
@@ -39779,7 +39782,7 @@
         <v>1</v>
       </c>
       <c r="AP187">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ187">
         <v>0.7</v>
@@ -41839,7 +41842,7 @@
         <v>1.33</v>
       </c>
       <c r="AP197">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ197">
         <v>1.57</v>
@@ -42869,7 +42872,7 @@
         <v>1.43</v>
       </c>
       <c r="AP202">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ202">
         <v>1.22</v>
@@ -43899,10 +43902,10 @@
         <v>0.14</v>
       </c>
       <c r="AP207">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ207">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR207">
         <v>1.36</v>
@@ -44108,7 +44111,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ208">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR208">
         <v>1.47</v>
@@ -48846,7 +48849,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ231">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR231">
         <v>1.87</v>
@@ -49464,7 +49467,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ234">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR234">
         <v>2.12</v>
@@ -49667,7 +49670,7 @@
         <v>1.29</v>
       </c>
       <c r="AP235">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ235">
         <v>1.33</v>
@@ -49873,7 +49876,7 @@
         <v>1</v>
       </c>
       <c r="AP236">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ236">
         <v>1.11</v>
@@ -50285,7 +50288,7 @@
         <v>1.43</v>
       </c>
       <c r="AP238">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ238">
         <v>1.67</v>
@@ -51315,7 +51318,7 @@
         <v>1.31</v>
       </c>
       <c r="AP243">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AQ243">
         <v>1.24</v>
@@ -52142,7 +52145,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ247">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AR247">
         <v>1.69</v>
@@ -52345,7 +52348,7 @@
         <v>1.5</v>
       </c>
       <c r="AP248">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AQ248">
         <v>1.41</v>
@@ -52757,10 +52760,10 @@
         <v>1.76</v>
       </c>
       <c r="AP250">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AQ250">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AR250">
         <v>1.42</v>
@@ -53584,7 +53587,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ254">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AR254">
         <v>1.51</v>
@@ -53993,7 +53996,7 @@
         <v>1.58</v>
       </c>
       <c r="AP256">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AQ256">
         <v>1.65</v>
@@ -54484,6 +54487,624 @@
       </c>
       <c r="BP258">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="259" spans="1:68">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>7820567</v>
+      </c>
+      <c r="C259" t="s">
+        <v>68</v>
+      </c>
+      <c r="D259" t="s">
+        <v>69</v>
+      </c>
+      <c r="E259" s="2">
+        <v>45850.66666666666</v>
+      </c>
+      <c r="F259">
+        <v>1</v>
+      </c>
+      <c r="G259" t="s">
+        <v>87</v>
+      </c>
+      <c r="H259" t="s">
+        <v>70</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259">
+        <v>0</v>
+      </c>
+      <c r="K259">
+        <v>0</v>
+      </c>
+      <c r="L259">
+        <v>1</v>
+      </c>
+      <c r="M259">
+        <v>1</v>
+      </c>
+      <c r="N259">
+        <v>2</v>
+      </c>
+      <c r="O259" t="s">
+        <v>138</v>
+      </c>
+      <c r="P259" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q259">
+        <v>2.5</v>
+      </c>
+      <c r="R259">
+        <v>1.95</v>
+      </c>
+      <c r="S259">
+        <v>6</v>
+      </c>
+      <c r="T259">
+        <v>1.57</v>
+      </c>
+      <c r="U259">
+        <v>2.25</v>
+      </c>
+      <c r="V259">
+        <v>3.75</v>
+      </c>
+      <c r="W259">
+        <v>1.25</v>
+      </c>
+      <c r="X259">
+        <v>13</v>
+      </c>
+      <c r="Y259">
+        <v>1.04</v>
+      </c>
+      <c r="Z259">
+        <v>1.8</v>
+      </c>
+      <c r="AA259">
+        <v>3.5</v>
+      </c>
+      <c r="AB259">
+        <v>5</v>
+      </c>
+      <c r="AC259">
+        <v>1.11</v>
+      </c>
+      <c r="AD259">
+        <v>6.25</v>
+      </c>
+      <c r="AE259">
+        <v>1.55</v>
+      </c>
+      <c r="AF259">
+        <v>2.3</v>
+      </c>
+      <c r="AG259">
+        <v>2.7</v>
+      </c>
+      <c r="AH259">
+        <v>1.44</v>
+      </c>
+      <c r="AI259">
+        <v>2.5</v>
+      </c>
+      <c r="AJ259">
+        <v>1.5</v>
+      </c>
+      <c r="AK259">
+        <v>1.16</v>
+      </c>
+      <c r="AL259">
+        <v>1.34</v>
+      </c>
+      <c r="AM259">
+        <v>1.95</v>
+      </c>
+      <c r="AN259">
+        <v>2.67</v>
+      </c>
+      <c r="AO259">
+        <v>1</v>
+      </c>
+      <c r="AP259">
+        <v>2.5</v>
+      </c>
+      <c r="AQ259">
+        <v>1</v>
+      </c>
+      <c r="AR259">
+        <v>1.72</v>
+      </c>
+      <c r="AS259">
+        <v>1.3</v>
+      </c>
+      <c r="AT259">
+        <v>3.02</v>
+      </c>
+      <c r="AU259">
+        <v>8</v>
+      </c>
+      <c r="AV259">
+        <v>4</v>
+      </c>
+      <c r="AW259">
+        <v>8</v>
+      </c>
+      <c r="AX259">
+        <v>6</v>
+      </c>
+      <c r="AY259">
+        <v>16</v>
+      </c>
+      <c r="AZ259">
+        <v>10</v>
+      </c>
+      <c r="BA259">
+        <v>7</v>
+      </c>
+      <c r="BB259">
+        <v>2</v>
+      </c>
+      <c r="BC259">
+        <v>9</v>
+      </c>
+      <c r="BD259">
+        <v>1.36</v>
+      </c>
+      <c r="BE259">
+        <v>7</v>
+      </c>
+      <c r="BF259">
+        <v>4.1</v>
+      </c>
+      <c r="BG259">
+        <v>1.39</v>
+      </c>
+      <c r="BH259">
+        <v>2.65</v>
+      </c>
+      <c r="BI259">
+        <v>1.72</v>
+      </c>
+      <c r="BJ259">
+        <v>1.93</v>
+      </c>
+      <c r="BK259">
+        <v>2.25</v>
+      </c>
+      <c r="BL259">
+        <v>1.53</v>
+      </c>
+      <c r="BM259">
+        <v>3.2</v>
+      </c>
+      <c r="BN259">
+        <v>1.29</v>
+      </c>
+      <c r="BO259">
+        <v>4.15</v>
+      </c>
+      <c r="BP259">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="260" spans="1:68">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>7820564</v>
+      </c>
+      <c r="C260" t="s">
+        <v>68</v>
+      </c>
+      <c r="D260" t="s">
+        <v>69</v>
+      </c>
+      <c r="E260" s="2">
+        <v>45850.77083333334</v>
+      </c>
+      <c r="F260">
+        <v>1</v>
+      </c>
+      <c r="G260" t="s">
+        <v>92</v>
+      </c>
+      <c r="H260" t="s">
+        <v>81</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+      <c r="J260">
+        <v>1</v>
+      </c>
+      <c r="K260">
+        <v>1</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+      <c r="M260">
+        <v>1</v>
+      </c>
+      <c r="N260">
+        <v>1</v>
+      </c>
+      <c r="O260" t="s">
+        <v>100</v>
+      </c>
+      <c r="P260" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q260">
+        <v>3</v>
+      </c>
+      <c r="R260">
+        <v>1.91</v>
+      </c>
+      <c r="S260">
+        <v>4.5</v>
+      </c>
+      <c r="T260">
+        <v>1.57</v>
+      </c>
+      <c r="U260">
+        <v>2.25</v>
+      </c>
+      <c r="V260">
+        <v>3.75</v>
+      </c>
+      <c r="W260">
+        <v>1.25</v>
+      </c>
+      <c r="X260">
+        <v>13</v>
+      </c>
+      <c r="Y260">
+        <v>1.04</v>
+      </c>
+      <c r="Z260">
+        <v>2.15</v>
+      </c>
+      <c r="AA260">
+        <v>2.9</v>
+      </c>
+      <c r="AB260">
+        <v>3.8</v>
+      </c>
+      <c r="AC260">
+        <v>1.12</v>
+      </c>
+      <c r="AD260">
+        <v>5.75</v>
+      </c>
+      <c r="AE260">
+        <v>1.55</v>
+      </c>
+      <c r="AF260">
+        <v>2.3</v>
+      </c>
+      <c r="AG260">
+        <v>2.7</v>
+      </c>
+      <c r="AH260">
+        <v>1.44</v>
+      </c>
+      <c r="AI260">
+        <v>2.2</v>
+      </c>
+      <c r="AJ260">
+        <v>1.62</v>
+      </c>
+      <c r="AK260">
+        <v>1.26</v>
+      </c>
+      <c r="AL260">
+        <v>1.37</v>
+      </c>
+      <c r="AM260">
+        <v>1.66</v>
+      </c>
+      <c r="AN260">
+        <v>1.5</v>
+      </c>
+      <c r="AO260">
+        <v>0.4</v>
+      </c>
+      <c r="AP260">
+        <v>1.33</v>
+      </c>
+      <c r="AQ260">
+        <v>0.64</v>
+      </c>
+      <c r="AR260">
+        <v>1.55</v>
+      </c>
+      <c r="AS260">
+        <v>1.21</v>
+      </c>
+      <c r="AT260">
+        <v>2.76</v>
+      </c>
+      <c r="AU260">
+        <v>9</v>
+      </c>
+      <c r="AV260">
+        <v>8</v>
+      </c>
+      <c r="AW260">
+        <v>9</v>
+      </c>
+      <c r="AX260">
+        <v>12</v>
+      </c>
+      <c r="AY260">
+        <v>18</v>
+      </c>
+      <c r="AZ260">
+        <v>20</v>
+      </c>
+      <c r="BA260">
+        <v>7</v>
+      </c>
+      <c r="BB260">
+        <v>8</v>
+      </c>
+      <c r="BC260">
+        <v>15</v>
+      </c>
+      <c r="BD260">
+        <v>1.6</v>
+      </c>
+      <c r="BE260">
+        <v>6.25</v>
+      </c>
+      <c r="BF260">
+        <v>2.87</v>
+      </c>
+      <c r="BG260">
+        <v>1.34</v>
+      </c>
+      <c r="BH260">
+        <v>2.85</v>
+      </c>
+      <c r="BI260">
+        <v>1.65</v>
+      </c>
+      <c r="BJ260">
+        <v>2.05</v>
+      </c>
+      <c r="BK260">
+        <v>2.1</v>
+      </c>
+      <c r="BL260">
+        <v>1.6</v>
+      </c>
+      <c r="BM260">
+        <v>2.9</v>
+      </c>
+      <c r="BN260">
+        <v>1.33</v>
+      </c>
+      <c r="BO260">
+        <v>3.5</v>
+      </c>
+      <c r="BP260">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="261" spans="1:68">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>7820557</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>69</v>
+      </c>
+      <c r="E261" s="2">
+        <v>45850.77083333334</v>
+      </c>
+      <c r="F261">
+        <v>1</v>
+      </c>
+      <c r="G261" t="s">
+        <v>93</v>
+      </c>
+      <c r="H261" t="s">
+        <v>77</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+      <c r="J261">
+        <v>1</v>
+      </c>
+      <c r="K261">
+        <v>1</v>
+      </c>
+      <c r="L261">
+        <v>0</v>
+      </c>
+      <c r="M261">
+        <v>3</v>
+      </c>
+      <c r="N261">
+        <v>3</v>
+      </c>
+      <c r="O261" t="s">
+        <v>100</v>
+      </c>
+      <c r="P261" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q261">
+        <v>2.75</v>
+      </c>
+      <c r="R261">
+        <v>1.91</v>
+      </c>
+      <c r="S261">
+        <v>5.5</v>
+      </c>
+      <c r="T261">
+        <v>1.62</v>
+      </c>
+      <c r="U261">
+        <v>2.2</v>
+      </c>
+      <c r="V261">
+        <v>4</v>
+      </c>
+      <c r="W261">
+        <v>1.22</v>
+      </c>
+      <c r="X261">
+        <v>13</v>
+      </c>
+      <c r="Y261">
+        <v>1.04</v>
+      </c>
+      <c r="Z261">
+        <v>1.95</v>
+      </c>
+      <c r="AA261">
+        <v>3.1</v>
+      </c>
+      <c r="AB261">
+        <v>4.5</v>
+      </c>
+      <c r="AC261">
+        <v>1.12</v>
+      </c>
+      <c r="AD261">
+        <v>5.75</v>
+      </c>
+      <c r="AE261">
+        <v>1.57</v>
+      </c>
+      <c r="AF261">
+        <v>2.25</v>
+      </c>
+      <c r="AG261">
+        <v>2.88</v>
+      </c>
+      <c r="AH261">
+        <v>1.4</v>
+      </c>
+      <c r="AI261">
+        <v>2.5</v>
+      </c>
+      <c r="AJ261">
+        <v>1.5</v>
+      </c>
+      <c r="AK261">
+        <v>1.2</v>
+      </c>
+      <c r="AL261">
+        <v>1.36</v>
+      </c>
+      <c r="AM261">
+        <v>1.78</v>
+      </c>
+      <c r="AN261">
+        <v>1.8</v>
+      </c>
+      <c r="AO261">
+        <v>0.88</v>
+      </c>
+      <c r="AP261">
+        <v>1.64</v>
+      </c>
+      <c r="AQ261">
+        <v>1.11</v>
+      </c>
+      <c r="AR261">
+        <v>1.76</v>
+      </c>
+      <c r="AS261">
+        <v>1.25</v>
+      </c>
+      <c r="AT261">
+        <v>3.01</v>
+      </c>
+      <c r="AU261">
+        <v>4</v>
+      </c>
+      <c r="AV261">
+        <v>4</v>
+      </c>
+      <c r="AW261">
+        <v>11</v>
+      </c>
+      <c r="AX261">
+        <v>3</v>
+      </c>
+      <c r="AY261">
+        <v>15</v>
+      </c>
+      <c r="AZ261">
+        <v>7</v>
+      </c>
+      <c r="BA261">
+        <v>9</v>
+      </c>
+      <c r="BB261">
+        <v>1</v>
+      </c>
+      <c r="BC261">
+        <v>10</v>
+      </c>
+      <c r="BD261">
+        <v>1.55</v>
+      </c>
+      <c r="BE261">
+        <v>6.25</v>
+      </c>
+      <c r="BF261">
+        <v>3</v>
+      </c>
+      <c r="BG261">
+        <v>1.38</v>
+      </c>
+      <c r="BH261">
+        <v>2.7</v>
+      </c>
+      <c r="BI261">
+        <v>1.7</v>
+      </c>
+      <c r="BJ261">
+        <v>1.95</v>
+      </c>
+      <c r="BK261">
+        <v>2.2</v>
+      </c>
+      <c r="BL261">
+        <v>1.55</v>
+      </c>
+      <c r="BM261">
+        <v>3.1</v>
+      </c>
+      <c r="BN261">
+        <v>1.3</v>
+      </c>
+      <c r="BO261">
+        <v>3.3</v>
+      </c>
+      <c r="BP261">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="322">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -978,6 +978,9 @@
   <si>
     <t>['4', '56', '90+5']</t>
   </si>
+  <si>
+    <t>['90+13']</t>
+  </si>
 </sst>
 </file>
 
@@ -1338,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP261"/>
+  <dimension ref="A1:BP262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -5795,7 +5798,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ22">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -7234,7 +7237,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ29">
         <v>1.11</v>
@@ -10739,7 +10742,7 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR46">
         <v>2.39</v>
@@ -12796,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ56">
         <v>1.38</v>
@@ -17331,7 +17334,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ78">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR78">
         <v>1.47</v>
@@ -17946,7 +17949,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ81">
         <v>1.86</v>
@@ -26804,7 +26807,7 @@
         <v>1.25</v>
       </c>
       <c r="AP124">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ124">
         <v>1.6</v>
@@ -27219,7 +27222,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ126">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR126">
         <v>2.03</v>
@@ -31133,7 +31136,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ145">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR145">
         <v>1.68</v>
@@ -37519,7 +37522,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ176">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR176">
         <v>1.58</v>
@@ -37722,7 +37725,7 @@
         <v>0.6</v>
       </c>
       <c r="AP177">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ177">
         <v>0.5</v>
@@ -42254,7 +42257,7 @@
         <v>0.8</v>
       </c>
       <c r="AP199">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ199">
         <v>0.63</v>
@@ -44317,7 +44320,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ209">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR209">
         <v>1.77</v>
@@ -48434,7 +48437,7 @@
         <v>1.14</v>
       </c>
       <c r="AP229">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ229">
         <v>1</v>
@@ -49879,7 +49882,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ236">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR236">
         <v>1.81</v>
@@ -51524,7 +51527,7 @@
         <v>1.44</v>
       </c>
       <c r="AP244">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AQ244">
         <v>1.65</v>
@@ -52557,7 +52560,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ249">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR249">
         <v>1.88</v>
@@ -55105,6 +55108,212 @@
       </c>
       <c r="BP261">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="262" spans="1:68">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>7820558</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262" t="s">
+        <v>69</v>
+      </c>
+      <c r="E262" s="2">
+        <v>45850.86458333334</v>
+      </c>
+      <c r="F262">
+        <v>1</v>
+      </c>
+      <c r="G262" t="s">
+        <v>97</v>
+      </c>
+      <c r="H262" t="s">
+        <v>75</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>0</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+      <c r="M262">
+        <v>1</v>
+      </c>
+      <c r="N262">
+        <v>1</v>
+      </c>
+      <c r="O262" t="s">
+        <v>100</v>
+      </c>
+      <c r="P262" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q262">
+        <v>2</v>
+      </c>
+      <c r="R262">
+        <v>2.25</v>
+      </c>
+      <c r="S262">
+        <v>7.5</v>
+      </c>
+      <c r="T262">
+        <v>1.4</v>
+      </c>
+      <c r="U262">
+        <v>2.75</v>
+      </c>
+      <c r="V262">
+        <v>3</v>
+      </c>
+      <c r="W262">
+        <v>1.36</v>
+      </c>
+      <c r="X262">
+        <v>9</v>
+      </c>
+      <c r="Y262">
+        <v>1.07</v>
+      </c>
+      <c r="Z262">
+        <v>1.48</v>
+      </c>
+      <c r="AA262">
+        <v>4</v>
+      </c>
+      <c r="AB262">
+        <v>7.5</v>
+      </c>
+      <c r="AC262">
+        <v>1.06</v>
+      </c>
+      <c r="AD262">
+        <v>8.5</v>
+      </c>
+      <c r="AE262">
+        <v>1.35</v>
+      </c>
+      <c r="AF262">
+        <v>3.1</v>
+      </c>
+      <c r="AG262">
+        <v>2.08</v>
+      </c>
+      <c r="AH262">
+        <v>1.73</v>
+      </c>
+      <c r="AI262">
+        <v>2.2</v>
+      </c>
+      <c r="AJ262">
+        <v>1.62</v>
+      </c>
+      <c r="AK262">
+        <v>1.1</v>
+      </c>
+      <c r="AL262">
+        <v>1.21</v>
+      </c>
+      <c r="AM262">
+        <v>2.6</v>
+      </c>
+      <c r="AN262">
+        <v>1.88</v>
+      </c>
+      <c r="AO262">
+        <v>1.11</v>
+      </c>
+      <c r="AP262">
+        <v>1.67</v>
+      </c>
+      <c r="AQ262">
+        <v>1.3</v>
+      </c>
+      <c r="AR262">
+        <v>1.72</v>
+      </c>
+      <c r="AS262">
+        <v>1.2</v>
+      </c>
+      <c r="AT262">
+        <v>2.92</v>
+      </c>
+      <c r="AU262">
+        <v>6</v>
+      </c>
+      <c r="AV262">
+        <v>4</v>
+      </c>
+      <c r="AW262">
+        <v>10</v>
+      </c>
+      <c r="AX262">
+        <v>4</v>
+      </c>
+      <c r="AY262">
+        <v>16</v>
+      </c>
+      <c r="AZ262">
+        <v>8</v>
+      </c>
+      <c r="BA262">
+        <v>5</v>
+      </c>
+      <c r="BB262">
+        <v>2</v>
+      </c>
+      <c r="BC262">
+        <v>7</v>
+      </c>
+      <c r="BD262">
+        <v>1.09</v>
+      </c>
+      <c r="BE262">
+        <v>11.5</v>
+      </c>
+      <c r="BF262">
+        <v>10.5</v>
+      </c>
+      <c r="BG262">
+        <v>1.35</v>
+      </c>
+      <c r="BH262">
+        <v>2.85</v>
+      </c>
+      <c r="BI262">
+        <v>1.63</v>
+      </c>
+      <c r="BJ262">
+        <v>2.05</v>
+      </c>
+      <c r="BK262">
+        <v>2.1</v>
+      </c>
+      <c r="BL262">
+        <v>1.6</v>
+      </c>
+      <c r="BM262">
+        <v>2.87</v>
+      </c>
+      <c r="BN262">
+        <v>1.34</v>
+      </c>
+      <c r="BO262">
+        <v>3.25</v>
+      </c>
+      <c r="BP262">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="324">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -754,6 +754,9 @@
     <t>['45+2']</t>
   </si>
   <si>
+    <t>['33', '55']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -980,6 +983,9 @@
   </si>
   <si>
     <t>['90+13']</t>
+  </si>
+  <si>
+    <t>['46', '83']</t>
   </si>
 </sst>
 </file>
@@ -1341,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP262"/>
+  <dimension ref="A1:BP270"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1597,7 +1603,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -2009,7 +2015,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2421,7 +2427,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2627,7 +2633,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -3245,7 +3251,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -5099,7 +5105,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5177,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ19">
         <v>0.89</v>
@@ -5383,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5511,7 +5517,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q21">
         <v>2.63</v>
@@ -5798,7 +5804,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ22">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5923,7 +5929,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6001,10 +6007,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6129,7 +6135,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6207,10 +6213,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6413,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25">
         <v>0.7</v>
@@ -6541,7 +6547,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6828,7 +6834,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ27">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -6953,7 +6959,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7237,10 +7243,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -9425,7 +9431,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9506,7 +9512,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ40">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR40">
         <v>1.12</v>
@@ -10249,7 +10255,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10455,7 +10461,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10661,7 +10667,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10742,7 +10748,7 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR46">
         <v>2.39</v>
@@ -10867,7 +10873,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10945,7 +10951,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AQ47">
         <v>0.29</v>
@@ -11073,7 +11079,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11154,7 +11160,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ48">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR48">
         <v>1.53</v>
@@ -11563,7 +11569,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50">
         <v>1.44</v>
@@ -11897,7 +11903,7 @@
         <v>131</v>
       </c>
       <c r="P52" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -12184,7 +12190,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ53">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR53">
         <v>1.58</v>
@@ -12309,7 +12315,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12387,7 +12393,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ54">
         <v>0.5</v>
@@ -12596,7 +12602,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AR55">
         <v>1.6</v>
@@ -12799,7 +12805,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
         <v>1.38</v>
@@ -13008,7 +13014,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ57">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR57">
         <v>0.73</v>
@@ -13133,7 +13139,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13417,7 +13423,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13623,7 +13629,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ60">
         <v>0.89</v>
@@ -13751,7 +13757,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -13832,7 +13838,7 @@
         <v>2</v>
       </c>
       <c r="AQ61">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR61">
         <v>0.96</v>
@@ -14987,7 +14993,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -16017,7 +16023,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -16716,7 +16722,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ75">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR75">
         <v>1.66</v>
@@ -17047,7 +17053,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q77">
         <v>5</v>
@@ -17253,7 +17259,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q78">
         <v>2.5</v>
@@ -17334,7 +17340,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ78">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR78">
         <v>1.47</v>
@@ -17459,7 +17465,7 @@
         <v>148</v>
       </c>
       <c r="P79" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q79">
         <v>3.2</v>
@@ -17746,7 +17752,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ80">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR80">
         <v>1.81</v>
@@ -17871,7 +17877,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -17949,7 +17955,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
         <v>1.86</v>
@@ -18077,7 +18083,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18567,7 +18573,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
         <v>0.14</v>
@@ -18695,7 +18701,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -18773,7 +18779,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ85">
         <v>0.5</v>
@@ -18979,7 +18985,7 @@
         <v>3</v>
       </c>
       <c r="AP86">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AQ86">
         <v>1.33</v>
@@ -19185,7 +19191,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ87">
         <v>0.29</v>
@@ -19394,7 +19400,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AR88">
         <v>1.23</v>
@@ -19519,7 +19525,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19725,7 +19731,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19806,7 +19812,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR90">
         <v>1.46</v>
@@ -20343,7 +20349,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20424,7 +20430,7 @@
         <v>2</v>
       </c>
       <c r="AQ93">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR93">
         <v>1.86</v>
@@ -20836,7 +20842,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ95">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR95">
         <v>1.94</v>
@@ -20961,7 +20967,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -21167,7 +21173,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21451,7 +21457,7 @@
         <v>0</v>
       </c>
       <c r="AP98">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ98">
         <v>0.75</v>
@@ -21657,10 +21663,10 @@
         <v>2.33</v>
       </c>
       <c r="AP99">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ99">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR99">
         <v>1.77</v>
@@ -21785,7 +21791,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23308,7 +23314,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ107">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR107">
         <v>1.43</v>
@@ -23433,7 +23439,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23639,7 +23645,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23845,7 +23851,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -23923,7 +23929,7 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ110">
         <v>1.44</v>
@@ -24257,7 +24263,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24544,7 +24550,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ113">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR113">
         <v>1.81</v>
@@ -24669,7 +24675,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24875,7 +24881,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -25081,7 +25087,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25287,7 +25293,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25574,7 +25580,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ118">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AR118">
         <v>1.5</v>
@@ -26111,7 +26117,7 @@
         <v>175</v>
       </c>
       <c r="P121" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q121">
         <v>4.33</v>
@@ -26317,7 +26323,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26523,7 +26529,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26604,7 +26610,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ123">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AR123">
         <v>1.76</v>
@@ -26807,7 +26813,7 @@
         <v>1.25</v>
       </c>
       <c r="AP124">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ124">
         <v>1.6</v>
@@ -27219,10 +27225,10 @@
         <v>1.67</v>
       </c>
       <c r="AP126">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AQ126">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR126">
         <v>2.03</v>
@@ -27553,7 +27559,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28046,7 +28052,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ130">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR130">
         <v>1.81</v>
@@ -28377,7 +28383,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28455,7 +28461,7 @@
         <v>1.75</v>
       </c>
       <c r="AP132">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ132">
         <v>1.33</v>
@@ -28867,7 +28873,7 @@
         <v>1.6</v>
       </c>
       <c r="AP134">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ134">
         <v>1.56</v>
@@ -28995,7 +29001,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -29282,7 +29288,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ136">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR136">
         <v>1.23</v>
@@ -29897,7 +29903,7 @@
         <v>0.8</v>
       </c>
       <c r="AP139">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ139">
         <v>0.5</v>
@@ -30103,7 +30109,7 @@
         <v>1.75</v>
       </c>
       <c r="AP140">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ140">
         <v>1.33</v>
@@ -30309,7 +30315,7 @@
         <v>1.33</v>
       </c>
       <c r="AP141">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -30930,7 +30936,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ144">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR144">
         <v>1.91</v>
@@ -31136,7 +31142,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ145">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR145">
         <v>1.68</v>
@@ -31261,7 +31267,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31467,7 +31473,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31548,7 +31554,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ147">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR147">
         <v>1.38</v>
@@ -31673,7 +31679,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31879,7 +31885,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -32085,7 +32091,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32703,7 +32709,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33115,7 +33121,7 @@
         <v>192</v>
       </c>
       <c r="P155" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33527,7 +33533,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -34351,7 +34357,7 @@
         <v>174</v>
       </c>
       <c r="P161" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34763,7 +34769,7 @@
         <v>196</v>
       </c>
       <c r="P163" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q163">
         <v>2.1</v>
@@ -34969,7 +34975,7 @@
         <v>197</v>
       </c>
       <c r="P164" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q164">
         <v>3.75</v>
@@ -35253,7 +35259,7 @@
         <v>0.2</v>
       </c>
       <c r="AP165">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ165">
         <v>0.75</v>
@@ -35668,7 +35674,7 @@
         <v>2</v>
       </c>
       <c r="AQ167">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR167">
         <v>1.93</v>
@@ -35793,7 +35799,7 @@
         <v>100</v>
       </c>
       <c r="P168" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q168">
         <v>4.33</v>
@@ -35874,7 +35880,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ168">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR168">
         <v>1.54</v>
@@ -35999,7 +36005,7 @@
         <v>199</v>
       </c>
       <c r="P169" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q169">
         <v>2.75</v>
@@ -36077,7 +36083,7 @@
         <v>0.8</v>
       </c>
       <c r="AP169">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ169">
         <v>0.88</v>
@@ -36489,7 +36495,7 @@
         <v>0.67</v>
       </c>
       <c r="AP171">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ171">
         <v>0.5</v>
@@ -36617,7 +36623,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q172">
         <v>2.38</v>
@@ -36695,7 +36701,7 @@
         <v>0.6</v>
       </c>
       <c r="AP172">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ172">
         <v>0.88</v>
@@ -36901,7 +36907,7 @@
         <v>1.4</v>
       </c>
       <c r="AP173">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AQ173">
         <v>1.57</v>
@@ -37029,7 +37035,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q174">
         <v>3.25</v>
@@ -37110,7 +37116,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ174">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AR174">
         <v>2.03</v>
@@ -37316,7 +37322,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ175">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR175">
         <v>1.83</v>
@@ -37522,7 +37528,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ176">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR176">
         <v>1.58</v>
@@ -37725,7 +37731,7 @@
         <v>0.6</v>
       </c>
       <c r="AP177">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ177">
         <v>0.5</v>
@@ -38265,7 +38271,7 @@
         <v>209</v>
       </c>
       <c r="P180" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38346,7 +38352,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ180">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR180">
         <v>1.79</v>
@@ -38471,7 +38477,7 @@
         <v>100</v>
       </c>
       <c r="P181" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38677,7 +38683,7 @@
         <v>108</v>
       </c>
       <c r="P182" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39501,7 +39507,7 @@
         <v>203</v>
       </c>
       <c r="P186" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39707,7 +39713,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q187">
         <v>4</v>
@@ -39785,7 +39791,7 @@
         <v>1</v>
       </c>
       <c r="AP187">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ187">
         <v>0.7</v>
@@ -40325,7 +40331,7 @@
         <v>151</v>
       </c>
       <c r="P190" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q190">
         <v>2.2</v>
@@ -40531,7 +40537,7 @@
         <v>100</v>
       </c>
       <c r="P191" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q191">
         <v>4</v>
@@ -40737,7 +40743,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41149,7 +41155,7 @@
         <v>100</v>
       </c>
       <c r="P194" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q194">
         <v>2.4</v>
@@ -41767,7 +41773,7 @@
         <v>100</v>
       </c>
       <c r="P197" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q197">
         <v>4.75</v>
@@ -41845,7 +41851,7 @@
         <v>1.33</v>
       </c>
       <c r="AP197">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ197">
         <v>1.57</v>
@@ -41973,7 +41979,7 @@
         <v>100</v>
       </c>
       <c r="P198" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q198">
         <v>3.1</v>
@@ -42051,7 +42057,7 @@
         <v>0.67</v>
       </c>
       <c r="AP198">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ198">
         <v>0.88</v>
@@ -42257,10 +42263,10 @@
         <v>0.8</v>
       </c>
       <c r="AP199">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ199">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR199">
         <v>1.67</v>
@@ -42875,7 +42881,7 @@
         <v>1.43</v>
       </c>
       <c r="AP202">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ202">
         <v>1.22</v>
@@ -43290,7 +43296,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ204">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR204">
         <v>1.17</v>
@@ -43699,7 +43705,7 @@
         <v>1.17</v>
       </c>
       <c r="AP206">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AQ206">
         <v>1.67</v>
@@ -43905,10 +43911,10 @@
         <v>0.14</v>
       </c>
       <c r="AP207">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ207">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR207">
         <v>1.36</v>
@@ -44114,7 +44120,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ208">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR208">
         <v>1.47</v>
@@ -44320,7 +44326,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ209">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR209">
         <v>1.77</v>
@@ -44857,7 +44863,7 @@
         <v>100</v>
       </c>
       <c r="P212" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45063,7 +45069,7 @@
         <v>102</v>
       </c>
       <c r="P213" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -46505,7 +46511,7 @@
         <v>226</v>
       </c>
       <c r="P220" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47123,7 +47129,7 @@
         <v>188</v>
       </c>
       <c r="P223" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47822,7 +47828,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ226">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AR226">
         <v>1.76</v>
@@ -48028,7 +48034,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ227">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR227">
         <v>1.33</v>
@@ -48153,7 +48159,7 @@
         <v>232</v>
       </c>
       <c r="P228" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q228">
         <v>4.33</v>
@@ -48437,7 +48443,7 @@
         <v>1.14</v>
       </c>
       <c r="AP229">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ229">
         <v>1</v>
@@ -48771,7 +48777,7 @@
         <v>156</v>
       </c>
       <c r="P231" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q231">
         <v>3.75</v>
@@ -48852,7 +48858,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ231">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR231">
         <v>1.87</v>
@@ -49261,10 +49267,10 @@
         <v>1.71</v>
       </c>
       <c r="AP233">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AQ233">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR233">
         <v>1.8</v>
@@ -49389,7 +49395,7 @@
         <v>236</v>
       </c>
       <c r="P234" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q234">
         <v>2.75</v>
@@ -49467,10 +49473,10 @@
         <v>0.13</v>
       </c>
       <c r="AP234">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ234">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR234">
         <v>2.12</v>
@@ -49673,10 +49679,10 @@
         <v>1.29</v>
       </c>
       <c r="AP235">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ235">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AR235">
         <v>1.57</v>
@@ -49801,7 +49807,7 @@
         <v>100</v>
       </c>
       <c r="P236" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q236">
         <v>2.25</v>
@@ -49879,10 +49885,10 @@
         <v>1</v>
       </c>
       <c r="AP236">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ236">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR236">
         <v>1.81</v>
@@ -50291,7 +50297,7 @@
         <v>1.43</v>
       </c>
       <c r="AP238">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ238">
         <v>1.67</v>
@@ -50419,7 +50425,7 @@
         <v>100</v>
       </c>
       <c r="P239" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q239">
         <v>3.6</v>
@@ -51037,7 +51043,7 @@
         <v>239</v>
       </c>
       <c r="P242" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q242">
         <v>2.95</v>
@@ -51115,7 +51121,7 @@
         <v>1.69</v>
       </c>
       <c r="AP242">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AQ242">
         <v>1.59</v>
@@ -51321,7 +51327,7 @@
         <v>1.31</v>
       </c>
       <c r="AP243">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AQ243">
         <v>1.24</v>
@@ -51449,7 +51455,7 @@
         <v>100</v>
       </c>
       <c r="P244" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q244">
         <v>2.4</v>
@@ -51527,7 +51533,7 @@
         <v>1.44</v>
       </c>
       <c r="AP244">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ244">
         <v>1.65</v>
@@ -51939,7 +51945,7 @@
         <v>1.69</v>
       </c>
       <c r="AP246">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AQ246">
         <v>1.59</v>
@@ -52067,7 +52073,7 @@
         <v>241</v>
       </c>
       <c r="P247" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q247">
         <v>2.2</v>
@@ -52148,7 +52154,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ247">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AR247">
         <v>1.69</v>
@@ -52273,7 +52279,7 @@
         <v>242</v>
       </c>
       <c r="P248" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q248">
         <v>2.63</v>
@@ -52351,7 +52357,7 @@
         <v>1.5</v>
       </c>
       <c r="AP248">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AQ248">
         <v>1.41</v>
@@ -52560,7 +52566,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ249">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AR249">
         <v>1.88</v>
@@ -52763,10 +52769,10 @@
         <v>1.76</v>
       </c>
       <c r="AP250">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AQ250">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AR250">
         <v>1.42</v>
@@ -52891,7 +52897,7 @@
         <v>179</v>
       </c>
       <c r="P251" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q251">
         <v>2.6</v>
@@ -52972,7 +52978,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ251">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AR251">
         <v>1.67</v>
@@ -53097,7 +53103,7 @@
         <v>100</v>
       </c>
       <c r="P252" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q252">
         <v>2.88</v>
@@ -53178,7 +53184,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ252">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AR252">
         <v>1.54</v>
@@ -53587,10 +53593,10 @@
         <v>1.83</v>
       </c>
       <c r="AP254">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AQ254">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AR254">
         <v>1.51</v>
@@ -53793,7 +53799,7 @@
         <v>1.5</v>
       </c>
       <c r="AP255">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AQ255">
         <v>1.65</v>
@@ -53921,7 +53927,7 @@
         <v>100</v>
       </c>
       <c r="P256" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q256">
         <v>3.2</v>
@@ -53999,7 +54005,7 @@
         <v>1.58</v>
       </c>
       <c r="AP256">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AQ256">
         <v>1.65</v>
@@ -54208,7 +54214,7 @@
         <v>1</v>
       </c>
       <c r="AQ257">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR257">
         <v>1.93</v>
@@ -54333,7 +54339,7 @@
         <v>245</v>
       </c>
       <c r="P258" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q258">
         <v>2.88</v>
@@ -54411,10 +54417,10 @@
         <v>1.56</v>
       </c>
       <c r="AP258">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ258">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR258">
         <v>2.03</v>
@@ -54617,7 +54623,7 @@
         <v>1</v>
       </c>
       <c r="AP259">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ259">
         <v>1</v>
@@ -54703,7 +54709,7 @@
         <v>259</v>
       </c>
       <c r="B260">
-        <v>7820564</v>
+        <v>7820557</v>
       </c>
       <c r="C260" t="s">
         <v>68</v>
@@ -54718,10 +54724,10 @@
         <v>1</v>
       </c>
       <c r="G260" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H260" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I260">
         <v>0</v>
@@ -54736,37 +54742,37 @@
         <v>0</v>
       </c>
       <c r="M260">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N260">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O260" t="s">
         <v>100</v>
       </c>
       <c r="P260" t="s">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="Q260">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R260">
         <v>1.91</v>
       </c>
       <c r="S260">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="T260">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U260">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V260">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="W260">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X260">
         <v>13</v>
@@ -54775,13 +54781,13 @@
         <v>1.04</v>
       </c>
       <c r="Z260">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AA260">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB260">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AC260">
         <v>1.12</v>
@@ -54790,118 +54796,118 @@
         <v>5.75</v>
       </c>
       <c r="AE260">
+        <v>1.57</v>
+      </c>
+      <c r="AF260">
+        <v>2.25</v>
+      </c>
+      <c r="AG260">
+        <v>2.88</v>
+      </c>
+      <c r="AH260">
+        <v>1.4</v>
+      </c>
+      <c r="AI260">
+        <v>2.5</v>
+      </c>
+      <c r="AJ260">
+        <v>1.5</v>
+      </c>
+      <c r="AK260">
+        <v>1.2</v>
+      </c>
+      <c r="AL260">
+        <v>1.36</v>
+      </c>
+      <c r="AM260">
+        <v>1.78</v>
+      </c>
+      <c r="AN260">
+        <v>1.8</v>
+      </c>
+      <c r="AO260">
+        <v>0.88</v>
+      </c>
+      <c r="AP260">
+        <v>1.5</v>
+      </c>
+      <c r="AQ260">
+        <v>1.3</v>
+      </c>
+      <c r="AR260">
+        <v>1.76</v>
+      </c>
+      <c r="AS260">
+        <v>1.25</v>
+      </c>
+      <c r="AT260">
+        <v>3.01</v>
+      </c>
+      <c r="AU260">
+        <v>4</v>
+      </c>
+      <c r="AV260">
+        <v>4</v>
+      </c>
+      <c r="AW260">
+        <v>11</v>
+      </c>
+      <c r="AX260">
+        <v>3</v>
+      </c>
+      <c r="AY260">
+        <v>15</v>
+      </c>
+      <c r="AZ260">
+        <v>7</v>
+      </c>
+      <c r="BA260">
+        <v>9</v>
+      </c>
+      <c r="BB260">
+        <v>1</v>
+      </c>
+      <c r="BC260">
+        <v>10</v>
+      </c>
+      <c r="BD260">
         <v>1.55</v>
-      </c>
-      <c r="AF260">
-        <v>2.3</v>
-      </c>
-      <c r="AG260">
-        <v>2.7</v>
-      </c>
-      <c r="AH260">
-        <v>1.44</v>
-      </c>
-      <c r="AI260">
-        <v>2.2</v>
-      </c>
-      <c r="AJ260">
-        <v>1.62</v>
-      </c>
-      <c r="AK260">
-        <v>1.26</v>
-      </c>
-      <c r="AL260">
-        <v>1.37</v>
-      </c>
-      <c r="AM260">
-        <v>1.66</v>
-      </c>
-      <c r="AN260">
-        <v>1.5</v>
-      </c>
-      <c r="AO260">
-        <v>0.4</v>
-      </c>
-      <c r="AP260">
-        <v>1.33</v>
-      </c>
-      <c r="AQ260">
-        <v>0.64</v>
-      </c>
-      <c r="AR260">
-        <v>1.55</v>
-      </c>
-      <c r="AS260">
-        <v>1.21</v>
-      </c>
-      <c r="AT260">
-        <v>2.76</v>
-      </c>
-      <c r="AU260">
-        <v>9</v>
-      </c>
-      <c r="AV260">
-        <v>8</v>
-      </c>
-      <c r="AW260">
-        <v>9</v>
-      </c>
-      <c r="AX260">
-        <v>12</v>
-      </c>
-      <c r="AY260">
-        <v>18</v>
-      </c>
-      <c r="AZ260">
-        <v>20</v>
-      </c>
-      <c r="BA260">
-        <v>7</v>
-      </c>
-      <c r="BB260">
-        <v>8</v>
-      </c>
-      <c r="BC260">
-        <v>15</v>
-      </c>
-      <c r="BD260">
-        <v>1.6</v>
       </c>
       <c r="BE260">
         <v>6.25</v>
       </c>
       <c r="BF260">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="BG260">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="BH260">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="BI260">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="BJ260">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BK260">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BL260">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BM260">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BN260">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BO260">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BP260">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="261" spans="1:68">
@@ -54909,7 +54915,7 @@
         <v>260</v>
       </c>
       <c r="B261">
-        <v>7820557</v>
+        <v>7820564</v>
       </c>
       <c r="C261" t="s">
         <v>68</v>
@@ -54924,10 +54930,10 @@
         <v>1</v>
       </c>
       <c r="G261" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H261" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I261">
         <v>0</v>
@@ -54942,37 +54948,37 @@
         <v>0</v>
       </c>
       <c r="M261">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N261">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O261" t="s">
         <v>100</v>
       </c>
       <c r="P261" t="s">
-        <v>320</v>
+        <v>169</v>
       </c>
       <c r="Q261">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R261">
         <v>1.91</v>
       </c>
       <c r="S261">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="T261">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="U261">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V261">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W261">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X261">
         <v>13</v>
@@ -54981,13 +54987,13 @@
         <v>1.04</v>
       </c>
       <c r="Z261">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA261">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB261">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC261">
         <v>1.12</v>
@@ -54996,118 +55002,118 @@
         <v>5.75</v>
       </c>
       <c r="AE261">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AF261">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG261">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH261">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI261">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ261">
+        <v>1.62</v>
+      </c>
+      <c r="AK261">
+        <v>1.26</v>
+      </c>
+      <c r="AL261">
+        <v>1.37</v>
+      </c>
+      <c r="AM261">
+        <v>1.66</v>
+      </c>
+      <c r="AN261">
         <v>1.5</v>
       </c>
-      <c r="AK261">
+      <c r="AO261">
+        <v>0.4</v>
+      </c>
+      <c r="AP261">
         <v>1.2</v>
       </c>
-      <c r="AL261">
-        <v>1.36</v>
-      </c>
-      <c r="AM261">
-        <v>1.78</v>
-      </c>
-      <c r="AN261">
-        <v>1.8</v>
-      </c>
-      <c r="AO261">
-        <v>0.88</v>
-      </c>
-      <c r="AP261">
-        <v>1.64</v>
-      </c>
       <c r="AQ261">
-        <v>1.11</v>
+        <v>0.83</v>
       </c>
       <c r="AR261">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AS261">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AT261">
-        <v>3.01</v>
+        <v>2.76</v>
       </c>
       <c r="AU261">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV261">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AW261">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX261">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AY261">
+        <v>18</v>
+      </c>
+      <c r="AZ261">
+        <v>20</v>
+      </c>
+      <c r="BA261">
+        <v>7</v>
+      </c>
+      <c r="BB261">
+        <v>8</v>
+      </c>
+      <c r="BC261">
         <v>15</v>
       </c>
-      <c r="AZ261">
-        <v>7</v>
-      </c>
-      <c r="BA261">
-        <v>9</v>
-      </c>
-      <c r="BB261">
-        <v>1</v>
-      </c>
-      <c r="BC261">
-        <v>10</v>
-      </c>
       <c r="BD261">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BE261">
         <v>6.25</v>
       </c>
       <c r="BF261">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="BG261">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="BH261">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="BI261">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="BJ261">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BK261">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BL261">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BM261">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="BN261">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BO261">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BP261">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="262" spans="1:68">
@@ -55157,7 +55163,7 @@
         <v>100</v>
       </c>
       <c r="P262" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q262">
         <v>2</v>
@@ -55235,10 +55241,10 @@
         <v>1.11</v>
       </c>
       <c r="AP262">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ262">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR262">
         <v>1.72</v>
@@ -55314,6 +55320,1654 @@
       </c>
       <c r="BP262">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="263" spans="1:68">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>7940203</v>
+      </c>
+      <c r="C263" t="s">
+        <v>68</v>
+      </c>
+      <c r="D263" t="s">
+        <v>69</v>
+      </c>
+      <c r="E263" s="2">
+        <v>45851.5</v>
+      </c>
+      <c r="F263">
+        <v>1</v>
+      </c>
+      <c r="G263" t="s">
+        <v>97</v>
+      </c>
+      <c r="H263" t="s">
+        <v>75</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>0</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+      <c r="M263">
+        <v>1</v>
+      </c>
+      <c r="N263">
+        <v>1</v>
+      </c>
+      <c r="O263" t="s">
+        <v>100</v>
+      </c>
+      <c r="P263" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q263">
+        <v>0</v>
+      </c>
+      <c r="R263">
+        <v>0</v>
+      </c>
+      <c r="S263">
+        <v>0</v>
+      </c>
+      <c r="T263">
+        <v>0</v>
+      </c>
+      <c r="U263">
+        <v>0</v>
+      </c>
+      <c r="V263">
+        <v>0</v>
+      </c>
+      <c r="W263">
+        <v>0</v>
+      </c>
+      <c r="X263">
+        <v>0</v>
+      </c>
+      <c r="Y263">
+        <v>0</v>
+      </c>
+      <c r="Z263">
+        <v>0</v>
+      </c>
+      <c r="AA263">
+        <v>0</v>
+      </c>
+      <c r="AB263">
+        <v>0</v>
+      </c>
+      <c r="AC263">
+        <v>0</v>
+      </c>
+      <c r="AD263">
+        <v>0</v>
+      </c>
+      <c r="AE263">
+        <v>0</v>
+      </c>
+      <c r="AF263">
+        <v>0</v>
+      </c>
+      <c r="AG263">
+        <v>0</v>
+      </c>
+      <c r="AH263">
+        <v>0</v>
+      </c>
+      <c r="AI263">
+        <v>0</v>
+      </c>
+      <c r="AJ263">
+        <v>0</v>
+      </c>
+      <c r="AK263">
+        <v>0</v>
+      </c>
+      <c r="AL263">
+        <v>0</v>
+      </c>
+      <c r="AM263">
+        <v>0</v>
+      </c>
+      <c r="AN263">
+        <v>1.67</v>
+      </c>
+      <c r="AO263">
+        <v>1.3</v>
+      </c>
+      <c r="AP263">
+        <v>1.5</v>
+      </c>
+      <c r="AQ263">
+        <v>1.45</v>
+      </c>
+      <c r="AR263">
+        <v>1.73</v>
+      </c>
+      <c r="AS263">
+        <v>1.18</v>
+      </c>
+      <c r="AT263">
+        <v>2.91</v>
+      </c>
+      <c r="AU263">
+        <v>2</v>
+      </c>
+      <c r="AV263">
+        <v>5</v>
+      </c>
+      <c r="AW263">
+        <v>7</v>
+      </c>
+      <c r="AX263">
+        <v>2</v>
+      </c>
+      <c r="AY263">
+        <v>9</v>
+      </c>
+      <c r="AZ263">
+        <v>7</v>
+      </c>
+      <c r="BA263">
+        <v>5</v>
+      </c>
+      <c r="BB263">
+        <v>2</v>
+      </c>
+      <c r="BC263">
+        <v>7</v>
+      </c>
+      <c r="BD263">
+        <v>0</v>
+      </c>
+      <c r="BE263">
+        <v>0</v>
+      </c>
+      <c r="BF263">
+        <v>0</v>
+      </c>
+      <c r="BG263">
+        <v>0</v>
+      </c>
+      <c r="BH263">
+        <v>0</v>
+      </c>
+      <c r="BI263">
+        <v>0</v>
+      </c>
+      <c r="BJ263">
+        <v>0</v>
+      </c>
+      <c r="BK263">
+        <v>0</v>
+      </c>
+      <c r="BL263">
+        <v>0</v>
+      </c>
+      <c r="BM263">
+        <v>0</v>
+      </c>
+      <c r="BN263">
+        <v>0</v>
+      </c>
+      <c r="BO263">
+        <v>0</v>
+      </c>
+      <c r="BP263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:68">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>7940197</v>
+      </c>
+      <c r="C264" t="s">
+        <v>68</v>
+      </c>
+      <c r="D264" t="s">
+        <v>69</v>
+      </c>
+      <c r="E264" s="2">
+        <v>45851.5</v>
+      </c>
+      <c r="F264">
+        <v>1</v>
+      </c>
+      <c r="G264" t="s">
+        <v>87</v>
+      </c>
+      <c r="H264" t="s">
+        <v>70</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>0</v>
+      </c>
+      <c r="L264">
+        <v>1</v>
+      </c>
+      <c r="M264">
+        <v>1</v>
+      </c>
+      <c r="N264">
+        <v>2</v>
+      </c>
+      <c r="O264" t="s">
+        <v>138</v>
+      </c>
+      <c r="P264" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q264">
+        <v>0</v>
+      </c>
+      <c r="R264">
+        <v>0</v>
+      </c>
+      <c r="S264">
+        <v>0</v>
+      </c>
+      <c r="T264">
+        <v>0</v>
+      </c>
+      <c r="U264">
+        <v>0</v>
+      </c>
+      <c r="V264">
+        <v>0</v>
+      </c>
+      <c r="W264">
+        <v>0</v>
+      </c>
+      <c r="X264">
+        <v>0</v>
+      </c>
+      <c r="Y264">
+        <v>0</v>
+      </c>
+      <c r="Z264">
+        <v>0</v>
+      </c>
+      <c r="AA264">
+        <v>0</v>
+      </c>
+      <c r="AB264">
+        <v>0</v>
+      </c>
+      <c r="AC264">
+        <v>0</v>
+      </c>
+      <c r="AD264">
+        <v>0</v>
+      </c>
+      <c r="AE264">
+        <v>0</v>
+      </c>
+      <c r="AF264">
+        <v>0</v>
+      </c>
+      <c r="AG264">
+        <v>0</v>
+      </c>
+      <c r="AH264">
+        <v>0</v>
+      </c>
+      <c r="AI264">
+        <v>0</v>
+      </c>
+      <c r="AJ264">
+        <v>0</v>
+      </c>
+      <c r="AK264">
+        <v>0</v>
+      </c>
+      <c r="AL264">
+        <v>0</v>
+      </c>
+      <c r="AM264">
+        <v>0</v>
+      </c>
+      <c r="AN264">
+        <v>2.5</v>
+      </c>
+      <c r="AO264">
+        <v>1</v>
+      </c>
+      <c r="AP264">
+        <v>2.36</v>
+      </c>
+      <c r="AQ264">
+        <v>1</v>
+      </c>
+      <c r="AR264">
+        <v>1.73</v>
+      </c>
+      <c r="AS264">
+        <v>1.28</v>
+      </c>
+      <c r="AT264">
+        <v>3.01</v>
+      </c>
+      <c r="AU264">
+        <v>6</v>
+      </c>
+      <c r="AV264">
+        <v>4</v>
+      </c>
+      <c r="AW264">
+        <v>5</v>
+      </c>
+      <c r="AX264">
+        <v>6</v>
+      </c>
+      <c r="AY264">
+        <v>11</v>
+      </c>
+      <c r="AZ264">
+        <v>10</v>
+      </c>
+      <c r="BA264">
+        <v>7</v>
+      </c>
+      <c r="BB264">
+        <v>2</v>
+      </c>
+      <c r="BC264">
+        <v>9</v>
+      </c>
+      <c r="BD264">
+        <v>0</v>
+      </c>
+      <c r="BE264">
+        <v>0</v>
+      </c>
+      <c r="BF264">
+        <v>0</v>
+      </c>
+      <c r="BG264">
+        <v>0</v>
+      </c>
+      <c r="BH264">
+        <v>0</v>
+      </c>
+      <c r="BI264">
+        <v>0</v>
+      </c>
+      <c r="BJ264">
+        <v>0</v>
+      </c>
+      <c r="BK264">
+        <v>0</v>
+      </c>
+      <c r="BL264">
+        <v>0</v>
+      </c>
+      <c r="BM264">
+        <v>0</v>
+      </c>
+      <c r="BN264">
+        <v>0</v>
+      </c>
+      <c r="BO264">
+        <v>0</v>
+      </c>
+      <c r="BP264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:68">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>7940201</v>
+      </c>
+      <c r="C265" t="s">
+        <v>68</v>
+      </c>
+      <c r="D265" t="s">
+        <v>69</v>
+      </c>
+      <c r="E265" s="2">
+        <v>45851.5</v>
+      </c>
+      <c r="F265">
+        <v>1</v>
+      </c>
+      <c r="G265" t="s">
+        <v>91</v>
+      </c>
+      <c r="H265" t="s">
+        <v>79</v>
+      </c>
+      <c r="I265">
+        <v>1</v>
+      </c>
+      <c r="J265">
+        <v>1</v>
+      </c>
+      <c r="K265">
+        <v>2</v>
+      </c>
+      <c r="L265">
+        <v>1</v>
+      </c>
+      <c r="M265">
+        <v>2</v>
+      </c>
+      <c r="N265">
+        <v>3</v>
+      </c>
+      <c r="O265" t="s">
+        <v>245</v>
+      </c>
+      <c r="P265" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q265">
+        <v>0</v>
+      </c>
+      <c r="R265">
+        <v>0</v>
+      </c>
+      <c r="S265">
+        <v>0</v>
+      </c>
+      <c r="T265">
+        <v>0</v>
+      </c>
+      <c r="U265">
+        <v>0</v>
+      </c>
+      <c r="V265">
+        <v>0</v>
+      </c>
+      <c r="W265">
+        <v>0</v>
+      </c>
+      <c r="X265">
+        <v>0</v>
+      </c>
+      <c r="Y265">
+        <v>0</v>
+      </c>
+      <c r="Z265">
+        <v>0</v>
+      </c>
+      <c r="AA265">
+        <v>0</v>
+      </c>
+      <c r="AB265">
+        <v>0</v>
+      </c>
+      <c r="AC265">
+        <v>0</v>
+      </c>
+      <c r="AD265">
+        <v>0</v>
+      </c>
+      <c r="AE265">
+        <v>0</v>
+      </c>
+      <c r="AF265">
+        <v>0</v>
+      </c>
+      <c r="AG265">
+        <v>0</v>
+      </c>
+      <c r="AH265">
+        <v>0</v>
+      </c>
+      <c r="AI265">
+        <v>0</v>
+      </c>
+      <c r="AJ265">
+        <v>0</v>
+      </c>
+      <c r="AK265">
+        <v>0</v>
+      </c>
+      <c r="AL265">
+        <v>0</v>
+      </c>
+      <c r="AM265">
+        <v>0</v>
+      </c>
+      <c r="AN265">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO265">
+        <v>1.7</v>
+      </c>
+      <c r="AP265">
+        <v>0.5</v>
+      </c>
+      <c r="AQ265">
+        <v>1.82</v>
+      </c>
+      <c r="AR265">
+        <v>1.93</v>
+      </c>
+      <c r="AS265">
+        <v>1.11</v>
+      </c>
+      <c r="AT265">
+        <v>3.04</v>
+      </c>
+      <c r="AU265">
+        <v>3</v>
+      </c>
+      <c r="AV265">
+        <v>3</v>
+      </c>
+      <c r="AW265">
+        <v>4</v>
+      </c>
+      <c r="AX265">
+        <v>3</v>
+      </c>
+      <c r="AY265">
+        <v>7</v>
+      </c>
+      <c r="AZ265">
+        <v>6</v>
+      </c>
+      <c r="BA265">
+        <v>1</v>
+      </c>
+      <c r="BB265">
+        <v>5</v>
+      </c>
+      <c r="BC265">
+        <v>6</v>
+      </c>
+      <c r="BD265">
+        <v>0</v>
+      </c>
+      <c r="BE265">
+        <v>0</v>
+      </c>
+      <c r="BF265">
+        <v>0</v>
+      </c>
+      <c r="BG265">
+        <v>0</v>
+      </c>
+      <c r="BH265">
+        <v>0</v>
+      </c>
+      <c r="BI265">
+        <v>0</v>
+      </c>
+      <c r="BJ265">
+        <v>0</v>
+      </c>
+      <c r="BK265">
+        <v>0</v>
+      </c>
+      <c r="BL265">
+        <v>0</v>
+      </c>
+      <c r="BM265">
+        <v>0</v>
+      </c>
+      <c r="BN265">
+        <v>0</v>
+      </c>
+      <c r="BO265">
+        <v>0</v>
+      </c>
+      <c r="BP265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:68">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>7940204</v>
+      </c>
+      <c r="C266" t="s">
+        <v>68</v>
+      </c>
+      <c r="D266" t="s">
+        <v>69</v>
+      </c>
+      <c r="E266" s="2">
+        <v>45851.5</v>
+      </c>
+      <c r="F266">
+        <v>1</v>
+      </c>
+      <c r="G266" t="s">
+        <v>92</v>
+      </c>
+      <c r="H266" t="s">
+        <v>81</v>
+      </c>
+      <c r="I266">
+        <v>0</v>
+      </c>
+      <c r="J266">
+        <v>1</v>
+      </c>
+      <c r="K266">
+        <v>1</v>
+      </c>
+      <c r="L266">
+        <v>0</v>
+      </c>
+      <c r="M266">
+        <v>1</v>
+      </c>
+      <c r="N266">
+        <v>1</v>
+      </c>
+      <c r="O266" t="s">
+        <v>100</v>
+      </c>
+      <c r="P266" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q266">
+        <v>0</v>
+      </c>
+      <c r="R266">
+        <v>0</v>
+      </c>
+      <c r="S266">
+        <v>0</v>
+      </c>
+      <c r="T266">
+        <v>0</v>
+      </c>
+      <c r="U266">
+        <v>0</v>
+      </c>
+      <c r="V266">
+        <v>0</v>
+      </c>
+      <c r="W266">
+        <v>0</v>
+      </c>
+      <c r="X266">
+        <v>0</v>
+      </c>
+      <c r="Y266">
+        <v>0</v>
+      </c>
+      <c r="Z266">
+        <v>0</v>
+      </c>
+      <c r="AA266">
+        <v>0</v>
+      </c>
+      <c r="AB266">
+        <v>0</v>
+      </c>
+      <c r="AC266">
+        <v>0</v>
+      </c>
+      <c r="AD266">
+        <v>0</v>
+      </c>
+      <c r="AE266">
+        <v>0</v>
+      </c>
+      <c r="AF266">
+        <v>0</v>
+      </c>
+      <c r="AG266">
+        <v>0</v>
+      </c>
+      <c r="AH266">
+        <v>0</v>
+      </c>
+      <c r="AI266">
+        <v>0</v>
+      </c>
+      <c r="AJ266">
+        <v>0</v>
+      </c>
+      <c r="AK266">
+        <v>0</v>
+      </c>
+      <c r="AL266">
+        <v>0</v>
+      </c>
+      <c r="AM266">
+        <v>0</v>
+      </c>
+      <c r="AN266">
+        <v>1.33</v>
+      </c>
+      <c r="AO266">
+        <v>0.64</v>
+      </c>
+      <c r="AP266">
+        <v>1.2</v>
+      </c>
+      <c r="AQ266">
+        <v>0.83</v>
+      </c>
+      <c r="AR266">
+        <v>1.6</v>
+      </c>
+      <c r="AS266">
+        <v>1.31</v>
+      </c>
+      <c r="AT266">
+        <v>2.91</v>
+      </c>
+      <c r="AU266">
+        <v>7</v>
+      </c>
+      <c r="AV266">
+        <v>6</v>
+      </c>
+      <c r="AW266">
+        <v>5</v>
+      </c>
+      <c r="AX266">
+        <v>5</v>
+      </c>
+      <c r="AY266">
+        <v>12</v>
+      </c>
+      <c r="AZ266">
+        <v>11</v>
+      </c>
+      <c r="BA266">
+        <v>7</v>
+      </c>
+      <c r="BB266">
+        <v>8</v>
+      </c>
+      <c r="BC266">
+        <v>15</v>
+      </c>
+      <c r="BD266">
+        <v>0</v>
+      </c>
+      <c r="BE266">
+        <v>0</v>
+      </c>
+      <c r="BF266">
+        <v>0</v>
+      </c>
+      <c r="BG266">
+        <v>0</v>
+      </c>
+      <c r="BH266">
+        <v>0</v>
+      </c>
+      <c r="BI266">
+        <v>0</v>
+      </c>
+      <c r="BJ266">
+        <v>0</v>
+      </c>
+      <c r="BK266">
+        <v>0</v>
+      </c>
+      <c r="BL266">
+        <v>0</v>
+      </c>
+      <c r="BM266">
+        <v>0</v>
+      </c>
+      <c r="BN266">
+        <v>0</v>
+      </c>
+      <c r="BO266">
+        <v>0</v>
+      </c>
+      <c r="BP266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:68">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7940200</v>
+      </c>
+      <c r="C267" t="s">
+        <v>68</v>
+      </c>
+      <c r="D267" t="s">
+        <v>69</v>
+      </c>
+      <c r="E267" s="2">
+        <v>45851.5</v>
+      </c>
+      <c r="F267">
+        <v>1</v>
+      </c>
+      <c r="G267" t="s">
+        <v>93</v>
+      </c>
+      <c r="H267" t="s">
+        <v>77</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>1</v>
+      </c>
+      <c r="K267">
+        <v>1</v>
+      </c>
+      <c r="L267">
+        <v>0</v>
+      </c>
+      <c r="M267">
+        <v>3</v>
+      </c>
+      <c r="N267">
+        <v>3</v>
+      </c>
+      <c r="O267" t="s">
+        <v>100</v>
+      </c>
+      <c r="P267" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q267">
+        <v>0</v>
+      </c>
+      <c r="R267">
+        <v>0</v>
+      </c>
+      <c r="S267">
+        <v>0</v>
+      </c>
+      <c r="T267">
+        <v>0</v>
+      </c>
+      <c r="U267">
+        <v>0</v>
+      </c>
+      <c r="V267">
+        <v>0</v>
+      </c>
+      <c r="W267">
+        <v>0</v>
+      </c>
+      <c r="X267">
+        <v>0</v>
+      </c>
+      <c r="Y267">
+        <v>0</v>
+      </c>
+      <c r="Z267">
+        <v>0</v>
+      </c>
+      <c r="AA267">
+        <v>0</v>
+      </c>
+      <c r="AB267">
+        <v>0</v>
+      </c>
+      <c r="AC267">
+        <v>0</v>
+      </c>
+      <c r="AD267">
+        <v>0</v>
+      </c>
+      <c r="AE267">
+        <v>0</v>
+      </c>
+      <c r="AF267">
+        <v>0</v>
+      </c>
+      <c r="AG267">
+        <v>0</v>
+      </c>
+      <c r="AH267">
+        <v>0</v>
+      </c>
+      <c r="AI267">
+        <v>0</v>
+      </c>
+      <c r="AJ267">
+        <v>0</v>
+      </c>
+      <c r="AK267">
+        <v>0</v>
+      </c>
+      <c r="AL267">
+        <v>0</v>
+      </c>
+      <c r="AM267">
+        <v>0</v>
+      </c>
+      <c r="AN267">
+        <v>1.64</v>
+      </c>
+      <c r="AO267">
+        <v>1.11</v>
+      </c>
+      <c r="AP267">
+        <v>1.5</v>
+      </c>
+      <c r="AQ267">
+        <v>1.3</v>
+      </c>
+      <c r="AR267">
+        <v>1.75</v>
+      </c>
+      <c r="AS267">
+        <v>1.21</v>
+      </c>
+      <c r="AT267">
+        <v>2.96</v>
+      </c>
+      <c r="AU267">
+        <v>2</v>
+      </c>
+      <c r="AV267">
+        <v>4</v>
+      </c>
+      <c r="AW267">
+        <v>9</v>
+      </c>
+      <c r="AX267">
+        <v>2</v>
+      </c>
+      <c r="AY267">
+        <v>11</v>
+      </c>
+      <c r="AZ267">
+        <v>6</v>
+      </c>
+      <c r="BA267">
+        <v>9</v>
+      </c>
+      <c r="BB267">
+        <v>1</v>
+      </c>
+      <c r="BC267">
+        <v>10</v>
+      </c>
+      <c r="BD267">
+        <v>0</v>
+      </c>
+      <c r="BE267">
+        <v>0</v>
+      </c>
+      <c r="BF267">
+        <v>0</v>
+      </c>
+      <c r="BG267">
+        <v>0</v>
+      </c>
+      <c r="BH267">
+        <v>0</v>
+      </c>
+      <c r="BI267">
+        <v>0</v>
+      </c>
+      <c r="BJ267">
+        <v>0</v>
+      </c>
+      <c r="BK267">
+        <v>0</v>
+      </c>
+      <c r="BL267">
+        <v>0</v>
+      </c>
+      <c r="BM267">
+        <v>0</v>
+      </c>
+      <c r="BN267">
+        <v>0</v>
+      </c>
+      <c r="BO267">
+        <v>0</v>
+      </c>
+      <c r="BP267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:68">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>7940207</v>
+      </c>
+      <c r="C268" t="s">
+        <v>68</v>
+      </c>
+      <c r="D268" t="s">
+        <v>69</v>
+      </c>
+      <c r="E268" s="2">
+        <v>45851.5</v>
+      </c>
+      <c r="F268">
+        <v>1</v>
+      </c>
+      <c r="G268" t="s">
+        <v>96</v>
+      </c>
+      <c r="H268" t="s">
+        <v>84</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+      <c r="J268">
+        <v>0</v>
+      </c>
+      <c r="K268">
+        <v>0</v>
+      </c>
+      <c r="L268">
+        <v>0</v>
+      </c>
+      <c r="M268">
+        <v>0</v>
+      </c>
+      <c r="N268">
+        <v>0</v>
+      </c>
+      <c r="O268" t="s">
+        <v>100</v>
+      </c>
+      <c r="P268" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q268">
+        <v>0</v>
+      </c>
+      <c r="R268">
+        <v>0</v>
+      </c>
+      <c r="S268">
+        <v>0</v>
+      </c>
+      <c r="T268">
+        <v>0</v>
+      </c>
+      <c r="U268">
+        <v>0</v>
+      </c>
+      <c r="V268">
+        <v>0</v>
+      </c>
+      <c r="W268">
+        <v>0</v>
+      </c>
+      <c r="X268">
+        <v>0</v>
+      </c>
+      <c r="Y268">
+        <v>0</v>
+      </c>
+      <c r="Z268">
+        <v>0</v>
+      </c>
+      <c r="AA268">
+        <v>0</v>
+      </c>
+      <c r="AB268">
+        <v>0</v>
+      </c>
+      <c r="AC268">
+        <v>0</v>
+      </c>
+      <c r="AD268">
+        <v>0</v>
+      </c>
+      <c r="AE268">
+        <v>0</v>
+      </c>
+      <c r="AF268">
+        <v>0</v>
+      </c>
+      <c r="AG268">
+        <v>0</v>
+      </c>
+      <c r="AH268">
+        <v>0</v>
+      </c>
+      <c r="AI268">
+        <v>0</v>
+      </c>
+      <c r="AJ268">
+        <v>0</v>
+      </c>
+      <c r="AK268">
+        <v>0</v>
+      </c>
+      <c r="AL268">
+        <v>0</v>
+      </c>
+      <c r="AM268">
+        <v>0</v>
+      </c>
+      <c r="AN268">
+        <v>1</v>
+      </c>
+      <c r="AO268">
+        <v>0.63</v>
+      </c>
+      <c r="AP268">
+        <v>1</v>
+      </c>
+      <c r="AQ268">
+        <v>0.67</v>
+      </c>
+      <c r="AR268">
+        <v>1.88</v>
+      </c>
+      <c r="AS268">
+        <v>1.33</v>
+      </c>
+      <c r="AT268">
+        <v>3.21</v>
+      </c>
+      <c r="AU268">
+        <v>3</v>
+      </c>
+      <c r="AV268">
+        <v>2</v>
+      </c>
+      <c r="AW268">
+        <v>6</v>
+      </c>
+      <c r="AX268">
+        <v>2</v>
+      </c>
+      <c r="AY268">
+        <v>9</v>
+      </c>
+      <c r="AZ268">
+        <v>4</v>
+      </c>
+      <c r="BA268">
+        <v>5</v>
+      </c>
+      <c r="BB268">
+        <v>2</v>
+      </c>
+      <c r="BC268">
+        <v>7</v>
+      </c>
+      <c r="BD268">
+        <v>0</v>
+      </c>
+      <c r="BE268">
+        <v>0</v>
+      </c>
+      <c r="BF268">
+        <v>0</v>
+      </c>
+      <c r="BG268">
+        <v>0</v>
+      </c>
+      <c r="BH268">
+        <v>0</v>
+      </c>
+      <c r="BI268">
+        <v>0</v>
+      </c>
+      <c r="BJ268">
+        <v>0</v>
+      </c>
+      <c r="BK268">
+        <v>0</v>
+      </c>
+      <c r="BL268">
+        <v>0</v>
+      </c>
+      <c r="BM268">
+        <v>0</v>
+      </c>
+      <c r="BN268">
+        <v>0</v>
+      </c>
+      <c r="BO268">
+        <v>0</v>
+      </c>
+      <c r="BP268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:68">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>7820566</v>
+      </c>
+      <c r="C269" t="s">
+        <v>68</v>
+      </c>
+      <c r="D269" t="s">
+        <v>69</v>
+      </c>
+      <c r="E269" s="2">
+        <v>45851.59375</v>
+      </c>
+      <c r="F269">
+        <v>1</v>
+      </c>
+      <c r="G269" t="s">
+        <v>88</v>
+      </c>
+      <c r="H269" t="s">
+        <v>76</v>
+      </c>
+      <c r="I269">
+        <v>1</v>
+      </c>
+      <c r="J269">
+        <v>0</v>
+      </c>
+      <c r="K269">
+        <v>1</v>
+      </c>
+      <c r="L269">
+        <v>2</v>
+      </c>
+      <c r="M269">
+        <v>2</v>
+      </c>
+      <c r="N269">
+        <v>4</v>
+      </c>
+      <c r="O269" t="s">
+        <v>246</v>
+      </c>
+      <c r="P269" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q269">
+        <v>4.75</v>
+      </c>
+      <c r="R269">
+        <v>1.91</v>
+      </c>
+      <c r="S269">
+        <v>2.88</v>
+      </c>
+      <c r="T269">
+        <v>1.57</v>
+      </c>
+      <c r="U269">
+        <v>2.25</v>
+      </c>
+      <c r="V269">
+        <v>3.75</v>
+      </c>
+      <c r="W269">
+        <v>1.25</v>
+      </c>
+      <c r="X269">
+        <v>13</v>
+      </c>
+      <c r="Y269">
+        <v>1.04</v>
+      </c>
+      <c r="Z269">
+        <v>4</v>
+      </c>
+      <c r="AA269">
+        <v>3.1</v>
+      </c>
+      <c r="AB269">
+        <v>2.1</v>
+      </c>
+      <c r="AC269">
+        <v>1.11</v>
+      </c>
+      <c r="AD269">
+        <v>6.25</v>
+      </c>
+      <c r="AE269">
+        <v>1.53</v>
+      </c>
+      <c r="AF269">
+        <v>2.3</v>
+      </c>
+      <c r="AG269">
+        <v>2.7</v>
+      </c>
+      <c r="AH269">
+        <v>1.44</v>
+      </c>
+      <c r="AI269">
+        <v>2.25</v>
+      </c>
+      <c r="AJ269">
+        <v>1.57</v>
+      </c>
+      <c r="AK269">
+        <v>1.7</v>
+      </c>
+      <c r="AL269">
+        <v>1.36</v>
+      </c>
+      <c r="AM269">
+        <v>1.25</v>
+      </c>
+      <c r="AN269">
+        <v>1.13</v>
+      </c>
+      <c r="AO269">
+        <v>1.33</v>
+      </c>
+      <c r="AP269">
+        <v>1.1</v>
+      </c>
+      <c r="AQ269">
+        <v>1.27</v>
+      </c>
+      <c r="AR269">
+        <v>1.69</v>
+      </c>
+      <c r="AS269">
+        <v>1.2</v>
+      </c>
+      <c r="AT269">
+        <v>2.89</v>
+      </c>
+      <c r="AU269">
+        <v>6</v>
+      </c>
+      <c r="AV269">
+        <v>5</v>
+      </c>
+      <c r="AW269">
+        <v>4</v>
+      </c>
+      <c r="AX269">
+        <v>9</v>
+      </c>
+      <c r="AY269">
+        <v>10</v>
+      </c>
+      <c r="AZ269">
+        <v>14</v>
+      </c>
+      <c r="BA269">
+        <v>2</v>
+      </c>
+      <c r="BB269">
+        <v>2</v>
+      </c>
+      <c r="BC269">
+        <v>4</v>
+      </c>
+      <c r="BD269">
+        <v>2.9</v>
+      </c>
+      <c r="BE269">
+        <v>6.25</v>
+      </c>
+      <c r="BF269">
+        <v>1.58</v>
+      </c>
+      <c r="BG269">
+        <v>1.41</v>
+      </c>
+      <c r="BH269">
+        <v>2.6</v>
+      </c>
+      <c r="BI269">
+        <v>1.75</v>
+      </c>
+      <c r="BJ269">
+        <v>1.9</v>
+      </c>
+      <c r="BK269">
+        <v>2.3</v>
+      </c>
+      <c r="BL269">
+        <v>1.5</v>
+      </c>
+      <c r="BM269">
+        <v>3.2</v>
+      </c>
+      <c r="BN269">
+        <v>1.28</v>
+      </c>
+      <c r="BO269">
+        <v>3.5</v>
+      </c>
+      <c r="BP269">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="270" spans="1:68">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>7940198</v>
+      </c>
+      <c r="C270" t="s">
+        <v>68</v>
+      </c>
+      <c r="D270" t="s">
+        <v>69</v>
+      </c>
+      <c r="E270" s="2">
+        <v>45851.59375</v>
+      </c>
+      <c r="F270">
+        <v>1</v>
+      </c>
+      <c r="G270" t="s">
+        <v>88</v>
+      </c>
+      <c r="H270" t="s">
+        <v>76</v>
+      </c>
+      <c r="I270">
+        <v>1</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270">
+        <v>1</v>
+      </c>
+      <c r="L270">
+        <v>2</v>
+      </c>
+      <c r="M270">
+        <v>2</v>
+      </c>
+      <c r="N270">
+        <v>4</v>
+      </c>
+      <c r="O270" t="s">
+        <v>246</v>
+      </c>
+      <c r="P270" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q270">
+        <v>0</v>
+      </c>
+      <c r="R270">
+        <v>0</v>
+      </c>
+      <c r="S270">
+        <v>0</v>
+      </c>
+      <c r="T270">
+        <v>0</v>
+      </c>
+      <c r="U270">
+        <v>0</v>
+      </c>
+      <c r="V270">
+        <v>0</v>
+      </c>
+      <c r="W270">
+        <v>0</v>
+      </c>
+      <c r="X270">
+        <v>0</v>
+      </c>
+      <c r="Y270">
+        <v>0</v>
+      </c>
+      <c r="Z270">
+        <v>0</v>
+      </c>
+      <c r="AA270">
+        <v>0</v>
+      </c>
+      <c r="AB270">
+        <v>0</v>
+      </c>
+      <c r="AC270">
+        <v>0</v>
+      </c>
+      <c r="AD270">
+        <v>0</v>
+      </c>
+      <c r="AE270">
+        <v>0</v>
+      </c>
+      <c r="AF270">
+        <v>0</v>
+      </c>
+      <c r="AG270">
+        <v>0</v>
+      </c>
+      <c r="AH270">
+        <v>0</v>
+      </c>
+      <c r="AI270">
+        <v>0</v>
+      </c>
+      <c r="AJ270">
+        <v>0</v>
+      </c>
+      <c r="AK270">
+        <v>0</v>
+      </c>
+      <c r="AL270">
+        <v>0</v>
+      </c>
+      <c r="AM270">
+        <v>0</v>
+      </c>
+      <c r="AN270">
+        <v>1.13</v>
+      </c>
+      <c r="AO270">
+        <v>1.33</v>
+      </c>
+      <c r="AP270">
+        <v>1.1</v>
+      </c>
+      <c r="AQ270">
+        <v>1.27</v>
+      </c>
+      <c r="AR270">
+        <v>1.69</v>
+      </c>
+      <c r="AS270">
+        <v>1.2</v>
+      </c>
+      <c r="AT270">
+        <v>2.89</v>
+      </c>
+      <c r="AU270">
+        <v>5</v>
+      </c>
+      <c r="AV270">
+        <v>5</v>
+      </c>
+      <c r="AW270">
+        <v>5</v>
+      </c>
+      <c r="AX270">
+        <v>7</v>
+      </c>
+      <c r="AY270">
+        <v>10</v>
+      </c>
+      <c r="AZ270">
+        <v>12</v>
+      </c>
+      <c r="BA270">
+        <v>2</v>
+      </c>
+      <c r="BB270">
+        <v>2</v>
+      </c>
+      <c r="BC270">
+        <v>4</v>
+      </c>
+      <c r="BD270">
+        <v>0</v>
+      </c>
+      <c r="BE270">
+        <v>0</v>
+      </c>
+      <c r="BF270">
+        <v>0</v>
+      </c>
+      <c r="BG270">
+        <v>0</v>
+      </c>
+      <c r="BH270">
+        <v>0</v>
+      </c>
+      <c r="BI270">
+        <v>0</v>
+      </c>
+      <c r="BJ270">
+        <v>0</v>
+      </c>
+      <c r="BK270">
+        <v>0</v>
+      </c>
+      <c r="BL270">
+        <v>0</v>
+      </c>
+      <c r="BM270">
+        <v>0</v>
+      </c>
+      <c r="BN270">
+        <v>0</v>
+      </c>
+      <c r="BO270">
+        <v>0</v>
+      </c>
+      <c r="BP270">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="326">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -757,6 +757,9 @@
     <t>['33', '55']</t>
   </si>
   <si>
+    <t>['4', '90+5']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -986,6 +989,9 @@
   </si>
   <si>
     <t>['46', '83']</t>
+  </si>
+  <si>
+    <t>['71', '88']</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP270"/>
+  <dimension ref="A1:BP276"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1603,7 +1609,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -2015,7 +2021,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2427,7 +2433,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2633,7 +2639,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -3251,7 +3257,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -4774,7 +4780,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4980,7 +4986,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ18">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5105,7 +5111,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5517,7 +5523,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q21">
         <v>2.63</v>
@@ -5801,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>1.45</v>
@@ -5929,7 +5935,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6135,7 +6141,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6547,7 +6553,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6628,7 +6634,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ26">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6959,7 +6965,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7655,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>1.44</v>
@@ -9431,7 +9437,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -10127,7 +10133,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
         <v>1.67</v>
@@ -10255,7 +10261,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10461,7 +10467,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10539,7 +10545,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ45">
         <v>1.33</v>
@@ -10667,7 +10673,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10873,7 +10879,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -10954,7 +10960,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ47">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AR47">
         <v>1.66</v>
@@ -11079,7 +11085,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11366,7 +11372,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR49">
         <v>1.6</v>
@@ -11903,7 +11909,7 @@
         <v>131</v>
       </c>
       <c r="P52" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11981,7 +11987,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AQ52">
         <v>0.7</v>
@@ -12315,7 +12321,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12808,7 +12814,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AR56">
         <v>1.44</v>
@@ -13139,7 +13145,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13757,7 +13763,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14993,7 +14999,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -15277,7 +15283,7 @@
         <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
         <v>1.6</v>
@@ -16023,7 +16029,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -16513,7 +16519,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ74">
         <v>0.75</v>
@@ -16928,7 +16934,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ76">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AR76">
         <v>1.36</v>
@@ -17053,7 +17059,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q77">
         <v>5</v>
@@ -17259,7 +17265,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q78">
         <v>2.5</v>
@@ -17465,7 +17471,7 @@
         <v>148</v>
       </c>
       <c r="P79" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q79">
         <v>3.2</v>
@@ -17543,7 +17549,7 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79">
         <v>1.44</v>
@@ -17877,7 +17883,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -18083,7 +18089,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18701,7 +18707,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -19194,7 +19200,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ87">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AR87">
         <v>1.31</v>
@@ -19525,7 +19531,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19731,7 +19737,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20349,7 +20355,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20967,7 +20973,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -21173,7 +21179,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21791,7 +21797,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21869,7 +21875,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ100">
         <v>0.5</v>
@@ -22284,7 +22290,7 @@
         <v>2</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR102">
         <v>1.05</v>
@@ -22487,7 +22493,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ103">
         <v>1.33</v>
@@ -23439,7 +23445,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23645,7 +23651,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23851,7 +23857,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -24263,7 +24269,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24341,7 +24347,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AQ112">
         <v>0.89</v>
@@ -24547,7 +24553,7 @@
         <v>0.25</v>
       </c>
       <c r="AP113">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ113">
         <v>0.83</v>
@@ -24675,7 +24681,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24881,7 +24887,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -25087,7 +25093,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25293,7 +25299,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25371,10 +25377,10 @@
         <v>0</v>
       </c>
       <c r="AP117">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ117">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR117">
         <v>1.81</v>
@@ -25992,7 +25998,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ120">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AR120">
         <v>1.33</v>
@@ -26117,7 +26123,7 @@
         <v>175</v>
       </c>
       <c r="P121" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q121">
         <v>4.33</v>
@@ -26323,7 +26329,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26404,7 +26410,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ122">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AR122">
         <v>2.07</v>
@@ -26529,7 +26535,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -27559,7 +27565,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -28383,7 +28389,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -28667,7 +28673,7 @@
         <v>0</v>
       </c>
       <c r="AP133">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AQ133">
         <v>0.14</v>
@@ -29001,7 +29007,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -29079,7 +29085,7 @@
         <v>0</v>
       </c>
       <c r="AP135">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ135">
         <v>0.88</v>
@@ -29700,7 +29706,7 @@
         <v>2</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR138">
         <v>1.9</v>
@@ -31267,7 +31273,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31473,7 +31479,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31679,7 +31685,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31885,7 +31891,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -31963,7 +31969,7 @@
         <v>0.25</v>
       </c>
       <c r="AP149">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ149">
         <v>0.88</v>
@@ -32091,7 +32097,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32709,7 +32715,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32993,7 +32999,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AQ154">
         <v>1.44</v>
@@ -33121,7 +33127,7 @@
         <v>192</v>
       </c>
       <c r="P155" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33533,7 +33539,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -34232,7 +34238,7 @@
         <v>2</v>
       </c>
       <c r="AQ160">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AR160">
         <v>1.59</v>
@@ -34357,7 +34363,7 @@
         <v>174</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34769,7 +34775,7 @@
         <v>196</v>
       </c>
       <c r="P163" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q163">
         <v>2.1</v>
@@ -34975,7 +34981,7 @@
         <v>197</v>
       </c>
       <c r="P164" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q164">
         <v>3.75</v>
@@ -35468,7 +35474,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ166">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AR166">
         <v>1.8</v>
@@ -35799,7 +35805,7 @@
         <v>100</v>
       </c>
       <c r="P168" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q168">
         <v>4.33</v>
@@ -36005,7 +36011,7 @@
         <v>199</v>
       </c>
       <c r="P169" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q169">
         <v>2.75</v>
@@ -36623,7 +36629,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q172">
         <v>2.38</v>
@@ -37035,7 +37041,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q174">
         <v>3.25</v>
@@ -37937,7 +37943,7 @@
         <v>1.67</v>
       </c>
       <c r="AP178">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ178">
         <v>1.22</v>
@@ -38271,7 +38277,7 @@
         <v>209</v>
       </c>
       <c r="P180" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38349,7 +38355,7 @@
         <v>0.17</v>
       </c>
       <c r="AP180">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ180">
         <v>0.83</v>
@@ -38477,7 +38483,7 @@
         <v>100</v>
       </c>
       <c r="P181" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38558,7 +38564,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ181">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR181">
         <v>1.25</v>
@@ -38683,7 +38689,7 @@
         <v>108</v>
       </c>
       <c r="P182" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39507,7 +39513,7 @@
         <v>203</v>
       </c>
       <c r="P186" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39588,7 +39594,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ186">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AR186">
         <v>1.6</v>
@@ -39713,7 +39719,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q187">
         <v>4</v>
@@ -40206,7 +40212,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ189">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AR189">
         <v>1.76</v>
@@ -40331,7 +40337,7 @@
         <v>151</v>
       </c>
       <c r="P190" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q190">
         <v>2.2</v>
@@ -40537,7 +40543,7 @@
         <v>100</v>
       </c>
       <c r="P191" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q191">
         <v>4</v>
@@ -40743,7 +40749,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41155,7 +41161,7 @@
         <v>100</v>
       </c>
       <c r="P194" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q194">
         <v>2.4</v>
@@ -41773,7 +41779,7 @@
         <v>100</v>
       </c>
       <c r="P197" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q197">
         <v>4.75</v>
@@ -41979,7 +41985,7 @@
         <v>100</v>
       </c>
       <c r="P198" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q198">
         <v>3.1</v>
@@ -42472,7 +42478,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ200">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR200">
         <v>1.77</v>
@@ -44323,7 +44329,7 @@
         <v>1.17</v>
       </c>
       <c r="AP209">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ209">
         <v>1.45</v>
@@ -44529,7 +44535,7 @@
         <v>0.67</v>
       </c>
       <c r="AP210">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AQ210">
         <v>0.88</v>
@@ -44863,7 +44869,7 @@
         <v>100</v>
       </c>
       <c r="P212" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45069,7 +45075,7 @@
         <v>102</v>
       </c>
       <c r="P213" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45356,7 +45362,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ214">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AR214">
         <v>2.02</v>
@@ -45562,7 +45568,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ215">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AR215">
         <v>1.78</v>
@@ -46511,7 +46517,7 @@
         <v>226</v>
       </c>
       <c r="P220" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47129,7 +47135,7 @@
         <v>188</v>
       </c>
       <c r="P223" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47825,7 +47831,7 @@
         <v>1.5</v>
       </c>
       <c r="AP226">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ226">
         <v>1.27</v>
@@ -48159,7 +48165,7 @@
         <v>232</v>
       </c>
       <c r="P228" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q228">
         <v>4.33</v>
@@ -48237,7 +48243,7 @@
         <v>1.38</v>
       </c>
       <c r="AP228">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AQ228">
         <v>1.22</v>
@@ -48446,7 +48452,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ229">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR229">
         <v>1.79</v>
@@ -48649,7 +48655,7 @@
         <v>0.88</v>
       </c>
       <c r="AP230">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ230">
         <v>0.7</v>
@@ -48777,7 +48783,7 @@
         <v>156</v>
       </c>
       <c r="P231" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q231">
         <v>3.75</v>
@@ -49395,7 +49401,7 @@
         <v>236</v>
       </c>
       <c r="P234" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q234">
         <v>2.75</v>
@@ -49807,7 +49813,7 @@
         <v>100</v>
       </c>
       <c r="P236" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q236">
         <v>2.25</v>
@@ -50091,7 +50097,7 @@
         <v>1</v>
       </c>
       <c r="AP237">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ237">
         <v>0.89</v>
@@ -50425,7 +50431,7 @@
         <v>100</v>
       </c>
       <c r="P239" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q239">
         <v>3.6</v>
@@ -50712,7 +50718,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ240">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AR240">
         <v>1.43</v>
@@ -51043,7 +51049,7 @@
         <v>239</v>
       </c>
       <c r="P242" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q242">
         <v>2.95</v>
@@ -51455,7 +51461,7 @@
         <v>100</v>
       </c>
       <c r="P244" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q244">
         <v>2.4</v>
@@ -51739,7 +51745,7 @@
         <v>1.25</v>
       </c>
       <c r="AP245">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ245">
         <v>1.24</v>
@@ -51948,7 +51954,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ246">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AR246">
         <v>1.46</v>
@@ -52073,7 +52079,7 @@
         <v>241</v>
       </c>
       <c r="P247" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q247">
         <v>2.2</v>
@@ -52151,7 +52157,7 @@
         <v>1.13</v>
       </c>
       <c r="AP247">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AQ247">
         <v>1.26</v>
@@ -52279,7 +52285,7 @@
         <v>242</v>
       </c>
       <c r="P248" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q248">
         <v>2.63</v>
@@ -52897,7 +52903,7 @@
         <v>179</v>
       </c>
       <c r="P251" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q251">
         <v>2.6</v>
@@ -52975,7 +52981,7 @@
         <v>1.76</v>
       </c>
       <c r="AP251">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AQ251">
         <v>1.76</v>
@@ -53103,7 +53109,7 @@
         <v>100</v>
       </c>
       <c r="P252" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q252">
         <v>2.88</v>
@@ -53181,7 +53187,7 @@
         <v>1.88</v>
       </c>
       <c r="AP252">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ252">
         <v>1.81</v>
@@ -53927,7 +53933,7 @@
         <v>100</v>
       </c>
       <c r="P256" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q256">
         <v>3.2</v>
@@ -54339,7 +54345,7 @@
         <v>245</v>
       </c>
       <c r="P258" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q258">
         <v>2.88</v>
@@ -54751,7 +54757,7 @@
         <v>100</v>
       </c>
       <c r="P260" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q260">
         <v>2.75</v>
@@ -55163,7 +55169,7 @@
         <v>100</v>
       </c>
       <c r="P262" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q262">
         <v>2</v>
@@ -55369,7 +55375,7 @@
         <v>100</v>
       </c>
       <c r="P263" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -55781,7 +55787,7 @@
         <v>245</v>
       </c>
       <c r="P265" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -56193,7 +56199,7 @@
         <v>100</v>
       </c>
       <c r="P267" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -56605,7 +56611,7 @@
         <v>246</v>
       </c>
       <c r="P269" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q269">
         <v>4.75</v>
@@ -56811,7 +56817,7 @@
         <v>246</v>
       </c>
       <c r="P270" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -56968,6 +56974,1242 @@
       </c>
       <c r="BP270">
         <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:68">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>7820559</v>
+      </c>
+      <c r="C271" t="s">
+        <v>68</v>
+      </c>
+      <c r="D271" t="s">
+        <v>69</v>
+      </c>
+      <c r="E271" s="2">
+        <v>45851.6875</v>
+      </c>
+      <c r="F271">
+        <v>1</v>
+      </c>
+      <c r="G271" t="s">
+        <v>90</v>
+      </c>
+      <c r="H271" t="s">
+        <v>72</v>
+      </c>
+      <c r="I271">
+        <v>1</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271">
+        <v>1</v>
+      </c>
+      <c r="L271">
+        <v>1</v>
+      </c>
+      <c r="M271">
+        <v>2</v>
+      </c>
+      <c r="N271">
+        <v>3</v>
+      </c>
+      <c r="O271" t="s">
+        <v>186</v>
+      </c>
+      <c r="P271" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q271">
+        <v>3.2</v>
+      </c>
+      <c r="R271">
+        <v>1.95</v>
+      </c>
+      <c r="S271">
+        <v>4</v>
+      </c>
+      <c r="T271">
+        <v>1.57</v>
+      </c>
+      <c r="U271">
+        <v>2.25</v>
+      </c>
+      <c r="V271">
+        <v>3.75</v>
+      </c>
+      <c r="W271">
+        <v>1.25</v>
+      </c>
+      <c r="X271">
+        <v>11</v>
+      </c>
+      <c r="Y271">
+        <v>1.05</v>
+      </c>
+      <c r="Z271">
+        <v>2.4</v>
+      </c>
+      <c r="AA271">
+        <v>3</v>
+      </c>
+      <c r="AB271">
+        <v>3.25</v>
+      </c>
+      <c r="AC271">
+        <v>1.11</v>
+      </c>
+      <c r="AD271">
+        <v>6.25</v>
+      </c>
+      <c r="AE271">
+        <v>1.5</v>
+      </c>
+      <c r="AF271">
+        <v>2.38</v>
+      </c>
+      <c r="AG271">
+        <v>2.6</v>
+      </c>
+      <c r="AH271">
+        <v>1.48</v>
+      </c>
+      <c r="AI271">
+        <v>2.1</v>
+      </c>
+      <c r="AJ271">
+        <v>1.67</v>
+      </c>
+      <c r="AK271">
+        <v>1.33</v>
+      </c>
+      <c r="AL271">
+        <v>1.37</v>
+      </c>
+      <c r="AM271">
+        <v>1.55</v>
+      </c>
+      <c r="AN271">
+        <v>1.88</v>
+      </c>
+      <c r="AO271">
+        <v>1</v>
+      </c>
+      <c r="AP271">
+        <v>1.5</v>
+      </c>
+      <c r="AQ271">
+        <v>1.4</v>
+      </c>
+      <c r="AR271">
+        <v>1.58</v>
+      </c>
+      <c r="AS271">
+        <v>1.32</v>
+      </c>
+      <c r="AT271">
+        <v>2.9</v>
+      </c>
+      <c r="AU271">
+        <v>7</v>
+      </c>
+      <c r="AV271">
+        <v>8</v>
+      </c>
+      <c r="AW271">
+        <v>9</v>
+      </c>
+      <c r="AX271">
+        <v>6</v>
+      </c>
+      <c r="AY271">
+        <v>16</v>
+      </c>
+      <c r="AZ271">
+        <v>14</v>
+      </c>
+      <c r="BA271">
+        <v>5</v>
+      </c>
+      <c r="BB271">
+        <v>4</v>
+      </c>
+      <c r="BC271">
+        <v>9</v>
+      </c>
+      <c r="BD271">
+        <v>1.9</v>
+      </c>
+      <c r="BE271">
+        <v>6</v>
+      </c>
+      <c r="BF271">
+        <v>2.25</v>
+      </c>
+      <c r="BG271">
+        <v>1.39</v>
+      </c>
+      <c r="BH271">
+        <v>2.65</v>
+      </c>
+      <c r="BI271">
+        <v>1.72</v>
+      </c>
+      <c r="BJ271">
+        <v>1.93</v>
+      </c>
+      <c r="BK271">
+        <v>2.25</v>
+      </c>
+      <c r="BL271">
+        <v>1.52</v>
+      </c>
+      <c r="BM271">
+        <v>3.1</v>
+      </c>
+      <c r="BN271">
+        <v>1.29</v>
+      </c>
+      <c r="BO271">
+        <v>3.7</v>
+      </c>
+      <c r="BP271">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="272" spans="1:68">
+      <c r="A272" s="1">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>7940206</v>
+      </c>
+      <c r="C272" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" t="s">
+        <v>69</v>
+      </c>
+      <c r="E272" s="2">
+        <v>45851.6875</v>
+      </c>
+      <c r="F272">
+        <v>1</v>
+      </c>
+      <c r="G272" t="s">
+        <v>90</v>
+      </c>
+      <c r="H272" t="s">
+        <v>72</v>
+      </c>
+      <c r="I272">
+        <v>1</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>1</v>
+      </c>
+      <c r="L272">
+        <v>1</v>
+      </c>
+      <c r="M272">
+        <v>2</v>
+      </c>
+      <c r="N272">
+        <v>3</v>
+      </c>
+      <c r="O272" t="s">
+        <v>186</v>
+      </c>
+      <c r="P272" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q272">
+        <v>2.75</v>
+      </c>
+      <c r="R272">
+        <v>1.95</v>
+      </c>
+      <c r="S272">
+        <v>5</v>
+      </c>
+      <c r="T272">
+        <v>1.57</v>
+      </c>
+      <c r="U272">
+        <v>2.25</v>
+      </c>
+      <c r="V272">
+        <v>3.75</v>
+      </c>
+      <c r="W272">
+        <v>1.25</v>
+      </c>
+      <c r="X272">
+        <v>11</v>
+      </c>
+      <c r="Y272">
+        <v>1.05</v>
+      </c>
+      <c r="Z272">
+        <v>2.2</v>
+      </c>
+      <c r="AA272">
+        <v>2.9</v>
+      </c>
+      <c r="AB272">
+        <v>3.75</v>
+      </c>
+      <c r="AC272">
+        <v>1.12</v>
+      </c>
+      <c r="AD272">
+        <v>6.7</v>
+      </c>
+      <c r="AE272">
+        <v>1.54</v>
+      </c>
+      <c r="AF272">
+        <v>2.58</v>
+      </c>
+      <c r="AG272">
+        <v>2.7</v>
+      </c>
+      <c r="AH272">
+        <v>1.44</v>
+      </c>
+      <c r="AI272">
+        <v>2.2</v>
+      </c>
+      <c r="AJ272">
+        <v>1.62</v>
+      </c>
+      <c r="AK272">
+        <v>1.3</v>
+      </c>
+      <c r="AL272">
+        <v>1.39</v>
+      </c>
+      <c r="AM272">
+        <v>1.58</v>
+      </c>
+      <c r="AN272">
+        <v>1.88</v>
+      </c>
+      <c r="AO272">
+        <v>1</v>
+      </c>
+      <c r="AP272">
+        <v>1.5</v>
+      </c>
+      <c r="AQ272">
+        <v>1.4</v>
+      </c>
+      <c r="AR272">
+        <v>1.58</v>
+      </c>
+      <c r="AS272">
+        <v>1.32</v>
+      </c>
+      <c r="AT272">
+        <v>2.9</v>
+      </c>
+      <c r="AU272">
+        <v>7</v>
+      </c>
+      <c r="AV272">
+        <v>9</v>
+      </c>
+      <c r="AW272">
+        <v>6</v>
+      </c>
+      <c r="AX272">
+        <v>3</v>
+      </c>
+      <c r="AY272">
+        <v>13</v>
+      </c>
+      <c r="AZ272">
+        <v>12</v>
+      </c>
+      <c r="BA272">
+        <v>5</v>
+      </c>
+      <c r="BB272">
+        <v>4</v>
+      </c>
+      <c r="BC272">
+        <v>9</v>
+      </c>
+      <c r="BD272">
+        <v>1.9</v>
+      </c>
+      <c r="BE272">
+        <v>6</v>
+      </c>
+      <c r="BF272">
+        <v>2.2</v>
+      </c>
+      <c r="BG272">
+        <v>1.39</v>
+      </c>
+      <c r="BH272">
+        <v>2.65</v>
+      </c>
+      <c r="BI272">
+        <v>1.72</v>
+      </c>
+      <c r="BJ272">
+        <v>1.93</v>
+      </c>
+      <c r="BK272">
+        <v>2.25</v>
+      </c>
+      <c r="BL272">
+        <v>1.52</v>
+      </c>
+      <c r="BM272">
+        <v>3.1</v>
+      </c>
+      <c r="BN272">
+        <v>1.29</v>
+      </c>
+      <c r="BO272">
+        <v>3.25</v>
+      </c>
+      <c r="BP272">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="273" spans="1:68">
+      <c r="A273" s="1">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>7820569</v>
+      </c>
+      <c r="C273" t="s">
+        <v>68</v>
+      </c>
+      <c r="D273" t="s">
+        <v>69</v>
+      </c>
+      <c r="E273" s="2">
+        <v>45851.6875</v>
+      </c>
+      <c r="F273">
+        <v>1</v>
+      </c>
+      <c r="G273" t="s">
+        <v>99</v>
+      </c>
+      <c r="H273" t="s">
+        <v>78</v>
+      </c>
+      <c r="I273">
+        <v>1</v>
+      </c>
+      <c r="J273">
+        <v>0</v>
+      </c>
+      <c r="K273">
+        <v>1</v>
+      </c>
+      <c r="L273">
+        <v>2</v>
+      </c>
+      <c r="M273">
+        <v>1</v>
+      </c>
+      <c r="N273">
+        <v>3</v>
+      </c>
+      <c r="O273" t="s">
+        <v>247</v>
+      </c>
+      <c r="P273" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q273">
+        <v>2.4</v>
+      </c>
+      <c r="R273">
+        <v>2</v>
+      </c>
+      <c r="S273">
+        <v>6</v>
+      </c>
+      <c r="T273">
+        <v>1.53</v>
+      </c>
+      <c r="U273">
+        <v>2.38</v>
+      </c>
+      <c r="V273">
+        <v>3.5</v>
+      </c>
+      <c r="W273">
+        <v>1.29</v>
+      </c>
+      <c r="X273">
+        <v>11</v>
+      </c>
+      <c r="Y273">
+        <v>1.05</v>
+      </c>
+      <c r="Z273">
+        <v>1.8</v>
+      </c>
+      <c r="AA273">
+        <v>3.5</v>
+      </c>
+      <c r="AB273">
+        <v>4.75</v>
+      </c>
+      <c r="AC273">
+        <v>1.09</v>
+      </c>
+      <c r="AD273">
+        <v>7</v>
+      </c>
+      <c r="AE273">
+        <v>1.48</v>
+      </c>
+      <c r="AF273">
+        <v>2.6</v>
+      </c>
+      <c r="AG273">
+        <v>2.5</v>
+      </c>
+      <c r="AH273">
+        <v>1.5</v>
+      </c>
+      <c r="AI273">
+        <v>2.25</v>
+      </c>
+      <c r="AJ273">
+        <v>1.57</v>
+      </c>
+      <c r="AK273">
+        <v>1.17</v>
+      </c>
+      <c r="AL273">
+        <v>1.31</v>
+      </c>
+      <c r="AM273">
+        <v>1.98</v>
+      </c>
+      <c r="AN273">
+        <v>1.5</v>
+      </c>
+      <c r="AO273">
+        <v>0.29</v>
+      </c>
+      <c r="AP273">
+        <v>1.8</v>
+      </c>
+      <c r="AQ273">
+        <v>0.22</v>
+      </c>
+      <c r="AR273">
+        <v>1.67</v>
+      </c>
+      <c r="AS273">
+        <v>1.23</v>
+      </c>
+      <c r="AT273">
+        <v>2.9</v>
+      </c>
+      <c r="AU273">
+        <v>5</v>
+      </c>
+      <c r="AV273">
+        <v>7</v>
+      </c>
+      <c r="AW273">
+        <v>5</v>
+      </c>
+      <c r="AX273">
+        <v>4</v>
+      </c>
+      <c r="AY273">
+        <v>10</v>
+      </c>
+      <c r="AZ273">
+        <v>11</v>
+      </c>
+      <c r="BA273">
+        <v>3</v>
+      </c>
+      <c r="BB273">
+        <v>7</v>
+      </c>
+      <c r="BC273">
+        <v>10</v>
+      </c>
+      <c r="BD273">
+        <v>1.49</v>
+      </c>
+      <c r="BE273">
+        <v>6.25</v>
+      </c>
+      <c r="BF273">
+        <v>3.3</v>
+      </c>
+      <c r="BG273">
+        <v>1.42</v>
+      </c>
+      <c r="BH273">
+        <v>2.55</v>
+      </c>
+      <c r="BI273">
+        <v>1.78</v>
+      </c>
+      <c r="BJ273">
+        <v>1.87</v>
+      </c>
+      <c r="BK273">
+        <v>2.35</v>
+      </c>
+      <c r="BL273">
+        <v>1.49</v>
+      </c>
+      <c r="BM273">
+        <v>3.3</v>
+      </c>
+      <c r="BN273">
+        <v>1.27</v>
+      </c>
+      <c r="BO273">
+        <v>3.45</v>
+      </c>
+      <c r="BP273">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="274" spans="1:68">
+      <c r="A274" s="1">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>7940196</v>
+      </c>
+      <c r="C274" t="s">
+        <v>68</v>
+      </c>
+      <c r="D274" t="s">
+        <v>69</v>
+      </c>
+      <c r="E274" s="2">
+        <v>45851.6875</v>
+      </c>
+      <c r="F274">
+        <v>1</v>
+      </c>
+      <c r="G274" t="s">
+        <v>99</v>
+      </c>
+      <c r="H274" t="s">
+        <v>78</v>
+      </c>
+      <c r="I274">
+        <v>1</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274">
+        <v>1</v>
+      </c>
+      <c r="L274">
+        <v>2</v>
+      </c>
+      <c r="M274">
+        <v>1</v>
+      </c>
+      <c r="N274">
+        <v>3</v>
+      </c>
+      <c r="O274" t="s">
+        <v>247</v>
+      </c>
+      <c r="P274" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q274">
+        <v>2.63</v>
+      </c>
+      <c r="R274">
+        <v>1.95</v>
+      </c>
+      <c r="S274">
+        <v>5.5</v>
+      </c>
+      <c r="T274">
+        <v>1.53</v>
+      </c>
+      <c r="U274">
+        <v>2.38</v>
+      </c>
+      <c r="V274">
+        <v>3.75</v>
+      </c>
+      <c r="W274">
+        <v>1.25</v>
+      </c>
+      <c r="X274">
+        <v>11</v>
+      </c>
+      <c r="Y274">
+        <v>1.05</v>
+      </c>
+      <c r="Z274">
+        <v>1.91</v>
+      </c>
+      <c r="AA274">
+        <v>3.25</v>
+      </c>
+      <c r="AB274">
+        <v>4.5</v>
+      </c>
+      <c r="AC274">
+        <v>1.12</v>
+      </c>
+      <c r="AD274">
+        <v>6.76</v>
+      </c>
+      <c r="AE274">
+        <v>1.54</v>
+      </c>
+      <c r="AF274">
+        <v>2.52</v>
+      </c>
+      <c r="AG274">
+        <v>2.6</v>
+      </c>
+      <c r="AH274">
+        <v>1.48</v>
+      </c>
+      <c r="AI274">
+        <v>2.25</v>
+      </c>
+      <c r="AJ274">
+        <v>1.57</v>
+      </c>
+      <c r="AK274">
+        <v>1.2</v>
+      </c>
+      <c r="AL274">
+        <v>1.34</v>
+      </c>
+      <c r="AM274">
+        <v>1.85</v>
+      </c>
+      <c r="AN274">
+        <v>1.5</v>
+      </c>
+      <c r="AO274">
+        <v>0.29</v>
+      </c>
+      <c r="AP274">
+        <v>1.8</v>
+      </c>
+      <c r="AQ274">
+        <v>0.22</v>
+      </c>
+      <c r="AR274">
+        <v>1.67</v>
+      </c>
+      <c r="AS274">
+        <v>1.23</v>
+      </c>
+      <c r="AT274">
+        <v>2.9</v>
+      </c>
+      <c r="AU274">
+        <v>4</v>
+      </c>
+      <c r="AV274">
+        <v>5</v>
+      </c>
+      <c r="AW274">
+        <v>5</v>
+      </c>
+      <c r="AX274">
+        <v>6</v>
+      </c>
+      <c r="AY274">
+        <v>9</v>
+      </c>
+      <c r="AZ274">
+        <v>11</v>
+      </c>
+      <c r="BA274">
+        <v>4</v>
+      </c>
+      <c r="BB274">
+        <v>7</v>
+      </c>
+      <c r="BC274">
+        <v>11</v>
+      </c>
+      <c r="BD274">
+        <v>1.5</v>
+      </c>
+      <c r="BE274">
+        <v>6.75</v>
+      </c>
+      <c r="BF274">
+        <v>3.2</v>
+      </c>
+      <c r="BG274">
+        <v>1.3</v>
+      </c>
+      <c r="BH274">
+        <v>3.1</v>
+      </c>
+      <c r="BI274">
+        <v>1.55</v>
+      </c>
+      <c r="BJ274">
+        <v>2.2</v>
+      </c>
+      <c r="BK274">
+        <v>1.98</v>
+      </c>
+      <c r="BL274">
+        <v>1.68</v>
+      </c>
+      <c r="BM274">
+        <v>2.65</v>
+      </c>
+      <c r="BN274">
+        <v>1.39</v>
+      </c>
+      <c r="BO274">
+        <v>3.75</v>
+      </c>
+      <c r="BP274">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="275" spans="1:68">
+      <c r="A275" s="1">
+        <v>274</v>
+      </c>
+      <c r="B275">
+        <v>7820555</v>
+      </c>
+      <c r="C275" t="s">
+        <v>68</v>
+      </c>
+      <c r="D275" t="s">
+        <v>69</v>
+      </c>
+      <c r="E275" s="2">
+        <v>45851.78125</v>
+      </c>
+      <c r="F275">
+        <v>1</v>
+      </c>
+      <c r="G275" t="s">
+        <v>98</v>
+      </c>
+      <c r="H275" t="s">
+        <v>83</v>
+      </c>
+      <c r="I275">
+        <v>0</v>
+      </c>
+      <c r="J275">
+        <v>0</v>
+      </c>
+      <c r="K275">
+        <v>0</v>
+      </c>
+      <c r="L275">
+        <v>0</v>
+      </c>
+      <c r="M275">
+        <v>0</v>
+      </c>
+      <c r="N275">
+        <v>0</v>
+      </c>
+      <c r="O275" t="s">
+        <v>100</v>
+      </c>
+      <c r="P275" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q275">
+        <v>3</v>
+      </c>
+      <c r="R275">
+        <v>1.91</v>
+      </c>
+      <c r="S275">
+        <v>4.5</v>
+      </c>
+      <c r="T275">
+        <v>1.62</v>
+      </c>
+      <c r="U275">
+        <v>2.2</v>
+      </c>
+      <c r="V275">
+        <v>4</v>
+      </c>
+      <c r="W275">
+        <v>1.22</v>
+      </c>
+      <c r="X275">
+        <v>13</v>
+      </c>
+      <c r="Y275">
+        <v>1.04</v>
+      </c>
+      <c r="Z275">
+        <v>2.15</v>
+      </c>
+      <c r="AA275">
+        <v>3.2</v>
+      </c>
+      <c r="AB275">
+        <v>3.6</v>
+      </c>
+      <c r="AC275">
+        <v>1.12</v>
+      </c>
+      <c r="AD275">
+        <v>5.75</v>
+      </c>
+      <c r="AE275">
+        <v>1.58</v>
+      </c>
+      <c r="AF275">
+        <v>2.2</v>
+      </c>
+      <c r="AG275">
+        <v>2.88</v>
+      </c>
+      <c r="AH275">
+        <v>1.4</v>
+      </c>
+      <c r="AI275">
+        <v>2.38</v>
+      </c>
+      <c r="AJ275">
+        <v>1.53</v>
+      </c>
+      <c r="AK275">
+        <v>1.26</v>
+      </c>
+      <c r="AL275">
+        <v>1.38</v>
+      </c>
+      <c r="AM275">
+        <v>1.65</v>
+      </c>
+      <c r="AN275">
+        <v>2.18</v>
+      </c>
+      <c r="AO275">
+        <v>1.38</v>
+      </c>
+      <c r="AP275">
+        <v>2</v>
+      </c>
+      <c r="AQ275">
+        <v>1.3</v>
+      </c>
+      <c r="AR275">
+        <v>1.73</v>
+      </c>
+      <c r="AS275">
+        <v>1.51</v>
+      </c>
+      <c r="AT275">
+        <v>3.24</v>
+      </c>
+      <c r="AU275">
+        <v>5</v>
+      </c>
+      <c r="AV275">
+        <v>5</v>
+      </c>
+      <c r="AW275">
+        <v>11</v>
+      </c>
+      <c r="AX275">
+        <v>1</v>
+      </c>
+      <c r="AY275">
+        <v>16</v>
+      </c>
+      <c r="AZ275">
+        <v>6</v>
+      </c>
+      <c r="BA275">
+        <v>4</v>
+      </c>
+      <c r="BB275">
+        <v>1</v>
+      </c>
+      <c r="BC275">
+        <v>5</v>
+      </c>
+      <c r="BD275">
+        <v>1.55</v>
+      </c>
+      <c r="BE275">
+        <v>6.25</v>
+      </c>
+      <c r="BF275">
+        <v>3</v>
+      </c>
+      <c r="BG275">
+        <v>1.41</v>
+      </c>
+      <c r="BH275">
+        <v>2.6</v>
+      </c>
+      <c r="BI275">
+        <v>1.75</v>
+      </c>
+      <c r="BJ275">
+        <v>1.9</v>
+      </c>
+      <c r="BK275">
+        <v>2.3</v>
+      </c>
+      <c r="BL275">
+        <v>1.5</v>
+      </c>
+      <c r="BM275">
+        <v>3.25</v>
+      </c>
+      <c r="BN275">
+        <v>1.28</v>
+      </c>
+      <c r="BO275">
+        <v>3.5</v>
+      </c>
+      <c r="BP275">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="276" spans="1:68">
+      <c r="A276" s="1">
+        <v>275</v>
+      </c>
+      <c r="B276">
+        <v>7940209</v>
+      </c>
+      <c r="C276" t="s">
+        <v>68</v>
+      </c>
+      <c r="D276" t="s">
+        <v>69</v>
+      </c>
+      <c r="E276" s="2">
+        <v>45851.78125</v>
+      </c>
+      <c r="F276">
+        <v>1</v>
+      </c>
+      <c r="G276" t="s">
+        <v>98</v>
+      </c>
+      <c r="H276" t="s">
+        <v>83</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>0</v>
+      </c>
+      <c r="L276">
+        <v>0</v>
+      </c>
+      <c r="M276">
+        <v>0</v>
+      </c>
+      <c r="N276">
+        <v>0</v>
+      </c>
+      <c r="O276" t="s">
+        <v>100</v>
+      </c>
+      <c r="P276" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q276">
+        <v>3.25</v>
+      </c>
+      <c r="R276">
+        <v>1.8</v>
+      </c>
+      <c r="S276">
+        <v>4.5</v>
+      </c>
+      <c r="T276">
+        <v>1.67</v>
+      </c>
+      <c r="U276">
+        <v>2.1</v>
+      </c>
+      <c r="V276">
+        <v>4.33</v>
+      </c>
+      <c r="W276">
+        <v>1.2</v>
+      </c>
+      <c r="X276">
+        <v>15</v>
+      </c>
+      <c r="Y276">
+        <v>1.03</v>
+      </c>
+      <c r="Z276">
+        <v>2.3</v>
+      </c>
+      <c r="AA276">
+        <v>3</v>
+      </c>
+      <c r="AB276">
+        <v>3.5</v>
+      </c>
+      <c r="AC276">
+        <v>1.15</v>
+      </c>
+      <c r="AD276">
+        <v>5.25</v>
+      </c>
+      <c r="AE276">
+        <v>1.56</v>
+      </c>
+      <c r="AF276">
+        <v>2.25</v>
+      </c>
+      <c r="AG276">
+        <v>2.88</v>
+      </c>
+      <c r="AH276">
+        <v>1.4</v>
+      </c>
+      <c r="AI276">
+        <v>2.38</v>
+      </c>
+      <c r="AJ276">
+        <v>1.53</v>
+      </c>
+      <c r="AK276">
+        <v>1.25</v>
+      </c>
+      <c r="AL276">
+        <v>1.42</v>
+      </c>
+      <c r="AM276">
+        <v>1.61</v>
+      </c>
+      <c r="AN276">
+        <v>2.18</v>
+      </c>
+      <c r="AO276">
+        <v>1.38</v>
+      </c>
+      <c r="AP276">
+        <v>2</v>
+      </c>
+      <c r="AQ276">
+        <v>1.3</v>
+      </c>
+      <c r="AR276">
+        <v>1.73</v>
+      </c>
+      <c r="AS276">
+        <v>1.51</v>
+      </c>
+      <c r="AT276">
+        <v>3.24</v>
+      </c>
+      <c r="AU276">
+        <v>5</v>
+      </c>
+      <c r="AV276">
+        <v>5</v>
+      </c>
+      <c r="AW276">
+        <v>8</v>
+      </c>
+      <c r="AX276">
+        <v>0</v>
+      </c>
+      <c r="AY276">
+        <v>13</v>
+      </c>
+      <c r="AZ276">
+        <v>5</v>
+      </c>
+      <c r="BA276">
+        <v>4</v>
+      </c>
+      <c r="BB276">
+        <v>1</v>
+      </c>
+      <c r="BC276">
+        <v>5</v>
+      </c>
+      <c r="BD276">
+        <v>1.55</v>
+      </c>
+      <c r="BE276">
+        <v>6.25</v>
+      </c>
+      <c r="BF276">
+        <v>3</v>
+      </c>
+      <c r="BG276">
+        <v>1.41</v>
+      </c>
+      <c r="BH276">
+        <v>2.6</v>
+      </c>
+      <c r="BI276">
+        <v>1.75</v>
+      </c>
+      <c r="BJ276">
+        <v>1.9</v>
+      </c>
+      <c r="BK276">
+        <v>2.3</v>
+      </c>
+      <c r="BL276">
+        <v>1.5</v>
+      </c>
+      <c r="BM276">
+        <v>3.25</v>
+      </c>
+      <c r="BN276">
+        <v>1.27</v>
+      </c>
+      <c r="BO276">
+        <v>3.45</v>
+      </c>
+      <c r="BP276">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="328">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,6 +760,9 @@
     <t>['4', '90+5']</t>
   </si>
   <si>
+    <t>['7', '39', '90+1']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -992,6 +995,9 @@
   </si>
   <si>
     <t>['71', '88']</t>
+  </si>
+  <si>
+    <t>['24']</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP276"/>
+  <dimension ref="A1:BP278"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1609,7 +1615,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -2021,7 +2027,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2433,7 +2439,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2639,7 +2645,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -3257,7 +3263,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -5111,7 +5117,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5523,7 +5529,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q21">
         <v>2.63</v>
@@ -5604,7 +5610,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ21">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5935,7 +5941,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6141,7 +6147,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6553,7 +6559,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6837,7 +6843,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AQ27">
         <v>0.83</v>
@@ -6965,7 +6971,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -9437,7 +9443,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -10136,7 +10142,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -10261,7 +10267,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10467,7 +10473,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10673,7 +10679,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10879,7 +10885,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -11085,7 +11091,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11909,7 +11915,7 @@
         <v>131</v>
       </c>
       <c r="P52" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -12321,7 +12327,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -12605,7 +12611,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AQ55">
         <v>1.27</v>
@@ -13145,7 +13151,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13763,7 +13769,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -14999,7 +15005,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -16029,7 +16035,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -16316,7 +16322,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ73">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR73">
         <v>1.21</v>
@@ -17059,7 +17065,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q77">
         <v>5</v>
@@ -17265,7 +17271,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q78">
         <v>2.5</v>
@@ -17471,7 +17477,7 @@
         <v>148</v>
       </c>
       <c r="P79" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q79">
         <v>3.2</v>
@@ -17883,7 +17889,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -18089,7 +18095,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18373,7 +18379,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AQ83">
         <v>0.89</v>
@@ -18707,7 +18713,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -19531,7 +19537,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19737,7 +19743,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20230,7 +20236,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ92">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR92">
         <v>1.29</v>
@@ -20355,7 +20361,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20973,7 +20979,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -21179,7 +21185,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21797,7 +21803,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23445,7 +23451,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23651,7 +23657,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23729,7 +23735,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AQ109">
         <v>0.7</v>
@@ -23857,7 +23863,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -24269,7 +24275,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24681,7 +24687,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24887,7 +24893,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -25093,7 +25099,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25299,7 +25305,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -26123,7 +26129,7 @@
         <v>175</v>
       </c>
       <c r="P121" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q121">
         <v>4.33</v>
@@ -26329,7 +26335,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26535,7 +26541,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -27565,7 +27571,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -27849,7 +27855,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AQ129">
         <v>0.5</v>
@@ -28389,7 +28395,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -29007,7 +29013,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -31273,7 +31279,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31479,7 +31485,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31685,7 +31691,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31766,7 +31772,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ148">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR148">
         <v>1.46</v>
@@ -31891,7 +31897,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -32097,7 +32103,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32715,7 +32721,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33127,7 +33133,7 @@
         <v>192</v>
       </c>
       <c r="P155" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33539,7 +33545,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -34363,7 +34369,7 @@
         <v>174</v>
       </c>
       <c r="P161" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34775,7 +34781,7 @@
         <v>196</v>
       </c>
       <c r="P163" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q163">
         <v>2.1</v>
@@ -34853,7 +34859,7 @@
         <v>1.5</v>
       </c>
       <c r="AP163">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AQ163">
         <v>1.56</v>
@@ -34981,7 +34987,7 @@
         <v>197</v>
       </c>
       <c r="P164" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q164">
         <v>3.75</v>
@@ -35805,7 +35811,7 @@
         <v>100</v>
       </c>
       <c r="P168" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q168">
         <v>4.33</v>
@@ -36011,7 +36017,7 @@
         <v>199</v>
       </c>
       <c r="P169" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q169">
         <v>2.75</v>
@@ -36629,7 +36635,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q172">
         <v>2.38</v>
@@ -37041,7 +37047,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q174">
         <v>3.25</v>
@@ -38152,7 +38158,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ179">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR179">
         <v>1.19</v>
@@ -38277,7 +38283,7 @@
         <v>209</v>
       </c>
       <c r="P180" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38483,7 +38489,7 @@
         <v>100</v>
       </c>
       <c r="P181" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38689,7 +38695,7 @@
         <v>108</v>
       </c>
       <c r="P182" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39513,7 +39519,7 @@
         <v>203</v>
       </c>
       <c r="P186" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39719,7 +39725,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q187">
         <v>4</v>
@@ -40337,7 +40343,7 @@
         <v>151</v>
       </c>
       <c r="P190" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q190">
         <v>2.2</v>
@@ -40415,7 +40421,7 @@
         <v>1.17</v>
       </c>
       <c r="AP190">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AQ190">
         <v>1</v>
@@ -40543,7 +40549,7 @@
         <v>100</v>
       </c>
       <c r="P191" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q191">
         <v>4</v>
@@ -40749,7 +40755,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41161,7 +41167,7 @@
         <v>100</v>
       </c>
       <c r="P194" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q194">
         <v>2.4</v>
@@ -41779,7 +41785,7 @@
         <v>100</v>
       </c>
       <c r="P197" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q197">
         <v>4.75</v>
@@ -41985,7 +41991,7 @@
         <v>100</v>
       </c>
       <c r="P198" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q198">
         <v>3.1</v>
@@ -43714,7 +43720,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ206">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR206">
         <v>1.83</v>
@@ -44869,7 +44875,7 @@
         <v>100</v>
       </c>
       <c r="P212" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45075,7 +45081,7 @@
         <v>102</v>
       </c>
       <c r="P213" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45359,7 +45365,7 @@
         <v>1.67</v>
       </c>
       <c r="AP214">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AQ214">
         <v>1.3</v>
@@ -46517,7 +46523,7 @@
         <v>226</v>
       </c>
       <c r="P220" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47135,7 +47141,7 @@
         <v>188</v>
       </c>
       <c r="P223" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -48165,7 +48171,7 @@
         <v>232</v>
       </c>
       <c r="P228" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q228">
         <v>4.33</v>
@@ -48783,7 +48789,7 @@
         <v>156</v>
       </c>
       <c r="P231" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q231">
         <v>3.75</v>
@@ -49401,7 +49407,7 @@
         <v>236</v>
       </c>
       <c r="P234" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q234">
         <v>2.75</v>
@@ -49813,7 +49819,7 @@
         <v>100</v>
       </c>
       <c r="P236" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q236">
         <v>2.25</v>
@@ -50306,7 +50312,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ238">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR238">
         <v>1.5</v>
@@ -50431,7 +50437,7 @@
         <v>100</v>
       </c>
       <c r="P239" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q239">
         <v>3.6</v>
@@ -50921,7 +50927,7 @@
         <v>1</v>
       </c>
       <c r="AP241">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AQ241">
         <v>0.88</v>
@@ -51049,7 +51055,7 @@
         <v>239</v>
       </c>
       <c r="P242" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q242">
         <v>2.95</v>
@@ -51461,7 +51467,7 @@
         <v>100</v>
       </c>
       <c r="P244" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q244">
         <v>2.4</v>
@@ -51542,7 +51548,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ244">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AR244">
         <v>1.6</v>
@@ -52079,7 +52085,7 @@
         <v>241</v>
       </c>
       <c r="P247" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q247">
         <v>2.2</v>
@@ -52285,7 +52291,7 @@
         <v>242</v>
       </c>
       <c r="P248" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q248">
         <v>2.63</v>
@@ -52569,7 +52575,7 @@
         <v>1.63</v>
       </c>
       <c r="AP249">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AQ249">
         <v>1.68</v>
@@ -52903,7 +52909,7 @@
         <v>179</v>
       </c>
       <c r="P251" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q251">
         <v>2.6</v>
@@ -53109,7 +53115,7 @@
         <v>100</v>
       </c>
       <c r="P252" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q252">
         <v>2.88</v>
@@ -53393,10 +53399,10 @@
         <v>1.53</v>
       </c>
       <c r="AP253">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AQ253">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AR253">
         <v>1.9</v>
@@ -53808,7 +53814,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ255">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AR255">
         <v>1.27</v>
@@ -53933,7 +53939,7 @@
         <v>100</v>
       </c>
       <c r="P256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q256">
         <v>3.2</v>
@@ -54014,7 +54020,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ256">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AR256">
         <v>1.48</v>
@@ -54345,7 +54351,7 @@
         <v>245</v>
       </c>
       <c r="P258" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q258">
         <v>2.88</v>
@@ -54757,7 +54763,7 @@
         <v>100</v>
       </c>
       <c r="P260" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q260">
         <v>2.75</v>
@@ -55169,7 +55175,7 @@
         <v>100</v>
       </c>
       <c r="P262" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q262">
         <v>2</v>
@@ -55375,7 +55381,7 @@
         <v>100</v>
       </c>
       <c r="P263" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -55787,7 +55793,7 @@
         <v>245</v>
       </c>
       <c r="P265" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -56199,7 +56205,7 @@
         <v>100</v>
       </c>
       <c r="P267" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -56611,7 +56617,7 @@
         <v>246</v>
       </c>
       <c r="P269" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q269">
         <v>4.75</v>
@@ -56817,7 +56823,7 @@
         <v>246</v>
       </c>
       <c r="P270" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -57023,7 +57029,7 @@
         <v>186</v>
       </c>
       <c r="P271" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q271">
         <v>3.2</v>
@@ -57229,7 +57235,7 @@
         <v>186</v>
       </c>
       <c r="P272" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q272">
         <v>2.75</v>
@@ -57435,7 +57441,7 @@
         <v>247</v>
       </c>
       <c r="P273" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q273">
         <v>2.4</v>
@@ -57641,7 +57647,7 @@
         <v>247</v>
       </c>
       <c r="P274" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q274">
         <v>2.63</v>
@@ -58210,6 +58216,418 @@
       </c>
       <c r="BP276">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="277" spans="1:68">
+      <c r="A277" s="1">
+        <v>276</v>
+      </c>
+      <c r="B277">
+        <v>7820563</v>
+      </c>
+      <c r="C277" t="s">
+        <v>68</v>
+      </c>
+      <c r="D277" t="s">
+        <v>69</v>
+      </c>
+      <c r="E277" s="2">
+        <v>45851.875</v>
+      </c>
+      <c r="F277">
+        <v>1</v>
+      </c>
+      <c r="G277" t="s">
+        <v>95</v>
+      </c>
+      <c r="H277" t="s">
+        <v>82</v>
+      </c>
+      <c r="I277">
+        <v>2</v>
+      </c>
+      <c r="J277">
+        <v>1</v>
+      </c>
+      <c r="K277">
+        <v>3</v>
+      </c>
+      <c r="L277">
+        <v>3</v>
+      </c>
+      <c r="M277">
+        <v>1</v>
+      </c>
+      <c r="N277">
+        <v>4</v>
+      </c>
+      <c r="O277" t="s">
+        <v>248</v>
+      </c>
+      <c r="P277" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q277">
+        <v>2.1</v>
+      </c>
+      <c r="R277">
+        <v>2</v>
+      </c>
+      <c r="S277">
+        <v>8.5</v>
+      </c>
+      <c r="T277">
+        <v>1.57</v>
+      </c>
+      <c r="U277">
+        <v>2.25</v>
+      </c>
+      <c r="V277">
+        <v>3.75</v>
+      </c>
+      <c r="W277">
+        <v>1.25</v>
+      </c>
+      <c r="X277">
+        <v>11</v>
+      </c>
+      <c r="Y277">
+        <v>1.05</v>
+      </c>
+      <c r="Z277">
+        <v>1.5</v>
+      </c>
+      <c r="AA277">
+        <v>3.9</v>
+      </c>
+      <c r="AB277">
+        <v>7.5</v>
+      </c>
+      <c r="AC277">
+        <v>1.1</v>
+      </c>
+      <c r="AD277">
+        <v>6.5</v>
+      </c>
+      <c r="AE277">
+        <v>1.45</v>
+      </c>
+      <c r="AF277">
+        <v>2.5</v>
+      </c>
+      <c r="AG277">
+        <v>2.6</v>
+      </c>
+      <c r="AH277">
+        <v>1.48</v>
+      </c>
+      <c r="AI277">
+        <v>2.75</v>
+      </c>
+      <c r="AJ277">
+        <v>1.4</v>
+      </c>
+      <c r="AK277">
+        <v>1.09</v>
+      </c>
+      <c r="AL277">
+        <v>1.27</v>
+      </c>
+      <c r="AM277">
+        <v>2.4</v>
+      </c>
+      <c r="AN277">
+        <v>2.18</v>
+      </c>
+      <c r="AO277">
+        <v>1.67</v>
+      </c>
+      <c r="AP277">
+        <v>2.31</v>
+      </c>
+      <c r="AQ277">
+        <v>1.43</v>
+      </c>
+      <c r="AR277">
+        <v>2.05</v>
+      </c>
+      <c r="AS277">
+        <v>1.22</v>
+      </c>
+      <c r="AT277">
+        <v>3.27</v>
+      </c>
+      <c r="AU277">
+        <v>7</v>
+      </c>
+      <c r="AV277">
+        <v>4</v>
+      </c>
+      <c r="AW277">
+        <v>6</v>
+      </c>
+      <c r="AX277">
+        <v>6</v>
+      </c>
+      <c r="AY277">
+        <v>13</v>
+      </c>
+      <c r="AZ277">
+        <v>10</v>
+      </c>
+      <c r="BA277">
+        <v>2</v>
+      </c>
+      <c r="BB277">
+        <v>4</v>
+      </c>
+      <c r="BC277">
+        <v>6</v>
+      </c>
+      <c r="BD277">
+        <v>1.27</v>
+      </c>
+      <c r="BE277">
+        <v>7.5</v>
+      </c>
+      <c r="BF277">
+        <v>5</v>
+      </c>
+      <c r="BG277">
+        <v>1.44</v>
+      </c>
+      <c r="BH277">
+        <v>2.5</v>
+      </c>
+      <c r="BI277">
+        <v>1.8</v>
+      </c>
+      <c r="BJ277">
+        <v>1.83</v>
+      </c>
+      <c r="BK277">
+        <v>2.4</v>
+      </c>
+      <c r="BL277">
+        <v>1.47</v>
+      </c>
+      <c r="BM277">
+        <v>3.4</v>
+      </c>
+      <c r="BN277">
+        <v>1.25</v>
+      </c>
+      <c r="BO277">
+        <v>4</v>
+      </c>
+      <c r="BP277">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="278" spans="1:68">
+      <c r="A278" s="1">
+        <v>277</v>
+      </c>
+      <c r="B278">
+        <v>7940208</v>
+      </c>
+      <c r="C278" t="s">
+        <v>68</v>
+      </c>
+      <c r="D278" t="s">
+        <v>69</v>
+      </c>
+      <c r="E278" s="2">
+        <v>45851.875</v>
+      </c>
+      <c r="F278">
+        <v>1</v>
+      </c>
+      <c r="G278" t="s">
+        <v>95</v>
+      </c>
+      <c r="H278" t="s">
+        <v>82</v>
+      </c>
+      <c r="I278">
+        <v>2</v>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="K278">
+        <v>3</v>
+      </c>
+      <c r="L278">
+        <v>3</v>
+      </c>
+      <c r="M278">
+        <v>1</v>
+      </c>
+      <c r="N278">
+        <v>4</v>
+      </c>
+      <c r="O278" t="s">
+        <v>248</v>
+      </c>
+      <c r="P278" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q278">
+        <v>2.3</v>
+      </c>
+      <c r="R278">
+        <v>2</v>
+      </c>
+      <c r="S278">
+        <v>7</v>
+      </c>
+      <c r="T278">
+        <v>1.57</v>
+      </c>
+      <c r="U278">
+        <v>2.25</v>
+      </c>
+      <c r="V278">
+        <v>3.75</v>
+      </c>
+      <c r="W278">
+        <v>1.25</v>
+      </c>
+      <c r="X278">
+        <v>11</v>
+      </c>
+      <c r="Y278">
+        <v>1.05</v>
+      </c>
+      <c r="Z278">
+        <v>1.62</v>
+      </c>
+      <c r="AA278">
+        <v>3.7</v>
+      </c>
+      <c r="AB278">
+        <v>6</v>
+      </c>
+      <c r="AC278">
+        <v>1.1</v>
+      </c>
+      <c r="AD278">
+        <v>6.5</v>
+      </c>
+      <c r="AE278">
+        <v>1.46</v>
+      </c>
+      <c r="AF278">
+        <v>2.48</v>
+      </c>
+      <c r="AG278">
+        <v>2.6</v>
+      </c>
+      <c r="AH278">
+        <v>1.48</v>
+      </c>
+      <c r="AI278">
+        <v>2.63</v>
+      </c>
+      <c r="AJ278">
+        <v>1.44</v>
+      </c>
+      <c r="AK278">
+        <v>1.12</v>
+      </c>
+      <c r="AL278">
+        <v>1.29</v>
+      </c>
+      <c r="AM278">
+        <v>2.2</v>
+      </c>
+      <c r="AN278">
+        <v>2.18</v>
+      </c>
+      <c r="AO278">
+        <v>1.67</v>
+      </c>
+      <c r="AP278">
+        <v>2.31</v>
+      </c>
+      <c r="AQ278">
+        <v>1.43</v>
+      </c>
+      <c r="AR278">
+        <v>2.05</v>
+      </c>
+      <c r="AS278">
+        <v>1.22</v>
+      </c>
+      <c r="AT278">
+        <v>3.27</v>
+      </c>
+      <c r="AU278">
+        <v>7</v>
+      </c>
+      <c r="AV278">
+        <v>4</v>
+      </c>
+      <c r="AW278">
+        <v>2</v>
+      </c>
+      <c r="AX278">
+        <v>4</v>
+      </c>
+      <c r="AY278">
+        <v>9</v>
+      </c>
+      <c r="AZ278">
+        <v>8</v>
+      </c>
+      <c r="BA278">
+        <v>2</v>
+      </c>
+      <c r="BB278">
+        <v>4</v>
+      </c>
+      <c r="BC278">
+        <v>6</v>
+      </c>
+      <c r="BD278">
+        <v>1.21</v>
+      </c>
+      <c r="BE278">
+        <v>8</v>
+      </c>
+      <c r="BF278">
+        <v>6</v>
+      </c>
+      <c r="BG278">
+        <v>1.57</v>
+      </c>
+      <c r="BH278">
+        <v>2.2</v>
+      </c>
+      <c r="BI278">
+        <v>2</v>
+      </c>
+      <c r="BJ278">
+        <v>1.66</v>
+      </c>
+      <c r="BK278">
+        <v>2.8</v>
+      </c>
+      <c r="BL278">
+        <v>1.36</v>
+      </c>
+      <c r="BM278">
+        <v>4</v>
+      </c>
+      <c r="BN278">
+        <v>1.19</v>
+      </c>
+      <c r="BO278">
+        <v>4.5</v>
+      </c>
+      <c r="BP278">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="328">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1359,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP278"/>
+  <dimension ref="A1:BP281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ17">
         <v>1.4</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18">
         <v>0.22</v>
@@ -5198,7 +5198,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ19">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -11169,7 +11169,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ48">
         <v>1.3</v>
@@ -13229,10 +13229,10 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AR58">
         <v>0.9</v>
@@ -13644,7 +13644,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ60">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR60">
         <v>2.21</v>
@@ -14877,7 +14877,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ66">
         <v>1.56</v>
@@ -15086,7 +15086,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ67">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AR67">
         <v>1.78</v>
@@ -16937,7 +16937,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ76">
         <v>1.3</v>
@@ -18382,7 +18382,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ83">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR83">
         <v>1.66</v>
@@ -20027,7 +20027,7 @@
         <v>1.5</v>
       </c>
       <c r="AP91">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -22090,7 +22090,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ101">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AR101">
         <v>1.73</v>
@@ -24356,7 +24356,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ112">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR112">
         <v>1.94</v>
@@ -25589,7 +25589,7 @@
         <v>1.33</v>
       </c>
       <c r="AP118">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ118">
         <v>1.27</v>
@@ -25798,7 +25798,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ119">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AR119">
         <v>1.24</v>
@@ -26207,7 +26207,7 @@
         <v>2.33</v>
       </c>
       <c r="AP121">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ121">
         <v>1.86</v>
@@ -27034,7 +27034,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ125">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR125">
         <v>1.05</v>
@@ -29503,7 +29503,7 @@
         <v>1.5</v>
       </c>
       <c r="AP137">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ137">
         <v>1.57</v>
@@ -30742,7 +30742,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ143">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AR143">
         <v>1.56</v>
@@ -33417,7 +33417,7 @@
         <v>1.6</v>
       </c>
       <c r="AP156">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ156">
         <v>1.6</v>
@@ -33626,7 +33626,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ157">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR157">
         <v>1.71</v>
@@ -37952,7 +37952,7 @@
         <v>2</v>
       </c>
       <c r="AQ178">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AR178">
         <v>1.78</v>
@@ -38155,7 +38155,7 @@
         <v>1.4</v>
       </c>
       <c r="AP179">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ179">
         <v>1.43</v>
@@ -38773,7 +38773,7 @@
         <v>1.33</v>
       </c>
       <c r="AP182">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ182">
         <v>1.33</v>
@@ -41454,7 +41454,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ195">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR195">
         <v>1.04</v>
@@ -42896,7 +42896,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ202">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AR202">
         <v>1.71</v>
@@ -43305,7 +43305,7 @@
         <v>1.83</v>
       </c>
       <c r="AP204">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ204">
         <v>1.82</v>
@@ -48043,7 +48043,7 @@
         <v>0.67</v>
       </c>
       <c r="AP227">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ227">
         <v>0.67</v>
@@ -48252,7 +48252,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ228">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AR228">
         <v>1.57</v>
@@ -49073,7 +49073,7 @@
         <v>1.14</v>
       </c>
       <c r="AP232">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ232">
         <v>1</v>
@@ -50106,7 +50106,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ237">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR237">
         <v>1.68</v>
@@ -51754,7 +51754,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ245">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AR245">
         <v>1.51</v>
@@ -52372,7 +52372,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ248">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR248">
         <v>1.5</v>
@@ -58628,6 +58628,624 @@
       </c>
       <c r="BP278">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="279" spans="1:68">
+      <c r="A279" s="1">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>7820568</v>
+      </c>
+      <c r="C279" t="s">
+        <v>68</v>
+      </c>
+      <c r="D279" t="s">
+        <v>69</v>
+      </c>
+      <c r="E279" s="2">
+        <v>45852.6875</v>
+      </c>
+      <c r="F279">
+        <v>1</v>
+      </c>
+      <c r="G279" t="s">
+        <v>86</v>
+      </c>
+      <c r="H279" t="s">
+        <v>74</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>0</v>
+      </c>
+      <c r="K279">
+        <v>0</v>
+      </c>
+      <c r="L279">
+        <v>1</v>
+      </c>
+      <c r="M279">
+        <v>0</v>
+      </c>
+      <c r="N279">
+        <v>1</v>
+      </c>
+      <c r="O279" t="s">
+        <v>178</v>
+      </c>
+      <c r="P279" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q279">
+        <v>4</v>
+      </c>
+      <c r="R279">
+        <v>1.83</v>
+      </c>
+      <c r="S279">
+        <v>3.4</v>
+      </c>
+      <c r="T279">
+        <v>1.67</v>
+      </c>
+      <c r="U279">
+        <v>2.1</v>
+      </c>
+      <c r="V279">
+        <v>4.33</v>
+      </c>
+      <c r="W279">
+        <v>1.2</v>
+      </c>
+      <c r="X279">
+        <v>15</v>
+      </c>
+      <c r="Y279">
+        <v>1.03</v>
+      </c>
+      <c r="Z279">
+        <v>3.25</v>
+      </c>
+      <c r="AA279">
+        <v>2.75</v>
+      </c>
+      <c r="AB279">
+        <v>2.5</v>
+      </c>
+      <c r="AC279">
+        <v>1.15</v>
+      </c>
+      <c r="AD279">
+        <v>5.25</v>
+      </c>
+      <c r="AE279">
+        <v>1.63</v>
+      </c>
+      <c r="AF279">
+        <v>2.1</v>
+      </c>
+      <c r="AG279">
+        <v>3.1</v>
+      </c>
+      <c r="AH279">
+        <v>1.36</v>
+      </c>
+      <c r="AI279">
+        <v>2.38</v>
+      </c>
+      <c r="AJ279">
+        <v>1.53</v>
+      </c>
+      <c r="AK279">
+        <v>1.5</v>
+      </c>
+      <c r="AL279">
+        <v>1.41</v>
+      </c>
+      <c r="AM279">
+        <v>1.34</v>
+      </c>
+      <c r="AN279">
+        <v>1.5</v>
+      </c>
+      <c r="AO279">
+        <v>0.89</v>
+      </c>
+      <c r="AP279">
+        <v>1.67</v>
+      </c>
+      <c r="AQ279">
+        <v>0.8</v>
+      </c>
+      <c r="AR279">
+        <v>1.15</v>
+      </c>
+      <c r="AS279">
+        <v>1.46</v>
+      </c>
+      <c r="AT279">
+        <v>2.61</v>
+      </c>
+      <c r="AU279">
+        <v>3</v>
+      </c>
+      <c r="AV279">
+        <v>6</v>
+      </c>
+      <c r="AW279">
+        <v>4</v>
+      </c>
+      <c r="AX279">
+        <v>11</v>
+      </c>
+      <c r="AY279">
+        <v>7</v>
+      </c>
+      <c r="AZ279">
+        <v>17</v>
+      </c>
+      <c r="BA279">
+        <v>2</v>
+      </c>
+      <c r="BB279">
+        <v>8</v>
+      </c>
+      <c r="BC279">
+        <v>10</v>
+      </c>
+      <c r="BD279">
+        <v>2.15</v>
+      </c>
+      <c r="BE279">
+        <v>6</v>
+      </c>
+      <c r="BF279">
+        <v>1.95</v>
+      </c>
+      <c r="BG279">
+        <v>1.44</v>
+      </c>
+      <c r="BH279">
+        <v>2.5</v>
+      </c>
+      <c r="BI279">
+        <v>1.8</v>
+      </c>
+      <c r="BJ279">
+        <v>1.83</v>
+      </c>
+      <c r="BK279">
+        <v>2.4</v>
+      </c>
+      <c r="BL279">
+        <v>1.46</v>
+      </c>
+      <c r="BM279">
+        <v>3.4</v>
+      </c>
+      <c r="BN279">
+        <v>1.26</v>
+      </c>
+      <c r="BO279">
+        <v>4</v>
+      </c>
+      <c r="BP279">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="280" spans="1:68">
+      <c r="A280" s="1">
+        <v>279</v>
+      </c>
+      <c r="B280">
+        <v>7940199</v>
+      </c>
+      <c r="C280" t="s">
+        <v>68</v>
+      </c>
+      <c r="D280" t="s">
+        <v>69</v>
+      </c>
+      <c r="E280" s="2">
+        <v>45852.79166666666</v>
+      </c>
+      <c r="F280">
+        <v>1</v>
+      </c>
+      <c r="G280" t="s">
+        <v>85</v>
+      </c>
+      <c r="H280" t="s">
+        <v>73</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280">
+        <v>0</v>
+      </c>
+      <c r="L280">
+        <v>0</v>
+      </c>
+      <c r="M280">
+        <v>0</v>
+      </c>
+      <c r="N280">
+        <v>0</v>
+      </c>
+      <c r="O280" t="s">
+        <v>100</v>
+      </c>
+      <c r="P280" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q280">
+        <v>3.2</v>
+      </c>
+      <c r="R280">
+        <v>1.95</v>
+      </c>
+      <c r="S280">
+        <v>4</v>
+      </c>
+      <c r="T280">
+        <v>1.53</v>
+      </c>
+      <c r="U280">
+        <v>2.38</v>
+      </c>
+      <c r="V280">
+        <v>3.5</v>
+      </c>
+      <c r="W280">
+        <v>1.29</v>
+      </c>
+      <c r="X280">
+        <v>11</v>
+      </c>
+      <c r="Y280">
+        <v>1.05</v>
+      </c>
+      <c r="Z280">
+        <v>2.45</v>
+      </c>
+      <c r="AA280">
+        <v>3</v>
+      </c>
+      <c r="AB280">
+        <v>3.3</v>
+      </c>
+      <c r="AC280">
+        <v>1.1</v>
+      </c>
+      <c r="AD280">
+        <v>6.5</v>
+      </c>
+      <c r="AE280">
+        <v>1.5</v>
+      </c>
+      <c r="AF280">
+        <v>2.38</v>
+      </c>
+      <c r="AG280">
+        <v>2.5</v>
+      </c>
+      <c r="AH280">
+        <v>1.5</v>
+      </c>
+      <c r="AI280">
+        <v>2.05</v>
+      </c>
+      <c r="AJ280">
+        <v>1.7</v>
+      </c>
+      <c r="AK280">
+        <v>1.34</v>
+      </c>
+      <c r="AL280">
+        <v>1.36</v>
+      </c>
+      <c r="AM280">
+        <v>1.55</v>
+      </c>
+      <c r="AN280">
+        <v>1.25</v>
+      </c>
+      <c r="AO280">
+        <v>1.22</v>
+      </c>
+      <c r="AP280">
+        <v>1.2</v>
+      </c>
+      <c r="AQ280">
+        <v>1.18</v>
+      </c>
+      <c r="AR280">
+        <v>1.3</v>
+      </c>
+      <c r="AS280">
+        <v>1.41</v>
+      </c>
+      <c r="AT280">
+        <v>2.71</v>
+      </c>
+      <c r="AU280">
+        <v>3</v>
+      </c>
+      <c r="AV280">
+        <v>5</v>
+      </c>
+      <c r="AW280">
+        <v>5</v>
+      </c>
+      <c r="AX280">
+        <v>3</v>
+      </c>
+      <c r="AY280">
+        <v>8</v>
+      </c>
+      <c r="AZ280">
+        <v>8</v>
+      </c>
+      <c r="BA280">
+        <v>6</v>
+      </c>
+      <c r="BB280">
+        <v>3</v>
+      </c>
+      <c r="BC280">
+        <v>9</v>
+      </c>
+      <c r="BD280">
+        <v>1.51</v>
+      </c>
+      <c r="BE280">
+        <v>6.5</v>
+      </c>
+      <c r="BF280">
+        <v>3.2</v>
+      </c>
+      <c r="BG280">
+        <v>1.44</v>
+      </c>
+      <c r="BH280">
+        <v>2.5</v>
+      </c>
+      <c r="BI280">
+        <v>1.82</v>
+      </c>
+      <c r="BJ280">
+        <v>1.83</v>
+      </c>
+      <c r="BK280">
+        <v>2.4</v>
+      </c>
+      <c r="BL280">
+        <v>1.46</v>
+      </c>
+      <c r="BM280">
+        <v>3.4</v>
+      </c>
+      <c r="BN280">
+        <v>1.25</v>
+      </c>
+      <c r="BO280">
+        <v>3.85</v>
+      </c>
+      <c r="BP280">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="281" spans="1:68">
+      <c r="A281" s="1">
+        <v>280</v>
+      </c>
+      <c r="B281">
+        <v>7820560</v>
+      </c>
+      <c r="C281" t="s">
+        <v>68</v>
+      </c>
+      <c r="D281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E281" s="2">
+        <v>45852.79166666666</v>
+      </c>
+      <c r="F281">
+        <v>1</v>
+      </c>
+      <c r="G281" t="s">
+        <v>85</v>
+      </c>
+      <c r="H281" t="s">
+        <v>73</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281">
+        <v>0</v>
+      </c>
+      <c r="L281">
+        <v>0</v>
+      </c>
+      <c r="M281">
+        <v>0</v>
+      </c>
+      <c r="N281">
+        <v>0</v>
+      </c>
+      <c r="O281" t="s">
+        <v>100</v>
+      </c>
+      <c r="P281" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q281">
+        <v>3.1</v>
+      </c>
+      <c r="R281">
+        <v>1.95</v>
+      </c>
+      <c r="S281">
+        <v>4</v>
+      </c>
+      <c r="T281">
+        <v>1.53</v>
+      </c>
+      <c r="U281">
+        <v>2.38</v>
+      </c>
+      <c r="V281">
+        <v>3.5</v>
+      </c>
+      <c r="W281">
+        <v>1.29</v>
+      </c>
+      <c r="X281">
+        <v>11</v>
+      </c>
+      <c r="Y281">
+        <v>1.05</v>
+      </c>
+      <c r="Z281">
+        <v>2.35</v>
+      </c>
+      <c r="AA281">
+        <v>2.9</v>
+      </c>
+      <c r="AB281">
+        <v>3.4</v>
+      </c>
+      <c r="AC281">
+        <v>1.1</v>
+      </c>
+      <c r="AD281">
+        <v>6.5</v>
+      </c>
+      <c r="AE281">
+        <v>1.5</v>
+      </c>
+      <c r="AF281">
+        <v>2.38</v>
+      </c>
+      <c r="AG281">
+        <v>2.5</v>
+      </c>
+      <c r="AH281">
+        <v>1.5</v>
+      </c>
+      <c r="AI281">
+        <v>2.05</v>
+      </c>
+      <c r="AJ281">
+        <v>1.7</v>
+      </c>
+      <c r="AK281">
+        <v>1.29</v>
+      </c>
+      <c r="AL281">
+        <v>1.35</v>
+      </c>
+      <c r="AM281">
+        <v>1.65</v>
+      </c>
+      <c r="AN281">
+        <v>1.25</v>
+      </c>
+      <c r="AO281">
+        <v>1.22</v>
+      </c>
+      <c r="AP281">
+        <v>1.2</v>
+      </c>
+      <c r="AQ281">
+        <v>1.18</v>
+      </c>
+      <c r="AR281">
+        <v>1.3</v>
+      </c>
+      <c r="AS281">
+        <v>1.41</v>
+      </c>
+      <c r="AT281">
+        <v>2.71</v>
+      </c>
+      <c r="AU281">
+        <v>3</v>
+      </c>
+      <c r="AV281">
+        <v>4</v>
+      </c>
+      <c r="AW281">
+        <v>7</v>
+      </c>
+      <c r="AX281">
+        <v>6</v>
+      </c>
+      <c r="AY281">
+        <v>10</v>
+      </c>
+      <c r="AZ281">
+        <v>10</v>
+      </c>
+      <c r="BA281">
+        <v>6</v>
+      </c>
+      <c r="BB281">
+        <v>3</v>
+      </c>
+      <c r="BC281">
+        <v>9</v>
+      </c>
+      <c r="BD281">
+        <v>1.51</v>
+      </c>
+      <c r="BE281">
+        <v>6.5</v>
+      </c>
+      <c r="BF281">
+        <v>3.2</v>
+      </c>
+      <c r="BG281">
+        <v>1.44</v>
+      </c>
+      <c r="BH281">
+        <v>2.5</v>
+      </c>
+      <c r="BI281">
+        <v>1.82</v>
+      </c>
+      <c r="BJ281">
+        <v>1.83</v>
+      </c>
+      <c r="BK281">
+        <v>2.45</v>
+      </c>
+      <c r="BL281">
+        <v>1.46</v>
+      </c>
+      <c r="BM281">
+        <v>3.4</v>
+      </c>
+      <c r="BN281">
+        <v>1.25</v>
+      </c>
+      <c r="BO281">
+        <v>3.8</v>
+      </c>
+      <c r="BP281">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Argentina Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -763,6 +763,9 @@
     <t>['7', '39', '90+1']</t>
   </si>
   <si>
+    <t>['45', '45+4']</t>
+  </si>
+  <si>
     <t>['18', '26', '48']</t>
   </si>
   <si>
@@ -998,6 +1001,9 @@
   </si>
   <si>
     <t>['24']</t>
+  </si>
+  <si>
+    <t>['85']</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP281"/>
+  <dimension ref="A1:BP285"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1615,7 +1621,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -2027,7 +2033,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2439,7 +2445,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2645,7 +2651,7 @@
         <v>102</v>
       </c>
       <c r="P7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -3263,7 +3269,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q10">
         <v>3.5</v>
@@ -5117,7 +5123,7 @@
         <v>111</v>
       </c>
       <c r="P19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -5529,7 +5535,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q21">
         <v>2.63</v>
@@ -5607,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21">
         <v>1.43</v>
@@ -5941,7 +5947,7 @@
         <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6147,7 +6153,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6434,7 +6440,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6559,7 +6565,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6637,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AQ26">
         <v>1.3</v>
@@ -6971,7 +6977,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -7670,7 +7676,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -9443,7 +9449,7 @@
         <v>124</v>
       </c>
       <c r="P40" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -10267,7 +10273,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q44">
         <v>2.63</v>
@@ -10473,7 +10479,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10679,7 +10685,7 @@
         <v>127</v>
       </c>
       <c r="P46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -10885,7 +10891,7 @@
         <v>128</v>
       </c>
       <c r="P47" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q47">
         <v>3.3</v>
@@ -11091,7 +11097,7 @@
         <v>104</v>
       </c>
       <c r="P48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q48">
         <v>3.15</v>
@@ -11584,7 +11590,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AR50">
         <v>2.5</v>
@@ -11787,7 +11793,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AQ51">
         <v>1.86</v>
@@ -11915,7 +11921,7 @@
         <v>131</v>
       </c>
       <c r="P52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -11996,7 +12002,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ52">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="AR52">
         <v>1.47</v>
@@ -12199,7 +12205,7 @@
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="AQ53">
         <v>1.82</v>
@@ -12327,7 +12333,7 @@
         <v>132</v>
       </c>
       <c r="P54" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -13151,7 +13157,7 @@
         <v>114</v>
       </c>
       <c r="P58" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q58">
         <v>3.5</v>
@@ -13769,7 +13775,7 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q61">
         <v>3.9</v>
@@ -15005,7 +15011,7 @@
         <v>100</v>
       </c>
       <c r="P67" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q67">
         <v>3.2</v>
@@ -16035,7 +16041,7 @@
         <v>100</v>
       </c>
       <c r="P72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q72">
         <v>4.5</v>
@@ -16731,7 +16737,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AQ75">
         <v>0.83</v>
@@ -17065,7 +17071,7 @@
         <v>146</v>
       </c>
       <c r="P77" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q77">
         <v>5</v>
@@ -17146,7 +17152,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="AR77">
         <v>2.48</v>
@@ -17271,7 +17277,7 @@
         <v>147</v>
       </c>
       <c r="P78" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q78">
         <v>2.5</v>
@@ -17477,7 +17483,7 @@
         <v>148</v>
       </c>
       <c r="P79" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q79">
         <v>3.2</v>
@@ -17558,7 +17564,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AR79">
         <v>1.76</v>
@@ -17889,7 +17895,7 @@
         <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -18095,7 +18101,7 @@
         <v>151</v>
       </c>
       <c r="P82" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18713,7 +18719,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q85">
         <v>2.75</v>
@@ -19537,7 +19543,7 @@
         <v>100</v>
       </c>
       <c r="P89" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19615,7 +19621,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -19743,7 +19749,7 @@
         <v>100</v>
       </c>
       <c r="P90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20361,7 +20367,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20979,7 +20985,7 @@
         <v>161</v>
       </c>
       <c r="P96" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q96">
         <v>2.1</v>
@@ -21185,7 +21191,7 @@
         <v>100</v>
       </c>
       <c r="P97" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q97">
         <v>6.5</v>
@@ -21803,7 +21809,7 @@
         <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23451,7 +23457,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23657,7 +23663,7 @@
         <v>100</v>
       </c>
       <c r="P109" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23738,7 +23744,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ109">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="AR109">
         <v>1.66</v>
@@ -23863,7 +23869,7 @@
         <v>169</v>
       </c>
       <c r="P110" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -23944,7 +23950,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ110">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AR110">
         <v>2.19</v>
@@ -24147,7 +24153,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AQ111">
         <v>0.5</v>
@@ -24275,7 +24281,7 @@
         <v>170</v>
       </c>
       <c r="P112" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q112">
         <v>3.6</v>
@@ -24687,7 +24693,7 @@
         <v>100</v>
       </c>
       <c r="P114" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q114">
         <v>3.25</v>
@@ -24765,7 +24771,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="AQ114">
         <v>1.6</v>
@@ -24893,7 +24899,7 @@
         <v>153</v>
       </c>
       <c r="P115" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -25099,7 +25105,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25305,7 +25311,7 @@
         <v>173</v>
       </c>
       <c r="P117" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -26001,7 +26007,7 @@
         <v>0.67</v>
       </c>
       <c r="AP120">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="AQ120">
         <v>0.22</v>
@@ -26129,7 +26135,7 @@
         <v>175</v>
       </c>
       <c r="P121" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q121">
         <v>4.33</v>
@@ -26335,7 +26341,7 @@
         <v>100</v>
       </c>
       <c r="P122" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q122">
         <v>4</v>
@@ -26541,7 +26547,7 @@
         <v>176</v>
       </c>
       <c r="P123" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -27446,7 +27452,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ127">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="AR127">
         <v>1.66</v>
@@ -27571,7 +27577,7 @@
         <v>100</v>
       </c>
       <c r="P128" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q128">
         <v>4</v>
@@ -27652,7 +27658,7 @@
         <v>1</v>
       </c>
       <c r="AQ128">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AR128">
         <v>2.27</v>
@@ -28395,7 +28401,7 @@
         <v>179</v>
       </c>
       <c r="P132" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q132">
         <v>2.75</v>
@@ -29013,7 +29019,7 @@
         <v>100</v>
       </c>
       <c r="P135" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q135">
         <v>2.05</v>
@@ -31279,7 +31285,7 @@
         <v>187</v>
       </c>
       <c r="P146" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31357,7 +31363,7 @@
         <v>0.75</v>
       </c>
       <c r="AP146">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AQ146">
         <v>0.5</v>
@@ -31485,7 +31491,7 @@
         <v>188</v>
       </c>
       <c r="P147" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31691,7 +31697,7 @@
         <v>100</v>
       </c>
       <c r="P148" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31897,7 +31903,7 @@
         <v>102</v>
       </c>
       <c r="P149" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -32103,7 +32109,7 @@
         <v>100</v>
       </c>
       <c r="P150" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32181,7 +32187,7 @@
         <v>0.8</v>
       </c>
       <c r="AP150">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AQ150">
         <v>1.44</v>
@@ -32721,7 +32727,7 @@
         <v>190</v>
       </c>
       <c r="P153" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32802,7 +32808,7 @@
         <v>2</v>
       </c>
       <c r="AQ153">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="AR153">
         <v>1.16</v>
@@ -33133,7 +33139,7 @@
         <v>192</v>
       </c>
       <c r="P155" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33214,7 +33220,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ155">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AR155">
         <v>1.88</v>
@@ -33545,7 +33551,7 @@
         <v>177</v>
       </c>
       <c r="P157" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -33829,7 +33835,7 @@
         <v>1.6</v>
       </c>
       <c r="AP158">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="AQ158">
         <v>1.33</v>
@@ -34369,7 +34375,7 @@
         <v>174</v>
       </c>
       <c r="P161" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34781,7 +34787,7 @@
         <v>196</v>
       </c>
       <c r="P163" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q163">
         <v>2.1</v>
@@ -34987,7 +34993,7 @@
         <v>197</v>
       </c>
       <c r="P164" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q164">
         <v>3.75</v>
@@ -35811,7 +35817,7 @@
         <v>100</v>
       </c>
       <c r="P168" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q168">
         <v>4.33</v>
@@ -36017,7 +36023,7 @@
         <v>199</v>
       </c>
       <c r="P169" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q169">
         <v>2.75</v>
@@ -36635,7 +36641,7 @@
         <v>202</v>
       </c>
       <c r="P172" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q172">
         <v>2.38</v>
@@ -37047,7 +37053,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q174">
         <v>3.25</v>
@@ -37331,7 +37337,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AQ175">
         <v>0.67</v>
@@ -38283,7 +38289,7 @@
         <v>209</v>
       </c>
       <c r="P180" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38489,7 +38495,7 @@
         <v>100</v>
       </c>
       <c r="P181" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38695,7 +38701,7 @@
         <v>108</v>
       </c>
       <c r="P182" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39394,7 +39400,7 @@
         <v>2</v>
       </c>
       <c r="AQ185">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AR185">
         <v>1.27</v>
@@ -39519,7 +39525,7 @@
         <v>203</v>
       </c>
       <c r="P186" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39725,7 +39731,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q187">
         <v>4</v>
@@ -39806,7 +39812,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ187">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="AR187">
         <v>1.57</v>
@@ -40343,7 +40349,7 @@
         <v>151</v>
       </c>
       <c r="P190" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q190">
         <v>2.2</v>
@@ -40549,7 +40555,7 @@
         <v>100</v>
       </c>
       <c r="P191" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q191">
         <v>4</v>
@@ -40755,7 +40761,7 @@
         <v>126</v>
       </c>
       <c r="P192" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41167,7 +41173,7 @@
         <v>100</v>
       </c>
       <c r="P194" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q194">
         <v>2.4</v>
@@ -41245,7 +41251,7 @@
         <v>0.33</v>
       </c>
       <c r="AP194">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="AQ194">
         <v>0.75</v>
@@ -41785,7 +41791,7 @@
         <v>100</v>
       </c>
       <c r="P197" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q197">
         <v>4.75</v>
@@ -41991,7 +41997,7 @@
         <v>100</v>
       </c>
       <c r="P198" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q198">
         <v>3.1</v>
@@ -42481,7 +42487,7 @@
         <v>1.17</v>
       </c>
       <c r="AP200">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AQ200">
         <v>1.4</v>
@@ -43102,7 +43108,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ203">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="AR203">
         <v>1.59</v>
@@ -44875,7 +44881,7 @@
         <v>100</v>
       </c>
       <c r="P212" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45081,7 +45087,7 @@
         <v>102</v>
       </c>
       <c r="P213" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -46523,7 +46529,7 @@
         <v>226</v>
       </c>
       <c r="P220" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -46810,7 +46816,7 @@
         <v>2</v>
       </c>
       <c r="AQ221">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AR221">
         <v>1.96</v>
@@ -47013,7 +47019,7 @@
         <v>0.57</v>
       </c>
       <c r="AP222">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="AQ222">
         <v>0.5</v>
@@ -47141,7 +47147,7 @@
         <v>188</v>
       </c>
       <c r="P223" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -48171,7 +48177,7 @@
         <v>232</v>
       </c>
       <c r="P228" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q228">
         <v>4.33</v>
@@ -48664,7 +48670,7 @@
         <v>2</v>
       </c>
       <c r="AQ230">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="AR230">
         <v>1.76</v>
@@ -48789,7 +48795,7 @@
         <v>156</v>
       </c>
       <c r="P231" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q231">
         <v>3.75</v>
@@ -48867,7 +48873,7 @@
         <v>0.86</v>
       </c>
       <c r="AP231">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AQ231">
         <v>1.3</v>
@@ -49407,7 +49413,7 @@
         <v>236</v>
       </c>
       <c r="P234" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q234">
         <v>2.75</v>
@@ -49819,7 +49825,7 @@
         <v>100</v>
       </c>
       <c r="P236" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q236">
         <v>2.25</v>
@@ -50437,7 +50443,7 @@
         <v>100</v>
       </c>
       <c r="P239" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q239">
         <v>3.6</v>
@@ -51055,7 +51061,7 @@
         <v>239</v>
       </c>
       <c r="P242" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q242">
         <v>2.95</v>
@@ -51136,7 +51142,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ242">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AR242">
         <v>1.31</v>
@@ -51342,7 +51348,7 @@
         <v>2</v>
       </c>
       <c r="AQ243">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AR243">
         <v>1.37</v>
@@ -51467,7 +51473,7 @@
         <v>100</v>
       </c>
       <c r="P244" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q244">
         <v>2.4</v>
@@ -52085,7 +52091,7 @@
         <v>241</v>
       </c>
       <c r="P247" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q247">
         <v>2.2</v>
@@ -52291,7 +52297,7 @@
         <v>242</v>
       </c>
       <c r="P248" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q248">
         <v>2.63</v>
@@ -52909,7 +52915,7 @@
         <v>179</v>
       </c>
       <c r="P251" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q251">
         <v>2.6</v>
@@ -53115,7 +53121,7 @@
         <v>100</v>
       </c>
       <c r="P252" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q252">
         <v>2.88</v>
@@ -53939,7 +53945,7 @@
         <v>100</v>
       </c>
       <c r="P256" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q256">
         <v>3.2</v>
@@ -54351,7 +54357,7 @@
         <v>245</v>
       </c>
       <c r="P258" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q258">
         <v>2.88</v>
@@ -54763,7 +54769,7 @@
         <v>100</v>
       </c>
       <c r="P260" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q260">
         <v>2.75</v>
@@ -55175,7 +55181,7 @@
         <v>100</v>
       </c>
       <c r="P262" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q262">
         <v>2</v>
@@ -55381,7 +55387,7 @@
         <v>100</v>
       </c>
       <c r="P263" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -55793,7 +55799,7 @@
         <v>245</v>
       </c>
       <c r="P265" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -56205,7 +56211,7 @@
         <v>100</v>
       </c>
       <c r="P267" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -56617,7 +56623,7 @@
         <v>246</v>
       </c>
       <c r="P269" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q269">
         <v>4.75</v>
@@ -56823,7 +56829,7 @@
         <v>246</v>
       </c>
       <c r="P270" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -57029,7 +57035,7 @@
         <v>186</v>
       </c>
       <c r="P271" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q271">
         <v>3.2</v>
@@ -57235,7 +57241,7 @@
         <v>186</v>
       </c>
       <c r="P272" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q272">
         <v>2.75</v>
@@ -57441,7 +57447,7 @@
         <v>247</v>
       </c>
       <c r="P273" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q273">
         <v>2.4</v>
@@ -57647,7 +57653,7 @@
         <v>247</v>
       </c>
       <c r="P274" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q274">
         <v>2.63</v>
@@ -58265,7 +58271,7 @@
         <v>248</v>
       </c>
       <c r="P277" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q277">
         <v>2.1</v>
@@ -58471,7 +58477,7 @@
         <v>248</v>
       </c>
       <c r="P278" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q278">
         <v>2.3</v>
@@ -59246,6 +59252,830 @@
       </c>
       <c r="BP281">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="282" spans="1:68">
+      <c r="A282" s="1">
+        <v>281</v>
+      </c>
+      <c r="B282">
+        <v>7940202</v>
+      </c>
+      <c r="C282" t="s">
+        <v>68</v>
+      </c>
+      <c r="D282" t="s">
+        <v>69</v>
+      </c>
+      <c r="E282" s="2">
+        <v>45852.88541666666</v>
+      </c>
+      <c r="F282">
+        <v>1</v>
+      </c>
+      <c r="G282" t="s">
+        <v>89</v>
+      </c>
+      <c r="H282" t="s">
+        <v>71</v>
+      </c>
+      <c r="I282">
+        <v>2</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>2</v>
+      </c>
+      <c r="L282">
+        <v>2</v>
+      </c>
+      <c r="M282">
+        <v>1</v>
+      </c>
+      <c r="N282">
+        <v>3</v>
+      </c>
+      <c r="O282" t="s">
+        <v>249</v>
+      </c>
+      <c r="P282" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q282">
+        <v>3.2</v>
+      </c>
+      <c r="R282">
+        <v>1.8</v>
+      </c>
+      <c r="S282">
+        <v>5</v>
+      </c>
+      <c r="T282">
+        <v>1.73</v>
+      </c>
+      <c r="U282">
+        <v>2</v>
+      </c>
+      <c r="V282">
+        <v>5</v>
+      </c>
+      <c r="W282">
+        <v>1.17</v>
+      </c>
+      <c r="X282">
+        <v>17</v>
+      </c>
+      <c r="Y282">
+        <v>1.03</v>
+      </c>
+      <c r="Z282">
+        <v>2.3</v>
+      </c>
+      <c r="AA282">
+        <v>2.7</v>
+      </c>
+      <c r="AB282">
+        <v>4.1</v>
+      </c>
+      <c r="AC282">
+        <v>1.17</v>
+      </c>
+      <c r="AD282">
+        <v>5</v>
+      </c>
+      <c r="AE282">
+        <v>1.81</v>
+      </c>
+      <c r="AF282">
+        <v>2.07</v>
+      </c>
+      <c r="AG282">
+        <v>3.5</v>
+      </c>
+      <c r="AH282">
+        <v>1.3</v>
+      </c>
+      <c r="AI282">
+        <v>2.63</v>
+      </c>
+      <c r="AJ282">
+        <v>1.44</v>
+      </c>
+      <c r="AK282">
+        <v>1.24</v>
+      </c>
+      <c r="AL282">
+        <v>1.44</v>
+      </c>
+      <c r="AM282">
+        <v>1.61</v>
+      </c>
+      <c r="AN282">
+        <v>0.88</v>
+      </c>
+      <c r="AO282">
+        <v>1.44</v>
+      </c>
+      <c r="AP282">
+        <v>1.3</v>
+      </c>
+      <c r="AQ282">
+        <v>1.18</v>
+      </c>
+      <c r="AR282">
+        <v>1.39</v>
+      </c>
+      <c r="AS282">
+        <v>1.48</v>
+      </c>
+      <c r="AT282">
+        <v>2.87</v>
+      </c>
+      <c r="AU282">
+        <v>5</v>
+      </c>
+      <c r="AV282">
+        <v>5</v>
+      </c>
+      <c r="AW282">
+        <v>3</v>
+      </c>
+      <c r="AX282">
+        <v>7</v>
+      </c>
+      <c r="AY282">
+        <v>8</v>
+      </c>
+      <c r="AZ282">
+        <v>12</v>
+      </c>
+      <c r="BA282">
+        <v>2</v>
+      </c>
+      <c r="BB282">
+        <v>4</v>
+      </c>
+      <c r="BC282">
+        <v>6</v>
+      </c>
+      <c r="BD282">
+        <v>1.57</v>
+      </c>
+      <c r="BE282">
+        <v>6.25</v>
+      </c>
+      <c r="BF282">
+        <v>3</v>
+      </c>
+      <c r="BG282">
+        <v>1.43</v>
+      </c>
+      <c r="BH282">
+        <v>2.5</v>
+      </c>
+      <c r="BI282">
+        <v>1.8</v>
+      </c>
+      <c r="BJ282">
+        <v>1.85</v>
+      </c>
+      <c r="BK282">
+        <v>2.4</v>
+      </c>
+      <c r="BL282">
+        <v>1.47</v>
+      </c>
+      <c r="BM282">
+        <v>3.4</v>
+      </c>
+      <c r="BN282">
+        <v>1.26</v>
+      </c>
+      <c r="BO282">
+        <v>3.9</v>
+      </c>
+      <c r="BP282">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:68">
+      <c r="A283" s="1">
+        <v>282</v>
+      </c>
+      <c r="B283">
+        <v>7940205</v>
+      </c>
+      <c r="C283" t="s">
+        <v>68</v>
+      </c>
+      <c r="D283" t="s">
+        <v>69</v>
+      </c>
+      <c r="E283" s="2">
+        <v>45852.88541666666</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+      <c r="G283" t="s">
+        <v>94</v>
+      </c>
+      <c r="H283" t="s">
+        <v>80</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>1</v>
+      </c>
+      <c r="L283">
+        <v>1</v>
+      </c>
+      <c r="M283">
+        <v>0</v>
+      </c>
+      <c r="N283">
+        <v>1</v>
+      </c>
+      <c r="O283" t="s">
+        <v>102</v>
+      </c>
+      <c r="P283" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q283">
+        <v>3.5</v>
+      </c>
+      <c r="R283">
+        <v>1.95</v>
+      </c>
+      <c r="S283">
+        <v>3.6</v>
+      </c>
+      <c r="T283">
+        <v>1.53</v>
+      </c>
+      <c r="U283">
+        <v>2.38</v>
+      </c>
+      <c r="V283">
+        <v>3.75</v>
+      </c>
+      <c r="W283">
+        <v>1.25</v>
+      </c>
+      <c r="X283">
+        <v>11</v>
+      </c>
+      <c r="Y283">
+        <v>1.05</v>
+      </c>
+      <c r="Z283">
+        <v>2.75</v>
+      </c>
+      <c r="AA283">
+        <v>2.9</v>
+      </c>
+      <c r="AB283">
+        <v>2.9</v>
+      </c>
+      <c r="AC283">
+        <v>1.11</v>
+      </c>
+      <c r="AD283">
+        <v>6.25</v>
+      </c>
+      <c r="AE283">
+        <v>1.48</v>
+      </c>
+      <c r="AF283">
+        <v>2.43</v>
+      </c>
+      <c r="AG283">
+        <v>2.6</v>
+      </c>
+      <c r="AH283">
+        <v>1.48</v>
+      </c>
+      <c r="AI283">
+        <v>2.05</v>
+      </c>
+      <c r="AJ283">
+        <v>1.7</v>
+      </c>
+      <c r="AK283">
+        <v>1.41</v>
+      </c>
+      <c r="AL283">
+        <v>1.37</v>
+      </c>
+      <c r="AM283">
+        <v>1.46</v>
+      </c>
+      <c r="AN283">
+        <v>1.44</v>
+      </c>
+      <c r="AO283">
+        <v>0.7</v>
+      </c>
+      <c r="AP283">
+        <v>1.73</v>
+      </c>
+      <c r="AQ283">
+        <v>0.58</v>
+      </c>
+      <c r="AR283">
+        <v>1.84</v>
+      </c>
+      <c r="AS283">
+        <v>1.33</v>
+      </c>
+      <c r="AT283">
+        <v>3.17</v>
+      </c>
+      <c r="AU283">
+        <v>9</v>
+      </c>
+      <c r="AV283">
+        <v>2</v>
+      </c>
+      <c r="AW283">
+        <v>8</v>
+      </c>
+      <c r="AX283">
+        <v>1</v>
+      </c>
+      <c r="AY283">
+        <v>17</v>
+      </c>
+      <c r="AZ283">
+        <v>3</v>
+      </c>
+      <c r="BA283">
+        <v>4</v>
+      </c>
+      <c r="BB283">
+        <v>1</v>
+      </c>
+      <c r="BC283">
+        <v>5</v>
+      </c>
+      <c r="BD283">
+        <v>1.52</v>
+      </c>
+      <c r="BE283">
+        <v>6.75</v>
+      </c>
+      <c r="BF283">
+        <v>3.1</v>
+      </c>
+      <c r="BG283">
+        <v>1.32</v>
+      </c>
+      <c r="BH283">
+        <v>3</v>
+      </c>
+      <c r="BI283">
+        <v>1.6</v>
+      </c>
+      <c r="BJ283">
+        <v>2.1</v>
+      </c>
+      <c r="BK283">
+        <v>2.05</v>
+      </c>
+      <c r="BL283">
+        <v>1.63</v>
+      </c>
+      <c r="BM283">
+        <v>2.8</v>
+      </c>
+      <c r="BN283">
+        <v>1.36</v>
+      </c>
+      <c r="BO283">
+        <v>4</v>
+      </c>
+      <c r="BP283">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="284" spans="1:68">
+      <c r="A284" s="1">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>7820562</v>
+      </c>
+      <c r="C284" t="s">
+        <v>68</v>
+      </c>
+      <c r="D284" t="s">
+        <v>69</v>
+      </c>
+      <c r="E284" s="2">
+        <v>45852.88541666666</v>
+      </c>
+      <c r="F284">
+        <v>1</v>
+      </c>
+      <c r="G284" t="s">
+        <v>89</v>
+      </c>
+      <c r="H284" t="s">
+        <v>71</v>
+      </c>
+      <c r="I284">
+        <v>2</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284">
+        <v>2</v>
+      </c>
+      <c r="L284">
+        <v>2</v>
+      </c>
+      <c r="M284">
+        <v>1</v>
+      </c>
+      <c r="N284">
+        <v>3</v>
+      </c>
+      <c r="O284" t="s">
+        <v>249</v>
+      </c>
+      <c r="P284" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q284">
+        <v>3.1</v>
+      </c>
+      <c r="R284">
+        <v>1.83</v>
+      </c>
+      <c r="S284">
+        <v>5</v>
+      </c>
+      <c r="T284">
+        <v>1.67</v>
+      </c>
+      <c r="U284">
+        <v>2.1</v>
+      </c>
+      <c r="V284">
+        <v>4.33</v>
+      </c>
+      <c r="W284">
+        <v>1.2</v>
+      </c>
+      <c r="X284">
+        <v>15</v>
+      </c>
+      <c r="Y284">
+        <v>1.03</v>
+      </c>
+      <c r="Z284">
+        <v>2.2</v>
+      </c>
+      <c r="AA284">
+        <v>2.8</v>
+      </c>
+      <c r="AB284">
+        <v>4.1</v>
+      </c>
+      <c r="AC284">
+        <v>1.14</v>
+      </c>
+      <c r="AD284">
+        <v>5.5</v>
+      </c>
+      <c r="AE284">
+        <v>1.58</v>
+      </c>
+      <c r="AF284">
+        <v>2.18</v>
+      </c>
+      <c r="AG284">
+        <v>3.1</v>
+      </c>
+      <c r="AH284">
+        <v>1.36</v>
+      </c>
+      <c r="AI284">
+        <v>2.5</v>
+      </c>
+      <c r="AJ284">
+        <v>1.5</v>
+      </c>
+      <c r="AK284">
+        <v>1.25</v>
+      </c>
+      <c r="AL284">
+        <v>1.39</v>
+      </c>
+      <c r="AM284">
+        <v>1.66</v>
+      </c>
+      <c r="AN284">
+        <v>0.88</v>
+      </c>
+      <c r="AO284">
+        <v>1.44</v>
+      </c>
+      <c r="AP284">
+        <v>1.3</v>
+      </c>
+      <c r="AQ284">
+        <v>1.18</v>
+      </c>
+      <c r="AR284">
+        <v>1.39</v>
+      </c>
+      <c r="AS284">
+        <v>1.48</v>
+      </c>
+      <c r="AT284">
+        <v>2.87</v>
+      </c>
+      <c r="AU284">
+        <v>7</v>
+      </c>
+      <c r="AV284">
+        <v>6</v>
+      </c>
+      <c r="AW284">
+        <v>3</v>
+      </c>
+      <c r="AX284">
+        <v>11</v>
+      </c>
+      <c r="AY284">
+        <v>10</v>
+      </c>
+      <c r="AZ284">
+        <v>17</v>
+      </c>
+      <c r="BA284">
+        <v>2</v>
+      </c>
+      <c r="BB284">
+        <v>4</v>
+      </c>
+      <c r="BC284">
+        <v>6</v>
+      </c>
+      <c r="BD284">
+        <v>1.55</v>
+      </c>
+      <c r="BE284">
+        <v>6.25</v>
+      </c>
+      <c r="BF284">
+        <v>3</v>
+      </c>
+      <c r="BG284">
+        <v>1.43</v>
+      </c>
+      <c r="BH284">
+        <v>2.5</v>
+      </c>
+      <c r="BI284">
+        <v>1.8</v>
+      </c>
+      <c r="BJ284">
+        <v>1.85</v>
+      </c>
+      <c r="BK284">
+        <v>2.4</v>
+      </c>
+      <c r="BL284">
+        <v>1.47</v>
+      </c>
+      <c r="BM284">
+        <v>3.4</v>
+      </c>
+      <c r="BN284">
+        <v>1.26</v>
+      </c>
+      <c r="BO284">
+        <v>3.8</v>
+      </c>
+      <c r="BP284">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="285" spans="1:68">
+      <c r="A285" s="1">
+        <v>284</v>
+      </c>
+      <c r="B285">
+        <v>7820556</v>
+      </c>
+      <c r="C285" t="s">
+        <v>68</v>
+      </c>
+      <c r="D285" t="s">
+        <v>69</v>
+      </c>
+      <c r="E285" s="2">
+        <v>45852.88541666666</v>
+      </c>
+      <c r="F285">
+        <v>1</v>
+      </c>
+      <c r="G285" t="s">
+        <v>94</v>
+      </c>
+      <c r="H285" t="s">
+        <v>80</v>
+      </c>
+      <c r="I285">
+        <v>1</v>
+      </c>
+      <c r="J285">
+        <v>0</v>
+      </c>
+      <c r="K285">
+        <v>1</v>
+      </c>
+      <c r="L285">
+        <v>1</v>
+      </c>
+      <c r="M285">
+        <v>0</v>
+      </c>
+      <c r="N285">
+        <v>1</v>
+      </c>
+      <c r="O285" t="s">
+        <v>102</v>
+      </c>
+      <c r="P285" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q285">
+        <v>3.4</v>
+      </c>
+      <c r="R285">
+        <v>1.95</v>
+      </c>
+      <c r="S285">
+        <v>3.6</v>
+      </c>
+      <c r="T285">
+        <v>1.53</v>
+      </c>
+      <c r="U285">
+        <v>2.38</v>
+      </c>
+      <c r="V285">
+        <v>3.5</v>
+      </c>
+      <c r="W285">
+        <v>1.29</v>
+      </c>
+      <c r="X285">
+        <v>11</v>
+      </c>
+      <c r="Y285">
+        <v>1.05</v>
+      </c>
+      <c r="Z285">
+        <v>2.63</v>
+      </c>
+      <c r="AA285">
+        <v>2.9</v>
+      </c>
+      <c r="AB285">
+        <v>3</v>
+      </c>
+      <c r="AC285">
+        <v>1.1</v>
+      </c>
+      <c r="AD285">
+        <v>6.5</v>
+      </c>
+      <c r="AE285">
+        <v>1.48</v>
+      </c>
+      <c r="AF285">
+        <v>2.43</v>
+      </c>
+      <c r="AG285">
+        <v>2.5</v>
+      </c>
+      <c r="AH285">
+        <v>1.5</v>
+      </c>
+      <c r="AI285">
+        <v>2</v>
+      </c>
+      <c r="AJ285">
+        <v>1.75</v>
+      </c>
+      <c r="AK285">
+        <v>1.41</v>
+      </c>
+      <c r="AL285">
+        <v>1.36</v>
+      </c>
+      <c r="AM285">
+        <v>1.47</v>
+      </c>
+      <c r="AN285">
+        <v>1.44</v>
+      </c>
+      <c r="AO285">
+        <v>0.7</v>
+      </c>
+      <c r="AP285">
+        <v>1.73</v>
+      </c>
+      <c r="AQ285">
+        <v>0.58</v>
+      </c>
+      <c r="AR285">
+        <v>1.84</v>
+      </c>
+      <c r="AS285">
+        <v>1.33</v>
+      </c>
+      <c r="AT285">
+        <v>3.17</v>
+      </c>
+      <c r="AU285">
+        <v>10</v>
+      </c>
+      <c r="AV285">
+        <v>2</v>
+      </c>
+      <c r="AW285">
+        <v>9</v>
+      </c>
+      <c r="AX285">
+        <v>6</v>
+      </c>
+      <c r="AY285">
+        <v>19</v>
+      </c>
+      <c r="AZ285">
+        <v>8</v>
+      </c>
+      <c r="BA285">
+        <v>4</v>
+      </c>
+      <c r="BB285">
+        <v>1</v>
+      </c>
+      <c r="BC285">
+        <v>5</v>
+      </c>
+      <c r="BD285">
+        <v>1.44</v>
+      </c>
+      <c r="BE285">
+        <v>6.75</v>
+      </c>
+      <c r="BF285">
+        <v>3.5</v>
+      </c>
+      <c r="BG285">
+        <v>1.38</v>
+      </c>
+      <c r="BH285">
+        <v>2.7</v>
+      </c>
+      <c r="BI285">
+        <v>1.71</v>
+      </c>
+      <c r="BJ285">
+        <v>1.95</v>
+      </c>
+      <c r="BK285">
+        <v>2.25</v>
+      </c>
+      <c r="BL285">
+        <v>1.53</v>
+      </c>
+      <c r="BM285">
+        <v>3.1</v>
+      </c>
+      <c r="BN285">
+        <v>1.3</v>
+      </c>
+      <c r="BO285">
+        <v>3.7</v>
+      </c>
+      <c r="BP285">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
